--- a/data/PTR.MI.xlsx
+++ b/data/PTR.MI.xlsx
@@ -42194,7 +42194,7 @@
         <v>3300</v>
       </c>
       <c r="C1819" t="n">
-        <v>2.59999990463257</v>
+        <v>2.64000010490417</v>
       </c>
       <c r="D1819" t="n">
         <v>2.59999990463257</v>
@@ -42206,6 +42206,29 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G1819" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1820">
+      <c r="A1820" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B1820" t="n">
+        <v>3190</v>
+      </c>
+      <c r="C1820" t="n">
+        <v>2.72000002861023</v>
+      </c>
+      <c r="D1820" t="n">
+        <v>2.59999990463257</v>
+      </c>
+      <c r="E1820" t="n">
+        <v>2.64000010490417</v>
+      </c>
+      <c r="F1820" t="n">
+        <v>2.72000002861023</v>
+      </c>
+      <c r="G1820" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/PTR.MI.xlsx
+++ b/data/PTR.MI.xlsx
@@ -42232,6 +42232,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1821">
+      <c r="A1821" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B1821" t="n">
+        <v>15768</v>
+      </c>
+      <c r="C1821" t="n">
+        <v>2.85999989509583</v>
+      </c>
+      <c r="D1821" t="n">
+        <v>2.6800000667572</v>
+      </c>
+      <c r="E1821" t="n">
+        <v>2.6800000667572</v>
+      </c>
+      <c r="F1821" t="n">
+        <v>2.77999997138977</v>
+      </c>
+      <c r="G1821" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/PTR.MI.xlsx
+++ b/data/PTR.MI.xlsx
@@ -42255,6 +42255,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1822">
+      <c r="A1822" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B1822" t="n">
+        <v>8835</v>
+      </c>
+      <c r="C1822" t="n">
+        <v>2.85999989509583</v>
+      </c>
+      <c r="D1822" t="n">
+        <v>2.6800000667572</v>
+      </c>
+      <c r="E1822" t="n">
+        <v>2.74000000953674</v>
+      </c>
+      <c r="F1822" t="n">
+        <v>2.83999991416931</v>
+      </c>
+      <c r="G1822" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/PTR.MI.xlsx
+++ b/data/PTR.MI.xlsx
@@ -42278,6 +42278,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1823">
+      <c r="A1823" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B1823" t="n">
+        <v>23379</v>
+      </c>
+      <c r="C1823" t="n">
+        <v>2.77999997138977</v>
+      </c>
+      <c r="D1823" t="n">
+        <v>2.57999992370605</v>
+      </c>
+      <c r="E1823" t="n">
+        <v>2.77999997138977</v>
+      </c>
+      <c r="F1823" t="n">
+        <v>2.61999988555908</v>
+      </c>
+      <c r="G1823" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/PTR.MI.xlsx
+++ b/data/PTR.MI.xlsx
@@ -42119,22 +42119,22 @@
     </row>
     <row r="1816">
       <c r="A1816" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B1816" t="n">
-        <v>700</v>
+        <v>13569</v>
       </c>
       <c r="C1816" t="n">
-        <v>2.59999990463257</v>
+        <v>2.64000010490417</v>
       </c>
       <c r="D1816" t="n">
-        <v>2.55999994277954</v>
+        <v>2.48000001907349</v>
       </c>
       <c r="E1816" t="n">
-        <v>2.55999994277954</v>
+        <v>2.48000001907349</v>
       </c>
       <c r="F1816" t="n">
-        <v>2.59999990463257</v>
+        <v>2.61999988555908</v>
       </c>
       <c r="G1816" t="s">
         <v>7</v>
@@ -42142,10 +42142,10 @@
     </row>
     <row r="1817">
       <c r="A1817" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B1817" t="n">
-        <v>1650</v>
+        <v>700</v>
       </c>
       <c r="C1817" t="n">
         <v>2.59999990463257</v>
@@ -42165,19 +42165,19 @@
     </row>
     <row r="1818">
       <c r="A1818" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B1818" t="n">
-        <v>800</v>
+        <v>1650</v>
       </c>
       <c r="C1818" t="n">
         <v>2.59999990463257</v>
       </c>
       <c r="D1818" t="n">
-        <v>2.53999996185303</v>
+        <v>2.55999994277954</v>
       </c>
       <c r="E1818" t="n">
-        <v>2.53999996185303</v>
+        <v>2.55999994277954</v>
       </c>
       <c r="F1818" t="n">
         <v>2.59999990463257</v>
@@ -42188,22 +42188,22 @@
     </row>
     <row r="1819">
       <c r="A1819" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B1819" t="n">
-        <v>3300</v>
+        <v>800</v>
       </c>
       <c r="C1819" t="n">
-        <v>2.64000010490417</v>
+        <v>2.59999990463257</v>
       </c>
       <c r="D1819" t="n">
+        <v>2.53999996185303</v>
+      </c>
+      <c r="E1819" t="n">
+        <v>2.53999996185303</v>
+      </c>
+      <c r="F1819" t="n">
         <v>2.59999990463257</v>
-      </c>
-      <c r="E1819" t="n">
-        <v>2.59999990463257</v>
-      </c>
-      <c r="F1819" t="n">
-        <v>2.64000010490417</v>
       </c>
       <c r="G1819" t="s">
         <v>7</v>
@@ -42211,22 +42211,22 @@
     </row>
     <row r="1820">
       <c r="A1820" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B1820" t="n">
-        <v>3190</v>
+        <v>3300</v>
       </c>
       <c r="C1820" t="n">
-        <v>2.72000002861023</v>
+        <v>2.64000010490417</v>
       </c>
       <c r="D1820" t="n">
         <v>2.59999990463257</v>
       </c>
       <c r="E1820" t="n">
+        <v>2.59999990463257</v>
+      </c>
+      <c r="F1820" t="n">
         <v>2.64000010490417</v>
-      </c>
-      <c r="F1820" t="n">
-        <v>2.72000002861023</v>
       </c>
       <c r="G1820" t="s">
         <v>7</v>
@@ -42234,22 +42234,22 @@
     </row>
     <row r="1821">
       <c r="A1821" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B1821" t="n">
-        <v>15768</v>
+        <v>3190</v>
       </c>
       <c r="C1821" t="n">
-        <v>2.85999989509583</v>
+        <v>2.72000002861023</v>
       </c>
       <c r="D1821" t="n">
-        <v>2.6800000667572</v>
+        <v>2.59999990463257</v>
       </c>
       <c r="E1821" t="n">
-        <v>2.6800000667572</v>
+        <v>2.64000010490417</v>
       </c>
       <c r="F1821" t="n">
-        <v>2.77999997138977</v>
+        <v>2.72000002861023</v>
       </c>
       <c r="G1821" t="s">
         <v>7</v>
@@ -42257,10 +42257,10 @@
     </row>
     <row r="1822">
       <c r="A1822" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B1822" t="n">
-        <v>8835</v>
+        <v>15768</v>
       </c>
       <c r="C1822" t="n">
         <v>2.85999989509583</v>
@@ -42269,10 +42269,10 @@
         <v>2.6800000667572</v>
       </c>
       <c r="E1822" t="n">
-        <v>2.74000000953674</v>
+        <v>2.6800000667572</v>
       </c>
       <c r="F1822" t="n">
-        <v>2.83999991416931</v>
+        <v>2.77999997138977</v>
       </c>
       <c r="G1822" t="s">
         <v>7</v>
@@ -42280,24 +42280,47 @@
     </row>
     <row r="1823">
       <c r="A1823" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46281.2916666667</v>
       </c>
       <c r="B1823" t="n">
-        <v>23379</v>
+        <v>8835</v>
       </c>
       <c r="C1823" t="n">
-        <v>2.77999997138977</v>
+        <v>2.85999989509583</v>
       </c>
       <c r="D1823" t="n">
-        <v>2.57999992370605</v>
+        <v>2.6800000667572</v>
       </c>
       <c r="E1823" t="n">
-        <v>2.77999997138977</v>
+        <v>2.74000000953674</v>
       </c>
       <c r="F1823" t="n">
+        <v>2.83999991416931</v>
+      </c>
+      <c r="G1823" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1824">
+      <c r="A1824" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B1824" t="n">
+        <v>4594</v>
+      </c>
+      <c r="C1824" t="n">
+        <v>2.70000004768372</v>
+      </c>
+      <c r="D1824" t="n">
         <v>2.61999988555908</v>
       </c>
-      <c r="G1823" t="s">
+      <c r="E1824" t="n">
+        <v>2.66000008583069</v>
+      </c>
+      <c r="F1824" t="n">
+        <v>2.6800000667572</v>
+      </c>
+      <c r="G1824" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/PTR.MI.xlsx
+++ b/data/PTR.MI.xlsx
@@ -525,7 +525,7 @@
         <v>3.69250011444092</v>
       </c>
       <c r="G6" t="n">
-        <v>3.2049388885498</v>
+        <v>3.20493865013123</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>3.56850004196167</v>
       </c>
       <c r="G7" t="n">
-        <v>3.0973117351532</v>
+        <v>3.09731149673462</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>3.43199992179871</v>
       </c>
       <c r="G10" t="n">
-        <v>2.97883534431458</v>
+        <v>2.978835105896</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G12" t="n">
-        <v>3.08125448226929</v>
+        <v>3.08125424385071</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>3.59400010108948</v>
       </c>
       <c r="G13" t="n">
-        <v>3.11944484710693</v>
+        <v>3.11944460868835</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G14" t="n">
-        <v>3.12465238571167</v>
+        <v>3.12465262413025</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G15" t="n">
-        <v>3.14201164245605</v>
+        <v>3.14201140403748</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G16" t="n">
-        <v>3.14201164245605</v>
+        <v>3.14201140403748</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G17" t="n">
-        <v>3.0899338722229</v>
+        <v>3.08993411064148</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G18" t="n">
-        <v>3.14201164245605</v>
+        <v>3.14201140403748</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G20" t="n">
-        <v>3.12465238571167</v>
+        <v>3.12465262413025</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G22" t="n">
-        <v>3.09861373901367</v>
+        <v>3.09861350059509</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G29" t="n">
-        <v>3.08125448226929</v>
+        <v>3.08125424385071</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G30" t="n">
-        <v>3.0899338722229</v>
+        <v>3.08993411064148</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G31" t="n">
-        <v>3.0899338722229</v>
+        <v>3.08993411064148</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G34" t="n">
-        <v>3.10729336738586</v>
+        <v>3.10729312896729</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>3.5</v>
       </c>
       <c r="G35" t="n">
-        <v>3.0378565788269</v>
+        <v>3.03785634040833</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G37" t="n">
-        <v>3.14201164245605</v>
+        <v>3.14201140403748</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G38" t="n">
-        <v>3.19408941268921</v>
+        <v>3.19408917427063</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G41" t="n">
-        <v>3.42843818664551</v>
+        <v>3.42843794822693</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>3.71499991416931</v>
       </c>
       <c r="G46" t="n">
-        <v>3.22446751594543</v>
+        <v>3.22446775436401</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>3.64499998092651</v>
       </c>
       <c r="G47" t="n">
-        <v>3.16371059417725</v>
+        <v>3.16371035575867</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>3.71499991416931</v>
       </c>
       <c r="G50" t="n">
-        <v>3.22446751594543</v>
+        <v>3.22446775436401</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>3.66499996185303</v>
       </c>
       <c r="G59" t="n">
-        <v>3.18106937408447</v>
+        <v>3.18106961250305</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>3.66499996185303</v>
       </c>
       <c r="G61" t="n">
-        <v>3.18106937408447</v>
+        <v>3.18106961250305</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G63" t="n">
-        <v>3.14201164245605</v>
+        <v>3.14201140403748</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>3.5550000667572</v>
       </c>
       <c r="G64" t="n">
-        <v>3.08559393882751</v>
+        <v>3.08559417724609</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>3.5550000667572</v>
       </c>
       <c r="G65" t="n">
-        <v>3.08559393882751</v>
+        <v>3.08559417724609</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G66" t="n">
-        <v>3.09861373901367</v>
+        <v>3.09861350059509</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>3.63499999046326</v>
       </c>
       <c r="G67" t="n">
-        <v>3.15503096580505</v>
+        <v>3.15503120422363</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G68" t="n">
-        <v>3.12465238571167</v>
+        <v>3.12465262413025</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G69" t="n">
-        <v>3.12465238571167</v>
+        <v>3.12465262413025</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G72" t="n">
-        <v>3.12465238571167</v>
+        <v>3.12465262413025</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G73" t="n">
-        <v>3.08125448226929</v>
+        <v>3.08125424385071</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G74" t="n">
-        <v>3.08125448226929</v>
+        <v>3.08125424385071</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G77" t="n">
-        <v>3.08125448226929</v>
+        <v>3.08125424385071</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G78" t="n">
-        <v>3.12465238571167</v>
+        <v>3.12465262413025</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G79" t="n">
-        <v>3.14201164245605</v>
+        <v>3.14201140403748</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G82" t="n">
-        <v>3.14201164245605</v>
+        <v>3.14201140403748</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G87" t="n">
-        <v>3.37636065483093</v>
+        <v>3.37636089324951</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G88" t="n">
-        <v>3.42843818664551</v>
+        <v>3.42843794822693</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G89" t="n">
-        <v>3.42843818664551</v>
+        <v>3.42843794822693</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>4</v>
       </c>
       <c r="G92" t="n">
-        <v>3.47183585166931</v>
+        <v>3.47183609008789</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G97" t="n">
-        <v>3.42843818664551</v>
+        <v>3.42843794822693</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>4</v>
       </c>
       <c r="G103" t="n">
-        <v>3.47183585166931</v>
+        <v>3.47183609008789</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>3.9449999332428</v>
       </c>
       <c r="G104" t="n">
-        <v>3.42409801483154</v>
+        <v>3.42409825325012</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>4</v>
       </c>
       <c r="G105" t="n">
-        <v>3.47183585166931</v>
+        <v>3.47183609008789</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>4.03499984741211</v>
       </c>
       <c r="G106" t="n">
-        <v>3.50221419334412</v>
+        <v>3.50221467018127</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G110" t="n">
-        <v>3.64542746543884</v>
+        <v>3.64542722702026</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G111" t="n">
-        <v>3.64542746543884</v>
+        <v>3.64542722702026</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>4.5</v>
       </c>
       <c r="G113" t="n">
-        <v>3.9058153629303</v>
+        <v>3.90581560134888</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>4.5</v>
       </c>
       <c r="G114" t="n">
-        <v>3.9058153629303</v>
+        <v>3.90581560134888</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G116" t="n">
-        <v>3.86241722106934</v>
+        <v>3.86241793632507</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G117" t="n">
-        <v>4.00997066497803</v>
+        <v>4.00997018814087</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G120" t="n">
-        <v>3.86241722106934</v>
+        <v>3.86241793632507</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G121" t="n">
-        <v>3.92317461967468</v>
+        <v>3.92317485809326</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G123" t="n">
-        <v>3.88845634460449</v>
+        <v>3.88845610618591</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>4.88500022888184</v>
       </c>
       <c r="G127" t="n">
-        <v>4.23997974395752</v>
+        <v>4.23998022079468</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G128" t="n">
-        <v>4.37451362609863</v>
+        <v>4.37451314926147</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G129" t="n">
-        <v>4.3831934928894</v>
+        <v>4.38319301605225</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>4.97499990463257</v>
       </c>
       <c r="G133" t="n">
-        <v>4.31809568405151</v>
+        <v>4.31809616088867</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G137" t="n">
-        <v>4.14016437530518</v>
+        <v>4.14016389846802</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G138" t="n">
-        <v>4.16620302200317</v>
+        <v>4.16620349884033</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G142" t="n">
-        <v>4.35715389251709</v>
+        <v>4.35715436935425</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G153" t="n">
-        <v>4.44394969940186</v>
+        <v>4.44395017623901</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G154" t="n">
-        <v>4.00129175186157</v>
+        <v>4.00129127502441</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G156" t="n">
-        <v>4.31375646591187</v>
+        <v>4.31375598907471</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G157" t="n">
-        <v>4.23564004898071</v>
+        <v>4.23564052581787</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G158" t="n">
-        <v>4.00129175186157</v>
+        <v>4.00129127502441</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G161" t="n">
-        <v>4.04468870162964</v>
+        <v>4.0446891784668</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>4.24499988555908</v>
       </c>
       <c r="G163" t="n">
-        <v>3.68448567390442</v>
+        <v>3.68448543548584</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G167" t="n">
-        <v>2.72539138793945</v>
+        <v>2.72539114952087</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G170" t="n">
-        <v>3.12465238571167</v>
+        <v>3.12465262413025</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G173" t="n">
-        <v>3.09861373901367</v>
+        <v>3.09861350059509</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G176" t="n">
-        <v>3.08125448226929</v>
+        <v>3.08125424385071</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G177" t="n">
-        <v>3.09861373901367</v>
+        <v>3.09861350059509</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G178" t="n">
-        <v>3.28956484794617</v>
+        <v>3.28956437110901</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G182" t="n">
-        <v>3.28956484794617</v>
+        <v>3.28956437110901</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G183" t="n">
-        <v>3.19408941268921</v>
+        <v>3.19408917427063</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G185" t="n">
-        <v>3.19408941268921</v>
+        <v>3.19408917427063</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G204" t="n">
-        <v>3.19408941268921</v>
+        <v>3.19408917427063</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G207" t="n">
-        <v>3.37636065483093</v>
+        <v>3.37636089324951</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G209" t="n">
-        <v>3.24616670608521</v>
+        <v>3.24616646766663</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G212" t="n">
-        <v>3.2722053527832</v>
+        <v>3.27220559120178</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G221" t="n">
-        <v>3.28956484794617</v>
+        <v>3.28956437110901</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G224" t="n">
-        <v>3.38504028320312</v>
+        <v>3.38504004478455</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G226" t="n">
-        <v>3.37636065483093</v>
+        <v>3.37636089324951</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G228" t="n">
-        <v>3.42843818664551</v>
+        <v>3.42843794822693</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G229" t="n">
-        <v>3.2722053527832</v>
+        <v>3.27220559120178</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G230" t="n">
-        <v>3.37636065483093</v>
+        <v>3.37636089324951</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G232" t="n">
-        <v>3.35032176971436</v>
+        <v>3.35032153129578</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G233" t="n">
-        <v>3.37636065483093</v>
+        <v>3.37636089324951</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G234" t="n">
-        <v>3.37636065483093</v>
+        <v>3.37636089324951</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G237" t="n">
-        <v>3.28956484794617</v>
+        <v>3.28956437110901</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G242" t="n">
-        <v>3.28956484794617</v>
+        <v>3.28956437110901</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G243" t="n">
-        <v>3.28956484794617</v>
+        <v>3.28956437110901</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G244" t="n">
-        <v>3.42843818664551</v>
+        <v>3.42843794822693</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G245" t="n">
-        <v>3.2722053527832</v>
+        <v>3.27220559120178</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G247" t="n">
-        <v>3.24616670608521</v>
+        <v>3.24616646766663</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G248" t="n">
-        <v>3.24616670608521</v>
+        <v>3.24616646766663</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G254" t="n">
-        <v>3.28956484794617</v>
+        <v>3.28956437110901</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G260" t="n">
-        <v>3.0899338722229</v>
+        <v>3.08993411064148</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G263" t="n">
-        <v>3.0899338722229</v>
+        <v>3.08993411064148</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G265" t="n">
-        <v>3.07257509231567</v>
+        <v>3.07257485389709</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7363,7 +7363,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G269" t="n">
-        <v>3.24616670608521</v>
+        <v>3.24616646766663</v>
       </c>
       <c r="H269" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G270" t="n">
-        <v>3.19408941268921</v>
+        <v>3.19408917427063</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G272" t="n">
-        <v>3.12465238571167</v>
+        <v>3.12465262413025</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G273" t="n">
-        <v>3.0204975605011</v>
+        <v>3.02049732208252</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G274" t="n">
-        <v>2.93370175361633</v>
+        <v>2.93370151519775</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G276" t="n">
-        <v>3.02917695045471</v>
+        <v>3.02917718887329</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G277" t="n">
-        <v>3.0204975605011</v>
+        <v>3.02049732208252</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G278" t="n">
-        <v>3.07257509231567</v>
+        <v>3.07257485389709</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>3.5</v>
       </c>
       <c r="G280" t="n">
-        <v>3.0378565788269</v>
+        <v>3.03785634040833</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G281" t="n">
-        <v>3.0638952255249</v>
+        <v>3.06389546394348</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G282" t="n">
-        <v>3.0638952255249</v>
+        <v>3.06389546394348</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G283" t="n">
-        <v>3.0638952255249</v>
+        <v>3.06389546394348</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>3.5</v>
       </c>
       <c r="G287" t="n">
-        <v>3.0378565788269</v>
+        <v>3.03785634040833</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G289" t="n">
-        <v>3.08125448226929</v>
+        <v>3.08125424385071</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>3.5</v>
       </c>
       <c r="G291" t="n">
-        <v>3.0378565788269</v>
+        <v>3.03785634040833</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>3.5</v>
       </c>
       <c r="G292" t="n">
-        <v>3.0378565788269</v>
+        <v>3.03785634040833</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G294" t="n">
-        <v>3.08125448226929</v>
+        <v>3.08125424385071</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>3.5</v>
       </c>
       <c r="G295" t="n">
-        <v>3.0378565788269</v>
+        <v>3.03785634040833</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G296" t="n">
-        <v>2.95106077194214</v>
+        <v>2.95106053352356</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G297" t="n">
-        <v>2.95106077194214</v>
+        <v>2.95106053352356</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G299" t="n">
-        <v>2.86426472663879</v>
+        <v>2.86426448822021</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G300" t="n">
-        <v>2.86426472663879</v>
+        <v>2.86426448822021</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G301" t="n">
-        <v>2.86426472663879</v>
+        <v>2.86426448822021</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G304" t="n">
-        <v>2.87294435501099</v>
+        <v>2.87294411659241</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>3.5</v>
       </c>
       <c r="G305" t="n">
-        <v>3.0378565788269</v>
+        <v>3.03785634040833</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G306" t="n">
-        <v>3.08125448226929</v>
+        <v>3.08125424385071</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G307" t="n">
-        <v>3.12465238571167</v>
+        <v>3.12465262413025</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G308" t="n">
-        <v>3.12465238571167</v>
+        <v>3.12465262413025</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G314" t="n">
-        <v>3.19408941268921</v>
+        <v>3.19408917427063</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G326" t="n">
-        <v>3.19408941268921</v>
+        <v>3.19408917427063</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G327" t="n">
-        <v>3.14201164245605</v>
+        <v>3.14201140403748</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G329" t="n">
-        <v>3.12465238571167</v>
+        <v>3.12465262413025</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G330" t="n">
-        <v>3.19408941268921</v>
+        <v>3.19408917427063</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>3.5</v>
       </c>
       <c r="G332" t="n">
-        <v>3.0378565788269</v>
+        <v>3.03785634040833</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G333" t="n">
-        <v>3.02917695045471</v>
+        <v>3.02917718887329</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G348" t="n">
-        <v>3.42843818664551</v>
+        <v>3.42843794822693</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9547,7 +9547,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G353" t="n">
-        <v>3.28956484794617</v>
+        <v>3.28956437110901</v>
       </c>
       <c r="H353" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G356" t="n">
-        <v>3.42843818664551</v>
+        <v>3.42843794822693</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G357" t="n">
-        <v>3.42843818664551</v>
+        <v>3.42843794822693</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G358" t="n">
-        <v>3.37636065483093</v>
+        <v>3.37636089324951</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>4</v>
       </c>
       <c r="G359" t="n">
-        <v>3.47183585166931</v>
+        <v>3.47183609008789</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>4</v>
       </c>
       <c r="G360" t="n">
-        <v>3.47183585166931</v>
+        <v>3.47183609008789</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G363" t="n">
-        <v>3.53336215019226</v>
+        <v>3.53336191177368</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9833,7 +9833,7 @@
         <v>4</v>
       </c>
       <c r="G364" t="n">
-        <v>3.51578307151794</v>
+        <v>3.51578330993652</v>
       </c>
       <c r="H364" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G366" t="n">
-        <v>3.47183609008789</v>
+        <v>3.47183585166931</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>4</v>
       </c>
       <c r="G367" t="n">
-        <v>3.51578307151794</v>
+        <v>3.51578330993652</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -9937,7 +9937,7 @@
         <v>4</v>
       </c>
       <c r="G368" t="n">
-        <v>3.51578307151794</v>
+        <v>3.51578330993652</v>
       </c>
       <c r="H368" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>4</v>
       </c>
       <c r="G369" t="n">
-        <v>3.51578307151794</v>
+        <v>3.51578330993652</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>4</v>
       </c>
       <c r="G370" t="n">
-        <v>3.51578307151794</v>
+        <v>3.51578330993652</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>4</v>
       </c>
       <c r="G371" t="n">
-        <v>3.51578307151794</v>
+        <v>3.51578330993652</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G373" t="n">
-        <v>3.77946734428406</v>
+        <v>3.77946710586548</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G374" t="n">
-        <v>3.85857224464417</v>
+        <v>3.85857176780701</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G376" t="n">
-        <v>3.82341384887695</v>
+        <v>3.82341432571411</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G377" t="n">
-        <v>3.70915102958679</v>
+        <v>3.70915126800537</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>4.5</v>
       </c>
       <c r="G381" t="n">
-        <v>3.95525598526001</v>
+        <v>3.95525622367859</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G384" t="n">
-        <v>3.77946734428406</v>
+        <v>3.77946710586548</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G385" t="n">
-        <v>3.77946734428406</v>
+        <v>3.77946710586548</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G386" t="n">
-        <v>3.64762544631958</v>
+        <v>3.64762496948242</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G387" t="n">
-        <v>3.42788887023926</v>
+        <v>3.42788863182068</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10457,7 +10457,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G388" t="n">
-        <v>3.55094075202942</v>
+        <v>3.550940990448</v>
       </c>
       <c r="H388" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G390" t="n">
-        <v>3.69157218933105</v>
+        <v>3.69157195091248</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G395" t="n">
-        <v>3.744309425354</v>
+        <v>3.74430918693542</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G396" t="n">
-        <v>3.77946734428406</v>
+        <v>3.77946710586548</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G397" t="n">
-        <v>3.82341384887695</v>
+        <v>3.82341432571411</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G398" t="n">
-        <v>3.77946734428406</v>
+        <v>3.77946710586548</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G399" t="n">
-        <v>3.70915102958679</v>
+        <v>3.70915126800537</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G402" t="n">
-        <v>3.60367798805237</v>
+        <v>3.60367774963379</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G403" t="n">
-        <v>3.68278288841248</v>
+        <v>3.6827826499939</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G408" t="n">
-        <v>3.78825640678406</v>
+        <v>3.78825688362122</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G412" t="n">
-        <v>3.97283506393433</v>
+        <v>3.97283530235291</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11107,7 +11107,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G413" t="n">
-        <v>4.06072950363159</v>
+        <v>4.06072902679443</v>
       </c>
       <c r="H413" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G428" t="n">
-        <v>4.21015024185181</v>
+        <v>4.21015071868896</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>4.75</v>
       </c>
       <c r="G429" t="n">
-        <v>4.17499303817749</v>
+        <v>4.17499256134033</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G430" t="n">
-        <v>4.28925561904907</v>
+        <v>4.28925609588623</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G431" t="n">
-        <v>4.28925561904907</v>
+        <v>4.28925609588623</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G432" t="n">
-        <v>4.21015024185181</v>
+        <v>4.21015071868896</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G434" t="n">
-        <v>4.22772979736328</v>
+        <v>4.22772932052612</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>4.75</v>
       </c>
       <c r="G435" t="n">
-        <v>4.17499303817749</v>
+        <v>4.17499256134033</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11705,7 +11705,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G436" t="n">
-        <v>4.21015024185181</v>
+        <v>4.21015071868896</v>
       </c>
       <c r="H436" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G437" t="n">
-        <v>4.07830810546875</v>
+        <v>4.07830858230591</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G448" t="n">
-        <v>4.41230773925781</v>
+        <v>4.41230821609497</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12069,7 +12069,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G450" t="n">
-        <v>4.21893978118896</v>
+        <v>4.21894025802612</v>
       </c>
       <c r="H450" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G452" t="n">
-        <v>4.21893978118896</v>
+        <v>4.21894025802612</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12147,7 +12147,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G453" t="n">
-        <v>4.21015024185181</v>
+        <v>4.21015071868896</v>
       </c>
       <c r="H453" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>4.75</v>
       </c>
       <c r="G454" t="n">
-        <v>4.17499303817749</v>
+        <v>4.17499256134033</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12225,7 +12225,7 @@
         <v>4.75</v>
       </c>
       <c r="G456" t="n">
-        <v>4.17499303817749</v>
+        <v>4.17499256134033</v>
       </c>
       <c r="H456" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>4.75</v>
       </c>
       <c r="G457" t="n">
-        <v>4.17499303817749</v>
+        <v>4.17499256134033</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12277,7 +12277,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G458" t="n">
-        <v>4.05194091796875</v>
+        <v>4.05194044113159</v>
       </c>
       <c r="H458" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G459" t="n">
-        <v>4.02557134628296</v>
+        <v>4.02557182312012</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G460" t="n">
-        <v>4.02557134628296</v>
+        <v>4.02557182312012</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12355,7 +12355,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G461" t="n">
-        <v>4.02557134628296</v>
+        <v>4.02557182312012</v>
       </c>
       <c r="H461" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G464" t="n">
-        <v>4.21015024185181</v>
+        <v>4.21015071868896</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G466" t="n">
-        <v>4.28925561904907</v>
+        <v>4.28925609588623</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12537,7 +12537,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G468" t="n">
-        <v>4.50020217895508</v>
+        <v>4.50020265579224</v>
       </c>
       <c r="H468" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>5</v>
       </c>
       <c r="G472" t="n">
-        <v>4.41898965835571</v>
+        <v>4.41899013519287</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12667,7 +12667,7 @@
         <v>5</v>
       </c>
       <c r="G473" t="n">
-        <v>4.41898965835571</v>
+        <v>4.41899013519287</v>
       </c>
       <c r="H473" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G474" t="n">
-        <v>4.57807350158691</v>
+        <v>4.57807397842407</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G478" t="n">
-        <v>4.64877796173096</v>
+        <v>4.6487774848938</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12823,7 +12823,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G479" t="n">
-        <v>4.56039762496948</v>
+        <v>4.56039810180664</v>
       </c>
       <c r="H479" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G481" t="n">
-        <v>4.56039762496948</v>
+        <v>4.56039810180664</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>5</v>
       </c>
       <c r="G485" t="n">
-        <v>4.41898965835571</v>
+        <v>4.41899013519287</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13005,7 +13005,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G486" t="n">
-        <v>4.37479972839355</v>
+        <v>4.37480020523071</v>
       </c>
       <c r="H486" t="s">
         <v>8</v>
@@ -13031,7 +13031,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G487" t="n">
-        <v>4.56039762496948</v>
+        <v>4.56039810180664</v>
       </c>
       <c r="H487" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G488" t="n">
-        <v>4.56039762496948</v>
+        <v>4.56039810180664</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G494" t="n">
-        <v>4.22455501556396</v>
+        <v>4.22455453872681</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13239,7 +13239,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G495" t="n">
-        <v>4.17152643203735</v>
+        <v>4.1715259552002</v>
       </c>
       <c r="H495" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G497" t="n">
-        <v>4.0301194190979</v>
+        <v>4.03011894226074</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13317,7 +13317,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G498" t="n">
-        <v>4.0301194190979</v>
+        <v>4.03011894226074</v>
       </c>
       <c r="H498" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G507" t="n">
-        <v>4.22455501556396</v>
+        <v>4.22455453872681</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -14045,7 +14045,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G526" t="n">
-        <v>4.57807350158691</v>
+        <v>4.57807397842407</v>
       </c>
       <c r="H526" t="s">
         <v>8</v>
@@ -14071,7 +14071,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G527" t="n">
-        <v>4.57807350158691</v>
+        <v>4.57807397842407</v>
       </c>
       <c r="H527" t="s">
         <v>8</v>
@@ -14201,7 +14201,7 @@
         <v>5</v>
       </c>
       <c r="G532" t="n">
-        <v>4.41898965835571</v>
+        <v>4.41899013519287</v>
       </c>
       <c r="H532" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G539" t="n">
-        <v>4.41015148162842</v>
+        <v>4.41015195846558</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14487,7 +14487,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G543" t="n">
-        <v>4.38363885879517</v>
+        <v>4.38363790512085</v>
       </c>
       <c r="H543" t="s">
         <v>8</v>
@@ -14513,7 +14513,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G544" t="n">
-        <v>4.36596202850342</v>
+        <v>4.36596250534058</v>
       </c>
       <c r="H544" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G545" t="n">
-        <v>4.36596202850342</v>
+        <v>4.36596250534058</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14565,7 +14565,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G546" t="n">
-        <v>4.33944845199585</v>
+        <v>4.33944797515869</v>
       </c>
       <c r="H546" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G547" t="n">
-        <v>4.33944845199585</v>
+        <v>4.33944797515869</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G548" t="n">
-        <v>4.33944845199585</v>
+        <v>4.33944797515869</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14747,7 +14747,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G553" t="n">
-        <v>4.31293439865112</v>
+        <v>4.31293487548828</v>
       </c>
       <c r="H553" t="s">
         <v>8</v>
@@ -14851,7 +14851,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G557" t="n">
-        <v>4.07430934906006</v>
+        <v>4.0743088722229</v>
       </c>
       <c r="H557" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G561" t="n">
-        <v>4.15385055541992</v>
+        <v>4.15385103225708</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -15085,7 +15085,7 @@
         <v>5</v>
       </c>
       <c r="G566" t="n">
-        <v>4.41898965835571</v>
+        <v>4.41899013519287</v>
       </c>
       <c r="H566" t="s">
         <v>8</v>
@@ -15163,7 +15163,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G569" t="n">
-        <v>4.57807350158691</v>
+        <v>4.57807397842407</v>
       </c>
       <c r="H569" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G573" t="n">
-        <v>4.73715734481812</v>
+        <v>4.73715782165527</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15423,7 +15423,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G579" t="n">
-        <v>4.89624071121216</v>
+        <v>4.89624118804932</v>
       </c>
       <c r="H579" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G580" t="n">
-        <v>4.94926929473877</v>
+        <v>4.94926881790161</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G581" t="n">
-        <v>5.10835313796997</v>
+        <v>5.10835266113281</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15501,7 +15501,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G582" t="n">
-        <v>5.26743602752686</v>
+        <v>5.26743650436401</v>
       </c>
       <c r="H582" t="s">
         <v>8</v>
@@ -15527,7 +15527,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G583" t="n">
-        <v>5.47954797744751</v>
+        <v>5.47954750061035</v>
       </c>
       <c r="H583" t="s">
         <v>8</v>
@@ -15605,7 +15605,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G586" t="n">
-        <v>5.47954797744751</v>
+        <v>5.47954750061035</v>
       </c>
       <c r="H586" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G587" t="n">
-        <v>5.47954797744751</v>
+        <v>5.47954750061035</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G588" t="n">
-        <v>5.70933485031128</v>
+        <v>5.70933532714844</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15761,7 +15761,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G592" t="n">
-        <v>5.51489973068237</v>
+        <v>5.51489925384521</v>
       </c>
       <c r="H592" t="s">
         <v>8</v>
@@ -15865,7 +15865,7 @@
         <v>6.71999979019165</v>
       </c>
       <c r="G596" t="n">
-        <v>5.93912220001221</v>
+        <v>5.93912315368652</v>
       </c>
       <c r="H596" t="s">
         <v>8</v>
@@ -15995,7 +15995,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G601" t="n">
-        <v>5.47954797744751</v>
+        <v>5.47954750061035</v>
       </c>
       <c r="H601" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G602" t="n">
-        <v>5.49722337722778</v>
+        <v>5.49722385406494</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>6.26000022888184</v>
       </c>
       <c r="G603" t="n">
-        <v>5.53257608413696</v>
+        <v>5.5325756072998</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16073,7 +16073,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G604" t="n">
-        <v>5.51489973068237</v>
+        <v>5.51489925384521</v>
       </c>
       <c r="H604" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G607" t="n">
-        <v>5.55025196075439</v>
+        <v>5.55025148391724</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>6.26000022888184</v>
       </c>
       <c r="G608" t="n">
-        <v>5.53257608413696</v>
+        <v>5.5325756072998</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16229,7 +16229,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G610" t="n">
-        <v>5.70933485031128</v>
+        <v>5.70933532714844</v>
       </c>
       <c r="H610" t="s">
         <v>8</v>
@@ -16385,7 +16385,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G616" t="n">
-        <v>5.88609457015991</v>
+        <v>5.88609504699707</v>
       </c>
       <c r="H616" t="s">
         <v>8</v>
@@ -16489,7 +16489,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G620" t="n">
-        <v>5.47954797744751</v>
+        <v>5.47954750061035</v>
       </c>
       <c r="H620" t="s">
         <v>8</v>
@@ -16515,7 +16515,7 @@
         <v>6.26000022888184</v>
       </c>
       <c r="G621" t="n">
-        <v>5.53257608413696</v>
+        <v>5.5325756072998</v>
       </c>
       <c r="H621" t="s">
         <v>8</v>
@@ -16697,7 +16697,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G628" t="n">
-        <v>5.88609457015991</v>
+        <v>5.88609504699707</v>
       </c>
       <c r="H628" t="s">
         <v>8</v>
@@ -16827,7 +16827,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G633" t="n">
-        <v>5.83306741714478</v>
+        <v>5.83306694030762</v>
       </c>
       <c r="H633" t="s">
         <v>8</v>
@@ -16853,7 +16853,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G634" t="n">
-        <v>5.83306741714478</v>
+        <v>5.83306694030762</v>
       </c>
       <c r="H634" t="s">
         <v>8</v>
@@ -16879,7 +16879,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G635" t="n">
-        <v>5.83306741714478</v>
+        <v>5.83306694030762</v>
       </c>
       <c r="H635" t="s">
         <v>8</v>
@@ -16905,7 +16905,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G636" t="n">
-        <v>5.70933485031128</v>
+        <v>5.70933532714844</v>
       </c>
       <c r="H636" t="s">
         <v>8</v>
@@ -16983,7 +16983,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G639" t="n">
-        <v>5.5856032371521</v>
+        <v>5.58560371398926</v>
       </c>
       <c r="H639" t="s">
         <v>8</v>
@@ -17009,7 +17009,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G640" t="n">
-        <v>5.70933485031128</v>
+        <v>5.70933532714844</v>
       </c>
       <c r="H640" t="s">
         <v>8</v>
@@ -17035,7 +17035,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G641" t="n">
-        <v>5.79771518707275</v>
+        <v>5.7977147102356</v>
       </c>
       <c r="H641" t="s">
         <v>8</v>
@@ -17061,7 +17061,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G642" t="n">
-        <v>5.79771518707275</v>
+        <v>5.7977147102356</v>
       </c>
       <c r="H642" t="s">
         <v>8</v>
@@ -17113,7 +17113,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G644" t="n">
-        <v>5.47954797744751</v>
+        <v>5.47954750061035</v>
       </c>
       <c r="H644" t="s">
         <v>8</v>
@@ -17139,7 +17139,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G645" t="n">
-        <v>5.47954797744751</v>
+        <v>5.47954750061035</v>
       </c>
       <c r="H645" t="s">
         <v>8</v>
@@ -17165,7 +17165,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G646" t="n">
-        <v>5.47954797744751</v>
+        <v>5.47954750061035</v>
       </c>
       <c r="H646" t="s">
         <v>8</v>
@@ -17217,7 +17217,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G648" t="n">
-        <v>5.26743602752686</v>
+        <v>5.26743650436401</v>
       </c>
       <c r="H648" t="s">
         <v>8</v>
@@ -17347,7 +17347,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G653" t="n">
-        <v>5.1260290145874</v>
+        <v>5.12602853775024</v>
       </c>
       <c r="H653" t="s">
         <v>8</v>
@@ -17373,7 +17373,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G654" t="n">
-        <v>4.94926929473877</v>
+        <v>4.94926881790161</v>
       </c>
       <c r="H654" t="s">
         <v>8</v>
@@ -17399,7 +17399,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G655" t="n">
-        <v>4.94926929473877</v>
+        <v>4.94926881790161</v>
       </c>
       <c r="H655" t="s">
         <v>8</v>
@@ -17477,7 +17477,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G658" t="n">
-        <v>5.1260290145874</v>
+        <v>5.12602853775024</v>
       </c>
       <c r="H658" t="s">
         <v>8</v>
@@ -17607,7 +17607,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G663" t="n">
-        <v>5.47954797744751</v>
+        <v>5.47954750061035</v>
       </c>
       <c r="H663" t="s">
         <v>8</v>
@@ -17685,7 +17685,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G666" t="n">
-        <v>4.71948146820068</v>
+        <v>4.71948194503784</v>
       </c>
       <c r="H666" t="s">
         <v>8</v>
@@ -17789,7 +17789,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G670" t="n">
-        <v>4.71948146820068</v>
+        <v>4.71948194503784</v>
       </c>
       <c r="H670" t="s">
         <v>8</v>
@@ -17815,7 +17815,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G671" t="n">
-        <v>4.57807350158691</v>
+        <v>4.57807397842407</v>
       </c>
       <c r="H671" t="s">
         <v>8</v>
@@ -17841,7 +17841,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G672" t="n">
-        <v>4.64877796173096</v>
+        <v>4.6487774848938</v>
       </c>
       <c r="H672" t="s">
         <v>8</v>
@@ -17945,7 +17945,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G676" t="n">
-        <v>4.24223041534424</v>
+        <v>4.2422308921814</v>
       </c>
       <c r="H676" t="s">
         <v>8</v>
@@ -17971,7 +17971,7 @@
         <v>5</v>
       </c>
       <c r="G677" t="n">
-        <v>4.41898965835571</v>
+        <v>4.41899013519287</v>
       </c>
       <c r="H677" t="s">
         <v>8</v>
@@ -18023,7 +18023,7 @@
         <v>5</v>
       </c>
       <c r="G679" t="n">
-        <v>4.41898965835571</v>
+        <v>4.41899013519287</v>
       </c>
       <c r="H679" t="s">
         <v>8</v>
@@ -18101,7 +18101,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G682" t="n">
-        <v>4.71948146820068</v>
+        <v>4.71948194503784</v>
       </c>
       <c r="H682" t="s">
         <v>8</v>
@@ -18361,7 +18361,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G692" t="n">
-        <v>4.87856531143188</v>
+        <v>4.87856483459473</v>
       </c>
       <c r="H692" t="s">
         <v>8</v>
@@ -18387,7 +18387,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G693" t="n">
-        <v>4.87856531143188</v>
+        <v>4.87856483459473</v>
       </c>
       <c r="H693" t="s">
         <v>8</v>
@@ -18439,7 +18439,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G695" t="n">
-        <v>4.87856531143188</v>
+        <v>4.87856483459473</v>
       </c>
       <c r="H695" t="s">
         <v>8</v>
@@ -18491,7 +18491,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G697" t="n">
-        <v>4.94926929473877</v>
+        <v>4.94926881790161</v>
       </c>
       <c r="H697" t="s">
         <v>8</v>
@@ -18517,7 +18517,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G698" t="n">
-        <v>4.94926929473877</v>
+        <v>4.94926881790161</v>
       </c>
       <c r="H698" t="s">
         <v>8</v>
@@ -18621,7 +18621,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G702" t="n">
-        <v>4.94926929473877</v>
+        <v>4.94926881790161</v>
       </c>
       <c r="H702" t="s">
         <v>8</v>
@@ -18699,7 +18699,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G705" t="n">
-        <v>5.14370441436768</v>
+        <v>5.14370489120483</v>
       </c>
       <c r="H705" t="s">
         <v>8</v>
@@ -18725,7 +18725,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G706" t="n">
-        <v>5.1260290145874</v>
+        <v>5.12602853775024</v>
       </c>
       <c r="H706" t="s">
         <v>8</v>
@@ -18777,7 +18777,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G708" t="n">
-        <v>4.98462057113647</v>
+        <v>4.98462104797363</v>
       </c>
       <c r="H708" t="s">
         <v>8</v>
@@ -18803,7 +18803,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G709" t="n">
-        <v>5.1260290145874</v>
+        <v>5.12602853775024</v>
       </c>
       <c r="H709" t="s">
         <v>8</v>
@@ -18829,7 +18829,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G710" t="n">
-        <v>5.1260290145874</v>
+        <v>5.12602853775024</v>
       </c>
       <c r="H710" t="s">
         <v>8</v>
@@ -18855,7 +18855,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G711" t="n">
-        <v>5.14370441436768</v>
+        <v>5.14370489120483</v>
       </c>
       <c r="H711" t="s">
         <v>8</v>
@@ -18881,7 +18881,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G712" t="n">
-        <v>5.14370441436768</v>
+        <v>5.14370489120483</v>
       </c>
       <c r="H712" t="s">
         <v>8</v>
@@ -18907,7 +18907,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G713" t="n">
-        <v>5.16138076782227</v>
+        <v>5.16138029098511</v>
       </c>
       <c r="H713" t="s">
         <v>8</v>
@@ -18959,7 +18959,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G715" t="n">
-        <v>5.14370441436768</v>
+        <v>5.14370489120483</v>
       </c>
       <c r="H715" t="s">
         <v>8</v>
@@ -19115,7 +19115,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G721" t="n">
-        <v>4.94926929473877</v>
+        <v>4.94926881790161</v>
       </c>
       <c r="H721" t="s">
         <v>8</v>
@@ -19141,7 +19141,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G722" t="n">
-        <v>5.16138076782227</v>
+        <v>5.16138029098511</v>
       </c>
       <c r="H722" t="s">
         <v>8</v>
@@ -19167,7 +19167,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G723" t="n">
-        <v>5.16138076782227</v>
+        <v>5.16138029098511</v>
       </c>
       <c r="H723" t="s">
         <v>8</v>
@@ -47848,6 +47848,32 @@
         <v>2.61999988555908</v>
       </c>
       <c r="H1826" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1827">
+      <c r="A1827" s="1" t="n">
+        <v>46287.2916666667</v>
+      </c>
+      <c r="B1827" t="n">
+        <v>12482</v>
+      </c>
+      <c r="C1827" t="n">
+        <v>2.6800000667572</v>
+      </c>
+      <c r="D1827" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="E1827" t="n">
+        <v>2.61999988555908</v>
+      </c>
+      <c r="F1827" t="n">
+        <v>2.57999992370605</v>
+      </c>
+      <c r="G1827" t="n">
+        <v>2.57999992370605</v>
+      </c>
+      <c r="H1827" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/PTR.MI.xlsx
+++ b/data/PTR.MI.xlsx
@@ -551,7 +551,7 @@
         <v>3.56850004196167</v>
       </c>
       <c r="G7" t="n">
-        <v>3.09731149673462</v>
+        <v>3.0973117351532</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>3.47849988937378</v>
       </c>
       <c r="G11" t="n">
-        <v>3.01919531822205</v>
+        <v>3.01919555664062</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G12" t="n">
-        <v>3.08125424385071</v>
+        <v>3.08125448226929</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G17" t="n">
-        <v>3.08993411064148</v>
+        <v>3.0899338722229</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G19" t="n">
-        <v>3.13333201408386</v>
+        <v>3.13333177566528</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G22" t="n">
-        <v>3.09861350059509</v>
+        <v>3.09861373901367</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>3.49850010871887</v>
       </c>
       <c r="G23" t="n">
-        <v>3.03655457496643</v>
+        <v>3.03655481338501</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G29" t="n">
-        <v>3.08125424385071</v>
+        <v>3.08125448226929</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G30" t="n">
-        <v>3.08993411064148</v>
+        <v>3.0899338722229</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G31" t="n">
-        <v>3.08993411064148</v>
+        <v>3.0899338722229</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>3.48200011253357</v>
       </c>
       <c r="G32" t="n">
-        <v>3.02223324775696</v>
+        <v>3.02223348617554</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>3.48200011253357</v>
       </c>
       <c r="G33" t="n">
-        <v>3.02223324775696</v>
+        <v>3.02223348617554</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G38" t="n">
-        <v>3.19408917427063</v>
+        <v>3.19408893585205</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G39" t="n">
-        <v>3.21144819259644</v>
+        <v>3.21144843101501</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G49" t="n">
-        <v>3.21144819259644</v>
+        <v>3.21144843101501</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G52" t="n">
-        <v>3.21144819259644</v>
+        <v>3.21144843101501</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G54" t="n">
-        <v>3.21144819259644</v>
+        <v>3.21144843101501</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G62" t="n">
-        <v>3.21144819259644</v>
+        <v>3.21144843101501</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>3.5550000667572</v>
       </c>
       <c r="G64" t="n">
-        <v>3.08559417724609</v>
+        <v>3.08559441566467</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>3.5550000667572</v>
       </c>
       <c r="G65" t="n">
-        <v>3.08559417724609</v>
+        <v>3.08559441566467</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G66" t="n">
-        <v>3.09861350059509</v>
+        <v>3.09861373901367</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>3.63499999046326</v>
       </c>
       <c r="G67" t="n">
-        <v>3.15503120422363</v>
+        <v>3.15503096580505</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G71" t="n">
-        <v>3.21144819259644</v>
+        <v>3.21144843101501</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G73" t="n">
-        <v>3.08125424385071</v>
+        <v>3.08125448226929</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G74" t="n">
-        <v>3.08125424385071</v>
+        <v>3.08125448226929</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G77" t="n">
-        <v>3.08125424385071</v>
+        <v>3.08125448226929</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G87" t="n">
-        <v>3.37636089324951</v>
+        <v>3.37636065483093</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G90" t="n">
-        <v>3.41975855827332</v>
+        <v>3.41975879669189</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G91" t="n">
-        <v>3.51523399353027</v>
+        <v>3.51523423194885</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G94" t="n">
-        <v>3.41975855827332</v>
+        <v>3.41975879669189</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G95" t="n">
-        <v>3.51523399353027</v>
+        <v>3.51523423194885</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>4.02500009536743</v>
       </c>
       <c r="G96" t="n">
-        <v>3.49353504180908</v>
+        <v>3.49353528022766</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>4.00500011444092</v>
       </c>
       <c r="G98" t="n">
-        <v>3.4761757850647</v>
+        <v>3.47617602348328</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>3.95499992370605</v>
       </c>
       <c r="G100" t="n">
-        <v>3.43277788162231</v>
+        <v>3.43277812004089</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>3.9449999332428</v>
       </c>
       <c r="G104" t="n">
-        <v>3.42409825325012</v>
+        <v>3.42409801483154</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>4.03499984741211</v>
       </c>
       <c r="G106" t="n">
-        <v>3.50221467018127</v>
+        <v>3.50221419334412</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G107" t="n">
-        <v>3.51523399353027</v>
+        <v>3.51523423194885</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G108" t="n">
-        <v>3.54995250701904</v>
+        <v>3.54995226860046</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G109" t="n">
-        <v>3.54995250701904</v>
+        <v>3.54995226860046</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G110" t="n">
-        <v>3.64542722702026</v>
+        <v>3.64542770385742</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G111" t="n">
-        <v>3.64542722702026</v>
+        <v>3.64542770385742</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>4.5</v>
       </c>
       <c r="G113" t="n">
-        <v>3.90581560134888</v>
+        <v>3.90581583976746</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>4.5</v>
       </c>
       <c r="G114" t="n">
-        <v>3.90581560134888</v>
+        <v>3.90581583976746</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G115" t="n">
-        <v>3.87109708786011</v>
+        <v>3.87109684944153</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G116" t="n">
-        <v>3.86241793632507</v>
+        <v>3.86241745948792</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G117" t="n">
-        <v>4.00997018814087</v>
+        <v>4.00997114181519</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G118" t="n">
-        <v>4.03600931167603</v>
+        <v>4.03600978851318</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G119" t="n">
-        <v>3.96657252311707</v>
+        <v>3.96657299995422</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G120" t="n">
-        <v>3.86241793632507</v>
+        <v>3.86241745948792</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G121" t="n">
-        <v>3.92317485809326</v>
+        <v>3.92317461967468</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G122" t="n">
-        <v>3.94053411483765</v>
+        <v>3.94053363800049</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G123" t="n">
-        <v>3.88845610618591</v>
+        <v>3.88845634460449</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G126" t="n">
-        <v>4.03600931167603</v>
+        <v>4.03600978851318</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G129" t="n">
-        <v>4.38319301605225</v>
+        <v>4.3831934928894</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G130" t="n">
-        <v>4.3918719291687</v>
+        <v>4.39187240600586</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G136" t="n">
-        <v>4.20092105865479</v>
+        <v>4.2009220123291</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G137" t="n">
-        <v>4.14016389846802</v>
+        <v>4.14016437530518</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G138" t="n">
-        <v>4.16620349884033</v>
+        <v>4.16620302200317</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G147" t="n">
-        <v>4.70433759689331</v>
+        <v>4.70433855056763</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>5.13000011444092</v>
       </c>
       <c r="G150" t="n">
-        <v>4.45262956619263</v>
+        <v>4.45263004302979</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G153" t="n">
-        <v>4.44395017623901</v>
+        <v>4.44394969940186</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G156" t="n">
-        <v>4.31375598907471</v>
+        <v>4.31375551223755</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G157" t="n">
-        <v>4.23564052581787</v>
+        <v>4.23564004898071</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G161" t="n">
-        <v>4.0446891784668</v>
+        <v>4.04468870162964</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G162" t="n">
-        <v>3.99261164665222</v>
+        <v>3.99261116981506</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>4.24499988555908</v>
       </c>
       <c r="G163" t="n">
-        <v>3.68448543548584</v>
+        <v>3.68448615074158</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G166" t="n">
-        <v>3.23748707771301</v>
+        <v>3.23748683929443</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G168" t="n">
-        <v>2.95974040031433</v>
+        <v>2.95974016189575</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G173" t="n">
-        <v>3.09861350059509</v>
+        <v>3.09861373901367</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>3.34500002861023</v>
       </c>
       <c r="G174" t="n">
-        <v>2.90332317352295</v>
+        <v>2.90332269668579</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G176" t="n">
-        <v>3.08125424385071</v>
+        <v>3.08125448226929</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G177" t="n">
-        <v>3.09861350059509</v>
+        <v>3.09861373901367</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G179" t="n">
-        <v>3.21144819259644</v>
+        <v>3.21144843101501</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G181" t="n">
-        <v>3.30692362785339</v>
+        <v>3.30692386627197</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G183" t="n">
-        <v>3.19408917427063</v>
+        <v>3.19408893585205</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G184" t="n">
-        <v>3.21144819259644</v>
+        <v>3.21144843101501</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G185" t="n">
-        <v>3.19408917427063</v>
+        <v>3.19408893585205</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G187" t="n">
-        <v>3.21144819259644</v>
+        <v>3.21144843101501</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G190" t="n">
-        <v>3.18540954589844</v>
+        <v>3.18540978431702</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G195" t="n">
-        <v>3.34164214134216</v>
+        <v>3.34164190292358</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G196" t="n">
-        <v>3.35900139808655</v>
+        <v>3.35900163650513</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G197" t="n">
-        <v>3.35900139808655</v>
+        <v>3.35900163650513</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G199" t="n">
-        <v>3.54995250701904</v>
+        <v>3.54995226860046</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G204" t="n">
-        <v>3.19408917427063</v>
+        <v>3.19408893585205</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G207" t="n">
-        <v>3.37636089324951</v>
+        <v>3.37636065483093</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G208" t="n">
-        <v>3.30692362785339</v>
+        <v>3.30692386627197</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G209" t="n">
-        <v>3.24616646766663</v>
+        <v>3.24616670608521</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G223" t="n">
-        <v>3.34164214134216</v>
+        <v>3.34164190292358</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G225" t="n">
-        <v>3.35900139808655</v>
+        <v>3.35900163650513</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G226" t="n">
-        <v>3.37636089324951</v>
+        <v>3.37636065483093</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G230" t="n">
-        <v>3.37636089324951</v>
+        <v>3.37636065483093</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G233" t="n">
-        <v>3.37636089324951</v>
+        <v>3.37636065483093</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G234" t="n">
-        <v>3.37636089324951</v>
+        <v>3.37636065483093</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G238" t="n">
-        <v>3.23748707771301</v>
+        <v>3.23748683929443</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G239" t="n">
-        <v>3.23748707771301</v>
+        <v>3.23748683929443</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G241" t="n">
-        <v>3.34164214134216</v>
+        <v>3.34164190292358</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G247" t="n">
-        <v>3.24616646766663</v>
+        <v>3.24616670608521</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G248" t="n">
-        <v>3.24616646766663</v>
+        <v>3.24616670608521</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G251" t="n">
-        <v>3.18540954589844</v>
+        <v>3.18540978431702</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G252" t="n">
-        <v>3.21144819259644</v>
+        <v>3.21144843101501</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G253" t="n">
-        <v>3.21144819259644</v>
+        <v>3.21144843101501</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G255" t="n">
-        <v>3.18540954589844</v>
+        <v>3.18540978431702</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G260" t="n">
-        <v>3.08993411064148</v>
+        <v>3.0899338722229</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G263" t="n">
-        <v>3.08993411064148</v>
+        <v>3.0899338722229</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G264" t="n">
-        <v>3.13333201408386</v>
+        <v>3.13333177566528</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G265" t="n">
-        <v>3.07257485389709</v>
+        <v>3.07257509231567</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7363,7 +7363,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G269" t="n">
-        <v>3.24616646766663</v>
+        <v>3.24616670608521</v>
       </c>
       <c r="H269" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G270" t="n">
-        <v>3.19408917427063</v>
+        <v>3.19408893585205</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G271" t="n">
-        <v>3.13333201408386</v>
+        <v>3.13333177566528</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G274" t="n">
-        <v>2.93370151519775</v>
+        <v>2.93370175361633</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G276" t="n">
-        <v>3.02917718887329</v>
+        <v>3.02917695045471</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G278" t="n">
-        <v>3.07257485389709</v>
+        <v>3.07257509231567</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G281" t="n">
-        <v>3.06389546394348</v>
+        <v>3.06389498710632</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G282" t="n">
-        <v>3.06389546394348</v>
+        <v>3.06389498710632</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G283" t="n">
-        <v>3.06389546394348</v>
+        <v>3.06389498710632</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G284" t="n">
-        <v>2.94238114356995</v>
+        <v>2.94238090515137</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G285" t="n">
-        <v>2.94238114356995</v>
+        <v>2.94238090515137</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G289" t="n">
-        <v>3.08125424385071</v>
+        <v>3.08125448226929</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G294" t="n">
-        <v>3.08125424385071</v>
+        <v>3.08125448226929</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G296" t="n">
-        <v>2.95106053352356</v>
+        <v>2.95106077194214</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G297" t="n">
-        <v>2.95106053352356</v>
+        <v>2.95106077194214</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G302" t="n">
-        <v>2.95974040031433</v>
+        <v>2.95974016189575</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G303" t="n">
-        <v>2.88162398338318</v>
+        <v>2.8816237449646</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G306" t="n">
-        <v>3.08125424385071</v>
+        <v>3.08125448226929</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G313" t="n">
-        <v>3.21144819259644</v>
+        <v>3.21144843101501</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G314" t="n">
-        <v>3.19408917427063</v>
+        <v>3.19408893585205</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G315" t="n">
-        <v>3.21144819259644</v>
+        <v>3.21144843101501</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G317" t="n">
-        <v>3.21144819259644</v>
+        <v>3.21144843101501</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G321" t="n">
-        <v>3.21144819259644</v>
+        <v>3.21144843101501</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G323" t="n">
-        <v>3.21144819259644</v>
+        <v>3.21144843101501</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G324" t="n">
-        <v>3.21144819259644</v>
+        <v>3.21144843101501</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G325" t="n">
-        <v>3.21144819259644</v>
+        <v>3.21144843101501</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G326" t="n">
-        <v>3.19408917427063</v>
+        <v>3.19408893585205</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G328" t="n">
-        <v>3.21144819259644</v>
+        <v>3.21144843101501</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G330" t="n">
-        <v>3.19408917427063</v>
+        <v>3.19408893585205</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G333" t="n">
-        <v>3.02917718887329</v>
+        <v>3.02917695045471</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G342" t="n">
-        <v>3.21144819259644</v>
+        <v>3.21144843101501</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G346" t="n">
-        <v>3.21144819259644</v>
+        <v>3.21144843101501</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G352" t="n">
-        <v>3.34164214134216</v>
+        <v>3.34164190292358</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G354" t="n">
-        <v>3.34164214134216</v>
+        <v>3.34164190292358</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G355" t="n">
-        <v>3.30692362785339</v>
+        <v>3.30692386627197</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G358" t="n">
-        <v>3.37636089324951</v>
+        <v>3.37636065483093</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G361" t="n">
-        <v>3.46304655075073</v>
+        <v>3.46304678916931</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G363" t="n">
-        <v>3.53336191177368</v>
+        <v>3.53336215019226</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G365" t="n">
-        <v>3.55973052978516</v>
+        <v>3.55973076820374</v>
       </c>
       <c r="H365" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G373" t="n">
-        <v>3.77946710586548</v>
+        <v>3.77946734428406</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G374" t="n">
-        <v>3.85857176780701</v>
+        <v>3.85857200622559</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10119,7 +10119,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G375" t="n">
-        <v>3.80583500862122</v>
+        <v>3.80583524703979</v>
       </c>
       <c r="H375" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G378" t="n">
-        <v>3.84978294372559</v>
+        <v>3.84978270530701</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G379" t="n">
-        <v>3.9025194644928</v>
+        <v>3.90251970291138</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G380" t="n">
-        <v>3.99041414260864</v>
+        <v>3.99041366577148</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>4.5</v>
       </c>
       <c r="G381" t="n">
-        <v>3.95525622367859</v>
+        <v>3.95525646209717</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G382" t="n">
-        <v>3.92888760566711</v>
+        <v>3.92888784408569</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G383" t="n">
-        <v>3.92009830474854</v>
+        <v>3.92009806632996</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G384" t="n">
-        <v>3.77946710586548</v>
+        <v>3.77946734428406</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G385" t="n">
-        <v>3.77946710586548</v>
+        <v>3.77946734428406</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G386" t="n">
-        <v>3.64762496948242</v>
+        <v>3.647625207901</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10457,7 +10457,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G388" t="n">
-        <v>3.550940990448</v>
+        <v>3.55094122886658</v>
       </c>
       <c r="H388" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G390" t="n">
-        <v>3.69157195091248</v>
+        <v>3.69157242774963</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10587,7 +10587,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G393" t="n">
-        <v>3.6739935874939</v>
+        <v>3.67399311065674</v>
       </c>
       <c r="H393" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G394" t="n">
-        <v>3.6739935874939</v>
+        <v>3.67399311065674</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G396" t="n">
-        <v>3.77946710586548</v>
+        <v>3.77946734428406</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G398" t="n">
-        <v>3.77946710586548</v>
+        <v>3.77946734428406</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G402" t="n">
-        <v>3.60367774963379</v>
+        <v>3.60367798805237</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G404" t="n">
-        <v>3.9025194644928</v>
+        <v>3.90251970291138</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G405" t="n">
-        <v>3.84978294372559</v>
+        <v>3.84978270530701</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -10925,7 +10925,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G406" t="n">
-        <v>3.84099340438843</v>
+        <v>3.84099316596985</v>
       </c>
       <c r="H406" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G408" t="n">
-        <v>3.78825688362122</v>
+        <v>3.78825664520264</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G409" t="n">
-        <v>4.04315090179443</v>
+        <v>4.04315042495728</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G412" t="n">
-        <v>3.97283530235291</v>
+        <v>3.97283506393433</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11107,7 +11107,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G413" t="n">
-        <v>4.06072902679443</v>
+        <v>4.06072998046875</v>
       </c>
       <c r="H413" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G414" t="n">
-        <v>4.04315090179443</v>
+        <v>4.04315042495728</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G415" t="n">
-        <v>4.04315090179443</v>
+        <v>4.04315042495728</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>4.59000015258789</v>
       </c>
       <c r="G417" t="n">
-        <v>4.03436183929443</v>
+        <v>4.03436136245728</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11237,7 +11237,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G418" t="n">
-        <v>4.08709812164307</v>
+        <v>4.08709859848022</v>
       </c>
       <c r="H418" t="s">
         <v>8</v>
@@ -11289,7 +11289,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G420" t="n">
-        <v>4.30683469772339</v>
+        <v>4.30683422088623</v>
       </c>
       <c r="H420" t="s">
         <v>8</v>
@@ -11367,7 +11367,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G423" t="n">
-        <v>4.28046607971191</v>
+        <v>4.28046560287476</v>
       </c>
       <c r="H423" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G424" t="n">
-        <v>4.30683469772339</v>
+        <v>4.30683422088623</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G426" t="n">
-        <v>4.25409746170044</v>
+        <v>4.25409841537476</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G430" t="n">
-        <v>4.28925609588623</v>
+        <v>4.28925561904907</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G431" t="n">
-        <v>4.28925609588623</v>
+        <v>4.28925561904907</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G438" t="n">
-        <v>4.25409746170044</v>
+        <v>4.25409841537476</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G439" t="n">
-        <v>4.38593912124634</v>
+        <v>4.3859395980835</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G440" t="n">
-        <v>4.38593912124634</v>
+        <v>4.3859395980835</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G441" t="n">
-        <v>4.30683469772339</v>
+        <v>4.30683422088623</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11861,7 +11861,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G442" t="n">
-        <v>4.30683469772339</v>
+        <v>4.30683422088623</v>
       </c>
       <c r="H442" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G443" t="n">
-        <v>4.35078191757202</v>
+        <v>4.35078144073486</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G447" t="n">
-        <v>4.38593912124634</v>
+        <v>4.3859395980835</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12069,7 +12069,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G450" t="n">
-        <v>4.21894025802612</v>
+        <v>4.21893978118896</v>
       </c>
       <c r="H450" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G451" t="n">
-        <v>4.30683469772339</v>
+        <v>4.30683422088623</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G452" t="n">
-        <v>4.21894025802612</v>
+        <v>4.21893978118896</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12381,7 +12381,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G462" t="n">
-        <v>4.08709812164307</v>
+        <v>4.08709859848022</v>
       </c>
       <c r="H462" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G466" t="n">
-        <v>4.28925609588623</v>
+        <v>4.28925561904907</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G467" t="n">
-        <v>4.35078191757202</v>
+        <v>4.35078144073486</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12537,7 +12537,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G468" t="n">
-        <v>4.50020265579224</v>
+        <v>4.50020217895508</v>
       </c>
       <c r="H468" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G474" t="n">
-        <v>4.57807397842407</v>
+        <v>4.57807350158691</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G478" t="n">
-        <v>4.6487774848938</v>
+        <v>4.64877796173096</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12823,7 +12823,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G479" t="n">
-        <v>4.56039810180664</v>
+        <v>4.56039762496948</v>
       </c>
       <c r="H479" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G481" t="n">
-        <v>4.56039810180664</v>
+        <v>4.56039762496948</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -13031,7 +13031,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G487" t="n">
-        <v>4.56039810180664</v>
+        <v>4.56039762496948</v>
       </c>
       <c r="H487" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G488" t="n">
-        <v>4.56039810180664</v>
+        <v>4.56039762496948</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13239,7 +13239,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G495" t="n">
-        <v>4.1715259552002</v>
+        <v>4.17152643203735</v>
       </c>
       <c r="H495" t="s">
         <v>8</v>
@@ -13265,7 +13265,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G496" t="n">
-        <v>4.10966110229492</v>
+        <v>4.10966062545776</v>
       </c>
       <c r="H496" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G503" t="n">
-        <v>4.10966110229492</v>
+        <v>4.10966062545776</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13473,7 +13473,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G504" t="n">
-        <v>4.10966110229492</v>
+        <v>4.10966062545776</v>
       </c>
       <c r="H504" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G506" t="n">
-        <v>4.10082292556763</v>
+        <v>4.10082244873047</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G511" t="n">
-        <v>4.10966110229492</v>
+        <v>4.10966062545776</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13681,7 +13681,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G512" t="n">
-        <v>4.10966110229492</v>
+        <v>4.10966062545776</v>
       </c>
       <c r="H512" t="s">
         <v>8</v>
@@ -13785,7 +13785,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G516" t="n">
-        <v>4.32177209854126</v>
+        <v>4.32177257537842</v>
       </c>
       <c r="H516" t="s">
         <v>8</v>
@@ -13889,7 +13889,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G520" t="n">
-        <v>4.4896936416626</v>
+        <v>4.48969411849976</v>
       </c>
       <c r="H520" t="s">
         <v>8</v>
@@ -14045,7 +14045,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G526" t="n">
-        <v>4.57807397842407</v>
+        <v>4.57807350158691</v>
       </c>
       <c r="H526" t="s">
         <v>8</v>
@@ -14071,7 +14071,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G527" t="n">
-        <v>4.57807397842407</v>
+        <v>4.57807350158691</v>
       </c>
       <c r="H527" t="s">
         <v>8</v>
@@ -14513,7 +14513,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G544" t="n">
-        <v>4.36596250534058</v>
+        <v>4.36596202850342</v>
       </c>
       <c r="H544" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G545" t="n">
-        <v>4.36596250534058</v>
+        <v>4.36596202850342</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14851,7 +14851,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G557" t="n">
-        <v>4.0743088722229</v>
+        <v>4.07430934906006</v>
       </c>
       <c r="H557" t="s">
         <v>8</v>
@@ -14877,7 +14877,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G558" t="n">
-        <v>4.10966110229492</v>
+        <v>4.10966062545776</v>
       </c>
       <c r="H558" t="s">
         <v>8</v>
@@ -14981,7 +14981,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G562" t="n">
-        <v>4.10966110229492</v>
+        <v>4.10966062545776</v>
       </c>
       <c r="H562" t="s">
         <v>8</v>
@@ -15163,7 +15163,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G569" t="n">
-        <v>4.57807397842407</v>
+        <v>4.57807350158691</v>
       </c>
       <c r="H569" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G573" t="n">
-        <v>4.73715782165527</v>
+        <v>4.73715734481812</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15423,7 +15423,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G579" t="n">
-        <v>4.89624118804932</v>
+        <v>4.89624071121216</v>
       </c>
       <c r="H579" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G581" t="n">
-        <v>5.10835266113281</v>
+        <v>5.10835313796997</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15553,7 +15553,7 @@
         <v>6.03999996185303</v>
       </c>
       <c r="G584" t="n">
-        <v>5.33814001083374</v>
+        <v>5.3381404876709</v>
       </c>
       <c r="H584" t="s">
         <v>8</v>
@@ -15787,7 +15787,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G593" t="n">
-        <v>5.56792783737183</v>
+        <v>5.56792736053467</v>
       </c>
       <c r="H593" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G594" t="n">
-        <v>5.56792783737183</v>
+        <v>5.56792736053467</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15865,7 +15865,7 @@
         <v>6.71999979019165</v>
       </c>
       <c r="G596" t="n">
-        <v>5.93912315368652</v>
+        <v>5.93912267684937</v>
       </c>
       <c r="H596" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>6.26000022888184</v>
       </c>
       <c r="G603" t="n">
-        <v>5.5325756072998</v>
+        <v>5.53257608413696</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G607" t="n">
-        <v>5.55025148391724</v>
+        <v>5.55025196075439</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>6.26000022888184</v>
       </c>
       <c r="G608" t="n">
-        <v>5.5325756072998</v>
+        <v>5.53257608413696</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16411,7 +16411,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G617" t="n">
-        <v>5.92144680023193</v>
+        <v>5.92144632339478</v>
       </c>
       <c r="H617" t="s">
         <v>8</v>
@@ -16515,7 +16515,7 @@
         <v>6.26000022888184</v>
       </c>
       <c r="G621" t="n">
-        <v>5.5325756072998</v>
+        <v>5.53257608413696</v>
       </c>
       <c r="H621" t="s">
         <v>8</v>
@@ -16671,7 +16671,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G627" t="n">
-        <v>6.00982666015625</v>
+        <v>6.00982713699341</v>
       </c>
       <c r="H627" t="s">
         <v>8</v>
@@ -16723,7 +16723,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G629" t="n">
-        <v>5.92144680023193</v>
+        <v>5.92144632339478</v>
       </c>
       <c r="H629" t="s">
         <v>8</v>
@@ -16749,7 +16749,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G630" t="n">
-        <v>6.00982666015625</v>
+        <v>6.00982713699341</v>
       </c>
       <c r="H630" t="s">
         <v>8</v>
@@ -17191,7 +17191,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G647" t="n">
-        <v>5.3734917640686</v>
+        <v>5.37349224090576</v>
       </c>
       <c r="H647" t="s">
         <v>8</v>
@@ -17529,7 +17529,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G660" t="n">
-        <v>5.23208475112915</v>
+        <v>5.23208427429199</v>
       </c>
       <c r="H660" t="s">
         <v>8</v>
@@ -17685,7 +17685,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G666" t="n">
-        <v>4.71948194503784</v>
+        <v>4.71948146820068</v>
       </c>
       <c r="H666" t="s">
         <v>8</v>
@@ -17789,7 +17789,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G670" t="n">
-        <v>4.71948194503784</v>
+        <v>4.71948146820068</v>
       </c>
       <c r="H670" t="s">
         <v>8</v>
@@ -17815,7 +17815,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G671" t="n">
-        <v>4.57807397842407</v>
+        <v>4.57807350158691</v>
       </c>
       <c r="H671" t="s">
         <v>8</v>
@@ -17841,7 +17841,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G672" t="n">
-        <v>4.6487774848938</v>
+        <v>4.64877796173096</v>
       </c>
       <c r="H672" t="s">
         <v>8</v>
@@ -18101,7 +18101,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G682" t="n">
-        <v>4.71948194503784</v>
+        <v>4.71948146820068</v>
       </c>
       <c r="H682" t="s">
         <v>8</v>
@@ -18309,7 +18309,7 @@
         <v>5.5</v>
       </c>
       <c r="G690" t="n">
-        <v>4.86088895797729</v>
+        <v>4.86088943481445</v>
       </c>
       <c r="H690" t="s">
         <v>8</v>
@@ -18543,7 +18543,7 @@
         <v>5.5</v>
       </c>
       <c r="G699" t="n">
-        <v>4.86088895797729</v>
+        <v>4.86088943481445</v>
       </c>
       <c r="H699" t="s">
         <v>8</v>
@@ -18907,7 +18907,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G713" t="n">
-        <v>5.16138029098511</v>
+        <v>5.16138076782227</v>
       </c>
       <c r="H713" t="s">
         <v>8</v>
@@ -19141,7 +19141,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G722" t="n">
-        <v>5.16138029098511</v>
+        <v>5.16138076782227</v>
       </c>
       <c r="H722" t="s">
         <v>8</v>
@@ -19167,7 +19167,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G723" t="n">
-        <v>5.16138029098511</v>
+        <v>5.16138076782227</v>
       </c>
       <c r="H723" t="s">
         <v>8</v>
@@ -19193,7 +19193,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G724" t="n">
-        <v>5.24976062774658</v>
+        <v>5.24976015090942</v>
       </c>
       <c r="H724" t="s">
         <v>8</v>
@@ -19427,7 +19427,7 @@
         <v>5.8600001335144</v>
       </c>
       <c r="G733" t="n">
-        <v>5.24438142776489</v>
+        <v>5.24438095092773</v>
       </c>
       <c r="H733" t="s">
         <v>8</v>
@@ -19453,7 +19453,7 @@
         <v>5.8600001335144</v>
       </c>
       <c r="G734" t="n">
-        <v>5.24438142776489</v>
+        <v>5.24438095092773</v>
       </c>
       <c r="H734" t="s">
         <v>8</v>
@@ -19557,7 +19557,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G738" t="n">
-        <v>5.26227998733521</v>
+        <v>5.26228046417236</v>
       </c>
       <c r="H738" t="s">
         <v>8</v>
@@ -19895,7 +19895,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G751" t="n">
-        <v>4.99379634857178</v>
+        <v>4.99379587173462</v>
       </c>
       <c r="H751" t="s">
         <v>8</v>
@@ -20077,7 +20077,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G758" t="n">
-        <v>5.31597709655762</v>
+        <v>5.31597661972046</v>
       </c>
       <c r="H758" t="s">
         <v>8</v>
@@ -20103,7 +20103,7 @@
         <v>6</v>
       </c>
       <c r="G759" t="n">
-        <v>5.36967372894287</v>
+        <v>5.36967325210571</v>
       </c>
       <c r="H759" t="s">
         <v>8</v>
@@ -20129,7 +20129,7 @@
         <v>6</v>
       </c>
       <c r="G760" t="n">
-        <v>5.36967372894287</v>
+        <v>5.36967325210571</v>
       </c>
       <c r="H760" t="s">
         <v>8</v>
@@ -20155,7 +20155,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G761" t="n">
-        <v>5.47706699371338</v>
+        <v>5.47706651687622</v>
       </c>
       <c r="H761" t="s">
         <v>8</v>
@@ -20337,7 +20337,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G768" t="n">
-        <v>5.72765207290649</v>
+        <v>5.72765159606934</v>
       </c>
       <c r="H768" t="s">
         <v>8</v>
@@ -20389,7 +20389,7 @@
         <v>6.51999998092651</v>
       </c>
       <c r="G770" t="n">
-        <v>5.83504486083984</v>
+        <v>5.835045337677</v>
       </c>
       <c r="H770" t="s">
         <v>8</v>
@@ -20415,7 +20415,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G771" t="n">
-        <v>5.72765207290649</v>
+        <v>5.72765159606934</v>
       </c>
       <c r="H771" t="s">
         <v>8</v>
@@ -20441,7 +20441,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G772" t="n">
-        <v>5.72765207290649</v>
+        <v>5.72765159606934</v>
       </c>
       <c r="H772" t="s">
         <v>8</v>
@@ -20519,7 +20519,7 @@
         <v>6.5</v>
       </c>
       <c r="G775" t="n">
-        <v>5.81714630126953</v>
+        <v>5.81714582443237</v>
       </c>
       <c r="H775" t="s">
         <v>8</v>
@@ -20571,7 +20571,7 @@
         <v>6.5</v>
       </c>
       <c r="G777" t="n">
-        <v>5.81714630126953</v>
+        <v>5.81714582443237</v>
       </c>
       <c r="H777" t="s">
         <v>8</v>
@@ -20675,7 +20675,7 @@
         <v>6.73999977111816</v>
       </c>
       <c r="G781" t="n">
-        <v>6.03193330764771</v>
+        <v>6.03193283081055</v>
       </c>
       <c r="H781" t="s">
         <v>8</v>
@@ -20753,7 +20753,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G784" t="n">
-        <v>6.08562994003296</v>
+        <v>6.08563041687012</v>
       </c>
       <c r="H784" t="s">
         <v>8</v>
@@ -20883,7 +20883,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G789" t="n">
-        <v>5.88874197006226</v>
+        <v>5.8887414932251</v>
       </c>
       <c r="H789" t="s">
         <v>8</v>
@@ -20935,7 +20935,7 @@
         <v>6.53999996185303</v>
       </c>
       <c r="G791" t="n">
-        <v>5.85294437408447</v>
+        <v>5.85294389724731</v>
       </c>
       <c r="H791" t="s">
         <v>8</v>
@@ -20961,7 +20961,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G792" t="n">
-        <v>5.72765207290649</v>
+        <v>5.72765159606934</v>
       </c>
       <c r="H792" t="s">
         <v>8</v>
@@ -21091,7 +21091,7 @@
         <v>6.5</v>
       </c>
       <c r="G797" t="n">
-        <v>5.81714630126953</v>
+        <v>5.81714582443237</v>
       </c>
       <c r="H797" t="s">
         <v>8</v>
@@ -21117,7 +21117,7 @@
         <v>6.5</v>
       </c>
       <c r="G798" t="n">
-        <v>5.81714630126953</v>
+        <v>5.81714582443237</v>
       </c>
       <c r="H798" t="s">
         <v>8</v>
@@ -21195,7 +21195,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G801" t="n">
-        <v>5.88874197006226</v>
+        <v>5.8887414932251</v>
       </c>
       <c r="H801" t="s">
         <v>8</v>
@@ -21351,7 +21351,7 @@
         <v>6.42000007629395</v>
       </c>
       <c r="G807" t="n">
-        <v>5.74555063247681</v>
+        <v>5.74555110931396</v>
       </c>
       <c r="H807" t="s">
         <v>8</v>
@@ -21455,7 +21455,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G811" t="n">
-        <v>5.5486626625061</v>
+        <v>5.54866218566895</v>
       </c>
       <c r="H811" t="s">
         <v>8</v>
@@ -21507,7 +21507,7 @@
         <v>5.8600001335144</v>
       </c>
       <c r="G813" t="n">
-        <v>5.24438142776489</v>
+        <v>5.24438095092773</v>
       </c>
       <c r="H813" t="s">
         <v>8</v>
@@ -21533,7 +21533,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G814" t="n">
-        <v>5.13698768615723</v>
+        <v>5.13698720932007</v>
       </c>
       <c r="H814" t="s">
         <v>8</v>
@@ -21559,7 +21559,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G815" t="n">
-        <v>5.13698768615723</v>
+        <v>5.13698720932007</v>
       </c>
       <c r="H815" t="s">
         <v>8</v>
@@ -21585,7 +21585,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G816" t="n">
-        <v>5.35177421569824</v>
+        <v>5.3517746925354</v>
       </c>
       <c r="H816" t="s">
         <v>8</v>
@@ -21611,7 +21611,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G817" t="n">
-        <v>4.83270645141602</v>
+        <v>4.83270597457886</v>
       </c>
       <c r="H817" t="s">
         <v>8</v>
@@ -21715,7 +21715,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G821" t="n">
-        <v>4.83270645141602</v>
+        <v>4.83270597457886</v>
       </c>
       <c r="H821" t="s">
         <v>8</v>
@@ -21767,7 +21767,7 @@
         <v>6</v>
       </c>
       <c r="G823" t="n">
-        <v>5.36967372894287</v>
+        <v>5.36967325210571</v>
       </c>
       <c r="H823" t="s">
         <v>8</v>
@@ -21793,7 +21793,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G824" t="n">
-        <v>5.47706699371338</v>
+        <v>5.47706651687622</v>
       </c>
       <c r="H824" t="s">
         <v>8</v>
@@ -21845,7 +21845,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G826" t="n">
-        <v>5.5486626625061</v>
+        <v>5.54866218566895</v>
       </c>
       <c r="H826" t="s">
         <v>8</v>
@@ -21871,7 +21871,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G827" t="n">
-        <v>5.5486626625061</v>
+        <v>5.54866218566895</v>
       </c>
       <c r="H827" t="s">
         <v>8</v>
@@ -21897,7 +21897,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G828" t="n">
-        <v>5.5486626625061</v>
+        <v>5.54866218566895</v>
       </c>
       <c r="H828" t="s">
         <v>8</v>
@@ -21923,7 +21923,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G829" t="n">
-        <v>5.5486626625061</v>
+        <v>5.54866218566895</v>
       </c>
       <c r="H829" t="s">
         <v>8</v>
@@ -21949,7 +21949,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G830" t="n">
-        <v>5.72765207290649</v>
+        <v>5.72765159606934</v>
       </c>
       <c r="H830" t="s">
         <v>8</v>
@@ -22001,7 +22001,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G832" t="n">
-        <v>5.72765207290649</v>
+        <v>5.72765159606934</v>
       </c>
       <c r="H832" t="s">
         <v>8</v>
@@ -22183,7 +22183,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G839" t="n">
-        <v>5.5486626625061</v>
+        <v>5.54866218566895</v>
       </c>
       <c r="H839" t="s">
         <v>8</v>
@@ -22209,7 +22209,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G840" t="n">
-        <v>5.53076314926147</v>
+        <v>5.53076362609863</v>
       </c>
       <c r="H840" t="s">
         <v>8</v>
@@ -22365,7 +22365,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G846" t="n">
-        <v>5.72765207290649</v>
+        <v>5.72765159606934</v>
       </c>
       <c r="H846" t="s">
         <v>8</v>
@@ -22417,7 +22417,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G848" t="n">
-        <v>5.72765207290649</v>
+        <v>5.72765159606934</v>
       </c>
       <c r="H848" t="s">
         <v>8</v>
@@ -22495,7 +22495,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G851" t="n">
-        <v>5.70975255966187</v>
+        <v>5.70975303649902</v>
       </c>
       <c r="H851" t="s">
         <v>8</v>
@@ -22521,7 +22521,7 @@
         <v>6.5</v>
       </c>
       <c r="G852" t="n">
-        <v>5.81714630126953</v>
+        <v>5.81714582443237</v>
       </c>
       <c r="H852" t="s">
         <v>8</v>
@@ -22547,7 +22547,7 @@
         <v>6.5</v>
       </c>
       <c r="G853" t="n">
-        <v>5.81714630126953</v>
+        <v>5.81714582443237</v>
       </c>
       <c r="H853" t="s">
         <v>8</v>
@@ -22625,7 +22625,7 @@
         <v>6.42000007629395</v>
       </c>
       <c r="G856" t="n">
-        <v>5.74555063247681</v>
+        <v>5.74555110931396</v>
       </c>
       <c r="H856" t="s">
         <v>8</v>
@@ -22651,7 +22651,7 @@
         <v>6.51999998092651</v>
       </c>
       <c r="G857" t="n">
-        <v>5.83504486083984</v>
+        <v>5.835045337677</v>
       </c>
       <c r="H857" t="s">
         <v>8</v>
@@ -22677,7 +22677,7 @@
         <v>6.51999998092651</v>
       </c>
       <c r="G858" t="n">
-        <v>5.83504486083984</v>
+        <v>5.835045337677</v>
       </c>
       <c r="H858" t="s">
         <v>8</v>
@@ -22703,7 +22703,7 @@
         <v>6.51999998092651</v>
       </c>
       <c r="G859" t="n">
-        <v>5.83504486083984</v>
+        <v>5.835045337677</v>
       </c>
       <c r="H859" t="s">
         <v>8</v>
@@ -22807,7 +22807,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G863" t="n">
-        <v>5.88874197006226</v>
+        <v>5.8887414932251</v>
       </c>
       <c r="H863" t="s">
         <v>8</v>
@@ -22859,7 +22859,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G865" t="n">
-        <v>5.88874197006226</v>
+        <v>5.8887414932251</v>
       </c>
       <c r="H865" t="s">
         <v>8</v>
@@ -22937,7 +22937,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G868" t="n">
-        <v>6.08562994003296</v>
+        <v>6.08563041687012</v>
       </c>
       <c r="H868" t="s">
         <v>8</v>
@@ -22963,7 +22963,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G869" t="n">
-        <v>6.08562994003296</v>
+        <v>6.08563041687012</v>
       </c>
       <c r="H869" t="s">
         <v>8</v>
@@ -23223,7 +23223,7 @@
         <v>6.5</v>
       </c>
       <c r="G879" t="n">
-        <v>5.81714630126953</v>
+        <v>5.81714582443237</v>
       </c>
       <c r="H879" t="s">
         <v>8</v>
@@ -23275,7 +23275,7 @@
         <v>6.73999977111816</v>
       </c>
       <c r="G881" t="n">
-        <v>6.03193330764771</v>
+        <v>6.03193283081055</v>
       </c>
       <c r="H881" t="s">
         <v>8</v>
@@ -23327,7 +23327,7 @@
         <v>6.71999979019165</v>
       </c>
       <c r="G883" t="n">
-        <v>6.01403379440308</v>
+        <v>6.01403427124023</v>
       </c>
       <c r="H883" t="s">
         <v>8</v>
@@ -23353,7 +23353,7 @@
         <v>6.71999979019165</v>
       </c>
       <c r="G884" t="n">
-        <v>6.01403379440308</v>
+        <v>6.01403427124023</v>
       </c>
       <c r="H884" t="s">
         <v>8</v>
@@ -23483,7 +23483,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G889" t="n">
-        <v>5.72765207290649</v>
+        <v>5.72765159606934</v>
       </c>
       <c r="H889" t="s">
         <v>8</v>
@@ -23509,7 +23509,7 @@
         <v>6.5</v>
       </c>
       <c r="G890" t="n">
-        <v>5.81714630126953</v>
+        <v>5.81714582443237</v>
       </c>
       <c r="H890" t="s">
         <v>8</v>
@@ -23535,7 +23535,7 @@
         <v>6.71999979019165</v>
       </c>
       <c r="G891" t="n">
-        <v>6.01403379440308</v>
+        <v>6.01403427124023</v>
       </c>
       <c r="H891" t="s">
         <v>8</v>
@@ -23561,7 +23561,7 @@
         <v>6.71999979019165</v>
       </c>
       <c r="G892" t="n">
-        <v>6.01403379440308</v>
+        <v>6.01403427124023</v>
       </c>
       <c r="H892" t="s">
         <v>8</v>
@@ -23587,7 +23587,7 @@
         <v>6.71999979019165</v>
       </c>
       <c r="G893" t="n">
-        <v>6.01403379440308</v>
+        <v>6.01403427124023</v>
       </c>
       <c r="H893" t="s">
         <v>8</v>
@@ -23847,7 +23847,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G903" t="n">
-        <v>6.98057556152344</v>
+        <v>6.9805760383606</v>
       </c>
       <c r="H903" t="s">
         <v>8</v>
@@ -23899,7 +23899,7 @@
         <v>7.57999992370605</v>
       </c>
       <c r="G905" t="n">
-        <v>6.78368759155273</v>
+        <v>6.78368711471558</v>
       </c>
       <c r="H905" t="s">
         <v>8</v>
@@ -23977,7 +23977,7 @@
         <v>7.03999996185303</v>
       </c>
       <c r="G908" t="n">
-        <v>6.30041694641113</v>
+        <v>6.30041646957397</v>
       </c>
       <c r="H908" t="s">
         <v>8</v>
@@ -24029,7 +24029,7 @@
         <v>7.1399998664856</v>
       </c>
       <c r="G910" t="n">
-        <v>6.38991117477417</v>
+        <v>6.38991165161133</v>
       </c>
       <c r="H910" t="s">
         <v>8</v>
@@ -24211,7 +24211,7 @@
         <v>7.26000022888184</v>
       </c>
       <c r="G917" t="n">
-        <v>6.49730491638184</v>
+        <v>6.49730539321899</v>
       </c>
       <c r="H917" t="s">
         <v>8</v>
@@ -24237,7 +24237,7 @@
         <v>7.42000007629395</v>
       </c>
       <c r="G918" t="n">
-        <v>6.64049673080444</v>
+        <v>6.64049625396729</v>
       </c>
       <c r="H918" t="s">
         <v>8</v>
@@ -24315,7 +24315,7 @@
         <v>7.34000015258789</v>
       </c>
       <c r="G921" t="n">
-        <v>6.56890058517456</v>
+        <v>6.56890106201172</v>
       </c>
       <c r="H921" t="s">
         <v>8</v>
@@ -24367,7 +24367,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G923" t="n">
-        <v>6.80158615112305</v>
+        <v>6.80158662796021</v>
       </c>
       <c r="H923" t="s">
         <v>8</v>
@@ -24601,7 +24601,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G932" t="n">
-        <v>6.80158615112305</v>
+        <v>6.80158662796021</v>
       </c>
       <c r="H932" t="s">
         <v>8</v>
@@ -24653,7 +24653,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G934" t="n">
-        <v>6.80158615112305</v>
+        <v>6.80158662796021</v>
       </c>
       <c r="H934" t="s">
         <v>8</v>
@@ -24705,7 +24705,7 @@
         <v>7.34000015258789</v>
       </c>
       <c r="G936" t="n">
-        <v>6.56890058517456</v>
+        <v>6.56890106201172</v>
       </c>
       <c r="H936" t="s">
         <v>8</v>
@@ -24861,7 +24861,7 @@
         <v>7.26000022888184</v>
       </c>
       <c r="G942" t="n">
-        <v>6.49730491638184</v>
+        <v>6.49730539321899</v>
       </c>
       <c r="H942" t="s">
         <v>8</v>
@@ -24887,7 +24887,7 @@
         <v>7.26000022888184</v>
       </c>
       <c r="G943" t="n">
-        <v>6.49730491638184</v>
+        <v>6.49730539321899</v>
       </c>
       <c r="H943" t="s">
         <v>8</v>
@@ -24913,7 +24913,7 @@
         <v>7.26000022888184</v>
       </c>
       <c r="G944" t="n">
-        <v>6.49730491638184</v>
+        <v>6.49730539321899</v>
       </c>
       <c r="H944" t="s">
         <v>8</v>
@@ -24965,7 +24965,7 @@
         <v>7.21999979019165</v>
       </c>
       <c r="G946" t="n">
-        <v>6.46150732040405</v>
+        <v>6.46150684356689</v>
       </c>
       <c r="H946" t="s">
         <v>8</v>
@@ -24991,7 +24991,7 @@
         <v>7.21999979019165</v>
       </c>
       <c r="G947" t="n">
-        <v>6.46150732040405</v>
+        <v>6.46150684356689</v>
       </c>
       <c r="H947" t="s">
         <v>8</v>
@@ -25355,7 +25355,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G961" t="n">
-        <v>6.08562994003296</v>
+        <v>6.08563041687012</v>
       </c>
       <c r="H961" t="s">
         <v>8</v>
@@ -25641,7 +25641,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G972" t="n">
-        <v>6.08562994003296</v>
+        <v>6.08563041687012</v>
       </c>
       <c r="H972" t="s">
         <v>8</v>
@@ -26993,7 +26993,7 @@
         <v>7.25</v>
       </c>
       <c r="G1024" t="n">
-        <v>6.48835563659668</v>
+        <v>6.48835515975952</v>
       </c>
       <c r="H1024" t="s">
         <v>8</v>
@@ -27097,7 +27097,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G1028" t="n">
-        <v>6.84633350372314</v>
+        <v>6.8463339805603</v>
       </c>
       <c r="H1028" t="s">
         <v>8</v>
@@ -27123,7 +27123,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G1029" t="n">
-        <v>6.98057556152344</v>
+        <v>6.9805760383606</v>
       </c>
       <c r="H1029" t="s">
         <v>8</v>
@@ -27149,7 +27149,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G1030" t="n">
-        <v>6.98057556152344</v>
+        <v>6.9805760383606</v>
       </c>
       <c r="H1030" t="s">
         <v>8</v>
@@ -27175,7 +27175,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G1031" t="n">
-        <v>6.98057556152344</v>
+        <v>6.9805760383606</v>
       </c>
       <c r="H1031" t="s">
         <v>8</v>
@@ -27227,7 +27227,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G1033" t="n">
-        <v>6.75683927536011</v>
+        <v>6.75683975219727</v>
       </c>
       <c r="H1033" t="s">
         <v>8</v>
@@ -27253,7 +27253,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G1034" t="n">
-        <v>6.75683927536011</v>
+        <v>6.75683975219727</v>
       </c>
       <c r="H1034" t="s">
         <v>8</v>
@@ -27279,7 +27279,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G1035" t="n">
-        <v>6.75683927536011</v>
+        <v>6.75683975219727</v>
       </c>
       <c r="H1035" t="s">
         <v>8</v>
@@ -27305,7 +27305,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G1036" t="n">
-        <v>6.75683927536011</v>
+        <v>6.75683975219727</v>
       </c>
       <c r="H1036" t="s">
         <v>8</v>
@@ -27331,7 +27331,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G1037" t="n">
-        <v>6.98057556152344</v>
+        <v>6.9805760383606</v>
       </c>
       <c r="H1037" t="s">
         <v>8</v>
@@ -27357,7 +27357,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G1038" t="n">
-        <v>6.80158615112305</v>
+        <v>6.80158662796021</v>
       </c>
       <c r="H1038" t="s">
         <v>8</v>
@@ -27383,7 +27383,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G1039" t="n">
-        <v>6.80158615112305</v>
+        <v>6.80158662796021</v>
       </c>
       <c r="H1039" t="s">
         <v>8</v>
@@ -27435,7 +27435,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G1041" t="n">
-        <v>6.80158615112305</v>
+        <v>6.80158662796021</v>
       </c>
       <c r="H1041" t="s">
         <v>8</v>
@@ -27461,7 +27461,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G1042" t="n">
-        <v>6.80158615112305</v>
+        <v>6.80158662796021</v>
       </c>
       <c r="H1042" t="s">
         <v>8</v>
@@ -27487,7 +27487,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G1043" t="n">
-        <v>6.80158615112305</v>
+        <v>6.80158662796021</v>
       </c>
       <c r="H1043" t="s">
         <v>8</v>
@@ -27513,7 +27513,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G1044" t="n">
-        <v>6.80158615112305</v>
+        <v>6.80158662796021</v>
       </c>
       <c r="H1044" t="s">
         <v>8</v>
@@ -27539,7 +27539,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G1045" t="n">
-        <v>6.80158615112305</v>
+        <v>6.80158662796021</v>
       </c>
       <c r="H1045" t="s">
         <v>8</v>
@@ -27565,7 +27565,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G1046" t="n">
-        <v>6.80158615112305</v>
+        <v>6.80158662796021</v>
       </c>
       <c r="H1046" t="s">
         <v>8</v>
@@ -27591,7 +27591,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G1047" t="n">
-        <v>6.80158615112305</v>
+        <v>6.80158662796021</v>
       </c>
       <c r="H1047" t="s">
         <v>8</v>
@@ -27617,7 +27617,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G1048" t="n">
-        <v>6.98057556152344</v>
+        <v>6.9805760383606</v>
       </c>
       <c r="H1048" t="s">
         <v>8</v>
@@ -27643,7 +27643,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G1049" t="n">
-        <v>6.84633350372314</v>
+        <v>6.8463339805603</v>
       </c>
       <c r="H1049" t="s">
         <v>8</v>
@@ -27669,7 +27669,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G1050" t="n">
-        <v>6.98057556152344</v>
+        <v>6.9805760383606</v>
       </c>
       <c r="H1050" t="s">
         <v>8</v>
@@ -27695,7 +27695,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G1051" t="n">
-        <v>6.98057556152344</v>
+        <v>6.9805760383606</v>
       </c>
       <c r="H1051" t="s">
         <v>8</v>
@@ -27721,7 +27721,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G1052" t="n">
-        <v>6.98057556152344</v>
+        <v>6.9805760383606</v>
       </c>
       <c r="H1052" t="s">
         <v>8</v>
@@ -27747,7 +27747,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G1053" t="n">
-        <v>6.80158615112305</v>
+        <v>6.80158662796021</v>
       </c>
       <c r="H1053" t="s">
         <v>8</v>
@@ -27903,7 +27903,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G1059" t="n">
-        <v>6.75683927536011</v>
+        <v>6.75683975219727</v>
       </c>
       <c r="H1059" t="s">
         <v>8</v>
@@ -27929,7 +27929,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G1060" t="n">
-        <v>6.75683927536011</v>
+        <v>6.75683975219727</v>
       </c>
       <c r="H1060" t="s">
         <v>8</v>
@@ -27955,7 +27955,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G1061" t="n">
-        <v>6.75683927536011</v>
+        <v>6.75683975219727</v>
       </c>
       <c r="H1061" t="s">
         <v>8</v>
@@ -28371,7 +28371,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G1077" t="n">
-        <v>5.86189365386963</v>
+        <v>5.86189413070679</v>
       </c>
       <c r="H1077" t="s">
         <v>8</v>
@@ -28397,7 +28397,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G1078" t="n">
-        <v>5.72765207290649</v>
+        <v>5.72765159606934</v>
       </c>
       <c r="H1078" t="s">
         <v>8</v>
@@ -28423,7 +28423,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G1079" t="n">
-        <v>5.86189365386963</v>
+        <v>5.86189413070679</v>
       </c>
       <c r="H1079" t="s">
         <v>8</v>
@@ -28501,7 +28501,7 @@
         <v>6</v>
       </c>
       <c r="G1082" t="n">
-        <v>5.36967372894287</v>
+        <v>5.36967325210571</v>
       </c>
       <c r="H1082" t="s">
         <v>8</v>
@@ -28527,7 +28527,7 @@
         <v>6</v>
       </c>
       <c r="G1083" t="n">
-        <v>5.36967372894287</v>
+        <v>5.36967325210571</v>
       </c>
       <c r="H1083" t="s">
         <v>8</v>
@@ -28553,7 +28553,7 @@
         <v>6</v>
       </c>
       <c r="G1084" t="n">
-        <v>5.36967372894287</v>
+        <v>5.36967325210571</v>
       </c>
       <c r="H1084" t="s">
         <v>8</v>
@@ -28605,7 +28605,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G1086" t="n">
-        <v>5.32492637634277</v>
+        <v>5.32492589950562</v>
       </c>
       <c r="H1086" t="s">
         <v>8</v>
@@ -28631,7 +28631,7 @@
         <v>6</v>
       </c>
       <c r="G1087" t="n">
-        <v>5.36967372894287</v>
+        <v>5.36967325210571</v>
       </c>
       <c r="H1087" t="s">
         <v>8</v>
@@ -28657,7 +28657,7 @@
         <v>6</v>
       </c>
       <c r="G1088" t="n">
-        <v>5.36967372894287</v>
+        <v>5.36967325210571</v>
       </c>
       <c r="H1088" t="s">
         <v>8</v>
@@ -28683,7 +28683,7 @@
         <v>6</v>
       </c>
       <c r="G1089" t="n">
-        <v>5.36967372894287</v>
+        <v>5.36967325210571</v>
       </c>
       <c r="H1089" t="s">
         <v>8</v>
@@ -28709,7 +28709,7 @@
         <v>6</v>
       </c>
       <c r="G1090" t="n">
-        <v>5.36967372894287</v>
+        <v>5.36967325210571</v>
       </c>
       <c r="H1090" t="s">
         <v>8</v>
@@ -28735,7 +28735,7 @@
         <v>6</v>
       </c>
       <c r="G1091" t="n">
-        <v>5.36967372894287</v>
+        <v>5.36967325210571</v>
       </c>
       <c r="H1091" t="s">
         <v>8</v>
@@ -28761,7 +28761,7 @@
         <v>6</v>
       </c>
       <c r="G1092" t="n">
-        <v>5.36967372894287</v>
+        <v>5.36967325210571</v>
       </c>
       <c r="H1092" t="s">
         <v>8</v>
@@ -28787,7 +28787,7 @@
         <v>6</v>
       </c>
       <c r="G1093" t="n">
-        <v>5.36967372894287</v>
+        <v>5.36967325210571</v>
       </c>
       <c r="H1093" t="s">
         <v>8</v>
@@ -28813,7 +28813,7 @@
         <v>6</v>
       </c>
       <c r="G1094" t="n">
-        <v>5.36967372894287</v>
+        <v>5.36967325210571</v>
       </c>
       <c r="H1094" t="s">
         <v>8</v>
@@ -28839,7 +28839,7 @@
         <v>6</v>
       </c>
       <c r="G1095" t="n">
-        <v>5.36967372894287</v>
+        <v>5.36967325210571</v>
       </c>
       <c r="H1095" t="s">
         <v>8</v>
@@ -29099,7 +29099,7 @@
         <v>6.25</v>
       </c>
       <c r="G1105" t="n">
-        <v>5.5934100151062</v>
+        <v>5.59340953826904</v>
       </c>
       <c r="H1105" t="s">
         <v>8</v>
@@ -29125,7 +29125,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G1106" t="n">
-        <v>5.5486626625061</v>
+        <v>5.54866218566895</v>
       </c>
       <c r="H1106" t="s">
         <v>8</v>
@@ -29229,7 +29229,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G1110" t="n">
-        <v>5.5486626625061</v>
+        <v>5.54866218566895</v>
       </c>
       <c r="H1110" t="s">
         <v>8</v>
@@ -29281,7 +29281,7 @@
         <v>6.5</v>
       </c>
       <c r="G1112" t="n">
-        <v>5.81714630126953</v>
+        <v>5.81714582443237</v>
       </c>
       <c r="H1112" t="s">
         <v>8</v>
@@ -29307,7 +29307,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G1113" t="n">
-        <v>5.72765207290649</v>
+        <v>5.72765159606934</v>
       </c>
       <c r="H1113" t="s">
         <v>8</v>
@@ -29333,7 +29333,7 @@
         <v>6.5</v>
       </c>
       <c r="G1114" t="n">
-        <v>5.81714630126953</v>
+        <v>5.81714582443237</v>
       </c>
       <c r="H1114" t="s">
         <v>8</v>
@@ -29437,7 +29437,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G1118" t="n">
-        <v>6.08562994003296</v>
+        <v>6.08563041687012</v>
       </c>
       <c r="H1118" t="s">
         <v>8</v>
@@ -29593,7 +29593,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G1124" t="n">
-        <v>6.75683927536011</v>
+        <v>6.75683975219727</v>
       </c>
       <c r="H1124" t="s">
         <v>8</v>
@@ -47874,6 +47874,32 @@
         <v>2.57999992370605</v>
       </c>
       <c r="H1827" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1828">
+      <c r="A1828" s="1" t="n">
+        <v>46288.2916666667</v>
+      </c>
+      <c r="B1828" t="n">
+        <v>7520</v>
+      </c>
+      <c r="C1828" t="n">
+        <v>2.53999996185303</v>
+      </c>
+      <c r="D1828" t="n">
+        <v>2.40000009536743</v>
+      </c>
+      <c r="E1828" t="n">
+        <v>2.53999996185303</v>
+      </c>
+      <c r="F1828" t="n">
+        <v>2.51999998092651</v>
+      </c>
+      <c r="G1828" t="n">
+        <v>2.51999998092651</v>
+      </c>
+      <c r="H1828" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/PTR.MI.xlsx
+++ b/data/PTR.MI.xlsx
@@ -551,7 +551,7 @@
         <v>3.56850004196167</v>
       </c>
       <c r="G7" t="n">
-        <v>3.0973117351532</v>
+        <v>3.09731197357178</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>3.5864999294281</v>
       </c>
       <c r="G8" t="n">
-        <v>3.11293506622314</v>
+        <v>3.11293482780457</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>3.43199992179871</v>
       </c>
       <c r="G10" t="n">
-        <v>2.978835105896</v>
+        <v>2.97883534431458</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G14" t="n">
-        <v>3.12465262413025</v>
+        <v>3.12465238571167</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G19" t="n">
-        <v>3.13333177566528</v>
+        <v>3.13333201408386</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G20" t="n">
-        <v>3.12465262413025</v>
+        <v>3.12465238571167</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G22" t="n">
-        <v>3.09861373901367</v>
+        <v>3.09861326217651</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G26" t="n">
-        <v>2.96841979026794</v>
+        <v>2.96842002868652</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>3.35050010681152</v>
       </c>
       <c r="G27" t="n">
-        <v>2.90809655189514</v>
+        <v>2.90809679031372</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>3.48200011253357</v>
       </c>
       <c r="G32" t="n">
-        <v>3.02223348617554</v>
+        <v>3.02223324775696</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>3.48200011253357</v>
       </c>
       <c r="G33" t="n">
-        <v>3.02223348617554</v>
+        <v>3.02223324775696</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G34" t="n">
-        <v>3.10729312896729</v>
+        <v>3.10729360580444</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G38" t="n">
-        <v>3.19408893585205</v>
+        <v>3.19408917427063</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G41" t="n">
-        <v>3.42843794822693</v>
+        <v>3.42843818664551</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G42" t="n">
-        <v>3.29824423789978</v>
+        <v>3.2982439994812</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>3.67499995231628</v>
       </c>
       <c r="G44" t="n">
-        <v>3.18974947929382</v>
+        <v>3.18974900245667</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G45" t="n">
-        <v>3.17672991752625</v>
+        <v>3.17673015594482</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>3.71499991416931</v>
       </c>
       <c r="G46" t="n">
-        <v>3.22446775436401</v>
+        <v>3.22446751594543</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>3.64499998092651</v>
       </c>
       <c r="G47" t="n">
-        <v>3.16371035575867</v>
+        <v>3.16371059417725</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>3.71499991416931</v>
       </c>
       <c r="G50" t="n">
-        <v>3.22446775436401</v>
+        <v>3.22446751594543</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G53" t="n">
-        <v>3.17672991752625</v>
+        <v>3.17673015594482</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G55" t="n">
-        <v>3.16805076599121</v>
+        <v>3.16805052757263</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G58" t="n">
-        <v>3.17672991752625</v>
+        <v>3.17673015594482</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>3.66499996185303</v>
       </c>
       <c r="G59" t="n">
-        <v>3.18106961250305</v>
+        <v>3.18106985092163</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>3.66499996185303</v>
       </c>
       <c r="G61" t="n">
-        <v>3.18106961250305</v>
+        <v>3.18106985092163</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>3.5550000667572</v>
       </c>
       <c r="G64" t="n">
-        <v>3.08559441566467</v>
+        <v>3.08559417724609</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>3.5550000667572</v>
       </c>
       <c r="G65" t="n">
-        <v>3.08559441566467</v>
+        <v>3.08559417724609</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G66" t="n">
-        <v>3.09861373901367</v>
+        <v>3.09861326217651</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>3.63499999046326</v>
       </c>
       <c r="G67" t="n">
-        <v>3.15503096580505</v>
+        <v>3.15503120422363</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G68" t="n">
-        <v>3.12465262413025</v>
+        <v>3.12465238571167</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G69" t="n">
-        <v>3.12465262413025</v>
+        <v>3.12465238571167</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G70" t="n">
-        <v>3.16805076599121</v>
+        <v>3.16805052757263</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G72" t="n">
-        <v>3.12465262413025</v>
+        <v>3.12465238571167</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G78" t="n">
-        <v>3.12465262413025</v>
+        <v>3.12465238571167</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>3.67499995231628</v>
       </c>
       <c r="G80" t="n">
-        <v>3.18974947929382</v>
+        <v>3.18974900245667</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G81" t="n">
-        <v>3.15937089920044</v>
+        <v>3.15937066078186</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G83" t="n">
-        <v>3.29824423789978</v>
+        <v>3.2982439994812</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G84" t="n">
-        <v>3.29824423789978</v>
+        <v>3.2982439994812</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G85" t="n">
-        <v>3.29824423789978</v>
+        <v>3.2982439994812</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G86" t="n">
-        <v>3.29824423789978</v>
+        <v>3.2982439994812</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G88" t="n">
-        <v>3.42843794822693</v>
+        <v>3.42843818664551</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G89" t="n">
-        <v>3.42843794822693</v>
+        <v>3.42843818664551</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G90" t="n">
-        <v>3.41975879669189</v>
+        <v>3.41975855827332</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G91" t="n">
-        <v>3.51523423194885</v>
+        <v>3.51523375511169</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>4</v>
       </c>
       <c r="G92" t="n">
-        <v>3.47183609008789</v>
+        <v>3.47183585166931</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G94" t="n">
-        <v>3.41975879669189</v>
+        <v>3.41975855827332</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G95" t="n">
-        <v>3.51523423194885</v>
+        <v>3.51523375511169</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>4.02500009536743</v>
       </c>
       <c r="G96" t="n">
-        <v>3.49353528022766</v>
+        <v>3.49353504180908</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G97" t="n">
-        <v>3.42843794822693</v>
+        <v>3.42843818664551</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>4.00500011444092</v>
       </c>
       <c r="G98" t="n">
-        <v>3.47617602348328</v>
+        <v>3.47617626190186</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G99" t="n">
-        <v>3.59334993362427</v>
+        <v>3.59335017204285</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G102" t="n">
-        <v>3.44579720497131</v>
+        <v>3.44579744338989</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>4</v>
       </c>
       <c r="G103" t="n">
-        <v>3.47183609008789</v>
+        <v>3.47183585166931</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>4</v>
       </c>
       <c r="G105" t="n">
-        <v>3.47183609008789</v>
+        <v>3.47183585166931</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>4.03499984741211</v>
       </c>
       <c r="G106" t="n">
-        <v>3.50221419334412</v>
+        <v>3.50221467018127</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G107" t="n">
-        <v>3.51523423194885</v>
+        <v>3.51523375511169</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G108" t="n">
-        <v>3.54995226860046</v>
+        <v>3.54995250701904</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G109" t="n">
-        <v>3.54995226860046</v>
+        <v>3.54995250701904</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>4.41499996185303</v>
       </c>
       <c r="G112" t="n">
-        <v>3.83203911781311</v>
+        <v>3.83203864097595</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>4.5</v>
       </c>
       <c r="G113" t="n">
-        <v>3.90581583976746</v>
+        <v>3.90581512451172</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>4.5</v>
       </c>
       <c r="G114" t="n">
-        <v>3.90581583976746</v>
+        <v>3.90581512451172</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G115" t="n">
-        <v>3.87109684944153</v>
+        <v>3.87109708786011</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G116" t="n">
-        <v>3.86241745948792</v>
+        <v>3.86241793632507</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G119" t="n">
-        <v>3.96657299995422</v>
+        <v>3.96657228469849</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G120" t="n">
-        <v>3.86241745948792</v>
+        <v>3.86241793632507</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G121" t="n">
-        <v>3.92317461967468</v>
+        <v>3.92317509651184</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G123" t="n">
-        <v>3.88845634460449</v>
+        <v>3.88845610618591</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G124" t="n">
-        <v>3.94921350479126</v>
+        <v>3.94921374320984</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G125" t="n">
-        <v>3.94921350479126</v>
+        <v>3.94921374320984</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G128" t="n">
-        <v>4.37451314926147</v>
+        <v>4.37451410293579</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G131" t="n">
-        <v>4.49602794647217</v>
+        <v>4.49602746963501</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G132" t="n">
-        <v>4.49602794647217</v>
+        <v>4.49602746963501</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G141" t="n">
-        <v>4.42659091949463</v>
+        <v>4.42659044265747</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G142" t="n">
-        <v>4.35715436935425</v>
+        <v>4.35715389251709</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G144" t="n">
-        <v>4.42659091949463</v>
+        <v>4.42659044265747</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G147" t="n">
-        <v>4.70433855056763</v>
+        <v>4.70433759689331</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G148" t="n">
-        <v>4.49602794647217</v>
+        <v>4.49602746963501</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>5.13000011444092</v>
       </c>
       <c r="G150" t="n">
-        <v>4.45263004302979</v>
+        <v>4.45262956619263</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G153" t="n">
-        <v>4.44394969940186</v>
+        <v>4.44395017623901</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G154" t="n">
-        <v>4.00129127502441</v>
+        <v>4.00129079818726</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G156" t="n">
-        <v>4.31375551223755</v>
+        <v>4.31375598907471</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G157" t="n">
-        <v>4.23564004898071</v>
+        <v>4.23563957214355</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G158" t="n">
-        <v>4.00129127502441</v>
+        <v>4.00129079818726</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G159" t="n">
-        <v>4.09676599502563</v>
+        <v>4.09676647186279</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G161" t="n">
-        <v>4.04468870162964</v>
+        <v>4.0446891784668</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>4.24499988555908</v>
       </c>
       <c r="G163" t="n">
-        <v>3.68448615074158</v>
+        <v>3.68448567390442</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G164" t="n">
-        <v>3.17672991752625</v>
+        <v>3.17673015594482</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G166" t="n">
-        <v>3.23748683929443</v>
+        <v>3.23748707771301</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G167" t="n">
-        <v>2.72539114952087</v>
+        <v>2.72539138793945</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G170" t="n">
-        <v>3.12465262413025</v>
+        <v>3.12465238571167</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G173" t="n">
-        <v>3.09861373901367</v>
+        <v>3.09861326217651</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G177" t="n">
-        <v>3.09861373901367</v>
+        <v>3.09861326217651</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G178" t="n">
-        <v>3.28956437110901</v>
+        <v>3.28956460952759</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G180" t="n">
-        <v>3.31560349464417</v>
+        <v>3.31560325622559</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G182" t="n">
-        <v>3.28956437110901</v>
+        <v>3.28956460952759</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G183" t="n">
-        <v>3.19408893585205</v>
+        <v>3.19408917427063</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G185" t="n">
-        <v>3.19408893585205</v>
+        <v>3.19408917427063</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G188" t="n">
-        <v>3.29824423789978</v>
+        <v>3.2982439994812</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G189" t="n">
-        <v>3.2288076877594</v>
+        <v>3.22880744934082</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G190" t="n">
-        <v>3.18540978431702</v>
+        <v>3.18540954589844</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G192" t="n">
-        <v>3.33296251296997</v>
+        <v>3.33296227455139</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G193" t="n">
-        <v>3.29824423789978</v>
+        <v>3.2982439994812</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G194" t="n">
-        <v>3.29824423789978</v>
+        <v>3.2982439994812</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G195" t="n">
-        <v>3.34164190292358</v>
+        <v>3.34164237976074</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G196" t="n">
-        <v>3.35900163650513</v>
+        <v>3.35900115966797</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G197" t="n">
-        <v>3.35900163650513</v>
+        <v>3.35900115966797</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G198" t="n">
-        <v>3.59334993362427</v>
+        <v>3.59335017204285</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G199" t="n">
-        <v>3.54995226860046</v>
+        <v>3.54995250701904</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G201" t="n">
-        <v>3.33296251296997</v>
+        <v>3.33296227455139</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G204" t="n">
-        <v>3.19408893585205</v>
+        <v>3.19408917427063</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G205" t="n">
-        <v>3.29824423789978</v>
+        <v>3.2982439994812</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G206" t="n">
-        <v>3.31560349464417</v>
+        <v>3.31560325622559</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G210" t="n">
-        <v>3.2288076877594</v>
+        <v>3.22880744934082</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G211" t="n">
-        <v>3.29824423789978</v>
+        <v>3.2982439994812</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G212" t="n">
-        <v>3.27220559120178</v>
+        <v>3.2722053527832</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G213" t="n">
-        <v>3.2288076877594</v>
+        <v>3.22880744934082</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G217" t="n">
-        <v>3.29824423789978</v>
+        <v>3.2982439994812</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G219" t="n">
-        <v>3.29824423789978</v>
+        <v>3.2982439994812</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G221" t="n">
-        <v>3.28956437110901</v>
+        <v>3.28956460952759</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G222" t="n">
-        <v>3.29824423789978</v>
+        <v>3.2982439994812</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G223" t="n">
-        <v>3.34164190292358</v>
+        <v>3.34164237976074</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G224" t="n">
-        <v>3.38504004478455</v>
+        <v>3.38504028320312</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G225" t="n">
-        <v>3.35900163650513</v>
+        <v>3.35900115966797</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G227" t="n">
-        <v>3.29824423789978</v>
+        <v>3.2982439994812</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G228" t="n">
-        <v>3.42843794822693</v>
+        <v>3.42843818664551</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G229" t="n">
-        <v>3.27220559120178</v>
+        <v>3.2722053527832</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G231" t="n">
-        <v>3.31560349464417</v>
+        <v>3.31560325622559</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G232" t="n">
-        <v>3.35032153129578</v>
+        <v>3.35032176971436</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G237" t="n">
-        <v>3.28956437110901</v>
+        <v>3.28956460952759</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G238" t="n">
-        <v>3.23748683929443</v>
+        <v>3.23748707771301</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G239" t="n">
-        <v>3.23748683929443</v>
+        <v>3.23748707771301</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G240" t="n">
-        <v>3.29824423789978</v>
+        <v>3.2982439994812</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G241" t="n">
-        <v>3.34164190292358</v>
+        <v>3.34164237976074</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G242" t="n">
-        <v>3.28956437110901</v>
+        <v>3.28956460952759</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G243" t="n">
-        <v>3.28956437110901</v>
+        <v>3.28956460952759</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G244" t="n">
-        <v>3.42843794822693</v>
+        <v>3.42843818664551</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G245" t="n">
-        <v>3.27220559120178</v>
+        <v>3.2722053527832</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G246" t="n">
-        <v>3.29824423789978</v>
+        <v>3.2982439994812</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G249" t="n">
-        <v>3.15937089920044</v>
+        <v>3.15937066078186</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G250" t="n">
-        <v>3.16805076599121</v>
+        <v>3.16805052757263</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G251" t="n">
-        <v>3.18540978431702</v>
+        <v>3.18540954589844</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G254" t="n">
-        <v>3.28956437110901</v>
+        <v>3.28956460952759</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G255" t="n">
-        <v>3.18540978431702</v>
+        <v>3.18540954589844</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G256" t="n">
-        <v>3.2288076877594</v>
+        <v>3.22880744934082</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G259" t="n">
-        <v>3.2288076877594</v>
+        <v>3.22880744934082</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G262" t="n">
-        <v>3.16805076599121</v>
+        <v>3.16805052757263</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G264" t="n">
-        <v>3.13333177566528</v>
+        <v>3.13333201408386</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G270" t="n">
-        <v>3.19408893585205</v>
+        <v>3.19408917427063</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G271" t="n">
-        <v>3.13333177566528</v>
+        <v>3.13333201408386</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G272" t="n">
-        <v>3.12465262413025</v>
+        <v>3.12465238571167</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G273" t="n">
-        <v>3.02049732208252</v>
+        <v>3.0204975605011</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G274" t="n">
-        <v>2.93370175361633</v>
+        <v>2.93370151519775</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G275" t="n">
-        <v>2.96841979026794</v>
+        <v>2.96842002868652</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G277" t="n">
-        <v>3.02049732208252</v>
+        <v>3.0204975605011</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G281" t="n">
-        <v>3.06389498710632</v>
+        <v>3.0638952255249</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G282" t="n">
-        <v>3.06389498710632</v>
+        <v>3.0638952255249</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G283" t="n">
-        <v>3.06389498710632</v>
+        <v>3.0638952255249</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G284" t="n">
-        <v>2.94238090515137</v>
+        <v>2.94238114356995</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G285" t="n">
-        <v>2.94238090515137</v>
+        <v>2.94238114356995</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G303" t="n">
-        <v>2.8816237449646</v>
+        <v>2.88162398338318</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G307" t="n">
-        <v>3.12465262413025</v>
+        <v>3.12465238571167</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G308" t="n">
-        <v>3.12465262413025</v>
+        <v>3.12465238571167</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G309" t="n">
-        <v>3.16805076599121</v>
+        <v>3.16805052757263</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G310" t="n">
-        <v>3.16805076599121</v>
+        <v>3.16805052757263</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G314" t="n">
-        <v>3.19408893585205</v>
+        <v>3.19408917427063</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G318" t="n">
-        <v>3.17672991752625</v>
+        <v>3.17673015594482</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G322" t="n">
-        <v>3.16805076599121</v>
+        <v>3.16805052757263</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G326" t="n">
-        <v>3.19408893585205</v>
+        <v>3.19408917427063</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G329" t="n">
-        <v>3.12465262413025</v>
+        <v>3.12465238571167</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G330" t="n">
-        <v>3.19408893585205</v>
+        <v>3.19408917427063</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G339" t="n">
-        <v>3.15937089920044</v>
+        <v>3.15937066078186</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G347" t="n">
-        <v>3.31560349464417</v>
+        <v>3.31560325622559</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G348" t="n">
-        <v>3.42843794822693</v>
+        <v>3.42843818664551</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G349" t="n">
-        <v>3.31560349464417</v>
+        <v>3.31560325622559</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G351" t="n">
-        <v>3.31560349464417</v>
+        <v>3.31560325622559</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G352" t="n">
-        <v>3.34164190292358</v>
+        <v>3.34164237976074</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9547,7 +9547,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G353" t="n">
-        <v>3.28956437110901</v>
+        <v>3.28956460952759</v>
       </c>
       <c r="H353" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G354" t="n">
-        <v>3.34164190292358</v>
+        <v>3.34164237976074</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G356" t="n">
-        <v>3.42843794822693</v>
+        <v>3.42843818664551</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G357" t="n">
-        <v>3.42843794822693</v>
+        <v>3.42843818664551</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>4</v>
       </c>
       <c r="G359" t="n">
-        <v>3.47183609008789</v>
+        <v>3.47183585166931</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>4</v>
       </c>
       <c r="G360" t="n">
-        <v>3.47183609008789</v>
+        <v>3.47183585166931</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G361" t="n">
-        <v>3.46304678916931</v>
+        <v>3.46304655075073</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G362" t="n">
-        <v>3.52457308769226</v>
+        <v>3.52457284927368</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G365" t="n">
-        <v>3.55973076820374</v>
+        <v>3.55973052978516</v>
       </c>
       <c r="H365" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G366" t="n">
-        <v>3.47183585166931</v>
+        <v>3.47183609008789</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G373" t="n">
-        <v>3.77946734428406</v>
+        <v>3.77946710586548</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G374" t="n">
-        <v>3.85857200622559</v>
+        <v>3.85857224464417</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10119,7 +10119,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G375" t="n">
-        <v>3.80583524703979</v>
+        <v>3.80583548545837</v>
       </c>
       <c r="H375" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G376" t="n">
-        <v>3.82341432571411</v>
+        <v>3.82341384887695</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G377" t="n">
-        <v>3.70915126800537</v>
+        <v>3.70915102958679</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G378" t="n">
-        <v>3.84978270530701</v>
+        <v>3.84978246688843</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G379" t="n">
-        <v>3.90251970291138</v>
+        <v>3.9025194644928</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>4.5</v>
       </c>
       <c r="G381" t="n">
-        <v>3.95525646209717</v>
+        <v>3.95525622367859</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G382" t="n">
-        <v>3.92888784408569</v>
+        <v>3.92888760566711</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G383" t="n">
-        <v>3.92009806632996</v>
+        <v>3.92009830474854</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G384" t="n">
-        <v>3.77946734428406</v>
+        <v>3.77946710586548</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G385" t="n">
-        <v>3.77946734428406</v>
+        <v>3.77946710586548</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G386" t="n">
-        <v>3.647625207901</v>
+        <v>3.64762496948242</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10457,7 +10457,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G388" t="n">
-        <v>3.55094122886658</v>
+        <v>3.550940990448</v>
       </c>
       <c r="H388" t="s">
         <v>8</v>
@@ -10483,7 +10483,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G389" t="n">
-        <v>3.58609890937805</v>
+        <v>3.58609867095947</v>
       </c>
       <c r="H389" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G390" t="n">
-        <v>3.69157242774963</v>
+        <v>3.69157195091248</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G391" t="n">
-        <v>3.52457308769226</v>
+        <v>3.52457284927368</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G392" t="n">
-        <v>3.62125658988953</v>
+        <v>3.62125682830811</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10587,7 +10587,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G393" t="n">
-        <v>3.67399311065674</v>
+        <v>3.67399334907532</v>
       </c>
       <c r="H393" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G394" t="n">
-        <v>3.67399311065674</v>
+        <v>3.67399334907532</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G396" t="n">
-        <v>3.77946734428406</v>
+        <v>3.77946710586548</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G397" t="n">
-        <v>3.82341432571411</v>
+        <v>3.82341384887695</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G398" t="n">
-        <v>3.77946734428406</v>
+        <v>3.77946710586548</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G399" t="n">
-        <v>3.70915126800537</v>
+        <v>3.70915102958679</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G400" t="n">
-        <v>3.62125658988953</v>
+        <v>3.62125682830811</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10795,7 +10795,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G401" t="n">
-        <v>3.58609890937805</v>
+        <v>3.58609867095947</v>
       </c>
       <c r="H401" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G402" t="n">
-        <v>3.60367798805237</v>
+        <v>3.60367774963379</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G403" t="n">
-        <v>3.6827826499939</v>
+        <v>3.68278336524963</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G404" t="n">
-        <v>3.90251970291138</v>
+        <v>3.9025194644928</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G405" t="n">
-        <v>3.84978270530701</v>
+        <v>3.84978246688843</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -10925,7 +10925,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G406" t="n">
-        <v>3.84099316596985</v>
+        <v>3.84099292755127</v>
       </c>
       <c r="H406" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G408" t="n">
-        <v>3.78825664520264</v>
+        <v>3.78825640678406</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G410" t="n">
-        <v>3.99920344352722</v>
+        <v>3.99920392036438</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G411" t="n">
-        <v>3.99920344352722</v>
+        <v>3.99920392036438</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G412" t="n">
-        <v>3.97283506393433</v>
+        <v>3.97283530235291</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G416" t="n">
-        <v>3.99920344352722</v>
+        <v>3.99920392036438</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>4.59000015258789</v>
       </c>
       <c r="G417" t="n">
-        <v>4.03436136245728</v>
+        <v>4.03436183929443</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11289,7 +11289,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G420" t="n">
-        <v>4.30683422088623</v>
+        <v>4.30683469772339</v>
       </c>
       <c r="H420" t="s">
         <v>8</v>
@@ -11367,7 +11367,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G423" t="n">
-        <v>4.28046560287476</v>
+        <v>4.28046607971191</v>
       </c>
       <c r="H423" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G424" t="n">
-        <v>4.30683422088623</v>
+        <v>4.30683469772339</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G425" t="n">
-        <v>4.29804515838623</v>
+        <v>4.29804468154907</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G426" t="n">
-        <v>4.25409841537476</v>
+        <v>4.25409746170044</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G438" t="n">
-        <v>4.25409841537476</v>
+        <v>4.25409746170044</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G439" t="n">
-        <v>4.3859395980835</v>
+        <v>4.38593912124634</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G440" t="n">
-        <v>4.3859395980835</v>
+        <v>4.38593912124634</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G441" t="n">
-        <v>4.30683422088623</v>
+        <v>4.30683469772339</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11861,7 +11861,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G442" t="n">
-        <v>4.30683422088623</v>
+        <v>4.30683469772339</v>
       </c>
       <c r="H442" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G443" t="n">
-        <v>4.35078144073486</v>
+        <v>4.35078191757202</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G447" t="n">
-        <v>4.3859395980835</v>
+        <v>4.38593912124634</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G448" t="n">
-        <v>4.41230821609497</v>
+        <v>4.41230773925781</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G451" t="n">
-        <v>4.30683422088623</v>
+        <v>4.30683469772339</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G459" t="n">
-        <v>4.02557182312012</v>
+        <v>4.02557229995728</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G460" t="n">
-        <v>4.02557182312012</v>
+        <v>4.02557229995728</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12355,7 +12355,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G461" t="n">
-        <v>4.02557182312012</v>
+        <v>4.02557229995728</v>
       </c>
       <c r="H461" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G467" t="n">
-        <v>4.35078144073486</v>
+        <v>4.35078191757202</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12537,7 +12537,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G468" t="n">
-        <v>4.50020217895508</v>
+        <v>4.50020265579224</v>
       </c>
       <c r="H468" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G474" t="n">
-        <v>4.57807350158691</v>
+        <v>4.57807397842407</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -13265,7 +13265,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G496" t="n">
-        <v>4.10966062545776</v>
+        <v>4.10966110229492</v>
       </c>
       <c r="H496" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G503" t="n">
-        <v>4.10966062545776</v>
+        <v>4.10966110229492</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13473,7 +13473,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G504" t="n">
-        <v>4.10966062545776</v>
+        <v>4.10966110229492</v>
       </c>
       <c r="H504" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G506" t="n">
-        <v>4.10082244873047</v>
+        <v>4.10082292556763</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G511" t="n">
-        <v>4.10966062545776</v>
+        <v>4.10966110229492</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13681,7 +13681,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G512" t="n">
-        <v>4.10966062545776</v>
+        <v>4.10966110229492</v>
       </c>
       <c r="H512" t="s">
         <v>8</v>
@@ -13785,7 +13785,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G516" t="n">
-        <v>4.32177257537842</v>
+        <v>4.32177209854126</v>
       </c>
       <c r="H516" t="s">
         <v>8</v>
@@ -13889,7 +13889,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G520" t="n">
-        <v>4.48969411849976</v>
+        <v>4.4896936416626</v>
       </c>
       <c r="H520" t="s">
         <v>8</v>
@@ -13941,7 +13941,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G522" t="n">
-        <v>4.5957498550415</v>
+        <v>4.59574937820435</v>
       </c>
       <c r="H522" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G523" t="n">
-        <v>4.5957498550415</v>
+        <v>4.59574937820435</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -13993,7 +13993,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G524" t="n">
-        <v>4.5957498550415</v>
+        <v>4.59574937820435</v>
       </c>
       <c r="H524" t="s">
         <v>8</v>
@@ -14019,7 +14019,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G525" t="n">
-        <v>4.5957498550415</v>
+        <v>4.59574937820435</v>
       </c>
       <c r="H525" t="s">
         <v>8</v>
@@ -14045,7 +14045,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G526" t="n">
-        <v>4.57807350158691</v>
+        <v>4.57807397842407</v>
       </c>
       <c r="H526" t="s">
         <v>8</v>
@@ -14071,7 +14071,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G527" t="n">
-        <v>4.57807350158691</v>
+        <v>4.57807397842407</v>
       </c>
       <c r="H527" t="s">
         <v>8</v>
@@ -14123,7 +14123,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G529" t="n">
-        <v>4.45434188842773</v>
+        <v>4.45434236526489</v>
       </c>
       <c r="H529" t="s">
         <v>8</v>
@@ -14487,7 +14487,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G543" t="n">
-        <v>4.38363790512085</v>
+        <v>4.38363838195801</v>
       </c>
       <c r="H543" t="s">
         <v>8</v>
@@ -14513,7 +14513,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G544" t="n">
-        <v>4.36596202850342</v>
+        <v>4.36596250534058</v>
       </c>
       <c r="H544" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G545" t="n">
-        <v>4.36596202850342</v>
+        <v>4.36596250534058</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14747,7 +14747,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G553" t="n">
-        <v>4.31293487548828</v>
+        <v>4.31293439865112</v>
       </c>
       <c r="H553" t="s">
         <v>8</v>
@@ -14825,7 +14825,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G556" t="n">
-        <v>4.11849880218506</v>
+        <v>4.1184983253479</v>
       </c>
       <c r="H556" t="s">
         <v>8</v>
@@ -14851,7 +14851,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G557" t="n">
-        <v>4.07430934906006</v>
+        <v>4.0743088722229</v>
       </c>
       <c r="H557" t="s">
         <v>8</v>
@@ -14877,7 +14877,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G558" t="n">
-        <v>4.10966062545776</v>
+        <v>4.10966110229492</v>
       </c>
       <c r="H558" t="s">
         <v>8</v>
@@ -14981,7 +14981,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G562" t="n">
-        <v>4.10966062545776</v>
+        <v>4.10966110229492</v>
       </c>
       <c r="H562" t="s">
         <v>8</v>
@@ -15163,7 +15163,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G569" t="n">
-        <v>4.57807350158691</v>
+        <v>4.57807397842407</v>
       </c>
       <c r="H569" t="s">
         <v>8</v>
@@ -15189,7 +15189,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G570" t="n">
-        <v>4.5957498550415</v>
+        <v>4.59574937820435</v>
       </c>
       <c r="H570" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G573" t="n">
-        <v>4.73715734481812</v>
+        <v>4.73715782165527</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15371,7 +15371,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G577" t="n">
-        <v>4.91391706466675</v>
+        <v>4.91391658782959</v>
       </c>
       <c r="H577" t="s">
         <v>8</v>
@@ -15423,7 +15423,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G579" t="n">
-        <v>4.89624071121216</v>
+        <v>4.89624118804932</v>
       </c>
       <c r="H579" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G581" t="n">
-        <v>5.10835313796997</v>
+        <v>5.10835266113281</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15501,7 +15501,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G582" t="n">
-        <v>5.26743650436401</v>
+        <v>5.26743602752686</v>
       </c>
       <c r="H582" t="s">
         <v>8</v>
@@ -15553,7 +15553,7 @@
         <v>6.03999996185303</v>
       </c>
       <c r="G584" t="n">
-        <v>5.3381404876709</v>
+        <v>5.33814001083374</v>
       </c>
       <c r="H584" t="s">
         <v>8</v>
@@ -15761,7 +15761,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G592" t="n">
-        <v>5.51489925384521</v>
+        <v>5.51489973068237</v>
       </c>
       <c r="H592" t="s">
         <v>8</v>
@@ -15787,7 +15787,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G593" t="n">
-        <v>5.56792736053467</v>
+        <v>5.56792783737183</v>
       </c>
       <c r="H593" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G594" t="n">
-        <v>5.56792736053467</v>
+        <v>5.56792783737183</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15969,7 +15969,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G600" t="n">
-        <v>5.72701120376587</v>
+        <v>5.72701168060303</v>
       </c>
       <c r="H600" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G602" t="n">
-        <v>5.49722385406494</v>
+        <v>5.49722337722778</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16073,7 +16073,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G604" t="n">
-        <v>5.51489925384521</v>
+        <v>5.51489973068237</v>
       </c>
       <c r="H604" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G605" t="n">
-        <v>5.72701120376587</v>
+        <v>5.72701168060303</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G606" t="n">
-        <v>5.72701120376587</v>
+        <v>5.72701168060303</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G611" t="n">
-        <v>5.72701120376587</v>
+        <v>5.72701168060303</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16281,7 +16281,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G612" t="n">
-        <v>5.72701120376587</v>
+        <v>5.72701168060303</v>
       </c>
       <c r="H612" t="s">
         <v>8</v>
@@ -16385,7 +16385,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G616" t="n">
-        <v>5.88609504699707</v>
+        <v>5.88609457015991</v>
       </c>
       <c r="H616" t="s">
         <v>8</v>
@@ -16411,7 +16411,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G617" t="n">
-        <v>5.92144632339478</v>
+        <v>5.92144680023193</v>
       </c>
       <c r="H617" t="s">
         <v>8</v>
@@ -16541,7 +16541,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G622" t="n">
-        <v>5.39116811752319</v>
+        <v>5.39116764068604</v>
       </c>
       <c r="H622" t="s">
         <v>8</v>
@@ -16671,7 +16671,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G627" t="n">
-        <v>6.00982713699341</v>
+        <v>6.00982666015625</v>
       </c>
       <c r="H627" t="s">
         <v>8</v>
@@ -16697,7 +16697,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G628" t="n">
-        <v>5.88609504699707</v>
+        <v>5.88609457015991</v>
       </c>
       <c r="H628" t="s">
         <v>8</v>
@@ -16723,7 +16723,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G629" t="n">
-        <v>5.92144632339478</v>
+        <v>5.92144680023193</v>
       </c>
       <c r="H629" t="s">
         <v>8</v>
@@ -16749,7 +16749,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G630" t="n">
-        <v>6.00982713699341</v>
+        <v>6.00982666015625</v>
       </c>
       <c r="H630" t="s">
         <v>8</v>
@@ -16827,7 +16827,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G633" t="n">
-        <v>5.83306694030762</v>
+        <v>5.83306741714478</v>
       </c>
       <c r="H633" t="s">
         <v>8</v>
@@ -16853,7 +16853,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G634" t="n">
-        <v>5.83306694030762</v>
+        <v>5.83306741714478</v>
       </c>
       <c r="H634" t="s">
         <v>8</v>
@@ -16879,7 +16879,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G635" t="n">
-        <v>5.83306694030762</v>
+        <v>5.83306741714478</v>
       </c>
       <c r="H635" t="s">
         <v>8</v>
@@ -16931,7 +16931,7 @@
         <v>6.44000005722046</v>
       </c>
       <c r="G637" t="n">
-        <v>5.69165945053101</v>
+        <v>5.69165897369385</v>
       </c>
       <c r="H637" t="s">
         <v>8</v>
@@ -16983,7 +16983,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G639" t="n">
-        <v>5.58560371398926</v>
+        <v>5.5856032371521</v>
       </c>
       <c r="H639" t="s">
         <v>8</v>
@@ -17191,7 +17191,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G647" t="n">
-        <v>5.37349224090576</v>
+        <v>5.3734917640686</v>
       </c>
       <c r="H647" t="s">
         <v>8</v>
@@ -17217,7 +17217,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G648" t="n">
-        <v>5.26743650436401</v>
+        <v>5.26743602752686</v>
       </c>
       <c r="H648" t="s">
         <v>8</v>
@@ -17243,7 +17243,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G649" t="n">
-        <v>5.39116811752319</v>
+        <v>5.39116764068604</v>
       </c>
       <c r="H649" t="s">
         <v>8</v>
@@ -17321,7 +17321,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G652" t="n">
-        <v>5.21440839767456</v>
+        <v>5.2144079208374</v>
       </c>
       <c r="H652" t="s">
         <v>8</v>
@@ -17347,7 +17347,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G653" t="n">
-        <v>5.12602853775024</v>
+        <v>5.1260290145874</v>
       </c>
       <c r="H653" t="s">
         <v>8</v>
@@ -17477,7 +17477,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G658" t="n">
-        <v>5.12602853775024</v>
+        <v>5.1260290145874</v>
       </c>
       <c r="H658" t="s">
         <v>8</v>
@@ -17529,7 +17529,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G660" t="n">
-        <v>5.23208427429199</v>
+        <v>5.23208475112915</v>
       </c>
       <c r="H660" t="s">
         <v>8</v>
@@ -17815,7 +17815,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G671" t="n">
-        <v>4.57807350158691</v>
+        <v>4.57807397842407</v>
       </c>
       <c r="H671" t="s">
         <v>8</v>
@@ -18179,7 +18179,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G685" t="n">
-        <v>4.5957498550415</v>
+        <v>4.59574937820435</v>
       </c>
       <c r="H685" t="s">
         <v>8</v>
@@ -18231,7 +18231,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G687" t="n">
-        <v>4.45434188842773</v>
+        <v>4.45434236526489</v>
       </c>
       <c r="H687" t="s">
         <v>8</v>
@@ -18309,7 +18309,7 @@
         <v>5.5</v>
       </c>
       <c r="G690" t="n">
-        <v>4.86088943481445</v>
+        <v>4.86088895797729</v>
       </c>
       <c r="H690" t="s">
         <v>8</v>
@@ -18361,7 +18361,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G692" t="n">
-        <v>4.87856483459473</v>
+        <v>4.87856531143188</v>
       </c>
       <c r="H692" t="s">
         <v>8</v>
@@ -18387,7 +18387,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G693" t="n">
-        <v>4.87856483459473</v>
+        <v>4.87856531143188</v>
       </c>
       <c r="H693" t="s">
         <v>8</v>
@@ -18413,7 +18413,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G694" t="n">
-        <v>4.93159294128418</v>
+        <v>4.93159341812134</v>
       </c>
       <c r="H694" t="s">
         <v>8</v>
@@ -18439,7 +18439,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G695" t="n">
-        <v>4.87856483459473</v>
+        <v>4.87856531143188</v>
       </c>
       <c r="H695" t="s">
         <v>8</v>
@@ -18543,7 +18543,7 @@
         <v>5.5</v>
       </c>
       <c r="G699" t="n">
-        <v>4.86088943481445</v>
+        <v>4.86088895797729</v>
       </c>
       <c r="H699" t="s">
         <v>8</v>
@@ -18725,7 +18725,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G706" t="n">
-        <v>5.12602853775024</v>
+        <v>5.1260290145874</v>
       </c>
       <c r="H706" t="s">
         <v>8</v>
@@ -18777,7 +18777,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G708" t="n">
-        <v>4.98462104797363</v>
+        <v>4.98462057113647</v>
       </c>
       <c r="H708" t="s">
         <v>8</v>
@@ -18803,7 +18803,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G709" t="n">
-        <v>5.12602853775024</v>
+        <v>5.1260290145874</v>
       </c>
       <c r="H709" t="s">
         <v>8</v>
@@ -18829,7 +18829,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G710" t="n">
-        <v>5.12602853775024</v>
+        <v>5.1260290145874</v>
       </c>
       <c r="H710" t="s">
         <v>8</v>
@@ -18907,7 +18907,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G713" t="n">
-        <v>5.16138076782227</v>
+        <v>5.16138029098511</v>
       </c>
       <c r="H713" t="s">
         <v>8</v>
@@ -19141,7 +19141,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G722" t="n">
-        <v>5.16138076782227</v>
+        <v>5.16138029098511</v>
       </c>
       <c r="H722" t="s">
         <v>8</v>
@@ -19167,7 +19167,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G723" t="n">
-        <v>5.16138076782227</v>
+        <v>5.16138029098511</v>
       </c>
       <c r="H723" t="s">
         <v>8</v>
@@ -19193,7 +19193,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G724" t="n">
-        <v>5.24976015090942</v>
+        <v>5.24976062774658</v>
       </c>
       <c r="H724" t="s">
         <v>8</v>
@@ -19427,7 +19427,7 @@
         <v>5.8600001335144</v>
       </c>
       <c r="G733" t="n">
-        <v>5.24438095092773</v>
+        <v>5.24438142776489</v>
       </c>
       <c r="H733" t="s">
         <v>8</v>
@@ -19453,7 +19453,7 @@
         <v>5.8600001335144</v>
       </c>
       <c r="G734" t="n">
-        <v>5.24438095092773</v>
+        <v>5.24438142776489</v>
       </c>
       <c r="H734" t="s">
         <v>8</v>
@@ -19557,7 +19557,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G738" t="n">
-        <v>5.26228046417236</v>
+        <v>5.26227998733521</v>
       </c>
       <c r="H738" t="s">
         <v>8</v>
@@ -19895,7 +19895,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G751" t="n">
-        <v>4.99379587173462</v>
+        <v>4.99379634857178</v>
       </c>
       <c r="H751" t="s">
         <v>8</v>
@@ -20077,7 +20077,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G758" t="n">
-        <v>5.31597661972046</v>
+        <v>5.31597709655762</v>
       </c>
       <c r="H758" t="s">
         <v>8</v>
@@ -20103,7 +20103,7 @@
         <v>6</v>
       </c>
       <c r="G759" t="n">
-        <v>5.36967325210571</v>
+        <v>5.36967372894287</v>
       </c>
       <c r="H759" t="s">
         <v>8</v>
@@ -20129,7 +20129,7 @@
         <v>6</v>
       </c>
       <c r="G760" t="n">
-        <v>5.36967325210571</v>
+        <v>5.36967372894287</v>
       </c>
       <c r="H760" t="s">
         <v>8</v>
@@ -20155,7 +20155,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G761" t="n">
-        <v>5.47706651687622</v>
+        <v>5.47706699371338</v>
       </c>
       <c r="H761" t="s">
         <v>8</v>
@@ -20337,7 +20337,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G768" t="n">
-        <v>5.72765159606934</v>
+        <v>5.72765207290649</v>
       </c>
       <c r="H768" t="s">
         <v>8</v>
@@ -20389,7 +20389,7 @@
         <v>6.51999998092651</v>
       </c>
       <c r="G770" t="n">
-        <v>5.835045337677</v>
+        <v>5.83504486083984</v>
       </c>
       <c r="H770" t="s">
         <v>8</v>
@@ -20415,7 +20415,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G771" t="n">
-        <v>5.72765159606934</v>
+        <v>5.72765207290649</v>
       </c>
       <c r="H771" t="s">
         <v>8</v>
@@ -20441,7 +20441,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G772" t="n">
-        <v>5.72765159606934</v>
+        <v>5.72765207290649</v>
       </c>
       <c r="H772" t="s">
         <v>8</v>
@@ -20519,7 +20519,7 @@
         <v>6.5</v>
       </c>
       <c r="G775" t="n">
-        <v>5.81714582443237</v>
+        <v>5.81714630126953</v>
       </c>
       <c r="H775" t="s">
         <v>8</v>
@@ -20571,7 +20571,7 @@
         <v>6.5</v>
       </c>
       <c r="G777" t="n">
-        <v>5.81714582443237</v>
+        <v>5.81714630126953</v>
       </c>
       <c r="H777" t="s">
         <v>8</v>
@@ -20675,7 +20675,7 @@
         <v>6.73999977111816</v>
       </c>
       <c r="G781" t="n">
-        <v>6.03193283081055</v>
+        <v>6.03193330764771</v>
       </c>
       <c r="H781" t="s">
         <v>8</v>
@@ -20753,7 +20753,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G784" t="n">
-        <v>6.08563041687012</v>
+        <v>6.08562994003296</v>
       </c>
       <c r="H784" t="s">
         <v>8</v>
@@ -20883,7 +20883,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G789" t="n">
-        <v>5.8887414932251</v>
+        <v>5.88874197006226</v>
       </c>
       <c r="H789" t="s">
         <v>8</v>
@@ -20935,7 +20935,7 @@
         <v>6.53999996185303</v>
       </c>
       <c r="G791" t="n">
-        <v>5.85294389724731</v>
+        <v>5.85294437408447</v>
       </c>
       <c r="H791" t="s">
         <v>8</v>
@@ -20961,7 +20961,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G792" t="n">
-        <v>5.72765159606934</v>
+        <v>5.72765207290649</v>
       </c>
       <c r="H792" t="s">
         <v>8</v>
@@ -21091,7 +21091,7 @@
         <v>6.5</v>
       </c>
       <c r="G797" t="n">
-        <v>5.81714582443237</v>
+        <v>5.81714630126953</v>
       </c>
       <c r="H797" t="s">
         <v>8</v>
@@ -21117,7 +21117,7 @@
         <v>6.5</v>
       </c>
       <c r="G798" t="n">
-        <v>5.81714582443237</v>
+        <v>5.81714630126953</v>
       </c>
       <c r="H798" t="s">
         <v>8</v>
@@ -21195,7 +21195,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G801" t="n">
-        <v>5.8887414932251</v>
+        <v>5.88874197006226</v>
       </c>
       <c r="H801" t="s">
         <v>8</v>
@@ -21351,7 +21351,7 @@
         <v>6.42000007629395</v>
       </c>
       <c r="G807" t="n">
-        <v>5.74555110931396</v>
+        <v>5.74555063247681</v>
       </c>
       <c r="H807" t="s">
         <v>8</v>
@@ -21455,7 +21455,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G811" t="n">
-        <v>5.54866218566895</v>
+        <v>5.5486626625061</v>
       </c>
       <c r="H811" t="s">
         <v>8</v>
@@ -21507,7 +21507,7 @@
         <v>5.8600001335144</v>
       </c>
       <c r="G813" t="n">
-        <v>5.24438095092773</v>
+        <v>5.24438142776489</v>
       </c>
       <c r="H813" t="s">
         <v>8</v>
@@ -21533,7 +21533,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G814" t="n">
-        <v>5.13698720932007</v>
+        <v>5.13698768615723</v>
       </c>
       <c r="H814" t="s">
         <v>8</v>
@@ -21559,7 +21559,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G815" t="n">
-        <v>5.13698720932007</v>
+        <v>5.13698768615723</v>
       </c>
       <c r="H815" t="s">
         <v>8</v>
@@ -21585,7 +21585,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G816" t="n">
-        <v>5.3517746925354</v>
+        <v>5.35177421569824</v>
       </c>
       <c r="H816" t="s">
         <v>8</v>
@@ -21611,7 +21611,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G817" t="n">
-        <v>4.83270597457886</v>
+        <v>4.83270645141602</v>
       </c>
       <c r="H817" t="s">
         <v>8</v>
@@ -21715,7 +21715,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G821" t="n">
-        <v>4.83270597457886</v>
+        <v>4.83270645141602</v>
       </c>
       <c r="H821" t="s">
         <v>8</v>
@@ -21767,7 +21767,7 @@
         <v>6</v>
       </c>
       <c r="G823" t="n">
-        <v>5.36967325210571</v>
+        <v>5.36967372894287</v>
       </c>
       <c r="H823" t="s">
         <v>8</v>
@@ -21793,7 +21793,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G824" t="n">
-        <v>5.47706651687622</v>
+        <v>5.47706699371338</v>
       </c>
       <c r="H824" t="s">
         <v>8</v>
@@ -21845,7 +21845,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G826" t="n">
-        <v>5.54866218566895</v>
+        <v>5.5486626625061</v>
       </c>
       <c r="H826" t="s">
         <v>8</v>
@@ -21871,7 +21871,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G827" t="n">
-        <v>5.54866218566895</v>
+        <v>5.5486626625061</v>
       </c>
       <c r="H827" t="s">
         <v>8</v>
@@ -21897,7 +21897,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G828" t="n">
-        <v>5.54866218566895</v>
+        <v>5.5486626625061</v>
       </c>
       <c r="H828" t="s">
         <v>8</v>
@@ -21923,7 +21923,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G829" t="n">
-        <v>5.54866218566895</v>
+        <v>5.5486626625061</v>
       </c>
       <c r="H829" t="s">
         <v>8</v>
@@ -21949,7 +21949,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G830" t="n">
-        <v>5.72765159606934</v>
+        <v>5.72765207290649</v>
       </c>
       <c r="H830" t="s">
         <v>8</v>
@@ -22001,7 +22001,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G832" t="n">
-        <v>5.72765159606934</v>
+        <v>5.72765207290649</v>
       </c>
       <c r="H832" t="s">
         <v>8</v>
@@ -22183,7 +22183,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G839" t="n">
-        <v>5.54866218566895</v>
+        <v>5.5486626625061</v>
       </c>
       <c r="H839" t="s">
         <v>8</v>
@@ -22209,7 +22209,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G840" t="n">
-        <v>5.53076362609863</v>
+        <v>5.53076314926147</v>
       </c>
       <c r="H840" t="s">
         <v>8</v>
@@ -22365,7 +22365,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G846" t="n">
-        <v>5.72765159606934</v>
+        <v>5.72765207290649</v>
       </c>
       <c r="H846" t="s">
         <v>8</v>
@@ -22417,7 +22417,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G848" t="n">
-        <v>5.72765159606934</v>
+        <v>5.72765207290649</v>
       </c>
       <c r="H848" t="s">
         <v>8</v>
@@ -22495,7 +22495,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G851" t="n">
-        <v>5.70975303649902</v>
+        <v>5.70975255966187</v>
       </c>
       <c r="H851" t="s">
         <v>8</v>
@@ -22521,7 +22521,7 @@
         <v>6.5</v>
       </c>
       <c r="G852" t="n">
-        <v>5.81714582443237</v>
+        <v>5.81714630126953</v>
       </c>
       <c r="H852" t="s">
         <v>8</v>
@@ -22547,7 +22547,7 @@
         <v>6.5</v>
       </c>
       <c r="G853" t="n">
-        <v>5.81714582443237</v>
+        <v>5.81714630126953</v>
       </c>
       <c r="H853" t="s">
         <v>8</v>
@@ -22625,7 +22625,7 @@
         <v>6.42000007629395</v>
       </c>
       <c r="G856" t="n">
-        <v>5.74555110931396</v>
+        <v>5.74555063247681</v>
       </c>
       <c r="H856" t="s">
         <v>8</v>
@@ -22651,7 +22651,7 @@
         <v>6.51999998092651</v>
       </c>
       <c r="G857" t="n">
-        <v>5.835045337677</v>
+        <v>5.83504486083984</v>
       </c>
       <c r="H857" t="s">
         <v>8</v>
@@ -22677,7 +22677,7 @@
         <v>6.51999998092651</v>
       </c>
       <c r="G858" t="n">
-        <v>5.835045337677</v>
+        <v>5.83504486083984</v>
       </c>
       <c r="H858" t="s">
         <v>8</v>
@@ -22703,7 +22703,7 @@
         <v>6.51999998092651</v>
       </c>
       <c r="G859" t="n">
-        <v>5.835045337677</v>
+        <v>5.83504486083984</v>
       </c>
       <c r="H859" t="s">
         <v>8</v>
@@ -22807,7 +22807,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G863" t="n">
-        <v>5.8887414932251</v>
+        <v>5.88874197006226</v>
       </c>
       <c r="H863" t="s">
         <v>8</v>
@@ -22859,7 +22859,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G865" t="n">
-        <v>5.8887414932251</v>
+        <v>5.88874197006226</v>
       </c>
       <c r="H865" t="s">
         <v>8</v>
@@ -22937,7 +22937,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G868" t="n">
-        <v>6.08563041687012</v>
+        <v>6.08562994003296</v>
       </c>
       <c r="H868" t="s">
         <v>8</v>
@@ -22963,7 +22963,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G869" t="n">
-        <v>6.08563041687012</v>
+        <v>6.08562994003296</v>
       </c>
       <c r="H869" t="s">
         <v>8</v>
@@ -23223,7 +23223,7 @@
         <v>6.5</v>
       </c>
       <c r="G879" t="n">
-        <v>5.81714582443237</v>
+        <v>5.81714630126953</v>
       </c>
       <c r="H879" t="s">
         <v>8</v>
@@ -23275,7 +23275,7 @@
         <v>6.73999977111816</v>
       </c>
       <c r="G881" t="n">
-        <v>6.03193283081055</v>
+        <v>6.03193330764771</v>
       </c>
       <c r="H881" t="s">
         <v>8</v>
@@ -23327,7 +23327,7 @@
         <v>6.71999979019165</v>
       </c>
       <c r="G883" t="n">
-        <v>6.01403427124023</v>
+        <v>6.01403379440308</v>
       </c>
       <c r="H883" t="s">
         <v>8</v>
@@ -23353,7 +23353,7 @@
         <v>6.71999979019165</v>
       </c>
       <c r="G884" t="n">
-        <v>6.01403427124023</v>
+        <v>6.01403379440308</v>
       </c>
       <c r="H884" t="s">
         <v>8</v>
@@ -23483,7 +23483,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G889" t="n">
-        <v>5.72765159606934</v>
+        <v>5.72765207290649</v>
       </c>
       <c r="H889" t="s">
         <v>8</v>
@@ -23509,7 +23509,7 @@
         <v>6.5</v>
       </c>
       <c r="G890" t="n">
-        <v>5.81714582443237</v>
+        <v>5.81714630126953</v>
       </c>
       <c r="H890" t="s">
         <v>8</v>
@@ -23535,7 +23535,7 @@
         <v>6.71999979019165</v>
       </c>
       <c r="G891" t="n">
-        <v>6.01403427124023</v>
+        <v>6.01403379440308</v>
       </c>
       <c r="H891" t="s">
         <v>8</v>
@@ -23561,7 +23561,7 @@
         <v>6.71999979019165</v>
       </c>
       <c r="G892" t="n">
-        <v>6.01403427124023</v>
+        <v>6.01403379440308</v>
       </c>
       <c r="H892" t="s">
         <v>8</v>
@@ -23587,7 +23587,7 @@
         <v>6.71999979019165</v>
       </c>
       <c r="G893" t="n">
-        <v>6.01403427124023</v>
+        <v>6.01403379440308</v>
       </c>
       <c r="H893" t="s">
         <v>8</v>
@@ -23847,7 +23847,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G903" t="n">
-        <v>6.9805760383606</v>
+        <v>6.98057556152344</v>
       </c>
       <c r="H903" t="s">
         <v>8</v>
@@ -23899,7 +23899,7 @@
         <v>7.57999992370605</v>
       </c>
       <c r="G905" t="n">
-        <v>6.78368711471558</v>
+        <v>6.78368759155273</v>
       </c>
       <c r="H905" t="s">
         <v>8</v>
@@ -23977,7 +23977,7 @@
         <v>7.03999996185303</v>
       </c>
       <c r="G908" t="n">
-        <v>6.30041646957397</v>
+        <v>6.30041694641113</v>
       </c>
       <c r="H908" t="s">
         <v>8</v>
@@ -24029,7 +24029,7 @@
         <v>7.1399998664856</v>
       </c>
       <c r="G910" t="n">
-        <v>6.38991165161133</v>
+        <v>6.38991117477417</v>
       </c>
       <c r="H910" t="s">
         <v>8</v>
@@ -24211,7 +24211,7 @@
         <v>7.26000022888184</v>
       </c>
       <c r="G917" t="n">
-        <v>6.49730539321899</v>
+        <v>6.49730491638184</v>
       </c>
       <c r="H917" t="s">
         <v>8</v>
@@ -24237,7 +24237,7 @@
         <v>7.42000007629395</v>
       </c>
       <c r="G918" t="n">
-        <v>6.64049625396729</v>
+        <v>6.64049673080444</v>
       </c>
       <c r="H918" t="s">
         <v>8</v>
@@ -24315,7 +24315,7 @@
         <v>7.34000015258789</v>
       </c>
       <c r="G921" t="n">
-        <v>6.56890106201172</v>
+        <v>6.56890058517456</v>
       </c>
       <c r="H921" t="s">
         <v>8</v>
@@ -24367,7 +24367,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G923" t="n">
-        <v>6.80158662796021</v>
+        <v>6.80158615112305</v>
       </c>
       <c r="H923" t="s">
         <v>8</v>
@@ -24601,7 +24601,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G932" t="n">
-        <v>6.80158662796021</v>
+        <v>6.80158615112305</v>
       </c>
       <c r="H932" t="s">
         <v>8</v>
@@ -24653,7 +24653,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G934" t="n">
-        <v>6.80158662796021</v>
+        <v>6.80158615112305</v>
       </c>
       <c r="H934" t="s">
         <v>8</v>
@@ -24705,7 +24705,7 @@
         <v>7.34000015258789</v>
       </c>
       <c r="G936" t="n">
-        <v>6.56890106201172</v>
+        <v>6.56890058517456</v>
       </c>
       <c r="H936" t="s">
         <v>8</v>
@@ -24861,7 +24861,7 @@
         <v>7.26000022888184</v>
       </c>
       <c r="G942" t="n">
-        <v>6.49730539321899</v>
+        <v>6.49730491638184</v>
       </c>
       <c r="H942" t="s">
         <v>8</v>
@@ -24887,7 +24887,7 @@
         <v>7.26000022888184</v>
       </c>
       <c r="G943" t="n">
-        <v>6.49730539321899</v>
+        <v>6.49730491638184</v>
       </c>
       <c r="H943" t="s">
         <v>8</v>
@@ -24913,7 +24913,7 @@
         <v>7.26000022888184</v>
       </c>
       <c r="G944" t="n">
-        <v>6.49730539321899</v>
+        <v>6.49730491638184</v>
       </c>
       <c r="H944" t="s">
         <v>8</v>
@@ -24965,7 +24965,7 @@
         <v>7.21999979019165</v>
       </c>
       <c r="G946" t="n">
-        <v>6.46150684356689</v>
+        <v>6.46150732040405</v>
       </c>
       <c r="H946" t="s">
         <v>8</v>
@@ -24991,7 +24991,7 @@
         <v>7.21999979019165</v>
       </c>
       <c r="G947" t="n">
-        <v>6.46150684356689</v>
+        <v>6.46150732040405</v>
       </c>
       <c r="H947" t="s">
         <v>8</v>
@@ -25355,7 +25355,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G961" t="n">
-        <v>6.08563041687012</v>
+        <v>6.08562994003296</v>
       </c>
       <c r="H961" t="s">
         <v>8</v>
@@ -25641,7 +25641,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G972" t="n">
-        <v>6.08563041687012</v>
+        <v>6.08562994003296</v>
       </c>
       <c r="H972" t="s">
         <v>8</v>
@@ -26993,7 +26993,7 @@
         <v>7.25</v>
       </c>
       <c r="G1024" t="n">
-        <v>6.48835515975952</v>
+        <v>6.48835563659668</v>
       </c>
       <c r="H1024" t="s">
         <v>8</v>
@@ -27097,7 +27097,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G1028" t="n">
-        <v>6.8463339805603</v>
+        <v>6.84633350372314</v>
       </c>
       <c r="H1028" t="s">
         <v>8</v>
@@ -27123,7 +27123,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G1029" t="n">
-        <v>6.9805760383606</v>
+        <v>6.98057556152344</v>
       </c>
       <c r="H1029" t="s">
         <v>8</v>
@@ -27149,7 +27149,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G1030" t="n">
-        <v>6.9805760383606</v>
+        <v>6.98057556152344</v>
       </c>
       <c r="H1030" t="s">
         <v>8</v>
@@ -27175,7 +27175,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G1031" t="n">
-        <v>6.9805760383606</v>
+        <v>6.98057556152344</v>
       </c>
       <c r="H1031" t="s">
         <v>8</v>
@@ -27227,7 +27227,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G1033" t="n">
-        <v>6.75683975219727</v>
+        <v>6.75683927536011</v>
       </c>
       <c r="H1033" t="s">
         <v>8</v>
@@ -27253,7 +27253,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G1034" t="n">
-        <v>6.75683975219727</v>
+        <v>6.75683927536011</v>
       </c>
       <c r="H1034" t="s">
         <v>8</v>
@@ -27279,7 +27279,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G1035" t="n">
-        <v>6.75683975219727</v>
+        <v>6.75683927536011</v>
       </c>
       <c r="H1035" t="s">
         <v>8</v>
@@ -27305,7 +27305,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G1036" t="n">
-        <v>6.75683975219727</v>
+        <v>6.75683927536011</v>
       </c>
       <c r="H1036" t="s">
         <v>8</v>
@@ -27331,7 +27331,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G1037" t="n">
-        <v>6.9805760383606</v>
+        <v>6.98057556152344</v>
       </c>
       <c r="H1037" t="s">
         <v>8</v>
@@ -27357,7 +27357,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G1038" t="n">
-        <v>6.80158662796021</v>
+        <v>6.80158615112305</v>
       </c>
       <c r="H1038" t="s">
         <v>8</v>
@@ -27383,7 +27383,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G1039" t="n">
-        <v>6.80158662796021</v>
+        <v>6.80158615112305</v>
       </c>
       <c r="H1039" t="s">
         <v>8</v>
@@ -27435,7 +27435,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G1041" t="n">
-        <v>6.80158662796021</v>
+        <v>6.80158615112305</v>
       </c>
       <c r="H1041" t="s">
         <v>8</v>
@@ -27461,7 +27461,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G1042" t="n">
-        <v>6.80158662796021</v>
+        <v>6.80158615112305</v>
       </c>
       <c r="H1042" t="s">
         <v>8</v>
@@ -27487,7 +27487,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G1043" t="n">
-        <v>6.80158662796021</v>
+        <v>6.80158615112305</v>
       </c>
       <c r="H1043" t="s">
         <v>8</v>
@@ -27513,7 +27513,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G1044" t="n">
-        <v>6.80158662796021</v>
+        <v>6.80158615112305</v>
       </c>
       <c r="H1044" t="s">
         <v>8</v>
@@ -27539,7 +27539,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G1045" t="n">
-        <v>6.80158662796021</v>
+        <v>6.80158615112305</v>
       </c>
       <c r="H1045" t="s">
         <v>8</v>
@@ -27565,7 +27565,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G1046" t="n">
-        <v>6.80158662796021</v>
+        <v>6.80158615112305</v>
       </c>
       <c r="H1046" t="s">
         <v>8</v>
@@ -27591,7 +27591,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G1047" t="n">
-        <v>6.80158662796021</v>
+        <v>6.80158615112305</v>
       </c>
       <c r="H1047" t="s">
         <v>8</v>
@@ -27617,7 +27617,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G1048" t="n">
-        <v>6.9805760383606</v>
+        <v>6.98057556152344</v>
       </c>
       <c r="H1048" t="s">
         <v>8</v>
@@ -27643,7 +27643,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G1049" t="n">
-        <v>6.8463339805603</v>
+        <v>6.84633350372314</v>
       </c>
       <c r="H1049" t="s">
         <v>8</v>
@@ -27669,7 +27669,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G1050" t="n">
-        <v>6.9805760383606</v>
+        <v>6.98057556152344</v>
       </c>
       <c r="H1050" t="s">
         <v>8</v>
@@ -27695,7 +27695,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G1051" t="n">
-        <v>6.9805760383606</v>
+        <v>6.98057556152344</v>
       </c>
       <c r="H1051" t="s">
         <v>8</v>
@@ -27721,7 +27721,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G1052" t="n">
-        <v>6.9805760383606</v>
+        <v>6.98057556152344</v>
       </c>
       <c r="H1052" t="s">
         <v>8</v>
@@ -27747,7 +27747,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G1053" t="n">
-        <v>6.80158662796021</v>
+        <v>6.80158615112305</v>
       </c>
       <c r="H1053" t="s">
         <v>8</v>
@@ -27903,7 +27903,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G1059" t="n">
-        <v>6.75683975219727</v>
+        <v>6.75683927536011</v>
       </c>
       <c r="H1059" t="s">
         <v>8</v>
@@ -27929,7 +27929,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G1060" t="n">
-        <v>6.75683975219727</v>
+        <v>6.75683927536011</v>
       </c>
       <c r="H1060" t="s">
         <v>8</v>
@@ -27955,7 +27955,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G1061" t="n">
-        <v>6.75683975219727</v>
+        <v>6.75683927536011</v>
       </c>
       <c r="H1061" t="s">
         <v>8</v>
@@ -28371,7 +28371,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G1077" t="n">
-        <v>5.86189413070679</v>
+        <v>5.86189365386963</v>
       </c>
       <c r="H1077" t="s">
         <v>8</v>
@@ -28397,7 +28397,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G1078" t="n">
-        <v>5.72765159606934</v>
+        <v>5.72765207290649</v>
       </c>
       <c r="H1078" t="s">
         <v>8</v>
@@ -28423,7 +28423,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G1079" t="n">
-        <v>5.86189413070679</v>
+        <v>5.86189365386963</v>
       </c>
       <c r="H1079" t="s">
         <v>8</v>
@@ -28501,7 +28501,7 @@
         <v>6</v>
       </c>
       <c r="G1082" t="n">
-        <v>5.36967325210571</v>
+        <v>5.36967372894287</v>
       </c>
       <c r="H1082" t="s">
         <v>8</v>
@@ -28527,7 +28527,7 @@
         <v>6</v>
       </c>
       <c r="G1083" t="n">
-        <v>5.36967325210571</v>
+        <v>5.36967372894287</v>
       </c>
       <c r="H1083" t="s">
         <v>8</v>
@@ -28553,7 +28553,7 @@
         <v>6</v>
       </c>
       <c r="G1084" t="n">
-        <v>5.36967325210571</v>
+        <v>5.36967372894287</v>
       </c>
       <c r="H1084" t="s">
         <v>8</v>
@@ -28605,7 +28605,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G1086" t="n">
-        <v>5.32492589950562</v>
+        <v>5.32492637634277</v>
       </c>
       <c r="H1086" t="s">
         <v>8</v>
@@ -28631,7 +28631,7 @@
         <v>6</v>
       </c>
       <c r="G1087" t="n">
-        <v>5.36967325210571</v>
+        <v>5.36967372894287</v>
       </c>
       <c r="H1087" t="s">
         <v>8</v>
@@ -28657,7 +28657,7 @@
         <v>6</v>
       </c>
       <c r="G1088" t="n">
-        <v>5.36967325210571</v>
+        <v>5.36967372894287</v>
       </c>
       <c r="H1088" t="s">
         <v>8</v>
@@ -28683,7 +28683,7 @@
         <v>6</v>
       </c>
       <c r="G1089" t="n">
-        <v>5.36967325210571</v>
+        <v>5.36967372894287</v>
       </c>
       <c r="H1089" t="s">
         <v>8</v>
@@ -28709,7 +28709,7 @@
         <v>6</v>
       </c>
       <c r="G1090" t="n">
-        <v>5.36967325210571</v>
+        <v>5.36967372894287</v>
       </c>
       <c r="H1090" t="s">
         <v>8</v>
@@ -28735,7 +28735,7 @@
         <v>6</v>
       </c>
       <c r="G1091" t="n">
-        <v>5.36967325210571</v>
+        <v>5.36967372894287</v>
       </c>
       <c r="H1091" t="s">
         <v>8</v>
@@ -28761,7 +28761,7 @@
         <v>6</v>
       </c>
       <c r="G1092" t="n">
-        <v>5.36967325210571</v>
+        <v>5.36967372894287</v>
       </c>
       <c r="H1092" t="s">
         <v>8</v>
@@ -28787,7 +28787,7 @@
         <v>6</v>
       </c>
       <c r="G1093" t="n">
-        <v>5.36967325210571</v>
+        <v>5.36967372894287</v>
       </c>
       <c r="H1093" t="s">
         <v>8</v>
@@ -28813,7 +28813,7 @@
         <v>6</v>
       </c>
       <c r="G1094" t="n">
-        <v>5.36967325210571</v>
+        <v>5.36967372894287</v>
       </c>
       <c r="H1094" t="s">
         <v>8</v>
@@ -28839,7 +28839,7 @@
         <v>6</v>
       </c>
       <c r="G1095" t="n">
-        <v>5.36967325210571</v>
+        <v>5.36967372894287</v>
       </c>
       <c r="H1095" t="s">
         <v>8</v>
@@ -29099,7 +29099,7 @@
         <v>6.25</v>
       </c>
       <c r="G1105" t="n">
-        <v>5.59340953826904</v>
+        <v>5.5934100151062</v>
       </c>
       <c r="H1105" t="s">
         <v>8</v>
@@ -29125,7 +29125,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G1106" t="n">
-        <v>5.54866218566895</v>
+        <v>5.5486626625061</v>
       </c>
       <c r="H1106" t="s">
         <v>8</v>
@@ -29229,7 +29229,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G1110" t="n">
-        <v>5.54866218566895</v>
+        <v>5.5486626625061</v>
       </c>
       <c r="H1110" t="s">
         <v>8</v>
@@ -29281,7 +29281,7 @@
         <v>6.5</v>
       </c>
       <c r="G1112" t="n">
-        <v>5.81714582443237</v>
+        <v>5.81714630126953</v>
       </c>
       <c r="H1112" t="s">
         <v>8</v>
@@ -29307,7 +29307,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G1113" t="n">
-        <v>5.72765159606934</v>
+        <v>5.72765207290649</v>
       </c>
       <c r="H1113" t="s">
         <v>8</v>
@@ -29333,7 +29333,7 @@
         <v>6.5</v>
       </c>
       <c r="G1114" t="n">
-        <v>5.81714582443237</v>
+        <v>5.81714630126953</v>
       </c>
       <c r="H1114" t="s">
         <v>8</v>
@@ -29437,7 +29437,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G1118" t="n">
-        <v>6.08563041687012</v>
+        <v>6.08562994003296</v>
       </c>
       <c r="H1118" t="s">
         <v>8</v>
@@ -29593,7 +29593,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G1124" t="n">
-        <v>6.75683975219727</v>
+        <v>6.75683927536011</v>
       </c>
       <c r="H1124" t="s">
         <v>8</v>
@@ -47900,6 +47900,32 @@
         <v>2.51999998092651</v>
       </c>
       <c r="H1828" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1829">
+      <c r="A1829" s="1" t="n">
+        <v>46289.2916666667</v>
+      </c>
+      <c r="B1829" t="n">
+        <v>7849</v>
+      </c>
+      <c r="C1829" t="n">
+        <v>2.51999998092651</v>
+      </c>
+      <c r="D1829" t="n">
+        <v>2.42000007629395</v>
+      </c>
+      <c r="E1829" t="n">
+        <v>2.51999998092651</v>
+      </c>
+      <c r="F1829" t="n">
+        <v>2.51999998092651</v>
+      </c>
+      <c r="G1829" t="n">
+        <v>2.51999998092651</v>
+      </c>
+      <c r="H1829" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/PTR.MI.xlsx
+++ b/data/PTR.MI.xlsx
@@ -499,7 +499,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G5" t="n">
-        <v>3.20276880264282</v>
+        <v>3.2027690410614</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>3.69250011444092</v>
       </c>
       <c r="G6" t="n">
-        <v>3.20493865013123</v>
+        <v>3.2049388885498</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G9" t="n">
-        <v>3.05521559715271</v>
+        <v>3.05521535873413</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>3.47849988937378</v>
       </c>
       <c r="G11" t="n">
-        <v>3.01919555664062</v>
+        <v>3.01919531822205</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G12" t="n">
-        <v>3.08125448226929</v>
+        <v>3.08125424385071</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G14" t="n">
-        <v>3.12465238571167</v>
+        <v>3.12465214729309</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G15" t="n">
-        <v>3.14201140403748</v>
+        <v>3.14201164245605</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G16" t="n">
-        <v>3.14201140403748</v>
+        <v>3.14201164245605</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G18" t="n">
-        <v>3.14201140403748</v>
+        <v>3.14201164245605</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G19" t="n">
-        <v>3.13333201408386</v>
+        <v>3.13333177566528</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G20" t="n">
-        <v>3.12465238571167</v>
+        <v>3.12465214729309</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G22" t="n">
-        <v>3.09861326217651</v>
+        <v>3.09861373901367</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>3.49850010871887</v>
       </c>
       <c r="G23" t="n">
-        <v>3.03655481338501</v>
+        <v>3.03655457496643</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G24" t="n">
-        <v>3.05521559715271</v>
+        <v>3.05521535873413</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G25" t="n">
-        <v>3.05521559715271</v>
+        <v>3.05521535873413</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G26" t="n">
-        <v>2.96842002868652</v>
+        <v>2.96841979026794</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G29" t="n">
-        <v>3.08125448226929</v>
+        <v>3.08125424385071</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>3.48200011253357</v>
       </c>
       <c r="G32" t="n">
-        <v>3.02223324775696</v>
+        <v>3.02223348617554</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>3.48200011253357</v>
       </c>
       <c r="G33" t="n">
-        <v>3.02223324775696</v>
+        <v>3.02223348617554</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G34" t="n">
-        <v>3.10729360580444</v>
+        <v>3.10729312896729</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>3.5</v>
       </c>
       <c r="G35" t="n">
-        <v>3.03785634040833</v>
+        <v>3.0378565788269</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G37" t="n">
-        <v>3.14201140403748</v>
+        <v>3.14201164245605</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G38" t="n">
-        <v>3.19408917427063</v>
+        <v>3.19408941268921</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G39" t="n">
-        <v>3.21144843101501</v>
+        <v>3.21144819259644</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G40" t="n">
-        <v>3.20276880264282</v>
+        <v>3.2027690410614</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G42" t="n">
-        <v>3.2982439994812</v>
+        <v>3.29824423789978</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G45" t="n">
-        <v>3.17673015594482</v>
+        <v>3.17672991752625</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>3.71499991416931</v>
       </c>
       <c r="G46" t="n">
-        <v>3.22446751594543</v>
+        <v>3.22446775436401</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G48" t="n">
-        <v>3.15069127082825</v>
+        <v>3.15069150924683</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G49" t="n">
-        <v>3.21144843101501</v>
+        <v>3.21144819259644</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>3.71499991416931</v>
       </c>
       <c r="G50" t="n">
-        <v>3.22446751594543</v>
+        <v>3.22446775436401</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G52" t="n">
-        <v>3.21144843101501</v>
+        <v>3.21144819259644</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G53" t="n">
-        <v>3.17673015594482</v>
+        <v>3.17672991752625</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G54" t="n">
-        <v>3.21144843101501</v>
+        <v>3.21144819259644</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G56" t="n">
-        <v>3.15069127082825</v>
+        <v>3.15069150924683</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G57" t="n">
-        <v>3.15069127082825</v>
+        <v>3.15069150924683</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G58" t="n">
-        <v>3.17673015594482</v>
+        <v>3.17672991752625</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>3.66499996185303</v>
       </c>
       <c r="G59" t="n">
-        <v>3.18106985092163</v>
+        <v>3.18106961250305</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G60" t="n">
-        <v>3.05521559715271</v>
+        <v>3.05521535873413</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>3.66499996185303</v>
       </c>
       <c r="G61" t="n">
-        <v>3.18106985092163</v>
+        <v>3.18106961250305</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G62" t="n">
-        <v>3.21144843101501</v>
+        <v>3.21144819259644</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G63" t="n">
-        <v>3.14201140403748</v>
+        <v>3.14201164245605</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>3.5550000667572</v>
       </c>
       <c r="G64" t="n">
-        <v>3.08559417724609</v>
+        <v>3.08559465408325</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>3.5550000667572</v>
       </c>
       <c r="G65" t="n">
-        <v>3.08559417724609</v>
+        <v>3.08559465408325</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G66" t="n">
-        <v>3.09861326217651</v>
+        <v>3.09861373901367</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>3.63499999046326</v>
       </c>
       <c r="G67" t="n">
-        <v>3.15503120422363</v>
+        <v>3.15503072738647</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G68" t="n">
-        <v>3.12465238571167</v>
+        <v>3.12465214729309</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G69" t="n">
-        <v>3.12465238571167</v>
+        <v>3.12465214729309</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G71" t="n">
-        <v>3.21144843101501</v>
+        <v>3.21144819259644</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G72" t="n">
-        <v>3.12465238571167</v>
+        <v>3.12465214729309</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G73" t="n">
-        <v>3.08125448226929</v>
+        <v>3.08125424385071</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G74" t="n">
-        <v>3.08125448226929</v>
+        <v>3.08125424385071</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G77" t="n">
-        <v>3.08125448226929</v>
+        <v>3.08125424385071</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G78" t="n">
-        <v>3.12465238571167</v>
+        <v>3.12465214729309</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G79" t="n">
-        <v>3.14201140403748</v>
+        <v>3.14201164245605</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G81" t="n">
-        <v>3.15937066078186</v>
+        <v>3.15937089920044</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G82" t="n">
-        <v>3.14201140403748</v>
+        <v>3.14201164245605</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G83" t="n">
-        <v>3.2982439994812</v>
+        <v>3.29824423789978</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G84" t="n">
-        <v>3.2982439994812</v>
+        <v>3.29824423789978</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G85" t="n">
-        <v>3.2982439994812</v>
+        <v>3.29824423789978</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G86" t="n">
-        <v>3.2982439994812</v>
+        <v>3.29824423789978</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G91" t="n">
-        <v>3.51523375511169</v>
+        <v>3.51523399353027</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>4</v>
       </c>
       <c r="G92" t="n">
-        <v>3.47183585166931</v>
+        <v>3.47183609008789</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G95" t="n">
-        <v>3.51523375511169</v>
+        <v>3.51523399353027</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>4.00500011444092</v>
       </c>
       <c r="G98" t="n">
-        <v>3.47617626190186</v>
+        <v>3.4761757850647</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G99" t="n">
-        <v>3.59335017204285</v>
+        <v>3.59334993362427</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>3.95499992370605</v>
       </c>
       <c r="G100" t="n">
-        <v>3.43277812004089</v>
+        <v>3.43277788162231</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G102" t="n">
-        <v>3.44579744338989</v>
+        <v>3.44579720497131</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>4</v>
       </c>
       <c r="G103" t="n">
-        <v>3.47183585166931</v>
+        <v>3.47183609008789</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>4</v>
       </c>
       <c r="G105" t="n">
-        <v>3.47183585166931</v>
+        <v>3.47183609008789</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>4.03499984741211</v>
       </c>
       <c r="G106" t="n">
-        <v>3.50221467018127</v>
+        <v>3.5022144317627</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G107" t="n">
-        <v>3.51523375511169</v>
+        <v>3.51523399353027</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G108" t="n">
-        <v>3.54995250701904</v>
+        <v>3.54995226860046</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G109" t="n">
-        <v>3.54995250701904</v>
+        <v>3.54995226860046</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G110" t="n">
-        <v>3.64542770385742</v>
+        <v>3.64542746543884</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G111" t="n">
-        <v>3.64542770385742</v>
+        <v>3.64542746543884</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>4.41499996185303</v>
       </c>
       <c r="G112" t="n">
-        <v>3.83203864097595</v>
+        <v>3.83203887939453</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>4.5</v>
       </c>
       <c r="G113" t="n">
-        <v>3.90581512451172</v>
+        <v>3.90581560134888</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>4.5</v>
       </c>
       <c r="G114" t="n">
-        <v>3.90581512451172</v>
+        <v>3.90581560134888</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G115" t="n">
-        <v>3.87109708786011</v>
+        <v>3.87109732627869</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G116" t="n">
-        <v>3.86241793632507</v>
+        <v>3.86241745948792</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G117" t="n">
-        <v>4.00997114181519</v>
+        <v>4.00997066497803</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G118" t="n">
-        <v>4.03600978851318</v>
+        <v>4.03600931167603</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G119" t="n">
-        <v>3.96657228469849</v>
+        <v>3.9665732383728</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G120" t="n">
-        <v>3.86241793632507</v>
+        <v>3.86241745948792</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G121" t="n">
-        <v>3.92317509651184</v>
+        <v>3.92317485809326</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G122" t="n">
-        <v>3.94053363800049</v>
+        <v>3.94053387641907</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G124" t="n">
-        <v>3.94921374320984</v>
+        <v>3.94921398162842</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G125" t="n">
-        <v>3.94921374320984</v>
+        <v>3.94921398162842</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G126" t="n">
-        <v>4.03600978851318</v>
+        <v>4.03600931167603</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>4.88500022888184</v>
       </c>
       <c r="G127" t="n">
-        <v>4.23998022079468</v>
+        <v>4.23997974395752</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G128" t="n">
-        <v>4.37451410293579</v>
+        <v>4.37451314926147</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G129" t="n">
-        <v>4.3831934928894</v>
+        <v>4.38319253921509</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G130" t="n">
-        <v>4.39187240600586</v>
+        <v>4.39187335968018</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>4.97499990463257</v>
       </c>
       <c r="G133" t="n">
-        <v>4.31809616088867</v>
+        <v>4.31809568405151</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G136" t="n">
-        <v>4.2009220123291</v>
+        <v>4.20092153549194</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>5</v>
       </c>
       <c r="G139" t="n">
-        <v>4.33979463577271</v>
+        <v>4.33979511260986</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G141" t="n">
-        <v>4.42659044265747</v>
+        <v>4.42659091949463</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G142" t="n">
-        <v>4.35715389251709</v>
+        <v>4.35715436935425</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>5</v>
       </c>
       <c r="G143" t="n">
-        <v>4.33979463577271</v>
+        <v>4.33979511260986</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G144" t="n">
-        <v>4.42659044265747</v>
+        <v>4.42659091949463</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G147" t="n">
-        <v>4.70433759689331</v>
+        <v>4.70433807373047</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>5.13000011444092</v>
       </c>
       <c r="G150" t="n">
-        <v>4.45262956619263</v>
+        <v>4.45263004302979</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G153" t="n">
-        <v>4.44395017623901</v>
+        <v>4.44394969940186</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>4.75500011444092</v>
       </c>
       <c r="G155" t="n">
-        <v>4.1271448135376</v>
+        <v>4.12714529037476</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G156" t="n">
-        <v>4.31375598907471</v>
+        <v>4.31375551223755</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G157" t="n">
-        <v>4.23563957214355</v>
+        <v>4.23564004898071</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G161" t="n">
-        <v>4.0446891784668</v>
+        <v>4.04468870162964</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G162" t="n">
-        <v>3.99261116981506</v>
+        <v>3.99261140823364</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>4.24499988555908</v>
       </c>
       <c r="G163" t="n">
-        <v>3.68448567390442</v>
+        <v>3.684485912323</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G164" t="n">
-        <v>3.17673015594482</v>
+        <v>3.17672991752625</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G165" t="n">
-        <v>3.26352596282959</v>
+        <v>3.26352572441101</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G168" t="n">
-        <v>2.95974016189575</v>
+        <v>2.95974040031433</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G170" t="n">
-        <v>3.12465238571167</v>
+        <v>3.12465214729309</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>3.375</v>
       </c>
       <c r="G171" t="n">
-        <v>2.92936158180237</v>
+        <v>2.92936182022095</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G173" t="n">
-        <v>3.09861326217651</v>
+        <v>3.09861373901367</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>3.34500002861023</v>
       </c>
       <c r="G174" t="n">
-        <v>2.90332269668579</v>
+        <v>2.90332293510437</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>3.72499990463257</v>
       </c>
       <c r="G175" t="n">
-        <v>3.23314714431763</v>
+        <v>3.23314690589905</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G176" t="n">
-        <v>3.08125448226929</v>
+        <v>3.08125424385071</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G177" t="n">
-        <v>3.09861326217651</v>
+        <v>3.09861373901367</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G179" t="n">
-        <v>3.21144843101501</v>
+        <v>3.21144819259644</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G183" t="n">
-        <v>3.19408917427063</v>
+        <v>3.19408941268921</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G184" t="n">
-        <v>3.21144843101501</v>
+        <v>3.21144819259644</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G185" t="n">
-        <v>3.19408917427063</v>
+        <v>3.19408941268921</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G187" t="n">
-        <v>3.21144843101501</v>
+        <v>3.21144819259644</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G188" t="n">
-        <v>3.2982439994812</v>
+        <v>3.29824423789978</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G190" t="n">
-        <v>3.18540954589844</v>
+        <v>3.18540978431702</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G192" t="n">
-        <v>3.33296227455139</v>
+        <v>3.33296275138855</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G193" t="n">
-        <v>3.2982439994812</v>
+        <v>3.29824423789978</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G194" t="n">
-        <v>3.2982439994812</v>
+        <v>3.29824423789978</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G196" t="n">
-        <v>3.35900115966797</v>
+        <v>3.35900139808655</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G197" t="n">
-        <v>3.35900115966797</v>
+        <v>3.35900139808655</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G198" t="n">
-        <v>3.59335017204285</v>
+        <v>3.59334993362427</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G199" t="n">
-        <v>3.54995250701904</v>
+        <v>3.54995226860046</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G200" t="n">
-        <v>3.48051595687866</v>
+        <v>3.48051571846008</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G201" t="n">
-        <v>3.33296227455139</v>
+        <v>3.33296275138855</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G204" t="n">
-        <v>3.19408917427063</v>
+        <v>3.19408941268921</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G205" t="n">
-        <v>3.2982439994812</v>
+        <v>3.29824423789978</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G211" t="n">
-        <v>3.2982439994812</v>
+        <v>3.29824423789978</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G215" t="n">
-        <v>3.26352596282959</v>
+        <v>3.26352572441101</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G217" t="n">
-        <v>3.2982439994812</v>
+        <v>3.29824423789978</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G219" t="n">
-        <v>3.2982439994812</v>
+        <v>3.29824423789978</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G220" t="n">
-        <v>3.26352596282959</v>
+        <v>3.26352572441101</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G222" t="n">
-        <v>3.2982439994812</v>
+        <v>3.29824423789978</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G225" t="n">
-        <v>3.35900115966797</v>
+        <v>3.35900139808655</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G227" t="n">
-        <v>3.2982439994812</v>
+        <v>3.29824423789978</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G240" t="n">
-        <v>3.2982439994812</v>
+        <v>3.29824423789978</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G246" t="n">
-        <v>3.2982439994812</v>
+        <v>3.29824423789978</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G249" t="n">
-        <v>3.15937066078186</v>
+        <v>3.15937089920044</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G251" t="n">
-        <v>3.18540954589844</v>
+        <v>3.18540978431702</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G252" t="n">
-        <v>3.21144843101501</v>
+        <v>3.21144819259644</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G253" t="n">
-        <v>3.21144843101501</v>
+        <v>3.21144819259644</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G255" t="n">
-        <v>3.18540954589844</v>
+        <v>3.18540978431702</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G264" t="n">
-        <v>3.13333201408386</v>
+        <v>3.13333177566528</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G265" t="n">
-        <v>3.07257509231567</v>
+        <v>3.07257461547852</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G270" t="n">
-        <v>3.19408917427063</v>
+        <v>3.19408941268921</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G271" t="n">
-        <v>3.13333201408386</v>
+        <v>3.13333177566528</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G272" t="n">
-        <v>3.12465238571167</v>
+        <v>3.12465214729309</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G273" t="n">
-        <v>3.0204975605011</v>
+        <v>3.02049732208252</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G274" t="n">
-        <v>2.93370151519775</v>
+        <v>2.93370127677917</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G275" t="n">
-        <v>2.96842002868652</v>
+        <v>2.96841979026794</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G277" t="n">
-        <v>3.0204975605011</v>
+        <v>3.02049732208252</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G278" t="n">
-        <v>3.07257509231567</v>
+        <v>3.07257461547852</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>3.5</v>
       </c>
       <c r="G280" t="n">
-        <v>3.03785634040833</v>
+        <v>3.0378565788269</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G281" t="n">
-        <v>3.0638952255249</v>
+        <v>3.06389546394348</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G282" t="n">
-        <v>3.0638952255249</v>
+        <v>3.06389546394348</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G283" t="n">
-        <v>3.0638952255249</v>
+        <v>3.06389546394348</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>3.5</v>
       </c>
       <c r="G287" t="n">
-        <v>3.03785634040833</v>
+        <v>3.0378565788269</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G289" t="n">
-        <v>3.08125448226929</v>
+        <v>3.08125424385071</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G290" t="n">
-        <v>3.05521559715271</v>
+        <v>3.05521535873413</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>3.5</v>
       </c>
       <c r="G291" t="n">
-        <v>3.03785634040833</v>
+        <v>3.0378565788269</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>3.5</v>
       </c>
       <c r="G292" t="n">
-        <v>3.03785634040833</v>
+        <v>3.0378565788269</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G294" t="n">
-        <v>3.08125448226929</v>
+        <v>3.08125424385071</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>3.5</v>
       </c>
       <c r="G295" t="n">
-        <v>3.03785634040833</v>
+        <v>3.0378565788269</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G299" t="n">
-        <v>2.86426448822021</v>
+        <v>2.86426496505737</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G300" t="n">
-        <v>2.86426448822021</v>
+        <v>2.86426496505737</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G301" t="n">
-        <v>2.86426448822021</v>
+        <v>2.86426496505737</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G302" t="n">
-        <v>2.95974016189575</v>
+        <v>2.95974040031433</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G303" t="n">
-        <v>2.88162398338318</v>
+        <v>2.8816237449646</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G304" t="n">
-        <v>2.87294411659241</v>
+        <v>2.87294459342957</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>3.5</v>
       </c>
       <c r="G305" t="n">
-        <v>3.03785634040833</v>
+        <v>3.0378565788269</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G306" t="n">
-        <v>3.08125448226929</v>
+        <v>3.08125424385071</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G307" t="n">
-        <v>3.12465238571167</v>
+        <v>3.12465214729309</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G308" t="n">
-        <v>3.12465238571167</v>
+        <v>3.12465214729309</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G313" t="n">
-        <v>3.21144843101501</v>
+        <v>3.21144819259644</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G314" t="n">
-        <v>3.19408917427063</v>
+        <v>3.19408941268921</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G315" t="n">
-        <v>3.21144843101501</v>
+        <v>3.21144819259644</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G317" t="n">
-        <v>3.21144843101501</v>
+        <v>3.21144819259644</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G318" t="n">
-        <v>3.17673015594482</v>
+        <v>3.17672991752625</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G320" t="n">
-        <v>3.20276880264282</v>
+        <v>3.2027690410614</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G321" t="n">
-        <v>3.21144843101501</v>
+        <v>3.21144819259644</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G323" t="n">
-        <v>3.21144843101501</v>
+        <v>3.21144819259644</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G324" t="n">
-        <v>3.21144843101501</v>
+        <v>3.21144819259644</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G325" t="n">
-        <v>3.21144843101501</v>
+        <v>3.21144819259644</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G326" t="n">
-        <v>3.19408917427063</v>
+        <v>3.19408941268921</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G327" t="n">
-        <v>3.14201140403748</v>
+        <v>3.14201164245605</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G328" t="n">
-        <v>3.21144843101501</v>
+        <v>3.21144819259644</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G329" t="n">
-        <v>3.12465238571167</v>
+        <v>3.12465214729309</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G330" t="n">
-        <v>3.19408917427063</v>
+        <v>3.19408941268921</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G331" t="n">
-        <v>3.05521559715271</v>
+        <v>3.05521535873413</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>3.5</v>
       </c>
       <c r="G332" t="n">
-        <v>3.03785634040833</v>
+        <v>3.0378565788269</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G334" t="n">
-        <v>3.15069127082825</v>
+        <v>3.15069150924683</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G335" t="n">
-        <v>3.20276880264282</v>
+        <v>3.2027690410614</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G336" t="n">
-        <v>3.20276880264282</v>
+        <v>3.2027690410614</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G337" t="n">
-        <v>3.20276880264282</v>
+        <v>3.2027690410614</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G339" t="n">
-        <v>3.15937066078186</v>
+        <v>3.15937089920044</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G341" t="n">
-        <v>3.20276880264282</v>
+        <v>3.2027690410614</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G342" t="n">
-        <v>3.21144843101501</v>
+        <v>3.21144819259644</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G343" t="n">
-        <v>3.15069127082825</v>
+        <v>3.15069150924683</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G344" t="n">
-        <v>3.15069127082825</v>
+        <v>3.15069150924683</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G346" t="n">
-        <v>3.21144843101501</v>
+        <v>3.21144819259644</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>4</v>
       </c>
       <c r="G359" t="n">
-        <v>3.47183585166931</v>
+        <v>3.47183609008789</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>4</v>
       </c>
       <c r="G360" t="n">
-        <v>3.47183585166931</v>
+        <v>3.47183609008789</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G363" t="n">
-        <v>3.53336215019226</v>
+        <v>3.53336191177368</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G365" t="n">
-        <v>3.55973052978516</v>
+        <v>3.55973076820374</v>
       </c>
       <c r="H365" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G373" t="n">
-        <v>3.77946710586548</v>
+        <v>3.77946734428406</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G374" t="n">
-        <v>3.85857224464417</v>
+        <v>3.85857200622559</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10119,7 +10119,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G375" t="n">
-        <v>3.80583548545837</v>
+        <v>3.80583524703979</v>
       </c>
       <c r="H375" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G376" t="n">
-        <v>3.82341384887695</v>
+        <v>3.82341408729553</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G377" t="n">
-        <v>3.70915102958679</v>
+        <v>3.70915126800537</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G380" t="n">
-        <v>3.99041366577148</v>
+        <v>3.99041414260864</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>4.5</v>
       </c>
       <c r="G381" t="n">
-        <v>3.95525622367859</v>
+        <v>3.95525598526001</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G382" t="n">
-        <v>3.92888760566711</v>
+        <v>3.92888784408569</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G384" t="n">
-        <v>3.77946710586548</v>
+        <v>3.77946734428406</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G385" t="n">
-        <v>3.77946710586548</v>
+        <v>3.77946734428406</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G387" t="n">
-        <v>3.42788863182068</v>
+        <v>3.42788887023926</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10483,7 +10483,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G389" t="n">
-        <v>3.58609867095947</v>
+        <v>3.58609890937805</v>
       </c>
       <c r="H389" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G390" t="n">
-        <v>3.69157195091248</v>
+        <v>3.69157218933105</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G395" t="n">
-        <v>3.74430918693542</v>
+        <v>3.744309425354</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G396" t="n">
-        <v>3.77946710586548</v>
+        <v>3.77946734428406</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G397" t="n">
-        <v>3.82341384887695</v>
+        <v>3.82341408729553</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G398" t="n">
-        <v>3.77946710586548</v>
+        <v>3.77946734428406</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G399" t="n">
-        <v>3.70915102958679</v>
+        <v>3.70915126800537</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10795,7 +10795,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G401" t="n">
-        <v>3.58609867095947</v>
+        <v>3.58609890937805</v>
       </c>
       <c r="H401" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G403" t="n">
-        <v>3.68278336524963</v>
+        <v>3.68278288841248</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -10925,7 +10925,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G406" t="n">
-        <v>3.84099292755127</v>
+        <v>3.84099316596985</v>
       </c>
       <c r="H406" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>4.25</v>
       </c>
       <c r="G407" t="n">
-        <v>3.73551964759827</v>
+        <v>3.73551940917969</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G409" t="n">
-        <v>4.04315042495728</v>
+        <v>4.04315090179443</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G412" t="n">
-        <v>3.97283530235291</v>
+        <v>3.97283506393433</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11107,7 +11107,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G413" t="n">
-        <v>4.06072998046875</v>
+        <v>4.06072950363159</v>
       </c>
       <c r="H413" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G414" t="n">
-        <v>4.04315042495728</v>
+        <v>4.04315090179443</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G415" t="n">
-        <v>4.04315042495728</v>
+        <v>4.04315090179443</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>5</v>
       </c>
       <c r="G421" t="n">
-        <v>4.3947286605835</v>
+        <v>4.39472913742065</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>5</v>
       </c>
       <c r="G422" t="n">
-        <v>4.3947286605835</v>
+        <v>4.39472913742065</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G425" t="n">
-        <v>4.29804468154907</v>
+        <v>4.29804515838623</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G426" t="n">
-        <v>4.25409746170044</v>
+        <v>4.2540979385376</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G427" t="n">
-        <v>4.34199237823486</v>
+        <v>4.34199190139771</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>4.75</v>
       </c>
       <c r="G429" t="n">
-        <v>4.17499256134033</v>
+        <v>4.17499303817749</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G430" t="n">
-        <v>4.28925561904907</v>
+        <v>4.28925609588623</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G431" t="n">
-        <v>4.28925561904907</v>
+        <v>4.28925609588623</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>4.75</v>
       </c>
       <c r="G435" t="n">
-        <v>4.17499256134033</v>
+        <v>4.17499303817749</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G438" t="n">
-        <v>4.25409746170044</v>
+        <v>4.2540979385376</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G443" t="n">
-        <v>4.35078191757202</v>
+        <v>4.35078144073486</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -11913,7 +11913,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G444" t="n">
-        <v>4.34199237823486</v>
+        <v>4.34199190139771</v>
       </c>
       <c r="H444" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G445" t="n">
-        <v>4.2628870010376</v>
+        <v>4.26288747787476</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G446" t="n">
-        <v>4.34199237823486</v>
+        <v>4.34199190139771</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>5</v>
       </c>
       <c r="G449" t="n">
-        <v>4.3947286605835</v>
+        <v>4.39472913742065</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12069,7 +12069,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G450" t="n">
-        <v>4.21893978118896</v>
+        <v>4.21894025802612</v>
       </c>
       <c r="H450" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G452" t="n">
-        <v>4.21893978118896</v>
+        <v>4.21894025802612</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>4.75</v>
       </c>
       <c r="G454" t="n">
-        <v>4.17499256134033</v>
+        <v>4.17499303817749</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12225,7 +12225,7 @@
         <v>4.75</v>
       </c>
       <c r="G456" t="n">
-        <v>4.17499256134033</v>
+        <v>4.17499303817749</v>
       </c>
       <c r="H456" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>4.75</v>
       </c>
       <c r="G457" t="n">
-        <v>4.17499256134033</v>
+        <v>4.17499303817749</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G459" t="n">
-        <v>4.02557229995728</v>
+        <v>4.02557182312012</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G460" t="n">
-        <v>4.02557229995728</v>
+        <v>4.02557182312012</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12355,7 +12355,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G461" t="n">
-        <v>4.02557229995728</v>
+        <v>4.02557182312012</v>
       </c>
       <c r="H461" t="s">
         <v>8</v>
@@ -12459,7 +12459,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G465" t="n">
-        <v>4.2628870010376</v>
+        <v>4.26288747787476</v>
       </c>
       <c r="H465" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G466" t="n">
-        <v>4.28925561904907</v>
+        <v>4.28925609588623</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G467" t="n">
-        <v>4.35078191757202</v>
+        <v>4.35078144073486</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12537,7 +12537,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G468" t="n">
-        <v>4.50020265579224</v>
+        <v>4.50020217895508</v>
       </c>
       <c r="H468" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G474" t="n">
-        <v>4.57807397842407</v>
+        <v>4.57807350158691</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G475" t="n">
-        <v>4.77250957489014</v>
+        <v>4.77250909805298</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G482" t="n">
-        <v>4.54272174835205</v>
+        <v>4.54272222518921</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -13005,7 +13005,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G486" t="n">
-        <v>4.37480020523071</v>
+        <v>4.37479972839355</v>
       </c>
       <c r="H486" t="s">
         <v>8</v>
@@ -13187,7 +13187,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G493" t="n">
-        <v>4.26874446868896</v>
+        <v>4.26874494552612</v>
       </c>
       <c r="H493" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G494" t="n">
-        <v>4.22455453872681</v>
+        <v>4.22455501556396</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G501" t="n">
-        <v>4.02128124237061</v>
+        <v>4.02128171920776</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13421,7 +13421,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G502" t="n">
-        <v>4.0831470489502</v>
+        <v>4.08314657211304</v>
       </c>
       <c r="H502" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G507" t="n">
-        <v>4.22455453872681</v>
+        <v>4.22455501556396</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13915,7 +13915,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G521" t="n">
-        <v>4.52504587173462</v>
+        <v>4.52504539489746</v>
       </c>
       <c r="H521" t="s">
         <v>8</v>
@@ -14045,7 +14045,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G526" t="n">
-        <v>4.57807397842407</v>
+        <v>4.57807350158691</v>
       </c>
       <c r="H526" t="s">
         <v>8</v>
@@ -14071,7 +14071,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G527" t="n">
-        <v>4.57807397842407</v>
+        <v>4.57807350158691</v>
       </c>
       <c r="H527" t="s">
         <v>8</v>
@@ -14123,7 +14123,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G529" t="n">
-        <v>4.45434236526489</v>
+        <v>4.45434188842773</v>
       </c>
       <c r="H529" t="s">
         <v>8</v>
@@ -14149,7 +14149,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G530" t="n">
-        <v>4.52504587173462</v>
+        <v>4.52504539489746</v>
       </c>
       <c r="H530" t="s">
         <v>8</v>
@@ -14175,7 +14175,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G531" t="n">
-        <v>4.52504587173462</v>
+        <v>4.52504539489746</v>
       </c>
       <c r="H531" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G534" t="n">
-        <v>4.26874446868896</v>
+        <v>4.26874494552612</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G535" t="n">
-        <v>4.28641986846924</v>
+        <v>4.2864203453064</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14305,7 +14305,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G536" t="n">
-        <v>4.28641986846924</v>
+        <v>4.2864203453064</v>
       </c>
       <c r="H536" t="s">
         <v>8</v>
@@ -14331,7 +14331,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G537" t="n">
-        <v>4.28641986846924</v>
+        <v>4.2864203453064</v>
       </c>
       <c r="H537" t="s">
         <v>8</v>
@@ -14357,7 +14357,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G538" t="n">
-        <v>4.28641986846924</v>
+        <v>4.2864203453064</v>
       </c>
       <c r="H538" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G539" t="n">
-        <v>4.41015195846558</v>
+        <v>4.41015148162842</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14487,7 +14487,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G543" t="n">
-        <v>4.38363838195801</v>
+        <v>4.38363885879517</v>
       </c>
       <c r="H543" t="s">
         <v>8</v>
@@ -14513,7 +14513,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G544" t="n">
-        <v>4.36596250534058</v>
+        <v>4.36596202850342</v>
       </c>
       <c r="H544" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G545" t="n">
-        <v>4.36596250534058</v>
+        <v>4.36596202850342</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14565,7 +14565,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G546" t="n">
-        <v>4.33944797515869</v>
+        <v>4.33944845199585</v>
       </c>
       <c r="H546" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G547" t="n">
-        <v>4.33944797515869</v>
+        <v>4.33944845199585</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G548" t="n">
-        <v>4.33944797515869</v>
+        <v>4.33944845199585</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14747,7 +14747,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G553" t="n">
-        <v>4.31293439865112</v>
+        <v>4.31293487548828</v>
       </c>
       <c r="H553" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G561" t="n">
-        <v>4.15385103225708</v>
+        <v>4.15385055541992</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G563" t="n">
-        <v>4.29525852203369</v>
+        <v>4.29525804519653</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15163,7 +15163,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G569" t="n">
-        <v>4.57807397842407</v>
+        <v>4.57807350158691</v>
       </c>
       <c r="H569" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G573" t="n">
-        <v>4.73715782165527</v>
+        <v>4.73715734481812</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15371,7 +15371,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G577" t="n">
-        <v>4.91391658782959</v>
+        <v>4.91391706466675</v>
       </c>
       <c r="H577" t="s">
         <v>8</v>
@@ -15423,7 +15423,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G579" t="n">
-        <v>4.89624118804932</v>
+        <v>4.89624071121216</v>
       </c>
       <c r="H579" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G580" t="n">
-        <v>4.94926881790161</v>
+        <v>4.94926929473877</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G581" t="n">
-        <v>5.10835266113281</v>
+        <v>5.10835313796997</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15501,7 +15501,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G582" t="n">
-        <v>5.26743602752686</v>
+        <v>5.26743650436401</v>
       </c>
       <c r="H582" t="s">
         <v>8</v>
@@ -15553,7 +15553,7 @@
         <v>6.03999996185303</v>
       </c>
       <c r="G584" t="n">
-        <v>5.33814001083374</v>
+        <v>5.33813953399658</v>
       </c>
       <c r="H584" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G588" t="n">
-        <v>5.70933532714844</v>
+        <v>5.70933485031128</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G589" t="n">
-        <v>5.65630769729614</v>
+        <v>5.65630722045898</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15709,7 +15709,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G590" t="n">
-        <v>5.65630769729614</v>
+        <v>5.65630722045898</v>
       </c>
       <c r="H590" t="s">
         <v>8</v>
@@ -15735,7 +15735,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G591" t="n">
-        <v>5.63863134384155</v>
+        <v>5.63863182067871</v>
       </c>
       <c r="H591" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G599" t="n">
-        <v>5.65630769729614</v>
+        <v>5.65630722045898</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -15969,7 +15969,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G600" t="n">
-        <v>5.72701168060303</v>
+        <v>5.72701120376587</v>
       </c>
       <c r="H600" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G605" t="n">
-        <v>5.72701168060303</v>
+        <v>5.72701120376587</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G606" t="n">
-        <v>5.72701168060303</v>
+        <v>5.72701120376587</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16203,7 +16203,7 @@
         <v>6.42000007629395</v>
       </c>
       <c r="G609" t="n">
-        <v>5.67398357391357</v>
+        <v>5.67398405075073</v>
       </c>
       <c r="H609" t="s">
         <v>8</v>
@@ -16229,7 +16229,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G610" t="n">
-        <v>5.70933532714844</v>
+        <v>5.70933485031128</v>
       </c>
       <c r="H610" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G611" t="n">
-        <v>5.72701168060303</v>
+        <v>5.72701120376587</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16281,7 +16281,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G612" t="n">
-        <v>5.72701168060303</v>
+        <v>5.72701120376587</v>
       </c>
       <c r="H612" t="s">
         <v>8</v>
@@ -16307,7 +16307,7 @@
         <v>6.53999996185303</v>
       </c>
       <c r="G613" t="n">
-        <v>5.78003931045532</v>
+        <v>5.78003883361816</v>
       </c>
       <c r="H613" t="s">
         <v>8</v>
@@ -16333,7 +16333,7 @@
         <v>6.5</v>
       </c>
       <c r="G614" t="n">
-        <v>5.7446870803833</v>
+        <v>5.74468660354614</v>
       </c>
       <c r="H614" t="s">
         <v>8</v>
@@ -16359,7 +16359,7 @@
         <v>6.5</v>
       </c>
       <c r="G615" t="n">
-        <v>5.7446870803833</v>
+        <v>5.74468660354614</v>
       </c>
       <c r="H615" t="s">
         <v>8</v>
@@ -16437,7 +16437,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G618" t="n">
-        <v>5.81539106369019</v>
+        <v>5.81539058685303</v>
       </c>
       <c r="H618" t="s">
         <v>8</v>
@@ -16463,7 +16463,7 @@
         <v>6.5</v>
       </c>
       <c r="G619" t="n">
-        <v>5.7446870803833</v>
+        <v>5.74468660354614</v>
       </c>
       <c r="H619" t="s">
         <v>8</v>
@@ -16541,7 +16541,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G622" t="n">
-        <v>5.39116764068604</v>
+        <v>5.39116811752319</v>
       </c>
       <c r="H622" t="s">
         <v>8</v>
@@ -16593,7 +16593,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G624" t="n">
-        <v>5.65630769729614</v>
+        <v>5.65630722045898</v>
       </c>
       <c r="H624" t="s">
         <v>8</v>
@@ -16619,7 +16619,7 @@
         <v>6.5</v>
       </c>
       <c r="G625" t="n">
-        <v>5.7446870803833</v>
+        <v>5.74468660354614</v>
       </c>
       <c r="H625" t="s">
         <v>8</v>
@@ -16645,7 +16645,7 @@
         <v>6.5</v>
       </c>
       <c r="G626" t="n">
-        <v>5.7446870803833</v>
+        <v>5.74468660354614</v>
       </c>
       <c r="H626" t="s">
         <v>8</v>
@@ -16671,7 +16671,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G627" t="n">
-        <v>6.00982666015625</v>
+        <v>6.00982713699341</v>
       </c>
       <c r="H627" t="s">
         <v>8</v>
@@ -16749,7 +16749,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G630" t="n">
-        <v>6.00982666015625</v>
+        <v>6.00982713699341</v>
       </c>
       <c r="H630" t="s">
         <v>8</v>
@@ -16905,7 +16905,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G636" t="n">
-        <v>5.70933532714844</v>
+        <v>5.70933485031128</v>
       </c>
       <c r="H636" t="s">
         <v>8</v>
@@ -16931,7 +16931,7 @@
         <v>6.44000005722046</v>
       </c>
       <c r="G637" t="n">
-        <v>5.69165897369385</v>
+        <v>5.69165945053101</v>
       </c>
       <c r="H637" t="s">
         <v>8</v>
@@ -16957,7 +16957,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G638" t="n">
-        <v>5.63863134384155</v>
+        <v>5.63863182067871</v>
       </c>
       <c r="H638" t="s">
         <v>8</v>
@@ -17009,7 +17009,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G640" t="n">
-        <v>5.70933532714844</v>
+        <v>5.70933485031128</v>
       </c>
       <c r="H640" t="s">
         <v>8</v>
@@ -17035,7 +17035,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G641" t="n">
-        <v>5.7977147102356</v>
+        <v>5.79771518707275</v>
       </c>
       <c r="H641" t="s">
         <v>8</v>
@@ -17061,7 +17061,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G642" t="n">
-        <v>5.7977147102356</v>
+        <v>5.79771518707275</v>
       </c>
       <c r="H642" t="s">
         <v>8</v>
@@ -17087,7 +17087,7 @@
         <v>6.53999996185303</v>
       </c>
       <c r="G643" t="n">
-        <v>5.78003931045532</v>
+        <v>5.78003883361816</v>
       </c>
       <c r="H643" t="s">
         <v>8</v>
@@ -17217,7 +17217,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G648" t="n">
-        <v>5.26743602752686</v>
+        <v>5.26743650436401</v>
       </c>
       <c r="H648" t="s">
         <v>8</v>
@@ -17243,7 +17243,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G649" t="n">
-        <v>5.39116764068604</v>
+        <v>5.39116811752319</v>
       </c>
       <c r="H649" t="s">
         <v>8</v>
@@ -17269,7 +17269,7 @@
         <v>6</v>
       </c>
       <c r="G650" t="n">
-        <v>5.30278825759888</v>
+        <v>5.30278778076172</v>
       </c>
       <c r="H650" t="s">
         <v>8</v>
@@ -17295,7 +17295,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G651" t="n">
-        <v>5.28511190414429</v>
+        <v>5.28511238098145</v>
       </c>
       <c r="H651" t="s">
         <v>8</v>
@@ -17321,7 +17321,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G652" t="n">
-        <v>5.2144079208374</v>
+        <v>5.21440839767456</v>
       </c>
       <c r="H652" t="s">
         <v>8</v>
@@ -17373,7 +17373,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G654" t="n">
-        <v>4.94926881790161</v>
+        <v>4.94926929473877</v>
       </c>
       <c r="H654" t="s">
         <v>8</v>
@@ -17399,7 +17399,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G655" t="n">
-        <v>4.94926881790161</v>
+        <v>4.94926929473877</v>
       </c>
       <c r="H655" t="s">
         <v>8</v>
@@ -17503,7 +17503,7 @@
         <v>6</v>
       </c>
       <c r="G659" t="n">
-        <v>5.30278825759888</v>
+        <v>5.30278778076172</v>
       </c>
       <c r="H659" t="s">
         <v>8</v>
@@ -17633,7 +17633,7 @@
         <v>6</v>
       </c>
       <c r="G664" t="n">
-        <v>5.30278825759888</v>
+        <v>5.30278778076172</v>
       </c>
       <c r="H664" t="s">
         <v>8</v>
@@ -17659,7 +17659,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G665" t="n">
-        <v>5.19673252105713</v>
+        <v>5.19673299789429</v>
       </c>
       <c r="H665" t="s">
         <v>8</v>
@@ -17685,7 +17685,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G666" t="n">
-        <v>4.71948146820068</v>
+        <v>4.71948194503784</v>
       </c>
       <c r="H666" t="s">
         <v>8</v>
@@ -17711,7 +17711,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G667" t="n">
-        <v>4.77250957489014</v>
+        <v>4.77250909805298</v>
       </c>
       <c r="H667" t="s">
         <v>8</v>
@@ -17789,7 +17789,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G670" t="n">
-        <v>4.71948146820068</v>
+        <v>4.71948194503784</v>
       </c>
       <c r="H670" t="s">
         <v>8</v>
@@ -17815,7 +17815,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G671" t="n">
-        <v>4.57807397842407</v>
+        <v>4.57807350158691</v>
       </c>
       <c r="H671" t="s">
         <v>8</v>
@@ -17867,7 +17867,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G673" t="n">
-        <v>4.28641986846924</v>
+        <v>4.2864203453064</v>
       </c>
       <c r="H673" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G674" t="n">
-        <v>4.28641986846924</v>
+        <v>4.2864203453064</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -18101,7 +18101,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G682" t="n">
-        <v>4.71948146820068</v>
+        <v>4.71948194503784</v>
       </c>
       <c r="H682" t="s">
         <v>8</v>
@@ -18127,7 +18127,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G683" t="n">
-        <v>4.77250957489014</v>
+        <v>4.77250909805298</v>
       </c>
       <c r="H683" t="s">
         <v>8</v>
@@ -18153,7 +18153,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G684" t="n">
-        <v>4.70180559158325</v>
+        <v>4.70180511474609</v>
       </c>
       <c r="H684" t="s">
         <v>8</v>
@@ -18231,7 +18231,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G687" t="n">
-        <v>4.45434236526489</v>
+        <v>4.45434188842773</v>
       </c>
       <c r="H687" t="s">
         <v>8</v>
@@ -18257,7 +18257,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G688" t="n">
-        <v>4.54272174835205</v>
+        <v>4.54272222518921</v>
       </c>
       <c r="H688" t="s">
         <v>8</v>
@@ -18309,7 +18309,7 @@
         <v>5.5</v>
       </c>
       <c r="G690" t="n">
-        <v>4.86088895797729</v>
+        <v>4.86088943481445</v>
       </c>
       <c r="H690" t="s">
         <v>8</v>
@@ -18335,7 +18335,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G691" t="n">
-        <v>4.77250957489014</v>
+        <v>4.77250909805298</v>
       </c>
       <c r="H691" t="s">
         <v>8</v>
@@ -18413,7 +18413,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G694" t="n">
-        <v>4.93159341812134</v>
+        <v>4.93159246444702</v>
       </c>
       <c r="H694" t="s">
         <v>8</v>
@@ -18491,7 +18491,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G697" t="n">
-        <v>4.94926881790161</v>
+        <v>4.94926929473877</v>
       </c>
       <c r="H697" t="s">
         <v>8</v>
@@ -18517,7 +18517,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G698" t="n">
-        <v>4.94926881790161</v>
+        <v>4.94926929473877</v>
       </c>
       <c r="H698" t="s">
         <v>8</v>
@@ -18543,7 +18543,7 @@
         <v>5.5</v>
       </c>
       <c r="G699" t="n">
-        <v>4.86088895797729</v>
+        <v>4.86088943481445</v>
       </c>
       <c r="H699" t="s">
         <v>8</v>
@@ -18621,7 +18621,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G702" t="n">
-        <v>4.94926881790161</v>
+        <v>4.94926929473877</v>
       </c>
       <c r="H702" t="s">
         <v>8</v>
@@ -18699,7 +18699,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G705" t="n">
-        <v>5.14370489120483</v>
+        <v>5.14370441436768</v>
       </c>
       <c r="H705" t="s">
         <v>8</v>
@@ -18751,7 +18751,7 @@
         <v>5.8600001335144</v>
       </c>
       <c r="G707" t="n">
-        <v>5.1790566444397</v>
+        <v>5.17905616760254</v>
       </c>
       <c r="H707" t="s">
         <v>8</v>
@@ -18855,7 +18855,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G711" t="n">
-        <v>5.14370489120483</v>
+        <v>5.14370441436768</v>
       </c>
       <c r="H711" t="s">
         <v>8</v>
@@ -18881,7 +18881,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G712" t="n">
-        <v>5.14370489120483</v>
+        <v>5.14370441436768</v>
       </c>
       <c r="H712" t="s">
         <v>8</v>
@@ -18907,7 +18907,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G713" t="n">
-        <v>5.16138029098511</v>
+        <v>5.16138076782227</v>
       </c>
       <c r="H713" t="s">
         <v>8</v>
@@ -18959,7 +18959,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G715" t="n">
-        <v>5.14370489120483</v>
+        <v>5.14370441436768</v>
       </c>
       <c r="H715" t="s">
         <v>8</v>
@@ -19115,7 +19115,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G721" t="n">
-        <v>4.94926881790161</v>
+        <v>4.94926929473877</v>
       </c>
       <c r="H721" t="s">
         <v>8</v>
@@ -19141,7 +19141,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G722" t="n">
-        <v>5.16138029098511</v>
+        <v>5.16138076782227</v>
       </c>
       <c r="H722" t="s">
         <v>8</v>
@@ -19167,7 +19167,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G723" t="n">
-        <v>5.16138029098511</v>
+        <v>5.16138076782227</v>
       </c>
       <c r="H723" t="s">
         <v>8</v>
@@ -19193,7 +19193,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G724" t="n">
-        <v>5.24976062774658</v>
+        <v>5.24976015090942</v>
       </c>
       <c r="H724" t="s">
         <v>8</v>
@@ -19427,7 +19427,7 @@
         <v>5.8600001335144</v>
       </c>
       <c r="G733" t="n">
-        <v>5.24438142776489</v>
+        <v>5.24438095092773</v>
       </c>
       <c r="H733" t="s">
         <v>8</v>
@@ -19453,7 +19453,7 @@
         <v>5.8600001335144</v>
       </c>
       <c r="G734" t="n">
-        <v>5.24438142776489</v>
+        <v>5.24438095092773</v>
       </c>
       <c r="H734" t="s">
         <v>8</v>
@@ -19557,7 +19557,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G738" t="n">
-        <v>5.26227998733521</v>
+        <v>5.26228046417236</v>
       </c>
       <c r="H738" t="s">
         <v>8</v>
@@ -19895,7 +19895,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G751" t="n">
-        <v>4.99379634857178</v>
+        <v>4.99379587173462</v>
       </c>
       <c r="H751" t="s">
         <v>8</v>
@@ -20077,7 +20077,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G758" t="n">
-        <v>5.31597709655762</v>
+        <v>5.31597661972046</v>
       </c>
       <c r="H758" t="s">
         <v>8</v>
@@ -20103,7 +20103,7 @@
         <v>6</v>
       </c>
       <c r="G759" t="n">
-        <v>5.36967372894287</v>
+        <v>5.36967325210571</v>
       </c>
       <c r="H759" t="s">
         <v>8</v>
@@ -20129,7 +20129,7 @@
         <v>6</v>
       </c>
       <c r="G760" t="n">
-        <v>5.36967372894287</v>
+        <v>5.36967325210571</v>
       </c>
       <c r="H760" t="s">
         <v>8</v>
@@ -20155,7 +20155,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G761" t="n">
-        <v>5.47706699371338</v>
+        <v>5.47706651687622</v>
       </c>
       <c r="H761" t="s">
         <v>8</v>
@@ -20337,7 +20337,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G768" t="n">
-        <v>5.72765207290649</v>
+        <v>5.72765159606934</v>
       </c>
       <c r="H768" t="s">
         <v>8</v>
@@ -20389,7 +20389,7 @@
         <v>6.51999998092651</v>
       </c>
       <c r="G770" t="n">
-        <v>5.83504486083984</v>
+        <v>5.835045337677</v>
       </c>
       <c r="H770" t="s">
         <v>8</v>
@@ -20415,7 +20415,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G771" t="n">
-        <v>5.72765207290649</v>
+        <v>5.72765159606934</v>
       </c>
       <c r="H771" t="s">
         <v>8</v>
@@ -20441,7 +20441,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G772" t="n">
-        <v>5.72765207290649</v>
+        <v>5.72765159606934</v>
       </c>
       <c r="H772" t="s">
         <v>8</v>
@@ -20519,7 +20519,7 @@
         <v>6.5</v>
       </c>
       <c r="G775" t="n">
-        <v>5.81714630126953</v>
+        <v>5.81714582443237</v>
       </c>
       <c r="H775" t="s">
         <v>8</v>
@@ -20571,7 +20571,7 @@
         <v>6.5</v>
       </c>
       <c r="G777" t="n">
-        <v>5.81714630126953</v>
+        <v>5.81714582443237</v>
       </c>
       <c r="H777" t="s">
         <v>8</v>
@@ -20675,7 +20675,7 @@
         <v>6.73999977111816</v>
       </c>
       <c r="G781" t="n">
-        <v>6.03193330764771</v>
+        <v>6.03193283081055</v>
       </c>
       <c r="H781" t="s">
         <v>8</v>
@@ -20753,7 +20753,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G784" t="n">
-        <v>6.08562994003296</v>
+        <v>6.08563041687012</v>
       </c>
       <c r="H784" t="s">
         <v>8</v>
@@ -20883,7 +20883,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G789" t="n">
-        <v>5.88874197006226</v>
+        <v>5.8887414932251</v>
       </c>
       <c r="H789" t="s">
         <v>8</v>
@@ -20935,7 +20935,7 @@
         <v>6.53999996185303</v>
       </c>
       <c r="G791" t="n">
-        <v>5.85294437408447</v>
+        <v>5.85294389724731</v>
       </c>
       <c r="H791" t="s">
         <v>8</v>
@@ -20961,7 +20961,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G792" t="n">
-        <v>5.72765207290649</v>
+        <v>5.72765159606934</v>
       </c>
       <c r="H792" t="s">
         <v>8</v>
@@ -21091,7 +21091,7 @@
         <v>6.5</v>
       </c>
       <c r="G797" t="n">
-        <v>5.81714630126953</v>
+        <v>5.81714582443237</v>
       </c>
       <c r="H797" t="s">
         <v>8</v>
@@ -21117,7 +21117,7 @@
         <v>6.5</v>
       </c>
       <c r="G798" t="n">
-        <v>5.81714630126953</v>
+        <v>5.81714582443237</v>
       </c>
       <c r="H798" t="s">
         <v>8</v>
@@ -21195,7 +21195,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G801" t="n">
-        <v>5.88874197006226</v>
+        <v>5.8887414932251</v>
       </c>
       <c r="H801" t="s">
         <v>8</v>
@@ -21351,7 +21351,7 @@
         <v>6.42000007629395</v>
       </c>
       <c r="G807" t="n">
-        <v>5.74555063247681</v>
+        <v>5.74555110931396</v>
       </c>
       <c r="H807" t="s">
         <v>8</v>
@@ -21455,7 +21455,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G811" t="n">
-        <v>5.5486626625061</v>
+        <v>5.54866218566895</v>
       </c>
       <c r="H811" t="s">
         <v>8</v>
@@ -21507,7 +21507,7 @@
         <v>5.8600001335144</v>
       </c>
       <c r="G813" t="n">
-        <v>5.24438142776489</v>
+        <v>5.24438095092773</v>
       </c>
       <c r="H813" t="s">
         <v>8</v>
@@ -21533,7 +21533,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G814" t="n">
-        <v>5.13698768615723</v>
+        <v>5.13698720932007</v>
       </c>
       <c r="H814" t="s">
         <v>8</v>
@@ -21559,7 +21559,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G815" t="n">
-        <v>5.13698768615723</v>
+        <v>5.13698720932007</v>
       </c>
       <c r="H815" t="s">
         <v>8</v>
@@ -21585,7 +21585,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G816" t="n">
-        <v>5.35177421569824</v>
+        <v>5.3517746925354</v>
       </c>
       <c r="H816" t="s">
         <v>8</v>
@@ -21611,7 +21611,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G817" t="n">
-        <v>4.83270645141602</v>
+        <v>4.83270597457886</v>
       </c>
       <c r="H817" t="s">
         <v>8</v>
@@ -21715,7 +21715,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G821" t="n">
-        <v>4.83270645141602</v>
+        <v>4.83270597457886</v>
       </c>
       <c r="H821" t="s">
         <v>8</v>
@@ -21767,7 +21767,7 @@
         <v>6</v>
       </c>
       <c r="G823" t="n">
-        <v>5.36967372894287</v>
+        <v>5.36967325210571</v>
       </c>
       <c r="H823" t="s">
         <v>8</v>
@@ -21793,7 +21793,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G824" t="n">
-        <v>5.47706699371338</v>
+        <v>5.47706651687622</v>
       </c>
       <c r="H824" t="s">
         <v>8</v>
@@ -21845,7 +21845,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G826" t="n">
-        <v>5.5486626625061</v>
+        <v>5.54866218566895</v>
       </c>
       <c r="H826" t="s">
         <v>8</v>
@@ -21871,7 +21871,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G827" t="n">
-        <v>5.5486626625061</v>
+        <v>5.54866218566895</v>
       </c>
       <c r="H827" t="s">
         <v>8</v>
@@ -21897,7 +21897,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G828" t="n">
-        <v>5.5486626625061</v>
+        <v>5.54866218566895</v>
       </c>
       <c r="H828" t="s">
         <v>8</v>
@@ -21923,7 +21923,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G829" t="n">
-        <v>5.5486626625061</v>
+        <v>5.54866218566895</v>
       </c>
       <c r="H829" t="s">
         <v>8</v>
@@ -21949,7 +21949,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G830" t="n">
-        <v>5.72765207290649</v>
+        <v>5.72765159606934</v>
       </c>
       <c r="H830" t="s">
         <v>8</v>
@@ -22001,7 +22001,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G832" t="n">
-        <v>5.72765207290649</v>
+        <v>5.72765159606934</v>
       </c>
       <c r="H832" t="s">
         <v>8</v>
@@ -22183,7 +22183,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G839" t="n">
-        <v>5.5486626625061</v>
+        <v>5.54866218566895</v>
       </c>
       <c r="H839" t="s">
         <v>8</v>
@@ -22209,7 +22209,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G840" t="n">
-        <v>5.53076314926147</v>
+        <v>5.53076362609863</v>
       </c>
       <c r="H840" t="s">
         <v>8</v>
@@ -22365,7 +22365,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G846" t="n">
-        <v>5.72765207290649</v>
+        <v>5.72765159606934</v>
       </c>
       <c r="H846" t="s">
         <v>8</v>
@@ -22417,7 +22417,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G848" t="n">
-        <v>5.72765207290649</v>
+        <v>5.72765159606934</v>
       </c>
       <c r="H848" t="s">
         <v>8</v>
@@ -22495,7 +22495,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G851" t="n">
-        <v>5.70975255966187</v>
+        <v>5.70975303649902</v>
       </c>
       <c r="H851" t="s">
         <v>8</v>
@@ -22521,7 +22521,7 @@
         <v>6.5</v>
       </c>
       <c r="G852" t="n">
-        <v>5.81714630126953</v>
+        <v>5.81714582443237</v>
       </c>
       <c r="H852" t="s">
         <v>8</v>
@@ -22547,7 +22547,7 @@
         <v>6.5</v>
       </c>
       <c r="G853" t="n">
-        <v>5.81714630126953</v>
+        <v>5.81714582443237</v>
       </c>
       <c r="H853" t="s">
         <v>8</v>
@@ -22625,7 +22625,7 @@
         <v>6.42000007629395</v>
       </c>
       <c r="G856" t="n">
-        <v>5.74555063247681</v>
+        <v>5.74555110931396</v>
       </c>
       <c r="H856" t="s">
         <v>8</v>
@@ -22651,7 +22651,7 @@
         <v>6.51999998092651</v>
       </c>
       <c r="G857" t="n">
-        <v>5.83504486083984</v>
+        <v>5.835045337677</v>
       </c>
       <c r="H857" t="s">
         <v>8</v>
@@ -22677,7 +22677,7 @@
         <v>6.51999998092651</v>
       </c>
       <c r="G858" t="n">
-        <v>5.83504486083984</v>
+        <v>5.835045337677</v>
       </c>
       <c r="H858" t="s">
         <v>8</v>
@@ -22703,7 +22703,7 @@
         <v>6.51999998092651</v>
       </c>
       <c r="G859" t="n">
-        <v>5.83504486083984</v>
+        <v>5.835045337677</v>
       </c>
       <c r="H859" t="s">
         <v>8</v>
@@ -22807,7 +22807,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G863" t="n">
-        <v>5.88874197006226</v>
+        <v>5.8887414932251</v>
       </c>
       <c r="H863" t="s">
         <v>8</v>
@@ -22859,7 +22859,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G865" t="n">
-        <v>5.88874197006226</v>
+        <v>5.8887414932251</v>
       </c>
       <c r="H865" t="s">
         <v>8</v>
@@ -22937,7 +22937,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G868" t="n">
-        <v>6.08562994003296</v>
+        <v>6.08563041687012</v>
       </c>
       <c r="H868" t="s">
         <v>8</v>
@@ -22963,7 +22963,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G869" t="n">
-        <v>6.08562994003296</v>
+        <v>6.08563041687012</v>
       </c>
       <c r="H869" t="s">
         <v>8</v>
@@ -23223,7 +23223,7 @@
         <v>6.5</v>
       </c>
       <c r="G879" t="n">
-        <v>5.81714630126953</v>
+        <v>5.81714582443237</v>
       </c>
       <c r="H879" t="s">
         <v>8</v>
@@ -23275,7 +23275,7 @@
         <v>6.73999977111816</v>
       </c>
       <c r="G881" t="n">
-        <v>6.03193330764771</v>
+        <v>6.03193283081055</v>
       </c>
       <c r="H881" t="s">
         <v>8</v>
@@ -23327,7 +23327,7 @@
         <v>6.71999979019165</v>
       </c>
       <c r="G883" t="n">
-        <v>6.01403379440308</v>
+        <v>6.01403427124023</v>
       </c>
       <c r="H883" t="s">
         <v>8</v>
@@ -23353,7 +23353,7 @@
         <v>6.71999979019165</v>
       </c>
       <c r="G884" t="n">
-        <v>6.01403379440308</v>
+        <v>6.01403427124023</v>
       </c>
       <c r="H884" t="s">
         <v>8</v>
@@ -23483,7 +23483,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G889" t="n">
-        <v>5.72765207290649</v>
+        <v>5.72765159606934</v>
       </c>
       <c r="H889" t="s">
         <v>8</v>
@@ -23509,7 +23509,7 @@
         <v>6.5</v>
       </c>
       <c r="G890" t="n">
-        <v>5.81714630126953</v>
+        <v>5.81714582443237</v>
       </c>
       <c r="H890" t="s">
         <v>8</v>
@@ -23535,7 +23535,7 @@
         <v>6.71999979019165</v>
       </c>
       <c r="G891" t="n">
-        <v>6.01403379440308</v>
+        <v>6.01403427124023</v>
       </c>
       <c r="H891" t="s">
         <v>8</v>
@@ -23561,7 +23561,7 @@
         <v>6.71999979019165</v>
       </c>
       <c r="G892" t="n">
-        <v>6.01403379440308</v>
+        <v>6.01403427124023</v>
       </c>
       <c r="H892" t="s">
         <v>8</v>
@@ -23587,7 +23587,7 @@
         <v>6.71999979019165</v>
       </c>
       <c r="G893" t="n">
-        <v>6.01403379440308</v>
+        <v>6.01403427124023</v>
       </c>
       <c r="H893" t="s">
         <v>8</v>
@@ -23847,7 +23847,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G903" t="n">
-        <v>6.98057556152344</v>
+        <v>6.9805760383606</v>
       </c>
       <c r="H903" t="s">
         <v>8</v>
@@ -23899,7 +23899,7 @@
         <v>7.57999992370605</v>
       </c>
       <c r="G905" t="n">
-        <v>6.78368759155273</v>
+        <v>6.78368711471558</v>
       </c>
       <c r="H905" t="s">
         <v>8</v>
@@ -23977,7 +23977,7 @@
         <v>7.03999996185303</v>
       </c>
       <c r="G908" t="n">
-        <v>6.30041694641113</v>
+        <v>6.30041646957397</v>
       </c>
       <c r="H908" t="s">
         <v>8</v>
@@ -24029,7 +24029,7 @@
         <v>7.1399998664856</v>
       </c>
       <c r="G910" t="n">
-        <v>6.38991117477417</v>
+        <v>6.38991165161133</v>
       </c>
       <c r="H910" t="s">
         <v>8</v>
@@ -24211,7 +24211,7 @@
         <v>7.26000022888184</v>
       </c>
       <c r="G917" t="n">
-        <v>6.49730491638184</v>
+        <v>6.49730539321899</v>
       </c>
       <c r="H917" t="s">
         <v>8</v>
@@ -24237,7 +24237,7 @@
         <v>7.42000007629395</v>
       </c>
       <c r="G918" t="n">
-        <v>6.64049673080444</v>
+        <v>6.64049625396729</v>
       </c>
       <c r="H918" t="s">
         <v>8</v>
@@ -24315,7 +24315,7 @@
         <v>7.34000015258789</v>
       </c>
       <c r="G921" t="n">
-        <v>6.56890058517456</v>
+        <v>6.56890106201172</v>
       </c>
       <c r="H921" t="s">
         <v>8</v>
@@ -24367,7 +24367,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G923" t="n">
-        <v>6.80158615112305</v>
+        <v>6.80158662796021</v>
       </c>
       <c r="H923" t="s">
         <v>8</v>
@@ -24601,7 +24601,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G932" t="n">
-        <v>6.80158615112305</v>
+        <v>6.80158662796021</v>
       </c>
       <c r="H932" t="s">
         <v>8</v>
@@ -24653,7 +24653,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G934" t="n">
-        <v>6.80158615112305</v>
+        <v>6.80158662796021</v>
       </c>
       <c r="H934" t="s">
         <v>8</v>
@@ -24705,7 +24705,7 @@
         <v>7.34000015258789</v>
       </c>
       <c r="G936" t="n">
-        <v>6.56890058517456</v>
+        <v>6.56890106201172</v>
       </c>
       <c r="H936" t="s">
         <v>8</v>
@@ -24861,7 +24861,7 @@
         <v>7.26000022888184</v>
       </c>
       <c r="G942" t="n">
-        <v>6.49730491638184</v>
+        <v>6.49730539321899</v>
       </c>
       <c r="H942" t="s">
         <v>8</v>
@@ -24887,7 +24887,7 @@
         <v>7.26000022888184</v>
       </c>
       <c r="G943" t="n">
-        <v>6.49730491638184</v>
+        <v>6.49730539321899</v>
       </c>
       <c r="H943" t="s">
         <v>8</v>
@@ -24913,7 +24913,7 @@
         <v>7.26000022888184</v>
       </c>
       <c r="G944" t="n">
-        <v>6.49730491638184</v>
+        <v>6.49730539321899</v>
       </c>
       <c r="H944" t="s">
         <v>8</v>
@@ -24965,7 +24965,7 @@
         <v>7.21999979019165</v>
       </c>
       <c r="G946" t="n">
-        <v>6.46150732040405</v>
+        <v>6.46150684356689</v>
       </c>
       <c r="H946" t="s">
         <v>8</v>
@@ -24991,7 +24991,7 @@
         <v>7.21999979019165</v>
       </c>
       <c r="G947" t="n">
-        <v>6.46150732040405</v>
+        <v>6.46150684356689</v>
       </c>
       <c r="H947" t="s">
         <v>8</v>
@@ -25355,7 +25355,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G961" t="n">
-        <v>6.08562994003296</v>
+        <v>6.08563041687012</v>
       </c>
       <c r="H961" t="s">
         <v>8</v>
@@ -25641,7 +25641,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G972" t="n">
-        <v>6.08562994003296</v>
+        <v>6.08563041687012</v>
       </c>
       <c r="H972" t="s">
         <v>8</v>
@@ -26993,7 +26993,7 @@
         <v>7.25</v>
       </c>
       <c r="G1024" t="n">
-        <v>6.48835563659668</v>
+        <v>6.48835515975952</v>
       </c>
       <c r="H1024" t="s">
         <v>8</v>
@@ -27097,7 +27097,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G1028" t="n">
-        <v>6.84633350372314</v>
+        <v>6.8463339805603</v>
       </c>
       <c r="H1028" t="s">
         <v>8</v>
@@ -27123,7 +27123,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G1029" t="n">
-        <v>6.98057556152344</v>
+        <v>6.9805760383606</v>
       </c>
       <c r="H1029" t="s">
         <v>8</v>
@@ -27149,7 +27149,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G1030" t="n">
-        <v>6.98057556152344</v>
+        <v>6.9805760383606</v>
       </c>
       <c r="H1030" t="s">
         <v>8</v>
@@ -27175,7 +27175,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G1031" t="n">
-        <v>6.98057556152344</v>
+        <v>6.9805760383606</v>
       </c>
       <c r="H1031" t="s">
         <v>8</v>
@@ -27227,7 +27227,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G1033" t="n">
-        <v>6.75683927536011</v>
+        <v>6.75683975219727</v>
       </c>
       <c r="H1033" t="s">
         <v>8</v>
@@ -27253,7 +27253,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G1034" t="n">
-        <v>6.75683927536011</v>
+        <v>6.75683975219727</v>
       </c>
       <c r="H1034" t="s">
         <v>8</v>
@@ -27279,7 +27279,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G1035" t="n">
-        <v>6.75683927536011</v>
+        <v>6.75683975219727</v>
       </c>
       <c r="H1035" t="s">
         <v>8</v>
@@ -27305,7 +27305,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G1036" t="n">
-        <v>6.75683927536011</v>
+        <v>6.75683975219727</v>
       </c>
       <c r="H1036" t="s">
         <v>8</v>
@@ -27331,7 +27331,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G1037" t="n">
-        <v>6.98057556152344</v>
+        <v>6.9805760383606</v>
       </c>
       <c r="H1037" t="s">
         <v>8</v>
@@ -27357,7 +27357,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G1038" t="n">
-        <v>6.80158615112305</v>
+        <v>6.80158662796021</v>
       </c>
       <c r="H1038" t="s">
         <v>8</v>
@@ -27383,7 +27383,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G1039" t="n">
-        <v>6.80158615112305</v>
+        <v>6.80158662796021</v>
       </c>
       <c r="H1039" t="s">
         <v>8</v>
@@ -27435,7 +27435,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G1041" t="n">
-        <v>6.80158615112305</v>
+        <v>6.80158662796021</v>
       </c>
       <c r="H1041" t="s">
         <v>8</v>
@@ -27461,7 +27461,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G1042" t="n">
-        <v>6.80158615112305</v>
+        <v>6.80158662796021</v>
       </c>
       <c r="H1042" t="s">
         <v>8</v>
@@ -27487,7 +27487,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G1043" t="n">
-        <v>6.80158615112305</v>
+        <v>6.80158662796021</v>
       </c>
       <c r="H1043" t="s">
         <v>8</v>
@@ -27513,7 +27513,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G1044" t="n">
-        <v>6.80158615112305</v>
+        <v>6.80158662796021</v>
       </c>
       <c r="H1044" t="s">
         <v>8</v>
@@ -27539,7 +27539,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G1045" t="n">
-        <v>6.80158615112305</v>
+        <v>6.80158662796021</v>
       </c>
       <c r="H1045" t="s">
         <v>8</v>
@@ -27565,7 +27565,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G1046" t="n">
-        <v>6.80158615112305</v>
+        <v>6.80158662796021</v>
       </c>
       <c r="H1046" t="s">
         <v>8</v>
@@ -27591,7 +27591,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G1047" t="n">
-        <v>6.80158615112305</v>
+        <v>6.80158662796021</v>
       </c>
       <c r="H1047" t="s">
         <v>8</v>
@@ -27617,7 +27617,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G1048" t="n">
-        <v>6.98057556152344</v>
+        <v>6.9805760383606</v>
       </c>
       <c r="H1048" t="s">
         <v>8</v>
@@ -27643,7 +27643,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G1049" t="n">
-        <v>6.84633350372314</v>
+        <v>6.8463339805603</v>
       </c>
       <c r="H1049" t="s">
         <v>8</v>
@@ -27669,7 +27669,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G1050" t="n">
-        <v>6.98057556152344</v>
+        <v>6.9805760383606</v>
       </c>
       <c r="H1050" t="s">
         <v>8</v>
@@ -27695,7 +27695,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G1051" t="n">
-        <v>6.98057556152344</v>
+        <v>6.9805760383606</v>
       </c>
       <c r="H1051" t="s">
         <v>8</v>
@@ -27721,7 +27721,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G1052" t="n">
-        <v>6.98057556152344</v>
+        <v>6.9805760383606</v>
       </c>
       <c r="H1052" t="s">
         <v>8</v>
@@ -27747,7 +27747,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G1053" t="n">
-        <v>6.80158615112305</v>
+        <v>6.80158662796021</v>
       </c>
       <c r="H1053" t="s">
         <v>8</v>
@@ -27903,7 +27903,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G1059" t="n">
-        <v>6.75683927536011</v>
+        <v>6.75683975219727</v>
       </c>
       <c r="H1059" t="s">
         <v>8</v>
@@ -27929,7 +27929,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G1060" t="n">
-        <v>6.75683927536011</v>
+        <v>6.75683975219727</v>
       </c>
       <c r="H1060" t="s">
         <v>8</v>
@@ -27955,7 +27955,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G1061" t="n">
-        <v>6.75683927536011</v>
+        <v>6.75683975219727</v>
       </c>
       <c r="H1061" t="s">
         <v>8</v>
@@ -28371,7 +28371,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G1077" t="n">
-        <v>5.86189365386963</v>
+        <v>5.86189413070679</v>
       </c>
       <c r="H1077" t="s">
         <v>8</v>
@@ -28397,7 +28397,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G1078" t="n">
-        <v>5.72765207290649</v>
+        <v>5.72765159606934</v>
       </c>
       <c r="H1078" t="s">
         <v>8</v>
@@ -28423,7 +28423,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G1079" t="n">
-        <v>5.86189365386963</v>
+        <v>5.86189413070679</v>
       </c>
       <c r="H1079" t="s">
         <v>8</v>
@@ -28501,7 +28501,7 @@
         <v>6</v>
       </c>
       <c r="G1082" t="n">
-        <v>5.36967372894287</v>
+        <v>5.36967325210571</v>
       </c>
       <c r="H1082" t="s">
         <v>8</v>
@@ -28527,7 +28527,7 @@
         <v>6</v>
       </c>
       <c r="G1083" t="n">
-        <v>5.36967372894287</v>
+        <v>5.36967325210571</v>
       </c>
       <c r="H1083" t="s">
         <v>8</v>
@@ -28553,7 +28553,7 @@
         <v>6</v>
       </c>
       <c r="G1084" t="n">
-        <v>5.36967372894287</v>
+        <v>5.36967325210571</v>
       </c>
       <c r="H1084" t="s">
         <v>8</v>
@@ -28605,7 +28605,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G1086" t="n">
-        <v>5.32492637634277</v>
+        <v>5.32492589950562</v>
       </c>
       <c r="H1086" t="s">
         <v>8</v>
@@ -28631,7 +28631,7 @@
         <v>6</v>
       </c>
       <c r="G1087" t="n">
-        <v>5.36967372894287</v>
+        <v>5.36967325210571</v>
       </c>
       <c r="H1087" t="s">
         <v>8</v>
@@ -28657,7 +28657,7 @@
         <v>6</v>
       </c>
       <c r="G1088" t="n">
-        <v>5.36967372894287</v>
+        <v>5.36967325210571</v>
       </c>
       <c r="H1088" t="s">
         <v>8</v>
@@ -28683,7 +28683,7 @@
         <v>6</v>
       </c>
       <c r="G1089" t="n">
-        <v>5.36967372894287</v>
+        <v>5.36967325210571</v>
       </c>
       <c r="H1089" t="s">
         <v>8</v>
@@ -28709,7 +28709,7 @@
         <v>6</v>
       </c>
       <c r="G1090" t="n">
-        <v>5.36967372894287</v>
+        <v>5.36967325210571</v>
       </c>
       <c r="H1090" t="s">
         <v>8</v>
@@ -28735,7 +28735,7 @@
         <v>6</v>
       </c>
       <c r="G1091" t="n">
-        <v>5.36967372894287</v>
+        <v>5.36967325210571</v>
       </c>
       <c r="H1091" t="s">
         <v>8</v>
@@ -28761,7 +28761,7 @@
         <v>6</v>
       </c>
       <c r="G1092" t="n">
-        <v>5.36967372894287</v>
+        <v>5.36967325210571</v>
       </c>
       <c r="H1092" t="s">
         <v>8</v>
@@ -28787,7 +28787,7 @@
         <v>6</v>
       </c>
       <c r="G1093" t="n">
-        <v>5.36967372894287</v>
+        <v>5.36967325210571</v>
       </c>
       <c r="H1093" t="s">
         <v>8</v>
@@ -28813,7 +28813,7 @@
         <v>6</v>
       </c>
       <c r="G1094" t="n">
-        <v>5.36967372894287</v>
+        <v>5.36967325210571</v>
       </c>
       <c r="H1094" t="s">
         <v>8</v>
@@ -28839,7 +28839,7 @@
         <v>6</v>
       </c>
       <c r="G1095" t="n">
-        <v>5.36967372894287</v>
+        <v>5.36967325210571</v>
       </c>
       <c r="H1095" t="s">
         <v>8</v>
@@ -29099,7 +29099,7 @@
         <v>6.25</v>
       </c>
       <c r="G1105" t="n">
-        <v>5.5934100151062</v>
+        <v>5.59340953826904</v>
       </c>
       <c r="H1105" t="s">
         <v>8</v>
@@ -29125,7 +29125,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G1106" t="n">
-        <v>5.5486626625061</v>
+        <v>5.54866218566895</v>
       </c>
       <c r="H1106" t="s">
         <v>8</v>
@@ -29229,7 +29229,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G1110" t="n">
-        <v>5.5486626625061</v>
+        <v>5.54866218566895</v>
       </c>
       <c r="H1110" t="s">
         <v>8</v>
@@ -29281,7 +29281,7 @@
         <v>6.5</v>
       </c>
       <c r="G1112" t="n">
-        <v>5.81714630126953</v>
+        <v>5.81714582443237</v>
       </c>
       <c r="H1112" t="s">
         <v>8</v>
@@ -29307,7 +29307,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G1113" t="n">
-        <v>5.72765207290649</v>
+        <v>5.72765159606934</v>
       </c>
       <c r="H1113" t="s">
         <v>8</v>
@@ -29333,7 +29333,7 @@
         <v>6.5</v>
       </c>
       <c r="G1114" t="n">
-        <v>5.81714630126953</v>
+        <v>5.81714582443237</v>
       </c>
       <c r="H1114" t="s">
         <v>8</v>
@@ -29437,7 +29437,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G1118" t="n">
-        <v>6.08562994003296</v>
+        <v>6.08563041687012</v>
       </c>
       <c r="H1118" t="s">
         <v>8</v>
@@ -29593,7 +29593,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G1124" t="n">
-        <v>6.75683927536011</v>
+        <v>6.75683975219727</v>
       </c>
       <c r="H1124" t="s">
         <v>8</v>
@@ -47926,6 +47926,32 @@
         <v>2.51999998092651</v>
       </c>
       <c r="H1829" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1830">
+      <c r="A1830" s="1" t="n">
+        <v>46290.2916666667</v>
+      </c>
+      <c r="B1830" t="n">
+        <v>330</v>
+      </c>
+      <c r="C1830" t="n">
+        <v>2.51999998092651</v>
+      </c>
+      <c r="D1830" t="n">
+        <v>2.42000007629395</v>
+      </c>
+      <c r="E1830" t="n">
+        <v>2.51999998092651</v>
+      </c>
+      <c r="F1830" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G1830" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H1830" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/PTR.MI.xlsx
+++ b/data/PTR.MI.xlsx
@@ -421,7 +421,7 @@
         <v>3.75</v>
       </c>
       <c r="G2" t="n">
-        <v>3.2548463344574</v>
+        <v>3.25484609603882</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -447,7 +447,7 @@
         <v>3.7409999370575</v>
       </c>
       <c r="G3" t="n">
-        <v>3.24703478813171</v>
+        <v>3.24703431129456</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>3.69250011444092</v>
       </c>
       <c r="G6" t="n">
-        <v>3.2049388885498</v>
+        <v>3.20493865013123</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>3.59400010108948</v>
       </c>
       <c r="G13" t="n">
-        <v>3.11944484710693</v>
+        <v>3.11944460868835</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G15" t="n">
-        <v>3.14201164245605</v>
+        <v>3.14201140403748</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G16" t="n">
-        <v>3.14201164245605</v>
+        <v>3.14201140403748</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G17" t="n">
-        <v>3.0899338722229</v>
+        <v>3.08993434906006</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G18" t="n">
-        <v>3.14201164245605</v>
+        <v>3.14201140403748</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G19" t="n">
-        <v>3.13333177566528</v>
+        <v>3.13333201408386</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>3.49850010871887</v>
       </c>
       <c r="G23" t="n">
-        <v>3.03655457496643</v>
+        <v>3.03655481338501</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G26" t="n">
-        <v>2.96842002868652</v>
+        <v>2.96841979026794</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>3.35050010681152</v>
       </c>
       <c r="G27" t="n">
-        <v>2.90809679031372</v>
+        <v>2.9080970287323</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G30" t="n">
-        <v>3.0899338722229</v>
+        <v>3.08993434906006</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G31" t="n">
-        <v>3.0899338722229</v>
+        <v>3.08993434906006</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>3.5</v>
       </c>
       <c r="G35" t="n">
-        <v>3.03785634040833</v>
+        <v>3.0378565788269</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>3.46499991416931</v>
       </c>
       <c r="G36" t="n">
-        <v>3.00747776031494</v>
+        <v>3.00747799873352</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G37" t="n">
-        <v>3.14201164245605</v>
+        <v>3.14201140403748</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G38" t="n">
-        <v>3.19408917427063</v>
+        <v>3.19408893585205</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G41" t="n">
-        <v>3.42843818664551</v>
+        <v>3.42843794822693</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>3.67499995231628</v>
       </c>
       <c r="G44" t="n">
-        <v>3.18974924087524</v>
+        <v>3.18974947929382</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>3.71499991416931</v>
       </c>
       <c r="G46" t="n">
-        <v>3.22446775436401</v>
+        <v>3.22446751594543</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G48" t="n">
-        <v>3.15069150924683</v>
+        <v>3.15069127082825</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>3.71499991416931</v>
       </c>
       <c r="G50" t="n">
-        <v>3.22446775436401</v>
+        <v>3.22446751594543</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>3.75</v>
       </c>
       <c r="G51" t="n">
-        <v>3.2548463344574</v>
+        <v>3.25484609603882</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G55" t="n">
-        <v>3.16805052757263</v>
+        <v>3.16805076599121</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G56" t="n">
-        <v>3.15069150924683</v>
+        <v>3.15069127082825</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G57" t="n">
-        <v>3.15069150924683</v>
+        <v>3.15069127082825</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>3.66499996185303</v>
       </c>
       <c r="G59" t="n">
-        <v>3.18106985092163</v>
+        <v>3.18106961250305</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>3.66499996185303</v>
       </c>
       <c r="G61" t="n">
-        <v>3.18106985092163</v>
+        <v>3.18106961250305</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G63" t="n">
-        <v>3.14201164245605</v>
+        <v>3.14201140403748</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>3.5550000667572</v>
       </c>
       <c r="G64" t="n">
-        <v>3.08559441566467</v>
+        <v>3.08559417724609</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>3.5550000667572</v>
       </c>
       <c r="G65" t="n">
-        <v>3.08559441566467</v>
+        <v>3.08559417724609</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>3.63499999046326</v>
       </c>
       <c r="G67" t="n">
-        <v>3.15503096580505</v>
+        <v>3.15503072738647</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G70" t="n">
-        <v>3.16805052757263</v>
+        <v>3.16805076599121</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G79" t="n">
-        <v>3.14201164245605</v>
+        <v>3.14201140403748</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>3.67499995231628</v>
       </c>
       <c r="G80" t="n">
-        <v>3.18974924087524</v>
+        <v>3.18974947929382</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G82" t="n">
-        <v>3.14201164245605</v>
+        <v>3.14201140403748</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G87" t="n">
-        <v>3.37636065483093</v>
+        <v>3.37636089324951</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G88" t="n">
-        <v>3.42843818664551</v>
+        <v>3.42843794822693</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G89" t="n">
-        <v>3.42843818664551</v>
+        <v>3.42843794822693</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G90" t="n">
-        <v>3.41975855827332</v>
+        <v>3.41975879669189</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G91" t="n">
-        <v>3.51523423194885</v>
+        <v>3.51523399353027</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>4</v>
       </c>
       <c r="G92" t="n">
-        <v>3.47183609008789</v>
+        <v>3.47183585166931</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G94" t="n">
-        <v>3.41975855827332</v>
+        <v>3.41975879669189</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G95" t="n">
-        <v>3.51523423194885</v>
+        <v>3.51523399353027</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>4.02500009536743</v>
       </c>
       <c r="G96" t="n">
-        <v>3.49353504180908</v>
+        <v>3.49353528022766</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G97" t="n">
-        <v>3.42843818664551</v>
+        <v>3.42843794822693</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>4.00500011444092</v>
       </c>
       <c r="G98" t="n">
-        <v>3.47617602348328</v>
+        <v>3.4761757850647</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>3.95499992370605</v>
       </c>
       <c r="G100" t="n">
-        <v>3.43277788162231</v>
+        <v>3.43277764320374</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G101" t="n">
-        <v>3.54127240180969</v>
+        <v>3.54127287864685</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G102" t="n">
-        <v>3.44579720497131</v>
+        <v>3.44579744338989</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>4</v>
       </c>
       <c r="G103" t="n">
-        <v>3.47183609008789</v>
+        <v>3.47183585166931</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>4</v>
       </c>
       <c r="G105" t="n">
-        <v>3.47183609008789</v>
+        <v>3.47183585166931</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G107" t="n">
-        <v>3.51523423194885</v>
+        <v>3.51523399353027</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G108" t="n">
-        <v>3.54995250701904</v>
+        <v>3.54995226860046</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G109" t="n">
-        <v>3.54995250701904</v>
+        <v>3.54995226860046</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G110" t="n">
-        <v>3.64542770385742</v>
+        <v>3.64542746543884</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G111" t="n">
-        <v>3.64542770385742</v>
+        <v>3.64542746543884</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>4.41499996185303</v>
       </c>
       <c r="G112" t="n">
-        <v>3.83203887939453</v>
+        <v>3.83203911781311</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>4.5</v>
       </c>
       <c r="G113" t="n">
-        <v>3.90581560134888</v>
+        <v>3.9058153629303</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>4.5</v>
       </c>
       <c r="G114" t="n">
-        <v>3.90581560134888</v>
+        <v>3.9058153629303</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G115" t="n">
-        <v>3.87109708786011</v>
+        <v>3.87109684944153</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G118" t="n">
-        <v>4.03600931167603</v>
+        <v>4.03600978851318</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G119" t="n">
-        <v>3.96657276153564</v>
+        <v>3.96657299995422</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G121" t="n">
-        <v>3.92317509651184</v>
+        <v>3.92317485809326</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G123" t="n">
-        <v>3.88845658302307</v>
+        <v>3.88845610618591</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G124" t="n">
-        <v>3.94921374320984</v>
+        <v>3.9492130279541</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G125" t="n">
-        <v>3.94921374320984</v>
+        <v>3.9492130279541</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G126" t="n">
-        <v>4.03600931167603</v>
+        <v>4.03600978851318</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G128" t="n">
-        <v>4.37451362609863</v>
+        <v>4.37451314926147</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G129" t="n">
-        <v>4.38319301605225</v>
+        <v>4.38319253921509</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G136" t="n">
-        <v>4.20092153549194</v>
+        <v>4.2009220123291</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>5</v>
       </c>
       <c r="G139" t="n">
-        <v>4.33979463577271</v>
+        <v>4.33979511260986</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G141" t="n">
-        <v>4.42659139633179</v>
+        <v>4.42659091949463</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G142" t="n">
-        <v>4.35715389251709</v>
+        <v>4.35715436935425</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>5</v>
       </c>
       <c r="G143" t="n">
-        <v>4.33979463577271</v>
+        <v>4.33979511260986</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G144" t="n">
-        <v>4.42659139633179</v>
+        <v>4.42659091949463</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G146" t="n">
-        <v>4.54810476303101</v>
+        <v>4.54810523986816</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G147" t="n">
-        <v>4.70433807373047</v>
+        <v>4.70433759689331</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G149" t="n">
-        <v>4.54810476303101</v>
+        <v>4.54810523986816</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>5.13000011444092</v>
       </c>
       <c r="G150" t="n">
-        <v>4.45263004302979</v>
+        <v>4.45262956619263</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G151" t="n">
-        <v>4.54810476303101</v>
+        <v>4.54810523986816</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G154" t="n">
-        <v>4.00129175186157</v>
+        <v>4.00129127502441</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>4.75500011444092</v>
       </c>
       <c r="G155" t="n">
-        <v>4.12714529037476</v>
+        <v>4.1271448135376</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G156" t="n">
-        <v>4.31375646591187</v>
+        <v>4.31375598907471</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G157" t="n">
-        <v>4.23563957214355</v>
+        <v>4.23564004898071</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G158" t="n">
-        <v>4.00129175186157</v>
+        <v>4.00129127502441</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G160" t="n">
-        <v>4.06204843521118</v>
+        <v>4.06204748153687</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G162" t="n">
-        <v>3.99261140823364</v>
+        <v>3.99261164665222</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G165" t="n">
-        <v>3.26352596282959</v>
+        <v>3.26352572441101</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G168" t="n">
-        <v>2.95974040031433</v>
+        <v>2.95974016189575</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>3.375</v>
       </c>
       <c r="G171" t="n">
-        <v>2.92936182022095</v>
+        <v>2.92936158180237</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G172" t="n">
-        <v>2.90766263008118</v>
+        <v>2.9076623916626</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G183" t="n">
-        <v>3.19408917427063</v>
+        <v>3.19408893585205</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G185" t="n">
-        <v>3.19408917427063</v>
+        <v>3.19408893585205</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G189" t="n">
-        <v>3.2288076877594</v>
+        <v>3.22880744934082</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G191" t="n">
-        <v>3.28088521957397</v>
+        <v>3.2808849811554</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G195" t="n">
-        <v>3.34164190292358</v>
+        <v>3.34164237976074</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G196" t="n">
-        <v>3.35900115966797</v>
+        <v>3.35900139808655</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G197" t="n">
-        <v>3.35900115966797</v>
+        <v>3.35900139808655</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G199" t="n">
-        <v>3.54995250701904</v>
+        <v>3.54995226860046</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G200" t="n">
-        <v>3.48051595687866</v>
+        <v>3.48051571846008</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>3.75</v>
       </c>
       <c r="G202" t="n">
-        <v>3.2548463344574</v>
+        <v>3.25484609603882</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>3.75</v>
       </c>
       <c r="G203" t="n">
-        <v>3.2548463344574</v>
+        <v>3.25484609603882</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G204" t="n">
-        <v>3.19408917427063</v>
+        <v>3.19408893585205</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G207" t="n">
-        <v>3.37636065483093</v>
+        <v>3.37636089324951</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G209" t="n">
-        <v>3.24616646766663</v>
+        <v>3.24616670608521</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G210" t="n">
-        <v>3.2288076877594</v>
+        <v>3.22880744934082</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G212" t="n">
-        <v>3.27220559120178</v>
+        <v>3.2722053527832</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G213" t="n">
-        <v>3.2288076877594</v>
+        <v>3.22880744934082</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G214" t="n">
-        <v>3.28088521957397</v>
+        <v>3.2808849811554</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G215" t="n">
-        <v>3.26352596282959</v>
+        <v>3.26352572441101</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G216" t="n">
-        <v>3.28088521957397</v>
+        <v>3.2808849811554</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G218" t="n">
-        <v>3.28088521957397</v>
+        <v>3.2808849811554</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G220" t="n">
-        <v>3.26352596282959</v>
+        <v>3.26352572441101</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G223" t="n">
-        <v>3.34164190292358</v>
+        <v>3.34164237976074</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G225" t="n">
-        <v>3.35900115966797</v>
+        <v>3.35900139808655</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G226" t="n">
-        <v>3.37636065483093</v>
+        <v>3.37636089324951</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G228" t="n">
-        <v>3.42843818664551</v>
+        <v>3.42843794822693</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G229" t="n">
-        <v>3.27220559120178</v>
+        <v>3.2722053527832</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G230" t="n">
-        <v>3.37636065483093</v>
+        <v>3.37636089324951</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G233" t="n">
-        <v>3.37636065483093</v>
+        <v>3.37636089324951</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G234" t="n">
-        <v>3.37636065483093</v>
+        <v>3.37636089324951</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G235" t="n">
-        <v>3.32428312301636</v>
+        <v>3.32428288459778</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G236" t="n">
-        <v>3.32428312301636</v>
+        <v>3.32428288459778</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G241" t="n">
-        <v>3.34164190292358</v>
+        <v>3.34164237976074</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G244" t="n">
-        <v>3.42843818664551</v>
+        <v>3.42843794822693</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G245" t="n">
-        <v>3.27220559120178</v>
+        <v>3.2722053527832</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G247" t="n">
-        <v>3.24616646766663</v>
+        <v>3.24616670608521</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G248" t="n">
-        <v>3.24616646766663</v>
+        <v>3.24616670608521</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G250" t="n">
-        <v>3.16805052757263</v>
+        <v>3.16805076599121</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G256" t="n">
-        <v>3.2288076877594</v>
+        <v>3.22880744934082</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>3.75</v>
       </c>
       <c r="G257" t="n">
-        <v>3.2548463344574</v>
+        <v>3.25484609603882</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G259" t="n">
-        <v>3.2288076877594</v>
+        <v>3.22880744934082</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G260" t="n">
-        <v>3.0899338722229</v>
+        <v>3.08993434906006</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G262" t="n">
-        <v>3.16805052757263</v>
+        <v>3.16805076599121</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G263" t="n">
-        <v>3.0899338722229</v>
+        <v>3.08993434906006</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G264" t="n">
-        <v>3.13333177566528</v>
+        <v>3.13333201408386</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G265" t="n">
-        <v>3.07257485389709</v>
+        <v>3.07257509231567</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7363,7 +7363,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G269" t="n">
-        <v>3.24616646766663</v>
+        <v>3.24616670608521</v>
       </c>
       <c r="H269" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G270" t="n">
-        <v>3.19408917427063</v>
+        <v>3.19408893585205</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G271" t="n">
-        <v>3.13333177566528</v>
+        <v>3.13333201408386</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G274" t="n">
-        <v>2.93370127677917</v>
+        <v>2.93370151519775</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G275" t="n">
-        <v>2.96842002868652</v>
+        <v>2.96841979026794</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G278" t="n">
-        <v>3.07257485389709</v>
+        <v>3.07257509231567</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>3.5</v>
       </c>
       <c r="G280" t="n">
-        <v>3.03785634040833</v>
+        <v>3.0378565788269</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G281" t="n">
-        <v>3.06389546394348</v>
+        <v>3.0638952255249</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G282" t="n">
-        <v>3.06389546394348</v>
+        <v>3.0638952255249</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G283" t="n">
-        <v>3.06389546394348</v>
+        <v>3.0638952255249</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G284" t="n">
-        <v>2.94238138198853</v>
+        <v>2.94238090515137</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G285" t="n">
-        <v>2.94238138198853</v>
+        <v>2.94238090515137</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>3.5</v>
       </c>
       <c r="G287" t="n">
-        <v>3.03785634040833</v>
+        <v>3.0378565788269</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>3.5</v>
       </c>
       <c r="G291" t="n">
-        <v>3.03785634040833</v>
+        <v>3.0378565788269</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>3.5</v>
       </c>
       <c r="G292" t="n">
-        <v>3.03785634040833</v>
+        <v>3.0378565788269</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>3.5</v>
       </c>
       <c r="G295" t="n">
-        <v>3.03785634040833</v>
+        <v>3.0378565788269</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G299" t="n">
-        <v>2.86426472663879</v>
+        <v>2.86426448822021</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G300" t="n">
-        <v>2.86426472663879</v>
+        <v>2.86426448822021</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G301" t="n">
-        <v>2.86426472663879</v>
+        <v>2.86426448822021</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G302" t="n">
-        <v>2.95974040031433</v>
+        <v>2.95974016189575</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G303" t="n">
-        <v>2.8816237449646</v>
+        <v>2.88162398338318</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G304" t="n">
-        <v>2.87294459342957</v>
+        <v>2.87294411659241</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>3.5</v>
       </c>
       <c r="G305" t="n">
-        <v>3.03785634040833</v>
+        <v>3.0378565788269</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G309" t="n">
-        <v>3.16805052757263</v>
+        <v>3.16805076599121</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G310" t="n">
-        <v>3.16805052757263</v>
+        <v>3.16805076599121</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G314" t="n">
-        <v>3.19408917427063</v>
+        <v>3.19408893585205</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>3.75</v>
       </c>
       <c r="G316" t="n">
-        <v>3.2548463344574</v>
+        <v>3.25484609603882</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G322" t="n">
-        <v>3.16805052757263</v>
+        <v>3.16805076599121</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G326" t="n">
-        <v>3.19408917427063</v>
+        <v>3.19408893585205</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G327" t="n">
-        <v>3.14201164245605</v>
+        <v>3.14201140403748</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G330" t="n">
-        <v>3.19408917427063</v>
+        <v>3.19408893585205</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>3.5</v>
       </c>
       <c r="G332" t="n">
-        <v>3.03785634040833</v>
+        <v>3.0378565788269</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G334" t="n">
-        <v>3.15069150924683</v>
+        <v>3.15069127082825</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G343" t="n">
-        <v>3.15069150924683</v>
+        <v>3.15069127082825</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G344" t="n">
-        <v>3.15069150924683</v>
+        <v>3.15069127082825</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G348" t="n">
-        <v>3.42843818664551</v>
+        <v>3.42843794822693</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G352" t="n">
-        <v>3.34164190292358</v>
+        <v>3.34164237976074</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G354" t="n">
-        <v>3.34164190292358</v>
+        <v>3.34164237976074</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G356" t="n">
-        <v>3.42843818664551</v>
+        <v>3.42843794822693</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G357" t="n">
-        <v>3.42843818664551</v>
+        <v>3.42843794822693</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G358" t="n">
-        <v>3.37636065483093</v>
+        <v>3.37636089324951</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>4</v>
       </c>
       <c r="G359" t="n">
-        <v>3.47183609008789</v>
+        <v>3.47183585166931</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>4</v>
       </c>
       <c r="G360" t="n">
-        <v>3.47183609008789</v>
+        <v>3.47183585166931</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G363" t="n">
-        <v>3.53336215019226</v>
+        <v>3.53336191177368</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G366" t="n">
-        <v>3.47183609008789</v>
+        <v>3.47183585166931</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G372" t="n">
-        <v>3.57730937004089</v>
+        <v>3.57730984687805</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G376" t="n">
-        <v>3.82341408729553</v>
+        <v>3.82341432571411</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G378" t="n">
-        <v>3.84978270530701</v>
+        <v>3.84978294372559</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G379" t="n">
-        <v>3.90251970291138</v>
+        <v>3.90251994132996</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G380" t="n">
-        <v>3.99041366577148</v>
+        <v>3.99041390419006</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>4.5</v>
       </c>
       <c r="G381" t="n">
-        <v>3.95525598526001</v>
+        <v>3.95525622367859</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G382" t="n">
-        <v>3.92888784408569</v>
+        <v>3.92888760566711</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G383" t="n">
-        <v>3.92009806632996</v>
+        <v>3.92009830474854</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10457,7 +10457,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G388" t="n">
-        <v>3.55094122886658</v>
+        <v>3.550940990448</v>
       </c>
       <c r="H388" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G390" t="n">
-        <v>3.69157218933105</v>
+        <v>3.69157242774963</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10587,7 +10587,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G393" t="n">
-        <v>3.67399334907532</v>
+        <v>3.67399311065674</v>
       </c>
       <c r="H393" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G394" t="n">
-        <v>3.67399334907532</v>
+        <v>3.67399311065674</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G395" t="n">
-        <v>3.744309425354</v>
+        <v>3.74430966377258</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G397" t="n">
-        <v>3.82341408729553</v>
+        <v>3.82341432571411</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G403" t="n">
-        <v>3.68278288841248</v>
+        <v>3.68278312683105</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G404" t="n">
-        <v>3.90251970291138</v>
+        <v>3.90251994132996</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G405" t="n">
-        <v>3.84978270530701</v>
+        <v>3.84978294372559</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -10925,7 +10925,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G406" t="n">
-        <v>3.84099316596985</v>
+        <v>3.84099292755127</v>
       </c>
       <c r="H406" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G409" t="n">
-        <v>4.04315090179443</v>
+        <v>4.04315042495728</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G410" t="n">
-        <v>3.99920344352722</v>
+        <v>3.9992036819458</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G411" t="n">
-        <v>3.99920344352722</v>
+        <v>3.9992036819458</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G414" t="n">
-        <v>4.04315090179443</v>
+        <v>4.04315042495728</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G415" t="n">
-        <v>4.04315090179443</v>
+        <v>4.04315042495728</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G416" t="n">
-        <v>3.99920344352722</v>
+        <v>3.9992036819458</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11237,7 +11237,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G418" t="n">
-        <v>4.08709859848022</v>
+        <v>4.08709764480591</v>
       </c>
       <c r="H418" t="s">
         <v>8</v>
@@ -11289,7 +11289,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G420" t="n">
-        <v>4.30683469772339</v>
+        <v>4.30683422088623</v>
       </c>
       <c r="H420" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>5</v>
       </c>
       <c r="G421" t="n">
-        <v>4.3947286605835</v>
+        <v>4.39472913742065</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>5</v>
       </c>
       <c r="G422" t="n">
-        <v>4.3947286605835</v>
+        <v>4.39472913742065</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11367,7 +11367,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G423" t="n">
-        <v>4.28046560287476</v>
+        <v>4.28046607971191</v>
       </c>
       <c r="H423" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G424" t="n">
-        <v>4.30683469772339</v>
+        <v>4.30683422088623</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G427" t="n">
-        <v>4.34199237823486</v>
+        <v>4.34199190139771</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G428" t="n">
-        <v>4.21015024185181</v>
+        <v>4.21015071868896</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>4.75</v>
       </c>
       <c r="G429" t="n">
-        <v>4.17499256134033</v>
+        <v>4.17499303817749</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G430" t="n">
-        <v>4.28925561904907</v>
+        <v>4.28925609588623</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G431" t="n">
-        <v>4.28925561904907</v>
+        <v>4.28925609588623</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G432" t="n">
-        <v>4.21015024185181</v>
+        <v>4.21015071868896</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G433" t="n">
-        <v>4.32441329956055</v>
+        <v>4.32441377639771</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>4.75</v>
       </c>
       <c r="G435" t="n">
-        <v>4.17499256134033</v>
+        <v>4.17499303817749</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11705,7 +11705,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G436" t="n">
-        <v>4.21015024185181</v>
+        <v>4.21015071868896</v>
       </c>
       <c r="H436" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G441" t="n">
-        <v>4.30683469772339</v>
+        <v>4.30683422088623</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11861,7 +11861,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G442" t="n">
-        <v>4.30683469772339</v>
+        <v>4.30683422088623</v>
       </c>
       <c r="H442" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G443" t="n">
-        <v>4.35078144073486</v>
+        <v>4.35078191757202</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -11913,7 +11913,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G444" t="n">
-        <v>4.34199237823486</v>
+        <v>4.34199190139771</v>
       </c>
       <c r="H444" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G445" t="n">
-        <v>4.2628870010376</v>
+        <v>4.26288652420044</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G446" t="n">
-        <v>4.34199237823486</v>
+        <v>4.34199190139771</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>5</v>
       </c>
       <c r="G449" t="n">
-        <v>4.3947286605835</v>
+        <v>4.39472913742065</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G451" t="n">
-        <v>4.30683469772339</v>
+        <v>4.30683422088623</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12147,7 +12147,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G453" t="n">
-        <v>4.21015024185181</v>
+        <v>4.21015071868896</v>
       </c>
       <c r="H453" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>4.75</v>
       </c>
       <c r="G454" t="n">
-        <v>4.17499256134033</v>
+        <v>4.17499303817749</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12225,7 +12225,7 @@
         <v>4.75</v>
       </c>
       <c r="G456" t="n">
-        <v>4.17499256134033</v>
+        <v>4.17499303817749</v>
       </c>
       <c r="H456" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>4.75</v>
       </c>
       <c r="G457" t="n">
-        <v>4.17499256134033</v>
+        <v>4.17499303817749</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12277,7 +12277,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G458" t="n">
-        <v>4.05193996429443</v>
+        <v>4.05194044113159</v>
       </c>
       <c r="H458" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G459" t="n">
-        <v>4.02557134628296</v>
+        <v>4.02557182312012</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G460" t="n">
-        <v>4.02557134628296</v>
+        <v>4.02557182312012</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12355,7 +12355,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G461" t="n">
-        <v>4.02557134628296</v>
+        <v>4.02557182312012</v>
       </c>
       <c r="H461" t="s">
         <v>8</v>
@@ -12381,7 +12381,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G462" t="n">
-        <v>4.08709859848022</v>
+        <v>4.08709764480591</v>
       </c>
       <c r="H462" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G464" t="n">
-        <v>4.21015024185181</v>
+        <v>4.21015071868896</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12459,7 +12459,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G465" t="n">
-        <v>4.2628870010376</v>
+        <v>4.26288652420044</v>
       </c>
       <c r="H465" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G466" t="n">
-        <v>4.28925561904907</v>
+        <v>4.28925609588623</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G467" t="n">
-        <v>4.35078144073486</v>
+        <v>4.35078191757202</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12537,7 +12537,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G468" t="n">
-        <v>4.50020217895508</v>
+        <v>4.50020265579224</v>
       </c>
       <c r="H468" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G475" t="n">
-        <v>4.77250909805298</v>
+        <v>4.77250957489014</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12771,7 +12771,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G477" t="n">
-        <v>4.75483322143555</v>
+        <v>4.75483369827271</v>
       </c>
       <c r="H477" t="s">
         <v>8</v>
@@ -13187,7 +13187,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G493" t="n">
-        <v>4.26874494552612</v>
+        <v>4.26874446868896</v>
       </c>
       <c r="H493" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G494" t="n">
-        <v>4.22455501556396</v>
+        <v>4.22455453872681</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13239,7 +13239,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G495" t="n">
-        <v>4.17152690887451</v>
+        <v>4.17152643203735</v>
       </c>
       <c r="H495" t="s">
         <v>8</v>
@@ -13265,7 +13265,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G496" t="n">
-        <v>4.10966110229492</v>
+        <v>4.10966062545776</v>
       </c>
       <c r="H496" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G497" t="n">
-        <v>4.03011846542358</v>
+        <v>4.03011894226074</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13317,7 +13317,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G498" t="n">
-        <v>4.03011846542358</v>
+        <v>4.03011894226074</v>
       </c>
       <c r="H498" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G503" t="n">
-        <v>4.10966110229492</v>
+        <v>4.10966062545776</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13473,7 +13473,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G504" t="n">
-        <v>4.10966110229492</v>
+        <v>4.10966062545776</v>
       </c>
       <c r="H504" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G506" t="n">
-        <v>4.10082292556763</v>
+        <v>4.10082244873047</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G507" t="n">
-        <v>4.22455501556396</v>
+        <v>4.22455453872681</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G511" t="n">
-        <v>4.10966110229492</v>
+        <v>4.10966062545776</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13681,7 +13681,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G512" t="n">
-        <v>4.10966110229492</v>
+        <v>4.10966062545776</v>
       </c>
       <c r="H512" t="s">
         <v>8</v>
@@ -13785,7 +13785,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G516" t="n">
-        <v>4.32177209854126</v>
+        <v>4.32177257537842</v>
       </c>
       <c r="H516" t="s">
         <v>8</v>
@@ -13941,7 +13941,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G522" t="n">
-        <v>4.59574937820435</v>
+        <v>4.5957498550415</v>
       </c>
       <c r="H522" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G523" t="n">
-        <v>4.59574937820435</v>
+        <v>4.5957498550415</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -13993,7 +13993,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G524" t="n">
-        <v>4.59574937820435</v>
+        <v>4.5957498550415</v>
       </c>
       <c r="H524" t="s">
         <v>8</v>
@@ -14019,7 +14019,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G525" t="n">
-        <v>4.59574937820435</v>
+        <v>4.5957498550415</v>
       </c>
       <c r="H525" t="s">
         <v>8</v>
@@ -14227,7 +14227,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G533" t="n">
-        <v>4.33061075210571</v>
+        <v>4.33061027526855</v>
       </c>
       <c r="H533" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G534" t="n">
-        <v>4.26874494552612</v>
+        <v>4.26874446868896</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G535" t="n">
-        <v>4.2864203453064</v>
+        <v>4.28641986846924</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14305,7 +14305,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G536" t="n">
-        <v>4.2864203453064</v>
+        <v>4.28641986846924</v>
       </c>
       <c r="H536" t="s">
         <v>8</v>
@@ -14331,7 +14331,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G537" t="n">
-        <v>4.2864203453064</v>
+        <v>4.28641986846924</v>
       </c>
       <c r="H537" t="s">
         <v>8</v>
@@ -14357,7 +14357,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G538" t="n">
-        <v>4.2864203453064</v>
+        <v>4.28641986846924</v>
       </c>
       <c r="H538" t="s">
         <v>8</v>
@@ -14487,7 +14487,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G543" t="n">
-        <v>4.38363838195801</v>
+        <v>4.38363790512085</v>
       </c>
       <c r="H543" t="s">
         <v>8</v>
@@ -14565,7 +14565,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G546" t="n">
-        <v>4.33944845199585</v>
+        <v>4.33944797515869</v>
       </c>
       <c r="H546" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G547" t="n">
-        <v>4.33944845199585</v>
+        <v>4.33944797515869</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G548" t="n">
-        <v>4.33944845199585</v>
+        <v>4.33944797515869</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14669,7 +14669,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G550" t="n">
-        <v>4.21571683883667</v>
+        <v>4.21571636199951</v>
       </c>
       <c r="H550" t="s">
         <v>8</v>
@@ -14877,7 +14877,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G558" t="n">
-        <v>4.10966110229492</v>
+        <v>4.10966062545776</v>
       </c>
       <c r="H558" t="s">
         <v>8</v>
@@ -14981,7 +14981,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G562" t="n">
-        <v>4.10966110229492</v>
+        <v>4.10966062545776</v>
       </c>
       <c r="H562" t="s">
         <v>8</v>
@@ -15033,7 +15033,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G564" t="n">
-        <v>4.33061075210571</v>
+        <v>4.33061027526855</v>
       </c>
       <c r="H564" t="s">
         <v>8</v>
@@ -15059,7 +15059,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G565" t="n">
-        <v>4.33061075210571</v>
+        <v>4.33061027526855</v>
       </c>
       <c r="H565" t="s">
         <v>8</v>
@@ -15189,7 +15189,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G570" t="n">
-        <v>4.59574937820435</v>
+        <v>4.5957498550415</v>
       </c>
       <c r="H570" t="s">
         <v>8</v>
@@ -15371,7 +15371,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G577" t="n">
-        <v>4.91391658782959</v>
+        <v>4.91391706466675</v>
       </c>
       <c r="H577" t="s">
         <v>8</v>
@@ -15397,7 +15397,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G578" t="n">
-        <v>4.9669451713562</v>
+        <v>4.96694469451904</v>
       </c>
       <c r="H578" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G580" t="n">
-        <v>4.94926929473877</v>
+        <v>4.94926881790161</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15553,7 +15553,7 @@
         <v>6.03999996185303</v>
       </c>
       <c r="G584" t="n">
-        <v>5.33814001083374</v>
+        <v>5.3381404876709</v>
       </c>
       <c r="H584" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G589" t="n">
-        <v>5.65630722045898</v>
+        <v>5.65630769729614</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15709,7 +15709,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G590" t="n">
-        <v>5.65630722045898</v>
+        <v>5.65630769729614</v>
       </c>
       <c r="H590" t="s">
         <v>8</v>
@@ -15761,7 +15761,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G592" t="n">
-        <v>5.51489973068237</v>
+        <v>5.51489925384521</v>
       </c>
       <c r="H592" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G599" t="n">
-        <v>5.65630722045898</v>
+        <v>5.65630769729614</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -15969,7 +15969,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G600" t="n">
-        <v>5.72701072692871</v>
+        <v>5.72701120376587</v>
       </c>
       <c r="H600" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G602" t="n">
-        <v>5.49722337722778</v>
+        <v>5.49722385406494</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16073,7 +16073,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G604" t="n">
-        <v>5.51489973068237</v>
+        <v>5.51489925384521</v>
       </c>
       <c r="H604" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G605" t="n">
-        <v>5.72701072692871</v>
+        <v>5.72701120376587</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G606" t="n">
-        <v>5.72701072692871</v>
+        <v>5.72701120376587</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G611" t="n">
-        <v>5.72701072692871</v>
+        <v>5.72701120376587</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16281,7 +16281,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G612" t="n">
-        <v>5.72701072692871</v>
+        <v>5.72701120376587</v>
       </c>
       <c r="H612" t="s">
         <v>8</v>
@@ -16307,7 +16307,7 @@
         <v>6.53999996185303</v>
       </c>
       <c r="G613" t="n">
-        <v>5.78003883361816</v>
+        <v>5.78003931045532</v>
       </c>
       <c r="H613" t="s">
         <v>8</v>
@@ -16333,7 +16333,7 @@
         <v>6.5</v>
       </c>
       <c r="G614" t="n">
-        <v>5.74468660354614</v>
+        <v>5.7446870803833</v>
       </c>
       <c r="H614" t="s">
         <v>8</v>
@@ -16359,7 +16359,7 @@
         <v>6.5</v>
       </c>
       <c r="G615" t="n">
-        <v>5.74468660354614</v>
+        <v>5.7446870803833</v>
       </c>
       <c r="H615" t="s">
         <v>8</v>
@@ -16411,7 +16411,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G617" t="n">
-        <v>5.92144680023193</v>
+        <v>5.92144632339478</v>
       </c>
       <c r="H617" t="s">
         <v>8</v>
@@ -16437,7 +16437,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G618" t="n">
-        <v>5.81539058685303</v>
+        <v>5.81539106369019</v>
       </c>
       <c r="H618" t="s">
         <v>8</v>
@@ -16463,7 +16463,7 @@
         <v>6.5</v>
       </c>
       <c r="G619" t="n">
-        <v>5.74468660354614</v>
+        <v>5.7446870803833</v>
       </c>
       <c r="H619" t="s">
         <v>8</v>
@@ -16541,7 +16541,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G622" t="n">
-        <v>5.39116764068604</v>
+        <v>5.39116811752319</v>
       </c>
       <c r="H622" t="s">
         <v>8</v>
@@ -16593,7 +16593,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G624" t="n">
-        <v>5.65630722045898</v>
+        <v>5.65630769729614</v>
       </c>
       <c r="H624" t="s">
         <v>8</v>
@@ -16619,7 +16619,7 @@
         <v>6.5</v>
       </c>
       <c r="G625" t="n">
-        <v>5.74468660354614</v>
+        <v>5.7446870803833</v>
       </c>
       <c r="H625" t="s">
         <v>8</v>
@@ -16645,7 +16645,7 @@
         <v>6.5</v>
       </c>
       <c r="G626" t="n">
-        <v>5.74468660354614</v>
+        <v>5.7446870803833</v>
       </c>
       <c r="H626" t="s">
         <v>8</v>
@@ -16723,7 +16723,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G629" t="n">
-        <v>5.92144680023193</v>
+        <v>5.92144632339478</v>
       </c>
       <c r="H629" t="s">
         <v>8</v>
@@ -16775,7 +16775,7 @@
         <v>6.78000020980835</v>
       </c>
       <c r="G631" t="n">
-        <v>5.99215126037598</v>
+        <v>5.99215078353882</v>
       </c>
       <c r="H631" t="s">
         <v>8</v>
@@ -16801,7 +16801,7 @@
         <v>6.78000020980835</v>
       </c>
       <c r="G632" t="n">
-        <v>5.99215126037598</v>
+        <v>5.99215078353882</v>
       </c>
       <c r="H632" t="s">
         <v>8</v>
@@ -16983,7 +16983,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G639" t="n">
-        <v>5.5856032371521</v>
+        <v>5.58560371398926</v>
       </c>
       <c r="H639" t="s">
         <v>8</v>
@@ -17087,7 +17087,7 @@
         <v>6.53999996185303</v>
       </c>
       <c r="G643" t="n">
-        <v>5.78003883361816</v>
+        <v>5.78003931045532</v>
       </c>
       <c r="H643" t="s">
         <v>8</v>
@@ -17243,7 +17243,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G649" t="n">
-        <v>5.39116764068604</v>
+        <v>5.39116811752319</v>
       </c>
       <c r="H649" t="s">
         <v>8</v>
@@ -17295,7 +17295,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G651" t="n">
-        <v>5.28511238098145</v>
+        <v>5.28511190414429</v>
       </c>
       <c r="H651" t="s">
         <v>8</v>
@@ -17347,7 +17347,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G653" t="n">
-        <v>5.1260290145874</v>
+        <v>5.12602853775024</v>
       </c>
       <c r="H653" t="s">
         <v>8</v>
@@ -17373,7 +17373,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G654" t="n">
-        <v>4.94926929473877</v>
+        <v>4.94926881790161</v>
       </c>
       <c r="H654" t="s">
         <v>8</v>
@@ -17399,7 +17399,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G655" t="n">
-        <v>4.94926929473877</v>
+        <v>4.94926881790161</v>
       </c>
       <c r="H655" t="s">
         <v>8</v>
@@ -17477,7 +17477,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G658" t="n">
-        <v>5.1260290145874</v>
+        <v>5.12602853775024</v>
       </c>
       <c r="H658" t="s">
         <v>8</v>
@@ -17659,7 +17659,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G665" t="n">
-        <v>5.19673299789429</v>
+        <v>5.19673252105713</v>
       </c>
       <c r="H665" t="s">
         <v>8</v>
@@ -17711,7 +17711,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G667" t="n">
-        <v>4.77250909805298</v>
+        <v>4.77250957489014</v>
       </c>
       <c r="H667" t="s">
         <v>8</v>
@@ -17763,7 +17763,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G669" t="n">
-        <v>4.75483322143555</v>
+        <v>4.75483369827271</v>
       </c>
       <c r="H669" t="s">
         <v>8</v>
@@ -17867,7 +17867,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G673" t="n">
-        <v>4.2864203453064</v>
+        <v>4.28641986846924</v>
       </c>
       <c r="H673" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G674" t="n">
-        <v>4.2864203453064</v>
+        <v>4.28641986846924</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -17919,7 +17919,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G675" t="n">
-        <v>4.33061075210571</v>
+        <v>4.33061027526855</v>
       </c>
       <c r="H675" t="s">
         <v>8</v>
@@ -17997,7 +17997,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G678" t="n">
-        <v>4.33061075210571</v>
+        <v>4.33061027526855</v>
       </c>
       <c r="H678" t="s">
         <v>8</v>
@@ -18127,7 +18127,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G683" t="n">
-        <v>4.77250909805298</v>
+        <v>4.77250957489014</v>
       </c>
       <c r="H683" t="s">
         <v>8</v>
@@ -18153,7 +18153,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G684" t="n">
-        <v>4.70180511474609</v>
+        <v>4.70180559158325</v>
       </c>
       <c r="H684" t="s">
         <v>8</v>
@@ -18179,7 +18179,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G685" t="n">
-        <v>4.59574937820435</v>
+        <v>4.5957498550415</v>
       </c>
       <c r="H685" t="s">
         <v>8</v>
@@ -18283,7 +18283,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G689" t="n">
-        <v>4.75483322143555</v>
+        <v>4.75483369827271</v>
       </c>
       <c r="H689" t="s">
         <v>8</v>
@@ -18335,7 +18335,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G691" t="n">
-        <v>4.77250909805298</v>
+        <v>4.77250957489014</v>
       </c>
       <c r="H691" t="s">
         <v>8</v>
@@ -18465,7 +18465,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G696" t="n">
-        <v>4.9669451713562</v>
+        <v>4.96694469451904</v>
       </c>
       <c r="H696" t="s">
         <v>8</v>
@@ -18491,7 +18491,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G697" t="n">
-        <v>4.94926929473877</v>
+        <v>4.94926881790161</v>
       </c>
       <c r="H697" t="s">
         <v>8</v>
@@ -18517,7 +18517,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G698" t="n">
-        <v>4.94926929473877</v>
+        <v>4.94926881790161</v>
       </c>
       <c r="H698" t="s">
         <v>8</v>
@@ -18569,7 +18569,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G700" t="n">
-        <v>4.75483322143555</v>
+        <v>4.75483369827271</v>
       </c>
       <c r="H700" t="s">
         <v>8</v>
@@ -18595,7 +18595,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G701" t="n">
-        <v>4.75483322143555</v>
+        <v>4.75483369827271</v>
       </c>
       <c r="H701" t="s">
         <v>8</v>
@@ -18621,7 +18621,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G702" t="n">
-        <v>4.94926929473877</v>
+        <v>4.94926881790161</v>
       </c>
       <c r="H702" t="s">
         <v>8</v>
@@ -18647,7 +18647,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G703" t="n">
-        <v>5.03764915466309</v>
+        <v>5.03764867782593</v>
       </c>
       <c r="H703" t="s">
         <v>8</v>
@@ -18673,7 +18673,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G704" t="n">
-        <v>5.03764915466309</v>
+        <v>5.03764867782593</v>
       </c>
       <c r="H704" t="s">
         <v>8</v>
@@ -18725,7 +18725,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G706" t="n">
-        <v>5.1260290145874</v>
+        <v>5.12602853775024</v>
       </c>
       <c r="H706" t="s">
         <v>8</v>
@@ -18803,7 +18803,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G709" t="n">
-        <v>5.1260290145874</v>
+        <v>5.12602853775024</v>
       </c>
       <c r="H709" t="s">
         <v>8</v>
@@ -18829,7 +18829,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G710" t="n">
-        <v>5.1260290145874</v>
+        <v>5.12602853775024</v>
       </c>
       <c r="H710" t="s">
         <v>8</v>
@@ -18985,7 +18985,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G716" t="n">
-        <v>5.03764915466309</v>
+        <v>5.03764867782593</v>
       </c>
       <c r="H716" t="s">
         <v>8</v>
@@ -19011,7 +19011,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G717" t="n">
-        <v>5.03764915466309</v>
+        <v>5.03764867782593</v>
       </c>
       <c r="H717" t="s">
         <v>8</v>
@@ -19037,7 +19037,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G718" t="n">
-        <v>5.03764915466309</v>
+        <v>5.03764867782593</v>
       </c>
       <c r="H718" t="s">
         <v>8</v>
@@ -19063,7 +19063,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G719" t="n">
-        <v>5.03764915466309</v>
+        <v>5.03764867782593</v>
       </c>
       <c r="H719" t="s">
         <v>8</v>
@@ -19089,7 +19089,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G720" t="n">
-        <v>5.03764915466309</v>
+        <v>5.03764867782593</v>
       </c>
       <c r="H720" t="s">
         <v>8</v>
@@ -19115,7 +19115,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G721" t="n">
-        <v>4.94926929473877</v>
+        <v>4.94926881790161</v>
       </c>
       <c r="H721" t="s">
         <v>8</v>
@@ -19219,7 +19219,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G725" t="n">
-        <v>5.03764915466309</v>
+        <v>5.03764867782593</v>
       </c>
       <c r="H725" t="s">
         <v>8</v>
@@ -48004,6 +48004,32 @@
         <v>2.40000009536743</v>
       </c>
       <c r="H1832" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1833">
+      <c r="A1833" s="1" t="n">
+        <v>46295.2916666667</v>
+      </c>
+      <c r="B1833" t="n">
+        <v>8649</v>
+      </c>
+      <c r="C1833" t="n">
+        <v>2.48000001907349</v>
+      </c>
+      <c r="D1833" t="n">
+        <v>2.33999991416931</v>
+      </c>
+      <c r="E1833" t="n">
+        <v>2.38000011444092</v>
+      </c>
+      <c r="F1833" t="n">
+        <v>2.44000005722046</v>
+      </c>
+      <c r="G1833" t="n">
+        <v>2.44000005722046</v>
+      </c>
+      <c r="H1833" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/PTR.MI.xlsx
+++ b/data/PTR.MI.xlsx
@@ -42593,8 +42593,31 @@
       <c r="E1836" t="n">
         <v>2.46000003814697</v>
       </c>
-      <c r="F1836"/>
+      <c r="F1836" t="n">
+        <v>2.40000009536743</v>
+      </c>
       <c r="G1836" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1837">
+      <c r="A1837" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B1837" t="n">
+        <v>3200</v>
+      </c>
+      <c r="C1837" t="n">
+        <v>2.48000001907349</v>
+      </c>
+      <c r="D1837" t="n">
+        <v>2.40000009536743</v>
+      </c>
+      <c r="E1837" t="n">
+        <v>2.46000003814697</v>
+      </c>
+      <c r="F1837"/>
+      <c r="G1837" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/PTR.MI.xlsx
+++ b/data/PTR.MI.xlsx
@@ -42616,8 +42616,31 @@
       <c r="E1837" t="n">
         <v>2.46000003814697</v>
       </c>
-      <c r="F1837"/>
+      <c r="F1837" t="n">
+        <v>2.40000009536743</v>
+      </c>
       <c r="G1837" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1838">
+      <c r="A1838" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B1838" t="n">
+        <v>500</v>
+      </c>
+      <c r="C1838" t="n">
+        <v>2.38000011444092</v>
+      </c>
+      <c r="D1838" t="n">
+        <v>2.38000011444092</v>
+      </c>
+      <c r="E1838" t="n">
+        <v>2.38000011444092</v>
+      </c>
+      <c r="F1838"/>
+      <c r="G1838" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/PTR.MI.xlsx
+++ b/data/PTR.MI.xlsx
@@ -42639,8 +42639,31 @@
       <c r="E1838" t="n">
         <v>2.38000011444092</v>
       </c>
-      <c r="F1838"/>
+      <c r="F1838" t="n">
+        <v>2.38000011444092</v>
+      </c>
       <c r="G1838" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1839">
+      <c r="A1839" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B1839" t="n">
+        <v>700</v>
+      </c>
+      <c r="C1839" t="n">
+        <v>2.42000007629395</v>
+      </c>
+      <c r="D1839" t="n">
+        <v>2.35999989509583</v>
+      </c>
+      <c r="E1839" t="n">
+        <v>2.35999989509583</v>
+      </c>
+      <c r="F1839"/>
+      <c r="G1839" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/PTR.MI.xlsx
+++ b/data/PTR.MI.xlsx
@@ -42662,8 +42662,31 @@
       <c r="E1839" t="n">
         <v>2.35999989509583</v>
       </c>
-      <c r="F1839"/>
+      <c r="F1839" t="n">
+        <v>2.42000007629395</v>
+      </c>
       <c r="G1839" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1840">
+      <c r="A1840" s="1" t="n">
+        <v>46304.2916666667</v>
+      </c>
+      <c r="B1840" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C1840" t="n">
+        <v>2.40000009536743</v>
+      </c>
+      <c r="D1840" t="n">
+        <v>2.38000011444092</v>
+      </c>
+      <c r="E1840" t="n">
+        <v>2.38000011444092</v>
+      </c>
+      <c r="F1840"/>
+      <c r="G1840" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/PTR.MI.xlsx
+++ b/data/PTR.MI.xlsx
@@ -42692,6 +42692,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1841">
+      <c r="A1841" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B1841" t="n">
+        <v>12192</v>
+      </c>
+      <c r="C1841" t="n">
+        <v>2.42000007629395</v>
+      </c>
+      <c r="D1841" t="n">
+        <v>2.27999997138977</v>
+      </c>
+      <c r="E1841" t="n">
+        <v>2.35999989509583</v>
+      </c>
+      <c r="F1841" t="n">
+        <v>2.42000007629395</v>
+      </c>
+      <c r="G1841" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/PTR.MI.xlsx
+++ b/data/PTR.MI.xlsx
@@ -421,7 +421,7 @@
         <v>3.75</v>
       </c>
       <c r="G2" t="n">
-        <v>3.2548463344574</v>
+        <v>3.25484609603882</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G4" t="n">
-        <v>3.22012805938721</v>
+        <v>3.22012782096863</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>3.56850004196167</v>
       </c>
       <c r="G7" t="n">
-        <v>3.09731197357178</v>
+        <v>3.0973117351532</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>3.5864999294281</v>
       </c>
       <c r="G8" t="n">
-        <v>3.11293482780457</v>
+        <v>3.11293458938599</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G9" t="n">
-        <v>3.05521583557129</v>
+        <v>3.05521559715271</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G15" t="n">
-        <v>3.14201140403748</v>
+        <v>3.14201164245605</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G16" t="n">
-        <v>3.14201140403748</v>
+        <v>3.14201164245605</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G18" t="n">
-        <v>3.14201140403748</v>
+        <v>3.14201164245605</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G22" t="n">
-        <v>3.09861326217651</v>
+        <v>3.09861350059509</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>3.49850010871887</v>
       </c>
       <c r="G23" t="n">
-        <v>3.03655481338501</v>
+        <v>3.03655457496643</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G24" t="n">
-        <v>3.05521583557129</v>
+        <v>3.05521559715271</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G25" t="n">
-        <v>3.05521583557129</v>
+        <v>3.05521559715271</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G26" t="n">
-        <v>2.96842002868652</v>
+        <v>2.96841979026794</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>3.46499991416931</v>
       </c>
       <c r="G36" t="n">
-        <v>3.00747799873352</v>
+        <v>3.00747776031494</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G37" t="n">
-        <v>3.14201140403748</v>
+        <v>3.14201164245605</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>3.67499995231628</v>
       </c>
       <c r="G44" t="n">
-        <v>3.18974924087524</v>
+        <v>3.18974947929382</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G45" t="n">
-        <v>3.17673015594482</v>
+        <v>3.17672991752625</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>3.71499991416931</v>
       </c>
       <c r="G46" t="n">
-        <v>3.22446751594543</v>
+        <v>3.22446775436401</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>3.64499998092651</v>
       </c>
       <c r="G47" t="n">
-        <v>3.16371035575867</v>
+        <v>3.16371059417725</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G48" t="n">
-        <v>3.15069127082825</v>
+        <v>3.15069150924683</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>3.71499991416931</v>
       </c>
       <c r="G50" t="n">
-        <v>3.22446751594543</v>
+        <v>3.22446775436401</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>3.75</v>
       </c>
       <c r="G51" t="n">
-        <v>3.2548463344574</v>
+        <v>3.25484609603882</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G53" t="n">
-        <v>3.17673015594482</v>
+        <v>3.17672991752625</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G56" t="n">
-        <v>3.15069127082825</v>
+        <v>3.15069150924683</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G57" t="n">
-        <v>3.15069127082825</v>
+        <v>3.15069150924683</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G58" t="n">
-        <v>3.17673015594482</v>
+        <v>3.17672991752625</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>3.66499996185303</v>
       </c>
       <c r="G59" t="n">
-        <v>3.18106985092163</v>
+        <v>3.18107008934021</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G60" t="n">
-        <v>3.05521583557129</v>
+        <v>3.05521559715271</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>3.66499996185303</v>
       </c>
       <c r="G61" t="n">
-        <v>3.18106985092163</v>
+        <v>3.18107008934021</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G63" t="n">
-        <v>3.14201140403748</v>
+        <v>3.14201164245605</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>3.5550000667572</v>
       </c>
       <c r="G64" t="n">
-        <v>3.08559417724609</v>
+        <v>3.08559441566467</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>3.5550000667572</v>
       </c>
       <c r="G65" t="n">
-        <v>3.08559417724609</v>
+        <v>3.08559441566467</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G66" t="n">
-        <v>3.09861326217651</v>
+        <v>3.09861350059509</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>3.63499999046326</v>
       </c>
       <c r="G67" t="n">
-        <v>3.15503120422363</v>
+        <v>3.15503072738647</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G79" t="n">
-        <v>3.14201140403748</v>
+        <v>3.14201164245605</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>3.67499995231628</v>
       </c>
       <c r="G80" t="n">
-        <v>3.18974924087524</v>
+        <v>3.18974947929382</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G82" t="n">
-        <v>3.14201140403748</v>
+        <v>3.14201164245605</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>4</v>
       </c>
       <c r="G92" t="n">
-        <v>3.47183609008789</v>
+        <v>3.47183632850647</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>4.02500009536743</v>
       </c>
       <c r="G96" t="n">
-        <v>3.49353504180908</v>
+        <v>3.49353528022766</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>4.00500011444092</v>
       </c>
       <c r="G98" t="n">
-        <v>3.47617602348328</v>
+        <v>3.4761757850647</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G99" t="n">
-        <v>3.59335017204285</v>
+        <v>3.59334993362427</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>3.95499992370605</v>
       </c>
       <c r="G100" t="n">
-        <v>3.43277788162231</v>
+        <v>3.43277764320374</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G101" t="n">
-        <v>3.54127287864685</v>
+        <v>3.54127264022827</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>4</v>
       </c>
       <c r="G103" t="n">
-        <v>3.47183609008789</v>
+        <v>3.47183632850647</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>3.9449999332428</v>
       </c>
       <c r="G104" t="n">
-        <v>3.42409825325012</v>
+        <v>3.42409801483154</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>4</v>
       </c>
       <c r="G105" t="n">
-        <v>3.47183609008789</v>
+        <v>3.47183632850647</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>4.03499984741211</v>
       </c>
       <c r="G106" t="n">
-        <v>3.5022144317627</v>
+        <v>3.50221467018127</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G108" t="n">
-        <v>3.54995250701904</v>
+        <v>3.54995226860046</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G109" t="n">
-        <v>3.54995250701904</v>
+        <v>3.54995226860046</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G110" t="n">
-        <v>3.64542722702026</v>
+        <v>3.64542746543884</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G111" t="n">
-        <v>3.64542722702026</v>
+        <v>3.64542746543884</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>4.41499996185303</v>
       </c>
       <c r="G112" t="n">
-        <v>3.83203911781311</v>
+        <v>3.83203887939453</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>4.5</v>
       </c>
       <c r="G113" t="n">
-        <v>3.90581512451172</v>
+        <v>3.9058153629303</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>4.5</v>
       </c>
       <c r="G114" t="n">
-        <v>3.90581512451172</v>
+        <v>3.9058153629303</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G115" t="n">
-        <v>3.87109708786011</v>
+        <v>3.87109684944153</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G116" t="n">
-        <v>3.86241793632507</v>
+        <v>3.86241698265076</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G117" t="n">
-        <v>4.00997114181519</v>
+        <v>4.00997066497803</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G119" t="n">
-        <v>3.96657228469849</v>
+        <v>3.96657276153564</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G120" t="n">
-        <v>3.86241793632507</v>
+        <v>3.86241698265076</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G121" t="n">
-        <v>3.92317509651184</v>
+        <v>3.9231743812561</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G122" t="n">
-        <v>3.94053363800049</v>
+        <v>3.94053339958191</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G123" t="n">
-        <v>3.88845658302307</v>
+        <v>3.88845634460449</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>4.88500022888184</v>
       </c>
       <c r="G127" t="n">
-        <v>4.23998022079468</v>
+        <v>4.23997974395752</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G128" t="n">
-        <v>4.37451362609863</v>
+        <v>4.37451314926147</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G129" t="n">
-        <v>4.3831934928894</v>
+        <v>4.38319301605225</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>4.97499990463257</v>
       </c>
       <c r="G133" t="n">
-        <v>4.31809616088867</v>
+        <v>4.31809568405151</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G138" t="n">
-        <v>4.16620302200317</v>
+        <v>4.16620397567749</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>5</v>
       </c>
       <c r="G139" t="n">
-        <v>4.33979463577271</v>
+        <v>4.33979511260986</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G142" t="n">
-        <v>4.35715389251709</v>
+        <v>4.35715436935425</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>5</v>
       </c>
       <c r="G143" t="n">
-        <v>4.33979463577271</v>
+        <v>4.33979511260986</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G147" t="n">
-        <v>4.70433759689331</v>
+        <v>4.70433807373047</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>5.13000011444092</v>
       </c>
       <c r="G150" t="n">
-        <v>4.45263004302979</v>
+        <v>4.45262956619263</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G153" t="n">
-        <v>4.44395017623901</v>
+        <v>4.44394969940186</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>4.75500011444092</v>
       </c>
       <c r="G155" t="n">
-        <v>4.1271448135376</v>
+        <v>4.12714529037476</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G157" t="n">
-        <v>4.23563957214355</v>
+        <v>4.23564004898071</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G159" t="n">
-        <v>4.09676647186279</v>
+        <v>4.09676599502563</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G161" t="n">
-        <v>4.0446891784668</v>
+        <v>4.04468870162964</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>4.24499988555908</v>
       </c>
       <c r="G163" t="n">
-        <v>3.68448567390442</v>
+        <v>3.68448638916016</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G164" t="n">
-        <v>3.17673015594482</v>
+        <v>3.17672991752625</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G165" t="n">
-        <v>3.26352596282959</v>
+        <v>3.26352572441101</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G167" t="n">
-        <v>2.72539114952087</v>
+        <v>2.72539138793945</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G168" t="n">
-        <v>2.95974016189575</v>
+        <v>2.95973992347717</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>3.375</v>
       </c>
       <c r="G171" t="n">
-        <v>2.92936134338379</v>
+        <v>2.92936158180237</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G173" t="n">
-        <v>3.09861326217651</v>
+        <v>3.09861350059509</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>3.34500002861023</v>
       </c>
       <c r="G174" t="n">
-        <v>2.90332269668579</v>
+        <v>2.90332293510437</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G177" t="n">
-        <v>3.09861326217651</v>
+        <v>3.09861350059509</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G178" t="n">
-        <v>3.28956460952759</v>
+        <v>3.28956437110901</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G182" t="n">
-        <v>3.28956460952759</v>
+        <v>3.28956437110901</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G186" t="n">
-        <v>3.22012805938721</v>
+        <v>3.22012782096863</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G189" t="n">
-        <v>3.22880744934082</v>
+        <v>3.2288076877594</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G192" t="n">
-        <v>3.33296227455139</v>
+        <v>3.33296275138855</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G196" t="n">
-        <v>3.35900115966797</v>
+        <v>3.35900139808655</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G197" t="n">
-        <v>3.35900115966797</v>
+        <v>3.35900139808655</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G198" t="n">
-        <v>3.59335017204285</v>
+        <v>3.59334993362427</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G199" t="n">
-        <v>3.54995250701904</v>
+        <v>3.54995226860046</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G200" t="n">
-        <v>3.48051595687866</v>
+        <v>3.48051571846008</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G201" t="n">
-        <v>3.33296227455139</v>
+        <v>3.33296275138855</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>3.75</v>
       </c>
       <c r="G202" t="n">
-        <v>3.2548463344574</v>
+        <v>3.25484609603882</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>3.75</v>
       </c>
       <c r="G203" t="n">
-        <v>3.2548463344574</v>
+        <v>3.25484609603882</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G209" t="n">
-        <v>3.24616670608521</v>
+        <v>3.24616694450378</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G210" t="n">
-        <v>3.22880744934082</v>
+        <v>3.2288076877594</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G213" t="n">
-        <v>3.22880744934082</v>
+        <v>3.2288076877594</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G215" t="n">
-        <v>3.26352596282959</v>
+        <v>3.26352572441101</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G220" t="n">
-        <v>3.26352596282959</v>
+        <v>3.26352572441101</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G221" t="n">
-        <v>3.28956460952759</v>
+        <v>3.28956437110901</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G224" t="n">
-        <v>3.38504028320312</v>
+        <v>3.38504004478455</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G225" t="n">
-        <v>3.35900115966797</v>
+        <v>3.35900139808655</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G237" t="n">
-        <v>3.28956460952759</v>
+        <v>3.28956437110901</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G242" t="n">
-        <v>3.28956460952759</v>
+        <v>3.28956437110901</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G243" t="n">
-        <v>3.28956460952759</v>
+        <v>3.28956437110901</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G247" t="n">
-        <v>3.24616670608521</v>
+        <v>3.24616694450378</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G248" t="n">
-        <v>3.24616670608521</v>
+        <v>3.24616694450378</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G254" t="n">
-        <v>3.28956460952759</v>
+        <v>3.28956437110901</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G256" t="n">
-        <v>3.22880744934082</v>
+        <v>3.2288076877594</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>3.75</v>
       </c>
       <c r="G257" t="n">
-        <v>3.2548463344574</v>
+        <v>3.25484609603882</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G259" t="n">
-        <v>3.22880744934082</v>
+        <v>3.2288076877594</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7363,7 +7363,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G269" t="n">
-        <v>3.24616670608521</v>
+        <v>3.24616694450378</v>
       </c>
       <c r="H269" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G273" t="n">
-        <v>3.02049732208252</v>
+        <v>3.0204975605011</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G275" t="n">
-        <v>2.96842002868652</v>
+        <v>2.96841979026794</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G276" t="n">
-        <v>3.02917695045471</v>
+        <v>3.02917718887329</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G277" t="n">
-        <v>3.02049732208252</v>
+        <v>3.0204975605011</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G279" t="n">
-        <v>2.99445867538452</v>
+        <v>2.99445843696594</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G284" t="n">
-        <v>2.94238114356995</v>
+        <v>2.94238090515137</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G285" t="n">
-        <v>2.94238114356995</v>
+        <v>2.94238090515137</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G288" t="n">
-        <v>2.99445867538452</v>
+        <v>2.99445843696594</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G290" t="n">
-        <v>3.05521583557129</v>
+        <v>3.05521559715271</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G298" t="n">
-        <v>2.99445867538452</v>
+        <v>2.99445843696594</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G299" t="n">
-        <v>2.86426472663879</v>
+        <v>2.86426448822021</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G300" t="n">
-        <v>2.86426472663879</v>
+        <v>2.86426448822021</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G301" t="n">
-        <v>2.86426472663879</v>
+        <v>2.86426448822021</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G302" t="n">
-        <v>2.95974016189575</v>
+        <v>2.95973992347717</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G303" t="n">
-        <v>2.88162398338318</v>
+        <v>2.8816237449646</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G304" t="n">
-        <v>2.87294411659241</v>
+        <v>2.87294435501099</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G311" t="n">
-        <v>3.22012805938721</v>
+        <v>3.22012782096863</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G312" t="n">
-        <v>3.22012805938721</v>
+        <v>3.22012782096863</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>3.75</v>
       </c>
       <c r="G316" t="n">
-        <v>3.2548463344574</v>
+        <v>3.25484609603882</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G318" t="n">
-        <v>3.17673015594482</v>
+        <v>3.17672991752625</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G327" t="n">
-        <v>3.14201140403748</v>
+        <v>3.14201164245605</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G331" t="n">
-        <v>3.05521583557129</v>
+        <v>3.05521559715271</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G333" t="n">
-        <v>3.02917695045471</v>
+        <v>3.02917718887329</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G334" t="n">
-        <v>3.15069127082825</v>
+        <v>3.15069150924683</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G343" t="n">
-        <v>3.15069127082825</v>
+        <v>3.15069150924683</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G344" t="n">
-        <v>3.15069127082825</v>
+        <v>3.15069150924683</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G345" t="n">
-        <v>3.22012805938721</v>
+        <v>3.22012782096863</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9547,7 +9547,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G353" t="n">
-        <v>3.28956460952759</v>
+        <v>3.28956437110901</v>
       </c>
       <c r="H353" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>4</v>
       </c>
       <c r="G359" t="n">
-        <v>3.47183609008789</v>
+        <v>3.47183632850647</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>4</v>
       </c>
       <c r="G360" t="n">
-        <v>3.47183609008789</v>
+        <v>3.47183632850647</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G362" t="n">
-        <v>3.52457284927368</v>
+        <v>3.52457308769226</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G363" t="n">
-        <v>3.53336215019226</v>
+        <v>3.53336191177368</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G365" t="n">
-        <v>3.55973052978516</v>
+        <v>3.55973076820374</v>
       </c>
       <c r="H365" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G372" t="n">
-        <v>3.57730960845947</v>
+        <v>3.57730984687805</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G373" t="n">
-        <v>3.77946710586548</v>
+        <v>3.77946734428406</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G374" t="n">
-        <v>3.85857224464417</v>
+        <v>3.85857200622559</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10119,7 +10119,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G375" t="n">
-        <v>3.80583548545837</v>
+        <v>3.80583500862122</v>
       </c>
       <c r="H375" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G376" t="n">
-        <v>3.82341384887695</v>
+        <v>3.82341408729553</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G377" t="n">
-        <v>3.70915102958679</v>
+        <v>3.70915126800537</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G378" t="n">
-        <v>3.84978246688843</v>
+        <v>3.84978294372559</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G379" t="n">
-        <v>3.9025194644928</v>
+        <v>3.90251994132996</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G380" t="n">
-        <v>3.99041366577148</v>
+        <v>3.99041342735291</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>4.5</v>
       </c>
       <c r="G381" t="n">
-        <v>3.95525622367859</v>
+        <v>3.95525598526001</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G384" t="n">
-        <v>3.77946710586548</v>
+        <v>3.77946734428406</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G385" t="n">
-        <v>3.77946710586548</v>
+        <v>3.77946734428406</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G386" t="n">
-        <v>3.64762496948242</v>
+        <v>3.647625207901</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10483,7 +10483,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G389" t="n">
-        <v>3.58609867095947</v>
+        <v>3.58609890937805</v>
       </c>
       <c r="H389" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G391" t="n">
-        <v>3.52457284927368</v>
+        <v>3.52457308769226</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G395" t="n">
-        <v>3.74430918693542</v>
+        <v>3.744309425354</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G396" t="n">
-        <v>3.77946710586548</v>
+        <v>3.77946734428406</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G397" t="n">
-        <v>3.82341384887695</v>
+        <v>3.82341408729553</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G398" t="n">
-        <v>3.77946710586548</v>
+        <v>3.77946734428406</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G399" t="n">
-        <v>3.70915102958679</v>
+        <v>3.70915126800537</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10795,7 +10795,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G401" t="n">
-        <v>3.58609867095947</v>
+        <v>3.58609890937805</v>
       </c>
       <c r="H401" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G403" t="n">
-        <v>3.68278336524963</v>
+        <v>3.68278312683105</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G404" t="n">
-        <v>3.9025194644928</v>
+        <v>3.90251994132996</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G405" t="n">
-        <v>3.84978246688843</v>
+        <v>3.84978294372559</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G408" t="n">
-        <v>3.78825640678406</v>
+        <v>3.78825664520264</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G410" t="n">
-        <v>3.99920392036438</v>
+        <v>3.9992036819458</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G411" t="n">
-        <v>3.99920392036438</v>
+        <v>3.9992036819458</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G412" t="n">
-        <v>3.97283530235291</v>
+        <v>3.97283506393433</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G416" t="n">
-        <v>3.99920392036438</v>
+        <v>3.9992036819458</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>4.59000015258789</v>
       </c>
       <c r="G417" t="n">
-        <v>4.03436183929443</v>
+        <v>4.03436136245728</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11237,7 +11237,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G418" t="n">
-        <v>4.08709859848022</v>
+        <v>4.08709812164307</v>
       </c>
       <c r="H418" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G419" t="n">
-        <v>4.14862394332886</v>
+        <v>4.1486234664917</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11289,7 +11289,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G420" t="n">
-        <v>4.30683469772339</v>
+        <v>4.30683422088623</v>
       </c>
       <c r="H420" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>5</v>
       </c>
       <c r="G421" t="n">
-        <v>4.3947286605835</v>
+        <v>4.39472913742065</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>5</v>
       </c>
       <c r="G422" t="n">
-        <v>4.3947286605835</v>
+        <v>4.39472913742065</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G424" t="n">
-        <v>4.30683469772339</v>
+        <v>4.30683422088623</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G426" t="n">
-        <v>4.25409746170044</v>
+        <v>4.2540979385376</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>4.75</v>
       </c>
       <c r="G429" t="n">
-        <v>4.17499256134033</v>
+        <v>4.17499303817749</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G430" t="n">
-        <v>4.28925561904907</v>
+        <v>4.28925609588623</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G431" t="n">
-        <v>4.28925561904907</v>
+        <v>4.28925609588623</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G433" t="n">
-        <v>4.32441329956055</v>
+        <v>4.32441377639771</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>4.75</v>
       </c>
       <c r="G435" t="n">
-        <v>4.17499256134033</v>
+        <v>4.17499303817749</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G438" t="n">
-        <v>4.25409746170044</v>
+        <v>4.2540979385376</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G439" t="n">
-        <v>4.38593912124634</v>
+        <v>4.3859395980835</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G440" t="n">
-        <v>4.38593912124634</v>
+        <v>4.3859395980835</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G441" t="n">
-        <v>4.30683469772339</v>
+        <v>4.30683422088623</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11861,7 +11861,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G442" t="n">
-        <v>4.30683469772339</v>
+        <v>4.30683422088623</v>
       </c>
       <c r="H442" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G445" t="n">
-        <v>4.2628870010376</v>
+        <v>4.26288652420044</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G447" t="n">
-        <v>4.38593912124634</v>
+        <v>4.3859395980835</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>5</v>
       </c>
       <c r="G449" t="n">
-        <v>4.3947286605835</v>
+        <v>4.39472913742065</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12069,7 +12069,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G450" t="n">
-        <v>4.21893978118896</v>
+        <v>4.21894025802612</v>
       </c>
       <c r="H450" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G451" t="n">
-        <v>4.30683469772339</v>
+        <v>4.30683422088623</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G452" t="n">
-        <v>4.21893978118896</v>
+        <v>4.21894025802612</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>4.75</v>
       </c>
       <c r="G454" t="n">
-        <v>4.17499256134033</v>
+        <v>4.17499303817749</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12225,7 +12225,7 @@
         <v>4.75</v>
       </c>
       <c r="G456" t="n">
-        <v>4.17499256134033</v>
+        <v>4.17499303817749</v>
       </c>
       <c r="H456" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>4.75</v>
       </c>
       <c r="G457" t="n">
-        <v>4.17499256134033</v>
+        <v>4.17499303817749</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12277,7 +12277,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G458" t="n">
-        <v>4.05194044113159</v>
+        <v>4.05193996429443</v>
       </c>
       <c r="H458" t="s">
         <v>8</v>
@@ -12381,7 +12381,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G462" t="n">
-        <v>4.08709859848022</v>
+        <v>4.08709812164307</v>
       </c>
       <c r="H462" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G463" t="n">
-        <v>4.14862394332886</v>
+        <v>4.1486234664917</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12459,7 +12459,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G465" t="n">
-        <v>4.2628870010376</v>
+        <v>4.26288652420044</v>
       </c>
       <c r="H465" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G466" t="n">
-        <v>4.28925561904907</v>
+        <v>4.28925609588623</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G478" t="n">
-        <v>4.64877796173096</v>
+        <v>4.6487774848938</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12823,7 +12823,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G479" t="n">
-        <v>4.56039762496948</v>
+        <v>4.56039810180664</v>
       </c>
       <c r="H479" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G481" t="n">
-        <v>4.56039762496948</v>
+        <v>4.56039810180664</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -13031,7 +13031,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G487" t="n">
-        <v>4.56039762496948</v>
+        <v>4.56039810180664</v>
       </c>
       <c r="H487" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G488" t="n">
-        <v>4.56039762496948</v>
+        <v>4.56039810180664</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13239,7 +13239,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G495" t="n">
-        <v>4.17152643203735</v>
+        <v>4.1715259552002</v>
       </c>
       <c r="H495" t="s">
         <v>8</v>
@@ -13941,7 +13941,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G522" t="n">
-        <v>4.59574937820435</v>
+        <v>4.5957498550415</v>
       </c>
       <c r="H522" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G523" t="n">
-        <v>4.59574937820435</v>
+        <v>4.5957498550415</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -13993,7 +13993,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G524" t="n">
-        <v>4.59574937820435</v>
+        <v>4.5957498550415</v>
       </c>
       <c r="H524" t="s">
         <v>8</v>
@@ -14019,7 +14019,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G525" t="n">
-        <v>4.59574937820435</v>
+        <v>4.5957498550415</v>
       </c>
       <c r="H525" t="s">
         <v>8</v>
@@ -14123,7 +14123,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G529" t="n">
-        <v>4.45434236526489</v>
+        <v>4.45434188842773</v>
       </c>
       <c r="H529" t="s">
         <v>8</v>
@@ -14487,7 +14487,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G543" t="n">
-        <v>4.38363838195801</v>
+        <v>4.38363790512085</v>
       </c>
       <c r="H543" t="s">
         <v>8</v>
@@ -14747,7 +14747,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G553" t="n">
-        <v>4.31293439865112</v>
+        <v>4.31293487548828</v>
       </c>
       <c r="H553" t="s">
         <v>8</v>
@@ -14825,7 +14825,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G556" t="n">
-        <v>4.1184983253479</v>
+        <v>4.11849880218506</v>
       </c>
       <c r="H556" t="s">
         <v>8</v>
@@ -15189,7 +15189,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G570" t="n">
-        <v>4.59574937820435</v>
+        <v>4.5957498550415</v>
       </c>
       <c r="H570" t="s">
         <v>8</v>
@@ -15371,7 +15371,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G577" t="n">
-        <v>4.91391658782959</v>
+        <v>4.91391706466675</v>
       </c>
       <c r="H577" t="s">
         <v>8</v>
@@ -15501,7 +15501,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G582" t="n">
-        <v>5.26743602752686</v>
+        <v>5.26743650436401</v>
       </c>
       <c r="H582" t="s">
         <v>8</v>
@@ -15761,7 +15761,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G592" t="n">
-        <v>5.51489973068237</v>
+        <v>5.51489925384521</v>
       </c>
       <c r="H592" t="s">
         <v>8</v>
@@ -15865,7 +15865,7 @@
         <v>6.71999979019165</v>
       </c>
       <c r="G596" t="n">
-        <v>5.93912267684937</v>
+        <v>5.93912315368652</v>
       </c>
       <c r="H596" t="s">
         <v>8</v>
@@ -15969,7 +15969,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G600" t="n">
-        <v>5.72701168060303</v>
+        <v>5.72701120376587</v>
       </c>
       <c r="H600" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G602" t="n">
-        <v>5.49722337722778</v>
+        <v>5.49722385406494</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>6.26000022888184</v>
       </c>
       <c r="G603" t="n">
-        <v>5.53257608413696</v>
+        <v>5.5325756072998</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16073,7 +16073,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G604" t="n">
-        <v>5.51489973068237</v>
+        <v>5.51489925384521</v>
       </c>
       <c r="H604" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G605" t="n">
-        <v>5.72701168060303</v>
+        <v>5.72701120376587</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G606" t="n">
-        <v>5.72701168060303</v>
+        <v>5.72701120376587</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G607" t="n">
-        <v>5.55025196075439</v>
+        <v>5.55025148391724</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>6.26000022888184</v>
       </c>
       <c r="G608" t="n">
-        <v>5.53257608413696</v>
+        <v>5.5325756072998</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G611" t="n">
-        <v>5.72701168060303</v>
+        <v>5.72701120376587</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16281,7 +16281,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G612" t="n">
-        <v>5.72701168060303</v>
+        <v>5.72701120376587</v>
       </c>
       <c r="H612" t="s">
         <v>8</v>
@@ -16385,7 +16385,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G616" t="n">
-        <v>5.88609457015991</v>
+        <v>5.88609504699707</v>
       </c>
       <c r="H616" t="s">
         <v>8</v>
@@ -16515,7 +16515,7 @@
         <v>6.26000022888184</v>
       </c>
       <c r="G621" t="n">
-        <v>5.53257608413696</v>
+        <v>5.5325756072998</v>
       </c>
       <c r="H621" t="s">
         <v>8</v>
@@ -16541,7 +16541,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G622" t="n">
-        <v>5.39116764068604</v>
+        <v>5.39116811752319</v>
       </c>
       <c r="H622" t="s">
         <v>8</v>
@@ -16697,7 +16697,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G628" t="n">
-        <v>5.88609457015991</v>
+        <v>5.88609504699707</v>
       </c>
       <c r="H628" t="s">
         <v>8</v>
@@ -16827,7 +16827,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G633" t="n">
-        <v>5.83306741714478</v>
+        <v>5.83306694030762</v>
       </c>
       <c r="H633" t="s">
         <v>8</v>
@@ -16853,7 +16853,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G634" t="n">
-        <v>5.83306741714478</v>
+        <v>5.83306694030762</v>
       </c>
       <c r="H634" t="s">
         <v>8</v>
@@ -16879,7 +16879,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G635" t="n">
-        <v>5.83306741714478</v>
+        <v>5.83306694030762</v>
       </c>
       <c r="H635" t="s">
         <v>8</v>
@@ -16931,7 +16931,7 @@
         <v>6.44000005722046</v>
       </c>
       <c r="G637" t="n">
-        <v>5.69165897369385</v>
+        <v>5.69165945053101</v>
       </c>
       <c r="H637" t="s">
         <v>8</v>
@@ -16983,7 +16983,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G639" t="n">
-        <v>5.5856032371521</v>
+        <v>5.58560371398926</v>
       </c>
       <c r="H639" t="s">
         <v>8</v>
@@ -17217,7 +17217,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G648" t="n">
-        <v>5.26743602752686</v>
+        <v>5.26743650436401</v>
       </c>
       <c r="H648" t="s">
         <v>8</v>
@@ -17243,7 +17243,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G649" t="n">
-        <v>5.39116764068604</v>
+        <v>5.39116811752319</v>
       </c>
       <c r="H649" t="s">
         <v>8</v>
@@ -17321,7 +17321,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G652" t="n">
-        <v>5.2144079208374</v>
+        <v>5.21440839767456</v>
       </c>
       <c r="H652" t="s">
         <v>8</v>
@@ -17347,7 +17347,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G653" t="n">
-        <v>5.1260290145874</v>
+        <v>5.12602853775024</v>
       </c>
       <c r="H653" t="s">
         <v>8</v>
@@ -17477,7 +17477,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G658" t="n">
-        <v>5.1260290145874</v>
+        <v>5.12602853775024</v>
       </c>
       <c r="H658" t="s">
         <v>8</v>
@@ -17685,7 +17685,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G666" t="n">
-        <v>4.71948146820068</v>
+        <v>4.71948194503784</v>
       </c>
       <c r="H666" t="s">
         <v>8</v>
@@ -17789,7 +17789,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G670" t="n">
-        <v>4.71948146820068</v>
+        <v>4.71948194503784</v>
       </c>
       <c r="H670" t="s">
         <v>8</v>
@@ -17841,7 +17841,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G672" t="n">
-        <v>4.64877796173096</v>
+        <v>4.6487774848938</v>
       </c>
       <c r="H672" t="s">
         <v>8</v>
@@ -18101,7 +18101,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G682" t="n">
-        <v>4.71948146820068</v>
+        <v>4.71948194503784</v>
       </c>
       <c r="H682" t="s">
         <v>8</v>
@@ -18179,7 +18179,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G685" t="n">
-        <v>4.59574937820435</v>
+        <v>4.5957498550415</v>
       </c>
       <c r="H685" t="s">
         <v>8</v>
@@ -18231,7 +18231,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G687" t="n">
-        <v>4.45434236526489</v>
+        <v>4.45434188842773</v>
       </c>
       <c r="H687" t="s">
         <v>8</v>
@@ -18361,7 +18361,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G692" t="n">
-        <v>4.87856531143188</v>
+        <v>4.87856483459473</v>
       </c>
       <c r="H692" t="s">
         <v>8</v>
@@ -18387,7 +18387,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G693" t="n">
-        <v>4.87856531143188</v>
+        <v>4.87856483459473</v>
       </c>
       <c r="H693" t="s">
         <v>8</v>
@@ -18413,7 +18413,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G694" t="n">
-        <v>4.93159341812134</v>
+        <v>4.93159294128418</v>
       </c>
       <c r="H694" t="s">
         <v>8</v>
@@ -18439,7 +18439,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G695" t="n">
-        <v>4.87856531143188</v>
+        <v>4.87856483459473</v>
       </c>
       <c r="H695" t="s">
         <v>8</v>
@@ -18725,7 +18725,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G706" t="n">
-        <v>5.1260290145874</v>
+        <v>5.12602853775024</v>
       </c>
       <c r="H706" t="s">
         <v>8</v>
@@ -18777,7 +18777,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G708" t="n">
-        <v>4.98462057113647</v>
+        <v>4.98462104797363</v>
       </c>
       <c r="H708" t="s">
         <v>8</v>
@@ -18803,7 +18803,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G709" t="n">
-        <v>5.1260290145874</v>
+        <v>5.12602853775024</v>
       </c>
       <c r="H709" t="s">
         <v>8</v>
@@ -18829,7 +18829,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G710" t="n">
-        <v>5.1260290145874</v>
+        <v>5.12602853775024</v>
       </c>
       <c r="H710" t="s">
         <v>8</v>
@@ -48290,6 +48290,32 @@
         <v>2.35999989509583</v>
       </c>
       <c r="H1843" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1844">
+      <c r="A1844" s="1" t="n">
+        <v>46310.2916666667</v>
+      </c>
+      <c r="B1844" t="n">
+        <v>2804</v>
+      </c>
+      <c r="C1844" t="n">
+        <v>2.35999989509583</v>
+      </c>
+      <c r="D1844" t="n">
+        <v>2.27999997138977</v>
+      </c>
+      <c r="E1844" t="n">
+        <v>2.29999995231628</v>
+      </c>
+      <c r="F1844" t="n">
+        <v>2.3199999332428</v>
+      </c>
+      <c r="G1844" t="n">
+        <v>2.3199999332428</v>
+      </c>
+      <c r="H1844" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/PTR.MI.xlsx
+++ b/data/PTR.MI.xlsx
@@ -421,7 +421,7 @@
         <v>3.75</v>
       </c>
       <c r="G2" t="n">
-        <v>3.25484609603882</v>
+        <v>3.2548463344574</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>3.56850004196167</v>
       </c>
       <c r="G7" t="n">
-        <v>3.0973117351532</v>
+        <v>3.09731197357178</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>3.43199992179871</v>
       </c>
       <c r="G10" t="n">
-        <v>2.978835105896</v>
+        <v>2.97883534431458</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G12" t="n">
-        <v>3.08125448226929</v>
+        <v>3.08125424385071</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G15" t="n">
-        <v>3.14201164245605</v>
+        <v>3.14201140403748</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G16" t="n">
-        <v>3.14201164245605</v>
+        <v>3.14201140403748</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G17" t="n">
-        <v>3.08993411064148</v>
+        <v>3.08993434906006</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G18" t="n">
-        <v>3.14201164245605</v>
+        <v>3.14201140403748</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G19" t="n">
-        <v>3.13333201408386</v>
+        <v>3.13333177566528</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G26" t="n">
-        <v>2.96841979026794</v>
+        <v>2.96842002868652</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G29" t="n">
-        <v>3.08125448226929</v>
+        <v>3.08125424385071</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G30" t="n">
-        <v>3.08993411064148</v>
+        <v>3.08993434906006</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G31" t="n">
-        <v>3.08993411064148</v>
+        <v>3.08993434906006</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>3.48200011253357</v>
       </c>
       <c r="G32" t="n">
-        <v>3.02223324775696</v>
+        <v>3.02223348617554</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>3.48200011253357</v>
       </c>
       <c r="G33" t="n">
-        <v>3.02223324775696</v>
+        <v>3.02223348617554</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G37" t="n">
-        <v>3.14201164245605</v>
+        <v>3.14201140403748</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G38" t="n">
-        <v>3.19408917427063</v>
+        <v>3.19408941268921</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G39" t="n">
-        <v>3.21144843101501</v>
+        <v>3.21144866943359</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G42" t="n">
-        <v>3.2982439994812</v>
+        <v>3.29824423789978</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>3.82500004768372</v>
       </c>
       <c r="G43" t="n">
-        <v>3.31994318962097</v>
+        <v>3.31994342803955</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>3.67499995231628</v>
       </c>
       <c r="G44" t="n">
-        <v>3.18974947929382</v>
+        <v>3.18974924087524</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>3.71499991416931</v>
       </c>
       <c r="G46" t="n">
-        <v>3.22446775436401</v>
+        <v>3.22446751594543</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>3.64499998092651</v>
       </c>
       <c r="G47" t="n">
-        <v>3.16371059417725</v>
+        <v>3.16371035575867</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G49" t="n">
-        <v>3.21144843101501</v>
+        <v>3.21144866943359</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>3.71499991416931</v>
       </c>
       <c r="G50" t="n">
-        <v>3.22446775436401</v>
+        <v>3.22446751594543</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>3.75</v>
       </c>
       <c r="G51" t="n">
-        <v>3.25484609603882</v>
+        <v>3.2548463344574</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G52" t="n">
-        <v>3.21144843101501</v>
+        <v>3.21144866943359</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G54" t="n">
-        <v>3.21144843101501</v>
+        <v>3.21144866943359</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>3.66499996185303</v>
       </c>
       <c r="G59" t="n">
-        <v>3.18107008934021</v>
+        <v>3.18106961250305</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>3.66499996185303</v>
       </c>
       <c r="G61" t="n">
-        <v>3.18107008934021</v>
+        <v>3.18106961250305</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G62" t="n">
-        <v>3.21144843101501</v>
+        <v>3.21144866943359</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G63" t="n">
-        <v>3.14201164245605</v>
+        <v>3.14201140403748</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>3.5550000667572</v>
       </c>
       <c r="G64" t="n">
-        <v>3.08559441566467</v>
+        <v>3.08559465408325</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>3.5550000667572</v>
       </c>
       <c r="G65" t="n">
-        <v>3.08559441566467</v>
+        <v>3.08559465408325</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>3.63499999046326</v>
       </c>
       <c r="G67" t="n">
-        <v>3.15503072738647</v>
+        <v>3.15503096580505</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G71" t="n">
-        <v>3.21144843101501</v>
+        <v>3.21144866943359</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G73" t="n">
-        <v>3.08125448226929</v>
+        <v>3.08125424385071</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G74" t="n">
-        <v>3.08125448226929</v>
+        <v>3.08125424385071</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G77" t="n">
-        <v>3.08125448226929</v>
+        <v>3.08125424385071</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G79" t="n">
-        <v>3.14201164245605</v>
+        <v>3.14201140403748</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>3.67499995231628</v>
       </c>
       <c r="G80" t="n">
-        <v>3.18974947929382</v>
+        <v>3.18974924087524</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G82" t="n">
-        <v>3.14201164245605</v>
+        <v>3.14201140403748</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G83" t="n">
-        <v>3.2982439994812</v>
+        <v>3.29824423789978</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G84" t="n">
-        <v>3.2982439994812</v>
+        <v>3.29824423789978</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G85" t="n">
-        <v>3.2982439994812</v>
+        <v>3.29824423789978</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G86" t="n">
-        <v>3.2982439994812</v>
+        <v>3.29824423789978</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G87" t="n">
-        <v>3.37636065483093</v>
+        <v>3.37636041641235</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G91" t="n">
-        <v>3.51523399353027</v>
+        <v>3.51523423194885</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>4</v>
       </c>
       <c r="G92" t="n">
-        <v>3.47183632850647</v>
+        <v>3.47183585166931</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G95" t="n">
-        <v>3.51523399353027</v>
+        <v>3.51523423194885</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>4.02500009536743</v>
       </c>
       <c r="G96" t="n">
-        <v>3.49353528022766</v>
+        <v>3.49353504180908</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>4.00500011444092</v>
       </c>
       <c r="G98" t="n">
-        <v>3.4761757850647</v>
+        <v>3.47617602348328</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>3.95499992370605</v>
       </c>
       <c r="G100" t="n">
-        <v>3.43277764320374</v>
+        <v>3.43277788162231</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G102" t="n">
-        <v>3.44579720497131</v>
+        <v>3.44579744338989</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>4</v>
       </c>
       <c r="G103" t="n">
-        <v>3.47183632850647</v>
+        <v>3.47183585166931</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>3.9449999332428</v>
       </c>
       <c r="G104" t="n">
-        <v>3.42409801483154</v>
+        <v>3.4240984916687</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>4</v>
       </c>
       <c r="G105" t="n">
-        <v>3.47183632850647</v>
+        <v>3.47183585166931</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>4.03499984741211</v>
       </c>
       <c r="G106" t="n">
-        <v>3.50221467018127</v>
+        <v>3.5022144317627</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G107" t="n">
-        <v>3.51523399353027</v>
+        <v>3.51523423194885</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G108" t="n">
-        <v>3.54995226860046</v>
+        <v>3.54995250701904</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G109" t="n">
-        <v>3.54995226860046</v>
+        <v>3.54995250701904</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G110" t="n">
-        <v>3.64542746543884</v>
+        <v>3.64542770385742</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G111" t="n">
-        <v>3.64542746543884</v>
+        <v>3.64542770385742</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>4.41499996185303</v>
       </c>
       <c r="G112" t="n">
-        <v>3.83203887939453</v>
+        <v>3.83203864097595</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>4.5</v>
       </c>
       <c r="G113" t="n">
-        <v>3.9058153629303</v>
+        <v>3.90581560134888</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>4.5</v>
       </c>
       <c r="G114" t="n">
-        <v>3.9058153629303</v>
+        <v>3.90581560134888</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G115" t="n">
-        <v>3.87109684944153</v>
+        <v>3.87109708786011</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G118" t="n">
-        <v>4.03600978851318</v>
+        <v>4.03600931167603</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G121" t="n">
-        <v>3.9231743812561</v>
+        <v>3.92317509651184</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G122" t="n">
-        <v>3.94053339958191</v>
+        <v>3.94053411483765</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G123" t="n">
-        <v>3.88845634460449</v>
+        <v>3.88845658302307</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G126" t="n">
-        <v>4.03600978851318</v>
+        <v>4.03600931167603</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G128" t="n">
-        <v>4.37451314926147</v>
+        <v>4.37451362609863</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G131" t="n">
-        <v>4.49602746963501</v>
+        <v>4.49602794647217</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G132" t="n">
-        <v>4.49602746963501</v>
+        <v>4.49602794647217</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>4.97499990463257</v>
       </c>
       <c r="G133" t="n">
-        <v>4.31809568405151</v>
+        <v>4.31809616088867</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G136" t="n">
-        <v>4.2009220123291</v>
+        <v>4.20092153549194</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G138" t="n">
-        <v>4.16620397567749</v>
+        <v>4.16620349884033</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>5</v>
       </c>
       <c r="G139" t="n">
-        <v>4.33979511260986</v>
+        <v>4.33979463577271</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G141" t="n">
-        <v>4.42659091949463</v>
+        <v>4.42659044265747</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>5</v>
       </c>
       <c r="G143" t="n">
-        <v>4.33979511260986</v>
+        <v>4.33979463577271</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G144" t="n">
-        <v>4.42659091949463</v>
+        <v>4.42659044265747</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G148" t="n">
-        <v>4.49602746963501</v>
+        <v>4.49602794647217</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G154" t="n">
-        <v>4.00129127502441</v>
+        <v>4.00129079818726</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G156" t="n">
-        <v>4.31375598907471</v>
+        <v>4.31375646591187</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G157" t="n">
-        <v>4.23564004898071</v>
+        <v>4.23563957214355</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G158" t="n">
-        <v>4.00129127502441</v>
+        <v>4.00129079818726</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G159" t="n">
-        <v>4.09676599502563</v>
+        <v>4.09676647186279</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>4.24499988555908</v>
       </c>
       <c r="G163" t="n">
-        <v>3.68448638916016</v>
+        <v>3.684485912323</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G165" t="n">
-        <v>3.26352572441101</v>
+        <v>3.26352596282959</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G168" t="n">
-        <v>2.95973992347717</v>
+        <v>2.95974016189575</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>3.72499990463257</v>
       </c>
       <c r="G175" t="n">
-        <v>3.23314714431763</v>
+        <v>3.23314738273621</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G176" t="n">
-        <v>3.08125448226929</v>
+        <v>3.08125424385071</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G179" t="n">
-        <v>3.21144843101501</v>
+        <v>3.21144866943359</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G180" t="n">
-        <v>3.31560325622559</v>
+        <v>3.31560349464417</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G183" t="n">
-        <v>3.19408917427063</v>
+        <v>3.19408941268921</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G184" t="n">
-        <v>3.21144843101501</v>
+        <v>3.21144866943359</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G185" t="n">
-        <v>3.19408917427063</v>
+        <v>3.19408941268921</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G187" t="n">
-        <v>3.21144843101501</v>
+        <v>3.21144866943359</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G188" t="n">
-        <v>3.2982439994812</v>
+        <v>3.29824423789978</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G189" t="n">
-        <v>3.2288076877594</v>
+        <v>3.22880744934082</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G190" t="n">
-        <v>3.18540954589844</v>
+        <v>3.18540930747986</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G192" t="n">
-        <v>3.33296275138855</v>
+        <v>3.33296251296997</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G193" t="n">
-        <v>3.2982439994812</v>
+        <v>3.29824423789978</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G194" t="n">
-        <v>3.2982439994812</v>
+        <v>3.29824423789978</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G195" t="n">
-        <v>3.34164237976074</v>
+        <v>3.34164214134216</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G196" t="n">
-        <v>3.35900139808655</v>
+        <v>3.35900115966797</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G197" t="n">
-        <v>3.35900139808655</v>
+        <v>3.35900115966797</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G199" t="n">
-        <v>3.54995226860046</v>
+        <v>3.54995250701904</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G200" t="n">
-        <v>3.48051571846008</v>
+        <v>3.48051595687866</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G201" t="n">
-        <v>3.33296275138855</v>
+        <v>3.33296251296997</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>3.75</v>
       </c>
       <c r="G202" t="n">
-        <v>3.25484609603882</v>
+        <v>3.2548463344574</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>3.75</v>
       </c>
       <c r="G203" t="n">
-        <v>3.25484609603882</v>
+        <v>3.2548463344574</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G204" t="n">
-        <v>3.19408917427063</v>
+        <v>3.19408941268921</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G205" t="n">
-        <v>3.2982439994812</v>
+        <v>3.29824423789978</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G206" t="n">
-        <v>3.31560325622559</v>
+        <v>3.31560349464417</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G207" t="n">
-        <v>3.37636065483093</v>
+        <v>3.37636041641235</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G209" t="n">
-        <v>3.24616694450378</v>
+        <v>3.24616646766663</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G210" t="n">
-        <v>3.2288076877594</v>
+        <v>3.22880744934082</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G211" t="n">
-        <v>3.2982439994812</v>
+        <v>3.29824423789978</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G213" t="n">
-        <v>3.2288076877594</v>
+        <v>3.22880744934082</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G215" t="n">
-        <v>3.26352572441101</v>
+        <v>3.26352596282959</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G217" t="n">
-        <v>3.2982439994812</v>
+        <v>3.29824423789978</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G219" t="n">
-        <v>3.2982439994812</v>
+        <v>3.29824423789978</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G220" t="n">
-        <v>3.26352572441101</v>
+        <v>3.26352596282959</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G222" t="n">
-        <v>3.2982439994812</v>
+        <v>3.29824423789978</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G223" t="n">
-        <v>3.34164237976074</v>
+        <v>3.34164214134216</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G224" t="n">
-        <v>3.38504004478455</v>
+        <v>3.38504028320312</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G225" t="n">
-        <v>3.35900139808655</v>
+        <v>3.35900115966797</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G226" t="n">
-        <v>3.37636065483093</v>
+        <v>3.37636041641235</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G227" t="n">
-        <v>3.2982439994812</v>
+        <v>3.29824423789978</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G230" t="n">
-        <v>3.37636065483093</v>
+        <v>3.37636041641235</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G231" t="n">
-        <v>3.31560325622559</v>
+        <v>3.31560349464417</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G232" t="n">
-        <v>3.35032176971436</v>
+        <v>3.35032153129578</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G233" t="n">
-        <v>3.37636065483093</v>
+        <v>3.37636041641235</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G234" t="n">
-        <v>3.37636065483093</v>
+        <v>3.37636041641235</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G235" t="n">
-        <v>3.32428288459778</v>
+        <v>3.32428312301636</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G236" t="n">
-        <v>3.32428288459778</v>
+        <v>3.32428312301636</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G240" t="n">
-        <v>3.2982439994812</v>
+        <v>3.29824423789978</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G241" t="n">
-        <v>3.34164237976074</v>
+        <v>3.34164214134216</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G246" t="n">
-        <v>3.2982439994812</v>
+        <v>3.29824423789978</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G247" t="n">
-        <v>3.24616694450378</v>
+        <v>3.24616646766663</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G248" t="n">
-        <v>3.24616694450378</v>
+        <v>3.24616646766663</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G251" t="n">
-        <v>3.18540954589844</v>
+        <v>3.18540930747986</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G252" t="n">
-        <v>3.21144843101501</v>
+        <v>3.21144866943359</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G253" t="n">
-        <v>3.21144843101501</v>
+        <v>3.21144866943359</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G255" t="n">
-        <v>3.18540954589844</v>
+        <v>3.18540930747986</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G256" t="n">
-        <v>3.2288076877594</v>
+        <v>3.22880744934082</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>3.75</v>
       </c>
       <c r="G257" t="n">
-        <v>3.25484609603882</v>
+        <v>3.2548463344574</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G259" t="n">
-        <v>3.2288076877594</v>
+        <v>3.22880744934082</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G260" t="n">
-        <v>3.08993411064148</v>
+        <v>3.08993434906006</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G263" t="n">
-        <v>3.08993411064148</v>
+        <v>3.08993434906006</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G264" t="n">
-        <v>3.13333201408386</v>
+        <v>3.13333177566528</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G265" t="n">
-        <v>3.07257509231567</v>
+        <v>3.07257461547852</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7363,7 +7363,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G269" t="n">
-        <v>3.24616694450378</v>
+        <v>3.24616646766663</v>
       </c>
       <c r="H269" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G270" t="n">
-        <v>3.19408917427063</v>
+        <v>3.19408941268921</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G271" t="n">
-        <v>3.13333201408386</v>
+        <v>3.13333177566528</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G273" t="n">
-        <v>3.0204975605011</v>
+        <v>3.02049732208252</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G275" t="n">
-        <v>2.96841979026794</v>
+        <v>2.96842002868652</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G277" t="n">
-        <v>3.0204975605011</v>
+        <v>3.02049732208252</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G278" t="n">
-        <v>3.07257509231567</v>
+        <v>3.07257461547852</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G279" t="n">
-        <v>2.99445843696594</v>
+        <v>2.99445867538452</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G284" t="n">
-        <v>2.94238090515137</v>
+        <v>2.94238114356995</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G285" t="n">
-        <v>2.94238090515137</v>
+        <v>2.94238114356995</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G288" t="n">
-        <v>2.99445843696594</v>
+        <v>2.99445867538452</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G289" t="n">
-        <v>3.08125448226929</v>
+        <v>3.08125424385071</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G294" t="n">
-        <v>3.08125448226929</v>
+        <v>3.08125424385071</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G296" t="n">
-        <v>2.95106077194214</v>
+        <v>2.95106053352356</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G297" t="n">
-        <v>2.95106077194214</v>
+        <v>2.95106053352356</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G298" t="n">
-        <v>2.99445843696594</v>
+        <v>2.99445867538452</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G302" t="n">
-        <v>2.95973992347717</v>
+        <v>2.95974016189575</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G303" t="n">
-        <v>2.8816237449646</v>
+        <v>2.88162398338318</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G304" t="n">
-        <v>2.87294435501099</v>
+        <v>2.87294459342957</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G306" t="n">
-        <v>3.08125448226929</v>
+        <v>3.08125424385071</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G313" t="n">
-        <v>3.21144843101501</v>
+        <v>3.21144866943359</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G314" t="n">
-        <v>3.19408917427063</v>
+        <v>3.19408941268921</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G315" t="n">
-        <v>3.21144843101501</v>
+        <v>3.21144866943359</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>3.75</v>
       </c>
       <c r="G316" t="n">
-        <v>3.25484609603882</v>
+        <v>3.2548463344574</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G317" t="n">
-        <v>3.21144843101501</v>
+        <v>3.21144866943359</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G321" t="n">
-        <v>3.21144843101501</v>
+        <v>3.21144866943359</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G323" t="n">
-        <v>3.21144843101501</v>
+        <v>3.21144866943359</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G324" t="n">
-        <v>3.21144843101501</v>
+        <v>3.21144866943359</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G325" t="n">
-        <v>3.21144843101501</v>
+        <v>3.21144866943359</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G326" t="n">
-        <v>3.19408917427063</v>
+        <v>3.19408941268921</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G327" t="n">
-        <v>3.14201164245605</v>
+        <v>3.14201140403748</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G328" t="n">
-        <v>3.21144843101501</v>
+        <v>3.21144866943359</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G330" t="n">
-        <v>3.19408917427063</v>
+        <v>3.19408941268921</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G342" t="n">
-        <v>3.21144843101501</v>
+        <v>3.21144866943359</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G346" t="n">
-        <v>3.21144843101501</v>
+        <v>3.21144866943359</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G347" t="n">
-        <v>3.31560325622559</v>
+        <v>3.31560349464417</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G349" t="n">
-        <v>3.31560325622559</v>
+        <v>3.31560349464417</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G351" t="n">
-        <v>3.31560325622559</v>
+        <v>3.31560349464417</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G352" t="n">
-        <v>3.34164237976074</v>
+        <v>3.34164214134216</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G354" t="n">
-        <v>3.34164237976074</v>
+        <v>3.34164214134216</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G358" t="n">
-        <v>3.37636065483093</v>
+        <v>3.37636041641235</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>4</v>
       </c>
       <c r="G359" t="n">
-        <v>3.47183632850647</v>
+        <v>3.47183585166931</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>4</v>
       </c>
       <c r="G360" t="n">
-        <v>3.47183632850647</v>
+        <v>3.47183585166931</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G366" t="n">
-        <v>3.47183609008789</v>
+        <v>3.47183585166931</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G372" t="n">
-        <v>3.57730984687805</v>
+        <v>3.57730960845947</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G373" t="n">
-        <v>3.77946734428406</v>
+        <v>3.77946710586548</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G374" t="n">
-        <v>3.85857200622559</v>
+        <v>3.85857176780701</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G376" t="n">
-        <v>3.82341408729553</v>
+        <v>3.82341432571411</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G380" t="n">
-        <v>3.99041342735291</v>
+        <v>3.99041366577148</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G383" t="n">
-        <v>3.92009830474854</v>
+        <v>3.92009806632996</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G384" t="n">
-        <v>3.77946734428406</v>
+        <v>3.77946710586548</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G385" t="n">
-        <v>3.77946734428406</v>
+        <v>3.77946710586548</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G386" t="n">
-        <v>3.647625207901</v>
+        <v>3.64762496948242</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G387" t="n">
-        <v>3.42788863182068</v>
+        <v>3.4278883934021</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10483,7 +10483,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G389" t="n">
-        <v>3.58609890937805</v>
+        <v>3.58609914779663</v>
       </c>
       <c r="H389" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G395" t="n">
-        <v>3.744309425354</v>
+        <v>3.74430918693542</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G396" t="n">
-        <v>3.77946734428406</v>
+        <v>3.77946710586548</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G397" t="n">
-        <v>3.82341408729553</v>
+        <v>3.82341432571411</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G398" t="n">
-        <v>3.77946734428406</v>
+        <v>3.77946710586548</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10795,7 +10795,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G401" t="n">
-        <v>3.58609890937805</v>
+        <v>3.58609914779663</v>
       </c>
       <c r="H401" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G402" t="n">
-        <v>3.60367774963379</v>
+        <v>3.60367751121521</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G403" t="n">
-        <v>3.68278312683105</v>
+        <v>3.68278288841248</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>4.25</v>
       </c>
       <c r="G407" t="n">
-        <v>3.73551964759827</v>
+        <v>3.73552012443542</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G408" t="n">
-        <v>3.78825664520264</v>
+        <v>3.78825688362122</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G410" t="n">
-        <v>3.9992036819458</v>
+        <v>3.99920392036438</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G411" t="n">
-        <v>3.9992036819458</v>
+        <v>3.99920392036438</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G412" t="n">
-        <v>3.97283506393433</v>
+        <v>3.97283530235291</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11107,7 +11107,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G413" t="n">
-        <v>4.06072998046875</v>
+        <v>4.06072950363159</v>
       </c>
       <c r="H413" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G416" t="n">
-        <v>3.9992036819458</v>
+        <v>3.99920392036438</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>4.59000015258789</v>
       </c>
       <c r="G417" t="n">
-        <v>4.03436136245728</v>
+        <v>4.03436088562012</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11289,7 +11289,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G420" t="n">
-        <v>4.30683422088623</v>
+        <v>4.30683469772339</v>
       </c>
       <c r="H420" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>5</v>
       </c>
       <c r="G421" t="n">
-        <v>4.39472913742065</v>
+        <v>4.3947286605835</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>5</v>
       </c>
       <c r="G422" t="n">
-        <v>4.39472913742065</v>
+        <v>4.3947286605835</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G424" t="n">
-        <v>4.30683422088623</v>
+        <v>4.30683469772339</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G433" t="n">
-        <v>4.32441377639771</v>
+        <v>4.32441329956055</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G439" t="n">
-        <v>4.3859395980835</v>
+        <v>4.38593912124634</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G440" t="n">
-        <v>4.3859395980835</v>
+        <v>4.38593912124634</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G441" t="n">
-        <v>4.30683422088623</v>
+        <v>4.30683469772339</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11861,7 +11861,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G442" t="n">
-        <v>4.30683422088623</v>
+        <v>4.30683469772339</v>
       </c>
       <c r="H442" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G445" t="n">
-        <v>4.26288652420044</v>
+        <v>4.2628870010376</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G447" t="n">
-        <v>4.3859395980835</v>
+        <v>4.38593912124634</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>5</v>
       </c>
       <c r="G449" t="n">
-        <v>4.39472913742065</v>
+        <v>4.3947286605835</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G451" t="n">
-        <v>4.30683422088623</v>
+        <v>4.30683469772339</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12277,7 +12277,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G458" t="n">
-        <v>4.05193996429443</v>
+        <v>4.05194044113159</v>
       </c>
       <c r="H458" t="s">
         <v>8</v>
@@ -12459,7 +12459,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G465" t="n">
-        <v>4.26288652420044</v>
+        <v>4.2628870010376</v>
       </c>
       <c r="H465" t="s">
         <v>8</v>
@@ -12537,7 +12537,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G468" t="n">
-        <v>4.50020265579224</v>
+        <v>4.50020217895508</v>
       </c>
       <c r="H468" t="s">
         <v>8</v>
@@ -48316,6 +48316,32 @@
         <v>2.3199999332428</v>
       </c>
       <c r="H1844" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1845">
+      <c r="A1845" s="1" t="n">
+        <v>46311.2916666667</v>
+      </c>
+      <c r="B1845" t="n">
+        <v>1466</v>
+      </c>
+      <c r="C1845" t="n">
+        <v>2.33999991416931</v>
+      </c>
+      <c r="D1845" t="n">
+        <v>2.33999991416931</v>
+      </c>
+      <c r="E1845" t="n">
+        <v>2.33999991416931</v>
+      </c>
+      <c r="F1845" t="n">
+        <v>2.33999991416931</v>
+      </c>
+      <c r="G1845" t="n">
+        <v>2.33999991416931</v>
+      </c>
+      <c r="H1845" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/PTR.MI.xlsx
+++ b/data/PTR.MI.xlsx
@@ -485,7 +485,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G4" t="n">
-        <v>3.22012805938721</v>
+        <v>3.22012829780579</v>
       </c>
       <c r="H4" t="n">
         <v>98299</v>
@@ -543,7 +543,7 @@
         <v>3.69250011444092</v>
       </c>
       <c r="G6" t="n">
-        <v>3.20493865013123</v>
+        <v>3.2049388885498</v>
       </c>
       <c r="H6" t="n">
         <v>56036</v>
@@ -572,7 +572,7 @@
         <v>3.56850004196167</v>
       </c>
       <c r="G7" t="n">
-        <v>3.09731197357178</v>
+        <v>3.0973117351532</v>
       </c>
       <c r="H7" t="n">
         <v>71079</v>
@@ -601,7 +601,7 @@
         <v>3.5864999294281</v>
       </c>
       <c r="G8" t="n">
-        <v>3.11293482780457</v>
+        <v>3.11293506622314</v>
       </c>
       <c r="H8" t="n">
         <v>37148</v>
@@ -630,7 +630,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G9" t="n">
-        <v>3.05521559715271</v>
+        <v>3.05521583557129</v>
       </c>
       <c r="H9" t="n">
         <v>21800</v>
@@ -746,7 +746,7 @@
         <v>3.59400010108948</v>
       </c>
       <c r="G13" t="n">
-        <v>3.11944460868835</v>
+        <v>3.11944484710693</v>
       </c>
       <c r="H13" t="n">
         <v>13465</v>
@@ -862,7 +862,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G17" t="n">
-        <v>3.08993411064148</v>
+        <v>3.0899338722229</v>
       </c>
       <c r="H17" t="n">
         <v>939</v>
@@ -920,7 +920,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G19" t="n">
-        <v>3.13333177566528</v>
+        <v>3.13333225250244</v>
       </c>
       <c r="H19" t="n">
         <v>26321</v>
@@ -978,7 +978,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G21" t="n">
-        <v>3.11597275733948</v>
+        <v>3.11597299575806</v>
       </c>
       <c r="H21" t="n">
         <v>210</v>
@@ -1065,7 +1065,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G24" t="n">
-        <v>3.05521559715271</v>
+        <v>3.05521583557129</v>
       </c>
       <c r="H24" t="n">
         <v>72</v>
@@ -1094,7 +1094,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G25" t="n">
-        <v>3.05521559715271</v>
+        <v>3.05521583557129</v>
       </c>
       <c r="H25" t="n">
         <v>520</v>
@@ -1123,7 +1123,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G26" t="n">
-        <v>2.96842002868652</v>
+        <v>2.96841979026794</v>
       </c>
       <c r="H26" t="n">
         <v>3800</v>
@@ -1152,7 +1152,7 @@
         <v>3.35050010681152</v>
       </c>
       <c r="G27" t="n">
-        <v>2.90809679031372</v>
+        <v>2.90809655189514</v>
       </c>
       <c r="H27" t="n">
         <v>9955</v>
@@ -1181,7 +1181,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G28" t="n">
-        <v>2.98577904701233</v>
+        <v>2.98577928543091</v>
       </c>
       <c r="H28" t="n">
         <v>6355</v>
@@ -1239,7 +1239,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G30" t="n">
-        <v>3.08993411064148</v>
+        <v>3.0899338722229</v>
       </c>
       <c r="H30" t="n">
         <v>11148</v>
@@ -1268,7 +1268,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G31" t="n">
-        <v>3.08993411064148</v>
+        <v>3.0899338722229</v>
       </c>
       <c r="H31" t="n">
         <v>1210</v>
@@ -1297,7 +1297,7 @@
         <v>3.48200011253357</v>
       </c>
       <c r="G32" t="n">
-        <v>3.02223324775696</v>
+        <v>3.02223348617554</v>
       </c>
       <c r="H32" t="n">
         <v>904</v>
@@ -1326,7 +1326,7 @@
         <v>3.48200011253357</v>
       </c>
       <c r="G33" t="n">
-        <v>3.02223324775696</v>
+        <v>3.02223348617554</v>
       </c>
       <c r="H33" t="n">
         <v>432</v>
@@ -1384,7 +1384,7 @@
         <v>3.5</v>
       </c>
       <c r="G35" t="n">
-        <v>3.03785634040833</v>
+        <v>3.0378565788269</v>
       </c>
       <c r="H35" t="n">
         <v>1400</v>
@@ -1558,7 +1558,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G41" t="n">
-        <v>3.42843794822693</v>
+        <v>3.42843818664551</v>
       </c>
       <c r="H41" t="n">
         <v>44559</v>
@@ -1616,7 +1616,7 @@
         <v>3.82500004768372</v>
       </c>
       <c r="G43" t="n">
-        <v>3.31994318962097</v>
+        <v>3.31994295120239</v>
       </c>
       <c r="H43" t="n">
         <v>5962</v>
@@ -1645,7 +1645,7 @@
         <v>3.67499995231628</v>
       </c>
       <c r="G44" t="n">
-        <v>3.18974947929382</v>
+        <v>3.18974924087524</v>
       </c>
       <c r="H44" t="n">
         <v>9040</v>
@@ -1703,7 +1703,7 @@
         <v>3.71499991416931</v>
       </c>
       <c r="G46" t="n">
-        <v>3.22446775436401</v>
+        <v>3.22446751594543</v>
       </c>
       <c r="H46" t="n">
         <v>3406</v>
@@ -1819,7 +1819,7 @@
         <v>3.71499991416931</v>
       </c>
       <c r="G50" t="n">
-        <v>3.22446775436401</v>
+        <v>3.22446751594543</v>
       </c>
       <c r="H50" t="n">
         <v>7667</v>
@@ -1964,7 +1964,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G55" t="n">
-        <v>3.16805076599121</v>
+        <v>3.16805052757263</v>
       </c>
       <c r="H55" t="n">
         <v>7217</v>
@@ -2109,7 +2109,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G60" t="n">
-        <v>3.05521559715271</v>
+        <v>3.05521583557129</v>
       </c>
       <c r="H60" t="n">
         <v>1420</v>
@@ -2225,7 +2225,7 @@
         <v>3.5550000667572</v>
       </c>
       <c r="G64" t="n">
-        <v>3.08559441566467</v>
+        <v>3.08559393882751</v>
       </c>
       <c r="H64" t="n">
         <v>550</v>
@@ -2254,7 +2254,7 @@
         <v>3.5550000667572</v>
       </c>
       <c r="G65" t="n">
-        <v>3.08559441566467</v>
+        <v>3.08559393882751</v>
       </c>
       <c r="H65" t="n">
         <v>2547</v>
@@ -2312,7 +2312,7 @@
         <v>3.63499999046326</v>
       </c>
       <c r="G67" t="n">
-        <v>3.15503096580505</v>
+        <v>3.15503120422363</v>
       </c>
       <c r="H67" t="n">
         <v>1440</v>
@@ -2399,7 +2399,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G70" t="n">
-        <v>3.16805076599121</v>
+        <v>3.16805052757263</v>
       </c>
       <c r="H70" t="n">
         <v>2550</v>
@@ -2544,7 +2544,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G75" t="n">
-        <v>3.11597275733948</v>
+        <v>3.11597299575806</v>
       </c>
       <c r="H75" t="n">
         <v>5620</v>
@@ -2573,7 +2573,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G76" t="n">
-        <v>3.11597275733948</v>
+        <v>3.11597299575806</v>
       </c>
       <c r="H76" t="n">
         <v>609</v>
@@ -2689,7 +2689,7 @@
         <v>3.67499995231628</v>
       </c>
       <c r="G80" t="n">
-        <v>3.18974947929382</v>
+        <v>3.18974924087524</v>
       </c>
       <c r="H80" t="n">
         <v>6929</v>
@@ -2718,7 +2718,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G81" t="n">
-        <v>3.15937066078186</v>
+        <v>3.15937089920044</v>
       </c>
       <c r="H81" t="n">
         <v>4191</v>
@@ -2921,7 +2921,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G88" t="n">
-        <v>3.42843794822693</v>
+        <v>3.42843818664551</v>
       </c>
       <c r="H88" t="n">
         <v>79090</v>
@@ -2950,7 +2950,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G89" t="n">
-        <v>3.42843794822693</v>
+        <v>3.42843818664551</v>
       </c>
       <c r="H89" t="n">
         <v>55032</v>
@@ -2979,7 +2979,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G90" t="n">
-        <v>3.41975879669189</v>
+        <v>3.41975855827332</v>
       </c>
       <c r="H90" t="n">
         <v>12161</v>
@@ -3008,7 +3008,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G91" t="n">
-        <v>3.51523423194885</v>
+        <v>3.51523399353027</v>
       </c>
       <c r="H91" t="n">
         <v>17593</v>
@@ -3066,7 +3066,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G93" t="n">
-        <v>3.46315622329712</v>
+        <v>3.46315670013428</v>
       </c>
       <c r="H93" t="n">
         <v>250</v>
@@ -3095,7 +3095,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G94" t="n">
-        <v>3.41975879669189</v>
+        <v>3.41975855827332</v>
       </c>
       <c r="H94" t="n">
         <v>3029</v>
@@ -3124,7 +3124,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G95" t="n">
-        <v>3.51523423194885</v>
+        <v>3.51523399353027</v>
       </c>
       <c r="H95" t="n">
         <v>1936</v>
@@ -3153,7 +3153,7 @@
         <v>4.02500009536743</v>
       </c>
       <c r="G96" t="n">
-        <v>3.49353528022766</v>
+        <v>3.4935348033905</v>
       </c>
       <c r="H96" t="n">
         <v>1493</v>
@@ -3182,7 +3182,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G97" t="n">
-        <v>3.42843794822693</v>
+        <v>3.42843818664551</v>
       </c>
       <c r="H97" t="n">
         <v>52799</v>
@@ -3211,7 +3211,7 @@
         <v>4.00500011444092</v>
       </c>
       <c r="G98" t="n">
-        <v>3.47617602348328</v>
+        <v>3.4761757850647</v>
       </c>
       <c r="H98" t="n">
         <v>4670</v>
@@ -3269,7 +3269,7 @@
         <v>3.95499992370605</v>
       </c>
       <c r="G100" t="n">
-        <v>3.43277764320374</v>
+        <v>3.43277788162231</v>
       </c>
       <c r="H100" t="n">
         <v>9435</v>
@@ -3298,7 +3298,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G101" t="n">
-        <v>3.54127287864685</v>
+        <v>3.54127264022827</v>
       </c>
       <c r="H101" t="n">
         <v>4200</v>
@@ -3385,7 +3385,7 @@
         <v>3.9449999332428</v>
       </c>
       <c r="G104" t="n">
-        <v>3.42409825325012</v>
+        <v>3.42409801483154</v>
       </c>
       <c r="H104" t="n">
         <v>26075</v>
@@ -3472,7 +3472,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G107" t="n">
-        <v>3.51523423194885</v>
+        <v>3.51523399353027</v>
       </c>
       <c r="H107" t="n">
         <v>17133</v>
@@ -3501,7 +3501,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G108" t="n">
-        <v>3.54995226860046</v>
+        <v>3.54995250701904</v>
       </c>
       <c r="H108" t="n">
         <v>3452</v>
@@ -3530,7 +3530,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G109" t="n">
-        <v>3.54995226860046</v>
+        <v>3.54995250701904</v>
       </c>
       <c r="H109" t="n">
         <v>9864</v>
@@ -3559,7 +3559,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G110" t="n">
-        <v>3.645427942276</v>
+        <v>3.64542746543884</v>
       </c>
       <c r="H110" t="n">
         <v>37685</v>
@@ -3588,7 +3588,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G111" t="n">
-        <v>3.645427942276</v>
+        <v>3.64542746543884</v>
       </c>
       <c r="H111" t="n">
         <v>19204</v>
@@ -3646,7 +3646,7 @@
         <v>4.5</v>
       </c>
       <c r="G113" t="n">
-        <v>3.90581560134888</v>
+        <v>3.9058153629303</v>
       </c>
       <c r="H113" t="n">
         <v>10114</v>
@@ -3675,7 +3675,7 @@
         <v>4.5</v>
       </c>
       <c r="G114" t="n">
-        <v>3.90581560134888</v>
+        <v>3.9058153629303</v>
       </c>
       <c r="H114" t="n">
         <v>36925</v>
@@ -3704,7 +3704,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G115" t="n">
-        <v>3.87109684944153</v>
+        <v>3.87109708786011</v>
       </c>
       <c r="H115" t="n">
         <v>4580</v>
@@ -3733,7 +3733,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G116" t="n">
-        <v>3.86241674423218</v>
+        <v>3.86241769790649</v>
       </c>
       <c r="H116" t="n">
         <v>17964</v>
@@ -3762,7 +3762,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G117" t="n">
-        <v>4.00997066497803</v>
+        <v>4.00997114181519</v>
       </c>
       <c r="H117" t="n">
         <v>10859</v>
@@ -3791,7 +3791,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G118" t="n">
-        <v>4.03600931167603</v>
+        <v>4.03600978851318</v>
       </c>
       <c r="H118" t="n">
         <v>50</v>
@@ -3820,7 +3820,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G119" t="n">
-        <v>3.96657276153564</v>
+        <v>3.96657299995422</v>
       </c>
       <c r="H119" t="n">
         <v>7065</v>
@@ -3849,7 +3849,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G120" t="n">
-        <v>3.86241674423218</v>
+        <v>3.86241769790649</v>
       </c>
       <c r="H120" t="n">
         <v>34190</v>
@@ -3965,7 +3965,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G124" t="n">
-        <v>3.94921374320984</v>
+        <v>3.94921350479126</v>
       </c>
       <c r="H124" t="n">
         <v>5841</v>
@@ -3994,7 +3994,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G125" t="n">
-        <v>3.94921374320984</v>
+        <v>3.94921350479126</v>
       </c>
       <c r="H125" t="n">
         <v>21549</v>
@@ -4023,7 +4023,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G126" t="n">
-        <v>4.03600931167603</v>
+        <v>4.03600978851318</v>
       </c>
       <c r="H126" t="n">
         <v>9991</v>
@@ -4081,7 +4081,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G128" t="n">
-        <v>4.37451267242432</v>
+        <v>4.37451314926147</v>
       </c>
       <c r="H128" t="n">
         <v>36739</v>
@@ -4110,7 +4110,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G129" t="n">
-        <v>4.3831934928894</v>
+        <v>4.38319301605225</v>
       </c>
       <c r="H129" t="n">
         <v>19996</v>
@@ -4139,7 +4139,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G130" t="n">
-        <v>4.39187288284302</v>
+        <v>4.39187240600586</v>
       </c>
       <c r="H130" t="n">
         <v>8599</v>
@@ -4226,7 +4226,7 @@
         <v>4.97499990463257</v>
       </c>
       <c r="G133" t="n">
-        <v>4.31809568405151</v>
+        <v>4.31809616088867</v>
       </c>
       <c r="H133" t="n">
         <v>8257</v>
@@ -4255,7 +4255,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G134" t="n">
-        <v>4.24431991577148</v>
+        <v>4.24431943893433</v>
       </c>
       <c r="H134" t="n">
         <v>9475</v>
@@ -4284,7 +4284,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G135" t="n">
-        <v>4.24431991577148</v>
+        <v>4.24431943893433</v>
       </c>
       <c r="H135" t="n">
         <v>1852</v>
@@ -4313,7 +4313,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G136" t="n">
-        <v>4.2009220123291</v>
+        <v>4.20092153549194</v>
       </c>
       <c r="H136" t="n">
         <v>13708</v>
@@ -4371,7 +4371,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G138" t="n">
-        <v>4.16620349884033</v>
+        <v>4.16620302200317</v>
       </c>
       <c r="H138" t="n">
         <v>23142</v>
@@ -4400,7 +4400,7 @@
         <v>5</v>
       </c>
       <c r="G139" t="n">
-        <v>4.33979511260986</v>
+        <v>4.33979463577271</v>
       </c>
       <c r="H139" t="n">
         <v>20858</v>
@@ -4429,7 +4429,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G140" t="n">
-        <v>4.51338720321655</v>
+        <v>4.51338672637939</v>
       </c>
       <c r="H140" t="n">
         <v>12739</v>
@@ -4516,7 +4516,7 @@
         <v>5</v>
       </c>
       <c r="G143" t="n">
-        <v>4.33979511260986</v>
+        <v>4.33979463577271</v>
       </c>
       <c r="H143" t="n">
         <v>9892</v>
@@ -4574,7 +4574,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G145" t="n">
-        <v>4.51338720321655</v>
+        <v>4.51338672637939</v>
       </c>
       <c r="H145" t="n">
         <v>10888</v>
@@ -4632,7 +4632,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G147" t="n">
-        <v>4.70433807373047</v>
+        <v>4.70433759689331</v>
       </c>
       <c r="H147" t="n">
         <v>15539</v>
@@ -4719,7 +4719,7 @@
         <v>5.13000011444092</v>
       </c>
       <c r="G150" t="n">
-        <v>4.45263004302979</v>
+        <v>4.45263051986694</v>
       </c>
       <c r="H150" t="n">
         <v>6278</v>
@@ -4777,7 +4777,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G152" t="n">
-        <v>4.51338720321655</v>
+        <v>4.51338672637939</v>
       </c>
       <c r="H152" t="n">
         <v>12525</v>
@@ -4806,7 +4806,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G153" t="n">
-        <v>4.44394969940186</v>
+        <v>4.44395017623901</v>
       </c>
       <c r="H153" t="n">
         <v>2010</v>
@@ -4835,7 +4835,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G154" t="n">
-        <v>4.00129127502441</v>
+        <v>4.00129175186157</v>
       </c>
       <c r="H154" t="n">
         <v>9345</v>
@@ -4864,7 +4864,7 @@
         <v>4.75500011444092</v>
       </c>
       <c r="G155" t="n">
-        <v>4.12714529037476</v>
+        <v>4.1271448135376</v>
       </c>
       <c r="H155" t="n">
         <v>9182</v>
@@ -4922,7 +4922,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G157" t="n">
-        <v>4.23564052581787</v>
+        <v>4.23564004898071</v>
       </c>
       <c r="H157" t="n">
         <v>8393</v>
@@ -4951,7 +4951,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G158" t="n">
-        <v>4.00129127502441</v>
+        <v>4.00129175186157</v>
       </c>
       <c r="H158" t="n">
         <v>25178</v>
@@ -5009,7 +5009,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G160" t="n">
-        <v>4.06204795837402</v>
+        <v>4.06204748153687</v>
       </c>
       <c r="H160" t="n">
         <v>4897</v>
@@ -5038,7 +5038,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G161" t="n">
-        <v>4.04468870162964</v>
+        <v>4.0446891784668</v>
       </c>
       <c r="H161" t="n">
         <v>300</v>
@@ -5067,7 +5067,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G162" t="n">
-        <v>3.99261140823364</v>
+        <v>3.99261116981506</v>
       </c>
       <c r="H162" t="n">
         <v>1599</v>
@@ -5154,7 +5154,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G165" t="n">
-        <v>3.26352572441101</v>
+        <v>3.26352620124817</v>
       </c>
       <c r="H165" t="n">
         <v>12420</v>
@@ -5270,7 +5270,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G169" t="n">
-        <v>2.98577904701233</v>
+        <v>2.98577928543091</v>
       </c>
       <c r="H169" t="n">
         <v>3440</v>
@@ -5357,7 +5357,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G172" t="n">
-        <v>2.9076623916626</v>
+        <v>2.90766263008118</v>
       </c>
       <c r="H172" t="n">
         <v>3900</v>
@@ -5444,7 +5444,7 @@
         <v>3.72499990463257</v>
       </c>
       <c r="G175" t="n">
-        <v>3.23314714431763</v>
+        <v>3.23314690589905</v>
       </c>
       <c r="H175" t="n">
         <v>35922</v>
@@ -5618,7 +5618,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G181" t="n">
-        <v>3.30692386627197</v>
+        <v>3.30692362785339</v>
       </c>
       <c r="H181" t="n">
         <v>2000</v>
@@ -5763,7 +5763,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G186" t="n">
-        <v>3.22012805938721</v>
+        <v>3.22012829780579</v>
       </c>
       <c r="H186" t="n">
         <v>4810</v>
@@ -5908,7 +5908,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G191" t="n">
-        <v>3.28088521957397</v>
+        <v>3.2808849811554</v>
       </c>
       <c r="H191" t="n">
         <v>15966</v>
@@ -6024,7 +6024,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G195" t="n">
-        <v>3.34164237976074</v>
+        <v>3.34164214134216</v>
       </c>
       <c r="H195" t="n">
         <v>6546</v>
@@ -6053,7 +6053,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G196" t="n">
-        <v>3.35900115966797</v>
+        <v>3.35900139808655</v>
       </c>
       <c r="H196" t="n">
         <v>2603</v>
@@ -6082,7 +6082,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G197" t="n">
-        <v>3.35900115966797</v>
+        <v>3.35900139808655</v>
       </c>
       <c r="H197" t="n">
         <v>1540</v>
@@ -6140,7 +6140,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G199" t="n">
-        <v>3.54995226860046</v>
+        <v>3.54995250701904</v>
       </c>
       <c r="H199" t="n">
         <v>11419</v>
@@ -6401,7 +6401,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G208" t="n">
-        <v>3.30692386627197</v>
+        <v>3.30692362785339</v>
       </c>
       <c r="H208" t="n">
         <v>11449</v>
@@ -6575,7 +6575,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G214" t="n">
-        <v>3.28088521957397</v>
+        <v>3.2808849811554</v>
       </c>
       <c r="H214" t="n">
         <v>1000</v>
@@ -6604,7 +6604,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G215" t="n">
-        <v>3.26352572441101</v>
+        <v>3.26352620124817</v>
       </c>
       <c r="H215" t="n">
         <v>2689</v>
@@ -6633,7 +6633,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G216" t="n">
-        <v>3.28088521957397</v>
+        <v>3.2808849811554</v>
       </c>
       <c r="H216" t="n">
         <v>5107</v>
@@ -6691,7 +6691,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G218" t="n">
-        <v>3.28088521957397</v>
+        <v>3.2808849811554</v>
       </c>
       <c r="H218" t="n">
         <v>3100</v>
@@ -6749,7 +6749,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G220" t="n">
-        <v>3.26352572441101</v>
+        <v>3.26352620124817</v>
       </c>
       <c r="H220" t="n">
         <v>285</v>
@@ -6836,7 +6836,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G223" t="n">
-        <v>3.34164237976074</v>
+        <v>3.34164214134216</v>
       </c>
       <c r="H223" t="n">
         <v>1631</v>
@@ -6894,7 +6894,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G225" t="n">
-        <v>3.35900115966797</v>
+        <v>3.35900139808655</v>
       </c>
       <c r="H225" t="n">
         <v>7946</v>
@@ -6981,7 +6981,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G228" t="n">
-        <v>3.42843794822693</v>
+        <v>3.42843818664551</v>
       </c>
       <c r="H228" t="n">
         <v>2439</v>
@@ -7097,7 +7097,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G232" t="n">
-        <v>3.35032153129578</v>
+        <v>3.35032176971436</v>
       </c>
       <c r="H232" t="n">
         <v>11475</v>
@@ -7184,7 +7184,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G235" t="n">
-        <v>3.32428312301636</v>
+        <v>3.32428288459778</v>
       </c>
       <c r="H235" t="n">
         <v>800</v>
@@ -7213,7 +7213,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G236" t="n">
-        <v>3.32428312301636</v>
+        <v>3.32428288459778</v>
       </c>
       <c r="H236" t="n">
         <v>0</v>
@@ -7358,7 +7358,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G241" t="n">
-        <v>3.34164237976074</v>
+        <v>3.34164214134216</v>
       </c>
       <c r="H241" t="n">
         <v>1540</v>
@@ -7445,7 +7445,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G244" t="n">
-        <v>3.42843794822693</v>
+        <v>3.42843818664551</v>
       </c>
       <c r="H244" t="n">
         <v>2009</v>
@@ -7590,7 +7590,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G249" t="n">
-        <v>3.15937066078186</v>
+        <v>3.15937089920044</v>
       </c>
       <c r="H249" t="n">
         <v>2094</v>
@@ -7619,7 +7619,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G250" t="n">
-        <v>3.16805076599121</v>
+        <v>3.16805052757263</v>
       </c>
       <c r="H250" t="n">
         <v>7430</v>
@@ -7909,7 +7909,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G260" t="n">
-        <v>3.08993411064148</v>
+        <v>3.0899338722229</v>
       </c>
       <c r="H260" t="n">
         <v>31039</v>
@@ -7938,7 +7938,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G261" t="n">
-        <v>3.11597275733948</v>
+        <v>3.11597299575806</v>
       </c>
       <c r="H261" t="n">
         <v>80</v>
@@ -7967,7 +7967,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G262" t="n">
-        <v>3.16805076599121</v>
+        <v>3.16805052757263</v>
       </c>
       <c r="H262" t="n">
         <v>1560</v>
@@ -7996,7 +7996,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G263" t="n">
-        <v>3.08993411064148</v>
+        <v>3.0899338722229</v>
       </c>
       <c r="H263" t="n">
         <v>5405</v>
@@ -8025,7 +8025,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G264" t="n">
-        <v>3.13333177566528</v>
+        <v>3.13333225250244</v>
       </c>
       <c r="H264" t="n">
         <v>100</v>
@@ -8054,7 +8054,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G265" t="n">
-        <v>3.07257485389709</v>
+        <v>3.07257509231567</v>
       </c>
       <c r="H265" t="n">
         <v>1250</v>
@@ -8083,7 +8083,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G266" t="n">
-        <v>3.11597275733948</v>
+        <v>3.11597299575806</v>
       </c>
       <c r="H266" t="n">
         <v>700</v>
@@ -8112,7 +8112,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G267" t="n">
-        <v>3.11597275733948</v>
+        <v>3.11597299575806</v>
       </c>
       <c r="H267" t="n">
         <v>0</v>
@@ -8141,7 +8141,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G268" t="n">
-        <v>3.11597275733948</v>
+        <v>3.11597299575806</v>
       </c>
       <c r="H268" t="n">
         <v>0</v>
@@ -8228,7 +8228,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G271" t="n">
-        <v>3.13333177566528</v>
+        <v>3.13333225250244</v>
       </c>
       <c r="H271" t="n">
         <v>2533</v>
@@ -8286,7 +8286,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G273" t="n">
-        <v>3.02049732208252</v>
+        <v>3.0204975605011</v>
       </c>
       <c r="H273" t="n">
         <v>5743</v>
@@ -8315,7 +8315,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G274" t="n">
-        <v>2.93370151519775</v>
+        <v>2.93370175361633</v>
       </c>
       <c r="H274" t="n">
         <v>4510</v>
@@ -8344,7 +8344,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G275" t="n">
-        <v>2.96842002868652</v>
+        <v>2.96841979026794</v>
       </c>
       <c r="H275" t="n">
         <v>11722</v>
@@ -8402,7 +8402,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G277" t="n">
-        <v>3.02049732208252</v>
+        <v>3.0204975605011</v>
       </c>
       <c r="H277" t="n">
         <v>10072</v>
@@ -8431,7 +8431,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G278" t="n">
-        <v>3.07257485389709</v>
+        <v>3.07257509231567</v>
       </c>
       <c r="H278" t="n">
         <v>4119</v>
@@ -8489,7 +8489,7 @@
         <v>3.5</v>
       </c>
       <c r="G280" t="n">
-        <v>3.03785634040833</v>
+        <v>3.0378565788269</v>
       </c>
       <c r="H280" t="n">
         <v>105</v>
@@ -8518,7 +8518,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G281" t="n">
-        <v>3.0638952255249</v>
+        <v>3.06389498710632</v>
       </c>
       <c r="H281" t="n">
         <v>1883</v>
@@ -8547,7 +8547,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G282" t="n">
-        <v>3.0638952255249</v>
+        <v>3.06389498710632</v>
       </c>
       <c r="H282" t="n">
         <v>0</v>
@@ -8576,7 +8576,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G283" t="n">
-        <v>3.0638952255249</v>
+        <v>3.06389498710632</v>
       </c>
       <c r="H283" t="n">
         <v>1100</v>
@@ -8605,7 +8605,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G284" t="n">
-        <v>2.94238114356995</v>
+        <v>2.94238138198853</v>
       </c>
       <c r="H284" t="n">
         <v>2758</v>
@@ -8634,7 +8634,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G285" t="n">
-        <v>2.94238114356995</v>
+        <v>2.94238138198853</v>
       </c>
       <c r="H285" t="n">
         <v>20</v>
@@ -8663,7 +8663,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G286" t="n">
-        <v>2.98577904701233</v>
+        <v>2.98577928543091</v>
       </c>
       <c r="H286" t="n">
         <v>6281</v>
@@ -8692,7 +8692,7 @@
         <v>3.5</v>
       </c>
       <c r="G287" t="n">
-        <v>3.03785634040833</v>
+        <v>3.0378565788269</v>
       </c>
       <c r="H287" t="n">
         <v>3634</v>
@@ -8779,7 +8779,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G290" t="n">
-        <v>3.05521559715271</v>
+        <v>3.05521583557129</v>
       </c>
       <c r="H290" t="n">
         <v>2450</v>
@@ -8808,7 +8808,7 @@
         <v>3.5</v>
       </c>
       <c r="G291" t="n">
-        <v>3.03785634040833</v>
+        <v>3.0378565788269</v>
       </c>
       <c r="H291" t="n">
         <v>10</v>
@@ -8837,7 +8837,7 @@
         <v>3.5</v>
       </c>
       <c r="G292" t="n">
-        <v>3.03785634040833</v>
+        <v>3.0378565788269</v>
       </c>
       <c r="H292" t="n">
         <v>0</v>
@@ -8866,7 +8866,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G293" t="n">
-        <v>2.98577904701233</v>
+        <v>2.98577928543091</v>
       </c>
       <c r="H293" t="n">
         <v>2137</v>
@@ -8924,7 +8924,7 @@
         <v>3.5</v>
       </c>
       <c r="G295" t="n">
-        <v>3.03785634040833</v>
+        <v>3.0378565788269</v>
       </c>
       <c r="H295" t="n">
         <v>700</v>
@@ -9156,7 +9156,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G303" t="n">
-        <v>2.8816237449646</v>
+        <v>2.88162398338318</v>
       </c>
       <c r="H303" t="n">
         <v>7318</v>
@@ -9185,7 +9185,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G304" t="n">
-        <v>2.87294435501099</v>
+        <v>2.87294411659241</v>
       </c>
       <c r="H304" t="n">
         <v>20000</v>
@@ -9214,7 +9214,7 @@
         <v>3.5</v>
       </c>
       <c r="G305" t="n">
-        <v>3.03785634040833</v>
+        <v>3.0378565788269</v>
       </c>
       <c r="H305" t="n">
         <v>28717</v>
@@ -9330,7 +9330,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G309" t="n">
-        <v>3.16805076599121</v>
+        <v>3.16805052757263</v>
       </c>
       <c r="H309" t="n">
         <v>340</v>
@@ -9359,7 +9359,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G310" t="n">
-        <v>3.16805076599121</v>
+        <v>3.16805052757263</v>
       </c>
       <c r="H310" t="n">
         <v>0</v>
@@ -9388,7 +9388,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G311" t="n">
-        <v>3.22012805938721</v>
+        <v>3.22012829780579</v>
       </c>
       <c r="H311" t="n">
         <v>688</v>
@@ -9417,7 +9417,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G312" t="n">
-        <v>3.22012805938721</v>
+        <v>3.22012829780579</v>
       </c>
       <c r="H312" t="n">
         <v>0</v>
@@ -9620,7 +9620,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G319" t="n">
-        <v>3.11597275733948</v>
+        <v>3.11597299575806</v>
       </c>
       <c r="H319" t="n">
         <v>5736</v>
@@ -9707,7 +9707,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G322" t="n">
-        <v>3.16805076599121</v>
+        <v>3.16805052757263</v>
       </c>
       <c r="H322" t="n">
         <v>408</v>
@@ -9968,7 +9968,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G331" t="n">
-        <v>3.05521559715271</v>
+        <v>3.05521583557129</v>
       </c>
       <c r="H331" t="n">
         <v>830</v>
@@ -9997,7 +9997,7 @@
         <v>3.5</v>
       </c>
       <c r="G332" t="n">
-        <v>3.03785634040833</v>
+        <v>3.0378565788269</v>
       </c>
       <c r="H332" t="n">
         <v>2958</v>
@@ -10171,7 +10171,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G338" t="n">
-        <v>3.11597275733948</v>
+        <v>3.11597299575806</v>
       </c>
       <c r="H338" t="n">
         <v>70</v>
@@ -10200,7 +10200,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G339" t="n">
-        <v>3.15937066078186</v>
+        <v>3.15937089920044</v>
       </c>
       <c r="H339" t="n">
         <v>100</v>
@@ -10229,7 +10229,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G340" t="n">
-        <v>3.11597275733948</v>
+        <v>3.11597299575806</v>
       </c>
       <c r="H340" t="n">
         <v>823</v>
@@ -10374,7 +10374,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G345" t="n">
-        <v>3.22012805938721</v>
+        <v>3.22012829780579</v>
       </c>
       <c r="H345" t="n">
         <v>3873</v>
@@ -10461,7 +10461,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G348" t="n">
-        <v>3.42843794822693</v>
+        <v>3.42843818664551</v>
       </c>
       <c r="H348" t="n">
         <v>10171</v>
@@ -10577,7 +10577,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G352" t="n">
-        <v>3.34164237976074</v>
+        <v>3.34164214134216</v>
       </c>
       <c r="H352" t="n">
         <v>1770</v>
@@ -10635,7 +10635,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G354" t="n">
-        <v>3.34164237976074</v>
+        <v>3.34164214134216</v>
       </c>
       <c r="H354" t="n">
         <v>1650</v>
@@ -10664,7 +10664,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G355" t="n">
-        <v>3.30692386627197</v>
+        <v>3.30692362785339</v>
       </c>
       <c r="H355" t="n">
         <v>20</v>
@@ -10693,7 +10693,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G356" t="n">
-        <v>3.42843794822693</v>
+        <v>3.42843818664551</v>
       </c>
       <c r="H356" t="n">
         <v>1020</v>
@@ -10722,7 +10722,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G357" t="n">
-        <v>3.42843794822693</v>
+        <v>3.42843818664551</v>
       </c>
       <c r="H357" t="n">
         <v>1750</v>
@@ -10838,7 +10838,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G361" t="n">
-        <v>3.46304678916931</v>
+        <v>3.46304655075073</v>
       </c>
       <c r="H361" t="n">
         <v>6479</v>
@@ -10896,7 +10896,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G363" t="n">
-        <v>3.53336191177368</v>
+        <v>3.53336215019226</v>
       </c>
       <c r="H363" t="n">
         <v>425644</v>
@@ -10954,7 +10954,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G365" t="n">
-        <v>3.55973076820374</v>
+        <v>3.55973052978516</v>
       </c>
       <c r="H365" t="n">
         <v>10835</v>
@@ -10983,7 +10983,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G366" t="n">
-        <v>3.47183585166931</v>
+        <v>3.47183609008789</v>
       </c>
       <c r="H366" t="n">
         <v>16015</v>
@@ -11215,7 +11215,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G374" t="n">
-        <v>3.85857224464417</v>
+        <v>3.85857200622559</v>
       </c>
       <c r="H374" t="n">
         <v>3601</v>
@@ -11302,7 +11302,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G377" t="n">
-        <v>3.70915150642395</v>
+        <v>3.70915126800537</v>
       </c>
       <c r="H377" t="n">
         <v>1400</v>
@@ -11360,7 +11360,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G379" t="n">
-        <v>3.90251970291138</v>
+        <v>3.9025194644928</v>
       </c>
       <c r="H379" t="n">
         <v>28775</v>
@@ -11418,7 +11418,7 @@
         <v>4.5</v>
       </c>
       <c r="G381" t="n">
-        <v>3.95525646209717</v>
+        <v>3.95525598526001</v>
       </c>
       <c r="H381" t="n">
         <v>11250</v>
@@ -11447,7 +11447,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G382" t="n">
-        <v>3.92888736724854</v>
+        <v>3.92888784408569</v>
       </c>
       <c r="H382" t="n">
         <v>12048</v>
@@ -11476,7 +11476,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G383" t="n">
-        <v>3.92009806632996</v>
+        <v>3.92009830474854</v>
       </c>
       <c r="H383" t="n">
         <v>30</v>
@@ -11563,7 +11563,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G386" t="n">
-        <v>3.647625207901</v>
+        <v>3.64762496948242</v>
       </c>
       <c r="H386" t="n">
         <v>7282</v>
@@ -11621,7 +11621,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G388" t="n">
-        <v>3.55094122886658</v>
+        <v>3.550940990448</v>
       </c>
       <c r="H388" t="n">
         <v>7442</v>
@@ -11766,7 +11766,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G393" t="n">
-        <v>3.67399311065674</v>
+        <v>3.67399334907532</v>
       </c>
       <c r="H393" t="n">
         <v>9627</v>
@@ -11795,7 +11795,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G394" t="n">
-        <v>3.67399311065674</v>
+        <v>3.67399334907532</v>
       </c>
       <c r="H394" t="n">
         <v>6027</v>
@@ -11824,7 +11824,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G395" t="n">
-        <v>3.744309425354</v>
+        <v>3.74430918693542</v>
       </c>
       <c r="H395" t="n">
         <v>15241</v>
@@ -11940,7 +11940,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G399" t="n">
-        <v>3.70915150642395</v>
+        <v>3.70915126800537</v>
       </c>
       <c r="H399" t="n">
         <v>1746</v>
@@ -12056,7 +12056,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G403" t="n">
-        <v>3.68278288841248</v>
+        <v>3.68278312683105</v>
       </c>
       <c r="H403" t="n">
         <v>5461</v>
@@ -12085,7 +12085,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G404" t="n">
-        <v>3.90251970291138</v>
+        <v>3.9025194644928</v>
       </c>
       <c r="H404" t="n">
         <v>16220</v>
@@ -12143,7 +12143,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G406" t="n">
-        <v>3.84099292755127</v>
+        <v>3.84099268913269</v>
       </c>
       <c r="H406" t="n">
         <v>7000</v>
@@ -12201,7 +12201,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G408" t="n">
-        <v>3.78825640678406</v>
+        <v>3.78825664520264</v>
       </c>
       <c r="H408" t="n">
         <v>9728</v>
@@ -12230,7 +12230,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G409" t="n">
-        <v>4.04315090179443</v>
+        <v>4.04315042495728</v>
       </c>
       <c r="H409" t="n">
         <v>11444</v>
@@ -12375,7 +12375,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G414" t="n">
-        <v>4.04315090179443</v>
+        <v>4.04315042495728</v>
       </c>
       <c r="H414" t="n">
         <v>4777</v>
@@ -12404,7 +12404,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G415" t="n">
-        <v>4.04315090179443</v>
+        <v>4.04315042495728</v>
       </c>
       <c r="H415" t="n">
         <v>0</v>
@@ -12462,7 +12462,7 @@
         <v>4.59000015258789</v>
       </c>
       <c r="G417" t="n">
-        <v>4.03436136245728</v>
+        <v>4.03436183929443</v>
       </c>
       <c r="H417" t="n">
         <v>6334</v>
@@ -12491,7 +12491,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G418" t="n">
-        <v>4.08709812164307</v>
+        <v>4.08709859848022</v>
       </c>
       <c r="H418" t="n">
         <v>6771</v>
@@ -12549,7 +12549,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G420" t="n">
-        <v>4.30683422088623</v>
+        <v>4.30683469772339</v>
       </c>
       <c r="H420" t="n">
         <v>32975</v>
@@ -12578,7 +12578,7 @@
         <v>5</v>
       </c>
       <c r="G421" t="n">
-        <v>4.39472913742065</v>
+        <v>4.3947286605835</v>
       </c>
       <c r="H421" t="n">
         <v>12311</v>
@@ -12607,7 +12607,7 @@
         <v>5</v>
       </c>
       <c r="G422" t="n">
-        <v>4.39472913742065</v>
+        <v>4.3947286605835</v>
       </c>
       <c r="H422" t="n">
         <v>7994</v>
@@ -12636,7 +12636,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G423" t="n">
-        <v>4.28046607971191</v>
+        <v>4.28046655654907</v>
       </c>
       <c r="H423" t="n">
         <v>7858</v>
@@ -12665,7 +12665,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G424" t="n">
-        <v>4.30683422088623</v>
+        <v>4.30683469772339</v>
       </c>
       <c r="H424" t="n">
         <v>1866</v>
@@ -12694,7 +12694,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G425" t="n">
-        <v>4.29804563522339</v>
+        <v>4.29804515838623</v>
       </c>
       <c r="H425" t="n">
         <v>2886</v>
@@ -12752,7 +12752,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G427" t="n">
-        <v>4.34199237823486</v>
+        <v>4.34199190139771</v>
       </c>
       <c r="H427" t="n">
         <v>6045</v>
@@ -12839,7 +12839,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G430" t="n">
-        <v>4.28925609588623</v>
+        <v>4.28925561904907</v>
       </c>
       <c r="H430" t="n">
         <v>7986</v>
@@ -12868,7 +12868,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G431" t="n">
-        <v>4.28925609588623</v>
+        <v>4.28925561904907</v>
       </c>
       <c r="H431" t="n">
         <v>2210</v>
@@ -12955,7 +12955,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G434" t="n">
-        <v>4.22772932052612</v>
+        <v>4.22772979736328</v>
       </c>
       <c r="H434" t="n">
         <v>5368</v>
@@ -13042,7 +13042,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G437" t="n">
-        <v>4.07830810546875</v>
+        <v>4.07830858230591</v>
       </c>
       <c r="H437" t="n">
         <v>2764</v>
@@ -13100,7 +13100,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G439" t="n">
-        <v>4.3859395980835</v>
+        <v>4.38593912124634</v>
       </c>
       <c r="H439" t="n">
         <v>2700</v>
@@ -13129,7 +13129,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G440" t="n">
-        <v>4.3859395980835</v>
+        <v>4.38593912124634</v>
       </c>
       <c r="H440" t="n">
         <v>100</v>
@@ -13158,7 +13158,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G441" t="n">
-        <v>4.30683422088623</v>
+        <v>4.30683469772339</v>
       </c>
       <c r="H441" t="n">
         <v>14413</v>
@@ -13187,7 +13187,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G442" t="n">
-        <v>4.30683422088623</v>
+        <v>4.30683469772339</v>
       </c>
       <c r="H442" t="n">
         <v>5600</v>
@@ -13245,7 +13245,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G444" t="n">
-        <v>4.34199237823486</v>
+        <v>4.34199190139771</v>
       </c>
       <c r="H444" t="n">
         <v>20</v>
@@ -13274,7 +13274,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G445" t="n">
-        <v>4.26288652420044</v>
+        <v>4.2628870010376</v>
       </c>
       <c r="H445" t="n">
         <v>2230</v>
@@ -13303,7 +13303,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G446" t="n">
-        <v>4.34199237823486</v>
+        <v>4.34199190139771</v>
       </c>
       <c r="H446" t="n">
         <v>1000</v>
@@ -13332,7 +13332,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G447" t="n">
-        <v>4.3859395980835</v>
+        <v>4.38593912124634</v>
       </c>
       <c r="H447" t="n">
         <v>20</v>
@@ -13390,7 +13390,7 @@
         <v>5</v>
       </c>
       <c r="G449" t="n">
-        <v>4.39472913742065</v>
+        <v>4.3947286605835</v>
       </c>
       <c r="H449" t="n">
         <v>900</v>
@@ -13419,7 +13419,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G450" t="n">
-        <v>4.21894025802612</v>
+        <v>4.21893978118896</v>
       </c>
       <c r="H450" t="n">
         <v>4300</v>
@@ -13448,7 +13448,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G451" t="n">
-        <v>4.30683422088623</v>
+        <v>4.30683469772339</v>
       </c>
       <c r="H451" t="n">
         <v>600</v>
@@ -13477,7 +13477,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G452" t="n">
-        <v>4.21894025802612</v>
+        <v>4.21893978118896</v>
       </c>
       <c r="H452" t="n">
         <v>1223</v>
@@ -13564,7 +13564,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G455" t="n">
-        <v>4.11346626281738</v>
+        <v>4.11346578598022</v>
       </c>
       <c r="H455" t="n">
         <v>1631</v>
@@ -13651,7 +13651,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G458" t="n">
-        <v>4.05194044113159</v>
+        <v>4.05194091796875</v>
       </c>
       <c r="H458" t="n">
         <v>1015</v>
@@ -13767,7 +13767,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G462" t="n">
-        <v>4.08709812164307</v>
+        <v>4.08709859848022</v>
       </c>
       <c r="H462" t="n">
         <v>155</v>
@@ -13854,7 +13854,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G465" t="n">
-        <v>4.26288652420044</v>
+        <v>4.2628870010376</v>
       </c>
       <c r="H465" t="n">
         <v>6017</v>
@@ -13883,7 +13883,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G466" t="n">
-        <v>4.28925609588623</v>
+        <v>4.28925561904907</v>
       </c>
       <c r="H466" t="n">
         <v>1395</v>
@@ -13941,7 +13941,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G468" t="n">
-        <v>4.50020217895508</v>
+        <v>4.50020265579224</v>
       </c>
       <c r="H468" t="n">
         <v>25612</v>
@@ -14057,7 +14057,7 @@
         <v>5</v>
       </c>
       <c r="G472" t="n">
-        <v>4.41899013519287</v>
+        <v>4.41898965835571</v>
       </c>
       <c r="H472" t="n">
         <v>6010</v>
@@ -14086,7 +14086,7 @@
         <v>5</v>
       </c>
       <c r="G473" t="n">
-        <v>4.41899013519287</v>
+        <v>4.41898965835571</v>
       </c>
       <c r="H473" t="n">
         <v>3807</v>
@@ -14434,7 +14434,7 @@
         <v>5</v>
       </c>
       <c r="G485" t="n">
-        <v>4.41899013519287</v>
+        <v>4.41898965835571</v>
       </c>
       <c r="H485" t="n">
         <v>7329</v>
@@ -14463,7 +14463,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G486" t="n">
-        <v>4.37480020523071</v>
+        <v>4.37479972839355</v>
       </c>
       <c r="H486" t="n">
         <v>1753</v>
@@ -14695,7 +14695,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G494" t="n">
-        <v>4.22455453872681</v>
+        <v>4.22455501556396</v>
       </c>
       <c r="H494" t="n">
         <v>1787</v>
@@ -14753,7 +14753,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G496" t="n">
-        <v>4.10966062545776</v>
+        <v>4.10966110229492</v>
       </c>
       <c r="H496" t="n">
         <v>2705</v>
@@ -14782,7 +14782,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G497" t="n">
-        <v>4.03011894226074</v>
+        <v>4.0301194190979</v>
       </c>
       <c r="H497" t="n">
         <v>4388</v>
@@ -14811,7 +14811,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G498" t="n">
-        <v>4.03011894226074</v>
+        <v>4.0301194190979</v>
       </c>
       <c r="H498" t="n">
         <v>18707</v>
@@ -14956,7 +14956,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G503" t="n">
-        <v>4.10966062545776</v>
+        <v>4.10966110229492</v>
       </c>
       <c r="H503" t="n">
         <v>3919</v>
@@ -14985,7 +14985,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G504" t="n">
-        <v>4.10966062545776</v>
+        <v>4.10966110229492</v>
       </c>
       <c r="H504" t="n">
         <v>0</v>
@@ -15043,7 +15043,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G506" t="n">
-        <v>4.10082244873047</v>
+        <v>4.10082292556763</v>
       </c>
       <c r="H506" t="n">
         <v>435</v>
@@ -15072,7 +15072,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G507" t="n">
-        <v>4.22455453872681</v>
+        <v>4.22455501556396</v>
       </c>
       <c r="H507" t="n">
         <v>450</v>
@@ -15188,7 +15188,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G511" t="n">
-        <v>4.10966062545776</v>
+        <v>4.10966110229492</v>
       </c>
       <c r="H511" t="n">
         <v>2700</v>
@@ -15217,7 +15217,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G512" t="n">
-        <v>4.10966062545776</v>
+        <v>4.10966110229492</v>
       </c>
       <c r="H512" t="n">
         <v>0</v>
@@ -15333,7 +15333,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G516" t="n">
-        <v>4.32177257537842</v>
+        <v>4.32177209854126</v>
       </c>
       <c r="H516" t="n">
         <v>2870</v>
@@ -15449,7 +15449,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G520" t="n">
-        <v>4.48969411849976</v>
+        <v>4.4896936416626</v>
       </c>
       <c r="H520" t="n">
         <v>1048</v>
@@ -15797,7 +15797,7 @@
         <v>5</v>
       </c>
       <c r="G532" t="n">
-        <v>4.41899013519287</v>
+        <v>4.41898965835571</v>
       </c>
       <c r="H532" t="n">
         <v>5500</v>
@@ -16000,7 +16000,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G539" t="n">
-        <v>4.41015195846558</v>
+        <v>4.41015148162842</v>
       </c>
       <c r="H539" t="n">
         <v>870</v>
@@ -16116,7 +16116,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G543" t="n">
-        <v>4.38363790512085</v>
+        <v>4.38363885879517</v>
       </c>
       <c r="H543" t="n">
         <v>902</v>
@@ -16203,7 +16203,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G546" t="n">
-        <v>4.33944797515869</v>
+        <v>4.33944845199585</v>
       </c>
       <c r="H546" t="n">
         <v>1600</v>
@@ -16232,7 +16232,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G547" t="n">
-        <v>4.33944797515869</v>
+        <v>4.33944845199585</v>
       </c>
       <c r="H547" t="n">
         <v>0</v>
@@ -16261,7 +16261,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G548" t="n">
-        <v>4.33944797515869</v>
+        <v>4.33944845199585</v>
       </c>
       <c r="H548" t="n">
         <v>0</v>
@@ -16406,7 +16406,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G553" t="n">
-        <v>4.31293487548828</v>
+        <v>4.31293439865112</v>
       </c>
       <c r="H553" t="n">
         <v>11439</v>
@@ -16551,7 +16551,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G558" t="n">
-        <v>4.10966062545776</v>
+        <v>4.10966110229492</v>
       </c>
       <c r="H558" t="n">
         <v>4550</v>
@@ -16638,7 +16638,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G561" t="n">
-        <v>4.15385103225708</v>
+        <v>4.15385055541992</v>
       </c>
       <c r="H561" t="n">
         <v>11912</v>
@@ -16667,7 +16667,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G562" t="n">
-        <v>4.10966062545776</v>
+        <v>4.10966110229492</v>
       </c>
       <c r="H562" t="n">
         <v>1123</v>
@@ -16783,7 +16783,7 @@
         <v>5</v>
       </c>
       <c r="G566" t="n">
-        <v>4.41899013519287</v>
+        <v>4.41898965835571</v>
       </c>
       <c r="H566" t="n">
         <v>23066</v>
@@ -17189,7 +17189,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G580" t="n">
-        <v>4.94926881790161</v>
+        <v>4.94926929473877</v>
       </c>
       <c r="H580" t="n">
         <v>3440</v>
@@ -17247,7 +17247,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G582" t="n">
-        <v>5.26743650436401</v>
+        <v>5.26743602752686</v>
       </c>
       <c r="H582" t="n">
         <v>19700</v>
@@ -17276,7 +17276,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G583" t="n">
-        <v>5.47954750061035</v>
+        <v>5.47954797744751</v>
       </c>
       <c r="H583" t="n">
         <v>51392</v>
@@ -17305,7 +17305,7 @@
         <v>6.03999996185303</v>
       </c>
       <c r="G584" t="n">
-        <v>5.3381404876709</v>
+        <v>5.33814001083374</v>
       </c>
       <c r="H584" t="n">
         <v>12438</v>
@@ -17363,7 +17363,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G586" t="n">
-        <v>5.47954750061035</v>
+        <v>5.47954797744751</v>
       </c>
       <c r="H586" t="n">
         <v>857</v>
@@ -17392,7 +17392,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G587" t="n">
-        <v>5.47954750061035</v>
+        <v>5.47954797744751</v>
       </c>
       <c r="H587" t="n">
         <v>16499</v>
@@ -17421,7 +17421,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G588" t="n">
-        <v>5.70933532714844</v>
+        <v>5.70933485031128</v>
       </c>
       <c r="H588" t="n">
         <v>1075</v>
@@ -17537,7 +17537,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G592" t="n">
-        <v>5.51489925384521</v>
+        <v>5.51489973068237</v>
       </c>
       <c r="H592" t="n">
         <v>637</v>
@@ -17566,7 +17566,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G593" t="n">
-        <v>5.56792736053467</v>
+        <v>5.56792783737183</v>
       </c>
       <c r="H593" t="n">
         <v>3180</v>
@@ -17595,7 +17595,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G594" t="n">
-        <v>5.56792736053467</v>
+        <v>5.56792783737183</v>
       </c>
       <c r="H594" t="n">
         <v>3910</v>
@@ -17653,7 +17653,7 @@
         <v>6.71999979019165</v>
       </c>
       <c r="G596" t="n">
-        <v>5.93912267684937</v>
+        <v>5.93912220001221</v>
       </c>
       <c r="H596" t="n">
         <v>3720</v>
@@ -17798,7 +17798,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G601" t="n">
-        <v>5.47954750061035</v>
+        <v>5.47954797744751</v>
       </c>
       <c r="H601" t="n">
         <v>2590</v>
@@ -17827,7 +17827,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G602" t="n">
-        <v>5.49722385406494</v>
+        <v>5.49722337722778</v>
       </c>
       <c r="H602" t="n">
         <v>2401</v>
@@ -17885,7 +17885,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G604" t="n">
-        <v>5.51489925384521</v>
+        <v>5.51489973068237</v>
       </c>
       <c r="H604" t="n">
         <v>946</v>
@@ -18059,7 +18059,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G610" t="n">
-        <v>5.70933532714844</v>
+        <v>5.70933485031128</v>
       </c>
       <c r="H610" t="n">
         <v>2183</v>
@@ -18233,7 +18233,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G616" t="n">
-        <v>5.88609504699707</v>
+        <v>5.88609457015991</v>
       </c>
       <c r="H616" t="n">
         <v>1889</v>
@@ -18262,7 +18262,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G617" t="n">
-        <v>5.92144632339478</v>
+        <v>5.92144680023193</v>
       </c>
       <c r="H617" t="n">
         <v>18955</v>
@@ -18349,7 +18349,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G620" t="n">
-        <v>5.47954750061035</v>
+        <v>5.47954797744751</v>
       </c>
       <c r="H620" t="n">
         <v>9540</v>
@@ -18552,7 +18552,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G627" t="n">
-        <v>6.00982713699341</v>
+        <v>6.00982666015625</v>
       </c>
       <c r="H627" t="n">
         <v>6922</v>
@@ -18581,7 +18581,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G628" t="n">
-        <v>5.88609504699707</v>
+        <v>5.88609457015991</v>
       </c>
       <c r="H628" t="n">
         <v>1335</v>
@@ -18610,7 +18610,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G629" t="n">
-        <v>5.92144632339478</v>
+        <v>5.92144680023193</v>
       </c>
       <c r="H629" t="n">
         <v>400</v>
@@ -18639,7 +18639,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G630" t="n">
-        <v>6.00982713699341</v>
+        <v>6.00982666015625</v>
       </c>
       <c r="H630" t="n">
         <v>16000</v>
@@ -18726,7 +18726,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G633" t="n">
-        <v>5.83306694030762</v>
+        <v>5.83306741714478</v>
       </c>
       <c r="H633" t="n">
         <v>2617</v>
@@ -18755,7 +18755,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G634" t="n">
-        <v>5.83306694030762</v>
+        <v>5.83306741714478</v>
       </c>
       <c r="H634" t="n">
         <v>0</v>
@@ -18784,7 +18784,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G635" t="n">
-        <v>5.83306694030762</v>
+        <v>5.83306741714478</v>
       </c>
       <c r="H635" t="n">
         <v>200</v>
@@ -18813,7 +18813,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G636" t="n">
-        <v>5.70933532714844</v>
+        <v>5.70933485031128</v>
       </c>
       <c r="H636" t="n">
         <v>250</v>
@@ -18900,7 +18900,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G639" t="n">
-        <v>5.58560371398926</v>
+        <v>5.5856032371521</v>
       </c>
       <c r="H639" t="n">
         <v>400</v>
@@ -18929,7 +18929,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G640" t="n">
-        <v>5.70933532714844</v>
+        <v>5.70933485031128</v>
       </c>
       <c r="H640" t="n">
         <v>150</v>
@@ -18958,7 +18958,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G641" t="n">
-        <v>5.7977147102356</v>
+        <v>5.79771518707275</v>
       </c>
       <c r="H641" t="n">
         <v>258</v>
@@ -18987,7 +18987,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G642" t="n">
-        <v>5.7977147102356</v>
+        <v>5.79771518707275</v>
       </c>
       <c r="H642" t="n">
         <v>1057</v>
@@ -19045,7 +19045,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G644" t="n">
-        <v>5.47954750061035</v>
+        <v>5.47954797744751</v>
       </c>
       <c r="H644" t="n">
         <v>1491</v>
@@ -19074,7 +19074,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G645" t="n">
-        <v>5.47954750061035</v>
+        <v>5.47954797744751</v>
       </c>
       <c r="H645" t="n">
         <v>1044</v>
@@ -19103,7 +19103,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G646" t="n">
-        <v>5.47954750061035</v>
+        <v>5.47954797744751</v>
       </c>
       <c r="H646" t="n">
         <v>300</v>
@@ -19132,7 +19132,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G647" t="n">
-        <v>5.37349224090576</v>
+        <v>5.3734917640686</v>
       </c>
       <c r="H647" t="n">
         <v>1250</v>
@@ -19161,7 +19161,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G648" t="n">
-        <v>5.26743650436401</v>
+        <v>5.26743602752686</v>
       </c>
       <c r="H648" t="n">
         <v>3000</v>
@@ -19306,7 +19306,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G653" t="n">
-        <v>5.12602853775024</v>
+        <v>5.1260290145874</v>
       </c>
       <c r="H653" t="n">
         <v>2025</v>
@@ -19335,7 +19335,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G654" t="n">
-        <v>4.94926881790161</v>
+        <v>4.94926929473877</v>
       </c>
       <c r="H654" t="n">
         <v>3137</v>
@@ -19364,7 +19364,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G655" t="n">
-        <v>4.94926881790161</v>
+        <v>4.94926929473877</v>
       </c>
       <c r="H655" t="n">
         <v>14439</v>
@@ -19451,7 +19451,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G658" t="n">
-        <v>5.12602853775024</v>
+        <v>5.1260290145874</v>
       </c>
       <c r="H658" t="n">
         <v>2873</v>
@@ -19509,7 +19509,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G660" t="n">
-        <v>5.23208427429199</v>
+        <v>5.23208475112915</v>
       </c>
       <c r="H660" t="n">
         <v>16216</v>
@@ -19596,7 +19596,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G663" t="n">
-        <v>5.47954750061035</v>
+        <v>5.47954797744751</v>
       </c>
       <c r="H663" t="n">
         <v>2792</v>
@@ -19973,7 +19973,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G676" t="n">
-        <v>4.2422308921814</v>
+        <v>4.24223041534424</v>
       </c>
       <c r="H676" t="n">
         <v>443</v>
@@ -20002,7 +20002,7 @@
         <v>5</v>
       </c>
       <c r="G677" t="n">
-        <v>4.41899013519287</v>
+        <v>4.41898965835571</v>
       </c>
       <c r="H677" t="n">
         <v>2692</v>
@@ -20060,7 +20060,7 @@
         <v>5</v>
       </c>
       <c r="G679" t="n">
-        <v>4.41899013519287</v>
+        <v>4.41898965835571</v>
       </c>
       <c r="H679" t="n">
         <v>8270</v>
@@ -20379,7 +20379,7 @@
         <v>5.5</v>
       </c>
       <c r="G690" t="n">
-        <v>4.86088943481445</v>
+        <v>4.86088895797729</v>
       </c>
       <c r="H690" t="n">
         <v>2318</v>
@@ -20437,7 +20437,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G692" t="n">
-        <v>4.87856483459473</v>
+        <v>4.87856531143188</v>
       </c>
       <c r="H692" t="n">
         <v>314</v>
@@ -20466,7 +20466,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G693" t="n">
-        <v>4.87856483459473</v>
+        <v>4.87856531143188</v>
       </c>
       <c r="H693" t="n">
         <v>0</v>
@@ -20524,7 +20524,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G695" t="n">
-        <v>4.87856483459473</v>
+        <v>4.87856531143188</v>
       </c>
       <c r="H695" t="n">
         <v>4531</v>
@@ -20582,7 +20582,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G697" t="n">
-        <v>4.94926881790161</v>
+        <v>4.94926929473877</v>
       </c>
       <c r="H697" t="n">
         <v>6290</v>
@@ -20611,7 +20611,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G698" t="n">
-        <v>4.94926881790161</v>
+        <v>4.94926929473877</v>
       </c>
       <c r="H698" t="n">
         <v>190</v>
@@ -20640,7 +20640,7 @@
         <v>5.5</v>
       </c>
       <c r="G699" t="n">
-        <v>4.86088943481445</v>
+        <v>4.86088895797729</v>
       </c>
       <c r="H699" t="n">
         <v>1100</v>
@@ -20727,7 +20727,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G702" t="n">
-        <v>4.94926881790161</v>
+        <v>4.94926929473877</v>
       </c>
       <c r="H702" t="n">
         <v>4149</v>
@@ -20814,7 +20814,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G705" t="n">
-        <v>5.14370489120483</v>
+        <v>5.14370441436768</v>
       </c>
       <c r="H705" t="n">
         <v>60299</v>
@@ -20843,7 +20843,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G706" t="n">
-        <v>5.12602853775024</v>
+        <v>5.1260290145874</v>
       </c>
       <c r="H706" t="n">
         <v>661</v>
@@ -20901,7 +20901,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G708" t="n">
-        <v>4.98462104797363</v>
+        <v>4.98462057113647</v>
       </c>
       <c r="H708" t="n">
         <v>1299</v>
@@ -20930,7 +20930,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G709" t="n">
-        <v>5.12602853775024</v>
+        <v>5.1260290145874</v>
       </c>
       <c r="H709" t="n">
         <v>6815</v>
@@ -20959,7 +20959,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G710" t="n">
-        <v>5.12602853775024</v>
+        <v>5.1260290145874</v>
       </c>
       <c r="H710" t="n">
         <v>0</v>
@@ -20988,7 +20988,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G711" t="n">
-        <v>5.14370489120483</v>
+        <v>5.14370441436768</v>
       </c>
       <c r="H711" t="n">
         <v>6657</v>
@@ -21017,7 +21017,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G712" t="n">
-        <v>5.14370489120483</v>
+        <v>5.14370441436768</v>
       </c>
       <c r="H712" t="n">
         <v>0</v>
@@ -21104,7 +21104,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G715" t="n">
-        <v>5.14370489120483</v>
+        <v>5.14370441436768</v>
       </c>
       <c r="H715" t="n">
         <v>3046</v>
@@ -21278,7 +21278,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G721" t="n">
-        <v>4.94926881790161</v>
+        <v>4.94926929473877</v>
       </c>
       <c r="H721" t="n">
         <v>277</v>
@@ -21365,7 +21365,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G724" t="n">
-        <v>5.24976015090942</v>
+        <v>5.24976062774658</v>
       </c>
       <c r="H724" t="n">
         <v>4500</v>
@@ -21626,7 +21626,7 @@
         <v>5.8600001335144</v>
       </c>
       <c r="G733" t="n">
-        <v>5.24438095092773</v>
+        <v>5.24438142776489</v>
       </c>
       <c r="H733" t="n">
         <v>1735</v>
@@ -21655,7 +21655,7 @@
         <v>5.8600001335144</v>
       </c>
       <c r="G734" t="n">
-        <v>5.24438095092773</v>
+        <v>5.24438142776489</v>
       </c>
       <c r="H734" t="n">
         <v>0</v>
@@ -21771,7 +21771,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G738" t="n">
-        <v>5.26228046417236</v>
+        <v>5.26227998733521</v>
       </c>
       <c r="H738" t="n">
         <v>40</v>
@@ -22148,7 +22148,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G751" t="n">
-        <v>4.99379587173462</v>
+        <v>4.99379634857178</v>
       </c>
       <c r="H751" t="n">
         <v>470</v>
@@ -22351,7 +22351,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G758" t="n">
-        <v>5.31597661972046</v>
+        <v>5.31597709655762</v>
       </c>
       <c r="H758" t="n">
         <v>1333</v>
@@ -22380,7 +22380,7 @@
         <v>6</v>
       </c>
       <c r="G759" t="n">
-        <v>5.36967325210571</v>
+        <v>5.36967372894287</v>
       </c>
       <c r="H759" t="n">
         <v>304</v>
@@ -22409,7 +22409,7 @@
         <v>6</v>
       </c>
       <c r="G760" t="n">
-        <v>5.36967325210571</v>
+        <v>5.36967372894287</v>
       </c>
       <c r="H760" t="n">
         <v>829</v>
@@ -22438,7 +22438,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G761" t="n">
-        <v>5.47706651687622</v>
+        <v>5.47706699371338</v>
       </c>
       <c r="H761" t="n">
         <v>270</v>
@@ -22641,7 +22641,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G768" t="n">
-        <v>5.72765159606934</v>
+        <v>5.72765207290649</v>
       </c>
       <c r="H768" t="n">
         <v>2958</v>
@@ -22699,7 +22699,7 @@
         <v>6.51999998092651</v>
       </c>
       <c r="G770" t="n">
-        <v>5.835045337677</v>
+        <v>5.83504486083984</v>
       </c>
       <c r="H770" t="n">
         <v>667</v>
@@ -22728,7 +22728,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G771" t="n">
-        <v>5.72765159606934</v>
+        <v>5.72765207290649</v>
       </c>
       <c r="H771" t="n">
         <v>678</v>
@@ -22757,7 +22757,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G772" t="n">
-        <v>5.72765159606934</v>
+        <v>5.72765207290649</v>
       </c>
       <c r="H772" t="n">
         <v>1540</v>
@@ -22844,7 +22844,7 @@
         <v>6.5</v>
       </c>
       <c r="G775" t="n">
-        <v>5.81714582443237</v>
+        <v>5.81714630126953</v>
       </c>
       <c r="H775" t="n">
         <v>11</v>
@@ -22902,7 +22902,7 @@
         <v>6.5</v>
       </c>
       <c r="G777" t="n">
-        <v>5.81714582443237</v>
+        <v>5.81714630126953</v>
       </c>
       <c r="H777" t="n">
         <v>6650</v>
@@ -23018,7 +23018,7 @@
         <v>6.73999977111816</v>
       </c>
       <c r="G781" t="n">
-        <v>6.03193283081055</v>
+        <v>6.03193330764771</v>
       </c>
       <c r="H781" t="n">
         <v>1012</v>
@@ -23105,7 +23105,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G784" t="n">
-        <v>6.08563041687012</v>
+        <v>6.08562994003296</v>
       </c>
       <c r="H784" t="n">
         <v>2889</v>
@@ -23250,7 +23250,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G789" t="n">
-        <v>5.8887414932251</v>
+        <v>5.88874197006226</v>
       </c>
       <c r="H789" t="n">
         <v>3581</v>
@@ -23308,7 +23308,7 @@
         <v>6.53999996185303</v>
       </c>
       <c r="G791" t="n">
-        <v>5.85294389724731</v>
+        <v>5.85294437408447</v>
       </c>
       <c r="H791" t="n">
         <v>31</v>
@@ -23337,7 +23337,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G792" t="n">
-        <v>5.72765159606934</v>
+        <v>5.72765207290649</v>
       </c>
       <c r="H792" t="n">
         <v>40050</v>
@@ -23482,7 +23482,7 @@
         <v>6.5</v>
       </c>
       <c r="G797" t="n">
-        <v>5.81714582443237</v>
+        <v>5.81714630126953</v>
       </c>
       <c r="H797" t="n">
         <v>1055</v>
@@ -23511,7 +23511,7 @@
         <v>6.5</v>
       </c>
       <c r="G798" t="n">
-        <v>5.81714582443237</v>
+        <v>5.81714630126953</v>
       </c>
       <c r="H798" t="n">
         <v>30000</v>
@@ -23598,7 +23598,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G801" t="n">
-        <v>5.8887414932251</v>
+        <v>5.88874197006226</v>
       </c>
       <c r="H801" t="n">
         <v>550</v>
@@ -23772,7 +23772,7 @@
         <v>6.42000007629395</v>
       </c>
       <c r="G807" t="n">
-        <v>5.74555110931396</v>
+        <v>5.74555063247681</v>
       </c>
       <c r="H807" t="n">
         <v>50</v>
@@ -23888,7 +23888,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G811" t="n">
-        <v>5.54866218566895</v>
+        <v>5.5486626625061</v>
       </c>
       <c r="H811" t="n">
         <v>1520</v>
@@ -23946,7 +23946,7 @@
         <v>5.8600001335144</v>
       </c>
       <c r="G813" t="n">
-        <v>5.24438095092773</v>
+        <v>5.24438142776489</v>
       </c>
       <c r="H813" t="n">
         <v>595</v>
@@ -23975,7 +23975,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G814" t="n">
-        <v>5.13698720932007</v>
+        <v>5.13698768615723</v>
       </c>
       <c r="H814" t="n">
         <v>33740</v>
@@ -24004,7 +24004,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G815" t="n">
-        <v>5.13698720932007</v>
+        <v>5.13698768615723</v>
       </c>
       <c r="H815" t="n">
         <v>0</v>
@@ -24033,7 +24033,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G816" t="n">
-        <v>5.3517746925354</v>
+        <v>5.35177421569824</v>
       </c>
       <c r="H816" t="n">
         <v>30550</v>
@@ -24062,7 +24062,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G817" t="n">
-        <v>4.83270597457886</v>
+        <v>4.83270645141602</v>
       </c>
       <c r="H817" t="n">
         <v>29376</v>
@@ -24178,7 +24178,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G821" t="n">
-        <v>4.83270597457886</v>
+        <v>4.83270645141602</v>
       </c>
       <c r="H821" t="n">
         <v>677</v>
@@ -24236,7 +24236,7 @@
         <v>6</v>
       </c>
       <c r="G823" t="n">
-        <v>5.36967325210571</v>
+        <v>5.36967372894287</v>
       </c>
       <c r="H823" t="n">
         <v>1900</v>
@@ -24265,7 +24265,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G824" t="n">
-        <v>5.47706651687622</v>
+        <v>5.47706699371338</v>
       </c>
       <c r="H824" t="n">
         <v>100</v>
@@ -24323,7 +24323,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G826" t="n">
-        <v>5.54866218566895</v>
+        <v>5.5486626625061</v>
       </c>
       <c r="H826" t="n">
         <v>610</v>
@@ -24352,7 +24352,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G827" t="n">
-        <v>5.54866218566895</v>
+        <v>5.5486626625061</v>
       </c>
       <c r="H827" t="n">
         <v>0</v>
@@ -24381,7 +24381,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G828" t="n">
-        <v>5.54866218566895</v>
+        <v>5.5486626625061</v>
       </c>
       <c r="H828" t="n">
         <v>600</v>
@@ -24410,7 +24410,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G829" t="n">
-        <v>5.54866218566895</v>
+        <v>5.5486626625061</v>
       </c>
       <c r="H829" t="n">
         <v>0</v>
@@ -24439,7 +24439,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G830" t="n">
-        <v>5.72765159606934</v>
+        <v>5.72765207290649</v>
       </c>
       <c r="H830" t="n">
         <v>1323</v>
@@ -24497,7 +24497,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G832" t="n">
-        <v>5.72765159606934</v>
+        <v>5.72765207290649</v>
       </c>
       <c r="H832" t="n">
         <v>420</v>
@@ -24700,7 +24700,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G839" t="n">
-        <v>5.54866218566895</v>
+        <v>5.5486626625061</v>
       </c>
       <c r="H839" t="n">
         <v>400</v>
@@ -24729,7 +24729,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G840" t="n">
-        <v>5.53076362609863</v>
+        <v>5.53076314926147</v>
       </c>
       <c r="H840" t="n">
         <v>422</v>
@@ -24903,7 +24903,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G846" t="n">
-        <v>5.72765159606934</v>
+        <v>5.72765207290649</v>
       </c>
       <c r="H846" t="n">
         <v>100</v>
@@ -24961,7 +24961,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G848" t="n">
-        <v>5.72765159606934</v>
+        <v>5.72765207290649</v>
       </c>
       <c r="H848" t="n">
         <v>1038</v>
@@ -25048,7 +25048,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G851" t="n">
-        <v>5.70975303649902</v>
+        <v>5.70975255966187</v>
       </c>
       <c r="H851" t="n">
         <v>961</v>
@@ -25077,7 +25077,7 @@
         <v>6.5</v>
       </c>
       <c r="G852" t="n">
-        <v>5.81714582443237</v>
+        <v>5.81714630126953</v>
       </c>
       <c r="H852" t="n">
         <v>263</v>
@@ -25106,7 +25106,7 @@
         <v>6.5</v>
       </c>
       <c r="G853" t="n">
-        <v>5.81714582443237</v>
+        <v>5.81714630126953</v>
       </c>
       <c r="H853" t="n">
         <v>1153</v>
@@ -25193,7 +25193,7 @@
         <v>6.42000007629395</v>
       </c>
       <c r="G856" t="n">
-        <v>5.74555110931396</v>
+        <v>5.74555063247681</v>
       </c>
       <c r="H856" t="n">
         <v>396</v>
@@ -25222,7 +25222,7 @@
         <v>6.51999998092651</v>
       </c>
       <c r="G857" t="n">
-        <v>5.835045337677</v>
+        <v>5.83504486083984</v>
       </c>
       <c r="H857" t="n">
         <v>100</v>
@@ -25251,7 +25251,7 @@
         <v>6.51999998092651</v>
       </c>
       <c r="G858" t="n">
-        <v>5.835045337677</v>
+        <v>5.83504486083984</v>
       </c>
       <c r="H858" t="n">
         <v>0</v>
@@ -25280,7 +25280,7 @@
         <v>6.51999998092651</v>
       </c>
       <c r="G859" t="n">
-        <v>5.835045337677</v>
+        <v>5.83504486083984</v>
       </c>
       <c r="H859" t="n">
         <v>0</v>
@@ -25396,7 +25396,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G863" t="n">
-        <v>5.8887414932251</v>
+        <v>5.88874197006226</v>
       </c>
       <c r="H863" t="n">
         <v>1364</v>
@@ -25454,7 +25454,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G865" t="n">
-        <v>5.8887414932251</v>
+        <v>5.88874197006226</v>
       </c>
       <c r="H865" t="n">
         <v>1988</v>
@@ -25541,7 +25541,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G868" t="n">
-        <v>6.08563041687012</v>
+        <v>6.08562994003296</v>
       </c>
       <c r="H868" t="n">
         <v>500</v>
@@ -25570,7 +25570,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G869" t="n">
-        <v>6.08563041687012</v>
+        <v>6.08562994003296</v>
       </c>
       <c r="H869" t="n">
         <v>0</v>
@@ -25860,7 +25860,7 @@
         <v>6.5</v>
       </c>
       <c r="G879" t="n">
-        <v>5.81714582443237</v>
+        <v>5.81714630126953</v>
       </c>
       <c r="H879" t="n">
         <v>314</v>
@@ -25918,7 +25918,7 @@
         <v>6.73999977111816</v>
       </c>
       <c r="G881" t="n">
-        <v>6.03193283081055</v>
+        <v>6.03193330764771</v>
       </c>
       <c r="H881" t="n">
         <v>400</v>
@@ -25976,7 +25976,7 @@
         <v>6.71999979019165</v>
       </c>
       <c r="G883" t="n">
-        <v>6.01403427124023</v>
+        <v>6.01403379440308</v>
       </c>
       <c r="H883" t="n">
         <v>200</v>
@@ -26005,7 +26005,7 @@
         <v>6.71999979019165</v>
       </c>
       <c r="G884" t="n">
-        <v>6.01403427124023</v>
+        <v>6.01403379440308</v>
       </c>
       <c r="H884" t="n">
         <v>0</v>
@@ -26150,7 +26150,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G889" t="n">
-        <v>5.72765159606934</v>
+        <v>5.72765207290649</v>
       </c>
       <c r="H889" t="n">
         <v>1703</v>
@@ -26179,7 +26179,7 @@
         <v>6.5</v>
       </c>
       <c r="G890" t="n">
-        <v>5.81714582443237</v>
+        <v>5.81714630126953</v>
       </c>
       <c r="H890" t="n">
         <v>662</v>
@@ -26208,7 +26208,7 @@
         <v>6.71999979019165</v>
       </c>
       <c r="G891" t="n">
-        <v>6.01403427124023</v>
+        <v>6.01403379440308</v>
       </c>
       <c r="H891" t="n">
         <v>155</v>
@@ -26237,7 +26237,7 @@
         <v>6.71999979019165</v>
       </c>
       <c r="G892" t="n">
-        <v>6.01403427124023</v>
+        <v>6.01403379440308</v>
       </c>
       <c r="H892" t="n">
         <v>0</v>
@@ -26266,7 +26266,7 @@
         <v>6.71999979019165</v>
       </c>
       <c r="G893" t="n">
-        <v>6.01403427124023</v>
+        <v>6.01403379440308</v>
       </c>
       <c r="H893" t="n">
         <v>0</v>
@@ -26556,7 +26556,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G903" t="n">
-        <v>6.9805760383606</v>
+        <v>6.98057556152344</v>
       </c>
       <c r="H903" t="n">
         <v>2180</v>
@@ -26614,7 +26614,7 @@
         <v>7.57999992370605</v>
       </c>
       <c r="G905" t="n">
-        <v>6.78368711471558</v>
+        <v>6.78368759155273</v>
       </c>
       <c r="H905" t="n">
         <v>2196</v>
@@ -26701,7 +26701,7 @@
         <v>7.03999996185303</v>
       </c>
       <c r="G908" t="n">
-        <v>6.30041646957397</v>
+        <v>6.30041694641113</v>
       </c>
       <c r="H908" t="n">
         <v>5650</v>
@@ -26759,7 +26759,7 @@
         <v>7.1399998664856</v>
       </c>
       <c r="G910" t="n">
-        <v>6.38991165161133</v>
+        <v>6.38991117477417</v>
       </c>
       <c r="H910" t="n">
         <v>1158</v>
@@ -26962,7 +26962,7 @@
         <v>7.26000022888184</v>
       </c>
       <c r="G917" t="n">
-        <v>6.49730539321899</v>
+        <v>6.49730491638184</v>
       </c>
       <c r="H917" t="n">
         <v>3000</v>
@@ -26991,7 +26991,7 @@
         <v>7.42000007629395</v>
       </c>
       <c r="G918" t="n">
-        <v>6.64049625396729</v>
+        <v>6.64049673080444</v>
       </c>
       <c r="H918" t="n">
         <v>2331</v>
@@ -27078,7 +27078,7 @@
         <v>7.34000015258789</v>
       </c>
       <c r="G921" t="n">
-        <v>6.56890106201172</v>
+        <v>6.56890058517456</v>
       </c>
       <c r="H921" t="n">
         <v>250</v>
@@ -27136,7 +27136,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G923" t="n">
-        <v>6.80158662796021</v>
+        <v>6.80158615112305</v>
       </c>
       <c r="H923" t="n">
         <v>2203</v>
@@ -27397,7 +27397,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G932" t="n">
-        <v>6.80158662796021</v>
+        <v>6.80158615112305</v>
       </c>
       <c r="H932" t="n">
         <v>2264</v>
@@ -27455,7 +27455,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G934" t="n">
-        <v>6.80158662796021</v>
+        <v>6.80158615112305</v>
       </c>
       <c r="H934" t="n">
         <v>1250</v>
@@ -27513,7 +27513,7 @@
         <v>7.34000015258789</v>
       </c>
       <c r="G936" t="n">
-        <v>6.56890106201172</v>
+        <v>6.56890058517456</v>
       </c>
       <c r="H936" t="n">
         <v>75</v>
@@ -27687,7 +27687,7 @@
         <v>7.26000022888184</v>
       </c>
       <c r="G942" t="n">
-        <v>6.49730539321899</v>
+        <v>6.49730491638184</v>
       </c>
       <c r="H942" t="n">
         <v>4218</v>
@@ -27716,7 +27716,7 @@
         <v>7.26000022888184</v>
       </c>
       <c r="G943" t="n">
-        <v>6.49730539321899</v>
+        <v>6.49730491638184</v>
       </c>
       <c r="H943" t="n">
         <v>0</v>
@@ -27745,7 +27745,7 @@
         <v>7.26000022888184</v>
       </c>
       <c r="G944" t="n">
-        <v>6.49730539321899</v>
+        <v>6.49730491638184</v>
       </c>
       <c r="H944" t="n">
         <v>0</v>
@@ -27803,7 +27803,7 @@
         <v>7.21999979019165</v>
       </c>
       <c r="G946" t="n">
-        <v>6.46150684356689</v>
+        <v>6.46150732040405</v>
       </c>
       <c r="H946" t="n">
         <v>103974</v>
@@ -27832,7 +27832,7 @@
         <v>7.21999979019165</v>
       </c>
       <c r="G947" t="n">
-        <v>6.46150684356689</v>
+        <v>6.46150732040405</v>
       </c>
       <c r="H947" t="n">
         <v>574</v>
@@ -28238,7 +28238,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G961" t="n">
-        <v>6.08563041687012</v>
+        <v>6.08562994003296</v>
       </c>
       <c r="H961" t="n">
         <v>1113</v>
@@ -28557,7 +28557,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G972" t="n">
-        <v>6.08563041687012</v>
+        <v>6.08562994003296</v>
       </c>
       <c r="H972" t="n">
         <v>250</v>
@@ -30065,7 +30065,7 @@
         <v>7.25</v>
       </c>
       <c r="G1024" t="n">
-        <v>6.48835515975952</v>
+        <v>6.48835563659668</v>
       </c>
       <c r="H1024" t="n">
         <v>712</v>
@@ -30181,7 +30181,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G1028" t="n">
-        <v>6.8463339805603</v>
+        <v>6.84633350372314</v>
       </c>
       <c r="H1028" t="n">
         <v>12728</v>
@@ -30210,7 +30210,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G1029" t="n">
-        <v>6.9805760383606</v>
+        <v>6.98057556152344</v>
       </c>
       <c r="H1029" t="n">
         <v>238</v>
@@ -30239,7 +30239,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G1030" t="n">
-        <v>6.9805760383606</v>
+        <v>6.98057556152344</v>
       </c>
       <c r="H1030" t="n">
         <v>1</v>
@@ -30268,7 +30268,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G1031" t="n">
-        <v>6.9805760383606</v>
+        <v>6.98057556152344</v>
       </c>
       <c r="H1031" t="n">
         <v>100</v>
@@ -30326,7 +30326,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G1033" t="n">
-        <v>6.75683975219727</v>
+        <v>6.75683927536011</v>
       </c>
       <c r="H1033" t="n">
         <v>670</v>
@@ -30355,7 +30355,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G1034" t="n">
-        <v>6.75683975219727</v>
+        <v>6.75683927536011</v>
       </c>
       <c r="H1034" t="n">
         <v>0</v>
@@ -30384,7 +30384,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G1035" t="n">
-        <v>6.75683975219727</v>
+        <v>6.75683927536011</v>
       </c>
       <c r="H1035" t="n">
         <v>0</v>
@@ -30413,7 +30413,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G1036" t="n">
-        <v>6.75683975219727</v>
+        <v>6.75683927536011</v>
       </c>
       <c r="H1036" t="n">
         <v>0</v>
@@ -30442,7 +30442,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G1037" t="n">
-        <v>6.9805760383606</v>
+        <v>6.98057556152344</v>
       </c>
       <c r="H1037" t="n">
         <v>500</v>
@@ -30471,7 +30471,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G1038" t="n">
-        <v>6.80158662796021</v>
+        <v>6.80158615112305</v>
       </c>
       <c r="H1038" t="n">
         <v>730</v>
@@ -30500,7 +30500,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G1039" t="n">
-        <v>6.80158662796021</v>
+        <v>6.80158615112305</v>
       </c>
       <c r="H1039" t="n">
         <v>0</v>
@@ -30558,7 +30558,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G1041" t="n">
-        <v>6.80158662796021</v>
+        <v>6.80158615112305</v>
       </c>
       <c r="H1041" t="n">
         <v>13</v>
@@ -30587,7 +30587,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G1042" t="n">
-        <v>6.80158662796021</v>
+        <v>6.80158615112305</v>
       </c>
       <c r="H1042" t="n">
         <v>0</v>
@@ -30616,7 +30616,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G1043" t="n">
-        <v>6.80158662796021</v>
+        <v>6.80158615112305</v>
       </c>
       <c r="H1043" t="n">
         <v>0</v>
@@ -30645,7 +30645,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G1044" t="n">
-        <v>6.80158662796021</v>
+        <v>6.80158615112305</v>
       </c>
       <c r="H1044" t="n">
         <v>0</v>
@@ -30674,7 +30674,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G1045" t="n">
-        <v>6.80158662796021</v>
+        <v>6.80158615112305</v>
       </c>
       <c r="H1045" t="n">
         <v>0</v>
@@ -30703,7 +30703,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G1046" t="n">
-        <v>6.80158662796021</v>
+        <v>6.80158615112305</v>
       </c>
       <c r="H1046" t="n">
         <v>0</v>
@@ -30732,7 +30732,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G1047" t="n">
-        <v>6.80158662796021</v>
+        <v>6.80158615112305</v>
       </c>
       <c r="H1047" t="n">
         <v>0</v>
@@ -30761,7 +30761,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G1048" t="n">
-        <v>6.9805760383606</v>
+        <v>6.98057556152344</v>
       </c>
       <c r="H1048" t="n">
         <v>601</v>
@@ -30790,7 +30790,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G1049" t="n">
-        <v>6.8463339805603</v>
+        <v>6.84633350372314</v>
       </c>
       <c r="H1049" t="n">
         <v>100</v>
@@ -30819,7 +30819,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G1050" t="n">
-        <v>6.9805760383606</v>
+        <v>6.98057556152344</v>
       </c>
       <c r="H1050" t="n">
         <v>460</v>
@@ -30848,7 +30848,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G1051" t="n">
-        <v>6.9805760383606</v>
+        <v>6.98057556152344</v>
       </c>
       <c r="H1051" t="n">
         <v>125</v>
@@ -30877,7 +30877,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G1052" t="n">
-        <v>6.9805760383606</v>
+        <v>6.98057556152344</v>
       </c>
       <c r="H1052" t="n">
         <v>0</v>
@@ -30906,7 +30906,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G1053" t="n">
-        <v>6.80158662796021</v>
+        <v>6.80158615112305</v>
       </c>
       <c r="H1053" t="n">
         <v>1684</v>
@@ -31080,7 +31080,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G1059" t="n">
-        <v>6.75683975219727</v>
+        <v>6.75683927536011</v>
       </c>
       <c r="H1059" t="n">
         <v>400</v>
@@ -31109,7 +31109,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G1060" t="n">
-        <v>6.75683975219727</v>
+        <v>6.75683927536011</v>
       </c>
       <c r="H1060" t="n">
         <v>0</v>
@@ -31138,7 +31138,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G1061" t="n">
-        <v>6.75683975219727</v>
+        <v>6.75683927536011</v>
       </c>
       <c r="H1061" t="n">
         <v>0</v>
@@ -31602,7 +31602,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G1077" t="n">
-        <v>5.86189413070679</v>
+        <v>5.86189365386963</v>
       </c>
       <c r="H1077" t="n">
         <v>846</v>
@@ -31631,7 +31631,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G1078" t="n">
-        <v>5.72765159606934</v>
+        <v>5.72765207290649</v>
       </c>
       <c r="H1078" t="n">
         <v>2019</v>
@@ -31660,7 +31660,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G1079" t="n">
-        <v>5.86189413070679</v>
+        <v>5.86189365386963</v>
       </c>
       <c r="H1079" t="n">
         <v>100</v>
@@ -31747,7 +31747,7 @@
         <v>6</v>
       </c>
       <c r="G1082" t="n">
-        <v>5.36967325210571</v>
+        <v>5.36967372894287</v>
       </c>
       <c r="H1082" t="n">
         <v>11354</v>
@@ -31776,7 +31776,7 @@
         <v>6</v>
       </c>
       <c r="G1083" t="n">
-        <v>5.36967325210571</v>
+        <v>5.36967372894287</v>
       </c>
       <c r="H1083" t="n">
         <v>25500</v>
@@ -31805,7 +31805,7 @@
         <v>6</v>
       </c>
       <c r="G1084" t="n">
-        <v>5.36967325210571</v>
+        <v>5.36967372894287</v>
       </c>
       <c r="H1084" t="n">
         <v>0</v>
@@ -31863,7 +31863,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G1086" t="n">
-        <v>5.32492589950562</v>
+        <v>5.32492637634277</v>
       </c>
       <c r="H1086" t="n">
         <v>6465</v>
@@ -31892,7 +31892,7 @@
         <v>6</v>
       </c>
       <c r="G1087" t="n">
-        <v>5.36967325210571</v>
+        <v>5.36967372894287</v>
       </c>
       <c r="H1087" t="n">
         <v>6931</v>
@@ -31921,7 +31921,7 @@
         <v>6</v>
       </c>
       <c r="G1088" t="n">
-        <v>5.36967325210571</v>
+        <v>5.36967372894287</v>
       </c>
       <c r="H1088" t="n">
         <v>0</v>
@@ -31950,7 +31950,7 @@
         <v>6</v>
       </c>
       <c r="G1089" t="n">
-        <v>5.36967325210571</v>
+        <v>5.36967372894287</v>
       </c>
       <c r="H1089" t="n">
         <v>0</v>
@@ -31979,7 +31979,7 @@
         <v>6</v>
       </c>
       <c r="G1090" t="n">
-        <v>5.36967325210571</v>
+        <v>5.36967372894287</v>
       </c>
       <c r="H1090" t="n">
         <v>850</v>
@@ -32008,7 +32008,7 @@
         <v>6</v>
       </c>
       <c r="G1091" t="n">
-        <v>5.36967325210571</v>
+        <v>5.36967372894287</v>
       </c>
       <c r="H1091" t="n">
         <v>240</v>
@@ -32037,7 +32037,7 @@
         <v>6</v>
       </c>
       <c r="G1092" t="n">
-        <v>5.36967325210571</v>
+        <v>5.36967372894287</v>
       </c>
       <c r="H1092" t="n">
         <v>650</v>
@@ -32066,7 +32066,7 @@
         <v>6</v>
       </c>
       <c r="G1093" t="n">
-        <v>5.36967325210571</v>
+        <v>5.36967372894287</v>
       </c>
       <c r="H1093" t="n">
         <v>675</v>
@@ -32095,7 +32095,7 @@
         <v>6</v>
       </c>
       <c r="G1094" t="n">
-        <v>5.36967325210571</v>
+        <v>5.36967372894287</v>
       </c>
       <c r="H1094" t="n">
         <v>0</v>
@@ -32124,7 +32124,7 @@
         <v>6</v>
       </c>
       <c r="G1095" t="n">
-        <v>5.36967325210571</v>
+        <v>5.36967372894287</v>
       </c>
       <c r="H1095" t="n">
         <v>0</v>
@@ -32414,7 +32414,7 @@
         <v>6.25</v>
       </c>
       <c r="G1105" t="n">
-        <v>5.59340953826904</v>
+        <v>5.5934100151062</v>
       </c>
       <c r="H1105" t="n">
         <v>14260</v>
@@ -32443,7 +32443,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G1106" t="n">
-        <v>5.54866218566895</v>
+        <v>5.5486626625061</v>
       </c>
       <c r="H1106" t="n">
         <v>39658</v>
@@ -32559,7 +32559,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G1110" t="n">
-        <v>5.54866218566895</v>
+        <v>5.5486626625061</v>
       </c>
       <c r="H1110" t="n">
         <v>21380</v>
@@ -32617,7 +32617,7 @@
         <v>6.5</v>
       </c>
       <c r="G1112" t="n">
-        <v>5.81714582443237</v>
+        <v>5.81714630126953</v>
       </c>
       <c r="H1112" t="n">
         <v>29853</v>
@@ -32646,7 +32646,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G1113" t="n">
-        <v>5.72765159606934</v>
+        <v>5.72765207290649</v>
       </c>
       <c r="H1113" t="n">
         <v>31724</v>
@@ -32675,7 +32675,7 @@
         <v>6.5</v>
       </c>
       <c r="G1114" t="n">
-        <v>5.81714582443237</v>
+        <v>5.81714630126953</v>
       </c>
       <c r="H1114" t="n">
         <v>15604</v>
@@ -32791,7 +32791,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G1118" t="n">
-        <v>6.08563041687012</v>
+        <v>6.08562994003296</v>
       </c>
       <c r="H1118" t="n">
         <v>46505</v>
@@ -32965,7 +32965,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G1124" t="n">
-        <v>6.75683975219727</v>
+        <v>6.75683927536011</v>
       </c>
       <c r="H1124" t="n">
         <v>52998</v>
@@ -53880,6 +53880,64 @@
         <v>1466</v>
       </c>
       <c r="I1845" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1846">
+      <c r="A1846" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1846" s="1" t="n">
+        <v>46314.2916666667</v>
+      </c>
+      <c r="C1846" t="n">
+        <v>2.38000011444092</v>
+      </c>
+      <c r="D1846" t="n">
+        <v>2.38000011444092</v>
+      </c>
+      <c r="E1846" t="n">
+        <v>2.33999991416931</v>
+      </c>
+      <c r="F1846" t="n">
+        <v>2.33999991416931</v>
+      </c>
+      <c r="G1846" t="n">
+        <v>2.33999991416931</v>
+      </c>
+      <c r="H1846" t="n">
+        <v>3711</v>
+      </c>
+      <c r="I1846" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1847">
+      <c r="A1847" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1847" s="1" t="n">
+        <v>46315.2916666667</v>
+      </c>
+      <c r="C1847" t="n">
+        <v>2.3199999332428</v>
+      </c>
+      <c r="D1847" t="n">
+        <v>2.35999989509583</v>
+      </c>
+      <c r="E1847" t="n">
+        <v>2.29999995231628</v>
+      </c>
+      <c r="F1847" t="n">
+        <v>2.29999995231628</v>
+      </c>
+      <c r="G1847" t="n">
+        <v>2.29999995231628</v>
+      </c>
+      <c r="H1847" t="n">
+        <v>13955</v>
+      </c>
+      <c r="I1847" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/PTR.MI.xlsx
+++ b/data/PTR.MI.xlsx
@@ -427,7 +427,7 @@
         <v>3.75</v>
       </c>
       <c r="G2" t="n">
-        <v>3.2548463344574</v>
+        <v>3.25484609603882</v>
       </c>
       <c r="H2" t="n">
         <v>859316</v>
@@ -485,7 +485,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G4" t="n">
-        <v>3.22012829780579</v>
+        <v>3.22012805938721</v>
       </c>
       <c r="H4" t="n">
         <v>98299</v>
@@ -543,7 +543,7 @@
         <v>3.69250011444092</v>
       </c>
       <c r="G6" t="n">
-        <v>3.2049388885498</v>
+        <v>3.20493865013123</v>
       </c>
       <c r="H6" t="n">
         <v>56036</v>
@@ -630,7 +630,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G9" t="n">
-        <v>3.05521583557129</v>
+        <v>3.05521559715271</v>
       </c>
       <c r="H9" t="n">
         <v>21800</v>
@@ -688,7 +688,7 @@
         <v>3.47849988937378</v>
       </c>
       <c r="G11" t="n">
-        <v>3.01919531822205</v>
+        <v>3.01919555664062</v>
       </c>
       <c r="H11" t="n">
         <v>324435</v>
@@ -746,7 +746,7 @@
         <v>3.59400010108948</v>
       </c>
       <c r="G13" t="n">
-        <v>3.11944484710693</v>
+        <v>3.11944460868835</v>
       </c>
       <c r="H13" t="n">
         <v>13465</v>
@@ -1065,7 +1065,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G24" t="n">
-        <v>3.05521583557129</v>
+        <v>3.05521559715271</v>
       </c>
       <c r="H24" t="n">
         <v>72</v>
@@ -1094,7 +1094,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G25" t="n">
-        <v>3.05521583557129</v>
+        <v>3.05521559715271</v>
       </c>
       <c r="H25" t="n">
         <v>520</v>
@@ -1384,7 +1384,7 @@
         <v>3.5</v>
       </c>
       <c r="G35" t="n">
-        <v>3.0378565788269</v>
+        <v>3.03785634040833</v>
       </c>
       <c r="H35" t="n">
         <v>1400</v>
@@ -1616,7 +1616,7 @@
         <v>3.82500004768372</v>
       </c>
       <c r="G43" t="n">
-        <v>3.31994295120239</v>
+        <v>3.31994318962097</v>
       </c>
       <c r="H43" t="n">
         <v>5962</v>
@@ -1645,7 +1645,7 @@
         <v>3.67499995231628</v>
       </c>
       <c r="G44" t="n">
-        <v>3.18974924087524</v>
+        <v>3.18974947929382</v>
       </c>
       <c r="H44" t="n">
         <v>9040</v>
@@ -1703,7 +1703,7 @@
         <v>3.71499991416931</v>
       </c>
       <c r="G46" t="n">
-        <v>3.22446751594543</v>
+        <v>3.22446775436401</v>
       </c>
       <c r="H46" t="n">
         <v>3406</v>
@@ -1761,7 +1761,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G48" t="n">
-        <v>3.15069127082825</v>
+        <v>3.15069103240967</v>
       </c>
       <c r="H48" t="n">
         <v>190</v>
@@ -1819,7 +1819,7 @@
         <v>3.71499991416931</v>
       </c>
       <c r="G50" t="n">
-        <v>3.22446751594543</v>
+        <v>3.22446775436401</v>
       </c>
       <c r="H50" t="n">
         <v>7667</v>
@@ -1848,7 +1848,7 @@
         <v>3.75</v>
       </c>
       <c r="G51" t="n">
-        <v>3.2548463344574</v>
+        <v>3.25484609603882</v>
       </c>
       <c r="H51" t="n">
         <v>37160</v>
@@ -1993,7 +1993,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G56" t="n">
-        <v>3.15069127082825</v>
+        <v>3.15069103240967</v>
       </c>
       <c r="H56" t="n">
         <v>6760</v>
@@ -2022,7 +2022,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G57" t="n">
-        <v>3.15069127082825</v>
+        <v>3.15069103240967</v>
       </c>
       <c r="H57" t="n">
         <v>100</v>
@@ -2109,7 +2109,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G60" t="n">
-        <v>3.05521583557129</v>
+        <v>3.05521559715271</v>
       </c>
       <c r="H60" t="n">
         <v>1420</v>
@@ -2225,7 +2225,7 @@
         <v>3.5550000667572</v>
       </c>
       <c r="G64" t="n">
-        <v>3.08559393882751</v>
+        <v>3.08559417724609</v>
       </c>
       <c r="H64" t="n">
         <v>550</v>
@@ -2254,7 +2254,7 @@
         <v>3.5550000667572</v>
       </c>
       <c r="G65" t="n">
-        <v>3.08559393882751</v>
+        <v>3.08559417724609</v>
       </c>
       <c r="H65" t="n">
         <v>2547</v>
@@ -2689,7 +2689,7 @@
         <v>3.67499995231628</v>
       </c>
       <c r="G80" t="n">
-        <v>3.18974924087524</v>
+        <v>3.18974947929382</v>
       </c>
       <c r="H80" t="n">
         <v>6929</v>
@@ -2718,7 +2718,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G81" t="n">
-        <v>3.15937089920044</v>
+        <v>3.15937066078186</v>
       </c>
       <c r="H81" t="n">
         <v>4191</v>
@@ -3037,7 +3037,7 @@
         <v>4</v>
       </c>
       <c r="G92" t="n">
-        <v>3.47183609008789</v>
+        <v>3.47183585166931</v>
       </c>
       <c r="H92" t="n">
         <v>9228</v>
@@ -3153,7 +3153,7 @@
         <v>4.02500009536743</v>
       </c>
       <c r="G96" t="n">
-        <v>3.4935348033905</v>
+        <v>3.49353504180908</v>
       </c>
       <c r="H96" t="n">
         <v>1493</v>
@@ -3356,7 +3356,7 @@
         <v>4</v>
       </c>
       <c r="G103" t="n">
-        <v>3.47183609008789</v>
+        <v>3.47183585166931</v>
       </c>
       <c r="H103" t="n">
         <v>11798</v>
@@ -3385,7 +3385,7 @@
         <v>3.9449999332428</v>
       </c>
       <c r="G104" t="n">
-        <v>3.42409801483154</v>
+        <v>3.42409825325012</v>
       </c>
       <c r="H104" t="n">
         <v>26075</v>
@@ -3414,7 +3414,7 @@
         <v>4</v>
       </c>
       <c r="G105" t="n">
-        <v>3.47183609008789</v>
+        <v>3.47183585166931</v>
       </c>
       <c r="H105" t="n">
         <v>5886</v>
@@ -3443,7 +3443,7 @@
         <v>4.03499984741211</v>
       </c>
       <c r="G106" t="n">
-        <v>3.5022144317627</v>
+        <v>3.50221467018127</v>
       </c>
       <c r="H106" t="n">
         <v>9593</v>
@@ -3617,7 +3617,7 @@
         <v>4.41499996185303</v>
       </c>
       <c r="G112" t="n">
-        <v>3.83203887939453</v>
+        <v>3.83203864097595</v>
       </c>
       <c r="H112" t="n">
         <v>30401</v>
@@ -3646,7 +3646,7 @@
         <v>4.5</v>
       </c>
       <c r="G113" t="n">
-        <v>3.9058153629303</v>
+        <v>3.90581560134888</v>
       </c>
       <c r="H113" t="n">
         <v>10114</v>
@@ -3675,7 +3675,7 @@
         <v>4.5</v>
       </c>
       <c r="G114" t="n">
-        <v>3.9058153629303</v>
+        <v>3.90581560134888</v>
       </c>
       <c r="H114" t="n">
         <v>36925</v>
@@ -3791,7 +3791,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G118" t="n">
-        <v>4.03600978851318</v>
+        <v>4.03600931167603</v>
       </c>
       <c r="H118" t="n">
         <v>50</v>
@@ -3820,7 +3820,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G119" t="n">
-        <v>3.96657299995422</v>
+        <v>3.96657252311707</v>
       </c>
       <c r="H119" t="n">
         <v>7065</v>
@@ -3907,7 +3907,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G122" t="n">
-        <v>3.94053363800049</v>
+        <v>3.94053339958191</v>
       </c>
       <c r="H122" t="n">
         <v>5398</v>
@@ -3965,7 +3965,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G124" t="n">
-        <v>3.94921350479126</v>
+        <v>3.94921374320984</v>
       </c>
       <c r="H124" t="n">
         <v>5841</v>
@@ -3994,7 +3994,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G125" t="n">
-        <v>3.94921350479126</v>
+        <v>3.94921374320984</v>
       </c>
       <c r="H125" t="n">
         <v>21549</v>
@@ -4023,7 +4023,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G126" t="n">
-        <v>4.03600978851318</v>
+        <v>4.03600931167603</v>
       </c>
       <c r="H126" t="n">
         <v>9991</v>
@@ -4255,7 +4255,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G134" t="n">
-        <v>4.24431943893433</v>
+        <v>4.24431896209717</v>
       </c>
       <c r="H134" t="n">
         <v>9475</v>
@@ -4284,7 +4284,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G135" t="n">
-        <v>4.24431943893433</v>
+        <v>4.24431896209717</v>
       </c>
       <c r="H135" t="n">
         <v>1852</v>
@@ -4342,7 +4342,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G137" t="n">
-        <v>4.14016437530518</v>
+        <v>4.14016389846802</v>
       </c>
       <c r="H137" t="n">
         <v>18698</v>
@@ -4429,7 +4429,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G140" t="n">
-        <v>4.51338672637939</v>
+        <v>4.51338720321655</v>
       </c>
       <c r="H140" t="n">
         <v>12739</v>
@@ -4574,7 +4574,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G145" t="n">
-        <v>4.51338672637939</v>
+        <v>4.51338720321655</v>
       </c>
       <c r="H145" t="n">
         <v>10888</v>
@@ -4603,7 +4603,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G146" t="n">
-        <v>4.54810476303101</v>
+        <v>4.54810523986816</v>
       </c>
       <c r="H146" t="n">
         <v>8672</v>
@@ -4632,7 +4632,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G147" t="n">
-        <v>4.70433759689331</v>
+        <v>4.70433807373047</v>
       </c>
       <c r="H147" t="n">
         <v>15539</v>
@@ -4690,7 +4690,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G149" t="n">
-        <v>4.54810476303101</v>
+        <v>4.54810523986816</v>
       </c>
       <c r="H149" t="n">
         <v>20634</v>
@@ -4719,7 +4719,7 @@
         <v>5.13000011444092</v>
       </c>
       <c r="G150" t="n">
-        <v>4.45263051986694</v>
+        <v>4.45263004302979</v>
       </c>
       <c r="H150" t="n">
         <v>6278</v>
@@ -4748,7 +4748,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G151" t="n">
-        <v>4.54810476303101</v>
+        <v>4.54810523986816</v>
       </c>
       <c r="H151" t="n">
         <v>3706</v>
@@ -4777,7 +4777,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G152" t="n">
-        <v>4.51338672637939</v>
+        <v>4.51338720321655</v>
       </c>
       <c r="H152" t="n">
         <v>12525</v>
@@ -4835,7 +4835,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G154" t="n">
-        <v>4.00129175186157</v>
+        <v>4.00129127502441</v>
       </c>
       <c r="H154" t="n">
         <v>9345</v>
@@ -4951,7 +4951,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G158" t="n">
-        <v>4.00129175186157</v>
+        <v>4.00129127502441</v>
       </c>
       <c r="H158" t="n">
         <v>25178</v>
@@ -5096,7 +5096,7 @@
         <v>4.24499988555908</v>
       </c>
       <c r="G163" t="n">
-        <v>3.684485912323</v>
+        <v>3.68448567390442</v>
       </c>
       <c r="H163" t="n">
         <v>8681</v>
@@ -5183,7 +5183,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G166" t="n">
-        <v>3.23748707771301</v>
+        <v>3.23748683929443</v>
       </c>
       <c r="H166" t="n">
         <v>4220</v>
@@ -5763,7 +5763,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G186" t="n">
-        <v>3.22012829780579</v>
+        <v>3.22012805938721</v>
       </c>
       <c r="H186" t="n">
         <v>4810</v>
@@ -5908,7 +5908,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G191" t="n">
-        <v>3.2808849811554</v>
+        <v>3.28088521957397</v>
       </c>
       <c r="H191" t="n">
         <v>15966</v>
@@ -6053,7 +6053,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G196" t="n">
-        <v>3.35900139808655</v>
+        <v>3.35900115966797</v>
       </c>
       <c r="H196" t="n">
         <v>2603</v>
@@ -6082,7 +6082,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G197" t="n">
-        <v>3.35900139808655</v>
+        <v>3.35900115966797</v>
       </c>
       <c r="H197" t="n">
         <v>1540</v>
@@ -6169,7 +6169,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G200" t="n">
-        <v>3.48051571846008</v>
+        <v>3.48051595687866</v>
       </c>
       <c r="H200" t="n">
         <v>8475</v>
@@ -6227,7 +6227,7 @@
         <v>3.75</v>
       </c>
       <c r="G202" t="n">
-        <v>3.2548463344574</v>
+        <v>3.25484609603882</v>
       </c>
       <c r="H202" t="n">
         <v>25406</v>
@@ -6256,7 +6256,7 @@
         <v>3.75</v>
       </c>
       <c r="G203" t="n">
-        <v>3.2548463344574</v>
+        <v>3.25484609603882</v>
       </c>
       <c r="H203" t="n">
         <v>5500</v>
@@ -6575,7 +6575,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G214" t="n">
-        <v>3.2808849811554</v>
+        <v>3.28088521957397</v>
       </c>
       <c r="H214" t="n">
         <v>1000</v>
@@ -6633,7 +6633,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G216" t="n">
-        <v>3.2808849811554</v>
+        <v>3.28088521957397</v>
       </c>
       <c r="H216" t="n">
         <v>5107</v>
@@ -6691,7 +6691,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G218" t="n">
-        <v>3.2808849811554</v>
+        <v>3.28088521957397</v>
       </c>
       <c r="H218" t="n">
         <v>3100</v>
@@ -6865,7 +6865,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G224" t="n">
-        <v>3.38504004478455</v>
+        <v>3.38504028320312</v>
       </c>
       <c r="H224" t="n">
         <v>2943</v>
@@ -6894,7 +6894,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G225" t="n">
-        <v>3.35900139808655</v>
+        <v>3.35900115966797</v>
       </c>
       <c r="H225" t="n">
         <v>7946</v>
@@ -7271,7 +7271,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G238" t="n">
-        <v>3.23748707771301</v>
+        <v>3.23748683929443</v>
       </c>
       <c r="H238" t="n">
         <v>386</v>
@@ -7300,7 +7300,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G239" t="n">
-        <v>3.23748707771301</v>
+        <v>3.23748683929443</v>
       </c>
       <c r="H239" t="n">
         <v>0</v>
@@ -7590,7 +7590,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G249" t="n">
-        <v>3.15937089920044</v>
+        <v>3.15937066078186</v>
       </c>
       <c r="H249" t="n">
         <v>2094</v>
@@ -7822,7 +7822,7 @@
         <v>3.75</v>
       </c>
       <c r="G257" t="n">
-        <v>3.2548463344574</v>
+        <v>3.25484609603882</v>
       </c>
       <c r="H257" t="n">
         <v>3790</v>
@@ -8286,7 +8286,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G273" t="n">
-        <v>3.0204975605011</v>
+        <v>3.02049732208252</v>
       </c>
       <c r="H273" t="n">
         <v>5743</v>
@@ -8315,7 +8315,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G274" t="n">
-        <v>2.93370175361633</v>
+        <v>2.93370151519775</v>
       </c>
       <c r="H274" t="n">
         <v>4510</v>
@@ -8402,7 +8402,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G277" t="n">
-        <v>3.0204975605011</v>
+        <v>3.02049732208252</v>
       </c>
       <c r="H277" t="n">
         <v>10072</v>
@@ -8489,7 +8489,7 @@
         <v>3.5</v>
       </c>
       <c r="G280" t="n">
-        <v>3.0378565788269</v>
+        <v>3.03785634040833</v>
       </c>
       <c r="H280" t="n">
         <v>105</v>
@@ -8518,7 +8518,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G281" t="n">
-        <v>3.06389498710632</v>
+        <v>3.0638952255249</v>
       </c>
       <c r="H281" t="n">
         <v>1883</v>
@@ -8547,7 +8547,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G282" t="n">
-        <v>3.06389498710632</v>
+        <v>3.0638952255249</v>
       </c>
       <c r="H282" t="n">
         <v>0</v>
@@ -8576,7 +8576,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G283" t="n">
-        <v>3.06389498710632</v>
+        <v>3.0638952255249</v>
       </c>
       <c r="H283" t="n">
         <v>1100</v>
@@ -8605,7 +8605,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G284" t="n">
-        <v>2.94238138198853</v>
+        <v>2.94238114356995</v>
       </c>
       <c r="H284" t="n">
         <v>2758</v>
@@ -8634,7 +8634,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G285" t="n">
-        <v>2.94238138198853</v>
+        <v>2.94238114356995</v>
       </c>
       <c r="H285" t="n">
         <v>20</v>
@@ -8692,7 +8692,7 @@
         <v>3.5</v>
       </c>
       <c r="G287" t="n">
-        <v>3.0378565788269</v>
+        <v>3.03785634040833</v>
       </c>
       <c r="H287" t="n">
         <v>3634</v>
@@ -8779,7 +8779,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G290" t="n">
-        <v>3.05521583557129</v>
+        <v>3.05521559715271</v>
       </c>
       <c r="H290" t="n">
         <v>2450</v>
@@ -8808,7 +8808,7 @@
         <v>3.5</v>
       </c>
       <c r="G291" t="n">
-        <v>3.0378565788269</v>
+        <v>3.03785634040833</v>
       </c>
       <c r="H291" t="n">
         <v>10</v>
@@ -8837,7 +8837,7 @@
         <v>3.5</v>
       </c>
       <c r="G292" t="n">
-        <v>3.0378565788269</v>
+        <v>3.03785634040833</v>
       </c>
       <c r="H292" t="n">
         <v>0</v>
@@ -8924,7 +8924,7 @@
         <v>3.5</v>
       </c>
       <c r="G295" t="n">
-        <v>3.0378565788269</v>
+        <v>3.03785634040833</v>
       </c>
       <c r="H295" t="n">
         <v>700</v>
@@ -8953,7 +8953,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G296" t="n">
-        <v>2.95106077194214</v>
+        <v>2.95106053352356</v>
       </c>
       <c r="H296" t="n">
         <v>2886</v>
@@ -8982,7 +8982,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G297" t="n">
-        <v>2.95106077194214</v>
+        <v>2.95106053352356</v>
       </c>
       <c r="H297" t="n">
         <v>599</v>
@@ -9040,7 +9040,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G299" t="n">
-        <v>2.86426472663879</v>
+        <v>2.86426496505737</v>
       </c>
       <c r="H299" t="n">
         <v>18061</v>
@@ -9069,7 +9069,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G300" t="n">
-        <v>2.86426472663879</v>
+        <v>2.86426496505737</v>
       </c>
       <c r="H300" t="n">
         <v>0</v>
@@ -9098,7 +9098,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G301" t="n">
-        <v>2.86426472663879</v>
+        <v>2.86426496505737</v>
       </c>
       <c r="H301" t="n">
         <v>14192</v>
@@ -9156,7 +9156,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G303" t="n">
-        <v>2.88162398338318</v>
+        <v>2.8816237449646</v>
       </c>
       <c r="H303" t="n">
         <v>7318</v>
@@ -9214,7 +9214,7 @@
         <v>3.5</v>
       </c>
       <c r="G305" t="n">
-        <v>3.0378565788269</v>
+        <v>3.03785634040833</v>
       </c>
       <c r="H305" t="n">
         <v>28717</v>
@@ -9388,7 +9388,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G311" t="n">
-        <v>3.22012829780579</v>
+        <v>3.22012805938721</v>
       </c>
       <c r="H311" t="n">
         <v>688</v>
@@ -9417,7 +9417,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G312" t="n">
-        <v>3.22012829780579</v>
+        <v>3.22012805938721</v>
       </c>
       <c r="H312" t="n">
         <v>0</v>
@@ -9533,7 +9533,7 @@
         <v>3.75</v>
       </c>
       <c r="G316" t="n">
-        <v>3.2548463344574</v>
+        <v>3.25484609603882</v>
       </c>
       <c r="H316" t="n">
         <v>2505</v>
@@ -9968,7 +9968,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G331" t="n">
-        <v>3.05521583557129</v>
+        <v>3.05521559715271</v>
       </c>
       <c r="H331" t="n">
         <v>830</v>
@@ -9997,7 +9997,7 @@
         <v>3.5</v>
       </c>
       <c r="G332" t="n">
-        <v>3.0378565788269</v>
+        <v>3.03785634040833</v>
       </c>
       <c r="H332" t="n">
         <v>2958</v>
@@ -10055,7 +10055,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G334" t="n">
-        <v>3.15069127082825</v>
+        <v>3.15069103240967</v>
       </c>
       <c r="H334" t="n">
         <v>1330</v>
@@ -10200,7 +10200,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G339" t="n">
-        <v>3.15937089920044</v>
+        <v>3.15937066078186</v>
       </c>
       <c r="H339" t="n">
         <v>100</v>
@@ -10316,7 +10316,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G343" t="n">
-        <v>3.15069127082825</v>
+        <v>3.15069103240967</v>
       </c>
       <c r="H343" t="n">
         <v>3072</v>
@@ -10345,7 +10345,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G344" t="n">
-        <v>3.15069127082825</v>
+        <v>3.15069103240967</v>
       </c>
       <c r="H344" t="n">
         <v>8220</v>
@@ -10374,7 +10374,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G345" t="n">
-        <v>3.22012829780579</v>
+        <v>3.22012805938721</v>
       </c>
       <c r="H345" t="n">
         <v>3873</v>
@@ -10780,7 +10780,7 @@
         <v>4</v>
       </c>
       <c r="G359" t="n">
-        <v>3.47183609008789</v>
+        <v>3.47183585166931</v>
       </c>
       <c r="H359" t="n">
         <v>3169</v>
@@ -10809,7 +10809,7 @@
         <v>4</v>
       </c>
       <c r="G360" t="n">
-        <v>3.47183609008789</v>
+        <v>3.47183585166931</v>
       </c>
       <c r="H360" t="n">
         <v>12</v>
@@ -10867,7 +10867,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G362" t="n">
-        <v>3.52457284927368</v>
+        <v>3.52457308769226</v>
       </c>
       <c r="H362" t="n">
         <v>1633</v>
@@ -10925,7 +10925,7 @@
         <v>4</v>
       </c>
       <c r="G364" t="n">
-        <v>3.51578330993652</v>
+        <v>3.51578307151794</v>
       </c>
       <c r="H364" t="n">
         <v>16056</v>
@@ -11012,7 +11012,7 @@
         <v>4</v>
       </c>
       <c r="G367" t="n">
-        <v>3.51578330993652</v>
+        <v>3.51578307151794</v>
       </c>
       <c r="H367" t="n">
         <v>8651</v>
@@ -11041,7 +11041,7 @@
         <v>4</v>
       </c>
       <c r="G368" t="n">
-        <v>3.51578330993652</v>
+        <v>3.51578307151794</v>
       </c>
       <c r="H368" t="n">
         <v>6801</v>
@@ -11070,7 +11070,7 @@
         <v>4</v>
       </c>
       <c r="G369" t="n">
-        <v>3.51578330993652</v>
+        <v>3.51578307151794</v>
       </c>
       <c r="H369" t="n">
         <v>0</v>
@@ -11099,7 +11099,7 @@
         <v>4</v>
       </c>
       <c r="G370" t="n">
-        <v>3.51578330993652</v>
+        <v>3.51578307151794</v>
       </c>
       <c r="H370" t="n">
         <v>0</v>
@@ -11128,7 +11128,7 @@
         <v>4</v>
       </c>
       <c r="G371" t="n">
-        <v>3.51578330993652</v>
+        <v>3.51578307151794</v>
       </c>
       <c r="H371" t="n">
         <v>0</v>
@@ -11273,7 +11273,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G376" t="n">
-        <v>3.82341432571411</v>
+        <v>3.82341408729553</v>
       </c>
       <c r="H376" t="n">
         <v>4874</v>
@@ -11331,7 +11331,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G378" t="n">
-        <v>3.84978270530701</v>
+        <v>3.84978294372559</v>
       </c>
       <c r="H378" t="n">
         <v>9179</v>
@@ -11389,7 +11389,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G380" t="n">
-        <v>3.99041366577148</v>
+        <v>3.99041342735291</v>
       </c>
       <c r="H380" t="n">
         <v>6050</v>
@@ -11418,7 +11418,7 @@
         <v>4.5</v>
       </c>
       <c r="G381" t="n">
-        <v>3.95525598526001</v>
+        <v>3.95525622367859</v>
       </c>
       <c r="H381" t="n">
         <v>11250</v>
@@ -11563,7 +11563,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G386" t="n">
-        <v>3.64762496948242</v>
+        <v>3.647625207901</v>
       </c>
       <c r="H386" t="n">
         <v>7282</v>
@@ -11592,7 +11592,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G387" t="n">
-        <v>3.42788863182068</v>
+        <v>3.42788887023926</v>
       </c>
       <c r="H387" t="n">
         <v>24073</v>
@@ -11708,7 +11708,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G391" t="n">
-        <v>3.52457284927368</v>
+        <v>3.52457308769226</v>
       </c>
       <c r="H391" t="n">
         <v>14867</v>
@@ -11737,7 +11737,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G392" t="n">
-        <v>3.62125682830811</v>
+        <v>3.62125658988953</v>
       </c>
       <c r="H392" t="n">
         <v>15062</v>
@@ -11824,7 +11824,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G395" t="n">
-        <v>3.74430918693542</v>
+        <v>3.744309425354</v>
       </c>
       <c r="H395" t="n">
         <v>15241</v>
@@ -11882,7 +11882,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G397" t="n">
-        <v>3.82341432571411</v>
+        <v>3.82341408729553</v>
       </c>
       <c r="H397" t="n">
         <v>1515</v>
@@ -11969,7 +11969,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G400" t="n">
-        <v>3.62125682830811</v>
+        <v>3.62125658988953</v>
       </c>
       <c r="H400" t="n">
         <v>1948</v>
@@ -12114,7 +12114,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G405" t="n">
-        <v>3.84978270530701</v>
+        <v>3.84978294372559</v>
       </c>
       <c r="H405" t="n">
         <v>10519</v>
@@ -12259,7 +12259,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G410" t="n">
-        <v>3.99920344352722</v>
+        <v>3.9992036819458</v>
       </c>
       <c r="H410" t="n">
         <v>13066</v>
@@ -12288,7 +12288,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G411" t="n">
-        <v>3.99920344352722</v>
+        <v>3.9992036819458</v>
       </c>
       <c r="H411" t="n">
         <v>3045</v>
@@ -12433,7 +12433,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G416" t="n">
-        <v>3.99920344352722</v>
+        <v>3.9992036819458</v>
       </c>
       <c r="H416" t="n">
         <v>20150</v>
@@ -12462,7 +12462,7 @@
         <v>4.59000015258789</v>
       </c>
       <c r="G417" t="n">
-        <v>4.03436183929443</v>
+        <v>4.03436136245728</v>
       </c>
       <c r="H417" t="n">
         <v>6334</v>
@@ -12491,7 +12491,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G418" t="n">
-        <v>4.08709859848022</v>
+        <v>4.08709812164307</v>
       </c>
       <c r="H418" t="n">
         <v>6771</v>
@@ -12549,7 +12549,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G420" t="n">
-        <v>4.30683469772339</v>
+        <v>4.30683422088623</v>
       </c>
       <c r="H420" t="n">
         <v>32975</v>
@@ -12665,7 +12665,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G424" t="n">
-        <v>4.30683469772339</v>
+        <v>4.30683422088623</v>
       </c>
       <c r="H424" t="n">
         <v>1866</v>
@@ -12694,7 +12694,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G425" t="n">
-        <v>4.29804515838623</v>
+        <v>4.29804468154907</v>
       </c>
       <c r="H425" t="n">
         <v>2886</v>
@@ -12926,7 +12926,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G433" t="n">
-        <v>4.32441329956055</v>
+        <v>4.32441377639771</v>
       </c>
       <c r="H433" t="n">
         <v>1529</v>
@@ -12955,7 +12955,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G434" t="n">
-        <v>4.22772979736328</v>
+        <v>4.22772932052612</v>
       </c>
       <c r="H434" t="n">
         <v>5368</v>
@@ -13158,7 +13158,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G441" t="n">
-        <v>4.30683469772339</v>
+        <v>4.30683422088623</v>
       </c>
       <c r="H441" t="n">
         <v>14413</v>
@@ -13187,7 +13187,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G442" t="n">
-        <v>4.30683469772339</v>
+        <v>4.30683422088623</v>
       </c>
       <c r="H442" t="n">
         <v>5600</v>
@@ -13274,7 +13274,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G445" t="n">
-        <v>4.2628870010376</v>
+        <v>4.26288652420044</v>
       </c>
       <c r="H445" t="n">
         <v>2230</v>
@@ -13448,7 +13448,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G451" t="n">
-        <v>4.30683469772339</v>
+        <v>4.30683422088623</v>
       </c>
       <c r="H451" t="n">
         <v>600</v>
@@ -13651,7 +13651,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G458" t="n">
-        <v>4.05194091796875</v>
+        <v>4.05194044113159</v>
       </c>
       <c r="H458" t="n">
         <v>1015</v>
@@ -13767,7 +13767,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G462" t="n">
-        <v>4.08709859848022</v>
+        <v>4.08709812164307</v>
       </c>
       <c r="H462" t="n">
         <v>155</v>
@@ -13854,7 +13854,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G465" t="n">
-        <v>4.2628870010376</v>
+        <v>4.26288652420044</v>
       </c>
       <c r="H465" t="n">
         <v>6017</v>
@@ -53938,6 +53938,35 @@
         <v>13955</v>
       </c>
       <c r="I1847" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1848">
+      <c r="A1848" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1848" s="1" t="n">
+        <v>46316.2916666667</v>
+      </c>
+      <c r="C1848" t="n">
+        <v>2.3199999332428</v>
+      </c>
+      <c r="D1848" t="n">
+        <v>2.3199999332428</v>
+      </c>
+      <c r="E1848" t="n">
+        <v>2.3199999332428</v>
+      </c>
+      <c r="F1848" t="n">
+        <v>2.3199999332428</v>
+      </c>
+      <c r="G1848" t="n">
+        <v>2.3199999332428</v>
+      </c>
+      <c r="H1848" t="n">
+        <v>1818</v>
+      </c>
+      <c r="I1848" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/PTR.MI.xlsx
+++ b/data/PTR.MI.xlsx
@@ -427,7 +427,7 @@
         <v>3.75</v>
       </c>
       <c r="G2" t="n">
-        <v>3.25484609603882</v>
+        <v>3.2548463344574</v>
       </c>
       <c r="H2" t="n">
         <v>859316</v>
@@ -543,7 +543,7 @@
         <v>3.69250011444092</v>
       </c>
       <c r="G6" t="n">
-        <v>3.20493865013123</v>
+        <v>3.20493912696838</v>
       </c>
       <c r="H6" t="n">
         <v>56036</v>
@@ -601,7 +601,7 @@
         <v>3.5864999294281</v>
       </c>
       <c r="G8" t="n">
-        <v>3.11293506622314</v>
+        <v>3.11293482780457</v>
       </c>
       <c r="H8" t="n">
         <v>37148</v>
@@ -775,7 +775,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G14" t="n">
-        <v>3.12465238571167</v>
+        <v>3.12465262413025</v>
       </c>
       <c r="H14" t="n">
         <v>10463</v>
@@ -804,7 +804,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G15" t="n">
-        <v>3.14201164245605</v>
+        <v>3.14201140403748</v>
       </c>
       <c r="H15" t="n">
         <v>8335</v>
@@ -833,7 +833,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G16" t="n">
-        <v>3.14201164245605</v>
+        <v>3.14201140403748</v>
       </c>
       <c r="H16" t="n">
         <v>6164</v>
@@ -891,7 +891,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G18" t="n">
-        <v>3.14201164245605</v>
+        <v>3.14201140403748</v>
       </c>
       <c r="H18" t="n">
         <v>10770</v>
@@ -920,7 +920,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G19" t="n">
-        <v>3.13333225250244</v>
+        <v>3.13333201408386</v>
       </c>
       <c r="H19" t="n">
         <v>26321</v>
@@ -949,7 +949,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G20" t="n">
-        <v>3.12465238571167</v>
+        <v>3.12465262413025</v>
       </c>
       <c r="H20" t="n">
         <v>1924</v>
@@ -978,7 +978,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G21" t="n">
-        <v>3.11597299575806</v>
+        <v>3.1159725189209</v>
       </c>
       <c r="H21" t="n">
         <v>210</v>
@@ -1007,7 +1007,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G22" t="n">
-        <v>3.09861350059509</v>
+        <v>3.09861373901367</v>
       </c>
       <c r="H22" t="n">
         <v>7918</v>
@@ -1036,7 +1036,7 @@
         <v>3.49850010871887</v>
       </c>
       <c r="G23" t="n">
-        <v>3.03655481338501</v>
+        <v>3.03655433654785</v>
       </c>
       <c r="H23" t="n">
         <v>800</v>
@@ -1181,7 +1181,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G28" t="n">
-        <v>2.98577928543091</v>
+        <v>2.98577904701233</v>
       </c>
       <c r="H28" t="n">
         <v>6355</v>
@@ -1297,7 +1297,7 @@
         <v>3.48200011253357</v>
       </c>
       <c r="G32" t="n">
-        <v>3.02223348617554</v>
+        <v>3.02223324775696</v>
       </c>
       <c r="H32" t="n">
         <v>904</v>
@@ -1326,7 +1326,7 @@
         <v>3.48200011253357</v>
       </c>
       <c r="G33" t="n">
-        <v>3.02223348617554</v>
+        <v>3.02223324775696</v>
       </c>
       <c r="H33" t="n">
         <v>432</v>
@@ -1355,7 +1355,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G34" t="n">
-        <v>3.10729312896729</v>
+        <v>3.10729336738586</v>
       </c>
       <c r="H34" t="n">
         <v>3335</v>
@@ -1384,7 +1384,7 @@
         <v>3.5</v>
       </c>
       <c r="G35" t="n">
-        <v>3.03785634040833</v>
+        <v>3.0378565788269</v>
       </c>
       <c r="H35" t="n">
         <v>1400</v>
@@ -1442,7 +1442,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G37" t="n">
-        <v>3.14201164245605</v>
+        <v>3.14201140403748</v>
       </c>
       <c r="H37" t="n">
         <v>49352</v>
@@ -1500,7 +1500,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G39" t="n">
-        <v>3.21144819259644</v>
+        <v>3.21144843101501</v>
       </c>
       <c r="H39" t="n">
         <v>28455</v>
@@ -1558,7 +1558,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G41" t="n">
-        <v>3.42843818664551</v>
+        <v>3.42843794822693</v>
       </c>
       <c r="H41" t="n">
         <v>44559</v>
@@ -1587,7 +1587,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G42" t="n">
-        <v>3.2982439994812</v>
+        <v>3.29824423789978</v>
       </c>
       <c r="H42" t="n">
         <v>4451</v>
@@ -1645,7 +1645,7 @@
         <v>3.67499995231628</v>
       </c>
       <c r="G44" t="n">
-        <v>3.18974947929382</v>
+        <v>3.18974924087524</v>
       </c>
       <c r="H44" t="n">
         <v>9040</v>
@@ -1674,7 +1674,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G45" t="n">
-        <v>3.17673015594482</v>
+        <v>3.17672991752625</v>
       </c>
       <c r="H45" t="n">
         <v>1155</v>
@@ -1761,7 +1761,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G48" t="n">
-        <v>3.15069103240967</v>
+        <v>3.15069127082825</v>
       </c>
       <c r="H48" t="n">
         <v>190</v>
@@ -1790,7 +1790,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G49" t="n">
-        <v>3.21144819259644</v>
+        <v>3.21144843101501</v>
       </c>
       <c r="H49" t="n">
         <v>17100</v>
@@ -1848,7 +1848,7 @@
         <v>3.75</v>
       </c>
       <c r="G51" t="n">
-        <v>3.25484609603882</v>
+        <v>3.2548463344574</v>
       </c>
       <c r="H51" t="n">
         <v>37160</v>
@@ -1877,7 +1877,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G52" t="n">
-        <v>3.21144819259644</v>
+        <v>3.21144843101501</v>
       </c>
       <c r="H52" t="n">
         <v>49416</v>
@@ -1906,7 +1906,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G53" t="n">
-        <v>3.17673015594482</v>
+        <v>3.17672991752625</v>
       </c>
       <c r="H53" t="n">
         <v>18126</v>
@@ -1935,7 +1935,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G54" t="n">
-        <v>3.21144819259644</v>
+        <v>3.21144843101501</v>
       </c>
       <c r="H54" t="n">
         <v>4498</v>
@@ -1993,7 +1993,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G56" t="n">
-        <v>3.15069103240967</v>
+        <v>3.15069127082825</v>
       </c>
       <c r="H56" t="n">
         <v>6760</v>
@@ -2022,7 +2022,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G57" t="n">
-        <v>3.15069103240967</v>
+        <v>3.15069127082825</v>
       </c>
       <c r="H57" t="n">
         <v>100</v>
@@ -2051,7 +2051,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G58" t="n">
-        <v>3.17673015594482</v>
+        <v>3.17672991752625</v>
       </c>
       <c r="H58" t="n">
         <v>1957</v>
@@ -2080,7 +2080,7 @@
         <v>3.66499996185303</v>
       </c>
       <c r="G59" t="n">
-        <v>3.18106961250305</v>
+        <v>3.18106985092163</v>
       </c>
       <c r="H59" t="n">
         <v>20</v>
@@ -2138,7 +2138,7 @@
         <v>3.66499996185303</v>
       </c>
       <c r="G61" t="n">
-        <v>3.18106961250305</v>
+        <v>3.18106985092163</v>
       </c>
       <c r="H61" t="n">
         <v>27542</v>
@@ -2167,7 +2167,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G62" t="n">
-        <v>3.21144819259644</v>
+        <v>3.21144843101501</v>
       </c>
       <c r="H62" t="n">
         <v>20</v>
@@ -2196,7 +2196,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G63" t="n">
-        <v>3.14201164245605</v>
+        <v>3.14201140403748</v>
       </c>
       <c r="H63" t="n">
         <v>2540</v>
@@ -2283,7 +2283,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G66" t="n">
-        <v>3.09861350059509</v>
+        <v>3.09861373901367</v>
       </c>
       <c r="H66" t="n">
         <v>4020</v>
@@ -2341,7 +2341,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G68" t="n">
-        <v>3.12465238571167</v>
+        <v>3.12465262413025</v>
       </c>
       <c r="H68" t="n">
         <v>2020</v>
@@ -2370,7 +2370,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G69" t="n">
-        <v>3.12465238571167</v>
+        <v>3.12465262413025</v>
       </c>
       <c r="H69" t="n">
         <v>7428</v>
@@ -2428,7 +2428,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G71" t="n">
-        <v>3.21144819259644</v>
+        <v>3.21144843101501</v>
       </c>
       <c r="H71" t="n">
         <v>2275</v>
@@ -2457,7 +2457,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G72" t="n">
-        <v>3.12465238571167</v>
+        <v>3.12465262413025</v>
       </c>
       <c r="H72" t="n">
         <v>29395</v>
@@ -2544,7 +2544,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G75" t="n">
-        <v>3.11597299575806</v>
+        <v>3.1159725189209</v>
       </c>
       <c r="H75" t="n">
         <v>5620</v>
@@ -2573,7 +2573,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G76" t="n">
-        <v>3.11597299575806</v>
+        <v>3.1159725189209</v>
       </c>
       <c r="H76" t="n">
         <v>609</v>
@@ -2631,7 +2631,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G78" t="n">
-        <v>3.12465238571167</v>
+        <v>3.12465262413025</v>
       </c>
       <c r="H78" t="n">
         <v>908</v>
@@ -2660,7 +2660,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G79" t="n">
-        <v>3.14201164245605</v>
+        <v>3.14201140403748</v>
       </c>
       <c r="H79" t="n">
         <v>66825</v>
@@ -2689,7 +2689,7 @@
         <v>3.67499995231628</v>
       </c>
       <c r="G80" t="n">
-        <v>3.18974947929382</v>
+        <v>3.18974924087524</v>
       </c>
       <c r="H80" t="n">
         <v>6929</v>
@@ -2747,7 +2747,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G82" t="n">
-        <v>3.14201164245605</v>
+        <v>3.14201140403748</v>
       </c>
       <c r="H82" t="n">
         <v>1300</v>
@@ -2776,7 +2776,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G83" t="n">
-        <v>3.2982439994812</v>
+        <v>3.29824423789978</v>
       </c>
       <c r="H83" t="n">
         <v>198082</v>
@@ -2805,7 +2805,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G84" t="n">
-        <v>3.2982439994812</v>
+        <v>3.29824423789978</v>
       </c>
       <c r="H84" t="n">
         <v>33903</v>
@@ -2834,7 +2834,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G85" t="n">
-        <v>3.2982439994812</v>
+        <v>3.29824423789978</v>
       </c>
       <c r="H85" t="n">
         <v>18308</v>
@@ -2863,7 +2863,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G86" t="n">
-        <v>3.2982439994812</v>
+        <v>3.29824423789978</v>
       </c>
       <c r="H86" t="n">
         <v>6890</v>
@@ -2921,7 +2921,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G88" t="n">
-        <v>3.42843818664551</v>
+        <v>3.42843794822693</v>
       </c>
       <c r="H88" t="n">
         <v>79090</v>
@@ -2950,7 +2950,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G89" t="n">
-        <v>3.42843818664551</v>
+        <v>3.42843794822693</v>
       </c>
       <c r="H89" t="n">
         <v>55032</v>
@@ -2979,7 +2979,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G90" t="n">
-        <v>3.41975855827332</v>
+        <v>3.41975879669189</v>
       </c>
       <c r="H90" t="n">
         <v>12161</v>
@@ -3066,7 +3066,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G93" t="n">
-        <v>3.46315670013428</v>
+        <v>3.4631564617157</v>
       </c>
       <c r="H93" t="n">
         <v>250</v>
@@ -3095,7 +3095,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G94" t="n">
-        <v>3.41975855827332</v>
+        <v>3.41975879669189</v>
       </c>
       <c r="H94" t="n">
         <v>3029</v>
@@ -3153,7 +3153,7 @@
         <v>4.02500009536743</v>
       </c>
       <c r="G96" t="n">
-        <v>3.49353504180908</v>
+        <v>3.49353528022766</v>
       </c>
       <c r="H96" t="n">
         <v>1493</v>
@@ -3182,7 +3182,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G97" t="n">
-        <v>3.42843818664551</v>
+        <v>3.42843794822693</v>
       </c>
       <c r="H97" t="n">
         <v>52799</v>
@@ -3211,7 +3211,7 @@
         <v>4.00500011444092</v>
       </c>
       <c r="G98" t="n">
-        <v>3.4761757850647</v>
+        <v>3.47617626190186</v>
       </c>
       <c r="H98" t="n">
         <v>4670</v>
@@ -3298,7 +3298,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G101" t="n">
-        <v>3.54127264022827</v>
+        <v>3.54127287864685</v>
       </c>
       <c r="H101" t="n">
         <v>4200</v>
@@ -3443,7 +3443,7 @@
         <v>4.03499984741211</v>
       </c>
       <c r="G106" t="n">
-        <v>3.50221467018127</v>
+        <v>3.50221419334412</v>
       </c>
       <c r="H106" t="n">
         <v>9593</v>
@@ -3617,7 +3617,7 @@
         <v>4.41499996185303</v>
       </c>
       <c r="G112" t="n">
-        <v>3.83203864097595</v>
+        <v>3.83203911781311</v>
       </c>
       <c r="H112" t="n">
         <v>30401</v>
@@ -3704,7 +3704,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G115" t="n">
-        <v>3.87109708786011</v>
+        <v>3.87109732627869</v>
       </c>
       <c r="H115" t="n">
         <v>4580</v>
@@ -3733,7 +3733,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G116" t="n">
-        <v>3.86241769790649</v>
+        <v>3.86241722106934</v>
       </c>
       <c r="H116" t="n">
         <v>17964</v>
@@ -3762,7 +3762,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G117" t="n">
-        <v>4.00997114181519</v>
+        <v>4.00997018814087</v>
       </c>
       <c r="H117" t="n">
         <v>10859</v>
@@ -3820,7 +3820,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G119" t="n">
-        <v>3.96657252311707</v>
+        <v>3.96657276153564</v>
       </c>
       <c r="H119" t="n">
         <v>7065</v>
@@ -3849,7 +3849,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G120" t="n">
-        <v>3.86241769790649</v>
+        <v>3.86241722106934</v>
       </c>
       <c r="H120" t="n">
         <v>34190</v>
@@ -3878,7 +3878,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G121" t="n">
-        <v>3.92317461967468</v>
+        <v>3.92317509651184</v>
       </c>
       <c r="H121" t="n">
         <v>67457</v>
@@ -3907,7 +3907,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G122" t="n">
-        <v>3.94053339958191</v>
+        <v>3.94053411483765</v>
       </c>
       <c r="H122" t="n">
         <v>5398</v>
@@ -3936,7 +3936,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G123" t="n">
-        <v>3.88845658302307</v>
+        <v>3.88845610618591</v>
       </c>
       <c r="H123" t="n">
         <v>13757</v>
@@ -3965,7 +3965,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G124" t="n">
-        <v>3.94921374320984</v>
+        <v>3.94921326637268</v>
       </c>
       <c r="H124" t="n">
         <v>5841</v>
@@ -3994,7 +3994,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G125" t="n">
-        <v>3.94921374320984</v>
+        <v>3.94921326637268</v>
       </c>
       <c r="H125" t="n">
         <v>21549</v>
@@ -4052,7 +4052,7 @@
         <v>4.88500022888184</v>
       </c>
       <c r="G127" t="n">
-        <v>4.23998022079468</v>
+        <v>4.23997974395752</v>
       </c>
       <c r="H127" t="n">
         <v>32038</v>
@@ -4081,7 +4081,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G128" t="n">
-        <v>4.37451314926147</v>
+        <v>4.37451362609863</v>
       </c>
       <c r="H128" t="n">
         <v>36739</v>
@@ -4139,7 +4139,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G130" t="n">
-        <v>4.39187240600586</v>
+        <v>4.39187288284302</v>
       </c>
       <c r="H130" t="n">
         <v>8599</v>
@@ -4226,7 +4226,7 @@
         <v>4.97499990463257</v>
       </c>
       <c r="G133" t="n">
-        <v>4.31809616088867</v>
+        <v>4.31809568405151</v>
       </c>
       <c r="H133" t="n">
         <v>8257</v>
@@ -4255,7 +4255,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G134" t="n">
-        <v>4.24431896209717</v>
+        <v>4.24431943893433</v>
       </c>
       <c r="H134" t="n">
         <v>9475</v>
@@ -4284,7 +4284,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G135" t="n">
-        <v>4.24431896209717</v>
+        <v>4.24431943893433</v>
       </c>
       <c r="H135" t="n">
         <v>1852</v>
@@ -4313,7 +4313,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G136" t="n">
-        <v>4.20092153549194</v>
+        <v>4.2009220123291</v>
       </c>
       <c r="H136" t="n">
         <v>13708</v>
@@ -4342,7 +4342,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G137" t="n">
-        <v>4.14016389846802</v>
+        <v>4.14016437530518</v>
       </c>
       <c r="H137" t="n">
         <v>18698</v>
@@ -4371,7 +4371,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G138" t="n">
-        <v>4.16620302200317</v>
+        <v>4.16620349884033</v>
       </c>
       <c r="H138" t="n">
         <v>23142</v>
@@ -4400,7 +4400,7 @@
         <v>5</v>
       </c>
       <c r="G139" t="n">
-        <v>4.33979463577271</v>
+        <v>4.33979511260986</v>
       </c>
       <c r="H139" t="n">
         <v>20858</v>
@@ -4516,7 +4516,7 @@
         <v>5</v>
       </c>
       <c r="G143" t="n">
-        <v>4.33979463577271</v>
+        <v>4.33979511260986</v>
       </c>
       <c r="H143" t="n">
         <v>9892</v>
@@ -4632,7 +4632,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G147" t="n">
-        <v>4.70433807373047</v>
+        <v>4.70433759689331</v>
       </c>
       <c r="H147" t="n">
         <v>15539</v>
@@ -4806,7 +4806,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G153" t="n">
-        <v>4.44395017623901</v>
+        <v>4.44394969940186</v>
       </c>
       <c r="H153" t="n">
         <v>2010</v>
@@ -4864,7 +4864,7 @@
         <v>4.75500011444092</v>
       </c>
       <c r="G155" t="n">
-        <v>4.1271448135376</v>
+        <v>4.12714529037476</v>
       </c>
       <c r="H155" t="n">
         <v>9182</v>
@@ -4893,7 +4893,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G156" t="n">
-        <v>4.31375598907471</v>
+        <v>4.31375646591187</v>
       </c>
       <c r="H156" t="n">
         <v>4730</v>
@@ -4922,7 +4922,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G157" t="n">
-        <v>4.23564004898071</v>
+        <v>4.23563957214355</v>
       </c>
       <c r="H157" t="n">
         <v>8393</v>
@@ -5009,7 +5009,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G160" t="n">
-        <v>4.06204748153687</v>
+        <v>4.06204795837402</v>
       </c>
       <c r="H160" t="n">
         <v>4897</v>
@@ -5038,7 +5038,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G161" t="n">
-        <v>4.0446891784668</v>
+        <v>4.04468870162964</v>
       </c>
       <c r="H161" t="n">
         <v>300</v>
@@ -5067,7 +5067,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G162" t="n">
-        <v>3.99261116981506</v>
+        <v>3.9926118850708</v>
       </c>
       <c r="H162" t="n">
         <v>1599</v>
@@ -5096,7 +5096,7 @@
         <v>4.24499988555908</v>
       </c>
       <c r="G163" t="n">
-        <v>3.68448567390442</v>
+        <v>3.684485912323</v>
       </c>
       <c r="H163" t="n">
         <v>8681</v>
@@ -5125,7 +5125,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G164" t="n">
-        <v>3.17673015594482</v>
+        <v>3.17672991752625</v>
       </c>
       <c r="H164" t="n">
         <v>13665</v>
@@ -5154,7 +5154,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G165" t="n">
-        <v>3.26352620124817</v>
+        <v>3.26352596282959</v>
       </c>
       <c r="H165" t="n">
         <v>12420</v>
@@ -5183,7 +5183,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G166" t="n">
-        <v>3.23748683929443</v>
+        <v>3.23748707771301</v>
       </c>
       <c r="H166" t="n">
         <v>4220</v>
@@ -5241,7 +5241,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G168" t="n">
-        <v>2.95974016189575</v>
+        <v>2.95974040031433</v>
       </c>
       <c r="H168" t="n">
         <v>11032</v>
@@ -5270,7 +5270,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G169" t="n">
-        <v>2.98577928543091</v>
+        <v>2.98577904701233</v>
       </c>
       <c r="H169" t="n">
         <v>3440</v>
@@ -5299,7 +5299,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G170" t="n">
-        <v>3.12465238571167</v>
+        <v>3.12465262413025</v>
       </c>
       <c r="H170" t="n">
         <v>862</v>
@@ -5386,7 +5386,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G173" t="n">
-        <v>3.09861350059509</v>
+        <v>3.09861373901367</v>
       </c>
       <c r="H173" t="n">
         <v>20403</v>
@@ -5444,7 +5444,7 @@
         <v>3.72499990463257</v>
       </c>
       <c r="G175" t="n">
-        <v>3.23314690589905</v>
+        <v>3.23314714431763</v>
       </c>
       <c r="H175" t="n">
         <v>35922</v>
@@ -5502,7 +5502,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G177" t="n">
-        <v>3.09861350059509</v>
+        <v>3.09861373901367</v>
       </c>
       <c r="H177" t="n">
         <v>2492</v>
@@ -5560,7 +5560,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G179" t="n">
-        <v>3.21144819259644</v>
+        <v>3.21144843101501</v>
       </c>
       <c r="H179" t="n">
         <v>6765</v>
@@ -5618,7 +5618,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G181" t="n">
-        <v>3.30692362785339</v>
+        <v>3.30692386627197</v>
       </c>
       <c r="H181" t="n">
         <v>2000</v>
@@ -5705,7 +5705,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G184" t="n">
-        <v>3.21144819259644</v>
+        <v>3.21144843101501</v>
       </c>
       <c r="H184" t="n">
         <v>4102</v>
@@ -5792,7 +5792,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G187" t="n">
-        <v>3.21144819259644</v>
+        <v>3.21144843101501</v>
       </c>
       <c r="H187" t="n">
         <v>10326</v>
@@ -5821,7 +5821,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G188" t="n">
-        <v>3.2982439994812</v>
+        <v>3.29824423789978</v>
       </c>
       <c r="H188" t="n">
         <v>5632</v>
@@ -5908,7 +5908,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G191" t="n">
-        <v>3.28088521957397</v>
+        <v>3.2808849811554</v>
       </c>
       <c r="H191" t="n">
         <v>15966</v>
@@ -5966,7 +5966,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G193" t="n">
-        <v>3.2982439994812</v>
+        <v>3.29824423789978</v>
       </c>
       <c r="H193" t="n">
         <v>13631</v>
@@ -5995,7 +5995,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G194" t="n">
-        <v>3.2982439994812</v>
+        <v>3.29824423789978</v>
       </c>
       <c r="H194" t="n">
         <v>5341</v>
@@ -6024,7 +6024,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G195" t="n">
-        <v>3.34164214134216</v>
+        <v>3.34164190292358</v>
       </c>
       <c r="H195" t="n">
         <v>6546</v>
@@ -6053,7 +6053,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G196" t="n">
-        <v>3.35900115966797</v>
+        <v>3.35900139808655</v>
       </c>
       <c r="H196" t="n">
         <v>2603</v>
@@ -6082,7 +6082,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G197" t="n">
-        <v>3.35900115966797</v>
+        <v>3.35900139808655</v>
       </c>
       <c r="H197" t="n">
         <v>1540</v>
@@ -6169,7 +6169,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G200" t="n">
-        <v>3.48051595687866</v>
+        <v>3.48051571846008</v>
       </c>
       <c r="H200" t="n">
         <v>8475</v>
@@ -6227,7 +6227,7 @@
         <v>3.75</v>
       </c>
       <c r="G202" t="n">
-        <v>3.25484609603882</v>
+        <v>3.2548463344574</v>
       </c>
       <c r="H202" t="n">
         <v>25406</v>
@@ -6256,7 +6256,7 @@
         <v>3.75</v>
       </c>
       <c r="G203" t="n">
-        <v>3.25484609603882</v>
+        <v>3.2548463344574</v>
       </c>
       <c r="H203" t="n">
         <v>5500</v>
@@ -6314,7 +6314,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G205" t="n">
-        <v>3.2982439994812</v>
+        <v>3.29824423789978</v>
       </c>
       <c r="H205" t="n">
         <v>4357</v>
@@ -6401,7 +6401,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G208" t="n">
-        <v>3.30692362785339</v>
+        <v>3.30692386627197</v>
       </c>
       <c r="H208" t="n">
         <v>11449</v>
@@ -6430,7 +6430,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G209" t="n">
-        <v>3.24616670608521</v>
+        <v>3.24616646766663</v>
       </c>
       <c r="H209" t="n">
         <v>13675</v>
@@ -6488,7 +6488,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G211" t="n">
-        <v>3.2982439994812</v>
+        <v>3.29824423789978</v>
       </c>
       <c r="H211" t="n">
         <v>8606</v>
@@ -6575,7 +6575,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G214" t="n">
-        <v>3.28088521957397</v>
+        <v>3.2808849811554</v>
       </c>
       <c r="H214" t="n">
         <v>1000</v>
@@ -6604,7 +6604,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G215" t="n">
-        <v>3.26352620124817</v>
+        <v>3.26352596282959</v>
       </c>
       <c r="H215" t="n">
         <v>2689</v>
@@ -6633,7 +6633,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G216" t="n">
-        <v>3.28088521957397</v>
+        <v>3.2808849811554</v>
       </c>
       <c r="H216" t="n">
         <v>5107</v>
@@ -6662,7 +6662,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G217" t="n">
-        <v>3.2982439994812</v>
+        <v>3.29824423789978</v>
       </c>
       <c r="H217" t="n">
         <v>16383</v>
@@ -6691,7 +6691,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G218" t="n">
-        <v>3.28088521957397</v>
+        <v>3.2808849811554</v>
       </c>
       <c r="H218" t="n">
         <v>3100</v>
@@ -6720,7 +6720,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G219" t="n">
-        <v>3.2982439994812</v>
+        <v>3.29824423789978</v>
       </c>
       <c r="H219" t="n">
         <v>6884</v>
@@ -6749,7 +6749,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G220" t="n">
-        <v>3.26352620124817</v>
+        <v>3.26352596282959</v>
       </c>
       <c r="H220" t="n">
         <v>285</v>
@@ -6807,7 +6807,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G222" t="n">
-        <v>3.2982439994812</v>
+        <v>3.29824423789978</v>
       </c>
       <c r="H222" t="n">
         <v>4259</v>
@@ -6836,7 +6836,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G223" t="n">
-        <v>3.34164214134216</v>
+        <v>3.34164190292358</v>
       </c>
       <c r="H223" t="n">
         <v>1631</v>
@@ -6865,7 +6865,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G224" t="n">
-        <v>3.38504028320312</v>
+        <v>3.38504004478455</v>
       </c>
       <c r="H224" t="n">
         <v>2943</v>
@@ -6894,7 +6894,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G225" t="n">
-        <v>3.35900115966797</v>
+        <v>3.35900139808655</v>
       </c>
       <c r="H225" t="n">
         <v>7946</v>
@@ -6952,7 +6952,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G227" t="n">
-        <v>3.2982439994812</v>
+        <v>3.29824423789978</v>
       </c>
       <c r="H227" t="n">
         <v>6610</v>
@@ -6981,7 +6981,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G228" t="n">
-        <v>3.42843818664551</v>
+        <v>3.42843794822693</v>
       </c>
       <c r="H228" t="n">
         <v>2439</v>
@@ -7184,7 +7184,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G235" t="n">
-        <v>3.32428288459778</v>
+        <v>3.32428312301636</v>
       </c>
       <c r="H235" t="n">
         <v>800</v>
@@ -7213,7 +7213,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G236" t="n">
-        <v>3.32428288459778</v>
+        <v>3.32428312301636</v>
       </c>
       <c r="H236" t="n">
         <v>0</v>
@@ -7271,7 +7271,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G238" t="n">
-        <v>3.23748683929443</v>
+        <v>3.23748707771301</v>
       </c>
       <c r="H238" t="n">
         <v>386</v>
@@ -7300,7 +7300,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G239" t="n">
-        <v>3.23748683929443</v>
+        <v>3.23748707771301</v>
       </c>
       <c r="H239" t="n">
         <v>0</v>
@@ -7329,7 +7329,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G240" t="n">
-        <v>3.2982439994812</v>
+        <v>3.29824423789978</v>
       </c>
       <c r="H240" t="n">
         <v>2500</v>
@@ -7358,7 +7358,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G241" t="n">
-        <v>3.34164214134216</v>
+        <v>3.34164190292358</v>
       </c>
       <c r="H241" t="n">
         <v>1540</v>
@@ -7445,7 +7445,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G244" t="n">
-        <v>3.42843818664551</v>
+        <v>3.42843794822693</v>
       </c>
       <c r="H244" t="n">
         <v>2009</v>
@@ -7503,7 +7503,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G246" t="n">
-        <v>3.2982439994812</v>
+        <v>3.29824423789978</v>
       </c>
       <c r="H246" t="n">
         <v>2471</v>
@@ -7532,7 +7532,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G247" t="n">
-        <v>3.24616670608521</v>
+        <v>3.24616646766663</v>
       </c>
       <c r="H247" t="n">
         <v>21876</v>
@@ -7561,7 +7561,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G248" t="n">
-        <v>3.24616670608521</v>
+        <v>3.24616646766663</v>
       </c>
       <c r="H248" t="n">
         <v>0</v>
@@ -7677,7 +7677,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G252" t="n">
-        <v>3.21144819259644</v>
+        <v>3.21144843101501</v>
       </c>
       <c r="H252" t="n">
         <v>57</v>
@@ -7706,7 +7706,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G253" t="n">
-        <v>3.21144819259644</v>
+        <v>3.21144843101501</v>
       </c>
       <c r="H253" t="n">
         <v>0</v>
@@ -7822,7 +7822,7 @@
         <v>3.75</v>
       </c>
       <c r="G257" t="n">
-        <v>3.25484609603882</v>
+        <v>3.2548463344574</v>
       </c>
       <c r="H257" t="n">
         <v>3790</v>
@@ -7938,7 +7938,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G261" t="n">
-        <v>3.11597299575806</v>
+        <v>3.1159725189209</v>
       </c>
       <c r="H261" t="n">
         <v>80</v>
@@ -8025,7 +8025,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G264" t="n">
-        <v>3.13333225250244</v>
+        <v>3.13333201408386</v>
       </c>
       <c r="H264" t="n">
         <v>100</v>
@@ -8054,7 +8054,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G265" t="n">
-        <v>3.07257509231567</v>
+        <v>3.07257485389709</v>
       </c>
       <c r="H265" t="n">
         <v>1250</v>
@@ -8083,7 +8083,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G266" t="n">
-        <v>3.11597299575806</v>
+        <v>3.1159725189209</v>
       </c>
       <c r="H266" t="n">
         <v>700</v>
@@ -8112,7 +8112,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G267" t="n">
-        <v>3.11597299575806</v>
+        <v>3.1159725189209</v>
       </c>
       <c r="H267" t="n">
         <v>0</v>
@@ -8141,7 +8141,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G268" t="n">
-        <v>3.11597299575806</v>
+        <v>3.1159725189209</v>
       </c>
       <c r="H268" t="n">
         <v>0</v>
@@ -8170,7 +8170,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G269" t="n">
-        <v>3.24616670608521</v>
+        <v>3.24616646766663</v>
       </c>
       <c r="H269" t="n">
         <v>750</v>
@@ -8228,7 +8228,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G271" t="n">
-        <v>3.13333225250244</v>
+        <v>3.13333201408386</v>
       </c>
       <c r="H271" t="n">
         <v>2533</v>
@@ -8257,7 +8257,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G272" t="n">
-        <v>3.12465238571167</v>
+        <v>3.12465262413025</v>
       </c>
       <c r="H272" t="n">
         <v>9221</v>
@@ -8431,7 +8431,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G278" t="n">
-        <v>3.07257509231567</v>
+        <v>3.07257485389709</v>
       </c>
       <c r="H278" t="n">
         <v>4119</v>
@@ -8489,7 +8489,7 @@
         <v>3.5</v>
       </c>
       <c r="G280" t="n">
-        <v>3.03785634040833</v>
+        <v>3.0378565788269</v>
       </c>
       <c r="H280" t="n">
         <v>105</v>
@@ -8663,7 +8663,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G286" t="n">
-        <v>2.98577928543091</v>
+        <v>2.98577904701233</v>
       </c>
       <c r="H286" t="n">
         <v>6281</v>
@@ -8692,7 +8692,7 @@
         <v>3.5</v>
       </c>
       <c r="G287" t="n">
-        <v>3.03785634040833</v>
+        <v>3.0378565788269</v>
       </c>
       <c r="H287" t="n">
         <v>3634</v>
@@ -8808,7 +8808,7 @@
         <v>3.5</v>
       </c>
       <c r="G291" t="n">
-        <v>3.03785634040833</v>
+        <v>3.0378565788269</v>
       </c>
       <c r="H291" t="n">
         <v>10</v>
@@ -8837,7 +8837,7 @@
         <v>3.5</v>
       </c>
       <c r="G292" t="n">
-        <v>3.03785634040833</v>
+        <v>3.0378565788269</v>
       </c>
       <c r="H292" t="n">
         <v>0</v>
@@ -8866,7 +8866,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G293" t="n">
-        <v>2.98577928543091</v>
+        <v>2.98577904701233</v>
       </c>
       <c r="H293" t="n">
         <v>2137</v>
@@ -8924,7 +8924,7 @@
         <v>3.5</v>
       </c>
       <c r="G295" t="n">
-        <v>3.03785634040833</v>
+        <v>3.0378565788269</v>
       </c>
       <c r="H295" t="n">
         <v>700</v>
@@ -9040,7 +9040,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G299" t="n">
-        <v>2.86426496505737</v>
+        <v>2.86426448822021</v>
       </c>
       <c r="H299" t="n">
         <v>18061</v>
@@ -9069,7 +9069,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G300" t="n">
-        <v>2.86426496505737</v>
+        <v>2.86426448822021</v>
       </c>
       <c r="H300" t="n">
         <v>0</v>
@@ -9098,7 +9098,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G301" t="n">
-        <v>2.86426496505737</v>
+        <v>2.86426448822021</v>
       </c>
       <c r="H301" t="n">
         <v>14192</v>
@@ -9127,7 +9127,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G302" t="n">
-        <v>2.95974016189575</v>
+        <v>2.95974040031433</v>
       </c>
       <c r="H302" t="n">
         <v>10987</v>
@@ -9185,7 +9185,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G304" t="n">
-        <v>2.87294411659241</v>
+        <v>2.87294435501099</v>
       </c>
       <c r="H304" t="n">
         <v>20000</v>
@@ -9214,7 +9214,7 @@
         <v>3.5</v>
       </c>
       <c r="G305" t="n">
-        <v>3.03785634040833</v>
+        <v>3.0378565788269</v>
       </c>
       <c r="H305" t="n">
         <v>28717</v>
@@ -9272,7 +9272,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G307" t="n">
-        <v>3.12465238571167</v>
+        <v>3.12465262413025</v>
       </c>
       <c r="H307" t="n">
         <v>9075</v>
@@ -9301,7 +9301,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G308" t="n">
-        <v>3.12465238571167</v>
+        <v>3.12465262413025</v>
       </c>
       <c r="H308" t="n">
         <v>6589</v>
@@ -9446,7 +9446,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G313" t="n">
-        <v>3.21144819259644</v>
+        <v>3.21144843101501</v>
       </c>
       <c r="H313" t="n">
         <v>2665</v>
@@ -9504,7 +9504,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G315" t="n">
-        <v>3.21144819259644</v>
+        <v>3.21144843101501</v>
       </c>
       <c r="H315" t="n">
         <v>456</v>
@@ -9533,7 +9533,7 @@
         <v>3.75</v>
       </c>
       <c r="G316" t="n">
-        <v>3.25484609603882</v>
+        <v>3.2548463344574</v>
       </c>
       <c r="H316" t="n">
         <v>2505</v>
@@ -9562,7 +9562,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G317" t="n">
-        <v>3.21144819259644</v>
+        <v>3.21144843101501</v>
       </c>
       <c r="H317" t="n">
         <v>1600</v>
@@ -9591,7 +9591,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G318" t="n">
-        <v>3.17673015594482</v>
+        <v>3.17672991752625</v>
       </c>
       <c r="H318" t="n">
         <v>6400</v>
@@ -9620,7 +9620,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G319" t="n">
-        <v>3.11597299575806</v>
+        <v>3.1159725189209</v>
       </c>
       <c r="H319" t="n">
         <v>5736</v>
@@ -9678,7 +9678,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G321" t="n">
-        <v>3.21144819259644</v>
+        <v>3.21144843101501</v>
       </c>
       <c r="H321" t="n">
         <v>2251</v>
@@ -9736,7 +9736,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G323" t="n">
-        <v>3.21144819259644</v>
+        <v>3.21144843101501</v>
       </c>
       <c r="H323" t="n">
         <v>220</v>
@@ -9765,7 +9765,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G324" t="n">
-        <v>3.21144819259644</v>
+        <v>3.21144843101501</v>
       </c>
       <c r="H324" t="n">
         <v>4700</v>
@@ -9794,7 +9794,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G325" t="n">
-        <v>3.21144819259644</v>
+        <v>3.21144843101501</v>
       </c>
       <c r="H325" t="n">
         <v>650</v>
@@ -9852,7 +9852,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G327" t="n">
-        <v>3.14201164245605</v>
+        <v>3.14201140403748</v>
       </c>
       <c r="H327" t="n">
         <v>1954</v>
@@ -9881,7 +9881,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G328" t="n">
-        <v>3.21144819259644</v>
+        <v>3.21144843101501</v>
       </c>
       <c r="H328" t="n">
         <v>2264</v>
@@ -9910,7 +9910,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G329" t="n">
-        <v>3.12465238571167</v>
+        <v>3.12465262413025</v>
       </c>
       <c r="H329" t="n">
         <v>3400</v>
@@ -9997,7 +9997,7 @@
         <v>3.5</v>
       </c>
       <c r="G332" t="n">
-        <v>3.03785634040833</v>
+        <v>3.0378565788269</v>
       </c>
       <c r="H332" t="n">
         <v>2958</v>
@@ -10055,7 +10055,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G334" t="n">
-        <v>3.15069103240967</v>
+        <v>3.15069127082825</v>
       </c>
       <c r="H334" t="n">
         <v>1330</v>
@@ -10171,7 +10171,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G338" t="n">
-        <v>3.11597299575806</v>
+        <v>3.1159725189209</v>
       </c>
       <c r="H338" t="n">
         <v>70</v>
@@ -10229,7 +10229,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G340" t="n">
-        <v>3.11597299575806</v>
+        <v>3.1159725189209</v>
       </c>
       <c r="H340" t="n">
         <v>823</v>
@@ -10287,7 +10287,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G342" t="n">
-        <v>3.21144819259644</v>
+        <v>3.21144843101501</v>
       </c>
       <c r="H342" t="n">
         <v>3660</v>
@@ -10316,7 +10316,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G343" t="n">
-        <v>3.15069103240967</v>
+        <v>3.15069127082825</v>
       </c>
       <c r="H343" t="n">
         <v>3072</v>
@@ -10345,7 +10345,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G344" t="n">
-        <v>3.15069103240967</v>
+        <v>3.15069127082825</v>
       </c>
       <c r="H344" t="n">
         <v>8220</v>
@@ -10403,7 +10403,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G346" t="n">
-        <v>3.21144819259644</v>
+        <v>3.21144843101501</v>
       </c>
       <c r="H346" t="n">
         <v>5550</v>
@@ -10461,7 +10461,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G348" t="n">
-        <v>3.42843818664551</v>
+        <v>3.42843794822693</v>
       </c>
       <c r="H348" t="n">
         <v>10171</v>
@@ -10577,7 +10577,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G352" t="n">
-        <v>3.34164214134216</v>
+        <v>3.34164190292358</v>
       </c>
       <c r="H352" t="n">
         <v>1770</v>
@@ -10635,7 +10635,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G354" t="n">
-        <v>3.34164214134216</v>
+        <v>3.34164190292358</v>
       </c>
       <c r="H354" t="n">
         <v>1650</v>
@@ -10664,7 +10664,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G355" t="n">
-        <v>3.30692362785339</v>
+        <v>3.30692386627197</v>
       </c>
       <c r="H355" t="n">
         <v>20</v>
@@ -10693,7 +10693,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G356" t="n">
-        <v>3.42843818664551</v>
+        <v>3.42843794822693</v>
       </c>
       <c r="H356" t="n">
         <v>1020</v>
@@ -10722,7 +10722,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G357" t="n">
-        <v>3.42843818664551</v>
+        <v>3.42843794822693</v>
       </c>
       <c r="H357" t="n">
         <v>1750</v>
@@ -10838,7 +10838,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G361" t="n">
-        <v>3.46304655075073</v>
+        <v>3.46304678916931</v>
       </c>
       <c r="H361" t="n">
         <v>6479</v>
@@ -10896,7 +10896,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G363" t="n">
-        <v>3.53336215019226</v>
+        <v>3.53336191177368</v>
       </c>
       <c r="H363" t="n">
         <v>425644</v>
@@ -10925,7 +10925,7 @@
         <v>4</v>
       </c>
       <c r="G364" t="n">
-        <v>3.51578307151794</v>
+        <v>3.51578330993652</v>
       </c>
       <c r="H364" t="n">
         <v>16056</v>
@@ -10983,7 +10983,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G366" t="n">
-        <v>3.47183609008789</v>
+        <v>3.47183585166931</v>
       </c>
       <c r="H366" t="n">
         <v>16015</v>
@@ -11012,7 +11012,7 @@
         <v>4</v>
       </c>
       <c r="G367" t="n">
-        <v>3.51578307151794</v>
+        <v>3.51578330993652</v>
       </c>
       <c r="H367" t="n">
         <v>8651</v>
@@ -11041,7 +11041,7 @@
         <v>4</v>
       </c>
       <c r="G368" t="n">
-        <v>3.51578307151794</v>
+        <v>3.51578330993652</v>
       </c>
       <c r="H368" t="n">
         <v>6801</v>
@@ -11070,7 +11070,7 @@
         <v>4</v>
       </c>
       <c r="G369" t="n">
-        <v>3.51578307151794</v>
+        <v>3.51578330993652</v>
       </c>
       <c r="H369" t="n">
         <v>0</v>
@@ -11099,7 +11099,7 @@
         <v>4</v>
       </c>
       <c r="G370" t="n">
-        <v>3.51578307151794</v>
+        <v>3.51578330993652</v>
       </c>
       <c r="H370" t="n">
         <v>0</v>
@@ -11128,7 +11128,7 @@
         <v>4</v>
       </c>
       <c r="G371" t="n">
-        <v>3.51578307151794</v>
+        <v>3.51578330993652</v>
       </c>
       <c r="H371" t="n">
         <v>0</v>
@@ -11244,7 +11244,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G375" t="n">
-        <v>3.80583548545837</v>
+        <v>3.80583524703979</v>
       </c>
       <c r="H375" t="n">
         <v>1180</v>
@@ -11273,7 +11273,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G376" t="n">
-        <v>3.82341408729553</v>
+        <v>3.82341432571411</v>
       </c>
       <c r="H376" t="n">
         <v>4874</v>
@@ -11331,7 +11331,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G378" t="n">
-        <v>3.84978294372559</v>
+        <v>3.84978270530701</v>
       </c>
       <c r="H378" t="n">
         <v>9179</v>
@@ -11389,7 +11389,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G380" t="n">
-        <v>3.99041342735291</v>
+        <v>3.99041414260864</v>
       </c>
       <c r="H380" t="n">
         <v>6050</v>
@@ -11418,7 +11418,7 @@
         <v>4.5</v>
       </c>
       <c r="G381" t="n">
-        <v>3.95525622367859</v>
+        <v>3.95525646209717</v>
       </c>
       <c r="H381" t="n">
         <v>11250</v>
@@ -11476,7 +11476,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G383" t="n">
-        <v>3.92009830474854</v>
+        <v>3.92009854316711</v>
       </c>
       <c r="H383" t="n">
         <v>30</v>
@@ -11679,7 +11679,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G390" t="n">
-        <v>3.69157218933105</v>
+        <v>3.69157195091248</v>
       </c>
       <c r="H390" t="n">
         <v>9963</v>
@@ -11766,7 +11766,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G393" t="n">
-        <v>3.67399334907532</v>
+        <v>3.6739935874939</v>
       </c>
       <c r="H393" t="n">
         <v>9627</v>
@@ -11795,7 +11795,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G394" t="n">
-        <v>3.67399334907532</v>
+        <v>3.6739935874939</v>
       </c>
       <c r="H394" t="n">
         <v>6027</v>
@@ -11824,7 +11824,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G395" t="n">
-        <v>3.744309425354</v>
+        <v>3.74430918693542</v>
       </c>
       <c r="H395" t="n">
         <v>15241</v>
@@ -11882,7 +11882,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G397" t="n">
-        <v>3.82341408729553</v>
+        <v>3.82341432571411</v>
       </c>
       <c r="H397" t="n">
         <v>1515</v>
@@ -12027,7 +12027,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G402" t="n">
-        <v>3.60367774963379</v>
+        <v>3.60367798805237</v>
       </c>
       <c r="H402" t="n">
         <v>31743</v>
@@ -12056,7 +12056,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G403" t="n">
-        <v>3.68278312683105</v>
+        <v>3.6827826499939</v>
       </c>
       <c r="H403" t="n">
         <v>5461</v>
@@ -12114,7 +12114,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G405" t="n">
-        <v>3.84978294372559</v>
+        <v>3.84978270530701</v>
       </c>
       <c r="H405" t="n">
         <v>10519</v>
@@ -12143,7 +12143,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G406" t="n">
-        <v>3.84099268913269</v>
+        <v>3.84099316596985</v>
       </c>
       <c r="H406" t="n">
         <v>7000</v>
@@ -12230,7 +12230,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G409" t="n">
-        <v>4.04315042495728</v>
+        <v>4.04315090179443</v>
       </c>
       <c r="H409" t="n">
         <v>11444</v>
@@ -12259,7 +12259,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G410" t="n">
-        <v>3.9992036819458</v>
+        <v>3.99920344352722</v>
       </c>
       <c r="H410" t="n">
         <v>13066</v>
@@ -12288,7 +12288,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G411" t="n">
-        <v>3.9992036819458</v>
+        <v>3.99920344352722</v>
       </c>
       <c r="H411" t="n">
         <v>3045</v>
@@ -12346,7 +12346,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G413" t="n">
-        <v>4.06072998046875</v>
+        <v>4.06072950363159</v>
       </c>
       <c r="H413" t="n">
         <v>1119</v>
@@ -12375,7 +12375,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G414" t="n">
-        <v>4.04315042495728</v>
+        <v>4.04315090179443</v>
       </c>
       <c r="H414" t="n">
         <v>4777</v>
@@ -12404,7 +12404,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G415" t="n">
-        <v>4.04315042495728</v>
+        <v>4.04315090179443</v>
       </c>
       <c r="H415" t="n">
         <v>0</v>
@@ -12433,7 +12433,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G416" t="n">
-        <v>3.9992036819458</v>
+        <v>3.99920344352722</v>
       </c>
       <c r="H416" t="n">
         <v>20150</v>
@@ -12462,7 +12462,7 @@
         <v>4.59000015258789</v>
       </c>
       <c r="G417" t="n">
-        <v>4.03436136245728</v>
+        <v>4.03436183929443</v>
       </c>
       <c r="H417" t="n">
         <v>6334</v>
@@ -12491,7 +12491,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G418" t="n">
-        <v>4.08709812164307</v>
+        <v>4.08709859848022</v>
       </c>
       <c r="H418" t="n">
         <v>6771</v>
@@ -12549,7 +12549,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G420" t="n">
-        <v>4.30683422088623</v>
+        <v>4.30683469772339</v>
       </c>
       <c r="H420" t="n">
         <v>32975</v>
@@ -12636,7 +12636,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G423" t="n">
-        <v>4.28046655654907</v>
+        <v>4.28046560287476</v>
       </c>
       <c r="H423" t="n">
         <v>7858</v>
@@ -12665,7 +12665,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G424" t="n">
-        <v>4.30683422088623</v>
+        <v>4.30683469772339</v>
       </c>
       <c r="H424" t="n">
         <v>1866</v>
@@ -12694,7 +12694,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G425" t="n">
-        <v>4.29804468154907</v>
+        <v>4.29804515838623</v>
       </c>
       <c r="H425" t="n">
         <v>2886</v>
@@ -12752,7 +12752,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G427" t="n">
-        <v>4.34199190139771</v>
+        <v>4.34199237823486</v>
       </c>
       <c r="H427" t="n">
         <v>6045</v>
@@ -12926,7 +12926,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G433" t="n">
-        <v>4.32441377639771</v>
+        <v>4.32441329956055</v>
       </c>
       <c r="H433" t="n">
         <v>1529</v>
@@ -13100,7 +13100,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G439" t="n">
-        <v>4.38593912124634</v>
+        <v>4.3859395980835</v>
       </c>
       <c r="H439" t="n">
         <v>2700</v>
@@ -13129,7 +13129,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G440" t="n">
-        <v>4.38593912124634</v>
+        <v>4.3859395980835</v>
       </c>
       <c r="H440" t="n">
         <v>100</v>
@@ -13158,7 +13158,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G441" t="n">
-        <v>4.30683422088623</v>
+        <v>4.30683469772339</v>
       </c>
       <c r="H441" t="n">
         <v>14413</v>
@@ -13187,7 +13187,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G442" t="n">
-        <v>4.30683422088623</v>
+        <v>4.30683469772339</v>
       </c>
       <c r="H442" t="n">
         <v>5600</v>
@@ -13245,7 +13245,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G444" t="n">
-        <v>4.34199190139771</v>
+        <v>4.34199237823486</v>
       </c>
       <c r="H444" t="n">
         <v>20</v>
@@ -13274,7 +13274,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G445" t="n">
-        <v>4.26288652420044</v>
+        <v>4.2628870010376</v>
       </c>
       <c r="H445" t="n">
         <v>2230</v>
@@ -13303,7 +13303,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G446" t="n">
-        <v>4.34199190139771</v>
+        <v>4.34199237823486</v>
       </c>
       <c r="H446" t="n">
         <v>1000</v>
@@ -13332,7 +13332,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G447" t="n">
-        <v>4.38593912124634</v>
+        <v>4.3859395980835</v>
       </c>
       <c r="H447" t="n">
         <v>20</v>
@@ -13361,7 +13361,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G448" t="n">
-        <v>4.41230773925781</v>
+        <v>4.41230821609497</v>
       </c>
       <c r="H448" t="n">
         <v>4280</v>
@@ -13448,7 +13448,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G451" t="n">
-        <v>4.30683422088623</v>
+        <v>4.30683469772339</v>
       </c>
       <c r="H451" t="n">
         <v>600</v>
@@ -13564,7 +13564,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G455" t="n">
-        <v>4.11346578598022</v>
+        <v>4.11346626281738</v>
       </c>
       <c r="H455" t="n">
         <v>1631</v>
@@ -13680,7 +13680,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G459" t="n">
-        <v>4.02557182312012</v>
+        <v>4.02557134628296</v>
       </c>
       <c r="H459" t="n">
         <v>4000</v>
@@ -13709,7 +13709,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G460" t="n">
-        <v>4.02557182312012</v>
+        <v>4.02557134628296</v>
       </c>
       <c r="H460" t="n">
         <v>1607</v>
@@ -13738,7 +13738,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G461" t="n">
-        <v>4.02557182312012</v>
+        <v>4.02557134628296</v>
       </c>
       <c r="H461" t="n">
         <v>1400</v>
@@ -13767,7 +13767,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G462" t="n">
-        <v>4.08709812164307</v>
+        <v>4.08709859848022</v>
       </c>
       <c r="H462" t="n">
         <v>155</v>
@@ -13854,7 +13854,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G465" t="n">
-        <v>4.26288652420044</v>
+        <v>4.2628870010376</v>
       </c>
       <c r="H465" t="n">
         <v>6017</v>
@@ -14057,7 +14057,7 @@
         <v>5</v>
       </c>
       <c r="G472" t="n">
-        <v>4.41898965835571</v>
+        <v>4.41899013519287</v>
       </c>
       <c r="H472" t="n">
         <v>6010</v>
@@ -14086,7 +14086,7 @@
         <v>5</v>
       </c>
       <c r="G473" t="n">
-        <v>4.41898965835571</v>
+        <v>4.41899013519287</v>
       </c>
       <c r="H473" t="n">
         <v>3807</v>
@@ -14434,7 +14434,7 @@
         <v>5</v>
       </c>
       <c r="G485" t="n">
-        <v>4.41898965835571</v>
+        <v>4.41899013519287</v>
       </c>
       <c r="H485" t="n">
         <v>7329</v>
@@ -14463,7 +14463,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G486" t="n">
-        <v>4.37479972839355</v>
+        <v>4.37480020523071</v>
       </c>
       <c r="H486" t="n">
         <v>1753</v>
@@ -14695,7 +14695,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G494" t="n">
-        <v>4.22455501556396</v>
+        <v>4.22455453872681</v>
       </c>
       <c r="H494" t="n">
         <v>1787</v>
@@ -14753,7 +14753,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G496" t="n">
-        <v>4.10966110229492</v>
+        <v>4.10966062545776</v>
       </c>
       <c r="H496" t="n">
         <v>2705</v>
@@ -14782,7 +14782,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G497" t="n">
-        <v>4.0301194190979</v>
+        <v>4.03011894226074</v>
       </c>
       <c r="H497" t="n">
         <v>4388</v>
@@ -14811,7 +14811,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G498" t="n">
-        <v>4.0301194190979</v>
+        <v>4.03011894226074</v>
       </c>
       <c r="H498" t="n">
         <v>18707</v>
@@ -14956,7 +14956,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G503" t="n">
-        <v>4.10966110229492</v>
+        <v>4.10966062545776</v>
       </c>
       <c r="H503" t="n">
         <v>3919</v>
@@ -14985,7 +14985,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G504" t="n">
-        <v>4.10966110229492</v>
+        <v>4.10966062545776</v>
       </c>
       <c r="H504" t="n">
         <v>0</v>
@@ -15043,7 +15043,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G506" t="n">
-        <v>4.10082292556763</v>
+        <v>4.10082244873047</v>
       </c>
       <c r="H506" t="n">
         <v>435</v>
@@ -15072,7 +15072,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G507" t="n">
-        <v>4.22455501556396</v>
+        <v>4.22455453872681</v>
       </c>
       <c r="H507" t="n">
         <v>450</v>
@@ -15188,7 +15188,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G511" t="n">
-        <v>4.10966110229492</v>
+        <v>4.10966062545776</v>
       </c>
       <c r="H511" t="n">
         <v>2700</v>
@@ -15217,7 +15217,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G512" t="n">
-        <v>4.10966110229492</v>
+        <v>4.10966062545776</v>
       </c>
       <c r="H512" t="n">
         <v>0</v>
@@ -15333,7 +15333,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G516" t="n">
-        <v>4.32177209854126</v>
+        <v>4.32177257537842</v>
       </c>
       <c r="H516" t="n">
         <v>2870</v>
@@ -15449,7 +15449,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G520" t="n">
-        <v>4.4896936416626</v>
+        <v>4.48969411849976</v>
       </c>
       <c r="H520" t="n">
         <v>1048</v>
@@ -15797,7 +15797,7 @@
         <v>5</v>
       </c>
       <c r="G532" t="n">
-        <v>4.41898965835571</v>
+        <v>4.41899013519287</v>
       </c>
       <c r="H532" t="n">
         <v>5500</v>
@@ -16000,7 +16000,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G539" t="n">
-        <v>4.41015148162842</v>
+        <v>4.41015195846558</v>
       </c>
       <c r="H539" t="n">
         <v>870</v>
@@ -16116,7 +16116,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G543" t="n">
-        <v>4.38363885879517</v>
+        <v>4.38363790512085</v>
       </c>
       <c r="H543" t="n">
         <v>902</v>
@@ -16203,7 +16203,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G546" t="n">
-        <v>4.33944845199585</v>
+        <v>4.33944797515869</v>
       </c>
       <c r="H546" t="n">
         <v>1600</v>
@@ -16232,7 +16232,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G547" t="n">
-        <v>4.33944845199585</v>
+        <v>4.33944797515869</v>
       </c>
       <c r="H547" t="n">
         <v>0</v>
@@ -16261,7 +16261,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G548" t="n">
-        <v>4.33944845199585</v>
+        <v>4.33944797515869</v>
       </c>
       <c r="H548" t="n">
         <v>0</v>
@@ -16406,7 +16406,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G553" t="n">
-        <v>4.31293439865112</v>
+        <v>4.31293487548828</v>
       </c>
       <c r="H553" t="n">
         <v>11439</v>
@@ -16551,7 +16551,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G558" t="n">
-        <v>4.10966110229492</v>
+        <v>4.10966062545776</v>
       </c>
       <c r="H558" t="n">
         <v>4550</v>
@@ -16638,7 +16638,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G561" t="n">
-        <v>4.15385055541992</v>
+        <v>4.15385103225708</v>
       </c>
       <c r="H561" t="n">
         <v>11912</v>
@@ -16667,7 +16667,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G562" t="n">
-        <v>4.10966110229492</v>
+        <v>4.10966062545776</v>
       </c>
       <c r="H562" t="n">
         <v>1123</v>
@@ -16783,7 +16783,7 @@
         <v>5</v>
       </c>
       <c r="G566" t="n">
-        <v>4.41898965835571</v>
+        <v>4.41899013519287</v>
       </c>
       <c r="H566" t="n">
         <v>23066</v>
@@ -17189,7 +17189,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G580" t="n">
-        <v>4.94926929473877</v>
+        <v>4.94926881790161</v>
       </c>
       <c r="H580" t="n">
         <v>3440</v>
@@ -17247,7 +17247,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G582" t="n">
-        <v>5.26743602752686</v>
+        <v>5.26743650436401</v>
       </c>
       <c r="H582" t="n">
         <v>19700</v>
@@ -17276,7 +17276,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G583" t="n">
-        <v>5.47954797744751</v>
+        <v>5.47954750061035</v>
       </c>
       <c r="H583" t="n">
         <v>51392</v>
@@ -17305,7 +17305,7 @@
         <v>6.03999996185303</v>
       </c>
       <c r="G584" t="n">
-        <v>5.33814001083374</v>
+        <v>5.3381404876709</v>
       </c>
       <c r="H584" t="n">
         <v>12438</v>
@@ -17363,7 +17363,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G586" t="n">
-        <v>5.47954797744751</v>
+        <v>5.47954750061035</v>
       </c>
       <c r="H586" t="n">
         <v>857</v>
@@ -17392,7 +17392,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G587" t="n">
-        <v>5.47954797744751</v>
+        <v>5.47954750061035</v>
       </c>
       <c r="H587" t="n">
         <v>16499</v>
@@ -17421,7 +17421,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G588" t="n">
-        <v>5.70933485031128</v>
+        <v>5.70933532714844</v>
       </c>
       <c r="H588" t="n">
         <v>1075</v>
@@ -17537,7 +17537,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G592" t="n">
-        <v>5.51489973068237</v>
+        <v>5.51489925384521</v>
       </c>
       <c r="H592" t="n">
         <v>637</v>
@@ -17566,7 +17566,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G593" t="n">
-        <v>5.56792783737183</v>
+        <v>5.56792736053467</v>
       </c>
       <c r="H593" t="n">
         <v>3180</v>
@@ -17595,7 +17595,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G594" t="n">
-        <v>5.56792783737183</v>
+        <v>5.56792736053467</v>
       </c>
       <c r="H594" t="n">
         <v>3910</v>
@@ -17653,7 +17653,7 @@
         <v>6.71999979019165</v>
       </c>
       <c r="G596" t="n">
-        <v>5.93912220001221</v>
+        <v>5.93912267684937</v>
       </c>
       <c r="H596" t="n">
         <v>3720</v>
@@ -17798,7 +17798,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G601" t="n">
-        <v>5.47954797744751</v>
+        <v>5.47954750061035</v>
       </c>
       <c r="H601" t="n">
         <v>2590</v>
@@ -17827,7 +17827,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G602" t="n">
-        <v>5.49722337722778</v>
+        <v>5.49722385406494</v>
       </c>
       <c r="H602" t="n">
         <v>2401</v>
@@ -17885,7 +17885,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G604" t="n">
-        <v>5.51489973068237</v>
+        <v>5.51489925384521</v>
       </c>
       <c r="H604" t="n">
         <v>946</v>
@@ -18059,7 +18059,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G610" t="n">
-        <v>5.70933485031128</v>
+        <v>5.70933532714844</v>
       </c>
       <c r="H610" t="n">
         <v>2183</v>
@@ -18233,7 +18233,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G616" t="n">
-        <v>5.88609457015991</v>
+        <v>5.88609504699707</v>
       </c>
       <c r="H616" t="n">
         <v>1889</v>
@@ -18262,7 +18262,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G617" t="n">
-        <v>5.92144680023193</v>
+        <v>5.92144632339478</v>
       </c>
       <c r="H617" t="n">
         <v>18955</v>
@@ -18349,7 +18349,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G620" t="n">
-        <v>5.47954797744751</v>
+        <v>5.47954750061035</v>
       </c>
       <c r="H620" t="n">
         <v>9540</v>
@@ -18552,7 +18552,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G627" t="n">
-        <v>6.00982666015625</v>
+        <v>6.00982713699341</v>
       </c>
       <c r="H627" t="n">
         <v>6922</v>
@@ -18581,7 +18581,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G628" t="n">
-        <v>5.88609457015991</v>
+        <v>5.88609504699707</v>
       </c>
       <c r="H628" t="n">
         <v>1335</v>
@@ -18610,7 +18610,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G629" t="n">
-        <v>5.92144680023193</v>
+        <v>5.92144632339478</v>
       </c>
       <c r="H629" t="n">
         <v>400</v>
@@ -18639,7 +18639,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G630" t="n">
-        <v>6.00982666015625</v>
+        <v>6.00982713699341</v>
       </c>
       <c r="H630" t="n">
         <v>16000</v>
@@ -18726,7 +18726,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G633" t="n">
-        <v>5.83306741714478</v>
+        <v>5.83306694030762</v>
       </c>
       <c r="H633" t="n">
         <v>2617</v>
@@ -18755,7 +18755,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G634" t="n">
-        <v>5.83306741714478</v>
+        <v>5.83306694030762</v>
       </c>
       <c r="H634" t="n">
         <v>0</v>
@@ -18784,7 +18784,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G635" t="n">
-        <v>5.83306741714478</v>
+        <v>5.83306694030762</v>
       </c>
       <c r="H635" t="n">
         <v>200</v>
@@ -18813,7 +18813,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G636" t="n">
-        <v>5.70933485031128</v>
+        <v>5.70933532714844</v>
       </c>
       <c r="H636" t="n">
         <v>250</v>
@@ -18900,7 +18900,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G639" t="n">
-        <v>5.5856032371521</v>
+        <v>5.58560371398926</v>
       </c>
       <c r="H639" t="n">
         <v>400</v>
@@ -18929,7 +18929,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G640" t="n">
-        <v>5.70933485031128</v>
+        <v>5.70933532714844</v>
       </c>
       <c r="H640" t="n">
         <v>150</v>
@@ -18958,7 +18958,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G641" t="n">
-        <v>5.79771518707275</v>
+        <v>5.7977147102356</v>
       </c>
       <c r="H641" t="n">
         <v>258</v>
@@ -18987,7 +18987,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G642" t="n">
-        <v>5.79771518707275</v>
+        <v>5.7977147102356</v>
       </c>
       <c r="H642" t="n">
         <v>1057</v>
@@ -19045,7 +19045,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G644" t="n">
-        <v>5.47954797744751</v>
+        <v>5.47954750061035</v>
       </c>
       <c r="H644" t="n">
         <v>1491</v>
@@ -19074,7 +19074,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G645" t="n">
-        <v>5.47954797744751</v>
+        <v>5.47954750061035</v>
       </c>
       <c r="H645" t="n">
         <v>1044</v>
@@ -19103,7 +19103,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G646" t="n">
-        <v>5.47954797744751</v>
+        <v>5.47954750061035</v>
       </c>
       <c r="H646" t="n">
         <v>300</v>
@@ -19132,7 +19132,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G647" t="n">
-        <v>5.3734917640686</v>
+        <v>5.37349224090576</v>
       </c>
       <c r="H647" t="n">
         <v>1250</v>
@@ -19161,7 +19161,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G648" t="n">
-        <v>5.26743602752686</v>
+        <v>5.26743650436401</v>
       </c>
       <c r="H648" t="n">
         <v>3000</v>
@@ -19306,7 +19306,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G653" t="n">
-        <v>5.1260290145874</v>
+        <v>5.12602853775024</v>
       </c>
       <c r="H653" t="n">
         <v>2025</v>
@@ -19335,7 +19335,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G654" t="n">
-        <v>4.94926929473877</v>
+        <v>4.94926881790161</v>
       </c>
       <c r="H654" t="n">
         <v>3137</v>
@@ -19364,7 +19364,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G655" t="n">
-        <v>4.94926929473877</v>
+        <v>4.94926881790161</v>
       </c>
       <c r="H655" t="n">
         <v>14439</v>
@@ -19451,7 +19451,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G658" t="n">
-        <v>5.1260290145874</v>
+        <v>5.12602853775024</v>
       </c>
       <c r="H658" t="n">
         <v>2873</v>
@@ -19509,7 +19509,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G660" t="n">
-        <v>5.23208475112915</v>
+        <v>5.23208427429199</v>
       </c>
       <c r="H660" t="n">
         <v>16216</v>
@@ -19596,7 +19596,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G663" t="n">
-        <v>5.47954797744751</v>
+        <v>5.47954750061035</v>
       </c>
       <c r="H663" t="n">
         <v>2792</v>
@@ -19973,7 +19973,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G676" t="n">
-        <v>4.24223041534424</v>
+        <v>4.2422308921814</v>
       </c>
       <c r="H676" t="n">
         <v>443</v>
@@ -20002,7 +20002,7 @@
         <v>5</v>
       </c>
       <c r="G677" t="n">
-        <v>4.41898965835571</v>
+        <v>4.41899013519287</v>
       </c>
       <c r="H677" t="n">
         <v>2692</v>
@@ -20060,7 +20060,7 @@
         <v>5</v>
       </c>
       <c r="G679" t="n">
-        <v>4.41898965835571</v>
+        <v>4.41899013519287</v>
       </c>
       <c r="H679" t="n">
         <v>8270</v>
@@ -20379,7 +20379,7 @@
         <v>5.5</v>
       </c>
       <c r="G690" t="n">
-        <v>4.86088895797729</v>
+        <v>4.86088943481445</v>
       </c>
       <c r="H690" t="n">
         <v>2318</v>
@@ -20437,7 +20437,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G692" t="n">
-        <v>4.87856531143188</v>
+        <v>4.87856483459473</v>
       </c>
       <c r="H692" t="n">
         <v>314</v>
@@ -20466,7 +20466,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G693" t="n">
-        <v>4.87856531143188</v>
+        <v>4.87856483459473</v>
       </c>
       <c r="H693" t="n">
         <v>0</v>
@@ -20524,7 +20524,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G695" t="n">
-        <v>4.87856531143188</v>
+        <v>4.87856483459473</v>
       </c>
       <c r="H695" t="n">
         <v>4531</v>
@@ -20582,7 +20582,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G697" t="n">
-        <v>4.94926929473877</v>
+        <v>4.94926881790161</v>
       </c>
       <c r="H697" t="n">
         <v>6290</v>
@@ -20611,7 +20611,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G698" t="n">
-        <v>4.94926929473877</v>
+        <v>4.94926881790161</v>
       </c>
       <c r="H698" t="n">
         <v>190</v>
@@ -20640,7 +20640,7 @@
         <v>5.5</v>
       </c>
       <c r="G699" t="n">
-        <v>4.86088895797729</v>
+        <v>4.86088943481445</v>
       </c>
       <c r="H699" t="n">
         <v>1100</v>
@@ -20727,7 +20727,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G702" t="n">
-        <v>4.94926929473877</v>
+        <v>4.94926881790161</v>
       </c>
       <c r="H702" t="n">
         <v>4149</v>
@@ -20814,7 +20814,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G705" t="n">
-        <v>5.14370441436768</v>
+        <v>5.14370489120483</v>
       </c>
       <c r="H705" t="n">
         <v>60299</v>
@@ -20843,7 +20843,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G706" t="n">
-        <v>5.1260290145874</v>
+        <v>5.12602853775024</v>
       </c>
       <c r="H706" t="n">
         <v>661</v>
@@ -20901,7 +20901,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G708" t="n">
-        <v>4.98462057113647</v>
+        <v>4.98462104797363</v>
       </c>
       <c r="H708" t="n">
         <v>1299</v>
@@ -20930,7 +20930,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G709" t="n">
-        <v>5.1260290145874</v>
+        <v>5.12602853775024</v>
       </c>
       <c r="H709" t="n">
         <v>6815</v>
@@ -20959,7 +20959,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G710" t="n">
-        <v>5.1260290145874</v>
+        <v>5.12602853775024</v>
       </c>
       <c r="H710" t="n">
         <v>0</v>
@@ -20988,7 +20988,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G711" t="n">
-        <v>5.14370441436768</v>
+        <v>5.14370489120483</v>
       </c>
       <c r="H711" t="n">
         <v>6657</v>
@@ -21017,7 +21017,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G712" t="n">
-        <v>5.14370441436768</v>
+        <v>5.14370489120483</v>
       </c>
       <c r="H712" t="n">
         <v>0</v>
@@ -21104,7 +21104,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G715" t="n">
-        <v>5.14370441436768</v>
+        <v>5.14370489120483</v>
       </c>
       <c r="H715" t="n">
         <v>3046</v>
@@ -21278,7 +21278,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G721" t="n">
-        <v>4.94926929473877</v>
+        <v>4.94926881790161</v>
       </c>
       <c r="H721" t="n">
         <v>277</v>
@@ -21365,7 +21365,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G724" t="n">
-        <v>5.24976062774658</v>
+        <v>5.24976015090942</v>
       </c>
       <c r="H724" t="n">
         <v>4500</v>
@@ -21626,7 +21626,7 @@
         <v>5.8600001335144</v>
       </c>
       <c r="G733" t="n">
-        <v>5.24438142776489</v>
+        <v>5.24438095092773</v>
       </c>
       <c r="H733" t="n">
         <v>1735</v>
@@ -21655,7 +21655,7 @@
         <v>5.8600001335144</v>
       </c>
       <c r="G734" t="n">
-        <v>5.24438142776489</v>
+        <v>5.24438095092773</v>
       </c>
       <c r="H734" t="n">
         <v>0</v>
@@ -21771,7 +21771,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G738" t="n">
-        <v>5.26227998733521</v>
+        <v>5.26228046417236</v>
       </c>
       <c r="H738" t="n">
         <v>40</v>
@@ -22148,7 +22148,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G751" t="n">
-        <v>4.99379634857178</v>
+        <v>4.99379587173462</v>
       </c>
       <c r="H751" t="n">
         <v>470</v>
@@ -22351,7 +22351,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G758" t="n">
-        <v>5.31597709655762</v>
+        <v>5.31597661972046</v>
       </c>
       <c r="H758" t="n">
         <v>1333</v>
@@ -22380,7 +22380,7 @@
         <v>6</v>
       </c>
       <c r="G759" t="n">
-        <v>5.36967372894287</v>
+        <v>5.36967325210571</v>
       </c>
       <c r="H759" t="n">
         <v>304</v>
@@ -22409,7 +22409,7 @@
         <v>6</v>
       </c>
       <c r="G760" t="n">
-        <v>5.36967372894287</v>
+        <v>5.36967325210571</v>
       </c>
       <c r="H760" t="n">
         <v>829</v>
@@ -22438,7 +22438,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G761" t="n">
-        <v>5.47706699371338</v>
+        <v>5.47706651687622</v>
       </c>
       <c r="H761" t="n">
         <v>270</v>
@@ -22641,7 +22641,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G768" t="n">
-        <v>5.72765207290649</v>
+        <v>5.72765159606934</v>
       </c>
       <c r="H768" t="n">
         <v>2958</v>
@@ -22699,7 +22699,7 @@
         <v>6.51999998092651</v>
       </c>
       <c r="G770" t="n">
-        <v>5.83504486083984</v>
+        <v>5.835045337677</v>
       </c>
       <c r="H770" t="n">
         <v>667</v>
@@ -22728,7 +22728,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G771" t="n">
-        <v>5.72765207290649</v>
+        <v>5.72765159606934</v>
       </c>
       <c r="H771" t="n">
         <v>678</v>
@@ -22757,7 +22757,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G772" t="n">
-        <v>5.72765207290649</v>
+        <v>5.72765159606934</v>
       </c>
       <c r="H772" t="n">
         <v>1540</v>
@@ -22844,7 +22844,7 @@
         <v>6.5</v>
       </c>
       <c r="G775" t="n">
-        <v>5.81714630126953</v>
+        <v>5.81714582443237</v>
       </c>
       <c r="H775" t="n">
         <v>11</v>
@@ -22902,7 +22902,7 @@
         <v>6.5</v>
       </c>
       <c r="G777" t="n">
-        <v>5.81714630126953</v>
+        <v>5.81714582443237</v>
       </c>
       <c r="H777" t="n">
         <v>6650</v>
@@ -23018,7 +23018,7 @@
         <v>6.73999977111816</v>
       </c>
       <c r="G781" t="n">
-        <v>6.03193330764771</v>
+        <v>6.03193283081055</v>
       </c>
       <c r="H781" t="n">
         <v>1012</v>
@@ -23105,7 +23105,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G784" t="n">
-        <v>6.08562994003296</v>
+        <v>6.08563041687012</v>
       </c>
       <c r="H784" t="n">
         <v>2889</v>
@@ -23250,7 +23250,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G789" t="n">
-        <v>5.88874197006226</v>
+        <v>5.8887414932251</v>
       </c>
       <c r="H789" t="n">
         <v>3581</v>
@@ -23308,7 +23308,7 @@
         <v>6.53999996185303</v>
       </c>
       <c r="G791" t="n">
-        <v>5.85294437408447</v>
+        <v>5.85294389724731</v>
       </c>
       <c r="H791" t="n">
         <v>31</v>
@@ -23337,7 +23337,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G792" t="n">
-        <v>5.72765207290649</v>
+        <v>5.72765159606934</v>
       </c>
       <c r="H792" t="n">
         <v>40050</v>
@@ -23482,7 +23482,7 @@
         <v>6.5</v>
       </c>
       <c r="G797" t="n">
-        <v>5.81714630126953</v>
+        <v>5.81714582443237</v>
       </c>
       <c r="H797" t="n">
         <v>1055</v>
@@ -23511,7 +23511,7 @@
         <v>6.5</v>
       </c>
       <c r="G798" t="n">
-        <v>5.81714630126953</v>
+        <v>5.81714582443237</v>
       </c>
       <c r="H798" t="n">
         <v>30000</v>
@@ -23598,7 +23598,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G801" t="n">
-        <v>5.88874197006226</v>
+        <v>5.8887414932251</v>
       </c>
       <c r="H801" t="n">
         <v>550</v>
@@ -23772,7 +23772,7 @@
         <v>6.42000007629395</v>
       </c>
       <c r="G807" t="n">
-        <v>5.74555063247681</v>
+        <v>5.74555110931396</v>
       </c>
       <c r="H807" t="n">
         <v>50</v>
@@ -23888,7 +23888,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G811" t="n">
-        <v>5.5486626625061</v>
+        <v>5.54866218566895</v>
       </c>
       <c r="H811" t="n">
         <v>1520</v>
@@ -23946,7 +23946,7 @@
         <v>5.8600001335144</v>
       </c>
       <c r="G813" t="n">
-        <v>5.24438142776489</v>
+        <v>5.24438095092773</v>
       </c>
       <c r="H813" t="n">
         <v>595</v>
@@ -23975,7 +23975,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G814" t="n">
-        <v>5.13698768615723</v>
+        <v>5.13698720932007</v>
       </c>
       <c r="H814" t="n">
         <v>33740</v>
@@ -24004,7 +24004,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G815" t="n">
-        <v>5.13698768615723</v>
+        <v>5.13698720932007</v>
       </c>
       <c r="H815" t="n">
         <v>0</v>
@@ -24033,7 +24033,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G816" t="n">
-        <v>5.35177421569824</v>
+        <v>5.3517746925354</v>
       </c>
       <c r="H816" t="n">
         <v>30550</v>
@@ -24062,7 +24062,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G817" t="n">
-        <v>4.83270645141602</v>
+        <v>4.83270597457886</v>
       </c>
       <c r="H817" t="n">
         <v>29376</v>
@@ -24178,7 +24178,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G821" t="n">
-        <v>4.83270645141602</v>
+        <v>4.83270597457886</v>
       </c>
       <c r="H821" t="n">
         <v>677</v>
@@ -24236,7 +24236,7 @@
         <v>6</v>
       </c>
       <c r="G823" t="n">
-        <v>5.36967372894287</v>
+        <v>5.36967325210571</v>
       </c>
       <c r="H823" t="n">
         <v>1900</v>
@@ -24265,7 +24265,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G824" t="n">
-        <v>5.47706699371338</v>
+        <v>5.47706651687622</v>
       </c>
       <c r="H824" t="n">
         <v>100</v>
@@ -24323,7 +24323,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G826" t="n">
-        <v>5.5486626625061</v>
+        <v>5.54866218566895</v>
       </c>
       <c r="H826" t="n">
         <v>610</v>
@@ -24352,7 +24352,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G827" t="n">
-        <v>5.5486626625061</v>
+        <v>5.54866218566895</v>
       </c>
       <c r="H827" t="n">
         <v>0</v>
@@ -24381,7 +24381,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G828" t="n">
-        <v>5.5486626625061</v>
+        <v>5.54866218566895</v>
       </c>
       <c r="H828" t="n">
         <v>600</v>
@@ -24410,7 +24410,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G829" t="n">
-        <v>5.5486626625061</v>
+        <v>5.54866218566895</v>
       </c>
       <c r="H829" t="n">
         <v>0</v>
@@ -24439,7 +24439,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G830" t="n">
-        <v>5.72765207290649</v>
+        <v>5.72765159606934</v>
       </c>
       <c r="H830" t="n">
         <v>1323</v>
@@ -24497,7 +24497,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G832" t="n">
-        <v>5.72765207290649</v>
+        <v>5.72765159606934</v>
       </c>
       <c r="H832" t="n">
         <v>420</v>
@@ -24700,7 +24700,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G839" t="n">
-        <v>5.5486626625061</v>
+        <v>5.54866218566895</v>
       </c>
       <c r="H839" t="n">
         <v>400</v>
@@ -24729,7 +24729,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G840" t="n">
-        <v>5.53076314926147</v>
+        <v>5.53076362609863</v>
       </c>
       <c r="H840" t="n">
         <v>422</v>
@@ -24903,7 +24903,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G846" t="n">
-        <v>5.72765207290649</v>
+        <v>5.72765159606934</v>
       </c>
       <c r="H846" t="n">
         <v>100</v>
@@ -24961,7 +24961,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G848" t="n">
-        <v>5.72765207290649</v>
+        <v>5.72765159606934</v>
       </c>
       <c r="H848" t="n">
         <v>1038</v>
@@ -25048,7 +25048,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G851" t="n">
-        <v>5.70975255966187</v>
+        <v>5.70975303649902</v>
       </c>
       <c r="H851" t="n">
         <v>961</v>
@@ -25077,7 +25077,7 @@
         <v>6.5</v>
       </c>
       <c r="G852" t="n">
-        <v>5.81714630126953</v>
+        <v>5.81714582443237</v>
       </c>
       <c r="H852" t="n">
         <v>263</v>
@@ -25106,7 +25106,7 @@
         <v>6.5</v>
       </c>
       <c r="G853" t="n">
-        <v>5.81714630126953</v>
+        <v>5.81714582443237</v>
       </c>
       <c r="H853" t="n">
         <v>1153</v>
@@ -25193,7 +25193,7 @@
         <v>6.42000007629395</v>
       </c>
       <c r="G856" t="n">
-        <v>5.74555063247681</v>
+        <v>5.74555110931396</v>
       </c>
       <c r="H856" t="n">
         <v>396</v>
@@ -25222,7 +25222,7 @@
         <v>6.51999998092651</v>
       </c>
       <c r="G857" t="n">
-        <v>5.83504486083984</v>
+        <v>5.835045337677</v>
       </c>
       <c r="H857" t="n">
         <v>100</v>
@@ -25251,7 +25251,7 @@
         <v>6.51999998092651</v>
       </c>
       <c r="G858" t="n">
-        <v>5.83504486083984</v>
+        <v>5.835045337677</v>
       </c>
       <c r="H858" t="n">
         <v>0</v>
@@ -25280,7 +25280,7 @@
         <v>6.51999998092651</v>
       </c>
       <c r="G859" t="n">
-        <v>5.83504486083984</v>
+        <v>5.835045337677</v>
       </c>
       <c r="H859" t="n">
         <v>0</v>
@@ -25396,7 +25396,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G863" t="n">
-        <v>5.88874197006226</v>
+        <v>5.8887414932251</v>
       </c>
       <c r="H863" t="n">
         <v>1364</v>
@@ -25454,7 +25454,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G865" t="n">
-        <v>5.88874197006226</v>
+        <v>5.8887414932251</v>
       </c>
       <c r="H865" t="n">
         <v>1988</v>
@@ -25541,7 +25541,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G868" t="n">
-        <v>6.08562994003296</v>
+        <v>6.08563041687012</v>
       </c>
       <c r="H868" t="n">
         <v>500</v>
@@ -25570,7 +25570,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G869" t="n">
-        <v>6.08562994003296</v>
+        <v>6.08563041687012</v>
       </c>
       <c r="H869" t="n">
         <v>0</v>
@@ -25860,7 +25860,7 @@
         <v>6.5</v>
       </c>
       <c r="G879" t="n">
-        <v>5.81714630126953</v>
+        <v>5.81714582443237</v>
       </c>
       <c r="H879" t="n">
         <v>314</v>
@@ -25918,7 +25918,7 @@
         <v>6.73999977111816</v>
       </c>
       <c r="G881" t="n">
-        <v>6.03193330764771</v>
+        <v>6.03193283081055</v>
       </c>
       <c r="H881" t="n">
         <v>400</v>
@@ -25976,7 +25976,7 @@
         <v>6.71999979019165</v>
       </c>
       <c r="G883" t="n">
-        <v>6.01403379440308</v>
+        <v>6.01403427124023</v>
       </c>
       <c r="H883" t="n">
         <v>200</v>
@@ -26005,7 +26005,7 @@
         <v>6.71999979019165</v>
       </c>
       <c r="G884" t="n">
-        <v>6.01403379440308</v>
+        <v>6.01403427124023</v>
       </c>
       <c r="H884" t="n">
         <v>0</v>
@@ -26150,7 +26150,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G889" t="n">
-        <v>5.72765207290649</v>
+        <v>5.72765159606934</v>
       </c>
       <c r="H889" t="n">
         <v>1703</v>
@@ -26179,7 +26179,7 @@
         <v>6.5</v>
       </c>
       <c r="G890" t="n">
-        <v>5.81714630126953</v>
+        <v>5.81714582443237</v>
       </c>
       <c r="H890" t="n">
         <v>662</v>
@@ -26208,7 +26208,7 @@
         <v>6.71999979019165</v>
       </c>
       <c r="G891" t="n">
-        <v>6.01403379440308</v>
+        <v>6.01403427124023</v>
       </c>
       <c r="H891" t="n">
         <v>155</v>
@@ -26237,7 +26237,7 @@
         <v>6.71999979019165</v>
       </c>
       <c r="G892" t="n">
-        <v>6.01403379440308</v>
+        <v>6.01403427124023</v>
       </c>
       <c r="H892" t="n">
         <v>0</v>
@@ -26266,7 +26266,7 @@
         <v>6.71999979019165</v>
       </c>
       <c r="G893" t="n">
-        <v>6.01403379440308</v>
+        <v>6.01403427124023</v>
       </c>
       <c r="H893" t="n">
         <v>0</v>
@@ -26556,7 +26556,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G903" t="n">
-        <v>6.98057556152344</v>
+        <v>6.9805760383606</v>
       </c>
       <c r="H903" t="n">
         <v>2180</v>
@@ -26614,7 +26614,7 @@
         <v>7.57999992370605</v>
       </c>
       <c r="G905" t="n">
-        <v>6.78368759155273</v>
+        <v>6.78368711471558</v>
       </c>
       <c r="H905" t="n">
         <v>2196</v>
@@ -26701,7 +26701,7 @@
         <v>7.03999996185303</v>
       </c>
       <c r="G908" t="n">
-        <v>6.30041694641113</v>
+        <v>6.30041646957397</v>
       </c>
       <c r="H908" t="n">
         <v>5650</v>
@@ -26759,7 +26759,7 @@
         <v>7.1399998664856</v>
       </c>
       <c r="G910" t="n">
-        <v>6.38991117477417</v>
+        <v>6.38991165161133</v>
       </c>
       <c r="H910" t="n">
         <v>1158</v>
@@ -26962,7 +26962,7 @@
         <v>7.26000022888184</v>
       </c>
       <c r="G917" t="n">
-        <v>6.49730491638184</v>
+        <v>6.49730539321899</v>
       </c>
       <c r="H917" t="n">
         <v>3000</v>
@@ -26991,7 +26991,7 @@
         <v>7.42000007629395</v>
       </c>
       <c r="G918" t="n">
-        <v>6.64049673080444</v>
+        <v>6.64049625396729</v>
       </c>
       <c r="H918" t="n">
         <v>2331</v>
@@ -27078,7 +27078,7 @@
         <v>7.34000015258789</v>
       </c>
       <c r="G921" t="n">
-        <v>6.56890058517456</v>
+        <v>6.56890106201172</v>
       </c>
       <c r="H921" t="n">
         <v>250</v>
@@ -27136,7 +27136,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G923" t="n">
-        <v>6.80158615112305</v>
+        <v>6.80158662796021</v>
       </c>
       <c r="H923" t="n">
         <v>2203</v>
@@ -27397,7 +27397,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G932" t="n">
-        <v>6.80158615112305</v>
+        <v>6.80158662796021</v>
       </c>
       <c r="H932" t="n">
         <v>2264</v>
@@ -27455,7 +27455,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G934" t="n">
-        <v>6.80158615112305</v>
+        <v>6.80158662796021</v>
       </c>
       <c r="H934" t="n">
         <v>1250</v>
@@ -27513,7 +27513,7 @@
         <v>7.34000015258789</v>
       </c>
       <c r="G936" t="n">
-        <v>6.56890058517456</v>
+        <v>6.56890106201172</v>
       </c>
       <c r="H936" t="n">
         <v>75</v>
@@ -27687,7 +27687,7 @@
         <v>7.26000022888184</v>
       </c>
       <c r="G942" t="n">
-        <v>6.49730491638184</v>
+        <v>6.49730539321899</v>
       </c>
       <c r="H942" t="n">
         <v>4218</v>
@@ -27716,7 +27716,7 @@
         <v>7.26000022888184</v>
       </c>
       <c r="G943" t="n">
-        <v>6.49730491638184</v>
+        <v>6.49730539321899</v>
       </c>
       <c r="H943" t="n">
         <v>0</v>
@@ -27745,7 +27745,7 @@
         <v>7.26000022888184</v>
       </c>
       <c r="G944" t="n">
-        <v>6.49730491638184</v>
+        <v>6.49730539321899</v>
       </c>
       <c r="H944" t="n">
         <v>0</v>
@@ -27803,7 +27803,7 @@
         <v>7.21999979019165</v>
       </c>
       <c r="G946" t="n">
-        <v>6.46150732040405</v>
+        <v>6.46150684356689</v>
       </c>
       <c r="H946" t="n">
         <v>103974</v>
@@ -27832,7 +27832,7 @@
         <v>7.21999979019165</v>
       </c>
       <c r="G947" t="n">
-        <v>6.46150732040405</v>
+        <v>6.46150684356689</v>
       </c>
       <c r="H947" t="n">
         <v>574</v>
@@ -28238,7 +28238,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G961" t="n">
-        <v>6.08562994003296</v>
+        <v>6.08563041687012</v>
       </c>
       <c r="H961" t="n">
         <v>1113</v>
@@ -28557,7 +28557,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G972" t="n">
-        <v>6.08562994003296</v>
+        <v>6.08563041687012</v>
       </c>
       <c r="H972" t="n">
         <v>250</v>
@@ -30065,7 +30065,7 @@
         <v>7.25</v>
       </c>
       <c r="G1024" t="n">
-        <v>6.48835563659668</v>
+        <v>6.48835515975952</v>
       </c>
       <c r="H1024" t="n">
         <v>712</v>
@@ -30181,7 +30181,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G1028" t="n">
-        <v>6.84633350372314</v>
+        <v>6.8463339805603</v>
       </c>
       <c r="H1028" t="n">
         <v>12728</v>
@@ -30210,7 +30210,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G1029" t="n">
-        <v>6.98057556152344</v>
+        <v>6.9805760383606</v>
       </c>
       <c r="H1029" t="n">
         <v>238</v>
@@ -30239,7 +30239,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G1030" t="n">
-        <v>6.98057556152344</v>
+        <v>6.9805760383606</v>
       </c>
       <c r="H1030" t="n">
         <v>1</v>
@@ -30268,7 +30268,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G1031" t="n">
-        <v>6.98057556152344</v>
+        <v>6.9805760383606</v>
       </c>
       <c r="H1031" t="n">
         <v>100</v>
@@ -30326,7 +30326,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G1033" t="n">
-        <v>6.75683927536011</v>
+        <v>6.75683975219727</v>
       </c>
       <c r="H1033" t="n">
         <v>670</v>
@@ -30355,7 +30355,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G1034" t="n">
-        <v>6.75683927536011</v>
+        <v>6.75683975219727</v>
       </c>
       <c r="H1034" t="n">
         <v>0</v>
@@ -30384,7 +30384,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G1035" t="n">
-        <v>6.75683927536011</v>
+        <v>6.75683975219727</v>
       </c>
       <c r="H1035" t="n">
         <v>0</v>
@@ -30413,7 +30413,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G1036" t="n">
-        <v>6.75683927536011</v>
+        <v>6.75683975219727</v>
       </c>
       <c r="H1036" t="n">
         <v>0</v>
@@ -30442,7 +30442,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G1037" t="n">
-        <v>6.98057556152344</v>
+        <v>6.9805760383606</v>
       </c>
       <c r="H1037" t="n">
         <v>500</v>
@@ -30471,7 +30471,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G1038" t="n">
-        <v>6.80158615112305</v>
+        <v>6.80158662796021</v>
       </c>
       <c r="H1038" t="n">
         <v>730</v>
@@ -30500,7 +30500,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G1039" t="n">
-        <v>6.80158615112305</v>
+        <v>6.80158662796021</v>
       </c>
       <c r="H1039" t="n">
         <v>0</v>
@@ -30558,7 +30558,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G1041" t="n">
-        <v>6.80158615112305</v>
+        <v>6.80158662796021</v>
       </c>
       <c r="H1041" t="n">
         <v>13</v>
@@ -30587,7 +30587,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G1042" t="n">
-        <v>6.80158615112305</v>
+        <v>6.80158662796021</v>
       </c>
       <c r="H1042" t="n">
         <v>0</v>
@@ -30616,7 +30616,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G1043" t="n">
-        <v>6.80158615112305</v>
+        <v>6.80158662796021</v>
       </c>
       <c r="H1043" t="n">
         <v>0</v>
@@ -30645,7 +30645,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G1044" t="n">
-        <v>6.80158615112305</v>
+        <v>6.80158662796021</v>
       </c>
       <c r="H1044" t="n">
         <v>0</v>
@@ -30674,7 +30674,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G1045" t="n">
-        <v>6.80158615112305</v>
+        <v>6.80158662796021</v>
       </c>
       <c r="H1045" t="n">
         <v>0</v>
@@ -30703,7 +30703,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G1046" t="n">
-        <v>6.80158615112305</v>
+        <v>6.80158662796021</v>
       </c>
       <c r="H1046" t="n">
         <v>0</v>
@@ -30732,7 +30732,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G1047" t="n">
-        <v>6.80158615112305</v>
+        <v>6.80158662796021</v>
       </c>
       <c r="H1047" t="n">
         <v>0</v>
@@ -30761,7 +30761,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G1048" t="n">
-        <v>6.98057556152344</v>
+        <v>6.9805760383606</v>
       </c>
       <c r="H1048" t="n">
         <v>601</v>
@@ -30790,7 +30790,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G1049" t="n">
-        <v>6.84633350372314</v>
+        <v>6.8463339805603</v>
       </c>
       <c r="H1049" t="n">
         <v>100</v>
@@ -30819,7 +30819,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G1050" t="n">
-        <v>6.98057556152344</v>
+        <v>6.9805760383606</v>
       </c>
       <c r="H1050" t="n">
         <v>460</v>
@@ -30848,7 +30848,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G1051" t="n">
-        <v>6.98057556152344</v>
+        <v>6.9805760383606</v>
       </c>
       <c r="H1051" t="n">
         <v>125</v>
@@ -30877,7 +30877,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G1052" t="n">
-        <v>6.98057556152344</v>
+        <v>6.9805760383606</v>
       </c>
       <c r="H1052" t="n">
         <v>0</v>
@@ -30906,7 +30906,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G1053" t="n">
-        <v>6.80158615112305</v>
+        <v>6.80158662796021</v>
       </c>
       <c r="H1053" t="n">
         <v>1684</v>
@@ -31080,7 +31080,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G1059" t="n">
-        <v>6.75683927536011</v>
+        <v>6.75683975219727</v>
       </c>
       <c r="H1059" t="n">
         <v>400</v>
@@ -31109,7 +31109,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G1060" t="n">
-        <v>6.75683927536011</v>
+        <v>6.75683975219727</v>
       </c>
       <c r="H1060" t="n">
         <v>0</v>
@@ -31138,7 +31138,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G1061" t="n">
-        <v>6.75683927536011</v>
+        <v>6.75683975219727</v>
       </c>
       <c r="H1061" t="n">
         <v>0</v>
@@ -31602,7 +31602,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G1077" t="n">
-        <v>5.86189365386963</v>
+        <v>5.86189413070679</v>
       </c>
       <c r="H1077" t="n">
         <v>846</v>
@@ -31631,7 +31631,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G1078" t="n">
-        <v>5.72765207290649</v>
+        <v>5.72765159606934</v>
       </c>
       <c r="H1078" t="n">
         <v>2019</v>
@@ -31660,7 +31660,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G1079" t="n">
-        <v>5.86189365386963</v>
+        <v>5.86189413070679</v>
       </c>
       <c r="H1079" t="n">
         <v>100</v>
@@ -31747,7 +31747,7 @@
         <v>6</v>
       </c>
       <c r="G1082" t="n">
-        <v>5.36967372894287</v>
+        <v>5.36967325210571</v>
       </c>
       <c r="H1082" t="n">
         <v>11354</v>
@@ -31776,7 +31776,7 @@
         <v>6</v>
       </c>
       <c r="G1083" t="n">
-        <v>5.36967372894287</v>
+        <v>5.36967325210571</v>
       </c>
       <c r="H1083" t="n">
         <v>25500</v>
@@ -31805,7 +31805,7 @@
         <v>6</v>
       </c>
       <c r="G1084" t="n">
-        <v>5.36967372894287</v>
+        <v>5.36967325210571</v>
       </c>
       <c r="H1084" t="n">
         <v>0</v>
@@ -31863,7 +31863,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G1086" t="n">
-        <v>5.32492637634277</v>
+        <v>5.32492589950562</v>
       </c>
       <c r="H1086" t="n">
         <v>6465</v>
@@ -31892,7 +31892,7 @@
         <v>6</v>
       </c>
       <c r="G1087" t="n">
-        <v>5.36967372894287</v>
+        <v>5.36967325210571</v>
       </c>
       <c r="H1087" t="n">
         <v>6931</v>
@@ -31921,7 +31921,7 @@
         <v>6</v>
       </c>
       <c r="G1088" t="n">
-        <v>5.36967372894287</v>
+        <v>5.36967325210571</v>
       </c>
       <c r="H1088" t="n">
         <v>0</v>
@@ -31950,7 +31950,7 @@
         <v>6</v>
       </c>
       <c r="G1089" t="n">
-        <v>5.36967372894287</v>
+        <v>5.36967325210571</v>
       </c>
       <c r="H1089" t="n">
         <v>0</v>
@@ -31979,7 +31979,7 @@
         <v>6</v>
       </c>
       <c r="G1090" t="n">
-        <v>5.36967372894287</v>
+        <v>5.36967325210571</v>
       </c>
       <c r="H1090" t="n">
         <v>850</v>
@@ -32008,7 +32008,7 @@
         <v>6</v>
       </c>
       <c r="G1091" t="n">
-        <v>5.36967372894287</v>
+        <v>5.36967325210571</v>
       </c>
       <c r="H1091" t="n">
         <v>240</v>
@@ -32037,7 +32037,7 @@
         <v>6</v>
       </c>
       <c r="G1092" t="n">
-        <v>5.36967372894287</v>
+        <v>5.36967325210571</v>
       </c>
       <c r="H1092" t="n">
         <v>650</v>
@@ -32066,7 +32066,7 @@
         <v>6</v>
       </c>
       <c r="G1093" t="n">
-        <v>5.36967372894287</v>
+        <v>5.36967325210571</v>
       </c>
       <c r="H1093" t="n">
         <v>675</v>
@@ -32095,7 +32095,7 @@
         <v>6</v>
       </c>
       <c r="G1094" t="n">
-        <v>5.36967372894287</v>
+        <v>5.36967325210571</v>
       </c>
       <c r="H1094" t="n">
         <v>0</v>
@@ -32124,7 +32124,7 @@
         <v>6</v>
       </c>
       <c r="G1095" t="n">
-        <v>5.36967372894287</v>
+        <v>5.36967325210571</v>
       </c>
       <c r="H1095" t="n">
         <v>0</v>
@@ -32414,7 +32414,7 @@
         <v>6.25</v>
       </c>
       <c r="G1105" t="n">
-        <v>5.5934100151062</v>
+        <v>5.59340953826904</v>
       </c>
       <c r="H1105" t="n">
         <v>14260</v>
@@ -32443,7 +32443,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G1106" t="n">
-        <v>5.5486626625061</v>
+        <v>5.54866218566895</v>
       </c>
       <c r="H1106" t="n">
         <v>39658</v>
@@ -32559,7 +32559,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G1110" t="n">
-        <v>5.5486626625061</v>
+        <v>5.54866218566895</v>
       </c>
       <c r="H1110" t="n">
         <v>21380</v>
@@ -32617,7 +32617,7 @@
         <v>6.5</v>
       </c>
       <c r="G1112" t="n">
-        <v>5.81714630126953</v>
+        <v>5.81714582443237</v>
       </c>
       <c r="H1112" t="n">
         <v>29853</v>
@@ -32646,7 +32646,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G1113" t="n">
-        <v>5.72765207290649</v>
+        <v>5.72765159606934</v>
       </c>
       <c r="H1113" t="n">
         <v>31724</v>
@@ -32675,7 +32675,7 @@
         <v>6.5</v>
       </c>
       <c r="G1114" t="n">
-        <v>5.81714630126953</v>
+        <v>5.81714582443237</v>
       </c>
       <c r="H1114" t="n">
         <v>15604</v>
@@ -32791,7 +32791,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G1118" t="n">
-        <v>6.08562994003296</v>
+        <v>6.08563041687012</v>
       </c>
       <c r="H1118" t="n">
         <v>46505</v>
@@ -32965,7 +32965,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G1124" t="n">
-        <v>6.75683927536011</v>
+        <v>6.75683975219727</v>
       </c>
       <c r="H1124" t="n">
         <v>52998</v>
@@ -53967,6 +53967,35 @@
         <v>1818</v>
       </c>
       <c r="I1848" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1849">
+      <c r="A1849" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1849" s="1" t="n">
+        <v>46317.2916666667</v>
+      </c>
+      <c r="C1849" t="n">
+        <v>2.27999997138977</v>
+      </c>
+      <c r="D1849" t="n">
+        <v>2.27999997138977</v>
+      </c>
+      <c r="E1849" t="n">
+        <v>2.25999999046326</v>
+      </c>
+      <c r="F1849" t="n">
+        <v>2.25999999046326</v>
+      </c>
+      <c r="G1849" t="n">
+        <v>2.25999999046326</v>
+      </c>
+      <c r="H1849" t="n">
+        <v>1277</v>
+      </c>
+      <c r="I1849" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/PTR.MI.xlsx
+++ b/data/PTR.MI.xlsx
@@ -485,7 +485,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G4" t="n">
-        <v>3.22012805938721</v>
+        <v>3.22012782096863</v>
       </c>
       <c r="H4" t="n">
         <v>98299</v>
@@ -543,7 +543,7 @@
         <v>3.69250011444092</v>
       </c>
       <c r="G6" t="n">
-        <v>3.20493912696838</v>
+        <v>3.20493865013123</v>
       </c>
       <c r="H6" t="n">
         <v>56036</v>
@@ -572,7 +572,7 @@
         <v>3.56850004196167</v>
       </c>
       <c r="G7" t="n">
-        <v>3.0973117351532</v>
+        <v>3.09731197357178</v>
       </c>
       <c r="H7" t="n">
         <v>71079</v>
@@ -601,7 +601,7 @@
         <v>3.5864999294281</v>
       </c>
       <c r="G8" t="n">
-        <v>3.11293482780457</v>
+        <v>3.11293458938599</v>
       </c>
       <c r="H8" t="n">
         <v>37148</v>
@@ -659,7 +659,7 @@
         <v>3.43199992179871</v>
       </c>
       <c r="G10" t="n">
-        <v>2.978835105896</v>
+        <v>2.97883534431458</v>
       </c>
       <c r="H10" t="n">
         <v>69299</v>
@@ -688,7 +688,7 @@
         <v>3.47849988937378</v>
       </c>
       <c r="G11" t="n">
-        <v>3.01919555664062</v>
+        <v>3.01919531822205</v>
       </c>
       <c r="H11" t="n">
         <v>324435</v>
@@ -717,7 +717,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G12" t="n">
-        <v>3.08125448226929</v>
+        <v>3.08125424385071</v>
       </c>
       <c r="H12" t="n">
         <v>29251</v>
@@ -775,7 +775,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G14" t="n">
-        <v>3.12465262413025</v>
+        <v>3.12465238571167</v>
       </c>
       <c r="H14" t="n">
         <v>10463</v>
@@ -862,7 +862,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G17" t="n">
-        <v>3.0899338722229</v>
+        <v>3.08993434906006</v>
       </c>
       <c r="H17" t="n">
         <v>939</v>
@@ -920,7 +920,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G19" t="n">
-        <v>3.13333201408386</v>
+        <v>3.13333177566528</v>
       </c>
       <c r="H19" t="n">
         <v>26321</v>
@@ -949,7 +949,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G20" t="n">
-        <v>3.12465262413025</v>
+        <v>3.12465238571167</v>
       </c>
       <c r="H20" t="n">
         <v>1924</v>
@@ -978,7 +978,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G21" t="n">
-        <v>3.1159725189209</v>
+        <v>3.11597275733948</v>
       </c>
       <c r="H21" t="n">
         <v>210</v>
@@ -1007,7 +1007,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G22" t="n">
-        <v>3.09861373901367</v>
+        <v>3.09861350059509</v>
       </c>
       <c r="H22" t="n">
         <v>7918</v>
@@ -1036,7 +1036,7 @@
         <v>3.49850010871887</v>
       </c>
       <c r="G23" t="n">
-        <v>3.03655433654785</v>
+        <v>3.03655457496643</v>
       </c>
       <c r="H23" t="n">
         <v>800</v>
@@ -1123,7 +1123,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G26" t="n">
-        <v>2.96841979026794</v>
+        <v>2.96842002868652</v>
       </c>
       <c r="H26" t="n">
         <v>3800</v>
@@ -1152,7 +1152,7 @@
         <v>3.35050010681152</v>
       </c>
       <c r="G27" t="n">
-        <v>2.90809655189514</v>
+        <v>2.90809679031372</v>
       </c>
       <c r="H27" t="n">
         <v>9955</v>
@@ -1210,7 +1210,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G29" t="n">
-        <v>3.08125448226929</v>
+        <v>3.08125424385071</v>
       </c>
       <c r="H29" t="n">
         <v>12055</v>
@@ -1239,7 +1239,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G30" t="n">
-        <v>3.0899338722229</v>
+        <v>3.08993434906006</v>
       </c>
       <c r="H30" t="n">
         <v>11148</v>
@@ -1268,7 +1268,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G31" t="n">
-        <v>3.0899338722229</v>
+        <v>3.08993434906006</v>
       </c>
       <c r="H31" t="n">
         <v>1210</v>
@@ -1297,7 +1297,7 @@
         <v>3.48200011253357</v>
       </c>
       <c r="G32" t="n">
-        <v>3.02223324775696</v>
+        <v>3.02223348617554</v>
       </c>
       <c r="H32" t="n">
         <v>904</v>
@@ -1326,7 +1326,7 @@
         <v>3.48200011253357</v>
       </c>
       <c r="G33" t="n">
-        <v>3.02223324775696</v>
+        <v>3.02223348617554</v>
       </c>
       <c r="H33" t="n">
         <v>432</v>
@@ -1384,7 +1384,7 @@
         <v>3.5</v>
       </c>
       <c r="G35" t="n">
-        <v>3.0378565788269</v>
+        <v>3.03785634040833</v>
       </c>
       <c r="H35" t="n">
         <v>1400</v>
@@ -1413,7 +1413,7 @@
         <v>3.46499991416931</v>
       </c>
       <c r="G36" t="n">
-        <v>3.00747799873352</v>
+        <v>3.00747776031494</v>
       </c>
       <c r="H36" t="n">
         <v>1547</v>
@@ -1471,7 +1471,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G38" t="n">
-        <v>3.19408917427063</v>
+        <v>3.19408941268921</v>
       </c>
       <c r="H38" t="n">
         <v>32777</v>
@@ -1500,7 +1500,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G39" t="n">
-        <v>3.21144843101501</v>
+        <v>3.21144866943359</v>
       </c>
       <c r="H39" t="n">
         <v>28455</v>
@@ -1558,7 +1558,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G41" t="n">
-        <v>3.42843794822693</v>
+        <v>3.42843818664551</v>
       </c>
       <c r="H41" t="n">
         <v>44559</v>
@@ -1616,7 +1616,7 @@
         <v>3.82500004768372</v>
       </c>
       <c r="G43" t="n">
-        <v>3.31994318962097</v>
+        <v>3.31994342803955</v>
       </c>
       <c r="H43" t="n">
         <v>5962</v>
@@ -1703,7 +1703,7 @@
         <v>3.71499991416931</v>
       </c>
       <c r="G46" t="n">
-        <v>3.22446775436401</v>
+        <v>3.22446751594543</v>
       </c>
       <c r="H46" t="n">
         <v>3406</v>
@@ -1732,7 +1732,7 @@
         <v>3.64499998092651</v>
       </c>
       <c r="G47" t="n">
-        <v>3.16371059417725</v>
+        <v>3.16371035575867</v>
       </c>
       <c r="H47" t="n">
         <v>3589</v>
@@ -1761,7 +1761,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G48" t="n">
-        <v>3.15069127082825</v>
+        <v>3.15069150924683</v>
       </c>
       <c r="H48" t="n">
         <v>190</v>
@@ -1790,7 +1790,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G49" t="n">
-        <v>3.21144843101501</v>
+        <v>3.21144866943359</v>
       </c>
       <c r="H49" t="n">
         <v>17100</v>
@@ -1819,7 +1819,7 @@
         <v>3.71499991416931</v>
       </c>
       <c r="G50" t="n">
-        <v>3.22446775436401</v>
+        <v>3.22446751594543</v>
       </c>
       <c r="H50" t="n">
         <v>7667</v>
@@ -1877,7 +1877,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G52" t="n">
-        <v>3.21144843101501</v>
+        <v>3.21144866943359</v>
       </c>
       <c r="H52" t="n">
         <v>49416</v>
@@ -1935,7 +1935,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G54" t="n">
-        <v>3.21144843101501</v>
+        <v>3.21144866943359</v>
       </c>
       <c r="H54" t="n">
         <v>4498</v>
@@ -1993,7 +1993,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G56" t="n">
-        <v>3.15069127082825</v>
+        <v>3.15069150924683</v>
       </c>
       <c r="H56" t="n">
         <v>6760</v>
@@ -2022,7 +2022,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G57" t="n">
-        <v>3.15069127082825</v>
+        <v>3.15069150924683</v>
       </c>
       <c r="H57" t="n">
         <v>100</v>
@@ -2080,7 +2080,7 @@
         <v>3.66499996185303</v>
       </c>
       <c r="G59" t="n">
-        <v>3.18106985092163</v>
+        <v>3.18106961250305</v>
       </c>
       <c r="H59" t="n">
         <v>20</v>
@@ -2138,7 +2138,7 @@
         <v>3.66499996185303</v>
       </c>
       <c r="G61" t="n">
-        <v>3.18106985092163</v>
+        <v>3.18106961250305</v>
       </c>
       <c r="H61" t="n">
         <v>27542</v>
@@ -2167,7 +2167,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G62" t="n">
-        <v>3.21144843101501</v>
+        <v>3.21144866943359</v>
       </c>
       <c r="H62" t="n">
         <v>20</v>
@@ -2225,7 +2225,7 @@
         <v>3.5550000667572</v>
       </c>
       <c r="G64" t="n">
-        <v>3.08559417724609</v>
+        <v>3.08559465408325</v>
       </c>
       <c r="H64" t="n">
         <v>550</v>
@@ -2254,7 +2254,7 @@
         <v>3.5550000667572</v>
       </c>
       <c r="G65" t="n">
-        <v>3.08559417724609</v>
+        <v>3.08559465408325</v>
       </c>
       <c r="H65" t="n">
         <v>2547</v>
@@ -2283,7 +2283,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G66" t="n">
-        <v>3.09861373901367</v>
+        <v>3.09861350059509</v>
       </c>
       <c r="H66" t="n">
         <v>4020</v>
@@ -2312,7 +2312,7 @@
         <v>3.63499999046326</v>
       </c>
       <c r="G67" t="n">
-        <v>3.15503120422363</v>
+        <v>3.15503096580505</v>
       </c>
       <c r="H67" t="n">
         <v>1440</v>
@@ -2341,7 +2341,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G68" t="n">
-        <v>3.12465262413025</v>
+        <v>3.12465238571167</v>
       </c>
       <c r="H68" t="n">
         <v>2020</v>
@@ -2370,7 +2370,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G69" t="n">
-        <v>3.12465262413025</v>
+        <v>3.12465238571167</v>
       </c>
       <c r="H69" t="n">
         <v>7428</v>
@@ -2428,7 +2428,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G71" t="n">
-        <v>3.21144843101501</v>
+        <v>3.21144866943359</v>
       </c>
       <c r="H71" t="n">
         <v>2275</v>
@@ -2457,7 +2457,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G72" t="n">
-        <v>3.12465262413025</v>
+        <v>3.12465238571167</v>
       </c>
       <c r="H72" t="n">
         <v>29395</v>
@@ -2486,7 +2486,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G73" t="n">
-        <v>3.08125448226929</v>
+        <v>3.08125424385071</v>
       </c>
       <c r="H73" t="n">
         <v>22487</v>
@@ -2515,7 +2515,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G74" t="n">
-        <v>3.08125448226929</v>
+        <v>3.08125424385071</v>
       </c>
       <c r="H74" t="n">
         <v>6950</v>
@@ -2544,7 +2544,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G75" t="n">
-        <v>3.1159725189209</v>
+        <v>3.11597275733948</v>
       </c>
       <c r="H75" t="n">
         <v>5620</v>
@@ -2573,7 +2573,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G76" t="n">
-        <v>3.1159725189209</v>
+        <v>3.11597275733948</v>
       </c>
       <c r="H76" t="n">
         <v>609</v>
@@ -2602,7 +2602,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G77" t="n">
-        <v>3.08125448226929</v>
+        <v>3.08125424385071</v>
       </c>
       <c r="H77" t="n">
         <v>1858</v>
@@ -2631,7 +2631,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G78" t="n">
-        <v>3.12465262413025</v>
+        <v>3.12465238571167</v>
       </c>
       <c r="H78" t="n">
         <v>908</v>
@@ -2892,7 +2892,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G87" t="n">
-        <v>3.37636065483093</v>
+        <v>3.37636041641235</v>
       </c>
       <c r="H87" t="n">
         <v>25644</v>
@@ -2921,7 +2921,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G88" t="n">
-        <v>3.42843794822693</v>
+        <v>3.42843818664551</v>
       </c>
       <c r="H88" t="n">
         <v>79090</v>
@@ -2950,7 +2950,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G89" t="n">
-        <v>3.42843794822693</v>
+        <v>3.42843818664551</v>
       </c>
       <c r="H89" t="n">
         <v>55032</v>
@@ -2979,7 +2979,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G90" t="n">
-        <v>3.41975879669189</v>
+        <v>3.41975855827332</v>
       </c>
       <c r="H90" t="n">
         <v>12161</v>
@@ -3008,7 +3008,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G91" t="n">
-        <v>3.51523399353027</v>
+        <v>3.51523423194885</v>
       </c>
       <c r="H91" t="n">
         <v>17593</v>
@@ -3095,7 +3095,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G94" t="n">
-        <v>3.41975879669189</v>
+        <v>3.41975855827332</v>
       </c>
       <c r="H94" t="n">
         <v>3029</v>
@@ -3124,7 +3124,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G95" t="n">
-        <v>3.51523399353027</v>
+        <v>3.51523423194885</v>
       </c>
       <c r="H95" t="n">
         <v>1936</v>
@@ -3153,7 +3153,7 @@
         <v>4.02500009536743</v>
       </c>
       <c r="G96" t="n">
-        <v>3.49353528022766</v>
+        <v>3.49353504180908</v>
       </c>
       <c r="H96" t="n">
         <v>1493</v>
@@ -3182,7 +3182,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G97" t="n">
-        <v>3.42843794822693</v>
+        <v>3.42843818664551</v>
       </c>
       <c r="H97" t="n">
         <v>52799</v>
@@ -3211,7 +3211,7 @@
         <v>4.00500011444092</v>
       </c>
       <c r="G98" t="n">
-        <v>3.47617626190186</v>
+        <v>3.47617602348328</v>
       </c>
       <c r="H98" t="n">
         <v>4670</v>
@@ -3240,7 +3240,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G99" t="n">
-        <v>3.59335017204285</v>
+        <v>3.59334993362427</v>
       </c>
       <c r="H99" t="n">
         <v>79600</v>
@@ -3298,7 +3298,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G101" t="n">
-        <v>3.54127287864685</v>
+        <v>3.54127264022827</v>
       </c>
       <c r="H101" t="n">
         <v>4200</v>
@@ -3327,7 +3327,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G102" t="n">
-        <v>3.44579720497131</v>
+        <v>3.44579744338989</v>
       </c>
       <c r="H102" t="n">
         <v>1743</v>
@@ -3385,7 +3385,7 @@
         <v>3.9449999332428</v>
       </c>
       <c r="G104" t="n">
-        <v>3.42409825325012</v>
+        <v>3.4240984916687</v>
       </c>
       <c r="H104" t="n">
         <v>26075</v>
@@ -3443,7 +3443,7 @@
         <v>4.03499984741211</v>
       </c>
       <c r="G106" t="n">
-        <v>3.50221419334412</v>
+        <v>3.5022144317627</v>
       </c>
       <c r="H106" t="n">
         <v>9593</v>
@@ -3472,7 +3472,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G107" t="n">
-        <v>3.51523399353027</v>
+        <v>3.51523423194885</v>
       </c>
       <c r="H107" t="n">
         <v>17133</v>
@@ -3559,7 +3559,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G110" t="n">
-        <v>3.64542746543884</v>
+        <v>3.64542770385742</v>
       </c>
       <c r="H110" t="n">
         <v>37685</v>
@@ -3588,7 +3588,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G111" t="n">
-        <v>3.64542746543884</v>
+        <v>3.64542770385742</v>
       </c>
       <c r="H111" t="n">
         <v>19204</v>
@@ -3617,7 +3617,7 @@
         <v>4.41499996185303</v>
       </c>
       <c r="G112" t="n">
-        <v>3.83203911781311</v>
+        <v>3.83203864097595</v>
       </c>
       <c r="H112" t="n">
         <v>30401</v>
@@ -3704,7 +3704,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G115" t="n">
-        <v>3.87109732627869</v>
+        <v>3.87109708786011</v>
       </c>
       <c r="H115" t="n">
         <v>4580</v>
@@ -3733,7 +3733,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G116" t="n">
-        <v>3.86241722106934</v>
+        <v>3.86241698265076</v>
       </c>
       <c r="H116" t="n">
         <v>17964</v>
@@ -3762,7 +3762,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G117" t="n">
-        <v>4.00997018814087</v>
+        <v>4.00997066497803</v>
       </c>
       <c r="H117" t="n">
         <v>10859</v>
@@ -3849,7 +3849,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G120" t="n">
-        <v>3.86241722106934</v>
+        <v>3.86241698265076</v>
       </c>
       <c r="H120" t="n">
         <v>34190</v>
@@ -3936,7 +3936,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G123" t="n">
-        <v>3.88845610618591</v>
+        <v>3.88845658302307</v>
       </c>
       <c r="H123" t="n">
         <v>13757</v>
@@ -3965,7 +3965,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G124" t="n">
-        <v>3.94921326637268</v>
+        <v>3.94921374320984</v>
       </c>
       <c r="H124" t="n">
         <v>5841</v>
@@ -3994,7 +3994,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G125" t="n">
-        <v>3.94921326637268</v>
+        <v>3.94921374320984</v>
       </c>
       <c r="H125" t="n">
         <v>21549</v>
@@ -4139,7 +4139,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G130" t="n">
-        <v>4.39187288284302</v>
+        <v>4.39187240600586</v>
       </c>
       <c r="H130" t="n">
         <v>8599</v>
@@ -4168,7 +4168,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G131" t="n">
-        <v>4.49602746963501</v>
+        <v>4.49602794647217</v>
       </c>
       <c r="H131" t="n">
         <v>4316</v>
@@ -4197,7 +4197,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G132" t="n">
-        <v>4.49602746963501</v>
+        <v>4.49602794647217</v>
       </c>
       <c r="H132" t="n">
         <v>2480</v>
@@ -4226,7 +4226,7 @@
         <v>4.97499990463257</v>
       </c>
       <c r="G133" t="n">
-        <v>4.31809568405151</v>
+        <v>4.31809616088867</v>
       </c>
       <c r="H133" t="n">
         <v>8257</v>
@@ -4313,7 +4313,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G136" t="n">
-        <v>4.2009220123291</v>
+        <v>4.20092153549194</v>
       </c>
       <c r="H136" t="n">
         <v>13708</v>
@@ -4400,7 +4400,7 @@
         <v>5</v>
       </c>
       <c r="G139" t="n">
-        <v>4.33979511260986</v>
+        <v>4.33979463577271</v>
       </c>
       <c r="H139" t="n">
         <v>20858</v>
@@ -4429,7 +4429,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G140" t="n">
-        <v>4.51338720321655</v>
+        <v>4.51338672637939</v>
       </c>
       <c r="H140" t="n">
         <v>12739</v>
@@ -4458,7 +4458,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G141" t="n">
-        <v>4.42659091949463</v>
+        <v>4.42659044265747</v>
       </c>
       <c r="H141" t="n">
         <v>9500</v>
@@ -4487,7 +4487,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G142" t="n">
-        <v>4.35715389251709</v>
+        <v>4.35715436935425</v>
       </c>
       <c r="H142" t="n">
         <v>21331</v>
@@ -4516,7 +4516,7 @@
         <v>5</v>
       </c>
       <c r="G143" t="n">
-        <v>4.33979511260986</v>
+        <v>4.33979463577271</v>
       </c>
       <c r="H143" t="n">
         <v>9892</v>
@@ -4545,7 +4545,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G144" t="n">
-        <v>4.42659091949463</v>
+        <v>4.42659044265747</v>
       </c>
       <c r="H144" t="n">
         <v>5800</v>
@@ -4574,7 +4574,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G145" t="n">
-        <v>4.51338720321655</v>
+        <v>4.51338672637939</v>
       </c>
       <c r="H145" t="n">
         <v>10888</v>
@@ -4603,7 +4603,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G146" t="n">
-        <v>4.54810523986816</v>
+        <v>4.54810476303101</v>
       </c>
       <c r="H146" t="n">
         <v>8672</v>
@@ -4632,7 +4632,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G147" t="n">
-        <v>4.70433759689331</v>
+        <v>4.70433807373047</v>
       </c>
       <c r="H147" t="n">
         <v>15539</v>
@@ -4661,7 +4661,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G148" t="n">
-        <v>4.49602746963501</v>
+        <v>4.49602794647217</v>
       </c>
       <c r="H148" t="n">
         <v>14318</v>
@@ -4690,7 +4690,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G149" t="n">
-        <v>4.54810523986816</v>
+        <v>4.54810476303101</v>
       </c>
       <c r="H149" t="n">
         <v>20634</v>
@@ -4719,7 +4719,7 @@
         <v>5.13000011444092</v>
       </c>
       <c r="G150" t="n">
-        <v>4.45263004302979</v>
+        <v>4.45262956619263</v>
       </c>
       <c r="H150" t="n">
         <v>6278</v>
@@ -4748,7 +4748,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G151" t="n">
-        <v>4.54810523986816</v>
+        <v>4.54810476303101</v>
       </c>
       <c r="H151" t="n">
         <v>3706</v>
@@ -4777,7 +4777,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G152" t="n">
-        <v>4.51338720321655</v>
+        <v>4.51338672637939</v>
       </c>
       <c r="H152" t="n">
         <v>12525</v>
@@ -4835,7 +4835,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G154" t="n">
-        <v>4.00129127502441</v>
+        <v>4.00129079818726</v>
       </c>
       <c r="H154" t="n">
         <v>9345</v>
@@ -4951,7 +4951,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G158" t="n">
-        <v>4.00129127502441</v>
+        <v>4.00129079818726</v>
       </c>
       <c r="H158" t="n">
         <v>25178</v>
@@ -4980,7 +4980,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G159" t="n">
-        <v>4.09676599502563</v>
+        <v>4.09676647186279</v>
       </c>
       <c r="H159" t="n">
         <v>11440</v>
@@ -5067,7 +5067,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G162" t="n">
-        <v>3.9926118850708</v>
+        <v>3.99261116981506</v>
       </c>
       <c r="H162" t="n">
         <v>1599</v>
@@ -5241,7 +5241,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G168" t="n">
-        <v>2.95974040031433</v>
+        <v>2.95974016189575</v>
       </c>
       <c r="H168" t="n">
         <v>11032</v>
@@ -5299,7 +5299,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G170" t="n">
-        <v>3.12465262413025</v>
+        <v>3.12465238571167</v>
       </c>
       <c r="H170" t="n">
         <v>862</v>
@@ -5386,7 +5386,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G173" t="n">
-        <v>3.09861373901367</v>
+        <v>3.09861350059509</v>
       </c>
       <c r="H173" t="n">
         <v>20403</v>
@@ -5444,7 +5444,7 @@
         <v>3.72499990463257</v>
       </c>
       <c r="G175" t="n">
-        <v>3.23314714431763</v>
+        <v>3.23314738273621</v>
       </c>
       <c r="H175" t="n">
         <v>35922</v>
@@ -5473,7 +5473,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G176" t="n">
-        <v>3.08125448226929</v>
+        <v>3.08125424385071</v>
       </c>
       <c r="H176" t="n">
         <v>9550</v>
@@ -5502,7 +5502,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G177" t="n">
-        <v>3.09861373901367</v>
+        <v>3.09861350059509</v>
       </c>
       <c r="H177" t="n">
         <v>2492</v>
@@ -5531,7 +5531,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G178" t="n">
-        <v>3.28956460952759</v>
+        <v>3.28956437110901</v>
       </c>
       <c r="H178" t="n">
         <v>12475</v>
@@ -5560,7 +5560,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G179" t="n">
-        <v>3.21144843101501</v>
+        <v>3.21144866943359</v>
       </c>
       <c r="H179" t="n">
         <v>6765</v>
@@ -5647,7 +5647,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G182" t="n">
-        <v>3.28956460952759</v>
+        <v>3.28956437110901</v>
       </c>
       <c r="H182" t="n">
         <v>11896</v>
@@ -5676,7 +5676,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G183" t="n">
-        <v>3.19408917427063</v>
+        <v>3.19408941268921</v>
       </c>
       <c r="H183" t="n">
         <v>14368</v>
@@ -5705,7 +5705,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G184" t="n">
-        <v>3.21144843101501</v>
+        <v>3.21144866943359</v>
       </c>
       <c r="H184" t="n">
         <v>4102</v>
@@ -5734,7 +5734,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G185" t="n">
-        <v>3.19408917427063</v>
+        <v>3.19408941268921</v>
       </c>
       <c r="H185" t="n">
         <v>20637</v>
@@ -5763,7 +5763,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G186" t="n">
-        <v>3.22012805938721</v>
+        <v>3.22012782096863</v>
       </c>
       <c r="H186" t="n">
         <v>4810</v>
@@ -5792,7 +5792,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G187" t="n">
-        <v>3.21144843101501</v>
+        <v>3.21144866943359</v>
       </c>
       <c r="H187" t="n">
         <v>10326</v>
@@ -5850,7 +5850,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G189" t="n">
-        <v>3.2288076877594</v>
+        <v>3.22880744934082</v>
       </c>
       <c r="H189" t="n">
         <v>7860</v>
@@ -5879,7 +5879,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G190" t="n">
-        <v>3.18540954589844</v>
+        <v>3.18540930747986</v>
       </c>
       <c r="H190" t="n">
         <v>13689</v>
@@ -6024,7 +6024,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G195" t="n">
-        <v>3.34164190292358</v>
+        <v>3.34164214134216</v>
       </c>
       <c r="H195" t="n">
         <v>6546</v>
@@ -6053,7 +6053,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G196" t="n">
-        <v>3.35900139808655</v>
+        <v>3.35900115966797</v>
       </c>
       <c r="H196" t="n">
         <v>2603</v>
@@ -6082,7 +6082,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G197" t="n">
-        <v>3.35900139808655</v>
+        <v>3.35900115966797</v>
       </c>
       <c r="H197" t="n">
         <v>1540</v>
@@ -6111,7 +6111,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G198" t="n">
-        <v>3.59335017204285</v>
+        <v>3.59334993362427</v>
       </c>
       <c r="H198" t="n">
         <v>40730</v>
@@ -6169,7 +6169,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G200" t="n">
-        <v>3.48051571846008</v>
+        <v>3.48051595687866</v>
       </c>
       <c r="H200" t="n">
         <v>8475</v>
@@ -6285,7 +6285,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G204" t="n">
-        <v>3.19408917427063</v>
+        <v>3.19408941268921</v>
       </c>
       <c r="H204" t="n">
         <v>55244</v>
@@ -6372,7 +6372,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G207" t="n">
-        <v>3.37636065483093</v>
+        <v>3.37636041641235</v>
       </c>
       <c r="H207" t="n">
         <v>12630</v>
@@ -6459,7 +6459,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G210" t="n">
-        <v>3.2288076877594</v>
+        <v>3.22880744934082</v>
       </c>
       <c r="H210" t="n">
         <v>9234</v>
@@ -6546,7 +6546,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G213" t="n">
-        <v>3.2288076877594</v>
+        <v>3.22880744934082</v>
       </c>
       <c r="H213" t="n">
         <v>1194</v>
@@ -6778,7 +6778,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G221" t="n">
-        <v>3.28956460952759</v>
+        <v>3.28956437110901</v>
       </c>
       <c r="H221" t="n">
         <v>8062</v>
@@ -6836,7 +6836,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G223" t="n">
-        <v>3.34164190292358</v>
+        <v>3.34164214134216</v>
       </c>
       <c r="H223" t="n">
         <v>1631</v>
@@ -6865,7 +6865,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G224" t="n">
-        <v>3.38504004478455</v>
+        <v>3.38504028320312</v>
       </c>
       <c r="H224" t="n">
         <v>2943</v>
@@ -6894,7 +6894,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G225" t="n">
-        <v>3.35900139808655</v>
+        <v>3.35900115966797</v>
       </c>
       <c r="H225" t="n">
         <v>7946</v>
@@ -6923,7 +6923,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G226" t="n">
-        <v>3.37636065483093</v>
+        <v>3.37636041641235</v>
       </c>
       <c r="H226" t="n">
         <v>19966</v>
@@ -6981,7 +6981,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G228" t="n">
-        <v>3.42843794822693</v>
+        <v>3.42843818664551</v>
       </c>
       <c r="H228" t="n">
         <v>2439</v>
@@ -7039,7 +7039,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G230" t="n">
-        <v>3.37636065483093</v>
+        <v>3.37636041641235</v>
       </c>
       <c r="H230" t="n">
         <v>4045</v>
@@ -7097,7 +7097,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G232" t="n">
-        <v>3.35032176971436</v>
+        <v>3.35032153129578</v>
       </c>
       <c r="H232" t="n">
         <v>11475</v>
@@ -7126,7 +7126,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G233" t="n">
-        <v>3.37636065483093</v>
+        <v>3.37636041641235</v>
       </c>
       <c r="H233" t="n">
         <v>111</v>
@@ -7155,7 +7155,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G234" t="n">
-        <v>3.37636065483093</v>
+        <v>3.37636041641235</v>
       </c>
       <c r="H234" t="n">
         <v>0</v>
@@ -7242,7 +7242,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G237" t="n">
-        <v>3.28956460952759</v>
+        <v>3.28956437110901</v>
       </c>
       <c r="H237" t="n">
         <v>451</v>
@@ -7358,7 +7358,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G241" t="n">
-        <v>3.34164190292358</v>
+        <v>3.34164214134216</v>
       </c>
       <c r="H241" t="n">
         <v>1540</v>
@@ -7387,7 +7387,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G242" t="n">
-        <v>3.28956460952759</v>
+        <v>3.28956437110901</v>
       </c>
       <c r="H242" t="n">
         <v>1</v>
@@ -7416,7 +7416,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G243" t="n">
-        <v>3.28956460952759</v>
+        <v>3.28956437110901</v>
       </c>
       <c r="H243" t="n">
         <v>0</v>
@@ -7445,7 +7445,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G244" t="n">
-        <v>3.42843794822693</v>
+        <v>3.42843818664551</v>
       </c>
       <c r="H244" t="n">
         <v>2009</v>
@@ -7648,7 +7648,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G251" t="n">
-        <v>3.18540954589844</v>
+        <v>3.18540930747986</v>
       </c>
       <c r="H251" t="n">
         <v>6820</v>
@@ -7677,7 +7677,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G252" t="n">
-        <v>3.21144843101501</v>
+        <v>3.21144866943359</v>
       </c>
       <c r="H252" t="n">
         <v>57</v>
@@ -7706,7 +7706,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G253" t="n">
-        <v>3.21144843101501</v>
+        <v>3.21144866943359</v>
       </c>
       <c r="H253" t="n">
         <v>0</v>
@@ -7735,7 +7735,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G254" t="n">
-        <v>3.28956460952759</v>
+        <v>3.28956437110901</v>
       </c>
       <c r="H254" t="n">
         <v>2105</v>
@@ -7764,7 +7764,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G255" t="n">
-        <v>3.18540954589844</v>
+        <v>3.18540930747986</v>
       </c>
       <c r="H255" t="n">
         <v>1005</v>
@@ -7793,7 +7793,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G256" t="n">
-        <v>3.2288076877594</v>
+        <v>3.22880744934082</v>
       </c>
       <c r="H256" t="n">
         <v>250</v>
@@ -7880,7 +7880,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G259" t="n">
-        <v>3.2288076877594</v>
+        <v>3.22880744934082</v>
       </c>
       <c r="H259" t="n">
         <v>29483</v>
@@ -7909,7 +7909,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G260" t="n">
-        <v>3.0899338722229</v>
+        <v>3.08993434906006</v>
       </c>
       <c r="H260" t="n">
         <v>31039</v>
@@ -7938,7 +7938,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G261" t="n">
-        <v>3.1159725189209</v>
+        <v>3.11597275733948</v>
       </c>
       <c r="H261" t="n">
         <v>80</v>
@@ -7996,7 +7996,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G263" t="n">
-        <v>3.0899338722229</v>
+        <v>3.08993434906006</v>
       </c>
       <c r="H263" t="n">
         <v>5405</v>
@@ -8025,7 +8025,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G264" t="n">
-        <v>3.13333201408386</v>
+        <v>3.13333177566528</v>
       </c>
       <c r="H264" t="n">
         <v>100</v>
@@ -8054,7 +8054,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G265" t="n">
-        <v>3.07257485389709</v>
+        <v>3.07257461547852</v>
       </c>
       <c r="H265" t="n">
         <v>1250</v>
@@ -8083,7 +8083,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G266" t="n">
-        <v>3.1159725189209</v>
+        <v>3.11597275733948</v>
       </c>
       <c r="H266" t="n">
         <v>700</v>
@@ -8112,7 +8112,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G267" t="n">
-        <v>3.1159725189209</v>
+        <v>3.11597275733948</v>
       </c>
       <c r="H267" t="n">
         <v>0</v>
@@ -8141,7 +8141,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G268" t="n">
-        <v>3.1159725189209</v>
+        <v>3.11597275733948</v>
       </c>
       <c r="H268" t="n">
         <v>0</v>
@@ -8199,7 +8199,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G270" t="n">
-        <v>3.19408917427063</v>
+        <v>3.19408941268921</v>
       </c>
       <c r="H270" t="n">
         <v>883</v>
@@ -8228,7 +8228,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G271" t="n">
-        <v>3.13333201408386</v>
+        <v>3.13333177566528</v>
       </c>
       <c r="H271" t="n">
         <v>2533</v>
@@ -8257,7 +8257,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G272" t="n">
-        <v>3.12465262413025</v>
+        <v>3.12465238571167</v>
       </c>
       <c r="H272" t="n">
         <v>9221</v>
@@ -8344,7 +8344,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G275" t="n">
-        <v>2.96841979026794</v>
+        <v>2.96842002868652</v>
       </c>
       <c r="H275" t="n">
         <v>11722</v>
@@ -8431,7 +8431,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G278" t="n">
-        <v>3.07257485389709</v>
+        <v>3.07257461547852</v>
       </c>
       <c r="H278" t="n">
         <v>4119</v>
@@ -8489,7 +8489,7 @@
         <v>3.5</v>
       </c>
       <c r="G280" t="n">
-        <v>3.0378565788269</v>
+        <v>3.03785634040833</v>
       </c>
       <c r="H280" t="n">
         <v>105</v>
@@ -8692,7 +8692,7 @@
         <v>3.5</v>
       </c>
       <c r="G287" t="n">
-        <v>3.0378565788269</v>
+        <v>3.03785634040833</v>
       </c>
       <c r="H287" t="n">
         <v>3634</v>
@@ -8750,7 +8750,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G289" t="n">
-        <v>3.08125448226929</v>
+        <v>3.08125424385071</v>
       </c>
       <c r="H289" t="n">
         <v>945</v>
@@ -8808,7 +8808,7 @@
         <v>3.5</v>
       </c>
       <c r="G291" t="n">
-        <v>3.0378565788269</v>
+        <v>3.03785634040833</v>
       </c>
       <c r="H291" t="n">
         <v>10</v>
@@ -8837,7 +8837,7 @@
         <v>3.5</v>
       </c>
       <c r="G292" t="n">
-        <v>3.0378565788269</v>
+        <v>3.03785634040833</v>
       </c>
       <c r="H292" t="n">
         <v>0</v>
@@ -8895,7 +8895,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G294" t="n">
-        <v>3.08125448226929</v>
+        <v>3.08125424385071</v>
       </c>
       <c r="H294" t="n">
         <v>4</v>
@@ -8924,7 +8924,7 @@
         <v>3.5</v>
       </c>
       <c r="G295" t="n">
-        <v>3.0378565788269</v>
+        <v>3.03785634040833</v>
       </c>
       <c r="H295" t="n">
         <v>700</v>
@@ -9127,7 +9127,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G302" t="n">
-        <v>2.95974040031433</v>
+        <v>2.95974016189575</v>
       </c>
       <c r="H302" t="n">
         <v>10987</v>
@@ -9156,7 +9156,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G303" t="n">
-        <v>2.8816237449646</v>
+        <v>2.88162398338318</v>
       </c>
       <c r="H303" t="n">
         <v>7318</v>
@@ -9185,7 +9185,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G304" t="n">
-        <v>2.87294435501099</v>
+        <v>2.87294459342957</v>
       </c>
       <c r="H304" t="n">
         <v>20000</v>
@@ -9214,7 +9214,7 @@
         <v>3.5</v>
       </c>
       <c r="G305" t="n">
-        <v>3.0378565788269</v>
+        <v>3.03785634040833</v>
       </c>
       <c r="H305" t="n">
         <v>28717</v>
@@ -9243,7 +9243,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G306" t="n">
-        <v>3.08125448226929</v>
+        <v>3.08125424385071</v>
       </c>
       <c r="H306" t="n">
         <v>17490</v>
@@ -9272,7 +9272,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G307" t="n">
-        <v>3.12465262413025</v>
+        <v>3.12465238571167</v>
       </c>
       <c r="H307" t="n">
         <v>9075</v>
@@ -9301,7 +9301,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G308" t="n">
-        <v>3.12465262413025</v>
+        <v>3.12465238571167</v>
       </c>
       <c r="H308" t="n">
         <v>6589</v>
@@ -9388,7 +9388,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G311" t="n">
-        <v>3.22012805938721</v>
+        <v>3.22012782096863</v>
       </c>
       <c r="H311" t="n">
         <v>688</v>
@@ -9417,7 +9417,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G312" t="n">
-        <v>3.22012805938721</v>
+        <v>3.22012782096863</v>
       </c>
       <c r="H312" t="n">
         <v>0</v>
@@ -9446,7 +9446,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G313" t="n">
-        <v>3.21144843101501</v>
+        <v>3.21144866943359</v>
       </c>
       <c r="H313" t="n">
         <v>2665</v>
@@ -9475,7 +9475,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G314" t="n">
-        <v>3.19408917427063</v>
+        <v>3.19408941268921</v>
       </c>
       <c r="H314" t="n">
         <v>9433</v>
@@ -9504,7 +9504,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G315" t="n">
-        <v>3.21144843101501</v>
+        <v>3.21144866943359</v>
       </c>
       <c r="H315" t="n">
         <v>456</v>
@@ -9562,7 +9562,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G317" t="n">
-        <v>3.21144843101501</v>
+        <v>3.21144866943359</v>
       </c>
       <c r="H317" t="n">
         <v>1600</v>
@@ -9620,7 +9620,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G319" t="n">
-        <v>3.1159725189209</v>
+        <v>3.11597275733948</v>
       </c>
       <c r="H319" t="n">
         <v>5736</v>
@@ -9678,7 +9678,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G321" t="n">
-        <v>3.21144843101501</v>
+        <v>3.21144866943359</v>
       </c>
       <c r="H321" t="n">
         <v>2251</v>
@@ -9736,7 +9736,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G323" t="n">
-        <v>3.21144843101501</v>
+        <v>3.21144866943359</v>
       </c>
       <c r="H323" t="n">
         <v>220</v>
@@ -9765,7 +9765,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G324" t="n">
-        <v>3.21144843101501</v>
+        <v>3.21144866943359</v>
       </c>
       <c r="H324" t="n">
         <v>4700</v>
@@ -9794,7 +9794,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G325" t="n">
-        <v>3.21144843101501</v>
+        <v>3.21144866943359</v>
       </c>
       <c r="H325" t="n">
         <v>650</v>
@@ -9823,7 +9823,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G326" t="n">
-        <v>3.19408917427063</v>
+        <v>3.19408941268921</v>
       </c>
       <c r="H326" t="n">
         <v>6000</v>
@@ -9881,7 +9881,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G328" t="n">
-        <v>3.21144843101501</v>
+        <v>3.21144866943359</v>
       </c>
       <c r="H328" t="n">
         <v>2264</v>
@@ -9910,7 +9910,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G329" t="n">
-        <v>3.12465262413025</v>
+        <v>3.12465238571167</v>
       </c>
       <c r="H329" t="n">
         <v>3400</v>
@@ -9939,7 +9939,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G330" t="n">
-        <v>3.19408917427063</v>
+        <v>3.19408941268921</v>
       </c>
       <c r="H330" t="n">
         <v>3070</v>
@@ -9997,7 +9997,7 @@
         <v>3.5</v>
       </c>
       <c r="G332" t="n">
-        <v>3.0378565788269</v>
+        <v>3.03785634040833</v>
       </c>
       <c r="H332" t="n">
         <v>2958</v>
@@ -10055,7 +10055,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G334" t="n">
-        <v>3.15069127082825</v>
+        <v>3.15069150924683</v>
       </c>
       <c r="H334" t="n">
         <v>1330</v>
@@ -10171,7 +10171,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G338" t="n">
-        <v>3.1159725189209</v>
+        <v>3.11597275733948</v>
       </c>
       <c r="H338" t="n">
         <v>70</v>
@@ -10229,7 +10229,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G340" t="n">
-        <v>3.1159725189209</v>
+        <v>3.11597275733948</v>
       </c>
       <c r="H340" t="n">
         <v>823</v>
@@ -10287,7 +10287,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G342" t="n">
-        <v>3.21144843101501</v>
+        <v>3.21144866943359</v>
       </c>
       <c r="H342" t="n">
         <v>3660</v>
@@ -10316,7 +10316,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G343" t="n">
-        <v>3.15069127082825</v>
+        <v>3.15069150924683</v>
       </c>
       <c r="H343" t="n">
         <v>3072</v>
@@ -10345,7 +10345,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G344" t="n">
-        <v>3.15069127082825</v>
+        <v>3.15069150924683</v>
       </c>
       <c r="H344" t="n">
         <v>8220</v>
@@ -10374,7 +10374,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G345" t="n">
-        <v>3.22012805938721</v>
+        <v>3.22012782096863</v>
       </c>
       <c r="H345" t="n">
         <v>3873</v>
@@ -10403,7 +10403,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G346" t="n">
-        <v>3.21144843101501</v>
+        <v>3.21144866943359</v>
       </c>
       <c r="H346" t="n">
         <v>5550</v>
@@ -10461,7 +10461,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G348" t="n">
-        <v>3.42843794822693</v>
+        <v>3.42843818664551</v>
       </c>
       <c r="H348" t="n">
         <v>10171</v>
@@ -10577,7 +10577,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G352" t="n">
-        <v>3.34164190292358</v>
+        <v>3.34164214134216</v>
       </c>
       <c r="H352" t="n">
         <v>1770</v>
@@ -10606,7 +10606,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G353" t="n">
-        <v>3.28956460952759</v>
+        <v>3.28956437110901</v>
       </c>
       <c r="H353" t="n">
         <v>300</v>
@@ -10635,7 +10635,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G354" t="n">
-        <v>3.34164190292358</v>
+        <v>3.34164214134216</v>
       </c>
       <c r="H354" t="n">
         <v>1650</v>
@@ -10693,7 +10693,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G356" t="n">
-        <v>3.42843794822693</v>
+        <v>3.42843818664551</v>
       </c>
       <c r="H356" t="n">
         <v>1020</v>
@@ -10722,7 +10722,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G357" t="n">
-        <v>3.42843794822693</v>
+        <v>3.42843818664551</v>
       </c>
       <c r="H357" t="n">
         <v>1750</v>
@@ -10751,7 +10751,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G358" t="n">
-        <v>3.37636065483093</v>
+        <v>3.37636041641235</v>
       </c>
       <c r="H358" t="n">
         <v>800</v>
@@ -10838,7 +10838,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G361" t="n">
-        <v>3.46304678916931</v>
+        <v>3.46304655075073</v>
       </c>
       <c r="H361" t="n">
         <v>6479</v>
@@ -10954,7 +10954,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G365" t="n">
-        <v>3.55973052978516</v>
+        <v>3.55973076820374</v>
       </c>
       <c r="H365" t="n">
         <v>10835</v>
@@ -11215,7 +11215,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G374" t="n">
-        <v>3.85857200622559</v>
+        <v>3.85857176780701</v>
       </c>
       <c r="H374" t="n">
         <v>3601</v>
@@ -11244,7 +11244,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G375" t="n">
-        <v>3.80583524703979</v>
+        <v>3.80583500862122</v>
       </c>
       <c r="H375" t="n">
         <v>1180</v>
@@ -11331,7 +11331,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G378" t="n">
-        <v>3.84978270530701</v>
+        <v>3.84978294372559</v>
       </c>
       <c r="H378" t="n">
         <v>9179</v>
@@ -11360,7 +11360,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G379" t="n">
-        <v>3.9025194644928</v>
+        <v>3.90251994132996</v>
       </c>
       <c r="H379" t="n">
         <v>28775</v>
@@ -11389,7 +11389,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G380" t="n">
-        <v>3.99041414260864</v>
+        <v>3.99041366577148</v>
       </c>
       <c r="H380" t="n">
         <v>6050</v>
@@ -11418,7 +11418,7 @@
         <v>4.5</v>
       </c>
       <c r="G381" t="n">
-        <v>3.95525646209717</v>
+        <v>3.95525598526001</v>
       </c>
       <c r="H381" t="n">
         <v>11250</v>
@@ -11447,7 +11447,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G382" t="n">
-        <v>3.92888784408569</v>
+        <v>3.92888760566711</v>
       </c>
       <c r="H382" t="n">
         <v>12048</v>
@@ -11476,7 +11476,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G383" t="n">
-        <v>3.92009854316711</v>
+        <v>3.92009806632996</v>
       </c>
       <c r="H383" t="n">
         <v>30</v>
@@ -11563,7 +11563,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G386" t="n">
-        <v>3.647625207901</v>
+        <v>3.64762496948242</v>
       </c>
       <c r="H386" t="n">
         <v>7282</v>
@@ -11592,7 +11592,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G387" t="n">
-        <v>3.42788887023926</v>
+        <v>3.4278883934021</v>
       </c>
       <c r="H387" t="n">
         <v>24073</v>
@@ -11650,7 +11650,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G389" t="n">
-        <v>3.58609890937805</v>
+        <v>3.58609914779663</v>
       </c>
       <c r="H389" t="n">
         <v>19347</v>
@@ -11737,7 +11737,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G392" t="n">
-        <v>3.62125658988953</v>
+        <v>3.62125682830811</v>
       </c>
       <c r="H392" t="n">
         <v>15062</v>
@@ -11766,7 +11766,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G393" t="n">
-        <v>3.6739935874939</v>
+        <v>3.67399334907532</v>
       </c>
       <c r="H393" t="n">
         <v>9627</v>
@@ -11795,7 +11795,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G394" t="n">
-        <v>3.6739935874939</v>
+        <v>3.67399334907532</v>
       </c>
       <c r="H394" t="n">
         <v>6027</v>
@@ -11969,7 +11969,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G400" t="n">
-        <v>3.62125658988953</v>
+        <v>3.62125682830811</v>
       </c>
       <c r="H400" t="n">
         <v>1948</v>
@@ -11998,7 +11998,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G401" t="n">
-        <v>3.58609890937805</v>
+        <v>3.58609914779663</v>
       </c>
       <c r="H401" t="n">
         <v>2243</v>
@@ -12027,7 +12027,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G402" t="n">
-        <v>3.60367798805237</v>
+        <v>3.60367751121521</v>
       </c>
       <c r="H402" t="n">
         <v>31743</v>
@@ -12056,7 +12056,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G403" t="n">
-        <v>3.6827826499939</v>
+        <v>3.68278288841248</v>
       </c>
       <c r="H403" t="n">
         <v>5461</v>
@@ -12085,7 +12085,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G404" t="n">
-        <v>3.9025194644928</v>
+        <v>3.90251994132996</v>
       </c>
       <c r="H404" t="n">
         <v>16220</v>
@@ -12114,7 +12114,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G405" t="n">
-        <v>3.84978270530701</v>
+        <v>3.84978294372559</v>
       </c>
       <c r="H405" t="n">
         <v>10519</v>
@@ -12143,7 +12143,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G406" t="n">
-        <v>3.84099316596985</v>
+        <v>3.84099292755127</v>
       </c>
       <c r="H406" t="n">
         <v>7000</v>
@@ -12172,7 +12172,7 @@
         <v>4.25</v>
       </c>
       <c r="G407" t="n">
-        <v>3.73551964759827</v>
+        <v>3.73552012443542</v>
       </c>
       <c r="H407" t="n">
         <v>7140</v>
@@ -12201,7 +12201,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G408" t="n">
-        <v>3.78825664520264</v>
+        <v>3.78825688362122</v>
       </c>
       <c r="H408" t="n">
         <v>9728</v>
@@ -12230,7 +12230,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G409" t="n">
-        <v>4.04315090179443</v>
+        <v>4.04315042495728</v>
       </c>
       <c r="H409" t="n">
         <v>11444</v>
@@ -12259,7 +12259,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G410" t="n">
-        <v>3.99920344352722</v>
+        <v>3.99920392036438</v>
       </c>
       <c r="H410" t="n">
         <v>13066</v>
@@ -12288,7 +12288,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G411" t="n">
-        <v>3.99920344352722</v>
+        <v>3.99920392036438</v>
       </c>
       <c r="H411" t="n">
         <v>3045</v>
@@ -12317,7 +12317,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G412" t="n">
-        <v>3.97283506393433</v>
+        <v>3.97283530235291</v>
       </c>
       <c r="H412" t="n">
         <v>3835</v>
@@ -12375,7 +12375,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G414" t="n">
-        <v>4.04315090179443</v>
+        <v>4.04315042495728</v>
       </c>
       <c r="H414" t="n">
         <v>4777</v>
@@ -12404,7 +12404,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G415" t="n">
-        <v>4.04315090179443</v>
+        <v>4.04315042495728</v>
       </c>
       <c r="H415" t="n">
         <v>0</v>
@@ -12433,7 +12433,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G416" t="n">
-        <v>3.99920344352722</v>
+        <v>3.99920392036438</v>
       </c>
       <c r="H416" t="n">
         <v>20150</v>
@@ -12462,7 +12462,7 @@
         <v>4.59000015258789</v>
       </c>
       <c r="G417" t="n">
-        <v>4.03436183929443</v>
+        <v>4.03436088562012</v>
       </c>
       <c r="H417" t="n">
         <v>6334</v>
@@ -12491,7 +12491,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G418" t="n">
-        <v>4.08709859848022</v>
+        <v>4.08709812164307</v>
       </c>
       <c r="H418" t="n">
         <v>6771</v>
@@ -12520,7 +12520,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G419" t="n">
-        <v>4.14862394332886</v>
+        <v>4.1486234664917</v>
       </c>
       <c r="H419" t="n">
         <v>3061</v>
@@ -12636,7 +12636,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G423" t="n">
-        <v>4.28046560287476</v>
+        <v>4.28046607971191</v>
       </c>
       <c r="H423" t="n">
         <v>7858</v>
@@ -12694,7 +12694,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G425" t="n">
-        <v>4.29804515838623</v>
+        <v>4.29804468154907</v>
       </c>
       <c r="H425" t="n">
         <v>2886</v>
@@ -12810,7 +12810,7 @@
         <v>4.75</v>
       </c>
       <c r="G429" t="n">
-        <v>4.17499256134033</v>
+        <v>4.17499303817749</v>
       </c>
       <c r="H429" t="n">
         <v>10</v>
@@ -12839,7 +12839,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G430" t="n">
-        <v>4.28925561904907</v>
+        <v>4.28925609588623</v>
       </c>
       <c r="H430" t="n">
         <v>7986</v>
@@ -12868,7 +12868,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G431" t="n">
-        <v>4.28925561904907</v>
+        <v>4.28925609588623</v>
       </c>
       <c r="H431" t="n">
         <v>2210</v>
@@ -12984,7 +12984,7 @@
         <v>4.75</v>
       </c>
       <c r="G435" t="n">
-        <v>4.17499256134033</v>
+        <v>4.17499303817749</v>
       </c>
       <c r="H435" t="n">
         <v>1500</v>
@@ -13100,7 +13100,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G439" t="n">
-        <v>4.3859395980835</v>
+        <v>4.38593912124634</v>
       </c>
       <c r="H439" t="n">
         <v>2700</v>
@@ -13129,7 +13129,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G440" t="n">
-        <v>4.3859395980835</v>
+        <v>4.38593912124634</v>
       </c>
       <c r="H440" t="n">
         <v>100</v>
@@ -13216,7 +13216,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G443" t="n">
-        <v>4.35078144073486</v>
+        <v>4.35078191757202</v>
       </c>
       <c r="H443" t="n">
         <v>180</v>
@@ -13332,7 +13332,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G447" t="n">
-        <v>4.3859395980835</v>
+        <v>4.38593912124634</v>
       </c>
       <c r="H447" t="n">
         <v>20</v>
@@ -13361,7 +13361,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G448" t="n">
-        <v>4.41230821609497</v>
+        <v>4.41230773925781</v>
       </c>
       <c r="H448" t="n">
         <v>4280</v>
@@ -13419,7 +13419,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G450" t="n">
-        <v>4.21893978118896</v>
+        <v>4.21894025802612</v>
       </c>
       <c r="H450" t="n">
         <v>4300</v>
@@ -13477,7 +13477,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G452" t="n">
-        <v>4.21893978118896</v>
+        <v>4.21894025802612</v>
       </c>
       <c r="H452" t="n">
         <v>1223</v>
@@ -13535,7 +13535,7 @@
         <v>4.75</v>
       </c>
       <c r="G454" t="n">
-        <v>4.17499256134033</v>
+        <v>4.17499303817749</v>
       </c>
       <c r="H454" t="n">
         <v>220</v>
@@ -13593,7 +13593,7 @@
         <v>4.75</v>
       </c>
       <c r="G456" t="n">
-        <v>4.17499256134033</v>
+        <v>4.17499303817749</v>
       </c>
       <c r="H456" t="n">
         <v>7</v>
@@ -13622,7 +13622,7 @@
         <v>4.75</v>
       </c>
       <c r="G457" t="n">
-        <v>4.17499256134033</v>
+        <v>4.17499303817749</v>
       </c>
       <c r="H457" t="n">
         <v>0</v>
@@ -13680,7 +13680,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G459" t="n">
-        <v>4.02557134628296</v>
+        <v>4.02557229995728</v>
       </c>
       <c r="H459" t="n">
         <v>4000</v>
@@ -13709,7 +13709,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G460" t="n">
-        <v>4.02557134628296</v>
+        <v>4.02557229995728</v>
       </c>
       <c r="H460" t="n">
         <v>1607</v>
@@ -13738,7 +13738,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G461" t="n">
-        <v>4.02557134628296</v>
+        <v>4.02557229995728</v>
       </c>
       <c r="H461" t="n">
         <v>1400</v>
@@ -13767,7 +13767,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G462" t="n">
-        <v>4.08709859848022</v>
+        <v>4.08709812164307</v>
       </c>
       <c r="H462" t="n">
         <v>155</v>
@@ -13796,7 +13796,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G463" t="n">
-        <v>4.14862394332886</v>
+        <v>4.1486234664917</v>
       </c>
       <c r="H463" t="n">
         <v>13</v>
@@ -13883,7 +13883,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G466" t="n">
-        <v>4.28925561904907</v>
+        <v>4.28925609588623</v>
       </c>
       <c r="H466" t="n">
         <v>1395</v>
@@ -13912,7 +13912,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G467" t="n">
-        <v>4.35078144073486</v>
+        <v>4.35078191757202</v>
       </c>
       <c r="H467" t="n">
         <v>12111</v>
@@ -13941,7 +13941,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G468" t="n">
-        <v>4.50020265579224</v>
+        <v>4.50020217895508</v>
       </c>
       <c r="H468" t="n">
         <v>25612</v>
@@ -14115,7 +14115,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G474" t="n">
-        <v>4.57807350158691</v>
+        <v>4.57807397842407</v>
       </c>
       <c r="H474" t="n">
         <v>5287</v>
@@ -14231,7 +14231,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G478" t="n">
-        <v>4.64877796173096</v>
+        <v>4.6487774848938</v>
       </c>
       <c r="H478" t="n">
         <v>1637</v>
@@ -14260,7 +14260,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G479" t="n">
-        <v>4.56039762496948</v>
+        <v>4.56039810180664</v>
       </c>
       <c r="H479" t="n">
         <v>500</v>
@@ -14318,7 +14318,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G481" t="n">
-        <v>4.56039762496948</v>
+        <v>4.56039810180664</v>
       </c>
       <c r="H481" t="n">
         <v>1763</v>
@@ -14492,7 +14492,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G487" t="n">
-        <v>4.56039762496948</v>
+        <v>4.56039810180664</v>
       </c>
       <c r="H487" t="n">
         <v>5900</v>
@@ -14521,7 +14521,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G488" t="n">
-        <v>4.56039762496948</v>
+        <v>4.56039810180664</v>
       </c>
       <c r="H488" t="n">
         <v>3324</v>
@@ -14724,7 +14724,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G495" t="n">
-        <v>4.17152643203735</v>
+        <v>4.1715259552002</v>
       </c>
       <c r="H495" t="n">
         <v>3325</v>
@@ -14753,7 +14753,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G496" t="n">
-        <v>4.10966062545776</v>
+        <v>4.10966110229492</v>
       </c>
       <c r="H496" t="n">
         <v>2705</v>
@@ -14956,7 +14956,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G503" t="n">
-        <v>4.10966062545776</v>
+        <v>4.10966110229492</v>
       </c>
       <c r="H503" t="n">
         <v>3919</v>
@@ -14985,7 +14985,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G504" t="n">
-        <v>4.10966062545776</v>
+        <v>4.10966110229492</v>
       </c>
       <c r="H504" t="n">
         <v>0</v>
@@ -15043,7 +15043,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G506" t="n">
-        <v>4.10082244873047</v>
+        <v>4.10082292556763</v>
       </c>
       <c r="H506" t="n">
         <v>435</v>
@@ -15188,7 +15188,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G511" t="n">
-        <v>4.10966062545776</v>
+        <v>4.10966110229492</v>
       </c>
       <c r="H511" t="n">
         <v>2700</v>
@@ -15217,7 +15217,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G512" t="n">
-        <v>4.10966062545776</v>
+        <v>4.10966110229492</v>
       </c>
       <c r="H512" t="n">
         <v>0</v>
@@ -15333,7 +15333,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G516" t="n">
-        <v>4.32177257537842</v>
+        <v>4.32177209854126</v>
       </c>
       <c r="H516" t="n">
         <v>2870</v>
@@ -15449,7 +15449,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G520" t="n">
-        <v>4.48969411849976</v>
+        <v>4.4896936416626</v>
       </c>
       <c r="H520" t="n">
         <v>1048</v>
@@ -15623,7 +15623,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G526" t="n">
-        <v>4.57807350158691</v>
+        <v>4.57807397842407</v>
       </c>
       <c r="H526" t="n">
         <v>2094</v>
@@ -15652,7 +15652,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G527" t="n">
-        <v>4.57807350158691</v>
+        <v>4.57807397842407</v>
       </c>
       <c r="H527" t="n">
         <v>50</v>
@@ -16145,7 +16145,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G544" t="n">
-        <v>4.36596202850342</v>
+        <v>4.36596250534058</v>
       </c>
       <c r="H544" t="n">
         <v>2872</v>
@@ -16174,7 +16174,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G545" t="n">
-        <v>4.36596202850342</v>
+        <v>4.36596250534058</v>
       </c>
       <c r="H545" t="n">
         <v>0</v>
@@ -16522,7 +16522,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G557" t="n">
-        <v>4.07430934906006</v>
+        <v>4.0743088722229</v>
       </c>
       <c r="H557" t="n">
         <v>4755</v>
@@ -16551,7 +16551,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G558" t="n">
-        <v>4.10966062545776</v>
+        <v>4.10966110229492</v>
       </c>
       <c r="H558" t="n">
         <v>4550</v>
@@ -16667,7 +16667,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G562" t="n">
-        <v>4.10966062545776</v>
+        <v>4.10966110229492</v>
       </c>
       <c r="H562" t="n">
         <v>1123</v>
@@ -16870,7 +16870,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G569" t="n">
-        <v>4.57807350158691</v>
+        <v>4.57807397842407</v>
       </c>
       <c r="H569" t="n">
         <v>10847</v>
@@ -16986,7 +16986,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G573" t="n">
-        <v>4.73715734481812</v>
+        <v>4.73715782165527</v>
       </c>
       <c r="H573" t="n">
         <v>798</v>
@@ -17160,7 +17160,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G579" t="n">
-        <v>4.89624071121216</v>
+        <v>4.89624118804932</v>
       </c>
       <c r="H579" t="n">
         <v>5879</v>
@@ -17218,7 +17218,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G581" t="n">
-        <v>5.10835313796997</v>
+        <v>5.10835266113281</v>
       </c>
       <c r="H581" t="n">
         <v>12053</v>
@@ -17305,7 +17305,7 @@
         <v>6.03999996185303</v>
       </c>
       <c r="G584" t="n">
-        <v>5.3381404876709</v>
+        <v>5.33814001083374</v>
       </c>
       <c r="H584" t="n">
         <v>12438</v>
@@ -17566,7 +17566,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G593" t="n">
-        <v>5.56792736053467</v>
+        <v>5.56792783737183</v>
       </c>
       <c r="H593" t="n">
         <v>3180</v>
@@ -17595,7 +17595,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G594" t="n">
-        <v>5.56792736053467</v>
+        <v>5.56792783737183</v>
       </c>
       <c r="H594" t="n">
         <v>3910</v>
@@ -17653,7 +17653,7 @@
         <v>6.71999979019165</v>
       </c>
       <c r="G596" t="n">
-        <v>5.93912267684937</v>
+        <v>5.93912315368652</v>
       </c>
       <c r="H596" t="n">
         <v>3720</v>
@@ -17856,7 +17856,7 @@
         <v>6.26000022888184</v>
       </c>
       <c r="G603" t="n">
-        <v>5.53257608413696</v>
+        <v>5.5325756072998</v>
       </c>
       <c r="H603" t="n">
         <v>20947</v>
@@ -17972,7 +17972,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G607" t="n">
-        <v>5.55025196075439</v>
+        <v>5.55025148391724</v>
       </c>
       <c r="H607" t="n">
         <v>880</v>
@@ -18001,7 +18001,7 @@
         <v>6.26000022888184</v>
       </c>
       <c r="G608" t="n">
-        <v>5.53257608413696</v>
+        <v>5.5325756072998</v>
       </c>
       <c r="H608" t="n">
         <v>2120</v>
@@ -18262,7 +18262,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G617" t="n">
-        <v>5.92144632339478</v>
+        <v>5.92144680023193</v>
       </c>
       <c r="H617" t="n">
         <v>18955</v>
@@ -18378,7 +18378,7 @@
         <v>6.26000022888184</v>
       </c>
       <c r="G621" t="n">
-        <v>5.53257608413696</v>
+        <v>5.5325756072998</v>
       </c>
       <c r="H621" t="n">
         <v>3812</v>
@@ -18552,7 +18552,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G627" t="n">
-        <v>6.00982713699341</v>
+        <v>6.00982666015625</v>
       </c>
       <c r="H627" t="n">
         <v>6922</v>
@@ -18610,7 +18610,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G629" t="n">
-        <v>5.92144632339478</v>
+        <v>5.92144680023193</v>
       </c>
       <c r="H629" t="n">
         <v>400</v>
@@ -18639,7 +18639,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G630" t="n">
-        <v>6.00982713699341</v>
+        <v>6.00982666015625</v>
       </c>
       <c r="H630" t="n">
         <v>16000</v>
@@ -19132,7 +19132,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G647" t="n">
-        <v>5.37349224090576</v>
+        <v>5.3734917640686</v>
       </c>
       <c r="H647" t="n">
         <v>1250</v>
@@ -19509,7 +19509,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G660" t="n">
-        <v>5.23208427429199</v>
+        <v>5.23208475112915</v>
       </c>
       <c r="H660" t="n">
         <v>16216</v>
@@ -19683,7 +19683,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G666" t="n">
-        <v>4.71948146820068</v>
+        <v>4.71948194503784</v>
       </c>
       <c r="H666" t="n">
         <v>18954</v>
@@ -19799,7 +19799,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G670" t="n">
-        <v>4.71948146820068</v>
+        <v>4.71948194503784</v>
       </c>
       <c r="H670" t="n">
         <v>875</v>
@@ -19828,7 +19828,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G671" t="n">
-        <v>4.57807350158691</v>
+        <v>4.57807397842407</v>
       </c>
       <c r="H671" t="n">
         <v>623</v>
@@ -19857,7 +19857,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G672" t="n">
-        <v>4.64877796173096</v>
+        <v>4.6487774848938</v>
       </c>
       <c r="H672" t="n">
         <v>11719</v>
@@ -20147,7 +20147,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G682" t="n">
-        <v>4.71948146820068</v>
+        <v>4.71948194503784</v>
       </c>
       <c r="H682" t="n">
         <v>13546</v>
@@ -20379,7 +20379,7 @@
         <v>5.5</v>
       </c>
       <c r="G690" t="n">
-        <v>4.86088943481445</v>
+        <v>4.86088895797729</v>
       </c>
       <c r="H690" t="n">
         <v>2318</v>
@@ -20640,7 +20640,7 @@
         <v>5.5</v>
       </c>
       <c r="G699" t="n">
-        <v>4.86088943481445</v>
+        <v>4.86088895797729</v>
       </c>
       <c r="H699" t="n">
         <v>1100</v>
@@ -21046,7 +21046,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G713" t="n">
-        <v>5.16138076782227</v>
+        <v>5.16138029098511</v>
       </c>
       <c r="H713" t="n">
         <v>3739</v>
@@ -21307,7 +21307,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G722" t="n">
-        <v>5.16138076782227</v>
+        <v>5.16138029098511</v>
       </c>
       <c r="H722" t="n">
         <v>1500</v>
@@ -21336,7 +21336,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G723" t="n">
-        <v>5.16138076782227</v>
+        <v>5.16138029098511</v>
       </c>
       <c r="H723" t="n">
         <v>0</v>
@@ -21365,7 +21365,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G724" t="n">
-        <v>5.24976015090942</v>
+        <v>5.24976062774658</v>
       </c>
       <c r="H724" t="n">
         <v>4500</v>
@@ -21626,7 +21626,7 @@
         <v>5.8600001335144</v>
       </c>
       <c r="G733" t="n">
-        <v>5.24438095092773</v>
+        <v>5.24438142776489</v>
       </c>
       <c r="H733" t="n">
         <v>1735</v>
@@ -21655,7 +21655,7 @@
         <v>5.8600001335144</v>
       </c>
       <c r="G734" t="n">
-        <v>5.24438095092773</v>
+        <v>5.24438142776489</v>
       </c>
       <c r="H734" t="n">
         <v>0</v>
@@ -21771,7 +21771,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G738" t="n">
-        <v>5.26228046417236</v>
+        <v>5.26227998733521</v>
       </c>
       <c r="H738" t="n">
         <v>40</v>
@@ -22148,7 +22148,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G751" t="n">
-        <v>4.99379587173462</v>
+        <v>4.99379634857178</v>
       </c>
       <c r="H751" t="n">
         <v>470</v>
@@ -22351,7 +22351,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G758" t="n">
-        <v>5.31597661972046</v>
+        <v>5.31597709655762</v>
       </c>
       <c r="H758" t="n">
         <v>1333</v>
@@ -22380,7 +22380,7 @@
         <v>6</v>
       </c>
       <c r="G759" t="n">
-        <v>5.36967325210571</v>
+        <v>5.36967372894287</v>
       </c>
       <c r="H759" t="n">
         <v>304</v>
@@ -22409,7 +22409,7 @@
         <v>6</v>
       </c>
       <c r="G760" t="n">
-        <v>5.36967325210571</v>
+        <v>5.36967372894287</v>
       </c>
       <c r="H760" t="n">
         <v>829</v>
@@ -22438,7 +22438,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G761" t="n">
-        <v>5.47706651687622</v>
+        <v>5.47706699371338</v>
       </c>
       <c r="H761" t="n">
         <v>270</v>
@@ -22641,7 +22641,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G768" t="n">
-        <v>5.72765159606934</v>
+        <v>5.72765207290649</v>
       </c>
       <c r="H768" t="n">
         <v>2958</v>
@@ -22699,7 +22699,7 @@
         <v>6.51999998092651</v>
       </c>
       <c r="G770" t="n">
-        <v>5.835045337677</v>
+        <v>5.83504486083984</v>
       </c>
       <c r="H770" t="n">
         <v>667</v>
@@ -22728,7 +22728,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G771" t="n">
-        <v>5.72765159606934</v>
+        <v>5.72765207290649</v>
       </c>
       <c r="H771" t="n">
         <v>678</v>
@@ -22757,7 +22757,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G772" t="n">
-        <v>5.72765159606934</v>
+        <v>5.72765207290649</v>
       </c>
       <c r="H772" t="n">
         <v>1540</v>
@@ -22844,7 +22844,7 @@
         <v>6.5</v>
       </c>
       <c r="G775" t="n">
-        <v>5.81714582443237</v>
+        <v>5.81714630126953</v>
       </c>
       <c r="H775" t="n">
         <v>11</v>
@@ -22902,7 +22902,7 @@
         <v>6.5</v>
       </c>
       <c r="G777" t="n">
-        <v>5.81714582443237</v>
+        <v>5.81714630126953</v>
       </c>
       <c r="H777" t="n">
         <v>6650</v>
@@ -23018,7 +23018,7 @@
         <v>6.73999977111816</v>
       </c>
       <c r="G781" t="n">
-        <v>6.03193283081055</v>
+        <v>6.03193330764771</v>
       </c>
       <c r="H781" t="n">
         <v>1012</v>
@@ -23105,7 +23105,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G784" t="n">
-        <v>6.08563041687012</v>
+        <v>6.08562994003296</v>
       </c>
       <c r="H784" t="n">
         <v>2889</v>
@@ -23250,7 +23250,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G789" t="n">
-        <v>5.8887414932251</v>
+        <v>5.88874197006226</v>
       </c>
       <c r="H789" t="n">
         <v>3581</v>
@@ -23308,7 +23308,7 @@
         <v>6.53999996185303</v>
       </c>
       <c r="G791" t="n">
-        <v>5.85294389724731</v>
+        <v>5.85294437408447</v>
       </c>
       <c r="H791" t="n">
         <v>31</v>
@@ -23337,7 +23337,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G792" t="n">
-        <v>5.72765159606934</v>
+        <v>5.72765207290649</v>
       </c>
       <c r="H792" t="n">
         <v>40050</v>
@@ -23482,7 +23482,7 @@
         <v>6.5</v>
       </c>
       <c r="G797" t="n">
-        <v>5.81714582443237</v>
+        <v>5.81714630126953</v>
       </c>
       <c r="H797" t="n">
         <v>1055</v>
@@ -23511,7 +23511,7 @@
         <v>6.5</v>
       </c>
       <c r="G798" t="n">
-        <v>5.81714582443237</v>
+        <v>5.81714630126953</v>
       </c>
       <c r="H798" t="n">
         <v>30000</v>
@@ -23598,7 +23598,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G801" t="n">
-        <v>5.8887414932251</v>
+        <v>5.88874197006226</v>
       </c>
       <c r="H801" t="n">
         <v>550</v>
@@ -23772,7 +23772,7 @@
         <v>6.42000007629395</v>
       </c>
       <c r="G807" t="n">
-        <v>5.74555110931396</v>
+        <v>5.74555063247681</v>
       </c>
       <c r="H807" t="n">
         <v>50</v>
@@ -23888,7 +23888,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G811" t="n">
-        <v>5.54866218566895</v>
+        <v>5.5486626625061</v>
       </c>
       <c r="H811" t="n">
         <v>1520</v>
@@ -23946,7 +23946,7 @@
         <v>5.8600001335144</v>
       </c>
       <c r="G813" t="n">
-        <v>5.24438095092773</v>
+        <v>5.24438142776489</v>
       </c>
       <c r="H813" t="n">
         <v>595</v>
@@ -23975,7 +23975,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G814" t="n">
-        <v>5.13698720932007</v>
+        <v>5.13698768615723</v>
       </c>
       <c r="H814" t="n">
         <v>33740</v>
@@ -24004,7 +24004,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G815" t="n">
-        <v>5.13698720932007</v>
+        <v>5.13698768615723</v>
       </c>
       <c r="H815" t="n">
         <v>0</v>
@@ -24033,7 +24033,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G816" t="n">
-        <v>5.3517746925354</v>
+        <v>5.35177421569824</v>
       </c>
       <c r="H816" t="n">
         <v>30550</v>
@@ -24062,7 +24062,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G817" t="n">
-        <v>4.83270597457886</v>
+        <v>4.83270645141602</v>
       </c>
       <c r="H817" t="n">
         <v>29376</v>
@@ -24178,7 +24178,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G821" t="n">
-        <v>4.83270597457886</v>
+        <v>4.83270645141602</v>
       </c>
       <c r="H821" t="n">
         <v>677</v>
@@ -24236,7 +24236,7 @@
         <v>6</v>
       </c>
       <c r="G823" t="n">
-        <v>5.36967325210571</v>
+        <v>5.36967372894287</v>
       </c>
       <c r="H823" t="n">
         <v>1900</v>
@@ -24265,7 +24265,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G824" t="n">
-        <v>5.47706651687622</v>
+        <v>5.47706699371338</v>
       </c>
       <c r="H824" t="n">
         <v>100</v>
@@ -24323,7 +24323,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G826" t="n">
-        <v>5.54866218566895</v>
+        <v>5.5486626625061</v>
       </c>
       <c r="H826" t="n">
         <v>610</v>
@@ -24352,7 +24352,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G827" t="n">
-        <v>5.54866218566895</v>
+        <v>5.5486626625061</v>
       </c>
       <c r="H827" t="n">
         <v>0</v>
@@ -24381,7 +24381,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G828" t="n">
-        <v>5.54866218566895</v>
+        <v>5.5486626625061</v>
       </c>
       <c r="H828" t="n">
         <v>600</v>
@@ -24410,7 +24410,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G829" t="n">
-        <v>5.54866218566895</v>
+        <v>5.5486626625061</v>
       </c>
       <c r="H829" t="n">
         <v>0</v>
@@ -24439,7 +24439,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G830" t="n">
-        <v>5.72765159606934</v>
+        <v>5.72765207290649</v>
       </c>
       <c r="H830" t="n">
         <v>1323</v>
@@ -24497,7 +24497,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G832" t="n">
-        <v>5.72765159606934</v>
+        <v>5.72765207290649</v>
       </c>
       <c r="H832" t="n">
         <v>420</v>
@@ -24700,7 +24700,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G839" t="n">
-        <v>5.54866218566895</v>
+        <v>5.5486626625061</v>
       </c>
       <c r="H839" t="n">
         <v>400</v>
@@ -24729,7 +24729,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G840" t="n">
-        <v>5.53076362609863</v>
+        <v>5.53076314926147</v>
       </c>
       <c r="H840" t="n">
         <v>422</v>
@@ -24903,7 +24903,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G846" t="n">
-        <v>5.72765159606934</v>
+        <v>5.72765207290649</v>
       </c>
       <c r="H846" t="n">
         <v>100</v>
@@ -24961,7 +24961,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G848" t="n">
-        <v>5.72765159606934</v>
+        <v>5.72765207290649</v>
       </c>
       <c r="H848" t="n">
         <v>1038</v>
@@ -25048,7 +25048,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G851" t="n">
-        <v>5.70975303649902</v>
+        <v>5.70975255966187</v>
       </c>
       <c r="H851" t="n">
         <v>961</v>
@@ -25077,7 +25077,7 @@
         <v>6.5</v>
       </c>
       <c r="G852" t="n">
-        <v>5.81714582443237</v>
+        <v>5.81714630126953</v>
       </c>
       <c r="H852" t="n">
         <v>263</v>
@@ -25106,7 +25106,7 @@
         <v>6.5</v>
       </c>
       <c r="G853" t="n">
-        <v>5.81714582443237</v>
+        <v>5.81714630126953</v>
       </c>
       <c r="H853" t="n">
         <v>1153</v>
@@ -25193,7 +25193,7 @@
         <v>6.42000007629395</v>
       </c>
       <c r="G856" t="n">
-        <v>5.74555110931396</v>
+        <v>5.74555063247681</v>
       </c>
       <c r="H856" t="n">
         <v>396</v>
@@ -25222,7 +25222,7 @@
         <v>6.51999998092651</v>
       </c>
       <c r="G857" t="n">
-        <v>5.835045337677</v>
+        <v>5.83504486083984</v>
       </c>
       <c r="H857" t="n">
         <v>100</v>
@@ -25251,7 +25251,7 @@
         <v>6.51999998092651</v>
       </c>
       <c r="G858" t="n">
-        <v>5.835045337677</v>
+        <v>5.83504486083984</v>
       </c>
       <c r="H858" t="n">
         <v>0</v>
@@ -25280,7 +25280,7 @@
         <v>6.51999998092651</v>
       </c>
       <c r="G859" t="n">
-        <v>5.835045337677</v>
+        <v>5.83504486083984</v>
       </c>
       <c r="H859" t="n">
         <v>0</v>
@@ -25396,7 +25396,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G863" t="n">
-        <v>5.8887414932251</v>
+        <v>5.88874197006226</v>
       </c>
       <c r="H863" t="n">
         <v>1364</v>
@@ -25454,7 +25454,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G865" t="n">
-        <v>5.8887414932251</v>
+        <v>5.88874197006226</v>
       </c>
       <c r="H865" t="n">
         <v>1988</v>
@@ -25541,7 +25541,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G868" t="n">
-        <v>6.08563041687012</v>
+        <v>6.08562994003296</v>
       </c>
       <c r="H868" t="n">
         <v>500</v>
@@ -25570,7 +25570,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G869" t="n">
-        <v>6.08563041687012</v>
+        <v>6.08562994003296</v>
       </c>
       <c r="H869" t="n">
         <v>0</v>
@@ -25860,7 +25860,7 @@
         <v>6.5</v>
       </c>
       <c r="G879" t="n">
-        <v>5.81714582443237</v>
+        <v>5.81714630126953</v>
       </c>
       <c r="H879" t="n">
         <v>314</v>
@@ -25918,7 +25918,7 @@
         <v>6.73999977111816</v>
       </c>
       <c r="G881" t="n">
-        <v>6.03193283081055</v>
+        <v>6.03193330764771</v>
       </c>
       <c r="H881" t="n">
         <v>400</v>
@@ -25976,7 +25976,7 @@
         <v>6.71999979019165</v>
       </c>
       <c r="G883" t="n">
-        <v>6.01403427124023</v>
+        <v>6.01403379440308</v>
       </c>
       <c r="H883" t="n">
         <v>200</v>
@@ -26005,7 +26005,7 @@
         <v>6.71999979019165</v>
       </c>
       <c r="G884" t="n">
-        <v>6.01403427124023</v>
+        <v>6.01403379440308</v>
       </c>
       <c r="H884" t="n">
         <v>0</v>
@@ -26150,7 +26150,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G889" t="n">
-        <v>5.72765159606934</v>
+        <v>5.72765207290649</v>
       </c>
       <c r="H889" t="n">
         <v>1703</v>
@@ -26179,7 +26179,7 @@
         <v>6.5</v>
       </c>
       <c r="G890" t="n">
-        <v>5.81714582443237</v>
+        <v>5.81714630126953</v>
       </c>
       <c r="H890" t="n">
         <v>662</v>
@@ -26208,7 +26208,7 @@
         <v>6.71999979019165</v>
       </c>
       <c r="G891" t="n">
-        <v>6.01403427124023</v>
+        <v>6.01403379440308</v>
       </c>
       <c r="H891" t="n">
         <v>155</v>
@@ -26237,7 +26237,7 @@
         <v>6.71999979019165</v>
       </c>
       <c r="G892" t="n">
-        <v>6.01403427124023</v>
+        <v>6.01403379440308</v>
       </c>
       <c r="H892" t="n">
         <v>0</v>
@@ -26266,7 +26266,7 @@
         <v>6.71999979019165</v>
       </c>
       <c r="G893" t="n">
-        <v>6.01403427124023</v>
+        <v>6.01403379440308</v>
       </c>
       <c r="H893" t="n">
         <v>0</v>
@@ -26556,7 +26556,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G903" t="n">
-        <v>6.9805760383606</v>
+        <v>6.98057556152344</v>
       </c>
       <c r="H903" t="n">
         <v>2180</v>
@@ -26614,7 +26614,7 @@
         <v>7.57999992370605</v>
       </c>
       <c r="G905" t="n">
-        <v>6.78368711471558</v>
+        <v>6.78368759155273</v>
       </c>
       <c r="H905" t="n">
         <v>2196</v>
@@ -26701,7 +26701,7 @@
         <v>7.03999996185303</v>
       </c>
       <c r="G908" t="n">
-        <v>6.30041646957397</v>
+        <v>6.30041694641113</v>
       </c>
       <c r="H908" t="n">
         <v>5650</v>
@@ -26759,7 +26759,7 @@
         <v>7.1399998664856</v>
       </c>
       <c r="G910" t="n">
-        <v>6.38991165161133</v>
+        <v>6.38991117477417</v>
       </c>
       <c r="H910" t="n">
         <v>1158</v>
@@ -26962,7 +26962,7 @@
         <v>7.26000022888184</v>
       </c>
       <c r="G917" t="n">
-        <v>6.49730539321899</v>
+        <v>6.49730491638184</v>
       </c>
       <c r="H917" t="n">
         <v>3000</v>
@@ -26991,7 +26991,7 @@
         <v>7.42000007629395</v>
       </c>
       <c r="G918" t="n">
-        <v>6.64049625396729</v>
+        <v>6.64049673080444</v>
       </c>
       <c r="H918" t="n">
         <v>2331</v>
@@ -27078,7 +27078,7 @@
         <v>7.34000015258789</v>
       </c>
       <c r="G921" t="n">
-        <v>6.56890106201172</v>
+        <v>6.56890058517456</v>
       </c>
       <c r="H921" t="n">
         <v>250</v>
@@ -27136,7 +27136,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G923" t="n">
-        <v>6.80158662796021</v>
+        <v>6.80158615112305</v>
       </c>
       <c r="H923" t="n">
         <v>2203</v>
@@ -27397,7 +27397,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G932" t="n">
-        <v>6.80158662796021</v>
+        <v>6.80158615112305</v>
       </c>
       <c r="H932" t="n">
         <v>2264</v>
@@ -27455,7 +27455,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G934" t="n">
-        <v>6.80158662796021</v>
+        <v>6.80158615112305</v>
       </c>
       <c r="H934" t="n">
         <v>1250</v>
@@ -27513,7 +27513,7 @@
         <v>7.34000015258789</v>
       </c>
       <c r="G936" t="n">
-        <v>6.56890106201172</v>
+        <v>6.56890058517456</v>
       </c>
       <c r="H936" t="n">
         <v>75</v>
@@ -27687,7 +27687,7 @@
         <v>7.26000022888184</v>
       </c>
       <c r="G942" t="n">
-        <v>6.49730539321899</v>
+        <v>6.49730491638184</v>
       </c>
       <c r="H942" t="n">
         <v>4218</v>
@@ -27716,7 +27716,7 @@
         <v>7.26000022888184</v>
       </c>
       <c r="G943" t="n">
-        <v>6.49730539321899</v>
+        <v>6.49730491638184</v>
       </c>
       <c r="H943" t="n">
         <v>0</v>
@@ -27745,7 +27745,7 @@
         <v>7.26000022888184</v>
       </c>
       <c r="G944" t="n">
-        <v>6.49730539321899</v>
+        <v>6.49730491638184</v>
       </c>
       <c r="H944" t="n">
         <v>0</v>
@@ -27803,7 +27803,7 @@
         <v>7.21999979019165</v>
       </c>
       <c r="G946" t="n">
-        <v>6.46150684356689</v>
+        <v>6.46150732040405</v>
       </c>
       <c r="H946" t="n">
         <v>103974</v>
@@ -27832,7 +27832,7 @@
         <v>7.21999979019165</v>
       </c>
       <c r="G947" t="n">
-        <v>6.46150684356689</v>
+        <v>6.46150732040405</v>
       </c>
       <c r="H947" t="n">
         <v>574</v>
@@ -28238,7 +28238,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G961" t="n">
-        <v>6.08563041687012</v>
+        <v>6.08562994003296</v>
       </c>
       <c r="H961" t="n">
         <v>1113</v>
@@ -28557,7 +28557,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G972" t="n">
-        <v>6.08563041687012</v>
+        <v>6.08562994003296</v>
       </c>
       <c r="H972" t="n">
         <v>250</v>
@@ -30065,7 +30065,7 @@
         <v>7.25</v>
       </c>
       <c r="G1024" t="n">
-        <v>6.48835515975952</v>
+        <v>6.48835563659668</v>
       </c>
       <c r="H1024" t="n">
         <v>712</v>
@@ -30181,7 +30181,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G1028" t="n">
-        <v>6.8463339805603</v>
+        <v>6.84633350372314</v>
       </c>
       <c r="H1028" t="n">
         <v>12728</v>
@@ -30210,7 +30210,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G1029" t="n">
-        <v>6.9805760383606</v>
+        <v>6.98057556152344</v>
       </c>
       <c r="H1029" t="n">
         <v>238</v>
@@ -30239,7 +30239,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G1030" t="n">
-        <v>6.9805760383606</v>
+        <v>6.98057556152344</v>
       </c>
       <c r="H1030" t="n">
         <v>1</v>
@@ -30268,7 +30268,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G1031" t="n">
-        <v>6.9805760383606</v>
+        <v>6.98057556152344</v>
       </c>
       <c r="H1031" t="n">
         <v>100</v>
@@ -30326,7 +30326,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G1033" t="n">
-        <v>6.75683975219727</v>
+        <v>6.75683927536011</v>
       </c>
       <c r="H1033" t="n">
         <v>670</v>
@@ -30355,7 +30355,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G1034" t="n">
-        <v>6.75683975219727</v>
+        <v>6.75683927536011</v>
       </c>
       <c r="H1034" t="n">
         <v>0</v>
@@ -30384,7 +30384,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G1035" t="n">
-        <v>6.75683975219727</v>
+        <v>6.75683927536011</v>
       </c>
       <c r="H1035" t="n">
         <v>0</v>
@@ -30413,7 +30413,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G1036" t="n">
-        <v>6.75683975219727</v>
+        <v>6.75683927536011</v>
       </c>
       <c r="H1036" t="n">
         <v>0</v>
@@ -30442,7 +30442,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G1037" t="n">
-        <v>6.9805760383606</v>
+        <v>6.98057556152344</v>
       </c>
       <c r="H1037" t="n">
         <v>500</v>
@@ -30471,7 +30471,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G1038" t="n">
-        <v>6.80158662796021</v>
+        <v>6.80158615112305</v>
       </c>
       <c r="H1038" t="n">
         <v>730</v>
@@ -30500,7 +30500,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G1039" t="n">
-        <v>6.80158662796021</v>
+        <v>6.80158615112305</v>
       </c>
       <c r="H1039" t="n">
         <v>0</v>
@@ -30558,7 +30558,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G1041" t="n">
-        <v>6.80158662796021</v>
+        <v>6.80158615112305</v>
       </c>
       <c r="H1041" t="n">
         <v>13</v>
@@ -30587,7 +30587,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G1042" t="n">
-        <v>6.80158662796021</v>
+        <v>6.80158615112305</v>
       </c>
       <c r="H1042" t="n">
         <v>0</v>
@@ -30616,7 +30616,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G1043" t="n">
-        <v>6.80158662796021</v>
+        <v>6.80158615112305</v>
       </c>
       <c r="H1043" t="n">
         <v>0</v>
@@ -30645,7 +30645,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G1044" t="n">
-        <v>6.80158662796021</v>
+        <v>6.80158615112305</v>
       </c>
       <c r="H1044" t="n">
         <v>0</v>
@@ -30674,7 +30674,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G1045" t="n">
-        <v>6.80158662796021</v>
+        <v>6.80158615112305</v>
       </c>
       <c r="H1045" t="n">
         <v>0</v>
@@ -30703,7 +30703,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G1046" t="n">
-        <v>6.80158662796021</v>
+        <v>6.80158615112305</v>
       </c>
       <c r="H1046" t="n">
         <v>0</v>
@@ -30732,7 +30732,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G1047" t="n">
-        <v>6.80158662796021</v>
+        <v>6.80158615112305</v>
       </c>
       <c r="H1047" t="n">
         <v>0</v>
@@ -30761,7 +30761,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G1048" t="n">
-        <v>6.9805760383606</v>
+        <v>6.98057556152344</v>
       </c>
       <c r="H1048" t="n">
         <v>601</v>
@@ -30790,7 +30790,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G1049" t="n">
-        <v>6.8463339805603</v>
+        <v>6.84633350372314</v>
       </c>
       <c r="H1049" t="n">
         <v>100</v>
@@ -30819,7 +30819,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G1050" t="n">
-        <v>6.9805760383606</v>
+        <v>6.98057556152344</v>
       </c>
       <c r="H1050" t="n">
         <v>460</v>
@@ -30848,7 +30848,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G1051" t="n">
-        <v>6.9805760383606</v>
+        <v>6.98057556152344</v>
       </c>
       <c r="H1051" t="n">
         <v>125</v>
@@ -30877,7 +30877,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G1052" t="n">
-        <v>6.9805760383606</v>
+        <v>6.98057556152344</v>
       </c>
       <c r="H1052" t="n">
         <v>0</v>
@@ -30906,7 +30906,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G1053" t="n">
-        <v>6.80158662796021</v>
+        <v>6.80158615112305</v>
       </c>
       <c r="H1053" t="n">
         <v>1684</v>
@@ -31080,7 +31080,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G1059" t="n">
-        <v>6.75683975219727</v>
+        <v>6.75683927536011</v>
       </c>
       <c r="H1059" t="n">
         <v>400</v>
@@ -31109,7 +31109,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G1060" t="n">
-        <v>6.75683975219727</v>
+        <v>6.75683927536011</v>
       </c>
       <c r="H1060" t="n">
         <v>0</v>
@@ -31138,7 +31138,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G1061" t="n">
-        <v>6.75683975219727</v>
+        <v>6.75683927536011</v>
       </c>
       <c r="H1061" t="n">
         <v>0</v>
@@ -31602,7 +31602,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G1077" t="n">
-        <v>5.86189413070679</v>
+        <v>5.86189365386963</v>
       </c>
       <c r="H1077" t="n">
         <v>846</v>
@@ -31631,7 +31631,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G1078" t="n">
-        <v>5.72765159606934</v>
+        <v>5.72765207290649</v>
       </c>
       <c r="H1078" t="n">
         <v>2019</v>
@@ -31660,7 +31660,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G1079" t="n">
-        <v>5.86189413070679</v>
+        <v>5.86189365386963</v>
       </c>
       <c r="H1079" t="n">
         <v>100</v>
@@ -31747,7 +31747,7 @@
         <v>6</v>
       </c>
       <c r="G1082" t="n">
-        <v>5.36967325210571</v>
+        <v>5.36967372894287</v>
       </c>
       <c r="H1082" t="n">
         <v>11354</v>
@@ -31776,7 +31776,7 @@
         <v>6</v>
       </c>
       <c r="G1083" t="n">
-        <v>5.36967325210571</v>
+        <v>5.36967372894287</v>
       </c>
       <c r="H1083" t="n">
         <v>25500</v>
@@ -31805,7 +31805,7 @@
         <v>6</v>
       </c>
       <c r="G1084" t="n">
-        <v>5.36967325210571</v>
+        <v>5.36967372894287</v>
       </c>
       <c r="H1084" t="n">
         <v>0</v>
@@ -31863,7 +31863,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G1086" t="n">
-        <v>5.32492589950562</v>
+        <v>5.32492637634277</v>
       </c>
       <c r="H1086" t="n">
         <v>6465</v>
@@ -31892,7 +31892,7 @@
         <v>6</v>
       </c>
       <c r="G1087" t="n">
-        <v>5.36967325210571</v>
+        <v>5.36967372894287</v>
       </c>
       <c r="H1087" t="n">
         <v>6931</v>
@@ -31921,7 +31921,7 @@
         <v>6</v>
       </c>
       <c r="G1088" t="n">
-        <v>5.36967325210571</v>
+        <v>5.36967372894287</v>
       </c>
       <c r="H1088" t="n">
         <v>0</v>
@@ -31950,7 +31950,7 @@
         <v>6</v>
       </c>
       <c r="G1089" t="n">
-        <v>5.36967325210571</v>
+        <v>5.36967372894287</v>
       </c>
       <c r="H1089" t="n">
         <v>0</v>
@@ -31979,7 +31979,7 @@
         <v>6</v>
       </c>
       <c r="G1090" t="n">
-        <v>5.36967325210571</v>
+        <v>5.36967372894287</v>
       </c>
       <c r="H1090" t="n">
         <v>850</v>
@@ -32008,7 +32008,7 @@
         <v>6</v>
       </c>
       <c r="G1091" t="n">
-        <v>5.36967325210571</v>
+        <v>5.36967372894287</v>
       </c>
       <c r="H1091" t="n">
         <v>240</v>
@@ -32037,7 +32037,7 @@
         <v>6</v>
       </c>
       <c r="G1092" t="n">
-        <v>5.36967325210571</v>
+        <v>5.36967372894287</v>
       </c>
       <c r="H1092" t="n">
         <v>650</v>
@@ -32066,7 +32066,7 @@
         <v>6</v>
       </c>
       <c r="G1093" t="n">
-        <v>5.36967325210571</v>
+        <v>5.36967372894287</v>
       </c>
       <c r="H1093" t="n">
         <v>675</v>
@@ -32095,7 +32095,7 @@
         <v>6</v>
       </c>
       <c r="G1094" t="n">
-        <v>5.36967325210571</v>
+        <v>5.36967372894287</v>
       </c>
       <c r="H1094" t="n">
         <v>0</v>
@@ -32124,7 +32124,7 @@
         <v>6</v>
       </c>
       <c r="G1095" t="n">
-        <v>5.36967325210571</v>
+        <v>5.36967372894287</v>
       </c>
       <c r="H1095" t="n">
         <v>0</v>
@@ -32414,7 +32414,7 @@
         <v>6.25</v>
       </c>
       <c r="G1105" t="n">
-        <v>5.59340953826904</v>
+        <v>5.5934100151062</v>
       </c>
       <c r="H1105" t="n">
         <v>14260</v>
@@ -32443,7 +32443,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G1106" t="n">
-        <v>5.54866218566895</v>
+        <v>5.5486626625061</v>
       </c>
       <c r="H1106" t="n">
         <v>39658</v>
@@ -32559,7 +32559,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G1110" t="n">
-        <v>5.54866218566895</v>
+        <v>5.5486626625061</v>
       </c>
       <c r="H1110" t="n">
         <v>21380</v>
@@ -32617,7 +32617,7 @@
         <v>6.5</v>
       </c>
       <c r="G1112" t="n">
-        <v>5.81714582443237</v>
+        <v>5.81714630126953</v>
       </c>
       <c r="H1112" t="n">
         <v>29853</v>
@@ -32646,7 +32646,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G1113" t="n">
-        <v>5.72765159606934</v>
+        <v>5.72765207290649</v>
       </c>
       <c r="H1113" t="n">
         <v>31724</v>
@@ -32675,7 +32675,7 @@
         <v>6.5</v>
       </c>
       <c r="G1114" t="n">
-        <v>5.81714582443237</v>
+        <v>5.81714630126953</v>
       </c>
       <c r="H1114" t="n">
         <v>15604</v>
@@ -32791,7 +32791,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G1118" t="n">
-        <v>6.08563041687012</v>
+        <v>6.08562994003296</v>
       </c>
       <c r="H1118" t="n">
         <v>46505</v>
@@ -32965,7 +32965,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G1124" t="n">
-        <v>6.75683975219727</v>
+        <v>6.75683927536011</v>
       </c>
       <c r="H1124" t="n">
         <v>52998</v>
@@ -53996,6 +53996,35 @@
         <v>1277</v>
       </c>
       <c r="I1849" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1850">
+      <c r="A1850" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1850" s="1" t="n">
+        <v>46318.2916666667</v>
+      </c>
+      <c r="C1850" t="n">
+        <v>2.22000002861023</v>
+      </c>
+      <c r="D1850" t="n">
+        <v>2.22000002861023</v>
+      </c>
+      <c r="E1850" t="n">
+        <v>2.22000002861023</v>
+      </c>
+      <c r="F1850" t="n">
+        <v>2.22000002861023</v>
+      </c>
+      <c r="G1850" t="n">
+        <v>2.22000002861023</v>
+      </c>
+      <c r="H1850" t="n">
+        <v>700</v>
+      </c>
+      <c r="I1850" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/PTR.MI.xlsx
+++ b/data/PTR.MI.xlsx
@@ -456,7 +456,7 @@
         <v>3.7409999370575</v>
       </c>
       <c r="G3" t="n">
-        <v>3.24703454971313</v>
+        <v>3.24703478813171</v>
       </c>
       <c r="H3" t="n">
         <v>329252</v>
@@ -543,7 +543,7 @@
         <v>3.69250011444092</v>
       </c>
       <c r="G6" t="n">
-        <v>3.20493865013123</v>
+        <v>3.2049388885498</v>
       </c>
       <c r="H6" t="n">
         <v>56036</v>
@@ -572,7 +572,7 @@
         <v>3.56850004196167</v>
       </c>
       <c r="G7" t="n">
-        <v>3.09731197357178</v>
+        <v>3.0973117351532</v>
       </c>
       <c r="H7" t="n">
         <v>71079</v>
@@ -601,7 +601,7 @@
         <v>3.5864999294281</v>
       </c>
       <c r="G8" t="n">
-        <v>3.11293458938599</v>
+        <v>3.11293482780457</v>
       </c>
       <c r="H8" t="n">
         <v>37148</v>
@@ -688,7 +688,7 @@
         <v>3.47849988937378</v>
       </c>
       <c r="G11" t="n">
-        <v>3.01919531822205</v>
+        <v>3.01919555664062</v>
       </c>
       <c r="H11" t="n">
         <v>324435</v>
@@ -717,7 +717,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G12" t="n">
-        <v>3.08125424385071</v>
+        <v>3.08125448226929</v>
       </c>
       <c r="H12" t="n">
         <v>29251</v>
@@ -746,7 +746,7 @@
         <v>3.59400010108948</v>
       </c>
       <c r="G13" t="n">
-        <v>3.11944460868835</v>
+        <v>3.11944484710693</v>
       </c>
       <c r="H13" t="n">
         <v>13465</v>
@@ -775,7 +775,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G14" t="n">
-        <v>3.12465238571167</v>
+        <v>3.12465262413025</v>
       </c>
       <c r="H14" t="n">
         <v>10463</v>
@@ -804,7 +804,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G15" t="n">
-        <v>3.14201140403748</v>
+        <v>3.14201164245605</v>
       </c>
       <c r="H15" t="n">
         <v>8335</v>
@@ -833,7 +833,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G16" t="n">
-        <v>3.14201140403748</v>
+        <v>3.14201164245605</v>
       </c>
       <c r="H16" t="n">
         <v>6164</v>
@@ -862,7 +862,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G17" t="n">
-        <v>3.08993434906006</v>
+        <v>3.0899338722229</v>
       </c>
       <c r="H17" t="n">
         <v>939</v>
@@ -891,7 +891,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G18" t="n">
-        <v>3.14201140403748</v>
+        <v>3.14201164245605</v>
       </c>
       <c r="H18" t="n">
         <v>10770</v>
@@ -949,7 +949,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G20" t="n">
-        <v>3.12465238571167</v>
+        <v>3.12465262413025</v>
       </c>
       <c r="H20" t="n">
         <v>1924</v>
@@ -1210,7 +1210,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G29" t="n">
-        <v>3.08125424385071</v>
+        <v>3.08125448226929</v>
       </c>
       <c r="H29" t="n">
         <v>12055</v>
@@ -1239,7 +1239,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G30" t="n">
-        <v>3.08993434906006</v>
+        <v>3.0899338722229</v>
       </c>
       <c r="H30" t="n">
         <v>11148</v>
@@ -1268,7 +1268,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G31" t="n">
-        <v>3.08993434906006</v>
+        <v>3.0899338722229</v>
       </c>
       <c r="H31" t="n">
         <v>1210</v>
@@ -1355,7 +1355,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G34" t="n">
-        <v>3.10729336738586</v>
+        <v>3.10729312896729</v>
       </c>
       <c r="H34" t="n">
         <v>3335</v>
@@ -1442,7 +1442,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G37" t="n">
-        <v>3.14201140403748</v>
+        <v>3.14201164245605</v>
       </c>
       <c r="H37" t="n">
         <v>49352</v>
@@ -1471,7 +1471,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G38" t="n">
-        <v>3.19408941268921</v>
+        <v>3.19408917427063</v>
       </c>
       <c r="H38" t="n">
         <v>32777</v>
@@ -1500,7 +1500,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G39" t="n">
-        <v>3.21144866943359</v>
+        <v>3.21144843101501</v>
       </c>
       <c r="H39" t="n">
         <v>28455</v>
@@ -1587,7 +1587,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G42" t="n">
-        <v>3.29824423789978</v>
+        <v>3.2982439994812</v>
       </c>
       <c r="H42" t="n">
         <v>4451</v>
@@ -1616,7 +1616,7 @@
         <v>3.82500004768372</v>
       </c>
       <c r="G43" t="n">
-        <v>3.31994342803955</v>
+        <v>3.31994318962097</v>
       </c>
       <c r="H43" t="n">
         <v>5962</v>
@@ -1674,7 +1674,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G45" t="n">
-        <v>3.17672991752625</v>
+        <v>3.17673015594482</v>
       </c>
       <c r="H45" t="n">
         <v>1155</v>
@@ -1703,7 +1703,7 @@
         <v>3.71499991416931</v>
       </c>
       <c r="G46" t="n">
-        <v>3.22446751594543</v>
+        <v>3.22446775436401</v>
       </c>
       <c r="H46" t="n">
         <v>3406</v>
@@ -1732,7 +1732,7 @@
         <v>3.64499998092651</v>
       </c>
       <c r="G47" t="n">
-        <v>3.16371035575867</v>
+        <v>3.16371059417725</v>
       </c>
       <c r="H47" t="n">
         <v>3589</v>
@@ -1790,7 +1790,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G49" t="n">
-        <v>3.21144866943359</v>
+        <v>3.21144843101501</v>
       </c>
       <c r="H49" t="n">
         <v>17100</v>
@@ -1819,7 +1819,7 @@
         <v>3.71499991416931</v>
       </c>
       <c r="G50" t="n">
-        <v>3.22446751594543</v>
+        <v>3.22446775436401</v>
       </c>
       <c r="H50" t="n">
         <v>7667</v>
@@ -1877,7 +1877,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G52" t="n">
-        <v>3.21144866943359</v>
+        <v>3.21144843101501</v>
       </c>
       <c r="H52" t="n">
         <v>49416</v>
@@ -1906,7 +1906,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G53" t="n">
-        <v>3.17672991752625</v>
+        <v>3.17673015594482</v>
       </c>
       <c r="H53" t="n">
         <v>18126</v>
@@ -1935,7 +1935,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G54" t="n">
-        <v>3.21144866943359</v>
+        <v>3.21144843101501</v>
       </c>
       <c r="H54" t="n">
         <v>4498</v>
@@ -2051,7 +2051,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G58" t="n">
-        <v>3.17672991752625</v>
+        <v>3.17673015594482</v>
       </c>
       <c r="H58" t="n">
         <v>1957</v>
@@ -2080,7 +2080,7 @@
         <v>3.66499996185303</v>
       </c>
       <c r="G59" t="n">
-        <v>3.18106961250305</v>
+        <v>3.18106985092163</v>
       </c>
       <c r="H59" t="n">
         <v>20</v>
@@ -2138,7 +2138,7 @@
         <v>3.66499996185303</v>
       </c>
       <c r="G61" t="n">
-        <v>3.18106961250305</v>
+        <v>3.18106985092163</v>
       </c>
       <c r="H61" t="n">
         <v>27542</v>
@@ -2167,7 +2167,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G62" t="n">
-        <v>3.21144866943359</v>
+        <v>3.21144843101501</v>
       </c>
       <c r="H62" t="n">
         <v>20</v>
@@ -2196,7 +2196,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G63" t="n">
-        <v>3.14201140403748</v>
+        <v>3.14201164245605</v>
       </c>
       <c r="H63" t="n">
         <v>2540</v>
@@ -2225,7 +2225,7 @@
         <v>3.5550000667572</v>
       </c>
       <c r="G64" t="n">
-        <v>3.08559465408325</v>
+        <v>3.08559441566467</v>
       </c>
       <c r="H64" t="n">
         <v>550</v>
@@ -2254,7 +2254,7 @@
         <v>3.5550000667572</v>
       </c>
       <c r="G65" t="n">
-        <v>3.08559465408325</v>
+        <v>3.08559441566467</v>
       </c>
       <c r="H65" t="n">
         <v>2547</v>
@@ -2341,7 +2341,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G68" t="n">
-        <v>3.12465238571167</v>
+        <v>3.12465262413025</v>
       </c>
       <c r="H68" t="n">
         <v>2020</v>
@@ -2370,7 +2370,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G69" t="n">
-        <v>3.12465238571167</v>
+        <v>3.12465262413025</v>
       </c>
       <c r="H69" t="n">
         <v>7428</v>
@@ -2428,7 +2428,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G71" t="n">
-        <v>3.21144866943359</v>
+        <v>3.21144843101501</v>
       </c>
       <c r="H71" t="n">
         <v>2275</v>
@@ -2457,7 +2457,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G72" t="n">
-        <v>3.12465238571167</v>
+        <v>3.12465262413025</v>
       </c>
       <c r="H72" t="n">
         <v>29395</v>
@@ -2486,7 +2486,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G73" t="n">
-        <v>3.08125424385071</v>
+        <v>3.08125448226929</v>
       </c>
       <c r="H73" t="n">
         <v>22487</v>
@@ -2515,7 +2515,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G74" t="n">
-        <v>3.08125424385071</v>
+        <v>3.08125448226929</v>
       </c>
       <c r="H74" t="n">
         <v>6950</v>
@@ -2602,7 +2602,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G77" t="n">
-        <v>3.08125424385071</v>
+        <v>3.08125448226929</v>
       </c>
       <c r="H77" t="n">
         <v>1858</v>
@@ -2631,7 +2631,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G78" t="n">
-        <v>3.12465238571167</v>
+        <v>3.12465262413025</v>
       </c>
       <c r="H78" t="n">
         <v>908</v>
@@ -2660,7 +2660,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G79" t="n">
-        <v>3.14201140403748</v>
+        <v>3.14201164245605</v>
       </c>
       <c r="H79" t="n">
         <v>66825</v>
@@ -2747,7 +2747,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G82" t="n">
-        <v>3.14201140403748</v>
+        <v>3.14201164245605</v>
       </c>
       <c r="H82" t="n">
         <v>1300</v>
@@ -2776,7 +2776,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G83" t="n">
-        <v>3.29824423789978</v>
+        <v>3.2982439994812</v>
       </c>
       <c r="H83" t="n">
         <v>198082</v>
@@ -2805,7 +2805,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G84" t="n">
-        <v>3.29824423789978</v>
+        <v>3.2982439994812</v>
       </c>
       <c r="H84" t="n">
         <v>33903</v>
@@ -2834,7 +2834,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G85" t="n">
-        <v>3.29824423789978</v>
+        <v>3.2982439994812</v>
       </c>
       <c r="H85" t="n">
         <v>18308</v>
@@ -2863,7 +2863,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G86" t="n">
-        <v>3.29824423789978</v>
+        <v>3.2982439994812</v>
       </c>
       <c r="H86" t="n">
         <v>6890</v>
@@ -2892,7 +2892,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G87" t="n">
-        <v>3.37636041641235</v>
+        <v>3.37636065483093</v>
       </c>
       <c r="H87" t="n">
         <v>25644</v>
@@ -3037,7 +3037,7 @@
         <v>4</v>
       </c>
       <c r="G92" t="n">
-        <v>3.47183585166931</v>
+        <v>3.47183609008789</v>
       </c>
       <c r="H92" t="n">
         <v>9228</v>
@@ -3298,7 +3298,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G101" t="n">
-        <v>3.54127264022827</v>
+        <v>3.54127240180969</v>
       </c>
       <c r="H101" t="n">
         <v>4200</v>
@@ -3327,7 +3327,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G102" t="n">
-        <v>3.44579744338989</v>
+        <v>3.44579720497131</v>
       </c>
       <c r="H102" t="n">
         <v>1743</v>
@@ -3356,7 +3356,7 @@
         <v>4</v>
       </c>
       <c r="G103" t="n">
-        <v>3.47183585166931</v>
+        <v>3.47183609008789</v>
       </c>
       <c r="H103" t="n">
         <v>11798</v>
@@ -3385,7 +3385,7 @@
         <v>3.9449999332428</v>
       </c>
       <c r="G104" t="n">
-        <v>3.4240984916687</v>
+        <v>3.42409825325012</v>
       </c>
       <c r="H104" t="n">
         <v>26075</v>
@@ -3414,7 +3414,7 @@
         <v>4</v>
       </c>
       <c r="G105" t="n">
-        <v>3.47183585166931</v>
+        <v>3.47183609008789</v>
       </c>
       <c r="H105" t="n">
         <v>5886</v>
@@ -3617,7 +3617,7 @@
         <v>4.41499996185303</v>
       </c>
       <c r="G112" t="n">
-        <v>3.83203864097595</v>
+        <v>3.83203887939453</v>
       </c>
       <c r="H112" t="n">
         <v>30401</v>
@@ -3733,7 +3733,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G116" t="n">
-        <v>3.86241698265076</v>
+        <v>3.86241722106934</v>
       </c>
       <c r="H116" t="n">
         <v>17964</v>
@@ -3849,7 +3849,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G120" t="n">
-        <v>3.86241698265076</v>
+        <v>3.86241722106934</v>
       </c>
       <c r="H120" t="n">
         <v>34190</v>
@@ -3907,7 +3907,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G122" t="n">
-        <v>3.94053411483765</v>
+        <v>3.94053363800049</v>
       </c>
       <c r="H122" t="n">
         <v>5398</v>
@@ -4168,7 +4168,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G131" t="n">
-        <v>4.49602794647217</v>
+        <v>4.49602746963501</v>
       </c>
       <c r="H131" t="n">
         <v>4316</v>
@@ -4197,7 +4197,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G132" t="n">
-        <v>4.49602794647217</v>
+        <v>4.49602746963501</v>
       </c>
       <c r="H132" t="n">
         <v>2480</v>
@@ -4226,7 +4226,7 @@
         <v>4.97499990463257</v>
       </c>
       <c r="G133" t="n">
-        <v>4.31809616088867</v>
+        <v>4.31809568405151</v>
       </c>
       <c r="H133" t="n">
         <v>8257</v>
@@ -4458,7 +4458,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G141" t="n">
-        <v>4.42659044265747</v>
+        <v>4.42659139633179</v>
       </c>
       <c r="H141" t="n">
         <v>9500</v>
@@ -4487,7 +4487,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G142" t="n">
-        <v>4.35715436935425</v>
+        <v>4.35715389251709</v>
       </c>
       <c r="H142" t="n">
         <v>21331</v>
@@ -4545,7 +4545,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G144" t="n">
-        <v>4.42659044265747</v>
+        <v>4.42659139633179</v>
       </c>
       <c r="H144" t="n">
         <v>5800</v>
@@ -4661,7 +4661,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G148" t="n">
-        <v>4.49602794647217</v>
+        <v>4.49602746963501</v>
       </c>
       <c r="H148" t="n">
         <v>14318</v>
@@ -4719,7 +4719,7 @@
         <v>5.13000011444092</v>
       </c>
       <c r="G150" t="n">
-        <v>4.45262956619263</v>
+        <v>4.45263004302979</v>
       </c>
       <c r="H150" t="n">
         <v>6278</v>
@@ -4835,7 +4835,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G154" t="n">
-        <v>4.00129079818726</v>
+        <v>4.00129175186157</v>
       </c>
       <c r="H154" t="n">
         <v>9345</v>
@@ -4951,7 +4951,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G158" t="n">
-        <v>4.00129079818726</v>
+        <v>4.00129175186157</v>
       </c>
       <c r="H158" t="n">
         <v>25178</v>
@@ -4980,7 +4980,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G159" t="n">
-        <v>4.09676647186279</v>
+        <v>4.09676599502563</v>
       </c>
       <c r="H159" t="n">
         <v>11440</v>
@@ -5009,7 +5009,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G160" t="n">
-        <v>4.06204795837402</v>
+        <v>4.06204843521118</v>
       </c>
       <c r="H160" t="n">
         <v>4897</v>
@@ -5067,7 +5067,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G162" t="n">
-        <v>3.99261116981506</v>
+        <v>3.99261140823364</v>
       </c>
       <c r="H162" t="n">
         <v>1599</v>
@@ -5125,7 +5125,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G164" t="n">
-        <v>3.17672991752625</v>
+        <v>3.17673015594482</v>
       </c>
       <c r="H164" t="n">
         <v>13665</v>
@@ -5212,7 +5212,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G167" t="n">
-        <v>2.72539138793945</v>
+        <v>2.72539114952087</v>
       </c>
       <c r="H167" t="n">
         <v>16142</v>
@@ -5241,7 +5241,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G168" t="n">
-        <v>2.95974016189575</v>
+        <v>2.95974040031433</v>
       </c>
       <c r="H168" t="n">
         <v>11032</v>
@@ -5299,7 +5299,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G170" t="n">
-        <v>3.12465238571167</v>
+        <v>3.12465262413025</v>
       </c>
       <c r="H170" t="n">
         <v>862</v>
@@ -5328,7 +5328,7 @@
         <v>3.375</v>
       </c>
       <c r="G171" t="n">
-        <v>2.92936158180237</v>
+        <v>2.92936182022095</v>
       </c>
       <c r="H171" t="n">
         <v>1699</v>
@@ -5473,7 +5473,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G176" t="n">
-        <v>3.08125424385071</v>
+        <v>3.08125448226929</v>
       </c>
       <c r="H176" t="n">
         <v>9550</v>
@@ -5560,7 +5560,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G179" t="n">
-        <v>3.21144866943359</v>
+        <v>3.21144843101501</v>
       </c>
       <c r="H179" t="n">
         <v>6765</v>
@@ -5589,7 +5589,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G180" t="n">
-        <v>3.31560349464417</v>
+        <v>3.31560325622559</v>
       </c>
       <c r="H180" t="n">
         <v>27302</v>
@@ -5676,7 +5676,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G183" t="n">
-        <v>3.19408941268921</v>
+        <v>3.19408917427063</v>
       </c>
       <c r="H183" t="n">
         <v>14368</v>
@@ -5705,7 +5705,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G184" t="n">
-        <v>3.21144866943359</v>
+        <v>3.21144843101501</v>
       </c>
       <c r="H184" t="n">
         <v>4102</v>
@@ -5734,7 +5734,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G185" t="n">
-        <v>3.19408941268921</v>
+        <v>3.19408917427063</v>
       </c>
       <c r="H185" t="n">
         <v>20637</v>
@@ -5792,7 +5792,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G187" t="n">
-        <v>3.21144866943359</v>
+        <v>3.21144843101501</v>
       </c>
       <c r="H187" t="n">
         <v>10326</v>
@@ -5821,7 +5821,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G188" t="n">
-        <v>3.29824423789978</v>
+        <v>3.2982439994812</v>
       </c>
       <c r="H188" t="n">
         <v>5632</v>
@@ -5850,7 +5850,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G189" t="n">
-        <v>3.22880744934082</v>
+        <v>3.2288076877594</v>
       </c>
       <c r="H189" t="n">
         <v>7860</v>
@@ -5879,7 +5879,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G190" t="n">
-        <v>3.18540930747986</v>
+        <v>3.18540954589844</v>
       </c>
       <c r="H190" t="n">
         <v>13689</v>
@@ -5908,7 +5908,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G191" t="n">
-        <v>3.2808849811554</v>
+        <v>3.28088521957397</v>
       </c>
       <c r="H191" t="n">
         <v>15966</v>
@@ -5966,7 +5966,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G193" t="n">
-        <v>3.29824423789978</v>
+        <v>3.2982439994812</v>
       </c>
       <c r="H193" t="n">
         <v>13631</v>
@@ -5995,7 +5995,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G194" t="n">
-        <v>3.29824423789978</v>
+        <v>3.2982439994812</v>
       </c>
       <c r="H194" t="n">
         <v>5341</v>
@@ -6024,7 +6024,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G195" t="n">
-        <v>3.34164214134216</v>
+        <v>3.34164190292358</v>
       </c>
       <c r="H195" t="n">
         <v>6546</v>
@@ -6285,7 +6285,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G204" t="n">
-        <v>3.19408941268921</v>
+        <v>3.19408917427063</v>
       </c>
       <c r="H204" t="n">
         <v>55244</v>
@@ -6314,7 +6314,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G205" t="n">
-        <v>3.29824423789978</v>
+        <v>3.2982439994812</v>
       </c>
       <c r="H205" t="n">
         <v>4357</v>
@@ -6343,7 +6343,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G206" t="n">
-        <v>3.31560349464417</v>
+        <v>3.31560325622559</v>
       </c>
       <c r="H206" t="n">
         <v>105630</v>
@@ -6372,7 +6372,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G207" t="n">
-        <v>3.37636041641235</v>
+        <v>3.37636065483093</v>
       </c>
       <c r="H207" t="n">
         <v>12630</v>
@@ -6459,7 +6459,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G210" t="n">
-        <v>3.22880744934082</v>
+        <v>3.2288076877594</v>
       </c>
       <c r="H210" t="n">
         <v>9234</v>
@@ -6488,7 +6488,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G211" t="n">
-        <v>3.29824423789978</v>
+        <v>3.2982439994812</v>
       </c>
       <c r="H211" t="n">
         <v>8606</v>
@@ -6517,7 +6517,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G212" t="n">
-        <v>3.2722053527832</v>
+        <v>3.27220559120178</v>
       </c>
       <c r="H212" t="n">
         <v>676</v>
@@ -6546,7 +6546,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G213" t="n">
-        <v>3.22880744934082</v>
+        <v>3.2288076877594</v>
       </c>
       <c r="H213" t="n">
         <v>1194</v>
@@ -6575,7 +6575,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G214" t="n">
-        <v>3.2808849811554</v>
+        <v>3.28088521957397</v>
       </c>
       <c r="H214" t="n">
         <v>1000</v>
@@ -6633,7 +6633,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G216" t="n">
-        <v>3.2808849811554</v>
+        <v>3.28088521957397</v>
       </c>
       <c r="H216" t="n">
         <v>5107</v>
@@ -6662,7 +6662,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G217" t="n">
-        <v>3.29824423789978</v>
+        <v>3.2982439994812</v>
       </c>
       <c r="H217" t="n">
         <v>16383</v>
@@ -6691,7 +6691,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G218" t="n">
-        <v>3.2808849811554</v>
+        <v>3.28088521957397</v>
       </c>
       <c r="H218" t="n">
         <v>3100</v>
@@ -6720,7 +6720,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G219" t="n">
-        <v>3.29824423789978</v>
+        <v>3.2982439994812</v>
       </c>
       <c r="H219" t="n">
         <v>6884</v>
@@ -6807,7 +6807,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G222" t="n">
-        <v>3.29824423789978</v>
+        <v>3.2982439994812</v>
       </c>
       <c r="H222" t="n">
         <v>4259</v>
@@ -6836,7 +6836,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G223" t="n">
-        <v>3.34164214134216</v>
+        <v>3.34164190292358</v>
       </c>
       <c r="H223" t="n">
         <v>1631</v>
@@ -6923,7 +6923,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G226" t="n">
-        <v>3.37636041641235</v>
+        <v>3.37636065483093</v>
       </c>
       <c r="H226" t="n">
         <v>19966</v>
@@ -6952,7 +6952,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G227" t="n">
-        <v>3.29824423789978</v>
+        <v>3.2982439994812</v>
       </c>
       <c r="H227" t="n">
         <v>6610</v>
@@ -7010,7 +7010,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G229" t="n">
-        <v>3.2722053527832</v>
+        <v>3.27220559120178</v>
       </c>
       <c r="H229" t="n">
         <v>2568</v>
@@ -7039,7 +7039,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G230" t="n">
-        <v>3.37636041641235</v>
+        <v>3.37636065483093</v>
       </c>
       <c r="H230" t="n">
         <v>4045</v>
@@ -7068,7 +7068,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G231" t="n">
-        <v>3.31560349464417</v>
+        <v>3.31560325622559</v>
       </c>
       <c r="H231" t="n">
         <v>5113</v>
@@ -7097,7 +7097,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G232" t="n">
-        <v>3.35032153129578</v>
+        <v>3.35032176971436</v>
       </c>
       <c r="H232" t="n">
         <v>11475</v>
@@ -7126,7 +7126,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G233" t="n">
-        <v>3.37636041641235</v>
+        <v>3.37636065483093</v>
       </c>
       <c r="H233" t="n">
         <v>111</v>
@@ -7155,7 +7155,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G234" t="n">
-        <v>3.37636041641235</v>
+        <v>3.37636065483093</v>
       </c>
       <c r="H234" t="n">
         <v>0</v>
@@ -7329,7 +7329,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G240" t="n">
-        <v>3.29824423789978</v>
+        <v>3.2982439994812</v>
       </c>
       <c r="H240" t="n">
         <v>2500</v>
@@ -7358,7 +7358,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G241" t="n">
-        <v>3.34164214134216</v>
+        <v>3.34164190292358</v>
       </c>
       <c r="H241" t="n">
         <v>1540</v>
@@ -7474,7 +7474,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G245" t="n">
-        <v>3.2722053527832</v>
+        <v>3.27220559120178</v>
       </c>
       <c r="H245" t="n">
         <v>51600</v>
@@ -7503,7 +7503,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G246" t="n">
-        <v>3.29824423789978</v>
+        <v>3.2982439994812</v>
       </c>
       <c r="H246" t="n">
         <v>2471</v>
@@ -7648,7 +7648,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G251" t="n">
-        <v>3.18540930747986</v>
+        <v>3.18540954589844</v>
       </c>
       <c r="H251" t="n">
         <v>6820</v>
@@ -7677,7 +7677,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G252" t="n">
-        <v>3.21144866943359</v>
+        <v>3.21144843101501</v>
       </c>
       <c r="H252" t="n">
         <v>57</v>
@@ -7706,7 +7706,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G253" t="n">
-        <v>3.21144866943359</v>
+        <v>3.21144843101501</v>
       </c>
       <c r="H253" t="n">
         <v>0</v>
@@ -7764,7 +7764,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G255" t="n">
-        <v>3.18540930747986</v>
+        <v>3.18540954589844</v>
       </c>
       <c r="H255" t="n">
         <v>1005</v>
@@ -7793,7 +7793,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G256" t="n">
-        <v>3.22880744934082</v>
+        <v>3.2288076877594</v>
       </c>
       <c r="H256" t="n">
         <v>250</v>
@@ -7880,7 +7880,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G259" t="n">
-        <v>3.22880744934082</v>
+        <v>3.2288076877594</v>
       </c>
       <c r="H259" t="n">
         <v>29483</v>
@@ -7909,7 +7909,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G260" t="n">
-        <v>3.08993434906006</v>
+        <v>3.0899338722229</v>
       </c>
       <c r="H260" t="n">
         <v>31039</v>
@@ -7996,7 +7996,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G263" t="n">
-        <v>3.08993434906006</v>
+        <v>3.0899338722229</v>
       </c>
       <c r="H263" t="n">
         <v>5405</v>
@@ -8054,7 +8054,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G265" t="n">
-        <v>3.07257461547852</v>
+        <v>3.07257485389709</v>
       </c>
       <c r="H265" t="n">
         <v>1250</v>
@@ -8199,7 +8199,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G270" t="n">
-        <v>3.19408941268921</v>
+        <v>3.19408917427063</v>
       </c>
       <c r="H270" t="n">
         <v>883</v>
@@ -8257,7 +8257,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G272" t="n">
-        <v>3.12465238571167</v>
+        <v>3.12465262413025</v>
       </c>
       <c r="H272" t="n">
         <v>9221</v>
@@ -8315,7 +8315,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G274" t="n">
-        <v>2.93370151519775</v>
+        <v>2.93370127677917</v>
       </c>
       <c r="H274" t="n">
         <v>4510</v>
@@ -8431,7 +8431,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G278" t="n">
-        <v>3.07257461547852</v>
+        <v>3.07257485389709</v>
       </c>
       <c r="H278" t="n">
         <v>4119</v>
@@ -8518,7 +8518,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G281" t="n">
-        <v>3.0638952255249</v>
+        <v>3.06389546394348</v>
       </c>
       <c r="H281" t="n">
         <v>1883</v>
@@ -8547,7 +8547,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G282" t="n">
-        <v>3.0638952255249</v>
+        <v>3.06389546394348</v>
       </c>
       <c r="H282" t="n">
         <v>0</v>
@@ -8576,7 +8576,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G283" t="n">
-        <v>3.0638952255249</v>
+        <v>3.06389546394348</v>
       </c>
       <c r="H283" t="n">
         <v>1100</v>
@@ -8605,7 +8605,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G284" t="n">
-        <v>2.94238114356995</v>
+        <v>2.94238138198853</v>
       </c>
       <c r="H284" t="n">
         <v>2758</v>
@@ -8634,7 +8634,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G285" t="n">
-        <v>2.94238114356995</v>
+        <v>2.94238138198853</v>
       </c>
       <c r="H285" t="n">
         <v>20</v>
@@ -8750,7 +8750,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G289" t="n">
-        <v>3.08125424385071</v>
+        <v>3.08125448226929</v>
       </c>
       <c r="H289" t="n">
         <v>945</v>
@@ -8895,7 +8895,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G294" t="n">
-        <v>3.08125424385071</v>
+        <v>3.08125448226929</v>
       </c>
       <c r="H294" t="n">
         <v>4</v>
@@ -8953,7 +8953,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G296" t="n">
-        <v>2.95106053352356</v>
+        <v>2.95106077194214</v>
       </c>
       <c r="H296" t="n">
         <v>2886</v>
@@ -8982,7 +8982,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G297" t="n">
-        <v>2.95106053352356</v>
+        <v>2.95106077194214</v>
       </c>
       <c r="H297" t="n">
         <v>599</v>
@@ -9040,7 +9040,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G299" t="n">
-        <v>2.86426448822021</v>
+        <v>2.86426472663879</v>
       </c>
       <c r="H299" t="n">
         <v>18061</v>
@@ -9069,7 +9069,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G300" t="n">
-        <v>2.86426448822021</v>
+        <v>2.86426472663879</v>
       </c>
       <c r="H300" t="n">
         <v>0</v>
@@ -9098,7 +9098,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G301" t="n">
-        <v>2.86426448822021</v>
+        <v>2.86426472663879</v>
       </c>
       <c r="H301" t="n">
         <v>14192</v>
@@ -9127,7 +9127,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G302" t="n">
-        <v>2.95974016189575</v>
+        <v>2.95974040031433</v>
       </c>
       <c r="H302" t="n">
         <v>10987</v>
@@ -9156,7 +9156,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G303" t="n">
-        <v>2.88162398338318</v>
+        <v>2.8816237449646</v>
       </c>
       <c r="H303" t="n">
         <v>7318</v>
@@ -9243,7 +9243,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G306" t="n">
-        <v>3.08125424385071</v>
+        <v>3.08125448226929</v>
       </c>
       <c r="H306" t="n">
         <v>17490</v>
@@ -9272,7 +9272,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G307" t="n">
-        <v>3.12465238571167</v>
+        <v>3.12465262413025</v>
       </c>
       <c r="H307" t="n">
         <v>9075</v>
@@ -9301,7 +9301,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G308" t="n">
-        <v>3.12465238571167</v>
+        <v>3.12465262413025</v>
       </c>
       <c r="H308" t="n">
         <v>6589</v>
@@ -9446,7 +9446,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G313" t="n">
-        <v>3.21144866943359</v>
+        <v>3.21144843101501</v>
       </c>
       <c r="H313" t="n">
         <v>2665</v>
@@ -9475,7 +9475,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G314" t="n">
-        <v>3.19408941268921</v>
+        <v>3.19408917427063</v>
       </c>
       <c r="H314" t="n">
         <v>9433</v>
@@ -9504,7 +9504,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G315" t="n">
-        <v>3.21144866943359</v>
+        <v>3.21144843101501</v>
       </c>
       <c r="H315" t="n">
         <v>456</v>
@@ -9562,7 +9562,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G317" t="n">
-        <v>3.21144866943359</v>
+        <v>3.21144843101501</v>
       </c>
       <c r="H317" t="n">
         <v>1600</v>
@@ -9591,7 +9591,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G318" t="n">
-        <v>3.17672991752625</v>
+        <v>3.17673015594482</v>
       </c>
       <c r="H318" t="n">
         <v>6400</v>
@@ -9678,7 +9678,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G321" t="n">
-        <v>3.21144866943359</v>
+        <v>3.21144843101501</v>
       </c>
       <c r="H321" t="n">
         <v>2251</v>
@@ -9736,7 +9736,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G323" t="n">
-        <v>3.21144866943359</v>
+        <v>3.21144843101501</v>
       </c>
       <c r="H323" t="n">
         <v>220</v>
@@ -9765,7 +9765,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G324" t="n">
-        <v>3.21144866943359</v>
+        <v>3.21144843101501</v>
       </c>
       <c r="H324" t="n">
         <v>4700</v>
@@ -9794,7 +9794,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G325" t="n">
-        <v>3.21144866943359</v>
+        <v>3.21144843101501</v>
       </c>
       <c r="H325" t="n">
         <v>650</v>
@@ -9823,7 +9823,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G326" t="n">
-        <v>3.19408941268921</v>
+        <v>3.19408917427063</v>
       </c>
       <c r="H326" t="n">
         <v>6000</v>
@@ -9852,7 +9852,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G327" t="n">
-        <v>3.14201140403748</v>
+        <v>3.14201164245605</v>
       </c>
       <c r="H327" t="n">
         <v>1954</v>
@@ -9881,7 +9881,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G328" t="n">
-        <v>3.21144866943359</v>
+        <v>3.21144843101501</v>
       </c>
       <c r="H328" t="n">
         <v>2264</v>
@@ -9910,7 +9910,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G329" t="n">
-        <v>3.12465238571167</v>
+        <v>3.12465262413025</v>
       </c>
       <c r="H329" t="n">
         <v>3400</v>
@@ -9939,7 +9939,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G330" t="n">
-        <v>3.19408941268921</v>
+        <v>3.19408917427063</v>
       </c>
       <c r="H330" t="n">
         <v>3070</v>
@@ -10287,7 +10287,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G342" t="n">
-        <v>3.21144866943359</v>
+        <v>3.21144843101501</v>
       </c>
       <c r="H342" t="n">
         <v>3660</v>
@@ -10403,7 +10403,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G346" t="n">
-        <v>3.21144866943359</v>
+        <v>3.21144843101501</v>
       </c>
       <c r="H346" t="n">
         <v>5550</v>
@@ -10432,7 +10432,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G347" t="n">
-        <v>3.31560349464417</v>
+        <v>3.31560325622559</v>
       </c>
       <c r="H347" t="n">
         <v>11800</v>
@@ -10490,7 +10490,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G349" t="n">
-        <v>3.31560349464417</v>
+        <v>3.31560325622559</v>
       </c>
       <c r="H349" t="n">
         <v>1269</v>
@@ -10548,7 +10548,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G351" t="n">
-        <v>3.31560349464417</v>
+        <v>3.31560325622559</v>
       </c>
       <c r="H351" t="n">
         <v>1729</v>
@@ -10577,7 +10577,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G352" t="n">
-        <v>3.34164214134216</v>
+        <v>3.34164190292358</v>
       </c>
       <c r="H352" t="n">
         <v>1770</v>
@@ -10635,7 +10635,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G354" t="n">
-        <v>3.34164214134216</v>
+        <v>3.34164190292358</v>
       </c>
       <c r="H354" t="n">
         <v>1650</v>
@@ -10751,7 +10751,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G358" t="n">
-        <v>3.37636041641235</v>
+        <v>3.37636065483093</v>
       </c>
       <c r="H358" t="n">
         <v>800</v>
@@ -10780,7 +10780,7 @@
         <v>4</v>
       </c>
       <c r="G359" t="n">
-        <v>3.47183585166931</v>
+        <v>3.47183609008789</v>
       </c>
       <c r="H359" t="n">
         <v>3169</v>
@@ -10809,7 +10809,7 @@
         <v>4</v>
       </c>
       <c r="G360" t="n">
-        <v>3.47183585166931</v>
+        <v>3.47183609008789</v>
       </c>
       <c r="H360" t="n">
         <v>12</v>
@@ -10867,7 +10867,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G362" t="n">
-        <v>3.52457308769226</v>
+        <v>3.52457284927368</v>
       </c>
       <c r="H362" t="n">
         <v>1633</v>
@@ -10896,7 +10896,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G363" t="n">
-        <v>3.53336191177368</v>
+        <v>3.53336215019226</v>
       </c>
       <c r="H363" t="n">
         <v>425644</v>
@@ -10983,7 +10983,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G366" t="n">
-        <v>3.47183585166931</v>
+        <v>3.47183609008789</v>
       </c>
       <c r="H366" t="n">
         <v>16015</v>
@@ -11157,7 +11157,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G372" t="n">
-        <v>3.57730960845947</v>
+        <v>3.57730937004089</v>
       </c>
       <c r="H372" t="n">
         <v>5500</v>
@@ -11215,7 +11215,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G374" t="n">
-        <v>3.85857176780701</v>
+        <v>3.85857224464417</v>
       </c>
       <c r="H374" t="n">
         <v>3601</v>
@@ -11244,7 +11244,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G375" t="n">
-        <v>3.80583500862122</v>
+        <v>3.80583524703979</v>
       </c>
       <c r="H375" t="n">
         <v>1180</v>
@@ -11273,7 +11273,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G376" t="n">
-        <v>3.82341432571411</v>
+        <v>3.82341408729553</v>
       </c>
       <c r="H376" t="n">
         <v>4874</v>
@@ -11331,7 +11331,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G378" t="n">
-        <v>3.84978294372559</v>
+        <v>3.84978270530701</v>
       </c>
       <c r="H378" t="n">
         <v>9179</v>
@@ -11360,7 +11360,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G379" t="n">
-        <v>3.90251994132996</v>
+        <v>3.90251970291138</v>
       </c>
       <c r="H379" t="n">
         <v>28775</v>
@@ -11447,7 +11447,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G382" t="n">
-        <v>3.92888760566711</v>
+        <v>3.92888784408569</v>
       </c>
       <c r="H382" t="n">
         <v>12048</v>
@@ -11563,7 +11563,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G386" t="n">
-        <v>3.64762496948242</v>
+        <v>3.647625207901</v>
       </c>
       <c r="H386" t="n">
         <v>7282</v>
@@ -11592,7 +11592,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G387" t="n">
-        <v>3.4278883934021</v>
+        <v>3.42788887023926</v>
       </c>
       <c r="H387" t="n">
         <v>24073</v>
@@ -11621,7 +11621,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G388" t="n">
-        <v>3.550940990448</v>
+        <v>3.55094122886658</v>
       </c>
       <c r="H388" t="n">
         <v>7442</v>
@@ -11650,7 +11650,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G389" t="n">
-        <v>3.58609914779663</v>
+        <v>3.58609890937805</v>
       </c>
       <c r="H389" t="n">
         <v>19347</v>
@@ -11679,7 +11679,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G390" t="n">
-        <v>3.69157195091248</v>
+        <v>3.69157218933105</v>
       </c>
       <c r="H390" t="n">
         <v>9963</v>
@@ -11708,7 +11708,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G391" t="n">
-        <v>3.52457308769226</v>
+        <v>3.52457284927368</v>
       </c>
       <c r="H391" t="n">
         <v>14867</v>
@@ -11737,7 +11737,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G392" t="n">
-        <v>3.62125682830811</v>
+        <v>3.62125658988953</v>
       </c>
       <c r="H392" t="n">
         <v>15062</v>
@@ -11824,7 +11824,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G395" t="n">
-        <v>3.74430918693542</v>
+        <v>3.744309425354</v>
       </c>
       <c r="H395" t="n">
         <v>15241</v>
@@ -11882,7 +11882,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G397" t="n">
-        <v>3.82341432571411</v>
+        <v>3.82341408729553</v>
       </c>
       <c r="H397" t="n">
         <v>1515</v>
@@ -11969,7 +11969,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G400" t="n">
-        <v>3.62125682830811</v>
+        <v>3.62125658988953</v>
       </c>
       <c r="H400" t="n">
         <v>1948</v>
@@ -11998,7 +11998,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G401" t="n">
-        <v>3.58609914779663</v>
+        <v>3.58609890937805</v>
       </c>
       <c r="H401" t="n">
         <v>2243</v>
@@ -12027,7 +12027,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G402" t="n">
-        <v>3.60367751121521</v>
+        <v>3.60367774963379</v>
       </c>
       <c r="H402" t="n">
         <v>31743</v>
@@ -12085,7 +12085,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G404" t="n">
-        <v>3.90251994132996</v>
+        <v>3.90251970291138</v>
       </c>
       <c r="H404" t="n">
         <v>16220</v>
@@ -12114,7 +12114,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G405" t="n">
-        <v>3.84978294372559</v>
+        <v>3.84978270530701</v>
       </c>
       <c r="H405" t="n">
         <v>10519</v>
@@ -12143,7 +12143,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G406" t="n">
-        <v>3.84099292755127</v>
+        <v>3.84099316596985</v>
       </c>
       <c r="H406" t="n">
         <v>7000</v>
@@ -12172,7 +12172,7 @@
         <v>4.25</v>
       </c>
       <c r="G407" t="n">
-        <v>3.73552012443542</v>
+        <v>3.73551964759827</v>
       </c>
       <c r="H407" t="n">
         <v>7140</v>
@@ -12201,7 +12201,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G408" t="n">
-        <v>3.78825688362122</v>
+        <v>3.78825640678406</v>
       </c>
       <c r="H408" t="n">
         <v>9728</v>
@@ -12230,7 +12230,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G409" t="n">
-        <v>4.04315042495728</v>
+        <v>4.04315090179443</v>
       </c>
       <c r="H409" t="n">
         <v>11444</v>
@@ -12259,7 +12259,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G410" t="n">
-        <v>3.99920392036438</v>
+        <v>3.99920344352722</v>
       </c>
       <c r="H410" t="n">
         <v>13066</v>
@@ -12288,7 +12288,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G411" t="n">
-        <v>3.99920392036438</v>
+        <v>3.99920344352722</v>
       </c>
       <c r="H411" t="n">
         <v>3045</v>
@@ -12317,7 +12317,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G412" t="n">
-        <v>3.97283530235291</v>
+        <v>3.97283506393433</v>
       </c>
       <c r="H412" t="n">
         <v>3835</v>
@@ -12346,7 +12346,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G413" t="n">
-        <v>4.06072950363159</v>
+        <v>4.06072998046875</v>
       </c>
       <c r="H413" t="n">
         <v>1119</v>
@@ -12375,7 +12375,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G414" t="n">
-        <v>4.04315042495728</v>
+        <v>4.04315090179443</v>
       </c>
       <c r="H414" t="n">
         <v>4777</v>
@@ -12404,7 +12404,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G415" t="n">
-        <v>4.04315042495728</v>
+        <v>4.04315090179443</v>
       </c>
       <c r="H415" t="n">
         <v>0</v>
@@ -12433,7 +12433,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G416" t="n">
-        <v>3.99920392036438</v>
+        <v>3.99920344352722</v>
       </c>
       <c r="H416" t="n">
         <v>20150</v>
@@ -12462,7 +12462,7 @@
         <v>4.59000015258789</v>
       </c>
       <c r="G417" t="n">
-        <v>4.03436088562012</v>
+        <v>4.03436136245728</v>
       </c>
       <c r="H417" t="n">
         <v>6334</v>
@@ -12491,7 +12491,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G418" t="n">
-        <v>4.08709812164307</v>
+        <v>4.08709859848022</v>
       </c>
       <c r="H418" t="n">
         <v>6771</v>
@@ -12520,7 +12520,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G419" t="n">
-        <v>4.1486234664917</v>
+        <v>4.14862394332886</v>
       </c>
       <c r="H419" t="n">
         <v>3061</v>
@@ -12636,7 +12636,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G423" t="n">
-        <v>4.28046607971191</v>
+        <v>4.28046560287476</v>
       </c>
       <c r="H423" t="n">
         <v>7858</v>
@@ -12694,7 +12694,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G425" t="n">
-        <v>4.29804468154907</v>
+        <v>4.29804515838623</v>
       </c>
       <c r="H425" t="n">
         <v>2886</v>
@@ -12781,7 +12781,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G428" t="n">
-        <v>4.21015071868896</v>
+        <v>4.21015024185181</v>
       </c>
       <c r="H428" t="n">
         <v>3290</v>
@@ -12810,7 +12810,7 @@
         <v>4.75</v>
       </c>
       <c r="G429" t="n">
-        <v>4.17499303817749</v>
+        <v>4.17499256134033</v>
       </c>
       <c r="H429" t="n">
         <v>10</v>
@@ -12839,7 +12839,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G430" t="n">
-        <v>4.28925609588623</v>
+        <v>4.28925561904907</v>
       </c>
       <c r="H430" t="n">
         <v>7986</v>
@@ -12868,7 +12868,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G431" t="n">
-        <v>4.28925609588623</v>
+        <v>4.28925561904907</v>
       </c>
       <c r="H431" t="n">
         <v>2210</v>
@@ -12897,7 +12897,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G432" t="n">
-        <v>4.21015071868896</v>
+        <v>4.21015024185181</v>
       </c>
       <c r="H432" t="n">
         <v>6072</v>
@@ -12984,7 +12984,7 @@
         <v>4.75</v>
       </c>
       <c r="G435" t="n">
-        <v>4.17499303817749</v>
+        <v>4.17499256134033</v>
       </c>
       <c r="H435" t="n">
         <v>1500</v>
@@ -13013,7 +13013,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G436" t="n">
-        <v>4.21015071868896</v>
+        <v>4.21015024185181</v>
       </c>
       <c r="H436" t="n">
         <v>86</v>
@@ -13042,7 +13042,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G437" t="n">
-        <v>4.07830858230591</v>
+        <v>4.07830810546875</v>
       </c>
       <c r="H437" t="n">
         <v>2764</v>
@@ -13100,7 +13100,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G439" t="n">
-        <v>4.38593912124634</v>
+        <v>4.3859395980835</v>
       </c>
       <c r="H439" t="n">
         <v>2700</v>
@@ -13129,7 +13129,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G440" t="n">
-        <v>4.38593912124634</v>
+        <v>4.3859395980835</v>
       </c>
       <c r="H440" t="n">
         <v>100</v>
@@ -13216,7 +13216,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G443" t="n">
-        <v>4.35078191757202</v>
+        <v>4.35078144073486</v>
       </c>
       <c r="H443" t="n">
         <v>180</v>
@@ -13332,7 +13332,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G447" t="n">
-        <v>4.38593912124634</v>
+        <v>4.3859395980835</v>
       </c>
       <c r="H447" t="n">
         <v>20</v>
@@ -13506,7 +13506,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G453" t="n">
-        <v>4.21015071868896</v>
+        <v>4.21015024185181</v>
       </c>
       <c r="H453" t="n">
         <v>1012</v>
@@ -13535,7 +13535,7 @@
         <v>4.75</v>
       </c>
       <c r="G454" t="n">
-        <v>4.17499303817749</v>
+        <v>4.17499256134033</v>
       </c>
       <c r="H454" t="n">
         <v>220</v>
@@ -13593,7 +13593,7 @@
         <v>4.75</v>
       </c>
       <c r="G456" t="n">
-        <v>4.17499303817749</v>
+        <v>4.17499256134033</v>
       </c>
       <c r="H456" t="n">
         <v>7</v>
@@ -13622,7 +13622,7 @@
         <v>4.75</v>
       </c>
       <c r="G457" t="n">
-        <v>4.17499303817749</v>
+        <v>4.17499256134033</v>
       </c>
       <c r="H457" t="n">
         <v>0</v>
@@ -13651,7 +13651,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G458" t="n">
-        <v>4.05194044113159</v>
+        <v>4.05193996429443</v>
       </c>
       <c r="H458" t="n">
         <v>1015</v>
@@ -13680,7 +13680,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G459" t="n">
-        <v>4.02557229995728</v>
+        <v>4.02557134628296</v>
       </c>
       <c r="H459" t="n">
         <v>4000</v>
@@ -13709,7 +13709,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G460" t="n">
-        <v>4.02557229995728</v>
+        <v>4.02557134628296</v>
       </c>
       <c r="H460" t="n">
         <v>1607</v>
@@ -13738,7 +13738,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G461" t="n">
-        <v>4.02557229995728</v>
+        <v>4.02557134628296</v>
       </c>
       <c r="H461" t="n">
         <v>1400</v>
@@ -13767,7 +13767,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G462" t="n">
-        <v>4.08709812164307</v>
+        <v>4.08709859848022</v>
       </c>
       <c r="H462" t="n">
         <v>155</v>
@@ -13796,7 +13796,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G463" t="n">
-        <v>4.1486234664917</v>
+        <v>4.14862394332886</v>
       </c>
       <c r="H463" t="n">
         <v>13</v>
@@ -13825,7 +13825,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G464" t="n">
-        <v>4.21015071868896</v>
+        <v>4.21015024185181</v>
       </c>
       <c r="H464" t="n">
         <v>909</v>
@@ -13883,7 +13883,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G466" t="n">
-        <v>4.28925609588623</v>
+        <v>4.28925561904907</v>
       </c>
       <c r="H466" t="n">
         <v>1395</v>
@@ -13912,7 +13912,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G467" t="n">
-        <v>4.35078191757202</v>
+        <v>4.35078144073486</v>
       </c>
       <c r="H467" t="n">
         <v>12111</v>
@@ -14115,7 +14115,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G474" t="n">
-        <v>4.57807397842407</v>
+        <v>4.57807350158691</v>
       </c>
       <c r="H474" t="n">
         <v>5287</v>
@@ -14144,7 +14144,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G475" t="n">
-        <v>4.77250957489014</v>
+        <v>4.77250909805298</v>
       </c>
       <c r="H475" t="n">
         <v>3681</v>
@@ -14202,7 +14202,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G477" t="n">
-        <v>4.75483369827271</v>
+        <v>4.75483322143555</v>
       </c>
       <c r="H477" t="n">
         <v>3810</v>
@@ -14231,7 +14231,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G478" t="n">
-        <v>4.6487774848938</v>
+        <v>4.64877796173096</v>
       </c>
       <c r="H478" t="n">
         <v>1637</v>
@@ -14260,7 +14260,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G479" t="n">
-        <v>4.56039810180664</v>
+        <v>4.56039762496948</v>
       </c>
       <c r="H479" t="n">
         <v>500</v>
@@ -14318,7 +14318,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G481" t="n">
-        <v>4.56039810180664</v>
+        <v>4.56039762496948</v>
       </c>
       <c r="H481" t="n">
         <v>1763</v>
@@ -14492,7 +14492,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G487" t="n">
-        <v>4.56039810180664</v>
+        <v>4.56039762496948</v>
       </c>
       <c r="H487" t="n">
         <v>5900</v>
@@ -14521,7 +14521,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G488" t="n">
-        <v>4.56039810180664</v>
+        <v>4.56039762496948</v>
       </c>
       <c r="H488" t="n">
         <v>3324</v>
@@ -14666,7 +14666,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G493" t="n">
-        <v>4.26874446868896</v>
+        <v>4.26874494552612</v>
       </c>
       <c r="H493" t="n">
         <v>2410</v>
@@ -14695,7 +14695,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G494" t="n">
-        <v>4.22455453872681</v>
+        <v>4.22455501556396</v>
       </c>
       <c r="H494" t="n">
         <v>1787</v>
@@ -14724,7 +14724,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G495" t="n">
-        <v>4.1715259552002</v>
+        <v>4.17152690887451</v>
       </c>
       <c r="H495" t="n">
         <v>3325</v>
@@ -14782,7 +14782,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G497" t="n">
-        <v>4.03011894226074</v>
+        <v>4.03011846542358</v>
       </c>
       <c r="H497" t="n">
         <v>4388</v>
@@ -14811,7 +14811,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G498" t="n">
-        <v>4.03011894226074</v>
+        <v>4.03011846542358</v>
       </c>
       <c r="H498" t="n">
         <v>18707</v>
@@ -15072,7 +15072,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G507" t="n">
-        <v>4.22455453872681</v>
+        <v>4.22455501556396</v>
       </c>
       <c r="H507" t="n">
         <v>450</v>
@@ -15449,7 +15449,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G520" t="n">
-        <v>4.4896936416626</v>
+        <v>4.48969411849976</v>
       </c>
       <c r="H520" t="n">
         <v>1048</v>
@@ -15507,7 +15507,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G522" t="n">
-        <v>4.5957498550415</v>
+        <v>4.59574937820435</v>
       </c>
       <c r="H522" t="n">
         <v>200</v>
@@ -15536,7 +15536,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G523" t="n">
-        <v>4.5957498550415</v>
+        <v>4.59574937820435</v>
       </c>
       <c r="H523" t="n">
         <v>592</v>
@@ -15565,7 +15565,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G524" t="n">
-        <v>4.5957498550415</v>
+        <v>4.59574937820435</v>
       </c>
       <c r="H524" t="n">
         <v>0</v>
@@ -15594,7 +15594,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G525" t="n">
-        <v>4.5957498550415</v>
+        <v>4.59574937820435</v>
       </c>
       <c r="H525" t="n">
         <v>20</v>
@@ -15623,7 +15623,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G526" t="n">
-        <v>4.57807397842407</v>
+        <v>4.57807350158691</v>
       </c>
       <c r="H526" t="n">
         <v>2094</v>
@@ -15652,7 +15652,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G527" t="n">
-        <v>4.57807397842407</v>
+        <v>4.57807350158691</v>
       </c>
       <c r="H527" t="n">
         <v>50</v>
@@ -15826,7 +15826,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G533" t="n">
-        <v>4.33061027526855</v>
+        <v>4.33061075210571</v>
       </c>
       <c r="H533" t="n">
         <v>1000</v>
@@ -15855,7 +15855,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G534" t="n">
-        <v>4.26874446868896</v>
+        <v>4.26874494552612</v>
       </c>
       <c r="H534" t="n">
         <v>1220</v>
@@ -15884,7 +15884,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G535" t="n">
-        <v>4.28641986846924</v>
+        <v>4.2864203453064</v>
       </c>
       <c r="H535" t="n">
         <v>1300</v>
@@ -15913,7 +15913,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G536" t="n">
-        <v>4.28641986846924</v>
+        <v>4.2864203453064</v>
       </c>
       <c r="H536" t="n">
         <v>20</v>
@@ -15942,7 +15942,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G537" t="n">
-        <v>4.28641986846924</v>
+        <v>4.2864203453064</v>
       </c>
       <c r="H537" t="n">
         <v>4125</v>
@@ -15971,7 +15971,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G538" t="n">
-        <v>4.28641986846924</v>
+        <v>4.2864203453064</v>
       </c>
       <c r="H538" t="n">
         <v>3365</v>
@@ -16116,7 +16116,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G543" t="n">
-        <v>4.38363790512085</v>
+        <v>4.38363838195801</v>
       </c>
       <c r="H543" t="n">
         <v>902</v>
@@ -16145,7 +16145,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G544" t="n">
-        <v>4.36596250534058</v>
+        <v>4.36596202850342</v>
       </c>
       <c r="H544" t="n">
         <v>2872</v>
@@ -16174,7 +16174,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G545" t="n">
-        <v>4.36596250534058</v>
+        <v>4.36596202850342</v>
       </c>
       <c r="H545" t="n">
         <v>0</v>
@@ -16203,7 +16203,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G546" t="n">
-        <v>4.33944797515869</v>
+        <v>4.33944845199585</v>
       </c>
       <c r="H546" t="n">
         <v>1600</v>
@@ -16232,7 +16232,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G547" t="n">
-        <v>4.33944797515869</v>
+        <v>4.33944845199585</v>
       </c>
       <c r="H547" t="n">
         <v>0</v>
@@ -16261,7 +16261,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G548" t="n">
-        <v>4.33944797515869</v>
+        <v>4.33944845199585</v>
       </c>
       <c r="H548" t="n">
         <v>0</v>
@@ -16319,7 +16319,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G550" t="n">
-        <v>4.21571636199951</v>
+        <v>4.21571683883667</v>
       </c>
       <c r="H550" t="n">
         <v>3340</v>
@@ -16522,7 +16522,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G557" t="n">
-        <v>4.0743088722229</v>
+        <v>4.07430934906006</v>
       </c>
       <c r="H557" t="n">
         <v>4755</v>
@@ -16725,7 +16725,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G564" t="n">
-        <v>4.33061027526855</v>
+        <v>4.33061075210571</v>
       </c>
       <c r="H564" t="n">
         <v>6148</v>
@@ -16754,7 +16754,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G565" t="n">
-        <v>4.33061027526855</v>
+        <v>4.33061075210571</v>
       </c>
       <c r="H565" t="n">
         <v>2408</v>
@@ -16870,7 +16870,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G569" t="n">
-        <v>4.57807397842407</v>
+        <v>4.57807350158691</v>
       </c>
       <c r="H569" t="n">
         <v>10847</v>
@@ -16899,7 +16899,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G570" t="n">
-        <v>4.5957498550415</v>
+        <v>4.59574937820435</v>
       </c>
       <c r="H570" t="n">
         <v>2181</v>
@@ -16986,7 +16986,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G573" t="n">
-        <v>4.73715782165527</v>
+        <v>4.73715734481812</v>
       </c>
       <c r="H573" t="n">
         <v>798</v>
@@ -17102,7 +17102,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G577" t="n">
-        <v>4.91391706466675</v>
+        <v>4.91391658782959</v>
       </c>
       <c r="H577" t="n">
         <v>7024</v>
@@ -17131,7 +17131,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G578" t="n">
-        <v>4.96694469451904</v>
+        <v>4.9669451713562</v>
       </c>
       <c r="H578" t="n">
         <v>3512</v>
@@ -17160,7 +17160,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G579" t="n">
-        <v>4.89624118804932</v>
+        <v>4.89624071121216</v>
       </c>
       <c r="H579" t="n">
         <v>5879</v>
@@ -17189,7 +17189,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G580" t="n">
-        <v>4.94926881790161</v>
+        <v>4.94926929473877</v>
       </c>
       <c r="H580" t="n">
         <v>3440</v>
@@ -17218,7 +17218,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G581" t="n">
-        <v>5.10835266113281</v>
+        <v>5.10835313796997</v>
       </c>
       <c r="H581" t="n">
         <v>12053</v>
@@ -17450,7 +17450,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G589" t="n">
-        <v>5.65630769729614</v>
+        <v>5.65630722045898</v>
       </c>
       <c r="H589" t="n">
         <v>6708</v>
@@ -17479,7 +17479,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G590" t="n">
-        <v>5.65630769729614</v>
+        <v>5.65630722045898</v>
       </c>
       <c r="H590" t="n">
         <v>1609</v>
@@ -17537,7 +17537,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G592" t="n">
-        <v>5.51489925384521</v>
+        <v>5.51489973068237</v>
       </c>
       <c r="H592" t="n">
         <v>637</v>
@@ -17566,7 +17566,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G593" t="n">
-        <v>5.56792783737183</v>
+        <v>5.56792736053467</v>
       </c>
       <c r="H593" t="n">
         <v>3180</v>
@@ -17595,7 +17595,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G594" t="n">
-        <v>5.56792783737183</v>
+        <v>5.56792736053467</v>
       </c>
       <c r="H594" t="n">
         <v>3910</v>
@@ -17653,7 +17653,7 @@
         <v>6.71999979019165</v>
       </c>
       <c r="G596" t="n">
-        <v>5.93912315368652</v>
+        <v>5.93912267684937</v>
       </c>
       <c r="H596" t="n">
         <v>3720</v>
@@ -17740,7 +17740,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G599" t="n">
-        <v>5.65630769729614</v>
+        <v>5.65630722045898</v>
       </c>
       <c r="H599" t="n">
         <v>6734</v>
@@ -17769,7 +17769,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G600" t="n">
-        <v>5.72701120376587</v>
+        <v>5.72701072692871</v>
       </c>
       <c r="H600" t="n">
         <v>9122</v>
@@ -17827,7 +17827,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G602" t="n">
-        <v>5.49722385406494</v>
+        <v>5.49722337722778</v>
       </c>
       <c r="H602" t="n">
         <v>2401</v>
@@ -17856,7 +17856,7 @@
         <v>6.26000022888184</v>
       </c>
       <c r="G603" t="n">
-        <v>5.5325756072998</v>
+        <v>5.53257608413696</v>
       </c>
       <c r="H603" t="n">
         <v>20947</v>
@@ -17885,7 +17885,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G604" t="n">
-        <v>5.51489925384521</v>
+        <v>5.51489973068237</v>
       </c>
       <c r="H604" t="n">
         <v>946</v>
@@ -17914,7 +17914,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G605" t="n">
-        <v>5.72701120376587</v>
+        <v>5.72701072692871</v>
       </c>
       <c r="H605" t="n">
         <v>1318</v>
@@ -17943,7 +17943,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G606" t="n">
-        <v>5.72701120376587</v>
+        <v>5.72701072692871</v>
       </c>
       <c r="H606" t="n">
         <v>11320</v>
@@ -17972,7 +17972,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G607" t="n">
-        <v>5.55025148391724</v>
+        <v>5.55025196075439</v>
       </c>
       <c r="H607" t="n">
         <v>880</v>
@@ -18001,7 +18001,7 @@
         <v>6.26000022888184</v>
       </c>
       <c r="G608" t="n">
-        <v>5.5325756072998</v>
+        <v>5.53257608413696</v>
       </c>
       <c r="H608" t="n">
         <v>2120</v>
@@ -18088,7 +18088,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G611" t="n">
-        <v>5.72701120376587</v>
+        <v>5.72701072692871</v>
       </c>
       <c r="H611" t="n">
         <v>6700</v>
@@ -18117,7 +18117,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G612" t="n">
-        <v>5.72701120376587</v>
+        <v>5.72701072692871</v>
       </c>
       <c r="H612" t="n">
         <v>280</v>
@@ -18146,7 +18146,7 @@
         <v>6.53999996185303</v>
       </c>
       <c r="G613" t="n">
-        <v>5.78003931045532</v>
+        <v>5.78003883361816</v>
       </c>
       <c r="H613" t="n">
         <v>8888</v>
@@ -18175,7 +18175,7 @@
         <v>6.5</v>
       </c>
       <c r="G614" t="n">
-        <v>5.7446870803833</v>
+        <v>5.74468660354614</v>
       </c>
       <c r="H614" t="n">
         <v>2162</v>
@@ -18204,7 +18204,7 @@
         <v>6.5</v>
       </c>
       <c r="G615" t="n">
-        <v>5.7446870803833</v>
+        <v>5.74468660354614</v>
       </c>
       <c r="H615" t="n">
         <v>0</v>
@@ -18291,7 +18291,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G618" t="n">
-        <v>5.81539106369019</v>
+        <v>5.81539058685303</v>
       </c>
       <c r="H618" t="n">
         <v>2408</v>
@@ -18320,7 +18320,7 @@
         <v>6.5</v>
       </c>
       <c r="G619" t="n">
-        <v>5.7446870803833</v>
+        <v>5.74468660354614</v>
       </c>
       <c r="H619" t="n">
         <v>600</v>
@@ -18378,7 +18378,7 @@
         <v>6.26000022888184</v>
       </c>
       <c r="G621" t="n">
-        <v>5.5325756072998</v>
+        <v>5.53257608413696</v>
       </c>
       <c r="H621" t="n">
         <v>3812</v>
@@ -18407,7 +18407,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G622" t="n">
-        <v>5.39116811752319</v>
+        <v>5.39116764068604</v>
       </c>
       <c r="H622" t="n">
         <v>10704</v>
@@ -18465,7 +18465,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G624" t="n">
-        <v>5.65630769729614</v>
+        <v>5.65630722045898</v>
       </c>
       <c r="H624" t="n">
         <v>4043</v>
@@ -18494,7 +18494,7 @@
         <v>6.5</v>
       </c>
       <c r="G625" t="n">
-        <v>5.7446870803833</v>
+        <v>5.74468660354614</v>
       </c>
       <c r="H625" t="n">
         <v>1890</v>
@@ -18523,7 +18523,7 @@
         <v>6.5</v>
       </c>
       <c r="G626" t="n">
-        <v>5.7446870803833</v>
+        <v>5.74468660354614</v>
       </c>
       <c r="H626" t="n">
         <v>4190</v>
@@ -18552,7 +18552,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G627" t="n">
-        <v>6.00982666015625</v>
+        <v>6.00982713699341</v>
       </c>
       <c r="H627" t="n">
         <v>6922</v>
@@ -18639,7 +18639,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G630" t="n">
-        <v>6.00982666015625</v>
+        <v>6.00982713699341</v>
       </c>
       <c r="H630" t="n">
         <v>16000</v>
@@ -18668,7 +18668,7 @@
         <v>6.78000020980835</v>
       </c>
       <c r="G631" t="n">
-        <v>5.99215078353882</v>
+        <v>5.99215126037598</v>
       </c>
       <c r="H631" t="n">
         <v>200</v>
@@ -18697,7 +18697,7 @@
         <v>6.78000020980835</v>
       </c>
       <c r="G632" t="n">
-        <v>5.99215078353882</v>
+        <v>5.99215126037598</v>
       </c>
       <c r="H632" t="n">
         <v>0</v>
@@ -18900,7 +18900,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G639" t="n">
-        <v>5.58560371398926</v>
+        <v>5.5856032371521</v>
       </c>
       <c r="H639" t="n">
         <v>400</v>
@@ -19016,7 +19016,7 @@
         <v>6.53999996185303</v>
       </c>
       <c r="G643" t="n">
-        <v>5.78003931045532</v>
+        <v>5.78003883361816</v>
       </c>
       <c r="H643" t="n">
         <v>282</v>
@@ -19132,7 +19132,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G647" t="n">
-        <v>5.3734917640686</v>
+        <v>5.37349224090576</v>
       </c>
       <c r="H647" t="n">
         <v>1250</v>
@@ -19190,7 +19190,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G649" t="n">
-        <v>5.39116811752319</v>
+        <v>5.39116764068604</v>
       </c>
       <c r="H649" t="n">
         <v>2460</v>
@@ -19248,7 +19248,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G651" t="n">
-        <v>5.28511190414429</v>
+        <v>5.28511238098145</v>
       </c>
       <c r="H651" t="n">
         <v>1224</v>
@@ -19306,7 +19306,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G653" t="n">
-        <v>5.12602853775024</v>
+        <v>5.1260290145874</v>
       </c>
       <c r="H653" t="n">
         <v>2025</v>
@@ -19335,7 +19335,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G654" t="n">
-        <v>4.94926881790161</v>
+        <v>4.94926929473877</v>
       </c>
       <c r="H654" t="n">
         <v>3137</v>
@@ -19364,7 +19364,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G655" t="n">
-        <v>4.94926881790161</v>
+        <v>4.94926929473877</v>
       </c>
       <c r="H655" t="n">
         <v>14439</v>
@@ -19451,7 +19451,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G658" t="n">
-        <v>5.12602853775024</v>
+        <v>5.1260290145874</v>
       </c>
       <c r="H658" t="n">
         <v>2873</v>
@@ -19509,7 +19509,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G660" t="n">
-        <v>5.23208475112915</v>
+        <v>5.23208427429199</v>
       </c>
       <c r="H660" t="n">
         <v>16216</v>
@@ -19654,7 +19654,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G665" t="n">
-        <v>5.19673252105713</v>
+        <v>5.19673299789429</v>
       </c>
       <c r="H665" t="n">
         <v>500</v>
@@ -19683,7 +19683,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G666" t="n">
-        <v>4.71948194503784</v>
+        <v>4.71948146820068</v>
       </c>
       <c r="H666" t="n">
         <v>18954</v>
@@ -19712,7 +19712,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G667" t="n">
-        <v>4.77250957489014</v>
+        <v>4.77250909805298</v>
       </c>
       <c r="H667" t="n">
         <v>19980</v>
@@ -19770,7 +19770,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G669" t="n">
-        <v>4.75483369827271</v>
+        <v>4.75483322143555</v>
       </c>
       <c r="H669" t="n">
         <v>1824</v>
@@ -19799,7 +19799,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G670" t="n">
-        <v>4.71948194503784</v>
+        <v>4.71948146820068</v>
       </c>
       <c r="H670" t="n">
         <v>875</v>
@@ -19828,7 +19828,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G671" t="n">
-        <v>4.57807397842407</v>
+        <v>4.57807350158691</v>
       </c>
       <c r="H671" t="n">
         <v>623</v>
@@ -19857,7 +19857,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G672" t="n">
-        <v>4.6487774848938</v>
+        <v>4.64877796173096</v>
       </c>
       <c r="H672" t="n">
         <v>11719</v>
@@ -19886,7 +19886,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G673" t="n">
-        <v>4.28641986846924</v>
+        <v>4.2864203453064</v>
       </c>
       <c r="H673" t="n">
         <v>7472</v>
@@ -19915,7 +19915,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G674" t="n">
-        <v>4.28641986846924</v>
+        <v>4.2864203453064</v>
       </c>
       <c r="H674" t="n">
         <v>1700</v>
@@ -19944,7 +19944,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G675" t="n">
-        <v>4.33061027526855</v>
+        <v>4.33061075210571</v>
       </c>
       <c r="H675" t="n">
         <v>4500</v>
@@ -20031,7 +20031,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G678" t="n">
-        <v>4.33061027526855</v>
+        <v>4.33061075210571</v>
       </c>
       <c r="H678" t="n">
         <v>2456</v>
@@ -20147,7 +20147,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G682" t="n">
-        <v>4.71948194503784</v>
+        <v>4.71948146820068</v>
       </c>
       <c r="H682" t="n">
         <v>13546</v>
@@ -20176,7 +20176,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G683" t="n">
-        <v>4.77250957489014</v>
+        <v>4.77250909805298</v>
       </c>
       <c r="H683" t="n">
         <v>830</v>
@@ -20205,7 +20205,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G684" t="n">
-        <v>4.70180559158325</v>
+        <v>4.70180511474609</v>
       </c>
       <c r="H684" t="n">
         <v>8359</v>
@@ -20234,7 +20234,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G685" t="n">
-        <v>4.5957498550415</v>
+        <v>4.59574937820435</v>
       </c>
       <c r="H685" t="n">
         <v>450</v>
@@ -20350,7 +20350,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G689" t="n">
-        <v>4.75483369827271</v>
+        <v>4.75483322143555</v>
       </c>
       <c r="H689" t="n">
         <v>2400</v>
@@ -20379,7 +20379,7 @@
         <v>5.5</v>
       </c>
       <c r="G690" t="n">
-        <v>4.86088895797729</v>
+        <v>4.86088943481445</v>
       </c>
       <c r="H690" t="n">
         <v>2318</v>
@@ -20408,7 +20408,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G691" t="n">
-        <v>4.77250957489014</v>
+        <v>4.77250909805298</v>
       </c>
       <c r="H691" t="n">
         <v>4740</v>
@@ -20553,7 +20553,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G696" t="n">
-        <v>4.96694469451904</v>
+        <v>4.9669451713562</v>
       </c>
       <c r="H696" t="n">
         <v>1712</v>
@@ -20582,7 +20582,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G697" t="n">
-        <v>4.94926881790161</v>
+        <v>4.94926929473877</v>
       </c>
       <c r="H697" t="n">
         <v>6290</v>
@@ -20611,7 +20611,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G698" t="n">
-        <v>4.94926881790161</v>
+        <v>4.94926929473877</v>
       </c>
       <c r="H698" t="n">
         <v>190</v>
@@ -20640,7 +20640,7 @@
         <v>5.5</v>
       </c>
       <c r="G699" t="n">
-        <v>4.86088895797729</v>
+        <v>4.86088943481445</v>
       </c>
       <c r="H699" t="n">
         <v>1100</v>
@@ -20669,7 +20669,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G700" t="n">
-        <v>4.75483369827271</v>
+        <v>4.75483322143555</v>
       </c>
       <c r="H700" t="n">
         <v>1074</v>
@@ -20698,7 +20698,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G701" t="n">
-        <v>4.75483369827271</v>
+        <v>4.75483322143555</v>
       </c>
       <c r="H701" t="n">
         <v>1300</v>
@@ -20727,7 +20727,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G702" t="n">
-        <v>4.94926881790161</v>
+        <v>4.94926929473877</v>
       </c>
       <c r="H702" t="n">
         <v>4149</v>
@@ -20756,7 +20756,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G703" t="n">
-        <v>5.03764867782593</v>
+        <v>5.03764915466309</v>
       </c>
       <c r="H703" t="n">
         <v>303</v>
@@ -20785,7 +20785,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G704" t="n">
-        <v>5.03764867782593</v>
+        <v>5.03764915466309</v>
       </c>
       <c r="H704" t="n">
         <v>0</v>
@@ -20843,7 +20843,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G706" t="n">
-        <v>5.12602853775024</v>
+        <v>5.1260290145874</v>
       </c>
       <c r="H706" t="n">
         <v>661</v>
@@ -20930,7 +20930,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G709" t="n">
-        <v>5.12602853775024</v>
+        <v>5.1260290145874</v>
       </c>
       <c r="H709" t="n">
         <v>6815</v>
@@ -20959,7 +20959,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G710" t="n">
-        <v>5.12602853775024</v>
+        <v>5.1260290145874</v>
       </c>
       <c r="H710" t="n">
         <v>0</v>
@@ -21046,7 +21046,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G713" t="n">
-        <v>5.16138029098511</v>
+        <v>5.16138076782227</v>
       </c>
       <c r="H713" t="n">
         <v>3739</v>
@@ -21133,7 +21133,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G716" t="n">
-        <v>5.03764867782593</v>
+        <v>5.03764915466309</v>
       </c>
       <c r="H716" t="n">
         <v>2467</v>
@@ -21162,7 +21162,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G717" t="n">
-        <v>5.03764867782593</v>
+        <v>5.03764915466309</v>
       </c>
       <c r="H717" t="n">
         <v>0</v>
@@ -21191,7 +21191,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G718" t="n">
-        <v>5.03764867782593</v>
+        <v>5.03764915466309</v>
       </c>
       <c r="H718" t="n">
         <v>0</v>
@@ -21220,7 +21220,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G719" t="n">
-        <v>5.03764867782593</v>
+        <v>5.03764915466309</v>
       </c>
       <c r="H719" t="n">
         <v>0</v>
@@ -21249,7 +21249,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G720" t="n">
-        <v>5.03764867782593</v>
+        <v>5.03764915466309</v>
       </c>
       <c r="H720" t="n">
         <v>1250</v>
@@ -21278,7 +21278,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G721" t="n">
-        <v>4.94926881790161</v>
+        <v>4.94926929473877</v>
       </c>
       <c r="H721" t="n">
         <v>277</v>
@@ -21307,7 +21307,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G722" t="n">
-        <v>5.16138029098511</v>
+        <v>5.16138076782227</v>
       </c>
       <c r="H722" t="n">
         <v>1500</v>
@@ -21336,7 +21336,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G723" t="n">
-        <v>5.16138029098511</v>
+        <v>5.16138076782227</v>
       </c>
       <c r="H723" t="n">
         <v>0</v>
@@ -21365,7 +21365,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G724" t="n">
-        <v>5.24976062774658</v>
+        <v>5.24976015090942</v>
       </c>
       <c r="H724" t="n">
         <v>4500</v>
@@ -21394,7 +21394,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G725" t="n">
-        <v>5.03764867782593</v>
+        <v>5.03764915466309</v>
       </c>
       <c r="H725" t="n">
         <v>6899</v>
@@ -21626,7 +21626,7 @@
         <v>5.8600001335144</v>
       </c>
       <c r="G733" t="n">
-        <v>5.24438142776489</v>
+        <v>5.24438095092773</v>
       </c>
       <c r="H733" t="n">
         <v>1735</v>
@@ -21655,7 +21655,7 @@
         <v>5.8600001335144</v>
       </c>
       <c r="G734" t="n">
-        <v>5.24438142776489</v>
+        <v>5.24438095092773</v>
       </c>
       <c r="H734" t="n">
         <v>0</v>
@@ -21771,7 +21771,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G738" t="n">
-        <v>5.26227998733521</v>
+        <v>5.26228046417236</v>
       </c>
       <c r="H738" t="n">
         <v>40</v>
@@ -22148,7 +22148,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G751" t="n">
-        <v>4.99379634857178</v>
+        <v>4.99379587173462</v>
       </c>
       <c r="H751" t="n">
         <v>470</v>
@@ -22351,7 +22351,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G758" t="n">
-        <v>5.31597709655762</v>
+        <v>5.31597661972046</v>
       </c>
       <c r="H758" t="n">
         <v>1333</v>
@@ -22380,7 +22380,7 @@
         <v>6</v>
       </c>
       <c r="G759" t="n">
-        <v>5.36967372894287</v>
+        <v>5.36967325210571</v>
       </c>
       <c r="H759" t="n">
         <v>304</v>
@@ -22409,7 +22409,7 @@
         <v>6</v>
       </c>
       <c r="G760" t="n">
-        <v>5.36967372894287</v>
+        <v>5.36967325210571</v>
       </c>
       <c r="H760" t="n">
         <v>829</v>
@@ -22438,7 +22438,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G761" t="n">
-        <v>5.47706699371338</v>
+        <v>5.47706651687622</v>
       </c>
       <c r="H761" t="n">
         <v>270</v>
@@ -22641,7 +22641,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G768" t="n">
-        <v>5.72765207290649</v>
+        <v>5.72765159606934</v>
       </c>
       <c r="H768" t="n">
         <v>2958</v>
@@ -22699,7 +22699,7 @@
         <v>6.51999998092651</v>
       </c>
       <c r="G770" t="n">
-        <v>5.83504486083984</v>
+        <v>5.835045337677</v>
       </c>
       <c r="H770" t="n">
         <v>667</v>
@@ -22728,7 +22728,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G771" t="n">
-        <v>5.72765207290649</v>
+        <v>5.72765159606934</v>
       </c>
       <c r="H771" t="n">
         <v>678</v>
@@ -22757,7 +22757,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G772" t="n">
-        <v>5.72765207290649</v>
+        <v>5.72765159606934</v>
       </c>
       <c r="H772" t="n">
         <v>1540</v>
@@ -22844,7 +22844,7 @@
         <v>6.5</v>
       </c>
       <c r="G775" t="n">
-        <v>5.81714630126953</v>
+        <v>5.81714582443237</v>
       </c>
       <c r="H775" t="n">
         <v>11</v>
@@ -22902,7 +22902,7 @@
         <v>6.5</v>
       </c>
       <c r="G777" t="n">
-        <v>5.81714630126953</v>
+        <v>5.81714582443237</v>
       </c>
       <c r="H777" t="n">
         <v>6650</v>
@@ -23018,7 +23018,7 @@
         <v>6.73999977111816</v>
       </c>
       <c r="G781" t="n">
-        <v>6.03193330764771</v>
+        <v>6.03193283081055</v>
       </c>
       <c r="H781" t="n">
         <v>1012</v>
@@ -23105,7 +23105,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G784" t="n">
-        <v>6.08562994003296</v>
+        <v>6.08563041687012</v>
       </c>
       <c r="H784" t="n">
         <v>2889</v>
@@ -23250,7 +23250,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G789" t="n">
-        <v>5.88874197006226</v>
+        <v>5.8887414932251</v>
       </c>
       <c r="H789" t="n">
         <v>3581</v>
@@ -23308,7 +23308,7 @@
         <v>6.53999996185303</v>
       </c>
       <c r="G791" t="n">
-        <v>5.85294437408447</v>
+        <v>5.85294389724731</v>
       </c>
       <c r="H791" t="n">
         <v>31</v>
@@ -23337,7 +23337,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G792" t="n">
-        <v>5.72765207290649</v>
+        <v>5.72765159606934</v>
       </c>
       <c r="H792" t="n">
         <v>40050</v>
@@ -23482,7 +23482,7 @@
         <v>6.5</v>
       </c>
       <c r="G797" t="n">
-        <v>5.81714630126953</v>
+        <v>5.81714582443237</v>
       </c>
       <c r="H797" t="n">
         <v>1055</v>
@@ -23511,7 +23511,7 @@
         <v>6.5</v>
       </c>
       <c r="G798" t="n">
-        <v>5.81714630126953</v>
+        <v>5.81714582443237</v>
       </c>
       <c r="H798" t="n">
         <v>30000</v>
@@ -23598,7 +23598,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G801" t="n">
-        <v>5.88874197006226</v>
+        <v>5.8887414932251</v>
       </c>
       <c r="H801" t="n">
         <v>550</v>
@@ -23772,7 +23772,7 @@
         <v>6.42000007629395</v>
       </c>
       <c r="G807" t="n">
-        <v>5.74555063247681</v>
+        <v>5.74555110931396</v>
       </c>
       <c r="H807" t="n">
         <v>50</v>
@@ -23888,7 +23888,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G811" t="n">
-        <v>5.5486626625061</v>
+        <v>5.54866218566895</v>
       </c>
       <c r="H811" t="n">
         <v>1520</v>
@@ -23946,7 +23946,7 @@
         <v>5.8600001335144</v>
       </c>
       <c r="G813" t="n">
-        <v>5.24438142776489</v>
+        <v>5.24438095092773</v>
       </c>
       <c r="H813" t="n">
         <v>595</v>
@@ -23975,7 +23975,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G814" t="n">
-        <v>5.13698768615723</v>
+        <v>5.13698720932007</v>
       </c>
       <c r="H814" t="n">
         <v>33740</v>
@@ -24004,7 +24004,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G815" t="n">
-        <v>5.13698768615723</v>
+        <v>5.13698720932007</v>
       </c>
       <c r="H815" t="n">
         <v>0</v>
@@ -24033,7 +24033,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G816" t="n">
-        <v>5.35177421569824</v>
+        <v>5.3517746925354</v>
       </c>
       <c r="H816" t="n">
         <v>30550</v>
@@ -24062,7 +24062,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G817" t="n">
-        <v>4.83270645141602</v>
+        <v>4.83270597457886</v>
       </c>
       <c r="H817" t="n">
         <v>29376</v>
@@ -24178,7 +24178,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G821" t="n">
-        <v>4.83270645141602</v>
+        <v>4.83270597457886</v>
       </c>
       <c r="H821" t="n">
         <v>677</v>
@@ -24236,7 +24236,7 @@
         <v>6</v>
       </c>
       <c r="G823" t="n">
-        <v>5.36967372894287</v>
+        <v>5.36967325210571</v>
       </c>
       <c r="H823" t="n">
         <v>1900</v>
@@ -24265,7 +24265,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G824" t="n">
-        <v>5.47706699371338</v>
+        <v>5.47706651687622</v>
       </c>
       <c r="H824" t="n">
         <v>100</v>
@@ -24323,7 +24323,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G826" t="n">
-        <v>5.5486626625061</v>
+        <v>5.54866218566895</v>
       </c>
       <c r="H826" t="n">
         <v>610</v>
@@ -24352,7 +24352,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G827" t="n">
-        <v>5.5486626625061</v>
+        <v>5.54866218566895</v>
       </c>
       <c r="H827" t="n">
         <v>0</v>
@@ -24381,7 +24381,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G828" t="n">
-        <v>5.5486626625061</v>
+        <v>5.54866218566895</v>
       </c>
       <c r="H828" t="n">
         <v>600</v>
@@ -24410,7 +24410,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G829" t="n">
-        <v>5.5486626625061</v>
+        <v>5.54866218566895</v>
       </c>
       <c r="H829" t="n">
         <v>0</v>
@@ -24439,7 +24439,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G830" t="n">
-        <v>5.72765207290649</v>
+        <v>5.72765159606934</v>
       </c>
       <c r="H830" t="n">
         <v>1323</v>
@@ -24497,7 +24497,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G832" t="n">
-        <v>5.72765207290649</v>
+        <v>5.72765159606934</v>
       </c>
       <c r="H832" t="n">
         <v>420</v>
@@ -24700,7 +24700,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G839" t="n">
-        <v>5.5486626625061</v>
+        <v>5.54866218566895</v>
       </c>
       <c r="H839" t="n">
         <v>400</v>
@@ -24729,7 +24729,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G840" t="n">
-        <v>5.53076314926147</v>
+        <v>5.53076362609863</v>
       </c>
       <c r="H840" t="n">
         <v>422</v>
@@ -24903,7 +24903,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G846" t="n">
-        <v>5.72765207290649</v>
+        <v>5.72765159606934</v>
       </c>
       <c r="H846" t="n">
         <v>100</v>
@@ -24961,7 +24961,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G848" t="n">
-        <v>5.72765207290649</v>
+        <v>5.72765159606934</v>
       </c>
       <c r="H848" t="n">
         <v>1038</v>
@@ -25048,7 +25048,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G851" t="n">
-        <v>5.70975255966187</v>
+        <v>5.70975303649902</v>
       </c>
       <c r="H851" t="n">
         <v>961</v>
@@ -25077,7 +25077,7 @@
         <v>6.5</v>
       </c>
       <c r="G852" t="n">
-        <v>5.81714630126953</v>
+        <v>5.81714582443237</v>
       </c>
       <c r="H852" t="n">
         <v>263</v>
@@ -25106,7 +25106,7 @@
         <v>6.5</v>
       </c>
       <c r="G853" t="n">
-        <v>5.81714630126953</v>
+        <v>5.81714582443237</v>
       </c>
       <c r="H853" t="n">
         <v>1153</v>
@@ -25193,7 +25193,7 @@
         <v>6.42000007629395</v>
       </c>
       <c r="G856" t="n">
-        <v>5.74555063247681</v>
+        <v>5.74555110931396</v>
       </c>
       <c r="H856" t="n">
         <v>396</v>
@@ -25222,7 +25222,7 @@
         <v>6.51999998092651</v>
       </c>
       <c r="G857" t="n">
-        <v>5.83504486083984</v>
+        <v>5.835045337677</v>
       </c>
       <c r="H857" t="n">
         <v>100</v>
@@ -25251,7 +25251,7 @@
         <v>6.51999998092651</v>
       </c>
       <c r="G858" t="n">
-        <v>5.83504486083984</v>
+        <v>5.835045337677</v>
       </c>
       <c r="H858" t="n">
         <v>0</v>
@@ -25280,7 +25280,7 @@
         <v>6.51999998092651</v>
       </c>
       <c r="G859" t="n">
-        <v>5.83504486083984</v>
+        <v>5.835045337677</v>
       </c>
       <c r="H859" t="n">
         <v>0</v>
@@ -25396,7 +25396,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G863" t="n">
-        <v>5.88874197006226</v>
+        <v>5.8887414932251</v>
       </c>
       <c r="H863" t="n">
         <v>1364</v>
@@ -25454,7 +25454,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G865" t="n">
-        <v>5.88874197006226</v>
+        <v>5.8887414932251</v>
       </c>
       <c r="H865" t="n">
         <v>1988</v>
@@ -25541,7 +25541,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G868" t="n">
-        <v>6.08562994003296</v>
+        <v>6.08563041687012</v>
       </c>
       <c r="H868" t="n">
         <v>500</v>
@@ -25570,7 +25570,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G869" t="n">
-        <v>6.08562994003296</v>
+        <v>6.08563041687012</v>
       </c>
       <c r="H869" t="n">
         <v>0</v>
@@ -25860,7 +25860,7 @@
         <v>6.5</v>
       </c>
       <c r="G879" t="n">
-        <v>5.81714630126953</v>
+        <v>5.81714582443237</v>
       </c>
       <c r="H879" t="n">
         <v>314</v>
@@ -25918,7 +25918,7 @@
         <v>6.73999977111816</v>
       </c>
       <c r="G881" t="n">
-        <v>6.03193330764771</v>
+        <v>6.03193283081055</v>
       </c>
       <c r="H881" t="n">
         <v>400</v>
@@ -25976,7 +25976,7 @@
         <v>6.71999979019165</v>
       </c>
       <c r="G883" t="n">
-        <v>6.01403379440308</v>
+        <v>6.01403427124023</v>
       </c>
       <c r="H883" t="n">
         <v>200</v>
@@ -26005,7 +26005,7 @@
         <v>6.71999979019165</v>
       </c>
       <c r="G884" t="n">
-        <v>6.01403379440308</v>
+        <v>6.01403427124023</v>
       </c>
       <c r="H884" t="n">
         <v>0</v>
@@ -26150,7 +26150,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G889" t="n">
-        <v>5.72765207290649</v>
+        <v>5.72765159606934</v>
       </c>
       <c r="H889" t="n">
         <v>1703</v>
@@ -26179,7 +26179,7 @@
         <v>6.5</v>
       </c>
       <c r="G890" t="n">
-        <v>5.81714630126953</v>
+        <v>5.81714582443237</v>
       </c>
       <c r="H890" t="n">
         <v>662</v>
@@ -26208,7 +26208,7 @@
         <v>6.71999979019165</v>
       </c>
       <c r="G891" t="n">
-        <v>6.01403379440308</v>
+        <v>6.01403427124023</v>
       </c>
       <c r="H891" t="n">
         <v>155</v>
@@ -26237,7 +26237,7 @@
         <v>6.71999979019165</v>
       </c>
       <c r="G892" t="n">
-        <v>6.01403379440308</v>
+        <v>6.01403427124023</v>
       </c>
       <c r="H892" t="n">
         <v>0</v>
@@ -26266,7 +26266,7 @@
         <v>6.71999979019165</v>
       </c>
       <c r="G893" t="n">
-        <v>6.01403379440308</v>
+        <v>6.01403427124023</v>
       </c>
       <c r="H893" t="n">
         <v>0</v>
@@ -26556,7 +26556,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G903" t="n">
-        <v>6.98057556152344</v>
+        <v>6.9805760383606</v>
       </c>
       <c r="H903" t="n">
         <v>2180</v>
@@ -26614,7 +26614,7 @@
         <v>7.57999992370605</v>
       </c>
       <c r="G905" t="n">
-        <v>6.78368759155273</v>
+        <v>6.78368711471558</v>
       </c>
       <c r="H905" t="n">
         <v>2196</v>
@@ -26701,7 +26701,7 @@
         <v>7.03999996185303</v>
       </c>
       <c r="G908" t="n">
-        <v>6.30041694641113</v>
+        <v>6.30041646957397</v>
       </c>
       <c r="H908" t="n">
         <v>5650</v>
@@ -26759,7 +26759,7 @@
         <v>7.1399998664856</v>
       </c>
       <c r="G910" t="n">
-        <v>6.38991117477417</v>
+        <v>6.38991165161133</v>
       </c>
       <c r="H910" t="n">
         <v>1158</v>
@@ -26962,7 +26962,7 @@
         <v>7.26000022888184</v>
       </c>
       <c r="G917" t="n">
-        <v>6.49730491638184</v>
+        <v>6.49730539321899</v>
       </c>
       <c r="H917" t="n">
         <v>3000</v>
@@ -26991,7 +26991,7 @@
         <v>7.42000007629395</v>
       </c>
       <c r="G918" t="n">
-        <v>6.64049673080444</v>
+        <v>6.64049625396729</v>
       </c>
       <c r="H918" t="n">
         <v>2331</v>
@@ -27078,7 +27078,7 @@
         <v>7.34000015258789</v>
       </c>
       <c r="G921" t="n">
-        <v>6.56890058517456</v>
+        <v>6.56890106201172</v>
       </c>
       <c r="H921" t="n">
         <v>250</v>
@@ -27136,7 +27136,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G923" t="n">
-        <v>6.80158615112305</v>
+        <v>6.80158662796021</v>
       </c>
       <c r="H923" t="n">
         <v>2203</v>
@@ -27397,7 +27397,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G932" t="n">
-        <v>6.80158615112305</v>
+        <v>6.80158662796021</v>
       </c>
       <c r="H932" t="n">
         <v>2264</v>
@@ -27455,7 +27455,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G934" t="n">
-        <v>6.80158615112305</v>
+        <v>6.80158662796021</v>
       </c>
       <c r="H934" t="n">
         <v>1250</v>
@@ -27513,7 +27513,7 @@
         <v>7.34000015258789</v>
       </c>
       <c r="G936" t="n">
-        <v>6.56890058517456</v>
+        <v>6.56890106201172</v>
       </c>
       <c r="H936" t="n">
         <v>75</v>
@@ -27687,7 +27687,7 @@
         <v>7.26000022888184</v>
       </c>
       <c r="G942" t="n">
-        <v>6.49730491638184</v>
+        <v>6.49730539321899</v>
       </c>
       <c r="H942" t="n">
         <v>4218</v>
@@ -27716,7 +27716,7 @@
         <v>7.26000022888184</v>
       </c>
       <c r="G943" t="n">
-        <v>6.49730491638184</v>
+        <v>6.49730539321899</v>
       </c>
       <c r="H943" t="n">
         <v>0</v>
@@ -27745,7 +27745,7 @@
         <v>7.26000022888184</v>
       </c>
       <c r="G944" t="n">
-        <v>6.49730491638184</v>
+        <v>6.49730539321899</v>
       </c>
       <c r="H944" t="n">
         <v>0</v>
@@ -27803,7 +27803,7 @@
         <v>7.21999979019165</v>
       </c>
       <c r="G946" t="n">
-        <v>6.46150732040405</v>
+        <v>6.46150684356689</v>
       </c>
       <c r="H946" t="n">
         <v>103974</v>
@@ -27832,7 +27832,7 @@
         <v>7.21999979019165</v>
       </c>
       <c r="G947" t="n">
-        <v>6.46150732040405</v>
+        <v>6.46150684356689</v>
       </c>
       <c r="H947" t="n">
         <v>574</v>
@@ -28238,7 +28238,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G961" t="n">
-        <v>6.08562994003296</v>
+        <v>6.08563041687012</v>
       </c>
       <c r="H961" t="n">
         <v>1113</v>
@@ -28557,7 +28557,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G972" t="n">
-        <v>6.08562994003296</v>
+        <v>6.08563041687012</v>
       </c>
       <c r="H972" t="n">
         <v>250</v>
@@ -30065,7 +30065,7 @@
         <v>7.25</v>
       </c>
       <c r="G1024" t="n">
-        <v>6.48835563659668</v>
+        <v>6.48835515975952</v>
       </c>
       <c r="H1024" t="n">
         <v>712</v>
@@ -30181,7 +30181,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G1028" t="n">
-        <v>6.84633350372314</v>
+        <v>6.8463339805603</v>
       </c>
       <c r="H1028" t="n">
         <v>12728</v>
@@ -30210,7 +30210,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G1029" t="n">
-        <v>6.98057556152344</v>
+        <v>6.9805760383606</v>
       </c>
       <c r="H1029" t="n">
         <v>238</v>
@@ -30239,7 +30239,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G1030" t="n">
-        <v>6.98057556152344</v>
+        <v>6.9805760383606</v>
       </c>
       <c r="H1030" t="n">
         <v>1</v>
@@ -30268,7 +30268,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G1031" t="n">
-        <v>6.98057556152344</v>
+        <v>6.9805760383606</v>
       </c>
       <c r="H1031" t="n">
         <v>100</v>
@@ -30326,7 +30326,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G1033" t="n">
-        <v>6.75683927536011</v>
+        <v>6.75683975219727</v>
       </c>
       <c r="H1033" t="n">
         <v>670</v>
@@ -30355,7 +30355,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G1034" t="n">
-        <v>6.75683927536011</v>
+        <v>6.75683975219727</v>
       </c>
       <c r="H1034" t="n">
         <v>0</v>
@@ -30384,7 +30384,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G1035" t="n">
-        <v>6.75683927536011</v>
+        <v>6.75683975219727</v>
       </c>
       <c r="H1035" t="n">
         <v>0</v>
@@ -30413,7 +30413,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G1036" t="n">
-        <v>6.75683927536011</v>
+        <v>6.75683975219727</v>
       </c>
       <c r="H1036" t="n">
         <v>0</v>
@@ -30442,7 +30442,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G1037" t="n">
-        <v>6.98057556152344</v>
+        <v>6.9805760383606</v>
       </c>
       <c r="H1037" t="n">
         <v>500</v>
@@ -30471,7 +30471,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G1038" t="n">
-        <v>6.80158615112305</v>
+        <v>6.80158662796021</v>
       </c>
       <c r="H1038" t="n">
         <v>730</v>
@@ -30500,7 +30500,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G1039" t="n">
-        <v>6.80158615112305</v>
+        <v>6.80158662796021</v>
       </c>
       <c r="H1039" t="n">
         <v>0</v>
@@ -30558,7 +30558,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G1041" t="n">
-        <v>6.80158615112305</v>
+        <v>6.80158662796021</v>
       </c>
       <c r="H1041" t="n">
         <v>13</v>
@@ -30587,7 +30587,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G1042" t="n">
-        <v>6.80158615112305</v>
+        <v>6.80158662796021</v>
       </c>
       <c r="H1042" t="n">
         <v>0</v>
@@ -30616,7 +30616,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G1043" t="n">
-        <v>6.80158615112305</v>
+        <v>6.80158662796021</v>
       </c>
       <c r="H1043" t="n">
         <v>0</v>
@@ -30645,7 +30645,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G1044" t="n">
-        <v>6.80158615112305</v>
+        <v>6.80158662796021</v>
       </c>
       <c r="H1044" t="n">
         <v>0</v>
@@ -30674,7 +30674,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G1045" t="n">
-        <v>6.80158615112305</v>
+        <v>6.80158662796021</v>
       </c>
       <c r="H1045" t="n">
         <v>0</v>
@@ -30703,7 +30703,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G1046" t="n">
-        <v>6.80158615112305</v>
+        <v>6.80158662796021</v>
       </c>
       <c r="H1046" t="n">
         <v>0</v>
@@ -30732,7 +30732,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G1047" t="n">
-        <v>6.80158615112305</v>
+        <v>6.80158662796021</v>
       </c>
       <c r="H1047" t="n">
         <v>0</v>
@@ -30761,7 +30761,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G1048" t="n">
-        <v>6.98057556152344</v>
+        <v>6.9805760383606</v>
       </c>
       <c r="H1048" t="n">
         <v>601</v>
@@ -30790,7 +30790,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G1049" t="n">
-        <v>6.84633350372314</v>
+        <v>6.8463339805603</v>
       </c>
       <c r="H1049" t="n">
         <v>100</v>
@@ -30819,7 +30819,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G1050" t="n">
-        <v>6.98057556152344</v>
+        <v>6.9805760383606</v>
       </c>
       <c r="H1050" t="n">
         <v>460</v>
@@ -30848,7 +30848,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G1051" t="n">
-        <v>6.98057556152344</v>
+        <v>6.9805760383606</v>
       </c>
       <c r="H1051" t="n">
         <v>125</v>
@@ -30877,7 +30877,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G1052" t="n">
-        <v>6.98057556152344</v>
+        <v>6.9805760383606</v>
       </c>
       <c r="H1052" t="n">
         <v>0</v>
@@ -30906,7 +30906,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G1053" t="n">
-        <v>6.80158615112305</v>
+        <v>6.80158662796021</v>
       </c>
       <c r="H1053" t="n">
         <v>1684</v>
@@ -31080,7 +31080,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G1059" t="n">
-        <v>6.75683927536011</v>
+        <v>6.75683975219727</v>
       </c>
       <c r="H1059" t="n">
         <v>400</v>
@@ -31109,7 +31109,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G1060" t="n">
-        <v>6.75683927536011</v>
+        <v>6.75683975219727</v>
       </c>
       <c r="H1060" t="n">
         <v>0</v>
@@ -31138,7 +31138,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G1061" t="n">
-        <v>6.75683927536011</v>
+        <v>6.75683975219727</v>
       </c>
       <c r="H1061" t="n">
         <v>0</v>
@@ -31602,7 +31602,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G1077" t="n">
-        <v>5.86189365386963</v>
+        <v>5.86189413070679</v>
       </c>
       <c r="H1077" t="n">
         <v>846</v>
@@ -31631,7 +31631,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G1078" t="n">
-        <v>5.72765207290649</v>
+        <v>5.72765159606934</v>
       </c>
       <c r="H1078" t="n">
         <v>2019</v>
@@ -31660,7 +31660,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G1079" t="n">
-        <v>5.86189365386963</v>
+        <v>5.86189413070679</v>
       </c>
       <c r="H1079" t="n">
         <v>100</v>
@@ -31747,7 +31747,7 @@
         <v>6</v>
       </c>
       <c r="G1082" t="n">
-        <v>5.36967372894287</v>
+        <v>5.36967325210571</v>
       </c>
       <c r="H1082" t="n">
         <v>11354</v>
@@ -31776,7 +31776,7 @@
         <v>6</v>
       </c>
       <c r="G1083" t="n">
-        <v>5.36967372894287</v>
+        <v>5.36967325210571</v>
       </c>
       <c r="H1083" t="n">
         <v>25500</v>
@@ -31805,7 +31805,7 @@
         <v>6</v>
       </c>
       <c r="G1084" t="n">
-        <v>5.36967372894287</v>
+        <v>5.36967325210571</v>
       </c>
       <c r="H1084" t="n">
         <v>0</v>
@@ -31863,7 +31863,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G1086" t="n">
-        <v>5.32492637634277</v>
+        <v>5.32492589950562</v>
       </c>
       <c r="H1086" t="n">
         <v>6465</v>
@@ -31892,7 +31892,7 @@
         <v>6</v>
       </c>
       <c r="G1087" t="n">
-        <v>5.36967372894287</v>
+        <v>5.36967325210571</v>
       </c>
       <c r="H1087" t="n">
         <v>6931</v>
@@ -31921,7 +31921,7 @@
         <v>6</v>
       </c>
       <c r="G1088" t="n">
-        <v>5.36967372894287</v>
+        <v>5.36967325210571</v>
       </c>
       <c r="H1088" t="n">
         <v>0</v>
@@ -31950,7 +31950,7 @@
         <v>6</v>
       </c>
       <c r="G1089" t="n">
-        <v>5.36967372894287</v>
+        <v>5.36967325210571</v>
       </c>
       <c r="H1089" t="n">
         <v>0</v>
@@ -31979,7 +31979,7 @@
         <v>6</v>
       </c>
       <c r="G1090" t="n">
-        <v>5.36967372894287</v>
+        <v>5.36967325210571</v>
       </c>
       <c r="H1090" t="n">
         <v>850</v>
@@ -32008,7 +32008,7 @@
         <v>6</v>
       </c>
       <c r="G1091" t="n">
-        <v>5.36967372894287</v>
+        <v>5.36967325210571</v>
       </c>
       <c r="H1091" t="n">
         <v>240</v>
@@ -32037,7 +32037,7 @@
         <v>6</v>
       </c>
       <c r="G1092" t="n">
-        <v>5.36967372894287</v>
+        <v>5.36967325210571</v>
       </c>
       <c r="H1092" t="n">
         <v>650</v>
@@ -32066,7 +32066,7 @@
         <v>6</v>
       </c>
       <c r="G1093" t="n">
-        <v>5.36967372894287</v>
+        <v>5.36967325210571</v>
       </c>
       <c r="H1093" t="n">
         <v>675</v>
@@ -32095,7 +32095,7 @@
         <v>6</v>
       </c>
       <c r="G1094" t="n">
-        <v>5.36967372894287</v>
+        <v>5.36967325210571</v>
       </c>
       <c r="H1094" t="n">
         <v>0</v>
@@ -32124,7 +32124,7 @@
         <v>6</v>
       </c>
       <c r="G1095" t="n">
-        <v>5.36967372894287</v>
+        <v>5.36967325210571</v>
       </c>
       <c r="H1095" t="n">
         <v>0</v>
@@ -32414,7 +32414,7 @@
         <v>6.25</v>
       </c>
       <c r="G1105" t="n">
-        <v>5.5934100151062</v>
+        <v>5.59340953826904</v>
       </c>
       <c r="H1105" t="n">
         <v>14260</v>
@@ -32443,7 +32443,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G1106" t="n">
-        <v>5.5486626625061</v>
+        <v>5.54866218566895</v>
       </c>
       <c r="H1106" t="n">
         <v>39658</v>
@@ -32559,7 +32559,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G1110" t="n">
-        <v>5.5486626625061</v>
+        <v>5.54866218566895</v>
       </c>
       <c r="H1110" t="n">
         <v>21380</v>
@@ -32617,7 +32617,7 @@
         <v>6.5</v>
       </c>
       <c r="G1112" t="n">
-        <v>5.81714630126953</v>
+        <v>5.81714582443237</v>
       </c>
       <c r="H1112" t="n">
         <v>29853</v>
@@ -32646,7 +32646,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G1113" t="n">
-        <v>5.72765207290649</v>
+        <v>5.72765159606934</v>
       </c>
       <c r="H1113" t="n">
         <v>31724</v>
@@ -32675,7 +32675,7 @@
         <v>6.5</v>
       </c>
       <c r="G1114" t="n">
-        <v>5.81714630126953</v>
+        <v>5.81714582443237</v>
       </c>
       <c r="H1114" t="n">
         <v>15604</v>
@@ -32791,7 +32791,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G1118" t="n">
-        <v>6.08562994003296</v>
+        <v>6.08563041687012</v>
       </c>
       <c r="H1118" t="n">
         <v>46505</v>
@@ -32965,7 +32965,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G1124" t="n">
-        <v>6.75683927536011</v>
+        <v>6.75683975219727</v>
       </c>
       <c r="H1124" t="n">
         <v>52998</v>
@@ -54025,6 +54025,35 @@
         <v>700</v>
       </c>
       <c r="I1850" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1851">
+      <c r="A1851" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1851" s="1" t="n">
+        <v>46321.3333333333</v>
+      </c>
+      <c r="C1851" t="n">
+        <v>2.1800000667572</v>
+      </c>
+      <c r="D1851" t="n">
+        <v>2.1800000667572</v>
+      </c>
+      <c r="E1851" t="n">
+        <v>2.16000008583069</v>
+      </c>
+      <c r="F1851" t="n">
+        <v>2.16000008583069</v>
+      </c>
+      <c r="G1851" t="n">
+        <v>2.16000008583069</v>
+      </c>
+      <c r="H1851" t="n">
+        <v>3355</v>
+      </c>
+      <c r="I1851" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/PTR.MI.xlsx
+++ b/data/PTR.MI.xlsx
@@ -456,7 +456,7 @@
         <v>3.7409999370575</v>
       </c>
       <c r="G3" t="n">
-        <v>3.24703478813171</v>
+        <v>3.24703454971313</v>
       </c>
       <c r="H3" t="n">
         <v>329252</v>
@@ -485,7 +485,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G4" t="n">
-        <v>3.22012782096863</v>
+        <v>3.22012805938721</v>
       </c>
       <c r="H4" t="n">
         <v>98299</v>
@@ -717,7 +717,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G12" t="n">
-        <v>3.08125448226929</v>
+        <v>3.08125424385071</v>
       </c>
       <c r="H12" t="n">
         <v>29251</v>
@@ -746,7 +746,7 @@
         <v>3.59400010108948</v>
       </c>
       <c r="G13" t="n">
-        <v>3.11944484710693</v>
+        <v>3.11944460868835</v>
       </c>
       <c r="H13" t="n">
         <v>13465</v>
@@ -775,7 +775,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G14" t="n">
-        <v>3.12465262413025</v>
+        <v>3.12465238571167</v>
       </c>
       <c r="H14" t="n">
         <v>10463</v>
@@ -949,7 +949,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G20" t="n">
-        <v>3.12465262413025</v>
+        <v>3.12465238571167</v>
       </c>
       <c r="H20" t="n">
         <v>1924</v>
@@ -1007,7 +1007,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G22" t="n">
-        <v>3.09861350059509</v>
+        <v>3.09861373901367</v>
       </c>
       <c r="H22" t="n">
         <v>7918</v>
@@ -1152,7 +1152,7 @@
         <v>3.35050010681152</v>
       </c>
       <c r="G27" t="n">
-        <v>2.90809679031372</v>
+        <v>2.90809655189514</v>
       </c>
       <c r="H27" t="n">
         <v>9955</v>
@@ -1210,7 +1210,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G29" t="n">
-        <v>3.08125448226929</v>
+        <v>3.08125424385071</v>
       </c>
       <c r="H29" t="n">
         <v>12055</v>
@@ -1413,7 +1413,7 @@
         <v>3.46499991416931</v>
       </c>
       <c r="G36" t="n">
-        <v>3.00747776031494</v>
+        <v>3.00747799873352</v>
       </c>
       <c r="H36" t="n">
         <v>1547</v>
@@ -1471,7 +1471,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G38" t="n">
-        <v>3.19408917427063</v>
+        <v>3.19408941268921</v>
       </c>
       <c r="H38" t="n">
         <v>32777</v>
@@ -1616,7 +1616,7 @@
         <v>3.82500004768372</v>
       </c>
       <c r="G43" t="n">
-        <v>3.31994318962097</v>
+        <v>3.31994342803955</v>
       </c>
       <c r="H43" t="n">
         <v>5962</v>
@@ -1674,7 +1674,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G45" t="n">
-        <v>3.17673015594482</v>
+        <v>3.17672991752625</v>
       </c>
       <c r="H45" t="n">
         <v>1155</v>
@@ -1703,7 +1703,7 @@
         <v>3.71499991416931</v>
       </c>
       <c r="G46" t="n">
-        <v>3.22446775436401</v>
+        <v>3.22446751594543</v>
       </c>
       <c r="H46" t="n">
         <v>3406</v>
@@ -1819,7 +1819,7 @@
         <v>3.71499991416931</v>
       </c>
       <c r="G50" t="n">
-        <v>3.22446775436401</v>
+        <v>3.22446751594543</v>
       </c>
       <c r="H50" t="n">
         <v>7667</v>
@@ -1906,7 +1906,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G53" t="n">
-        <v>3.17673015594482</v>
+        <v>3.17672991752625</v>
       </c>
       <c r="H53" t="n">
         <v>18126</v>
@@ -2051,7 +2051,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G58" t="n">
-        <v>3.17673015594482</v>
+        <v>3.17672991752625</v>
       </c>
       <c r="H58" t="n">
         <v>1957</v>
@@ -2080,7 +2080,7 @@
         <v>3.66499996185303</v>
       </c>
       <c r="G59" t="n">
-        <v>3.18106985092163</v>
+        <v>3.18106961250305</v>
       </c>
       <c r="H59" t="n">
         <v>20</v>
@@ -2138,7 +2138,7 @@
         <v>3.66499996185303</v>
       </c>
       <c r="G61" t="n">
-        <v>3.18106985092163</v>
+        <v>3.18106961250305</v>
       </c>
       <c r="H61" t="n">
         <v>27542</v>
@@ -2225,7 +2225,7 @@
         <v>3.5550000667572</v>
       </c>
       <c r="G64" t="n">
-        <v>3.08559441566467</v>
+        <v>3.08559465408325</v>
       </c>
       <c r="H64" t="n">
         <v>550</v>
@@ -2254,7 +2254,7 @@
         <v>3.5550000667572</v>
       </c>
       <c r="G65" t="n">
-        <v>3.08559441566467</v>
+        <v>3.08559465408325</v>
       </c>
       <c r="H65" t="n">
         <v>2547</v>
@@ -2283,7 +2283,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G66" t="n">
-        <v>3.09861350059509</v>
+        <v>3.09861373901367</v>
       </c>
       <c r="H66" t="n">
         <v>4020</v>
@@ -2341,7 +2341,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G68" t="n">
-        <v>3.12465262413025</v>
+        <v>3.12465238571167</v>
       </c>
       <c r="H68" t="n">
         <v>2020</v>
@@ -2370,7 +2370,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G69" t="n">
-        <v>3.12465262413025</v>
+        <v>3.12465238571167</v>
       </c>
       <c r="H69" t="n">
         <v>7428</v>
@@ -2457,7 +2457,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G72" t="n">
-        <v>3.12465262413025</v>
+        <v>3.12465238571167</v>
       </c>
       <c r="H72" t="n">
         <v>29395</v>
@@ -2486,7 +2486,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G73" t="n">
-        <v>3.08125448226929</v>
+        <v>3.08125424385071</v>
       </c>
       <c r="H73" t="n">
         <v>22487</v>
@@ -2515,7 +2515,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G74" t="n">
-        <v>3.08125448226929</v>
+        <v>3.08125424385071</v>
       </c>
       <c r="H74" t="n">
         <v>6950</v>
@@ -2602,7 +2602,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G77" t="n">
-        <v>3.08125448226929</v>
+        <v>3.08125424385071</v>
       </c>
       <c r="H77" t="n">
         <v>1858</v>
@@ -2631,7 +2631,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G78" t="n">
-        <v>3.12465262413025</v>
+        <v>3.12465238571167</v>
       </c>
       <c r="H78" t="n">
         <v>908</v>
@@ -3066,7 +3066,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G93" t="n">
-        <v>3.4631564617157</v>
+        <v>3.46315670013428</v>
       </c>
       <c r="H93" t="n">
         <v>250</v>
@@ -3298,7 +3298,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G101" t="n">
-        <v>3.54127240180969</v>
+        <v>3.54127264022827</v>
       </c>
       <c r="H101" t="n">
         <v>4200</v>
@@ -3646,7 +3646,7 @@
         <v>4.5</v>
       </c>
       <c r="G113" t="n">
-        <v>3.90581560134888</v>
+        <v>3.90581512451172</v>
       </c>
       <c r="H113" t="n">
         <v>10114</v>
@@ -3675,7 +3675,7 @@
         <v>4.5</v>
       </c>
       <c r="G114" t="n">
-        <v>3.90581560134888</v>
+        <v>3.90581512451172</v>
       </c>
       <c r="H114" t="n">
         <v>36925</v>
@@ -3704,7 +3704,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G115" t="n">
-        <v>3.87109708786011</v>
+        <v>3.87109684944153</v>
       </c>
       <c r="H115" t="n">
         <v>4580</v>
@@ -3733,7 +3733,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G116" t="n">
-        <v>3.86241722106934</v>
+        <v>3.86241674423218</v>
       </c>
       <c r="H116" t="n">
         <v>17964</v>
@@ -3849,7 +3849,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G120" t="n">
-        <v>3.86241722106934</v>
+        <v>3.86241674423218</v>
       </c>
       <c r="H120" t="n">
         <v>34190</v>
@@ -3878,7 +3878,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G121" t="n">
-        <v>3.92317509651184</v>
+        <v>3.92317461967468</v>
       </c>
       <c r="H121" t="n">
         <v>67457</v>
@@ -3936,7 +3936,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G123" t="n">
-        <v>3.88845658302307</v>
+        <v>3.88845610618591</v>
       </c>
       <c r="H123" t="n">
         <v>13757</v>
@@ -4052,7 +4052,7 @@
         <v>4.88500022888184</v>
       </c>
       <c r="G127" t="n">
-        <v>4.23997974395752</v>
+        <v>4.23998022079468</v>
       </c>
       <c r="H127" t="n">
         <v>32038</v>
@@ -4081,7 +4081,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G128" t="n">
-        <v>4.37451362609863</v>
+        <v>4.37451267242432</v>
       </c>
       <c r="H128" t="n">
         <v>36739</v>
@@ -4168,7 +4168,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G131" t="n">
-        <v>4.49602746963501</v>
+        <v>4.49602699279785</v>
       </c>
       <c r="H131" t="n">
         <v>4316</v>
@@ -4197,7 +4197,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G132" t="n">
-        <v>4.49602746963501</v>
+        <v>4.49602699279785</v>
       </c>
       <c r="H132" t="n">
         <v>2480</v>
@@ -4226,7 +4226,7 @@
         <v>4.97499990463257</v>
       </c>
       <c r="G133" t="n">
-        <v>4.31809568405151</v>
+        <v>4.31809616088867</v>
       </c>
       <c r="H133" t="n">
         <v>8257</v>
@@ -4313,7 +4313,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G136" t="n">
-        <v>4.20092153549194</v>
+        <v>4.2009220123291</v>
       </c>
       <c r="H136" t="n">
         <v>13708</v>
@@ -4371,7 +4371,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G138" t="n">
-        <v>4.16620349884033</v>
+        <v>4.16620397567749</v>
       </c>
       <c r="H138" t="n">
         <v>23142</v>
@@ -4458,7 +4458,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G141" t="n">
-        <v>4.42659139633179</v>
+        <v>4.42659091949463</v>
       </c>
       <c r="H141" t="n">
         <v>9500</v>
@@ -4545,7 +4545,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G144" t="n">
-        <v>4.42659139633179</v>
+        <v>4.42659091949463</v>
       </c>
       <c r="H144" t="n">
         <v>5800</v>
@@ -4661,7 +4661,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G148" t="n">
-        <v>4.49602746963501</v>
+        <v>4.49602699279785</v>
       </c>
       <c r="H148" t="n">
         <v>14318</v>
@@ -4835,7 +4835,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G154" t="n">
-        <v>4.00129175186157</v>
+        <v>4.00129079818726</v>
       </c>
       <c r="H154" t="n">
         <v>9345</v>
@@ -4893,7 +4893,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G156" t="n">
-        <v>4.31375646591187</v>
+        <v>4.31375598907471</v>
       </c>
       <c r="H156" t="n">
         <v>4730</v>
@@ -4922,7 +4922,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G157" t="n">
-        <v>4.23563957214355</v>
+        <v>4.23564004898071</v>
       </c>
       <c r="H157" t="n">
         <v>8393</v>
@@ -4951,7 +4951,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G158" t="n">
-        <v>4.00129175186157</v>
+        <v>4.00129079818726</v>
       </c>
       <c r="H158" t="n">
         <v>25178</v>
@@ -5125,7 +5125,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G164" t="n">
-        <v>3.17673015594482</v>
+        <v>3.17672991752625</v>
       </c>
       <c r="H164" t="n">
         <v>13665</v>
@@ -5154,7 +5154,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G165" t="n">
-        <v>3.26352596282959</v>
+        <v>3.26352572441101</v>
       </c>
       <c r="H165" t="n">
         <v>12420</v>
@@ -5299,7 +5299,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G170" t="n">
-        <v>3.12465262413025</v>
+        <v>3.12465238571167</v>
       </c>
       <c r="H170" t="n">
         <v>862</v>
@@ -5386,7 +5386,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G173" t="n">
-        <v>3.09861350059509</v>
+        <v>3.09861373901367</v>
       </c>
       <c r="H173" t="n">
         <v>20403</v>
@@ -5444,7 +5444,7 @@
         <v>3.72499990463257</v>
       </c>
       <c r="G175" t="n">
-        <v>3.23314738273621</v>
+        <v>3.23314714431763</v>
       </c>
       <c r="H175" t="n">
         <v>35922</v>
@@ -5473,7 +5473,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G176" t="n">
-        <v>3.08125448226929</v>
+        <v>3.08125424385071</v>
       </c>
       <c r="H176" t="n">
         <v>9550</v>
@@ -5502,7 +5502,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G177" t="n">
-        <v>3.09861350059509</v>
+        <v>3.09861373901367</v>
       </c>
       <c r="H177" t="n">
         <v>2492</v>
@@ -5589,7 +5589,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G180" t="n">
-        <v>3.31560325622559</v>
+        <v>3.31560301780701</v>
       </c>
       <c r="H180" t="n">
         <v>27302</v>
@@ -5676,7 +5676,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G183" t="n">
-        <v>3.19408917427063</v>
+        <v>3.19408941268921</v>
       </c>
       <c r="H183" t="n">
         <v>14368</v>
@@ -5734,7 +5734,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G185" t="n">
-        <v>3.19408917427063</v>
+        <v>3.19408941268921</v>
       </c>
       <c r="H185" t="n">
         <v>20637</v>
@@ -5763,7 +5763,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G186" t="n">
-        <v>3.22012782096863</v>
+        <v>3.22012805938721</v>
       </c>
       <c r="H186" t="n">
         <v>4810</v>
@@ -5908,7 +5908,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G191" t="n">
-        <v>3.28088521957397</v>
+        <v>3.2808849811554</v>
       </c>
       <c r="H191" t="n">
         <v>15966</v>
@@ -5937,7 +5937,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G192" t="n">
-        <v>3.33296251296997</v>
+        <v>3.33296275138855</v>
       </c>
       <c r="H192" t="n">
         <v>11266</v>
@@ -6169,7 +6169,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G200" t="n">
-        <v>3.48051595687866</v>
+        <v>3.48051571846008</v>
       </c>
       <c r="H200" t="n">
         <v>8475</v>
@@ -6198,7 +6198,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G201" t="n">
-        <v>3.33296251296997</v>
+        <v>3.33296275138855</v>
       </c>
       <c r="H201" t="n">
         <v>9437</v>
@@ -6285,7 +6285,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G204" t="n">
-        <v>3.19408917427063</v>
+        <v>3.19408941268921</v>
       </c>
       <c r="H204" t="n">
         <v>55244</v>
@@ -6343,7 +6343,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G206" t="n">
-        <v>3.31560325622559</v>
+        <v>3.31560301780701</v>
       </c>
       <c r="H206" t="n">
         <v>105630</v>
@@ -6430,7 +6430,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G209" t="n">
-        <v>3.24616646766663</v>
+        <v>3.24616670608521</v>
       </c>
       <c r="H209" t="n">
         <v>13675</v>
@@ -6517,7 +6517,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G212" t="n">
-        <v>3.27220559120178</v>
+        <v>3.2722053527832</v>
       </c>
       <c r="H212" t="n">
         <v>676</v>
@@ -6575,7 +6575,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G214" t="n">
-        <v>3.28088521957397</v>
+        <v>3.2808849811554</v>
       </c>
       <c r="H214" t="n">
         <v>1000</v>
@@ -6604,7 +6604,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G215" t="n">
-        <v>3.26352596282959</v>
+        <v>3.26352572441101</v>
       </c>
       <c r="H215" t="n">
         <v>2689</v>
@@ -6633,7 +6633,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G216" t="n">
-        <v>3.28088521957397</v>
+        <v>3.2808849811554</v>
       </c>
       <c r="H216" t="n">
         <v>5107</v>
@@ -6691,7 +6691,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G218" t="n">
-        <v>3.28088521957397</v>
+        <v>3.2808849811554</v>
       </c>
       <c r="H218" t="n">
         <v>3100</v>
@@ -6749,7 +6749,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G220" t="n">
-        <v>3.26352596282959</v>
+        <v>3.26352572441101</v>
       </c>
       <c r="H220" t="n">
         <v>285</v>
@@ -7010,7 +7010,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G229" t="n">
-        <v>3.27220559120178</v>
+        <v>3.2722053527832</v>
       </c>
       <c r="H229" t="n">
         <v>2568</v>
@@ -7068,7 +7068,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G231" t="n">
-        <v>3.31560325622559</v>
+        <v>3.31560301780701</v>
       </c>
       <c r="H231" t="n">
         <v>5113</v>
@@ -7184,7 +7184,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G235" t="n">
-        <v>3.32428312301636</v>
+        <v>3.32428288459778</v>
       </c>
       <c r="H235" t="n">
         <v>800</v>
@@ -7213,7 +7213,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G236" t="n">
-        <v>3.32428312301636</v>
+        <v>3.32428288459778</v>
       </c>
       <c r="H236" t="n">
         <v>0</v>
@@ -7474,7 +7474,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G245" t="n">
-        <v>3.27220559120178</v>
+        <v>3.2722053527832</v>
       </c>
       <c r="H245" t="n">
         <v>51600</v>
@@ -7532,7 +7532,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G247" t="n">
-        <v>3.24616646766663</v>
+        <v>3.24616670608521</v>
       </c>
       <c r="H247" t="n">
         <v>21876</v>
@@ -7561,7 +7561,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G248" t="n">
-        <v>3.24616646766663</v>
+        <v>3.24616670608521</v>
       </c>
       <c r="H248" t="n">
         <v>0</v>
@@ -8170,7 +8170,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G269" t="n">
-        <v>3.24616646766663</v>
+        <v>3.24616670608521</v>
       </c>
       <c r="H269" t="n">
         <v>750</v>
@@ -8199,7 +8199,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G270" t="n">
-        <v>3.19408917427063</v>
+        <v>3.19408941268921</v>
       </c>
       <c r="H270" t="n">
         <v>883</v>
@@ -8257,7 +8257,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G272" t="n">
-        <v>3.12465262413025</v>
+        <v>3.12465238571167</v>
       </c>
       <c r="H272" t="n">
         <v>9221</v>
@@ -8315,7 +8315,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G274" t="n">
-        <v>2.93370127677917</v>
+        <v>2.93370151519775</v>
       </c>
       <c r="H274" t="n">
         <v>4510</v>
@@ -8373,7 +8373,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G276" t="n">
-        <v>3.02917718887329</v>
+        <v>3.02917695045471</v>
       </c>
       <c r="H276" t="n">
         <v>4096</v>
@@ -8518,7 +8518,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G281" t="n">
-        <v>3.06389546394348</v>
+        <v>3.0638952255249</v>
       </c>
       <c r="H281" t="n">
         <v>1883</v>
@@ -8547,7 +8547,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G282" t="n">
-        <v>3.06389546394348</v>
+        <v>3.0638952255249</v>
       </c>
       <c r="H282" t="n">
         <v>0</v>
@@ -8576,7 +8576,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G283" t="n">
-        <v>3.06389546394348</v>
+        <v>3.0638952255249</v>
       </c>
       <c r="H283" t="n">
         <v>1100</v>
@@ -8750,7 +8750,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G289" t="n">
-        <v>3.08125448226929</v>
+        <v>3.08125424385071</v>
       </c>
       <c r="H289" t="n">
         <v>945</v>
@@ -8895,7 +8895,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G294" t="n">
-        <v>3.08125448226929</v>
+        <v>3.08125424385071</v>
       </c>
       <c r="H294" t="n">
         <v>4</v>
@@ -9185,7 +9185,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G304" t="n">
-        <v>2.87294459342957</v>
+        <v>2.87294435501099</v>
       </c>
       <c r="H304" t="n">
         <v>20000</v>
@@ -9243,7 +9243,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G306" t="n">
-        <v>3.08125448226929</v>
+        <v>3.08125424385071</v>
       </c>
       <c r="H306" t="n">
         <v>17490</v>
@@ -9272,7 +9272,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G307" t="n">
-        <v>3.12465262413025</v>
+        <v>3.12465238571167</v>
       </c>
       <c r="H307" t="n">
         <v>9075</v>
@@ -9301,7 +9301,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G308" t="n">
-        <v>3.12465262413025</v>
+        <v>3.12465238571167</v>
       </c>
       <c r="H308" t="n">
         <v>6589</v>
@@ -9388,7 +9388,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G311" t="n">
-        <v>3.22012782096863</v>
+        <v>3.22012805938721</v>
       </c>
       <c r="H311" t="n">
         <v>688</v>
@@ -9417,7 +9417,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G312" t="n">
-        <v>3.22012782096863</v>
+        <v>3.22012805938721</v>
       </c>
       <c r="H312" t="n">
         <v>0</v>
@@ -9475,7 +9475,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G314" t="n">
-        <v>3.19408917427063</v>
+        <v>3.19408941268921</v>
       </c>
       <c r="H314" t="n">
         <v>9433</v>
@@ -9591,7 +9591,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G318" t="n">
-        <v>3.17673015594482</v>
+        <v>3.17672991752625</v>
       </c>
       <c r="H318" t="n">
         <v>6400</v>
@@ -9823,7 +9823,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G326" t="n">
-        <v>3.19408917427063</v>
+        <v>3.19408941268921</v>
       </c>
       <c r="H326" t="n">
         <v>6000</v>
@@ -9910,7 +9910,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G329" t="n">
-        <v>3.12465262413025</v>
+        <v>3.12465238571167</v>
       </c>
       <c r="H329" t="n">
         <v>3400</v>
@@ -9939,7 +9939,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G330" t="n">
-        <v>3.19408917427063</v>
+        <v>3.19408941268921</v>
       </c>
       <c r="H330" t="n">
         <v>3070</v>
@@ -10026,7 +10026,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G333" t="n">
-        <v>3.02917718887329</v>
+        <v>3.02917695045471</v>
       </c>
       <c r="H333" t="n">
         <v>614</v>
@@ -10374,7 +10374,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G345" t="n">
-        <v>3.22012782096863</v>
+        <v>3.22012805938721</v>
       </c>
       <c r="H345" t="n">
         <v>3873</v>
@@ -10432,7 +10432,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G347" t="n">
-        <v>3.31560325622559</v>
+        <v>3.31560301780701</v>
       </c>
       <c r="H347" t="n">
         <v>11800</v>
@@ -10490,7 +10490,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G349" t="n">
-        <v>3.31560325622559</v>
+        <v>3.31560301780701</v>
       </c>
       <c r="H349" t="n">
         <v>1269</v>
@@ -10548,7 +10548,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G351" t="n">
-        <v>3.31560325622559</v>
+        <v>3.31560301780701</v>
       </c>
       <c r="H351" t="n">
         <v>1729</v>
@@ -54054,6 +54054,35 @@
         <v>3355</v>
       </c>
       <c r="I1851" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1852">
+      <c r="A1852" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1852" s="1" t="n">
+        <v>46322.3333333333</v>
+      </c>
+      <c r="C1852" t="n">
+        <v>2.20000004768372</v>
+      </c>
+      <c r="D1852" t="n">
+        <v>2.38000011444092</v>
+      </c>
+      <c r="E1852" t="n">
+        <v>2.20000004768372</v>
+      </c>
+      <c r="F1852" t="n">
+        <v>2.25999999046326</v>
+      </c>
+      <c r="G1852" t="n">
+        <v>2.25999999046326</v>
+      </c>
+      <c r="H1852" t="n">
+        <v>7625</v>
+      </c>
+      <c r="I1852" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/PTR.MI.xlsx
+++ b/data/PTR.MI.xlsx
@@ -543,7 +543,7 @@
         <v>3.69250011444092</v>
       </c>
       <c r="G6" t="n">
-        <v>3.2049388885498</v>
+        <v>3.20493865013123</v>
       </c>
       <c r="H6" t="n">
         <v>56036</v>
@@ -572,7 +572,7 @@
         <v>3.56850004196167</v>
       </c>
       <c r="G7" t="n">
-        <v>3.0973117351532</v>
+        <v>3.09731197357178</v>
       </c>
       <c r="H7" t="n">
         <v>71079</v>
@@ -717,7 +717,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G12" t="n">
-        <v>3.08125424385071</v>
+        <v>3.08125448226929</v>
       </c>
       <c r="H12" t="n">
         <v>29251</v>
@@ -804,7 +804,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G15" t="n">
-        <v>3.14201164245605</v>
+        <v>3.14201140403748</v>
       </c>
       <c r="H15" t="n">
         <v>8335</v>
@@ -833,7 +833,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G16" t="n">
-        <v>3.14201164245605</v>
+        <v>3.14201140403748</v>
       </c>
       <c r="H16" t="n">
         <v>6164</v>
@@ -891,7 +891,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G18" t="n">
-        <v>3.14201164245605</v>
+        <v>3.14201140403748</v>
       </c>
       <c r="H18" t="n">
         <v>10770</v>
@@ -920,7 +920,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G19" t="n">
-        <v>3.13333177566528</v>
+        <v>3.13333201408386</v>
       </c>
       <c r="H19" t="n">
         <v>26321</v>
@@ -1007,7 +1007,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G22" t="n">
-        <v>3.09861373901367</v>
+        <v>3.09861326217651</v>
       </c>
       <c r="H22" t="n">
         <v>7918</v>
@@ -1036,7 +1036,7 @@
         <v>3.49850010871887</v>
       </c>
       <c r="G23" t="n">
-        <v>3.03655457496643</v>
+        <v>3.03655481338501</v>
       </c>
       <c r="H23" t="n">
         <v>800</v>
@@ -1152,7 +1152,7 @@
         <v>3.35050010681152</v>
       </c>
       <c r="G27" t="n">
-        <v>2.90809655189514</v>
+        <v>2.90809679031372</v>
       </c>
       <c r="H27" t="n">
         <v>9955</v>
@@ -1210,7 +1210,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G29" t="n">
-        <v>3.08125424385071</v>
+        <v>3.08125448226929</v>
       </c>
       <c r="H29" t="n">
         <v>12055</v>
@@ -1297,7 +1297,7 @@
         <v>3.48200011253357</v>
       </c>
       <c r="G32" t="n">
-        <v>3.02223348617554</v>
+        <v>3.02223324775696</v>
       </c>
       <c r="H32" t="n">
         <v>904</v>
@@ -1326,7 +1326,7 @@
         <v>3.48200011253357</v>
       </c>
       <c r="G33" t="n">
-        <v>3.02223348617554</v>
+        <v>3.02223324775696</v>
       </c>
       <c r="H33" t="n">
         <v>432</v>
@@ -1355,7 +1355,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G34" t="n">
-        <v>3.10729312896729</v>
+        <v>3.10729360580444</v>
       </c>
       <c r="H34" t="n">
         <v>3335</v>
@@ -1442,7 +1442,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G37" t="n">
-        <v>3.14201164245605</v>
+        <v>3.14201140403748</v>
       </c>
       <c r="H37" t="n">
         <v>49352</v>
@@ -1471,7 +1471,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G38" t="n">
-        <v>3.19408941268921</v>
+        <v>3.19408917427063</v>
       </c>
       <c r="H38" t="n">
         <v>32777</v>
@@ -1616,7 +1616,7 @@
         <v>3.82500004768372</v>
       </c>
       <c r="G43" t="n">
-        <v>3.31994342803955</v>
+        <v>3.31994318962097</v>
       </c>
       <c r="H43" t="n">
         <v>5962</v>
@@ -1645,7 +1645,7 @@
         <v>3.67499995231628</v>
       </c>
       <c r="G44" t="n">
-        <v>3.18974924087524</v>
+        <v>3.18974900245667</v>
       </c>
       <c r="H44" t="n">
         <v>9040</v>
@@ -1674,7 +1674,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G45" t="n">
-        <v>3.17672991752625</v>
+        <v>3.17673015594482</v>
       </c>
       <c r="H45" t="n">
         <v>1155</v>
@@ -1761,7 +1761,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G48" t="n">
-        <v>3.15069150924683</v>
+        <v>3.15069127082825</v>
       </c>
       <c r="H48" t="n">
         <v>190</v>
@@ -1906,7 +1906,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G53" t="n">
-        <v>3.17672991752625</v>
+        <v>3.17673015594482</v>
       </c>
       <c r="H53" t="n">
         <v>18126</v>
@@ -1993,7 +1993,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G56" t="n">
-        <v>3.15069150924683</v>
+        <v>3.15069127082825</v>
       </c>
       <c r="H56" t="n">
         <v>6760</v>
@@ -2022,7 +2022,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G57" t="n">
-        <v>3.15069150924683</v>
+        <v>3.15069127082825</v>
       </c>
       <c r="H57" t="n">
         <v>100</v>
@@ -2051,7 +2051,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G58" t="n">
-        <v>3.17672991752625</v>
+        <v>3.17673015594482</v>
       </c>
       <c r="H58" t="n">
         <v>1957</v>
@@ -2080,7 +2080,7 @@
         <v>3.66499996185303</v>
       </c>
       <c r="G59" t="n">
-        <v>3.18106961250305</v>
+        <v>3.18106985092163</v>
       </c>
       <c r="H59" t="n">
         <v>20</v>
@@ -2138,7 +2138,7 @@
         <v>3.66499996185303</v>
       </c>
       <c r="G61" t="n">
-        <v>3.18106961250305</v>
+        <v>3.18106985092163</v>
       </c>
       <c r="H61" t="n">
         <v>27542</v>
@@ -2196,7 +2196,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G63" t="n">
-        <v>3.14201164245605</v>
+        <v>3.14201140403748</v>
       </c>
       <c r="H63" t="n">
         <v>2540</v>
@@ -2225,7 +2225,7 @@
         <v>3.5550000667572</v>
       </c>
       <c r="G64" t="n">
-        <v>3.08559465408325</v>
+        <v>3.08559417724609</v>
       </c>
       <c r="H64" t="n">
         <v>550</v>
@@ -2254,7 +2254,7 @@
         <v>3.5550000667572</v>
       </c>
       <c r="G65" t="n">
-        <v>3.08559465408325</v>
+        <v>3.08559417724609</v>
       </c>
       <c r="H65" t="n">
         <v>2547</v>
@@ -2283,7 +2283,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G66" t="n">
-        <v>3.09861373901367</v>
+        <v>3.09861326217651</v>
       </c>
       <c r="H66" t="n">
         <v>4020</v>
@@ -2312,7 +2312,7 @@
         <v>3.63499999046326</v>
       </c>
       <c r="G67" t="n">
-        <v>3.15503096580505</v>
+        <v>3.15503120422363</v>
       </c>
       <c r="H67" t="n">
         <v>1440</v>
@@ -2486,7 +2486,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G73" t="n">
-        <v>3.08125424385071</v>
+        <v>3.08125448226929</v>
       </c>
       <c r="H73" t="n">
         <v>22487</v>
@@ -2515,7 +2515,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G74" t="n">
-        <v>3.08125424385071</v>
+        <v>3.08125448226929</v>
       </c>
       <c r="H74" t="n">
         <v>6950</v>
@@ -2602,7 +2602,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G77" t="n">
-        <v>3.08125424385071</v>
+        <v>3.08125448226929</v>
       </c>
       <c r="H77" t="n">
         <v>1858</v>
@@ -2660,7 +2660,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G79" t="n">
-        <v>3.14201164245605</v>
+        <v>3.14201140403748</v>
       </c>
       <c r="H79" t="n">
         <v>66825</v>
@@ -2689,7 +2689,7 @@
         <v>3.67499995231628</v>
       </c>
       <c r="G80" t="n">
-        <v>3.18974924087524</v>
+        <v>3.18974900245667</v>
       </c>
       <c r="H80" t="n">
         <v>6929</v>
@@ -2747,7 +2747,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G82" t="n">
-        <v>3.14201164245605</v>
+        <v>3.14201140403748</v>
       </c>
       <c r="H82" t="n">
         <v>1300</v>
@@ -3008,7 +3008,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G91" t="n">
-        <v>3.51523423194885</v>
+        <v>3.51523375511169</v>
       </c>
       <c r="H91" t="n">
         <v>17593</v>
@@ -3037,7 +3037,7 @@
         <v>4</v>
       </c>
       <c r="G92" t="n">
-        <v>3.47183609008789</v>
+        <v>3.47183585166931</v>
       </c>
       <c r="H92" t="n">
         <v>9228</v>
@@ -3066,7 +3066,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G93" t="n">
-        <v>3.46315670013428</v>
+        <v>3.4631564617157</v>
       </c>
       <c r="H93" t="n">
         <v>250</v>
@@ -3124,7 +3124,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G95" t="n">
-        <v>3.51523423194885</v>
+        <v>3.51523375511169</v>
       </c>
       <c r="H95" t="n">
         <v>1936</v>
@@ -3211,7 +3211,7 @@
         <v>4.00500011444092</v>
       </c>
       <c r="G98" t="n">
-        <v>3.47617602348328</v>
+        <v>3.47617626190186</v>
       </c>
       <c r="H98" t="n">
         <v>4670</v>
@@ -3240,7 +3240,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G99" t="n">
-        <v>3.59334993362427</v>
+        <v>3.59335017204285</v>
       </c>
       <c r="H99" t="n">
         <v>79600</v>
@@ -3269,7 +3269,7 @@
         <v>3.95499992370605</v>
       </c>
       <c r="G100" t="n">
-        <v>3.43277788162231</v>
+        <v>3.43277812004089</v>
       </c>
       <c r="H100" t="n">
         <v>9435</v>
@@ -3327,7 +3327,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G102" t="n">
-        <v>3.44579720497131</v>
+        <v>3.44579744338989</v>
       </c>
       <c r="H102" t="n">
         <v>1743</v>
@@ -3356,7 +3356,7 @@
         <v>4</v>
       </c>
       <c r="G103" t="n">
-        <v>3.47183609008789</v>
+        <v>3.47183585166931</v>
       </c>
       <c r="H103" t="n">
         <v>11798</v>
@@ -3385,7 +3385,7 @@
         <v>3.9449999332428</v>
       </c>
       <c r="G104" t="n">
-        <v>3.42409825325012</v>
+        <v>3.42409801483154</v>
       </c>
       <c r="H104" t="n">
         <v>26075</v>
@@ -3414,7 +3414,7 @@
         <v>4</v>
       </c>
       <c r="G105" t="n">
-        <v>3.47183609008789</v>
+        <v>3.47183585166931</v>
       </c>
       <c r="H105" t="n">
         <v>5886</v>
@@ -3443,7 +3443,7 @@
         <v>4.03499984741211</v>
       </c>
       <c r="G106" t="n">
-        <v>3.5022144317627</v>
+        <v>3.50221467018127</v>
       </c>
       <c r="H106" t="n">
         <v>9593</v>
@@ -3472,7 +3472,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G107" t="n">
-        <v>3.51523423194885</v>
+        <v>3.51523375511169</v>
       </c>
       <c r="H107" t="n">
         <v>17133</v>
@@ -3617,7 +3617,7 @@
         <v>4.41499996185303</v>
       </c>
       <c r="G112" t="n">
-        <v>3.83203887939453</v>
+        <v>3.83203864097595</v>
       </c>
       <c r="H112" t="n">
         <v>30401</v>
@@ -3704,7 +3704,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G115" t="n">
-        <v>3.87109684944153</v>
+        <v>3.87109708786011</v>
       </c>
       <c r="H115" t="n">
         <v>4580</v>
@@ -3733,7 +3733,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G116" t="n">
-        <v>3.86241674423218</v>
+        <v>3.86241793632507</v>
       </c>
       <c r="H116" t="n">
         <v>17964</v>
@@ -3762,7 +3762,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G117" t="n">
-        <v>4.00997066497803</v>
+        <v>4.00997114181519</v>
       </c>
       <c r="H117" t="n">
         <v>10859</v>
@@ -3791,7 +3791,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G118" t="n">
-        <v>4.03600931167603</v>
+        <v>4.03600978851318</v>
       </c>
       <c r="H118" t="n">
         <v>50</v>
@@ -3820,7 +3820,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G119" t="n">
-        <v>3.96657276153564</v>
+        <v>3.96657228469849</v>
       </c>
       <c r="H119" t="n">
         <v>7065</v>
@@ -3849,7 +3849,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G120" t="n">
-        <v>3.86241674423218</v>
+        <v>3.86241793632507</v>
       </c>
       <c r="H120" t="n">
         <v>34190</v>
@@ -3878,7 +3878,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G121" t="n">
-        <v>3.92317461967468</v>
+        <v>3.92317509651184</v>
       </c>
       <c r="H121" t="n">
         <v>67457</v>
@@ -4023,7 +4023,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G126" t="n">
-        <v>4.03600931167603</v>
+        <v>4.03600978851318</v>
       </c>
       <c r="H126" t="n">
         <v>9991</v>
@@ -4081,7 +4081,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G128" t="n">
-        <v>4.37451267242432</v>
+        <v>4.37451410293579</v>
       </c>
       <c r="H128" t="n">
         <v>36739</v>
@@ -4110,7 +4110,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G129" t="n">
-        <v>4.38319301605225</v>
+        <v>4.3831934928894</v>
       </c>
       <c r="H129" t="n">
         <v>19996</v>
@@ -4168,7 +4168,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G131" t="n">
-        <v>4.49602699279785</v>
+        <v>4.49602746963501</v>
       </c>
       <c r="H131" t="n">
         <v>4316</v>
@@ -4197,7 +4197,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G132" t="n">
-        <v>4.49602699279785</v>
+        <v>4.49602746963501</v>
       </c>
       <c r="H132" t="n">
         <v>2480</v>
@@ -4371,7 +4371,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G138" t="n">
-        <v>4.16620397567749</v>
+        <v>4.16620302200317</v>
       </c>
       <c r="H138" t="n">
         <v>23142</v>
@@ -4458,7 +4458,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G141" t="n">
-        <v>4.42659091949463</v>
+        <v>4.42659044265747</v>
       </c>
       <c r="H141" t="n">
         <v>9500</v>
@@ -4545,7 +4545,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G144" t="n">
-        <v>4.42659091949463</v>
+        <v>4.42659044265747</v>
       </c>
       <c r="H144" t="n">
         <v>5800</v>
@@ -4632,7 +4632,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G147" t="n">
-        <v>4.70433807373047</v>
+        <v>4.70433759689331</v>
       </c>
       <c r="H147" t="n">
         <v>15539</v>
@@ -4661,7 +4661,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G148" t="n">
-        <v>4.49602699279785</v>
+        <v>4.49602746963501</v>
       </c>
       <c r="H148" t="n">
         <v>14318</v>
@@ -4719,7 +4719,7 @@
         <v>5.13000011444092</v>
       </c>
       <c r="G150" t="n">
-        <v>4.45263004302979</v>
+        <v>4.45262956619263</v>
       </c>
       <c r="H150" t="n">
         <v>6278</v>
@@ -4806,7 +4806,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G153" t="n">
-        <v>4.44394969940186</v>
+        <v>4.44395017623901</v>
       </c>
       <c r="H153" t="n">
         <v>2010</v>
@@ -4864,7 +4864,7 @@
         <v>4.75500011444092</v>
       </c>
       <c r="G155" t="n">
-        <v>4.12714529037476</v>
+        <v>4.1271448135376</v>
       </c>
       <c r="H155" t="n">
         <v>9182</v>
@@ -4922,7 +4922,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G157" t="n">
-        <v>4.23564004898071</v>
+        <v>4.23563957214355</v>
       </c>
       <c r="H157" t="n">
         <v>8393</v>
@@ -4980,7 +4980,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G159" t="n">
-        <v>4.09676599502563</v>
+        <v>4.09676647186279</v>
       </c>
       <c r="H159" t="n">
         <v>11440</v>
@@ -5009,7 +5009,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G160" t="n">
-        <v>4.06204843521118</v>
+        <v>4.06204795837402</v>
       </c>
       <c r="H160" t="n">
         <v>4897</v>
@@ -5038,7 +5038,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G161" t="n">
-        <v>4.04468870162964</v>
+        <v>4.0446891784668</v>
       </c>
       <c r="H161" t="n">
         <v>300</v>
@@ -5067,7 +5067,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G162" t="n">
-        <v>3.99261140823364</v>
+        <v>3.99261116981506</v>
       </c>
       <c r="H162" t="n">
         <v>1599</v>
@@ -5096,7 +5096,7 @@
         <v>4.24499988555908</v>
       </c>
       <c r="G163" t="n">
-        <v>3.684485912323</v>
+        <v>3.68448567390442</v>
       </c>
       <c r="H163" t="n">
         <v>8681</v>
@@ -5125,7 +5125,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G164" t="n">
-        <v>3.17672991752625</v>
+        <v>3.17673015594482</v>
       </c>
       <c r="H164" t="n">
         <v>13665</v>
@@ -5154,7 +5154,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G165" t="n">
-        <v>3.26352572441101</v>
+        <v>3.26352596282959</v>
       </c>
       <c r="H165" t="n">
         <v>12420</v>
@@ -5212,7 +5212,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G167" t="n">
-        <v>2.72539114952087</v>
+        <v>2.72539138793945</v>
       </c>
       <c r="H167" t="n">
         <v>16142</v>
@@ -5241,7 +5241,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G168" t="n">
-        <v>2.95974040031433</v>
+        <v>2.95974016189575</v>
       </c>
       <c r="H168" t="n">
         <v>11032</v>
@@ -5328,7 +5328,7 @@
         <v>3.375</v>
       </c>
       <c r="G171" t="n">
-        <v>2.92936182022095</v>
+        <v>2.92936158180237</v>
       </c>
       <c r="H171" t="n">
         <v>1699</v>
@@ -5386,7 +5386,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G173" t="n">
-        <v>3.09861373901367</v>
+        <v>3.09861326217651</v>
       </c>
       <c r="H173" t="n">
         <v>20403</v>
@@ -5415,7 +5415,7 @@
         <v>3.34500002861023</v>
       </c>
       <c r="G174" t="n">
-        <v>2.90332293510437</v>
+        <v>2.90332269668579</v>
       </c>
       <c r="H174" t="n">
         <v>4051</v>
@@ -5473,7 +5473,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G176" t="n">
-        <v>3.08125424385071</v>
+        <v>3.08125448226929</v>
       </c>
       <c r="H176" t="n">
         <v>9550</v>
@@ -5502,7 +5502,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G177" t="n">
-        <v>3.09861373901367</v>
+        <v>3.09861326217651</v>
       </c>
       <c r="H177" t="n">
         <v>2492</v>
@@ -5531,7 +5531,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G178" t="n">
-        <v>3.28956437110901</v>
+        <v>3.28956460952759</v>
       </c>
       <c r="H178" t="n">
         <v>12475</v>
@@ -5589,7 +5589,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G180" t="n">
-        <v>3.31560301780701</v>
+        <v>3.31560325622559</v>
       </c>
       <c r="H180" t="n">
         <v>27302</v>
@@ -5647,7 +5647,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G182" t="n">
-        <v>3.28956437110901</v>
+        <v>3.28956460952759</v>
       </c>
       <c r="H182" t="n">
         <v>11896</v>
@@ -5676,7 +5676,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G183" t="n">
-        <v>3.19408941268921</v>
+        <v>3.19408917427063</v>
       </c>
       <c r="H183" t="n">
         <v>14368</v>
@@ -5734,7 +5734,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G185" t="n">
-        <v>3.19408941268921</v>
+        <v>3.19408917427063</v>
       </c>
       <c r="H185" t="n">
         <v>20637</v>
@@ -5850,7 +5850,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G189" t="n">
-        <v>3.2288076877594</v>
+        <v>3.22880744934082</v>
       </c>
       <c r="H189" t="n">
         <v>7860</v>
@@ -5937,7 +5937,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G192" t="n">
-        <v>3.33296275138855</v>
+        <v>3.33296227455139</v>
       </c>
       <c r="H192" t="n">
         <v>11266</v>
@@ -6024,7 +6024,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G195" t="n">
-        <v>3.34164190292358</v>
+        <v>3.34164237976074</v>
       </c>
       <c r="H195" t="n">
         <v>6546</v>
@@ -6111,7 +6111,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G198" t="n">
-        <v>3.59334993362427</v>
+        <v>3.59335017204285</v>
       </c>
       <c r="H198" t="n">
         <v>40730</v>
@@ -6169,7 +6169,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G200" t="n">
-        <v>3.48051571846008</v>
+        <v>3.48051595687866</v>
       </c>
       <c r="H200" t="n">
         <v>8475</v>
@@ -6198,7 +6198,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G201" t="n">
-        <v>3.33296275138855</v>
+        <v>3.33296227455139</v>
       </c>
       <c r="H201" t="n">
         <v>9437</v>
@@ -6285,7 +6285,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G204" t="n">
-        <v>3.19408941268921</v>
+        <v>3.19408917427063</v>
       </c>
       <c r="H204" t="n">
         <v>55244</v>
@@ -6343,7 +6343,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G206" t="n">
-        <v>3.31560301780701</v>
+        <v>3.31560325622559</v>
       </c>
       <c r="H206" t="n">
         <v>105630</v>
@@ -6459,7 +6459,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G210" t="n">
-        <v>3.2288076877594</v>
+        <v>3.22880744934082</v>
       </c>
       <c r="H210" t="n">
         <v>9234</v>
@@ -6546,7 +6546,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G213" t="n">
-        <v>3.2288076877594</v>
+        <v>3.22880744934082</v>
       </c>
       <c r="H213" t="n">
         <v>1194</v>
@@ -6604,7 +6604,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G215" t="n">
-        <v>3.26352572441101</v>
+        <v>3.26352596282959</v>
       </c>
       <c r="H215" t="n">
         <v>2689</v>
@@ -6749,7 +6749,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G220" t="n">
-        <v>3.26352572441101</v>
+        <v>3.26352596282959</v>
       </c>
       <c r="H220" t="n">
         <v>285</v>
@@ -6778,7 +6778,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G221" t="n">
-        <v>3.28956437110901</v>
+        <v>3.28956460952759</v>
       </c>
       <c r="H221" t="n">
         <v>8062</v>
@@ -6836,7 +6836,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G223" t="n">
-        <v>3.34164190292358</v>
+        <v>3.34164237976074</v>
       </c>
       <c r="H223" t="n">
         <v>1631</v>
@@ -7068,7 +7068,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G231" t="n">
-        <v>3.31560301780701</v>
+        <v>3.31560325622559</v>
       </c>
       <c r="H231" t="n">
         <v>5113</v>
@@ -7242,7 +7242,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G237" t="n">
-        <v>3.28956437110901</v>
+        <v>3.28956460952759</v>
       </c>
       <c r="H237" t="n">
         <v>451</v>
@@ -7358,7 +7358,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G241" t="n">
-        <v>3.34164190292358</v>
+        <v>3.34164237976074</v>
       </c>
       <c r="H241" t="n">
         <v>1540</v>
@@ -7387,7 +7387,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G242" t="n">
-        <v>3.28956437110901</v>
+        <v>3.28956460952759</v>
       </c>
       <c r="H242" t="n">
         <v>1</v>
@@ -7416,7 +7416,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G243" t="n">
-        <v>3.28956437110901</v>
+        <v>3.28956460952759</v>
       </c>
       <c r="H243" t="n">
         <v>0</v>
@@ -7735,7 +7735,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G254" t="n">
-        <v>3.28956437110901</v>
+        <v>3.28956460952759</v>
       </c>
       <c r="H254" t="n">
         <v>2105</v>
@@ -7793,7 +7793,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G256" t="n">
-        <v>3.2288076877594</v>
+        <v>3.22880744934082</v>
       </c>
       <c r="H256" t="n">
         <v>250</v>
@@ -7880,7 +7880,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G259" t="n">
-        <v>3.2288076877594</v>
+        <v>3.22880744934082</v>
       </c>
       <c r="H259" t="n">
         <v>29483</v>
@@ -8025,7 +8025,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G264" t="n">
-        <v>3.13333177566528</v>
+        <v>3.13333201408386</v>
       </c>
       <c r="H264" t="n">
         <v>100</v>
@@ -8054,7 +8054,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G265" t="n">
-        <v>3.07257485389709</v>
+        <v>3.07257509231567</v>
       </c>
       <c r="H265" t="n">
         <v>1250</v>
@@ -8199,7 +8199,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G270" t="n">
-        <v>3.19408941268921</v>
+        <v>3.19408917427063</v>
       </c>
       <c r="H270" t="n">
         <v>883</v>
@@ -8228,7 +8228,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G271" t="n">
-        <v>3.13333177566528</v>
+        <v>3.13333201408386</v>
       </c>
       <c r="H271" t="n">
         <v>2533</v>
@@ -8286,7 +8286,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G273" t="n">
-        <v>3.02049732208252</v>
+        <v>3.0204975605011</v>
       </c>
       <c r="H273" t="n">
         <v>5743</v>
@@ -8402,7 +8402,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G277" t="n">
-        <v>3.02049732208252</v>
+        <v>3.0204975605011</v>
       </c>
       <c r="H277" t="n">
         <v>10072</v>
@@ -8431,7 +8431,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G278" t="n">
-        <v>3.07257485389709</v>
+        <v>3.07257509231567</v>
       </c>
       <c r="H278" t="n">
         <v>4119</v>
@@ -8605,7 +8605,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G284" t="n">
-        <v>2.94238138198853</v>
+        <v>2.94238114356995</v>
       </c>
       <c r="H284" t="n">
         <v>2758</v>
@@ -8634,7 +8634,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G285" t="n">
-        <v>2.94238138198853</v>
+        <v>2.94238114356995</v>
       </c>
       <c r="H285" t="n">
         <v>20</v>
@@ -8750,7 +8750,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G289" t="n">
-        <v>3.08125424385071</v>
+        <v>3.08125448226929</v>
       </c>
       <c r="H289" t="n">
         <v>945</v>
@@ -8895,7 +8895,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G294" t="n">
-        <v>3.08125424385071</v>
+        <v>3.08125448226929</v>
       </c>
       <c r="H294" t="n">
         <v>4</v>
@@ -9040,7 +9040,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G299" t="n">
-        <v>2.86426472663879</v>
+        <v>2.86426448822021</v>
       </c>
       <c r="H299" t="n">
         <v>18061</v>
@@ -9069,7 +9069,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G300" t="n">
-        <v>2.86426472663879</v>
+        <v>2.86426448822021</v>
       </c>
       <c r="H300" t="n">
         <v>0</v>
@@ -9098,7 +9098,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G301" t="n">
-        <v>2.86426472663879</v>
+        <v>2.86426448822021</v>
       </c>
       <c r="H301" t="n">
         <v>14192</v>
@@ -9127,7 +9127,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G302" t="n">
-        <v>2.95974040031433</v>
+        <v>2.95974016189575</v>
       </c>
       <c r="H302" t="n">
         <v>10987</v>
@@ -9156,7 +9156,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G303" t="n">
-        <v>2.8816237449646</v>
+        <v>2.88162398338318</v>
       </c>
       <c r="H303" t="n">
         <v>7318</v>
@@ -9185,7 +9185,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G304" t="n">
-        <v>2.87294435501099</v>
+        <v>2.87294411659241</v>
       </c>
       <c r="H304" t="n">
         <v>20000</v>
@@ -9243,7 +9243,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G306" t="n">
-        <v>3.08125424385071</v>
+        <v>3.08125448226929</v>
       </c>
       <c r="H306" t="n">
         <v>17490</v>
@@ -9475,7 +9475,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G314" t="n">
-        <v>3.19408941268921</v>
+        <v>3.19408917427063</v>
       </c>
       <c r="H314" t="n">
         <v>9433</v>
@@ -9591,7 +9591,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G318" t="n">
-        <v>3.17672991752625</v>
+        <v>3.17673015594482</v>
       </c>
       <c r="H318" t="n">
         <v>6400</v>
@@ -9823,7 +9823,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G326" t="n">
-        <v>3.19408941268921</v>
+        <v>3.19408917427063</v>
       </c>
       <c r="H326" t="n">
         <v>6000</v>
@@ -9852,7 +9852,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G327" t="n">
-        <v>3.14201164245605</v>
+        <v>3.14201140403748</v>
       </c>
       <c r="H327" t="n">
         <v>1954</v>
@@ -9939,7 +9939,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G330" t="n">
-        <v>3.19408941268921</v>
+        <v>3.19408917427063</v>
       </c>
       <c r="H330" t="n">
         <v>3070</v>
@@ -10055,7 +10055,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G334" t="n">
-        <v>3.15069150924683</v>
+        <v>3.15069127082825</v>
       </c>
       <c r="H334" t="n">
         <v>1330</v>
@@ -10316,7 +10316,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G343" t="n">
-        <v>3.15069150924683</v>
+        <v>3.15069127082825</v>
       </c>
       <c r="H343" t="n">
         <v>3072</v>
@@ -10345,7 +10345,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G344" t="n">
-        <v>3.15069150924683</v>
+        <v>3.15069127082825</v>
       </c>
       <c r="H344" t="n">
         <v>8220</v>
@@ -10432,7 +10432,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G347" t="n">
-        <v>3.31560301780701</v>
+        <v>3.31560325622559</v>
       </c>
       <c r="H347" t="n">
         <v>11800</v>
@@ -10490,7 +10490,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G349" t="n">
-        <v>3.31560301780701</v>
+        <v>3.31560325622559</v>
       </c>
       <c r="H349" t="n">
         <v>1269</v>
@@ -10548,7 +10548,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G351" t="n">
-        <v>3.31560301780701</v>
+        <v>3.31560325622559</v>
       </c>
       <c r="H351" t="n">
         <v>1729</v>
@@ -10577,7 +10577,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G352" t="n">
-        <v>3.34164190292358</v>
+        <v>3.34164237976074</v>
       </c>
       <c r="H352" t="n">
         <v>1770</v>
@@ -10606,7 +10606,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G353" t="n">
-        <v>3.28956437110901</v>
+        <v>3.28956460952759</v>
       </c>
       <c r="H353" t="n">
         <v>300</v>
@@ -10635,7 +10635,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G354" t="n">
-        <v>3.34164190292358</v>
+        <v>3.34164237976074</v>
       </c>
       <c r="H354" t="n">
         <v>1650</v>
@@ -10780,7 +10780,7 @@
         <v>4</v>
       </c>
       <c r="G359" t="n">
-        <v>3.47183609008789</v>
+        <v>3.47183585166931</v>
       </c>
       <c r="H359" t="n">
         <v>3169</v>
@@ -10809,7 +10809,7 @@
         <v>4</v>
       </c>
       <c r="G360" t="n">
-        <v>3.47183609008789</v>
+        <v>3.47183585166931</v>
       </c>
       <c r="H360" t="n">
         <v>12</v>
@@ -10954,7 +10954,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G365" t="n">
-        <v>3.55973076820374</v>
+        <v>3.55973052978516</v>
       </c>
       <c r="H365" t="n">
         <v>10835</v>
@@ -11157,7 +11157,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G372" t="n">
-        <v>3.57730937004089</v>
+        <v>3.57730960845947</v>
       </c>
       <c r="H372" t="n">
         <v>5500</v>
@@ -11244,7 +11244,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G375" t="n">
-        <v>3.80583524703979</v>
+        <v>3.80583548545837</v>
       </c>
       <c r="H375" t="n">
         <v>1180</v>
@@ -11273,7 +11273,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G376" t="n">
-        <v>3.82341408729553</v>
+        <v>3.82341384887695</v>
       </c>
       <c r="H376" t="n">
         <v>4874</v>
@@ -11302,7 +11302,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G377" t="n">
-        <v>3.70915126800537</v>
+        <v>3.70915102958679</v>
       </c>
       <c r="H377" t="n">
         <v>1400</v>
@@ -11331,7 +11331,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G378" t="n">
-        <v>3.84978270530701</v>
+        <v>3.84978246688843</v>
       </c>
       <c r="H378" t="n">
         <v>9179</v>
@@ -11360,7 +11360,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G379" t="n">
-        <v>3.90251970291138</v>
+        <v>3.9025194644928</v>
       </c>
       <c r="H379" t="n">
         <v>28775</v>
@@ -11418,7 +11418,7 @@
         <v>4.5</v>
       </c>
       <c r="G381" t="n">
-        <v>3.95525598526001</v>
+        <v>3.95525622367859</v>
       </c>
       <c r="H381" t="n">
         <v>11250</v>
@@ -11447,7 +11447,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G382" t="n">
-        <v>3.92888784408569</v>
+        <v>3.92888760566711</v>
       </c>
       <c r="H382" t="n">
         <v>12048</v>
@@ -11476,7 +11476,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G383" t="n">
-        <v>3.92009806632996</v>
+        <v>3.92009830474854</v>
       </c>
       <c r="H383" t="n">
         <v>30</v>
@@ -11563,7 +11563,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G386" t="n">
-        <v>3.647625207901</v>
+        <v>3.64762496948242</v>
       </c>
       <c r="H386" t="n">
         <v>7282</v>
@@ -11592,7 +11592,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G387" t="n">
-        <v>3.42788887023926</v>
+        <v>3.42788863182068</v>
       </c>
       <c r="H387" t="n">
         <v>24073</v>
@@ -11621,7 +11621,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G388" t="n">
-        <v>3.55094122886658</v>
+        <v>3.550940990448</v>
       </c>
       <c r="H388" t="n">
         <v>7442</v>
@@ -11650,7 +11650,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G389" t="n">
-        <v>3.58609890937805</v>
+        <v>3.58609867095947</v>
       </c>
       <c r="H389" t="n">
         <v>19347</v>
@@ -11679,7 +11679,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G390" t="n">
-        <v>3.69157218933105</v>
+        <v>3.69157195091248</v>
       </c>
       <c r="H390" t="n">
         <v>9963</v>
@@ -11737,7 +11737,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G392" t="n">
-        <v>3.62125658988953</v>
+        <v>3.62125682830811</v>
       </c>
       <c r="H392" t="n">
         <v>15062</v>
@@ -11824,7 +11824,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G395" t="n">
-        <v>3.744309425354</v>
+        <v>3.74430918693542</v>
       </c>
       <c r="H395" t="n">
         <v>15241</v>
@@ -11882,7 +11882,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G397" t="n">
-        <v>3.82341408729553</v>
+        <v>3.82341384887695</v>
       </c>
       <c r="H397" t="n">
         <v>1515</v>
@@ -11940,7 +11940,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G399" t="n">
-        <v>3.70915126800537</v>
+        <v>3.70915102958679</v>
       </c>
       <c r="H399" t="n">
         <v>1746</v>
@@ -11969,7 +11969,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G400" t="n">
-        <v>3.62125658988953</v>
+        <v>3.62125682830811</v>
       </c>
       <c r="H400" t="n">
         <v>1948</v>
@@ -11998,7 +11998,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G401" t="n">
-        <v>3.58609890937805</v>
+        <v>3.58609867095947</v>
       </c>
       <c r="H401" t="n">
         <v>2243</v>
@@ -12056,7 +12056,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G403" t="n">
-        <v>3.68278288841248</v>
+        <v>3.68278336524963</v>
       </c>
       <c r="H403" t="n">
         <v>5461</v>
@@ -12085,7 +12085,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G404" t="n">
-        <v>3.90251970291138</v>
+        <v>3.9025194644928</v>
       </c>
       <c r="H404" t="n">
         <v>16220</v>
@@ -12114,7 +12114,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G405" t="n">
-        <v>3.84978270530701</v>
+        <v>3.84978246688843</v>
       </c>
       <c r="H405" t="n">
         <v>10519</v>
@@ -12143,7 +12143,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G406" t="n">
-        <v>3.84099316596985</v>
+        <v>3.84099292755127</v>
       </c>
       <c r="H406" t="n">
         <v>7000</v>
@@ -12230,7 +12230,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G409" t="n">
-        <v>4.04315090179443</v>
+        <v>4.04315042495728</v>
       </c>
       <c r="H409" t="n">
         <v>11444</v>
@@ -12259,7 +12259,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G410" t="n">
-        <v>3.99920344352722</v>
+        <v>3.99920392036438</v>
       </c>
       <c r="H410" t="n">
         <v>13066</v>
@@ -12288,7 +12288,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G411" t="n">
-        <v>3.99920344352722</v>
+        <v>3.99920392036438</v>
       </c>
       <c r="H411" t="n">
         <v>3045</v>
@@ -12317,7 +12317,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G412" t="n">
-        <v>3.97283506393433</v>
+        <v>3.97283530235291</v>
       </c>
       <c r="H412" t="n">
         <v>3835</v>
@@ -12375,7 +12375,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G414" t="n">
-        <v>4.04315090179443</v>
+        <v>4.04315042495728</v>
       </c>
       <c r="H414" t="n">
         <v>4777</v>
@@ -12404,7 +12404,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G415" t="n">
-        <v>4.04315090179443</v>
+        <v>4.04315042495728</v>
       </c>
       <c r="H415" t="n">
         <v>0</v>
@@ -12433,7 +12433,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G416" t="n">
-        <v>3.99920344352722</v>
+        <v>3.99920392036438</v>
       </c>
       <c r="H416" t="n">
         <v>20150</v>
@@ -12462,7 +12462,7 @@
         <v>4.59000015258789</v>
       </c>
       <c r="G417" t="n">
-        <v>4.03436136245728</v>
+        <v>4.03436183929443</v>
       </c>
       <c r="H417" t="n">
         <v>6334</v>
@@ -12636,7 +12636,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G423" t="n">
-        <v>4.28046560287476</v>
+        <v>4.28046607971191</v>
       </c>
       <c r="H423" t="n">
         <v>7858</v>
@@ -12694,7 +12694,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G425" t="n">
-        <v>4.29804515838623</v>
+        <v>4.29804468154907</v>
       </c>
       <c r="H425" t="n">
         <v>2886</v>
@@ -12723,7 +12723,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G426" t="n">
-        <v>4.2540979385376</v>
+        <v>4.25409746170044</v>
       </c>
       <c r="H426" t="n">
         <v>2079</v>
@@ -12781,7 +12781,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G428" t="n">
-        <v>4.21015024185181</v>
+        <v>4.21015071868896</v>
       </c>
       <c r="H428" t="n">
         <v>3290</v>
@@ -12897,7 +12897,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G432" t="n">
-        <v>4.21015024185181</v>
+        <v>4.21015071868896</v>
       </c>
       <c r="H432" t="n">
         <v>6072</v>
@@ -13013,7 +13013,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G436" t="n">
-        <v>4.21015024185181</v>
+        <v>4.21015071868896</v>
       </c>
       <c r="H436" t="n">
         <v>86</v>
@@ -13042,7 +13042,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G437" t="n">
-        <v>4.07830810546875</v>
+        <v>4.07830858230591</v>
       </c>
       <c r="H437" t="n">
         <v>2764</v>
@@ -13071,7 +13071,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G438" t="n">
-        <v>4.2540979385376</v>
+        <v>4.25409746170044</v>
       </c>
       <c r="H438" t="n">
         <v>3588</v>
@@ -13100,7 +13100,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G439" t="n">
-        <v>4.3859395980835</v>
+        <v>4.38593912124634</v>
       </c>
       <c r="H439" t="n">
         <v>2700</v>
@@ -13129,7 +13129,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G440" t="n">
-        <v>4.3859395980835</v>
+        <v>4.38593912124634</v>
       </c>
       <c r="H440" t="n">
         <v>100</v>
@@ -13216,7 +13216,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G443" t="n">
-        <v>4.35078144073486</v>
+        <v>4.35078191757202</v>
       </c>
       <c r="H443" t="n">
         <v>180</v>
@@ -13332,7 +13332,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G447" t="n">
-        <v>4.3859395980835</v>
+        <v>4.38593912124634</v>
       </c>
       <c r="H447" t="n">
         <v>20</v>
@@ -13419,7 +13419,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G450" t="n">
-        <v>4.21894025802612</v>
+        <v>4.21893978118896</v>
       </c>
       <c r="H450" t="n">
         <v>4300</v>
@@ -13477,7 +13477,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G452" t="n">
-        <v>4.21894025802612</v>
+        <v>4.21893978118896</v>
       </c>
       <c r="H452" t="n">
         <v>1223</v>
@@ -13506,7 +13506,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G453" t="n">
-        <v>4.21015024185181</v>
+        <v>4.21015071868896</v>
       </c>
       <c r="H453" t="n">
         <v>1012</v>
@@ -13651,7 +13651,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G458" t="n">
-        <v>4.05193996429443</v>
+        <v>4.05194044113159</v>
       </c>
       <c r="H458" t="n">
         <v>1015</v>
@@ -13680,7 +13680,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G459" t="n">
-        <v>4.02557134628296</v>
+        <v>4.02557229995728</v>
       </c>
       <c r="H459" t="n">
         <v>4000</v>
@@ -13709,7 +13709,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G460" t="n">
-        <v>4.02557134628296</v>
+        <v>4.02557229995728</v>
       </c>
       <c r="H460" t="n">
         <v>1607</v>
@@ -13738,7 +13738,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G461" t="n">
-        <v>4.02557134628296</v>
+        <v>4.02557229995728</v>
       </c>
       <c r="H461" t="n">
         <v>1400</v>
@@ -13825,7 +13825,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G464" t="n">
-        <v>4.21015024185181</v>
+        <v>4.21015071868896</v>
       </c>
       <c r="H464" t="n">
         <v>909</v>
@@ -13912,7 +13912,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G467" t="n">
-        <v>4.35078144073486</v>
+        <v>4.35078191757202</v>
       </c>
       <c r="H467" t="n">
         <v>12111</v>
@@ -13941,7 +13941,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G468" t="n">
-        <v>4.50020217895508</v>
+        <v>4.50020265579224</v>
       </c>
       <c r="H468" t="n">
         <v>25612</v>
@@ -14115,7 +14115,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G474" t="n">
-        <v>4.57807350158691</v>
+        <v>4.57807397842407</v>
       </c>
       <c r="H474" t="n">
         <v>5287</v>
@@ -14144,7 +14144,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G475" t="n">
-        <v>4.77250909805298</v>
+        <v>4.77250957489014</v>
       </c>
       <c r="H475" t="n">
         <v>3681</v>
@@ -14202,7 +14202,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G477" t="n">
-        <v>4.75483322143555</v>
+        <v>4.75483369827271</v>
       </c>
       <c r="H477" t="n">
         <v>3810</v>
@@ -14666,7 +14666,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G493" t="n">
-        <v>4.26874494552612</v>
+        <v>4.26874446868896</v>
       </c>
       <c r="H493" t="n">
         <v>2410</v>
@@ -14695,7 +14695,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G494" t="n">
-        <v>4.22455501556396</v>
+        <v>4.22455453872681</v>
       </c>
       <c r="H494" t="n">
         <v>1787</v>
@@ -14724,7 +14724,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G495" t="n">
-        <v>4.17152690887451</v>
+        <v>4.17152643203735</v>
       </c>
       <c r="H495" t="n">
         <v>3325</v>
@@ -14782,7 +14782,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G497" t="n">
-        <v>4.03011846542358</v>
+        <v>4.03011894226074</v>
       </c>
       <c r="H497" t="n">
         <v>4388</v>
@@ -14811,7 +14811,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G498" t="n">
-        <v>4.03011846542358</v>
+        <v>4.03011894226074</v>
       </c>
       <c r="H498" t="n">
         <v>18707</v>
@@ -15072,7 +15072,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G507" t="n">
-        <v>4.22455501556396</v>
+        <v>4.22455453872681</v>
       </c>
       <c r="H507" t="n">
         <v>450</v>
@@ -15449,7 +15449,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G520" t="n">
-        <v>4.48969411849976</v>
+        <v>4.4896936416626</v>
       </c>
       <c r="H520" t="n">
         <v>1048</v>
@@ -15623,7 +15623,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G526" t="n">
-        <v>4.57807350158691</v>
+        <v>4.57807397842407</v>
       </c>
       <c r="H526" t="n">
         <v>2094</v>
@@ -15652,7 +15652,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G527" t="n">
-        <v>4.57807350158691</v>
+        <v>4.57807397842407</v>
       </c>
       <c r="H527" t="n">
         <v>50</v>
@@ -15710,7 +15710,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G529" t="n">
-        <v>4.45434188842773</v>
+        <v>4.45434236526489</v>
       </c>
       <c r="H529" t="n">
         <v>1100</v>
@@ -15826,7 +15826,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G533" t="n">
-        <v>4.33061075210571</v>
+        <v>4.33061027526855</v>
       </c>
       <c r="H533" t="n">
         <v>1000</v>
@@ -15855,7 +15855,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G534" t="n">
-        <v>4.26874494552612</v>
+        <v>4.26874446868896</v>
       </c>
       <c r="H534" t="n">
         <v>1220</v>
@@ -15884,7 +15884,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G535" t="n">
-        <v>4.2864203453064</v>
+        <v>4.28641986846924</v>
       </c>
       <c r="H535" t="n">
         <v>1300</v>
@@ -15913,7 +15913,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G536" t="n">
-        <v>4.2864203453064</v>
+        <v>4.28641986846924</v>
       </c>
       <c r="H536" t="n">
         <v>20</v>
@@ -15942,7 +15942,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G537" t="n">
-        <v>4.2864203453064</v>
+        <v>4.28641986846924</v>
       </c>
       <c r="H537" t="n">
         <v>4125</v>
@@ -15971,7 +15971,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G538" t="n">
-        <v>4.2864203453064</v>
+        <v>4.28641986846924</v>
       </c>
       <c r="H538" t="n">
         <v>3365</v>
@@ -16145,7 +16145,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G544" t="n">
-        <v>4.36596202850342</v>
+        <v>4.36596250534058</v>
       </c>
       <c r="H544" t="n">
         <v>2872</v>
@@ -16174,7 +16174,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G545" t="n">
-        <v>4.36596202850342</v>
+        <v>4.36596250534058</v>
       </c>
       <c r="H545" t="n">
         <v>0</v>
@@ -16203,7 +16203,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G546" t="n">
-        <v>4.33944845199585</v>
+        <v>4.33944797515869</v>
       </c>
       <c r="H546" t="n">
         <v>1600</v>
@@ -16232,7 +16232,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G547" t="n">
-        <v>4.33944845199585</v>
+        <v>4.33944797515869</v>
       </c>
       <c r="H547" t="n">
         <v>0</v>
@@ -16261,7 +16261,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G548" t="n">
-        <v>4.33944845199585</v>
+        <v>4.33944797515869</v>
       </c>
       <c r="H548" t="n">
         <v>0</v>
@@ -16319,7 +16319,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G550" t="n">
-        <v>4.21571683883667</v>
+        <v>4.21571636199951</v>
       </c>
       <c r="H550" t="n">
         <v>3340</v>
@@ -16406,7 +16406,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G553" t="n">
-        <v>4.31293487548828</v>
+        <v>4.31293439865112</v>
       </c>
       <c r="H553" t="n">
         <v>11439</v>
@@ -16493,7 +16493,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G556" t="n">
-        <v>4.11849880218506</v>
+        <v>4.1184983253479</v>
       </c>
       <c r="H556" t="n">
         <v>15801</v>
@@ -16522,7 +16522,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G557" t="n">
-        <v>4.07430934906006</v>
+        <v>4.0743088722229</v>
       </c>
       <c r="H557" t="n">
         <v>4755</v>
@@ -16725,7 +16725,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G564" t="n">
-        <v>4.33061075210571</v>
+        <v>4.33061027526855</v>
       </c>
       <c r="H564" t="n">
         <v>6148</v>
@@ -16754,7 +16754,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G565" t="n">
-        <v>4.33061075210571</v>
+        <v>4.33061027526855</v>
       </c>
       <c r="H565" t="n">
         <v>2408</v>
@@ -16870,7 +16870,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G569" t="n">
-        <v>4.57807350158691</v>
+        <v>4.57807397842407</v>
       </c>
       <c r="H569" t="n">
         <v>10847</v>
@@ -16986,7 +16986,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G573" t="n">
-        <v>4.73715734481812</v>
+        <v>4.73715782165527</v>
       </c>
       <c r="H573" t="n">
         <v>798</v>
@@ -17131,7 +17131,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G578" t="n">
-        <v>4.9669451713562</v>
+        <v>4.96694469451904</v>
       </c>
       <c r="H578" t="n">
         <v>3512</v>
@@ -17160,7 +17160,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G579" t="n">
-        <v>4.89624071121216</v>
+        <v>4.89624118804932</v>
       </c>
       <c r="H579" t="n">
         <v>5879</v>
@@ -17189,7 +17189,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G580" t="n">
-        <v>4.94926929473877</v>
+        <v>4.94926881790161</v>
       </c>
       <c r="H580" t="n">
         <v>3440</v>
@@ -17218,7 +17218,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G581" t="n">
-        <v>5.10835313796997</v>
+        <v>5.10835266113281</v>
       </c>
       <c r="H581" t="n">
         <v>12053</v>
@@ -17247,7 +17247,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G582" t="n">
-        <v>5.26743650436401</v>
+        <v>5.26743602752686</v>
       </c>
       <c r="H582" t="n">
         <v>19700</v>
@@ -17450,7 +17450,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G589" t="n">
-        <v>5.65630722045898</v>
+        <v>5.65630769729614</v>
       </c>
       <c r="H589" t="n">
         <v>6708</v>
@@ -17479,7 +17479,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G590" t="n">
-        <v>5.65630722045898</v>
+        <v>5.65630769729614</v>
       </c>
       <c r="H590" t="n">
         <v>1609</v>
@@ -17566,7 +17566,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G593" t="n">
-        <v>5.56792736053467</v>
+        <v>5.56792783737183</v>
       </c>
       <c r="H593" t="n">
         <v>3180</v>
@@ -17595,7 +17595,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G594" t="n">
-        <v>5.56792736053467</v>
+        <v>5.56792783737183</v>
       </c>
       <c r="H594" t="n">
         <v>3910</v>
@@ -17740,7 +17740,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G599" t="n">
-        <v>5.65630722045898</v>
+        <v>5.65630769729614</v>
       </c>
       <c r="H599" t="n">
         <v>6734</v>
@@ -17769,7 +17769,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G600" t="n">
-        <v>5.72701072692871</v>
+        <v>5.72701168060303</v>
       </c>
       <c r="H600" t="n">
         <v>9122</v>
@@ -17914,7 +17914,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G605" t="n">
-        <v>5.72701072692871</v>
+        <v>5.72701168060303</v>
       </c>
       <c r="H605" t="n">
         <v>1318</v>
@@ -17943,7 +17943,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G606" t="n">
-        <v>5.72701072692871</v>
+        <v>5.72701168060303</v>
       </c>
       <c r="H606" t="n">
         <v>11320</v>
@@ -18088,7 +18088,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G611" t="n">
-        <v>5.72701072692871</v>
+        <v>5.72701168060303</v>
       </c>
       <c r="H611" t="n">
         <v>6700</v>
@@ -18117,7 +18117,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G612" t="n">
-        <v>5.72701072692871</v>
+        <v>5.72701168060303</v>
       </c>
       <c r="H612" t="n">
         <v>280</v>
@@ -18146,7 +18146,7 @@
         <v>6.53999996185303</v>
       </c>
       <c r="G613" t="n">
-        <v>5.78003883361816</v>
+        <v>5.78003931045532</v>
       </c>
       <c r="H613" t="n">
         <v>8888</v>
@@ -18175,7 +18175,7 @@
         <v>6.5</v>
       </c>
       <c r="G614" t="n">
-        <v>5.74468660354614</v>
+        <v>5.7446870803833</v>
       </c>
       <c r="H614" t="n">
         <v>2162</v>
@@ -18204,7 +18204,7 @@
         <v>6.5</v>
       </c>
       <c r="G615" t="n">
-        <v>5.74468660354614</v>
+        <v>5.7446870803833</v>
       </c>
       <c r="H615" t="n">
         <v>0</v>
@@ -18233,7 +18233,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G616" t="n">
-        <v>5.88609504699707</v>
+        <v>5.88609457015991</v>
       </c>
       <c r="H616" t="n">
         <v>1889</v>
@@ -18291,7 +18291,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G618" t="n">
-        <v>5.81539058685303</v>
+        <v>5.81539106369019</v>
       </c>
       <c r="H618" t="n">
         <v>2408</v>
@@ -18320,7 +18320,7 @@
         <v>6.5</v>
       </c>
       <c r="G619" t="n">
-        <v>5.74468660354614</v>
+        <v>5.7446870803833</v>
       </c>
       <c r="H619" t="n">
         <v>600</v>
@@ -18465,7 +18465,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G624" t="n">
-        <v>5.65630722045898</v>
+        <v>5.65630769729614</v>
       </c>
       <c r="H624" t="n">
         <v>4043</v>
@@ -18494,7 +18494,7 @@
         <v>6.5</v>
       </c>
       <c r="G625" t="n">
-        <v>5.74468660354614</v>
+        <v>5.7446870803833</v>
       </c>
       <c r="H625" t="n">
         <v>1890</v>
@@ -18523,7 +18523,7 @@
         <v>6.5</v>
       </c>
       <c r="G626" t="n">
-        <v>5.74468660354614</v>
+        <v>5.7446870803833</v>
       </c>
       <c r="H626" t="n">
         <v>4190</v>
@@ -18552,7 +18552,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G627" t="n">
-        <v>6.00982713699341</v>
+        <v>6.00982666015625</v>
       </c>
       <c r="H627" t="n">
         <v>6922</v>
@@ -18581,7 +18581,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G628" t="n">
-        <v>5.88609504699707</v>
+        <v>5.88609457015991</v>
       </c>
       <c r="H628" t="n">
         <v>1335</v>
@@ -18639,7 +18639,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G630" t="n">
-        <v>6.00982713699341</v>
+        <v>6.00982666015625</v>
       </c>
       <c r="H630" t="n">
         <v>16000</v>
@@ -18668,7 +18668,7 @@
         <v>6.78000020980835</v>
       </c>
       <c r="G631" t="n">
-        <v>5.99215126037598</v>
+        <v>5.99215078353882</v>
       </c>
       <c r="H631" t="n">
         <v>200</v>
@@ -18697,7 +18697,7 @@
         <v>6.78000020980835</v>
       </c>
       <c r="G632" t="n">
-        <v>5.99215126037598</v>
+        <v>5.99215078353882</v>
       </c>
       <c r="H632" t="n">
         <v>0</v>
@@ -18726,7 +18726,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G633" t="n">
-        <v>5.83306694030762</v>
+        <v>5.83306741714478</v>
       </c>
       <c r="H633" t="n">
         <v>2617</v>
@@ -18755,7 +18755,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G634" t="n">
-        <v>5.83306694030762</v>
+        <v>5.83306741714478</v>
       </c>
       <c r="H634" t="n">
         <v>0</v>
@@ -18784,7 +18784,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G635" t="n">
-        <v>5.83306694030762</v>
+        <v>5.83306741714478</v>
       </c>
       <c r="H635" t="n">
         <v>200</v>
@@ -18842,7 +18842,7 @@
         <v>6.44000005722046</v>
       </c>
       <c r="G637" t="n">
-        <v>5.69165945053101</v>
+        <v>5.69165897369385</v>
       </c>
       <c r="H637" t="n">
         <v>405</v>
@@ -19016,7 +19016,7 @@
         <v>6.53999996185303</v>
       </c>
       <c r="G643" t="n">
-        <v>5.78003883361816</v>
+        <v>5.78003931045532</v>
       </c>
       <c r="H643" t="n">
         <v>282</v>
@@ -19132,7 +19132,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G647" t="n">
-        <v>5.37349224090576</v>
+        <v>5.3734917640686</v>
       </c>
       <c r="H647" t="n">
         <v>1250</v>
@@ -19161,7 +19161,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G648" t="n">
-        <v>5.26743650436401</v>
+        <v>5.26743602752686</v>
       </c>
       <c r="H648" t="n">
         <v>3000</v>
@@ -19248,7 +19248,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G651" t="n">
-        <v>5.28511238098145</v>
+        <v>5.28511190414429</v>
       </c>
       <c r="H651" t="n">
         <v>1224</v>
@@ -19277,7 +19277,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G652" t="n">
-        <v>5.21440839767456</v>
+        <v>5.2144079208374</v>
       </c>
       <c r="H652" t="n">
         <v>7874</v>
@@ -19335,7 +19335,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G654" t="n">
-        <v>4.94926929473877</v>
+        <v>4.94926881790161</v>
       </c>
       <c r="H654" t="n">
         <v>3137</v>
@@ -19364,7 +19364,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G655" t="n">
-        <v>4.94926929473877</v>
+        <v>4.94926881790161</v>
       </c>
       <c r="H655" t="n">
         <v>14439</v>
@@ -19509,7 +19509,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G660" t="n">
-        <v>5.23208427429199</v>
+        <v>5.23208475112915</v>
       </c>
       <c r="H660" t="n">
         <v>16216</v>
@@ -19654,7 +19654,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G665" t="n">
-        <v>5.19673299789429</v>
+        <v>5.19673252105713</v>
       </c>
       <c r="H665" t="n">
         <v>500</v>
@@ -19712,7 +19712,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G667" t="n">
-        <v>4.77250909805298</v>
+        <v>4.77250957489014</v>
       </c>
       <c r="H667" t="n">
         <v>19980</v>
@@ -19770,7 +19770,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G669" t="n">
-        <v>4.75483322143555</v>
+        <v>4.75483369827271</v>
       </c>
       <c r="H669" t="n">
         <v>1824</v>
@@ -19828,7 +19828,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G671" t="n">
-        <v>4.57807350158691</v>
+        <v>4.57807397842407</v>
       </c>
       <c r="H671" t="n">
         <v>623</v>
@@ -19886,7 +19886,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G673" t="n">
-        <v>4.2864203453064</v>
+        <v>4.28641986846924</v>
       </c>
       <c r="H673" t="n">
         <v>7472</v>
@@ -19915,7 +19915,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G674" t="n">
-        <v>4.2864203453064</v>
+        <v>4.28641986846924</v>
       </c>
       <c r="H674" t="n">
         <v>1700</v>
@@ -19944,7 +19944,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G675" t="n">
-        <v>4.33061075210571</v>
+        <v>4.33061027526855</v>
       </c>
       <c r="H675" t="n">
         <v>4500</v>
@@ -20031,7 +20031,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G678" t="n">
-        <v>4.33061075210571</v>
+        <v>4.33061027526855</v>
       </c>
       <c r="H678" t="n">
         <v>2456</v>
@@ -20176,7 +20176,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G683" t="n">
-        <v>4.77250909805298</v>
+        <v>4.77250957489014</v>
       </c>
       <c r="H683" t="n">
         <v>830</v>
@@ -20205,7 +20205,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G684" t="n">
-        <v>4.70180511474609</v>
+        <v>4.70180559158325</v>
       </c>
       <c r="H684" t="n">
         <v>8359</v>
@@ -20292,7 +20292,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G687" t="n">
-        <v>4.45434188842773</v>
+        <v>4.45434236526489</v>
       </c>
       <c r="H687" t="n">
         <v>1187</v>
@@ -20350,7 +20350,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G689" t="n">
-        <v>4.75483322143555</v>
+        <v>4.75483369827271</v>
       </c>
       <c r="H689" t="n">
         <v>2400</v>
@@ -20379,7 +20379,7 @@
         <v>5.5</v>
       </c>
       <c r="G690" t="n">
-        <v>4.86088943481445</v>
+        <v>4.86088895797729</v>
       </c>
       <c r="H690" t="n">
         <v>2318</v>
@@ -20408,7 +20408,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G691" t="n">
-        <v>4.77250909805298</v>
+        <v>4.77250957489014</v>
       </c>
       <c r="H691" t="n">
         <v>4740</v>
@@ -20437,7 +20437,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G692" t="n">
-        <v>4.87856483459473</v>
+        <v>4.87856531143188</v>
       </c>
       <c r="H692" t="n">
         <v>314</v>
@@ -20466,7 +20466,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G693" t="n">
-        <v>4.87856483459473</v>
+        <v>4.87856531143188</v>
       </c>
       <c r="H693" t="n">
         <v>0</v>
@@ -20495,7 +20495,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G694" t="n">
-        <v>4.93159294128418</v>
+        <v>4.93159341812134</v>
       </c>
       <c r="H694" t="n">
         <v>1580</v>
@@ -20524,7 +20524,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G695" t="n">
-        <v>4.87856483459473</v>
+        <v>4.87856531143188</v>
       </c>
       <c r="H695" t="n">
         <v>4531</v>
@@ -20553,7 +20553,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G696" t="n">
-        <v>4.9669451713562</v>
+        <v>4.96694469451904</v>
       </c>
       <c r="H696" t="n">
         <v>1712</v>
@@ -20582,7 +20582,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G697" t="n">
-        <v>4.94926929473877</v>
+        <v>4.94926881790161</v>
       </c>
       <c r="H697" t="n">
         <v>6290</v>
@@ -20611,7 +20611,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G698" t="n">
-        <v>4.94926929473877</v>
+        <v>4.94926881790161</v>
       </c>
       <c r="H698" t="n">
         <v>190</v>
@@ -20640,7 +20640,7 @@
         <v>5.5</v>
       </c>
       <c r="G699" t="n">
-        <v>4.86088943481445</v>
+        <v>4.86088895797729</v>
       </c>
       <c r="H699" t="n">
         <v>1100</v>
@@ -20669,7 +20669,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G700" t="n">
-        <v>4.75483322143555</v>
+        <v>4.75483369827271</v>
       </c>
       <c r="H700" t="n">
         <v>1074</v>
@@ -20698,7 +20698,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G701" t="n">
-        <v>4.75483322143555</v>
+        <v>4.75483369827271</v>
       </c>
       <c r="H701" t="n">
         <v>1300</v>
@@ -20727,7 +20727,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G702" t="n">
-        <v>4.94926929473877</v>
+        <v>4.94926881790161</v>
       </c>
       <c r="H702" t="n">
         <v>4149</v>
@@ -20756,7 +20756,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G703" t="n">
-        <v>5.03764915466309</v>
+        <v>5.03764867782593</v>
       </c>
       <c r="H703" t="n">
         <v>303</v>
@@ -20785,7 +20785,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G704" t="n">
-        <v>5.03764915466309</v>
+        <v>5.03764867782593</v>
       </c>
       <c r="H704" t="n">
         <v>0</v>
@@ -20901,7 +20901,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G708" t="n">
-        <v>4.98462104797363</v>
+        <v>4.98462057113647</v>
       </c>
       <c r="H708" t="n">
         <v>1299</v>
@@ -21046,7 +21046,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G713" t="n">
-        <v>5.16138076782227</v>
+        <v>5.16138029098511</v>
       </c>
       <c r="H713" t="n">
         <v>3739</v>
@@ -21133,7 +21133,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G716" t="n">
-        <v>5.03764915466309</v>
+        <v>5.03764867782593</v>
       </c>
       <c r="H716" t="n">
         <v>2467</v>
@@ -21162,7 +21162,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G717" t="n">
-        <v>5.03764915466309</v>
+        <v>5.03764867782593</v>
       </c>
       <c r="H717" t="n">
         <v>0</v>
@@ -21191,7 +21191,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G718" t="n">
-        <v>5.03764915466309</v>
+        <v>5.03764867782593</v>
       </c>
       <c r="H718" t="n">
         <v>0</v>
@@ -21220,7 +21220,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G719" t="n">
-        <v>5.03764915466309</v>
+        <v>5.03764867782593</v>
       </c>
       <c r="H719" t="n">
         <v>0</v>
@@ -21249,7 +21249,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G720" t="n">
-        <v>5.03764915466309</v>
+        <v>5.03764867782593</v>
       </c>
       <c r="H720" t="n">
         <v>1250</v>
@@ -21278,7 +21278,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G721" t="n">
-        <v>4.94926929473877</v>
+        <v>4.94926881790161</v>
       </c>
       <c r="H721" t="n">
         <v>277</v>
@@ -21307,7 +21307,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G722" t="n">
-        <v>5.16138076782227</v>
+        <v>5.16138029098511</v>
       </c>
       <c r="H722" t="n">
         <v>1500</v>
@@ -21336,7 +21336,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G723" t="n">
-        <v>5.16138076782227</v>
+        <v>5.16138029098511</v>
       </c>
       <c r="H723" t="n">
         <v>0</v>
@@ -21365,7 +21365,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G724" t="n">
-        <v>5.24976015090942</v>
+        <v>5.24976062774658</v>
       </c>
       <c r="H724" t="n">
         <v>4500</v>
@@ -21394,7 +21394,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G725" t="n">
-        <v>5.03764915466309</v>
+        <v>5.03764867782593</v>
       </c>
       <c r="H725" t="n">
         <v>6899</v>
@@ -21626,7 +21626,7 @@
         <v>5.8600001335144</v>
       </c>
       <c r="G733" t="n">
-        <v>5.24438095092773</v>
+        <v>5.24438142776489</v>
       </c>
       <c r="H733" t="n">
         <v>1735</v>
@@ -21655,7 +21655,7 @@
         <v>5.8600001335144</v>
       </c>
       <c r="G734" t="n">
-        <v>5.24438095092773</v>
+        <v>5.24438142776489</v>
       </c>
       <c r="H734" t="n">
         <v>0</v>
@@ -21771,7 +21771,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G738" t="n">
-        <v>5.26228046417236</v>
+        <v>5.26227998733521</v>
       </c>
       <c r="H738" t="n">
         <v>40</v>
@@ -22148,7 +22148,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G751" t="n">
-        <v>4.99379587173462</v>
+        <v>4.99379634857178</v>
       </c>
       <c r="H751" t="n">
         <v>470</v>
@@ -22351,7 +22351,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G758" t="n">
-        <v>5.31597661972046</v>
+        <v>5.31597709655762</v>
       </c>
       <c r="H758" t="n">
         <v>1333</v>
@@ -22380,7 +22380,7 @@
         <v>6</v>
       </c>
       <c r="G759" t="n">
-        <v>5.36967325210571</v>
+        <v>5.36967372894287</v>
       </c>
       <c r="H759" t="n">
         <v>304</v>
@@ -22409,7 +22409,7 @@
         <v>6</v>
       </c>
       <c r="G760" t="n">
-        <v>5.36967325210571</v>
+        <v>5.36967372894287</v>
       </c>
       <c r="H760" t="n">
         <v>829</v>
@@ -22438,7 +22438,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G761" t="n">
-        <v>5.47706651687622</v>
+        <v>5.47706699371338</v>
       </c>
       <c r="H761" t="n">
         <v>270</v>
@@ -22641,7 +22641,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G768" t="n">
-        <v>5.72765159606934</v>
+        <v>5.72765207290649</v>
       </c>
       <c r="H768" t="n">
         <v>2958</v>
@@ -22699,7 +22699,7 @@
         <v>6.51999998092651</v>
       </c>
       <c r="G770" t="n">
-        <v>5.835045337677</v>
+        <v>5.83504486083984</v>
       </c>
       <c r="H770" t="n">
         <v>667</v>
@@ -22728,7 +22728,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G771" t="n">
-        <v>5.72765159606934</v>
+        <v>5.72765207290649</v>
       </c>
       <c r="H771" t="n">
         <v>678</v>
@@ -22757,7 +22757,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G772" t="n">
-        <v>5.72765159606934</v>
+        <v>5.72765207290649</v>
       </c>
       <c r="H772" t="n">
         <v>1540</v>
@@ -22844,7 +22844,7 @@
         <v>6.5</v>
       </c>
       <c r="G775" t="n">
-        <v>5.81714582443237</v>
+        <v>5.81714630126953</v>
       </c>
       <c r="H775" t="n">
         <v>11</v>
@@ -22902,7 +22902,7 @@
         <v>6.5</v>
       </c>
       <c r="G777" t="n">
-        <v>5.81714582443237</v>
+        <v>5.81714630126953</v>
       </c>
       <c r="H777" t="n">
         <v>6650</v>
@@ -23018,7 +23018,7 @@
         <v>6.73999977111816</v>
       </c>
       <c r="G781" t="n">
-        <v>6.03193283081055</v>
+        <v>6.03193330764771</v>
       </c>
       <c r="H781" t="n">
         <v>1012</v>
@@ -23105,7 +23105,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G784" t="n">
-        <v>6.08563041687012</v>
+        <v>6.08562994003296</v>
       </c>
       <c r="H784" t="n">
         <v>2889</v>
@@ -23250,7 +23250,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G789" t="n">
-        <v>5.8887414932251</v>
+        <v>5.88874197006226</v>
       </c>
       <c r="H789" t="n">
         <v>3581</v>
@@ -23308,7 +23308,7 @@
         <v>6.53999996185303</v>
       </c>
       <c r="G791" t="n">
-        <v>5.85294389724731</v>
+        <v>5.85294437408447</v>
       </c>
       <c r="H791" t="n">
         <v>31</v>
@@ -23337,7 +23337,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G792" t="n">
-        <v>5.72765159606934</v>
+        <v>5.72765207290649</v>
       </c>
       <c r="H792" t="n">
         <v>40050</v>
@@ -23482,7 +23482,7 @@
         <v>6.5</v>
       </c>
       <c r="G797" t="n">
-        <v>5.81714582443237</v>
+        <v>5.81714630126953</v>
       </c>
       <c r="H797" t="n">
         <v>1055</v>
@@ -23511,7 +23511,7 @@
         <v>6.5</v>
       </c>
       <c r="G798" t="n">
-        <v>5.81714582443237</v>
+        <v>5.81714630126953</v>
       </c>
       <c r="H798" t="n">
         <v>30000</v>
@@ -23598,7 +23598,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G801" t="n">
-        <v>5.8887414932251</v>
+        <v>5.88874197006226</v>
       </c>
       <c r="H801" t="n">
         <v>550</v>
@@ -23772,7 +23772,7 @@
         <v>6.42000007629395</v>
       </c>
       <c r="G807" t="n">
-        <v>5.74555110931396</v>
+        <v>5.74555063247681</v>
       </c>
       <c r="H807" t="n">
         <v>50</v>
@@ -23888,7 +23888,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G811" t="n">
-        <v>5.54866218566895</v>
+        <v>5.5486626625061</v>
       </c>
       <c r="H811" t="n">
         <v>1520</v>
@@ -23946,7 +23946,7 @@
         <v>5.8600001335144</v>
       </c>
       <c r="G813" t="n">
-        <v>5.24438095092773</v>
+        <v>5.24438142776489</v>
       </c>
       <c r="H813" t="n">
         <v>595</v>
@@ -23975,7 +23975,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G814" t="n">
-        <v>5.13698720932007</v>
+        <v>5.13698768615723</v>
       </c>
       <c r="H814" t="n">
         <v>33740</v>
@@ -24004,7 +24004,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G815" t="n">
-        <v>5.13698720932007</v>
+        <v>5.13698768615723</v>
       </c>
       <c r="H815" t="n">
         <v>0</v>
@@ -24033,7 +24033,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G816" t="n">
-        <v>5.3517746925354</v>
+        <v>5.35177421569824</v>
       </c>
       <c r="H816" t="n">
         <v>30550</v>
@@ -24062,7 +24062,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G817" t="n">
-        <v>4.83270597457886</v>
+        <v>4.83270645141602</v>
       </c>
       <c r="H817" t="n">
         <v>29376</v>
@@ -24178,7 +24178,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G821" t="n">
-        <v>4.83270597457886</v>
+        <v>4.83270645141602</v>
       </c>
       <c r="H821" t="n">
         <v>677</v>
@@ -24236,7 +24236,7 @@
         <v>6</v>
       </c>
       <c r="G823" t="n">
-        <v>5.36967325210571</v>
+        <v>5.36967372894287</v>
       </c>
       <c r="H823" t="n">
         <v>1900</v>
@@ -24265,7 +24265,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G824" t="n">
-        <v>5.47706651687622</v>
+        <v>5.47706699371338</v>
       </c>
       <c r="H824" t="n">
         <v>100</v>
@@ -24323,7 +24323,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G826" t="n">
-        <v>5.54866218566895</v>
+        <v>5.5486626625061</v>
       </c>
       <c r="H826" t="n">
         <v>610</v>
@@ -24352,7 +24352,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G827" t="n">
-        <v>5.54866218566895</v>
+        <v>5.5486626625061</v>
       </c>
       <c r="H827" t="n">
         <v>0</v>
@@ -24381,7 +24381,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G828" t="n">
-        <v>5.54866218566895</v>
+        <v>5.5486626625061</v>
       </c>
       <c r="H828" t="n">
         <v>600</v>
@@ -24410,7 +24410,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G829" t="n">
-        <v>5.54866218566895</v>
+        <v>5.5486626625061</v>
       </c>
       <c r="H829" t="n">
         <v>0</v>
@@ -24439,7 +24439,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G830" t="n">
-        <v>5.72765159606934</v>
+        <v>5.72765207290649</v>
       </c>
       <c r="H830" t="n">
         <v>1323</v>
@@ -24497,7 +24497,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G832" t="n">
-        <v>5.72765159606934</v>
+        <v>5.72765207290649</v>
       </c>
       <c r="H832" t="n">
         <v>420</v>
@@ -24700,7 +24700,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G839" t="n">
-        <v>5.54866218566895</v>
+        <v>5.5486626625061</v>
       </c>
       <c r="H839" t="n">
         <v>400</v>
@@ -24729,7 +24729,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G840" t="n">
-        <v>5.53076362609863</v>
+        <v>5.53076314926147</v>
       </c>
       <c r="H840" t="n">
         <v>422</v>
@@ -24903,7 +24903,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G846" t="n">
-        <v>5.72765159606934</v>
+        <v>5.72765207290649</v>
       </c>
       <c r="H846" t="n">
         <v>100</v>
@@ -24961,7 +24961,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G848" t="n">
-        <v>5.72765159606934</v>
+        <v>5.72765207290649</v>
       </c>
       <c r="H848" t="n">
         <v>1038</v>
@@ -25048,7 +25048,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G851" t="n">
-        <v>5.70975303649902</v>
+        <v>5.70975255966187</v>
       </c>
       <c r="H851" t="n">
         <v>961</v>
@@ -25077,7 +25077,7 @@
         <v>6.5</v>
       </c>
       <c r="G852" t="n">
-        <v>5.81714582443237</v>
+        <v>5.81714630126953</v>
       </c>
       <c r="H852" t="n">
         <v>263</v>
@@ -25106,7 +25106,7 @@
         <v>6.5</v>
       </c>
       <c r="G853" t="n">
-        <v>5.81714582443237</v>
+        <v>5.81714630126953</v>
       </c>
       <c r="H853" t="n">
         <v>1153</v>
@@ -25193,7 +25193,7 @@
         <v>6.42000007629395</v>
       </c>
       <c r="G856" t="n">
-        <v>5.74555110931396</v>
+        <v>5.74555063247681</v>
       </c>
       <c r="H856" t="n">
         <v>396</v>
@@ -25222,7 +25222,7 @@
         <v>6.51999998092651</v>
       </c>
       <c r="G857" t="n">
-        <v>5.835045337677</v>
+        <v>5.83504486083984</v>
       </c>
       <c r="H857" t="n">
         <v>100</v>
@@ -25251,7 +25251,7 @@
         <v>6.51999998092651</v>
       </c>
       <c r="G858" t="n">
-        <v>5.835045337677</v>
+        <v>5.83504486083984</v>
       </c>
       <c r="H858" t="n">
         <v>0</v>
@@ -25280,7 +25280,7 @@
         <v>6.51999998092651</v>
       </c>
       <c r="G859" t="n">
-        <v>5.835045337677</v>
+        <v>5.83504486083984</v>
       </c>
       <c r="H859" t="n">
         <v>0</v>
@@ -25396,7 +25396,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G863" t="n">
-        <v>5.8887414932251</v>
+        <v>5.88874197006226</v>
       </c>
       <c r="H863" t="n">
         <v>1364</v>
@@ -25454,7 +25454,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G865" t="n">
-        <v>5.8887414932251</v>
+        <v>5.88874197006226</v>
       </c>
       <c r="H865" t="n">
         <v>1988</v>
@@ -25541,7 +25541,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G868" t="n">
-        <v>6.08563041687012</v>
+        <v>6.08562994003296</v>
       </c>
       <c r="H868" t="n">
         <v>500</v>
@@ -25570,7 +25570,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G869" t="n">
-        <v>6.08563041687012</v>
+        <v>6.08562994003296</v>
       </c>
       <c r="H869" t="n">
         <v>0</v>
@@ -25860,7 +25860,7 @@
         <v>6.5</v>
       </c>
       <c r="G879" t="n">
-        <v>5.81714582443237</v>
+        <v>5.81714630126953</v>
       </c>
       <c r="H879" t="n">
         <v>314</v>
@@ -25918,7 +25918,7 @@
         <v>6.73999977111816</v>
       </c>
       <c r="G881" t="n">
-        <v>6.03193283081055</v>
+        <v>6.03193330764771</v>
       </c>
       <c r="H881" t="n">
         <v>400</v>
@@ -25976,7 +25976,7 @@
         <v>6.71999979019165</v>
       </c>
       <c r="G883" t="n">
-        <v>6.01403427124023</v>
+        <v>6.01403379440308</v>
       </c>
       <c r="H883" t="n">
         <v>200</v>
@@ -26005,7 +26005,7 @@
         <v>6.71999979019165</v>
       </c>
       <c r="G884" t="n">
-        <v>6.01403427124023</v>
+        <v>6.01403379440308</v>
       </c>
       <c r="H884" t="n">
         <v>0</v>
@@ -26150,7 +26150,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G889" t="n">
-        <v>5.72765159606934</v>
+        <v>5.72765207290649</v>
       </c>
       <c r="H889" t="n">
         <v>1703</v>
@@ -26179,7 +26179,7 @@
         <v>6.5</v>
       </c>
       <c r="G890" t="n">
-        <v>5.81714582443237</v>
+        <v>5.81714630126953</v>
       </c>
       <c r="H890" t="n">
         <v>662</v>
@@ -26208,7 +26208,7 @@
         <v>6.71999979019165</v>
       </c>
       <c r="G891" t="n">
-        <v>6.01403427124023</v>
+        <v>6.01403379440308</v>
       </c>
       <c r="H891" t="n">
         <v>155</v>
@@ -26237,7 +26237,7 @@
         <v>6.71999979019165</v>
       </c>
       <c r="G892" t="n">
-        <v>6.01403427124023</v>
+        <v>6.01403379440308</v>
       </c>
       <c r="H892" t="n">
         <v>0</v>
@@ -26266,7 +26266,7 @@
         <v>6.71999979019165</v>
       </c>
       <c r="G893" t="n">
-        <v>6.01403427124023</v>
+        <v>6.01403379440308</v>
       </c>
       <c r="H893" t="n">
         <v>0</v>
@@ -26556,7 +26556,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G903" t="n">
-        <v>6.9805760383606</v>
+        <v>6.98057556152344</v>
       </c>
       <c r="H903" t="n">
         <v>2180</v>
@@ -26614,7 +26614,7 @@
         <v>7.57999992370605</v>
       </c>
       <c r="G905" t="n">
-        <v>6.78368711471558</v>
+        <v>6.78368759155273</v>
       </c>
       <c r="H905" t="n">
         <v>2196</v>
@@ -26701,7 +26701,7 @@
         <v>7.03999996185303</v>
       </c>
       <c r="G908" t="n">
-        <v>6.30041646957397</v>
+        <v>6.30041694641113</v>
       </c>
       <c r="H908" t="n">
         <v>5650</v>
@@ -26759,7 +26759,7 @@
         <v>7.1399998664856</v>
       </c>
       <c r="G910" t="n">
-        <v>6.38991165161133</v>
+        <v>6.38991117477417</v>
       </c>
       <c r="H910" t="n">
         <v>1158</v>
@@ -26962,7 +26962,7 @@
         <v>7.26000022888184</v>
       </c>
       <c r="G917" t="n">
-        <v>6.49730539321899</v>
+        <v>6.49730491638184</v>
       </c>
       <c r="H917" t="n">
         <v>3000</v>
@@ -26991,7 +26991,7 @@
         <v>7.42000007629395</v>
       </c>
       <c r="G918" t="n">
-        <v>6.64049625396729</v>
+        <v>6.64049673080444</v>
       </c>
       <c r="H918" t="n">
         <v>2331</v>
@@ -27078,7 +27078,7 @@
         <v>7.34000015258789</v>
       </c>
       <c r="G921" t="n">
-        <v>6.56890106201172</v>
+        <v>6.56890058517456</v>
       </c>
       <c r="H921" t="n">
         <v>250</v>
@@ -27136,7 +27136,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G923" t="n">
-        <v>6.80158662796021</v>
+        <v>6.80158615112305</v>
       </c>
       <c r="H923" t="n">
         <v>2203</v>
@@ -27397,7 +27397,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G932" t="n">
-        <v>6.80158662796021</v>
+        <v>6.80158615112305</v>
       </c>
       <c r="H932" t="n">
         <v>2264</v>
@@ -27455,7 +27455,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G934" t="n">
-        <v>6.80158662796021</v>
+        <v>6.80158615112305</v>
       </c>
       <c r="H934" t="n">
         <v>1250</v>
@@ -27513,7 +27513,7 @@
         <v>7.34000015258789</v>
       </c>
       <c r="G936" t="n">
-        <v>6.56890106201172</v>
+        <v>6.56890058517456</v>
       </c>
       <c r="H936" t="n">
         <v>75</v>
@@ -27687,7 +27687,7 @@
         <v>7.26000022888184</v>
       </c>
       <c r="G942" t="n">
-        <v>6.49730539321899</v>
+        <v>6.49730491638184</v>
       </c>
       <c r="H942" t="n">
         <v>4218</v>
@@ -27716,7 +27716,7 @@
         <v>7.26000022888184</v>
       </c>
       <c r="G943" t="n">
-        <v>6.49730539321899</v>
+        <v>6.49730491638184</v>
       </c>
       <c r="H943" t="n">
         <v>0</v>
@@ -27745,7 +27745,7 @@
         <v>7.26000022888184</v>
       </c>
       <c r="G944" t="n">
-        <v>6.49730539321899</v>
+        <v>6.49730491638184</v>
       </c>
       <c r="H944" t="n">
         <v>0</v>
@@ -27803,7 +27803,7 @@
         <v>7.21999979019165</v>
       </c>
       <c r="G946" t="n">
-        <v>6.46150684356689</v>
+        <v>6.46150732040405</v>
       </c>
       <c r="H946" t="n">
         <v>103974</v>
@@ -27832,7 +27832,7 @@
         <v>7.21999979019165</v>
       </c>
       <c r="G947" t="n">
-        <v>6.46150684356689</v>
+        <v>6.46150732040405</v>
       </c>
       <c r="H947" t="n">
         <v>574</v>
@@ -28238,7 +28238,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G961" t="n">
-        <v>6.08563041687012</v>
+        <v>6.08562994003296</v>
       </c>
       <c r="H961" t="n">
         <v>1113</v>
@@ -28557,7 +28557,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G972" t="n">
-        <v>6.08563041687012</v>
+        <v>6.08562994003296</v>
       </c>
       <c r="H972" t="n">
         <v>250</v>
@@ -30065,7 +30065,7 @@
         <v>7.25</v>
       </c>
       <c r="G1024" t="n">
-        <v>6.48835515975952</v>
+        <v>6.48835563659668</v>
       </c>
       <c r="H1024" t="n">
         <v>712</v>
@@ -30181,7 +30181,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G1028" t="n">
-        <v>6.8463339805603</v>
+        <v>6.84633350372314</v>
       </c>
       <c r="H1028" t="n">
         <v>12728</v>
@@ -30210,7 +30210,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G1029" t="n">
-        <v>6.9805760383606</v>
+        <v>6.98057556152344</v>
       </c>
       <c r="H1029" t="n">
         <v>238</v>
@@ -30239,7 +30239,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G1030" t="n">
-        <v>6.9805760383606</v>
+        <v>6.98057556152344</v>
       </c>
       <c r="H1030" t="n">
         <v>1</v>
@@ -30268,7 +30268,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G1031" t="n">
-        <v>6.9805760383606</v>
+        <v>6.98057556152344</v>
       </c>
       <c r="H1031" t="n">
         <v>100</v>
@@ -30326,7 +30326,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G1033" t="n">
-        <v>6.75683975219727</v>
+        <v>6.75683927536011</v>
       </c>
       <c r="H1033" t="n">
         <v>670</v>
@@ -30355,7 +30355,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G1034" t="n">
-        <v>6.75683975219727</v>
+        <v>6.75683927536011</v>
       </c>
       <c r="H1034" t="n">
         <v>0</v>
@@ -30384,7 +30384,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G1035" t="n">
-        <v>6.75683975219727</v>
+        <v>6.75683927536011</v>
       </c>
       <c r="H1035" t="n">
         <v>0</v>
@@ -30413,7 +30413,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G1036" t="n">
-        <v>6.75683975219727</v>
+        <v>6.75683927536011</v>
       </c>
       <c r="H1036" t="n">
         <v>0</v>
@@ -30442,7 +30442,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G1037" t="n">
-        <v>6.9805760383606</v>
+        <v>6.98057556152344</v>
       </c>
       <c r="H1037" t="n">
         <v>500</v>
@@ -30471,7 +30471,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G1038" t="n">
-        <v>6.80158662796021</v>
+        <v>6.80158615112305</v>
       </c>
       <c r="H1038" t="n">
         <v>730</v>
@@ -30500,7 +30500,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G1039" t="n">
-        <v>6.80158662796021</v>
+        <v>6.80158615112305</v>
       </c>
       <c r="H1039" t="n">
         <v>0</v>
@@ -30558,7 +30558,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G1041" t="n">
-        <v>6.80158662796021</v>
+        <v>6.80158615112305</v>
       </c>
       <c r="H1041" t="n">
         <v>13</v>
@@ -30587,7 +30587,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G1042" t="n">
-        <v>6.80158662796021</v>
+        <v>6.80158615112305</v>
       </c>
       <c r="H1042" t="n">
         <v>0</v>
@@ -30616,7 +30616,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G1043" t="n">
-        <v>6.80158662796021</v>
+        <v>6.80158615112305</v>
       </c>
       <c r="H1043" t="n">
         <v>0</v>
@@ -30645,7 +30645,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G1044" t="n">
-        <v>6.80158662796021</v>
+        <v>6.80158615112305</v>
       </c>
       <c r="H1044" t="n">
         <v>0</v>
@@ -30674,7 +30674,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G1045" t="n">
-        <v>6.80158662796021</v>
+        <v>6.80158615112305</v>
       </c>
       <c r="H1045" t="n">
         <v>0</v>
@@ -30703,7 +30703,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G1046" t="n">
-        <v>6.80158662796021</v>
+        <v>6.80158615112305</v>
       </c>
       <c r="H1046" t="n">
         <v>0</v>
@@ -30732,7 +30732,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G1047" t="n">
-        <v>6.80158662796021</v>
+        <v>6.80158615112305</v>
       </c>
       <c r="H1047" t="n">
         <v>0</v>
@@ -30761,7 +30761,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G1048" t="n">
-        <v>6.9805760383606</v>
+        <v>6.98057556152344</v>
       </c>
       <c r="H1048" t="n">
         <v>601</v>
@@ -30790,7 +30790,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G1049" t="n">
-        <v>6.8463339805603</v>
+        <v>6.84633350372314</v>
       </c>
       <c r="H1049" t="n">
         <v>100</v>
@@ -30819,7 +30819,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G1050" t="n">
-        <v>6.9805760383606</v>
+        <v>6.98057556152344</v>
       </c>
       <c r="H1050" t="n">
         <v>460</v>
@@ -30848,7 +30848,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G1051" t="n">
-        <v>6.9805760383606</v>
+        <v>6.98057556152344</v>
       </c>
       <c r="H1051" t="n">
         <v>125</v>
@@ -30877,7 +30877,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G1052" t="n">
-        <v>6.9805760383606</v>
+        <v>6.98057556152344</v>
       </c>
       <c r="H1052" t="n">
         <v>0</v>
@@ -30906,7 +30906,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G1053" t="n">
-        <v>6.80158662796021</v>
+        <v>6.80158615112305</v>
       </c>
       <c r="H1053" t="n">
         <v>1684</v>
@@ -31080,7 +31080,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G1059" t="n">
-        <v>6.75683975219727</v>
+        <v>6.75683927536011</v>
       </c>
       <c r="H1059" t="n">
         <v>400</v>
@@ -31109,7 +31109,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G1060" t="n">
-        <v>6.75683975219727</v>
+        <v>6.75683927536011</v>
       </c>
       <c r="H1060" t="n">
         <v>0</v>
@@ -31138,7 +31138,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G1061" t="n">
-        <v>6.75683975219727</v>
+        <v>6.75683927536011</v>
       </c>
       <c r="H1061" t="n">
         <v>0</v>
@@ -31602,7 +31602,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G1077" t="n">
-        <v>5.86189413070679</v>
+        <v>5.86189365386963</v>
       </c>
       <c r="H1077" t="n">
         <v>846</v>
@@ -31631,7 +31631,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G1078" t="n">
-        <v>5.72765159606934</v>
+        <v>5.72765207290649</v>
       </c>
       <c r="H1078" t="n">
         <v>2019</v>
@@ -31660,7 +31660,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G1079" t="n">
-        <v>5.86189413070679</v>
+        <v>5.86189365386963</v>
       </c>
       <c r="H1079" t="n">
         <v>100</v>
@@ -31747,7 +31747,7 @@
         <v>6</v>
       </c>
       <c r="G1082" t="n">
-        <v>5.36967325210571</v>
+        <v>5.36967372894287</v>
       </c>
       <c r="H1082" t="n">
         <v>11354</v>
@@ -31776,7 +31776,7 @@
         <v>6</v>
       </c>
       <c r="G1083" t="n">
-        <v>5.36967325210571</v>
+        <v>5.36967372894287</v>
       </c>
       <c r="H1083" t="n">
         <v>25500</v>
@@ -31805,7 +31805,7 @@
         <v>6</v>
       </c>
       <c r="G1084" t="n">
-        <v>5.36967325210571</v>
+        <v>5.36967372894287</v>
       </c>
       <c r="H1084" t="n">
         <v>0</v>
@@ -31863,7 +31863,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G1086" t="n">
-        <v>5.32492589950562</v>
+        <v>5.32492637634277</v>
       </c>
       <c r="H1086" t="n">
         <v>6465</v>
@@ -31892,7 +31892,7 @@
         <v>6</v>
       </c>
       <c r="G1087" t="n">
-        <v>5.36967325210571</v>
+        <v>5.36967372894287</v>
       </c>
       <c r="H1087" t="n">
         <v>6931</v>
@@ -31921,7 +31921,7 @@
         <v>6</v>
       </c>
       <c r="G1088" t="n">
-        <v>5.36967325210571</v>
+        <v>5.36967372894287</v>
       </c>
       <c r="H1088" t="n">
         <v>0</v>
@@ -31950,7 +31950,7 @@
         <v>6</v>
       </c>
       <c r="G1089" t="n">
-        <v>5.36967325210571</v>
+        <v>5.36967372894287</v>
       </c>
       <c r="H1089" t="n">
         <v>0</v>
@@ -31979,7 +31979,7 @@
         <v>6</v>
       </c>
       <c r="G1090" t="n">
-        <v>5.36967325210571</v>
+        <v>5.36967372894287</v>
       </c>
       <c r="H1090" t="n">
         <v>850</v>
@@ -32008,7 +32008,7 @@
         <v>6</v>
       </c>
       <c r="G1091" t="n">
-        <v>5.36967325210571</v>
+        <v>5.36967372894287</v>
       </c>
       <c r="H1091" t="n">
         <v>240</v>
@@ -32037,7 +32037,7 @@
         <v>6</v>
       </c>
       <c r="G1092" t="n">
-        <v>5.36967325210571</v>
+        <v>5.36967372894287</v>
       </c>
       <c r="H1092" t="n">
         <v>650</v>
@@ -32066,7 +32066,7 @@
         <v>6</v>
       </c>
       <c r="G1093" t="n">
-        <v>5.36967325210571</v>
+        <v>5.36967372894287</v>
       </c>
       <c r="H1093" t="n">
         <v>675</v>
@@ -32095,7 +32095,7 @@
         <v>6</v>
       </c>
       <c r="G1094" t="n">
-        <v>5.36967325210571</v>
+        <v>5.36967372894287</v>
       </c>
       <c r="H1094" t="n">
         <v>0</v>
@@ -32124,7 +32124,7 @@
         <v>6</v>
       </c>
       <c r="G1095" t="n">
-        <v>5.36967325210571</v>
+        <v>5.36967372894287</v>
       </c>
       <c r="H1095" t="n">
         <v>0</v>
@@ -32414,7 +32414,7 @@
         <v>6.25</v>
       </c>
       <c r="G1105" t="n">
-        <v>5.59340953826904</v>
+        <v>5.5934100151062</v>
       </c>
       <c r="H1105" t="n">
         <v>14260</v>
@@ -32443,7 +32443,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G1106" t="n">
-        <v>5.54866218566895</v>
+        <v>5.5486626625061</v>
       </c>
       <c r="H1106" t="n">
         <v>39658</v>
@@ -32559,7 +32559,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G1110" t="n">
-        <v>5.54866218566895</v>
+        <v>5.5486626625061</v>
       </c>
       <c r="H1110" t="n">
         <v>21380</v>
@@ -32617,7 +32617,7 @@
         <v>6.5</v>
       </c>
       <c r="G1112" t="n">
-        <v>5.81714582443237</v>
+        <v>5.81714630126953</v>
       </c>
       <c r="H1112" t="n">
         <v>29853</v>
@@ -32646,7 +32646,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G1113" t="n">
-        <v>5.72765159606934</v>
+        <v>5.72765207290649</v>
       </c>
       <c r="H1113" t="n">
         <v>31724</v>
@@ -32675,7 +32675,7 @@
         <v>6.5</v>
       </c>
       <c r="G1114" t="n">
-        <v>5.81714582443237</v>
+        <v>5.81714630126953</v>
       </c>
       <c r="H1114" t="n">
         <v>15604</v>
@@ -32791,7 +32791,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G1118" t="n">
-        <v>6.08563041687012</v>
+        <v>6.08562994003296</v>
       </c>
       <c r="H1118" t="n">
         <v>46505</v>
@@ -32965,7 +32965,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G1124" t="n">
-        <v>6.75683975219727</v>
+        <v>6.75683927536011</v>
       </c>
       <c r="H1124" t="n">
         <v>52998</v>
@@ -54083,6 +54083,35 @@
         <v>7625</v>
       </c>
       <c r="I1852" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1853">
+      <c r="A1853" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1853" s="1" t="n">
+        <v>46323.3333333333</v>
+      </c>
+      <c r="C1853" t="n">
+        <v>2.20000004768372</v>
+      </c>
+      <c r="D1853" t="n">
+        <v>2.20000004768372</v>
+      </c>
+      <c r="E1853" t="n">
+        <v>2.20000004768372</v>
+      </c>
+      <c r="F1853" t="n">
+        <v>2.20000004768372</v>
+      </c>
+      <c r="G1853" t="n">
+        <v>2.20000004768372</v>
+      </c>
+      <c r="H1853" t="n">
+        <v>1000</v>
+      </c>
+      <c r="I1853" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/PTR.MI.xlsx
+++ b/data/PTR.MI.xlsx
@@ -427,7 +427,7 @@
         <v>3.75</v>
       </c>
       <c r="G2" t="n">
-        <v>3.2548463344574</v>
+        <v>3.25484609603882</v>
       </c>
       <c r="H2" t="n">
         <v>859316</v>
@@ -456,7 +456,7 @@
         <v>3.7409999370575</v>
       </c>
       <c r="G3" t="n">
-        <v>3.24703454971313</v>
+        <v>3.24703431129456</v>
       </c>
       <c r="H3" t="n">
         <v>329252</v>
@@ -485,7 +485,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G4" t="n">
-        <v>3.22012805938721</v>
+        <v>3.22012782096863</v>
       </c>
       <c r="H4" t="n">
         <v>98299</v>
@@ -543,7 +543,7 @@
         <v>3.69250011444092</v>
       </c>
       <c r="G6" t="n">
-        <v>3.20493865013123</v>
+        <v>3.2049388885498</v>
       </c>
       <c r="H6" t="n">
         <v>56036</v>
@@ -572,7 +572,7 @@
         <v>3.56850004196167</v>
       </c>
       <c r="G7" t="n">
-        <v>3.09731197357178</v>
+        <v>3.09731149673462</v>
       </c>
       <c r="H7" t="n">
         <v>71079</v>
@@ -804,7 +804,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G15" t="n">
-        <v>3.14201140403748</v>
+        <v>3.14201164245605</v>
       </c>
       <c r="H15" t="n">
         <v>8335</v>
@@ -833,7 +833,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G16" t="n">
-        <v>3.14201140403748</v>
+        <v>3.14201164245605</v>
       </c>
       <c r="H16" t="n">
         <v>6164</v>
@@ -891,7 +891,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G18" t="n">
-        <v>3.14201140403748</v>
+        <v>3.14201164245605</v>
       </c>
       <c r="H18" t="n">
         <v>10770</v>
@@ -1007,7 +1007,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G22" t="n">
-        <v>3.09861326217651</v>
+        <v>3.09861373901367</v>
       </c>
       <c r="H22" t="n">
         <v>7918</v>
@@ -1036,7 +1036,7 @@
         <v>3.49850010871887</v>
       </c>
       <c r="G23" t="n">
-        <v>3.03655481338501</v>
+        <v>3.03655457496643</v>
       </c>
       <c r="H23" t="n">
         <v>800</v>
@@ -1123,7 +1123,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G26" t="n">
-        <v>2.96842002868652</v>
+        <v>2.96841979026794</v>
       </c>
       <c r="H26" t="n">
         <v>3800</v>
@@ -1152,7 +1152,7 @@
         <v>3.35050010681152</v>
       </c>
       <c r="G27" t="n">
-        <v>2.90809679031372</v>
+        <v>2.90809655189514</v>
       </c>
       <c r="H27" t="n">
         <v>9955</v>
@@ -1181,7 +1181,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G28" t="n">
-        <v>2.98577904701233</v>
+        <v>2.98577928543091</v>
       </c>
       <c r="H28" t="n">
         <v>6355</v>
@@ -1297,7 +1297,7 @@
         <v>3.48200011253357</v>
       </c>
       <c r="G32" t="n">
-        <v>3.02223324775696</v>
+        <v>3.02223348617554</v>
       </c>
       <c r="H32" t="n">
         <v>904</v>
@@ -1326,7 +1326,7 @@
         <v>3.48200011253357</v>
       </c>
       <c r="G33" t="n">
-        <v>3.02223324775696</v>
+        <v>3.02223348617554</v>
       </c>
       <c r="H33" t="n">
         <v>432</v>
@@ -1355,7 +1355,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G34" t="n">
-        <v>3.10729360580444</v>
+        <v>3.10729336738586</v>
       </c>
       <c r="H34" t="n">
         <v>3335</v>
@@ -1384,7 +1384,7 @@
         <v>3.5</v>
       </c>
       <c r="G35" t="n">
-        <v>3.03785634040833</v>
+        <v>3.0378565788269</v>
       </c>
       <c r="H35" t="n">
         <v>1400</v>
@@ -1442,7 +1442,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G37" t="n">
-        <v>3.14201140403748</v>
+        <v>3.14201164245605</v>
       </c>
       <c r="H37" t="n">
         <v>49352</v>
@@ -1500,7 +1500,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G39" t="n">
-        <v>3.21144843101501</v>
+        <v>3.21144819259644</v>
       </c>
       <c r="H39" t="n">
         <v>28455</v>
@@ -1587,7 +1587,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G42" t="n">
-        <v>3.2982439994812</v>
+        <v>3.29824423789978</v>
       </c>
       <c r="H42" t="n">
         <v>4451</v>
@@ -1645,7 +1645,7 @@
         <v>3.67499995231628</v>
       </c>
       <c r="G44" t="n">
-        <v>3.18974900245667</v>
+        <v>3.18974947929382</v>
       </c>
       <c r="H44" t="n">
         <v>9040</v>
@@ -1674,7 +1674,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G45" t="n">
-        <v>3.17673015594482</v>
+        <v>3.17672991752625</v>
       </c>
       <c r="H45" t="n">
         <v>1155</v>
@@ -1703,7 +1703,7 @@
         <v>3.71499991416931</v>
       </c>
       <c r="G46" t="n">
-        <v>3.22446751594543</v>
+        <v>3.22446775436401</v>
       </c>
       <c r="H46" t="n">
         <v>3406</v>
@@ -1761,7 +1761,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G48" t="n">
-        <v>3.15069127082825</v>
+        <v>3.15069150924683</v>
       </c>
       <c r="H48" t="n">
         <v>190</v>
@@ -1790,7 +1790,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G49" t="n">
-        <v>3.21144843101501</v>
+        <v>3.21144819259644</v>
       </c>
       <c r="H49" t="n">
         <v>17100</v>
@@ -1819,7 +1819,7 @@
         <v>3.71499991416931</v>
       </c>
       <c r="G50" t="n">
-        <v>3.22446751594543</v>
+        <v>3.22446775436401</v>
       </c>
       <c r="H50" t="n">
         <v>7667</v>
@@ -1848,7 +1848,7 @@
         <v>3.75</v>
       </c>
       <c r="G51" t="n">
-        <v>3.2548463344574</v>
+        <v>3.25484609603882</v>
       </c>
       <c r="H51" t="n">
         <v>37160</v>
@@ -1877,7 +1877,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G52" t="n">
-        <v>3.21144843101501</v>
+        <v>3.21144819259644</v>
       </c>
       <c r="H52" t="n">
         <v>49416</v>
@@ -1906,7 +1906,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G53" t="n">
-        <v>3.17673015594482</v>
+        <v>3.17672991752625</v>
       </c>
       <c r="H53" t="n">
         <v>18126</v>
@@ -1935,7 +1935,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G54" t="n">
-        <v>3.21144843101501</v>
+        <v>3.21144819259644</v>
       </c>
       <c r="H54" t="n">
         <v>4498</v>
@@ -1993,7 +1993,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G56" t="n">
-        <v>3.15069127082825</v>
+        <v>3.15069150924683</v>
       </c>
       <c r="H56" t="n">
         <v>6760</v>
@@ -2022,7 +2022,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G57" t="n">
-        <v>3.15069127082825</v>
+        <v>3.15069150924683</v>
       </c>
       <c r="H57" t="n">
         <v>100</v>
@@ -2051,7 +2051,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G58" t="n">
-        <v>3.17673015594482</v>
+        <v>3.17672991752625</v>
       </c>
       <c r="H58" t="n">
         <v>1957</v>
@@ -2167,7 +2167,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G62" t="n">
-        <v>3.21144843101501</v>
+        <v>3.21144819259644</v>
       </c>
       <c r="H62" t="n">
         <v>20</v>
@@ -2196,7 +2196,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G63" t="n">
-        <v>3.14201140403748</v>
+        <v>3.14201164245605</v>
       </c>
       <c r="H63" t="n">
         <v>2540</v>
@@ -2225,7 +2225,7 @@
         <v>3.5550000667572</v>
       </c>
       <c r="G64" t="n">
-        <v>3.08559417724609</v>
+        <v>3.08559441566467</v>
       </c>
       <c r="H64" t="n">
         <v>550</v>
@@ -2254,7 +2254,7 @@
         <v>3.5550000667572</v>
       </c>
       <c r="G65" t="n">
-        <v>3.08559417724609</v>
+        <v>3.08559441566467</v>
       </c>
       <c r="H65" t="n">
         <v>2547</v>
@@ -2283,7 +2283,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G66" t="n">
-        <v>3.09861326217651</v>
+        <v>3.09861373901367</v>
       </c>
       <c r="H66" t="n">
         <v>4020</v>
@@ -2312,7 +2312,7 @@
         <v>3.63499999046326</v>
       </c>
       <c r="G67" t="n">
-        <v>3.15503120422363</v>
+        <v>3.15503072738647</v>
       </c>
       <c r="H67" t="n">
         <v>1440</v>
@@ -2428,7 +2428,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G71" t="n">
-        <v>3.21144843101501</v>
+        <v>3.21144819259644</v>
       </c>
       <c r="H71" t="n">
         <v>2275</v>
@@ -2660,7 +2660,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G79" t="n">
-        <v>3.14201140403748</v>
+        <v>3.14201164245605</v>
       </c>
       <c r="H79" t="n">
         <v>66825</v>
@@ -2689,7 +2689,7 @@
         <v>3.67499995231628</v>
       </c>
       <c r="G80" t="n">
-        <v>3.18974900245667</v>
+        <v>3.18974947929382</v>
       </c>
       <c r="H80" t="n">
         <v>6929</v>
@@ -2747,7 +2747,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G82" t="n">
-        <v>3.14201140403748</v>
+        <v>3.14201164245605</v>
       </c>
       <c r="H82" t="n">
         <v>1300</v>
@@ -2776,7 +2776,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G83" t="n">
-        <v>3.2982439994812</v>
+        <v>3.29824423789978</v>
       </c>
       <c r="H83" t="n">
         <v>198082</v>
@@ -2805,7 +2805,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G84" t="n">
-        <v>3.2982439994812</v>
+        <v>3.29824423789978</v>
       </c>
       <c r="H84" t="n">
         <v>33903</v>
@@ -2834,7 +2834,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G85" t="n">
-        <v>3.2982439994812</v>
+        <v>3.29824423789978</v>
       </c>
       <c r="H85" t="n">
         <v>18308</v>
@@ -2863,7 +2863,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G86" t="n">
-        <v>3.2982439994812</v>
+        <v>3.29824423789978</v>
       </c>
       <c r="H86" t="n">
         <v>6890</v>
@@ -3008,7 +3008,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G91" t="n">
-        <v>3.51523375511169</v>
+        <v>3.51523399353027</v>
       </c>
       <c r="H91" t="n">
         <v>17593</v>
@@ -3066,7 +3066,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G93" t="n">
-        <v>3.4631564617157</v>
+        <v>3.46315670013428</v>
       </c>
       <c r="H93" t="n">
         <v>250</v>
@@ -3124,7 +3124,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G95" t="n">
-        <v>3.51523375511169</v>
+        <v>3.51523399353027</v>
       </c>
       <c r="H95" t="n">
         <v>1936</v>
@@ -3153,7 +3153,7 @@
         <v>4.02500009536743</v>
       </c>
       <c r="G96" t="n">
-        <v>3.49353504180908</v>
+        <v>3.49353528022766</v>
       </c>
       <c r="H96" t="n">
         <v>1493</v>
@@ -3211,7 +3211,7 @@
         <v>4.00500011444092</v>
       </c>
       <c r="G98" t="n">
-        <v>3.47617626190186</v>
+        <v>3.47617602348328</v>
       </c>
       <c r="H98" t="n">
         <v>4670</v>
@@ -3240,7 +3240,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G99" t="n">
-        <v>3.59335017204285</v>
+        <v>3.59334993362427</v>
       </c>
       <c r="H99" t="n">
         <v>79600</v>
@@ -3269,7 +3269,7 @@
         <v>3.95499992370605</v>
       </c>
       <c r="G100" t="n">
-        <v>3.43277812004089</v>
+        <v>3.43277764320374</v>
       </c>
       <c r="H100" t="n">
         <v>9435</v>
@@ -3327,7 +3327,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G102" t="n">
-        <v>3.44579744338989</v>
+        <v>3.44579720497131</v>
       </c>
       <c r="H102" t="n">
         <v>1743</v>
@@ -3385,7 +3385,7 @@
         <v>3.9449999332428</v>
       </c>
       <c r="G104" t="n">
-        <v>3.42409801483154</v>
+        <v>3.42409825325012</v>
       </c>
       <c r="H104" t="n">
         <v>26075</v>
@@ -3472,7 +3472,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G107" t="n">
-        <v>3.51523375511169</v>
+        <v>3.51523399353027</v>
       </c>
       <c r="H107" t="n">
         <v>17133</v>
@@ -3559,7 +3559,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G110" t="n">
-        <v>3.64542770385742</v>
+        <v>3.64542746543884</v>
       </c>
       <c r="H110" t="n">
         <v>37685</v>
@@ -3588,7 +3588,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G111" t="n">
-        <v>3.64542770385742</v>
+        <v>3.64542746543884</v>
       </c>
       <c r="H111" t="n">
         <v>19204</v>
@@ -3617,7 +3617,7 @@
         <v>4.41499996185303</v>
       </c>
       <c r="G112" t="n">
-        <v>3.83203864097595</v>
+        <v>3.83203911781311</v>
       </c>
       <c r="H112" t="n">
         <v>30401</v>
@@ -3646,7 +3646,7 @@
         <v>4.5</v>
       </c>
       <c r="G113" t="n">
-        <v>3.90581512451172</v>
+        <v>3.9058153629303</v>
       </c>
       <c r="H113" t="n">
         <v>10114</v>
@@ -3675,7 +3675,7 @@
         <v>4.5</v>
       </c>
       <c r="G114" t="n">
-        <v>3.90581512451172</v>
+        <v>3.9058153629303</v>
       </c>
       <c r="H114" t="n">
         <v>36925</v>
@@ -3733,7 +3733,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G116" t="n">
-        <v>3.86241793632507</v>
+        <v>3.86241722106934</v>
       </c>
       <c r="H116" t="n">
         <v>17964</v>
@@ -3762,7 +3762,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G117" t="n">
-        <v>4.00997114181519</v>
+        <v>4.00997018814087</v>
       </c>
       <c r="H117" t="n">
         <v>10859</v>
@@ -3820,7 +3820,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G119" t="n">
-        <v>3.96657228469849</v>
+        <v>3.96657276153564</v>
       </c>
       <c r="H119" t="n">
         <v>7065</v>
@@ -3849,7 +3849,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G120" t="n">
-        <v>3.86241793632507</v>
+        <v>3.86241722106934</v>
       </c>
       <c r="H120" t="n">
         <v>34190</v>
@@ -3878,7 +3878,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G121" t="n">
-        <v>3.92317509651184</v>
+        <v>3.92317461967468</v>
       </c>
       <c r="H121" t="n">
         <v>67457</v>
@@ -3907,7 +3907,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G122" t="n">
-        <v>3.94053363800049</v>
+        <v>3.94053387641907</v>
       </c>
       <c r="H122" t="n">
         <v>5398</v>
@@ -3965,7 +3965,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G124" t="n">
-        <v>3.94921374320984</v>
+        <v>3.94921398162842</v>
       </c>
       <c r="H124" t="n">
         <v>5841</v>
@@ -3994,7 +3994,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G125" t="n">
-        <v>3.94921374320984</v>
+        <v>3.94921398162842</v>
       </c>
       <c r="H125" t="n">
         <v>21549</v>
@@ -4052,7 +4052,7 @@
         <v>4.88500022888184</v>
       </c>
       <c r="G127" t="n">
-        <v>4.23998022079468</v>
+        <v>4.23997926712036</v>
       </c>
       <c r="H127" t="n">
         <v>32038</v>
@@ -4081,7 +4081,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G128" t="n">
-        <v>4.37451410293579</v>
+        <v>4.37451314926147</v>
       </c>
       <c r="H128" t="n">
         <v>36739</v>
@@ -4139,7 +4139,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G130" t="n">
-        <v>4.39187240600586</v>
+        <v>4.39187288284302</v>
       </c>
       <c r="H130" t="n">
         <v>8599</v>
@@ -4226,7 +4226,7 @@
         <v>4.97499990463257</v>
       </c>
       <c r="G133" t="n">
-        <v>4.31809616088867</v>
+        <v>4.31809568405151</v>
       </c>
       <c r="H133" t="n">
         <v>8257</v>
@@ -4255,7 +4255,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G134" t="n">
-        <v>4.24431943893433</v>
+        <v>4.24431896209717</v>
       </c>
       <c r="H134" t="n">
         <v>9475</v>
@@ -4284,7 +4284,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G135" t="n">
-        <v>4.24431943893433</v>
+        <v>4.24431896209717</v>
       </c>
       <c r="H135" t="n">
         <v>1852</v>
@@ -4371,7 +4371,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G138" t="n">
-        <v>4.16620302200317</v>
+        <v>4.16620397567749</v>
       </c>
       <c r="H138" t="n">
         <v>23142</v>
@@ -4400,7 +4400,7 @@
         <v>5</v>
       </c>
       <c r="G139" t="n">
-        <v>4.33979463577271</v>
+        <v>4.33979511260986</v>
       </c>
       <c r="H139" t="n">
         <v>20858</v>
@@ -4429,7 +4429,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G140" t="n">
-        <v>4.51338672637939</v>
+        <v>4.51338624954224</v>
       </c>
       <c r="H140" t="n">
         <v>12739</v>
@@ -4458,7 +4458,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G141" t="n">
-        <v>4.42659044265747</v>
+        <v>4.42659091949463</v>
       </c>
       <c r="H141" t="n">
         <v>9500</v>
@@ -4487,7 +4487,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G142" t="n">
-        <v>4.35715389251709</v>
+        <v>4.35715436935425</v>
       </c>
       <c r="H142" t="n">
         <v>21331</v>
@@ -4516,7 +4516,7 @@
         <v>5</v>
       </c>
       <c r="G143" t="n">
-        <v>4.33979463577271</v>
+        <v>4.33979511260986</v>
       </c>
       <c r="H143" t="n">
         <v>9892</v>
@@ -4545,7 +4545,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G144" t="n">
-        <v>4.42659044265747</v>
+        <v>4.42659091949463</v>
       </c>
       <c r="H144" t="n">
         <v>5800</v>
@@ -4574,7 +4574,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G145" t="n">
-        <v>4.51338672637939</v>
+        <v>4.51338624954224</v>
       </c>
       <c r="H145" t="n">
         <v>10888</v>
@@ -4603,7 +4603,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G146" t="n">
-        <v>4.54810476303101</v>
+        <v>4.54810523986816</v>
       </c>
       <c r="H146" t="n">
         <v>8672</v>
@@ -4632,7 +4632,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G147" t="n">
-        <v>4.70433759689331</v>
+        <v>4.70433807373047</v>
       </c>
       <c r="H147" t="n">
         <v>15539</v>
@@ -4690,7 +4690,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G149" t="n">
-        <v>4.54810476303101</v>
+        <v>4.54810523986816</v>
       </c>
       <c r="H149" t="n">
         <v>20634</v>
@@ -4719,7 +4719,7 @@
         <v>5.13000011444092</v>
       </c>
       <c r="G150" t="n">
-        <v>4.45262956619263</v>
+        <v>4.45263004302979</v>
       </c>
       <c r="H150" t="n">
         <v>6278</v>
@@ -4748,7 +4748,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G151" t="n">
-        <v>4.54810476303101</v>
+        <v>4.54810523986816</v>
       </c>
       <c r="H151" t="n">
         <v>3706</v>
@@ -4777,7 +4777,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G152" t="n">
-        <v>4.51338672637939</v>
+        <v>4.51338624954224</v>
       </c>
       <c r="H152" t="n">
         <v>12525</v>
@@ -4806,7 +4806,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G153" t="n">
-        <v>4.44395017623901</v>
+        <v>4.44394969940186</v>
       </c>
       <c r="H153" t="n">
         <v>2010</v>
@@ -4835,7 +4835,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G154" t="n">
-        <v>4.00129079818726</v>
+        <v>4.00129127502441</v>
       </c>
       <c r="H154" t="n">
         <v>9345</v>
@@ -4864,7 +4864,7 @@
         <v>4.75500011444092</v>
       </c>
       <c r="G155" t="n">
-        <v>4.1271448135376</v>
+        <v>4.12714529037476</v>
       </c>
       <c r="H155" t="n">
         <v>9182</v>
@@ -4922,7 +4922,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G157" t="n">
-        <v>4.23563957214355</v>
+        <v>4.23564052581787</v>
       </c>
       <c r="H157" t="n">
         <v>8393</v>
@@ -4951,7 +4951,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G158" t="n">
-        <v>4.00129079818726</v>
+        <v>4.00129127502441</v>
       </c>
       <c r="H158" t="n">
         <v>25178</v>
@@ -4980,7 +4980,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G159" t="n">
-        <v>4.09676647186279</v>
+        <v>4.09676599502563</v>
       </c>
       <c r="H159" t="n">
         <v>11440</v>
@@ -5038,7 +5038,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G161" t="n">
-        <v>4.0446891784668</v>
+        <v>4.04468822479248</v>
       </c>
       <c r="H161" t="n">
         <v>300</v>
@@ -5067,7 +5067,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G162" t="n">
-        <v>3.99261116981506</v>
+        <v>3.99261164665222</v>
       </c>
       <c r="H162" t="n">
         <v>1599</v>
@@ -5096,7 +5096,7 @@
         <v>4.24499988555908</v>
       </c>
       <c r="G163" t="n">
-        <v>3.68448567390442</v>
+        <v>3.684485912323</v>
       </c>
       <c r="H163" t="n">
         <v>8681</v>
@@ -5125,7 +5125,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G164" t="n">
-        <v>3.17673015594482</v>
+        <v>3.17672991752625</v>
       </c>
       <c r="H164" t="n">
         <v>13665</v>
@@ -5183,7 +5183,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G166" t="n">
-        <v>3.23748707771301</v>
+        <v>3.23748683929443</v>
       </c>
       <c r="H166" t="n">
         <v>4220</v>
@@ -5212,7 +5212,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G167" t="n">
-        <v>2.72539138793945</v>
+        <v>2.72539162635803</v>
       </c>
       <c r="H167" t="n">
         <v>16142</v>
@@ -5270,7 +5270,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G169" t="n">
-        <v>2.98577904701233</v>
+        <v>2.98577928543091</v>
       </c>
       <c r="H169" t="n">
         <v>3440</v>
@@ -5328,7 +5328,7 @@
         <v>3.375</v>
       </c>
       <c r="G171" t="n">
-        <v>2.92936158180237</v>
+        <v>2.92936182022095</v>
       </c>
       <c r="H171" t="n">
         <v>1699</v>
@@ -5386,7 +5386,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G173" t="n">
-        <v>3.09861326217651</v>
+        <v>3.09861373901367</v>
       </c>
       <c r="H173" t="n">
         <v>20403</v>
@@ -5415,7 +5415,7 @@
         <v>3.34500002861023</v>
       </c>
       <c r="G174" t="n">
-        <v>2.90332269668579</v>
+        <v>2.90332293510437</v>
       </c>
       <c r="H174" t="n">
         <v>4051</v>
@@ -5502,7 +5502,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G177" t="n">
-        <v>3.09861326217651</v>
+        <v>3.09861373901367</v>
       </c>
       <c r="H177" t="n">
         <v>2492</v>
@@ -5531,7 +5531,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G178" t="n">
-        <v>3.28956460952759</v>
+        <v>3.28956437110901</v>
       </c>
       <c r="H178" t="n">
         <v>12475</v>
@@ -5560,7 +5560,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G179" t="n">
-        <v>3.21144843101501</v>
+        <v>3.21144819259644</v>
       </c>
       <c r="H179" t="n">
         <v>6765</v>
@@ -5618,7 +5618,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G181" t="n">
-        <v>3.30692386627197</v>
+        <v>3.30692362785339</v>
       </c>
       <c r="H181" t="n">
         <v>2000</v>
@@ -5647,7 +5647,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G182" t="n">
-        <v>3.28956460952759</v>
+        <v>3.28956437110901</v>
       </c>
       <c r="H182" t="n">
         <v>11896</v>
@@ -5705,7 +5705,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G184" t="n">
-        <v>3.21144843101501</v>
+        <v>3.21144819259644</v>
       </c>
       <c r="H184" t="n">
         <v>4102</v>
@@ -5763,7 +5763,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G186" t="n">
-        <v>3.22012805938721</v>
+        <v>3.22012782096863</v>
       </c>
       <c r="H186" t="n">
         <v>4810</v>
@@ -5792,7 +5792,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G187" t="n">
-        <v>3.21144843101501</v>
+        <v>3.21144819259644</v>
       </c>
       <c r="H187" t="n">
         <v>10326</v>
@@ -5821,7 +5821,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G188" t="n">
-        <v>3.2982439994812</v>
+        <v>3.29824423789978</v>
       </c>
       <c r="H188" t="n">
         <v>5632</v>
@@ -5879,7 +5879,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G190" t="n">
-        <v>3.18540954589844</v>
+        <v>3.18540978431702</v>
       </c>
       <c r="H190" t="n">
         <v>13689</v>
@@ -5937,7 +5937,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G192" t="n">
-        <v>3.33296227455139</v>
+        <v>3.33296275138855</v>
       </c>
       <c r="H192" t="n">
         <v>11266</v>
@@ -5966,7 +5966,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G193" t="n">
-        <v>3.2982439994812</v>
+        <v>3.29824423789978</v>
       </c>
       <c r="H193" t="n">
         <v>13631</v>
@@ -5995,7 +5995,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G194" t="n">
-        <v>3.2982439994812</v>
+        <v>3.29824423789978</v>
       </c>
       <c r="H194" t="n">
         <v>5341</v>
@@ -6111,7 +6111,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G198" t="n">
-        <v>3.59335017204285</v>
+        <v>3.59334993362427</v>
       </c>
       <c r="H198" t="n">
         <v>40730</v>
@@ -6198,7 +6198,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G201" t="n">
-        <v>3.33296227455139</v>
+        <v>3.33296275138855</v>
       </c>
       <c r="H201" t="n">
         <v>9437</v>
@@ -6227,7 +6227,7 @@
         <v>3.75</v>
       </c>
       <c r="G202" t="n">
-        <v>3.2548463344574</v>
+        <v>3.25484609603882</v>
       </c>
       <c r="H202" t="n">
         <v>25406</v>
@@ -6256,7 +6256,7 @@
         <v>3.75</v>
       </c>
       <c r="G203" t="n">
-        <v>3.2548463344574</v>
+        <v>3.25484609603882</v>
       </c>
       <c r="H203" t="n">
         <v>5500</v>
@@ -6314,7 +6314,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G205" t="n">
-        <v>3.2982439994812</v>
+        <v>3.29824423789978</v>
       </c>
       <c r="H205" t="n">
         <v>4357</v>
@@ -6401,7 +6401,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G208" t="n">
-        <v>3.30692386627197</v>
+        <v>3.30692362785339</v>
       </c>
       <c r="H208" t="n">
         <v>11449</v>
@@ -6488,7 +6488,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G211" t="n">
-        <v>3.2982439994812</v>
+        <v>3.29824423789978</v>
       </c>
       <c r="H211" t="n">
         <v>8606</v>
@@ -6662,7 +6662,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G217" t="n">
-        <v>3.2982439994812</v>
+        <v>3.29824423789978</v>
       </c>
       <c r="H217" t="n">
         <v>16383</v>
@@ -6720,7 +6720,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G219" t="n">
-        <v>3.2982439994812</v>
+        <v>3.29824423789978</v>
       </c>
       <c r="H219" t="n">
         <v>6884</v>
@@ -6778,7 +6778,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G221" t="n">
-        <v>3.28956460952759</v>
+        <v>3.28956437110901</v>
       </c>
       <c r="H221" t="n">
         <v>8062</v>
@@ -6807,7 +6807,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G222" t="n">
-        <v>3.2982439994812</v>
+        <v>3.29824423789978</v>
       </c>
       <c r="H222" t="n">
         <v>4259</v>
@@ -6865,7 +6865,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G224" t="n">
-        <v>3.38504028320312</v>
+        <v>3.3850405216217</v>
       </c>
       <c r="H224" t="n">
         <v>2943</v>
@@ -6952,7 +6952,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G227" t="n">
-        <v>3.2982439994812</v>
+        <v>3.29824423789978</v>
       </c>
       <c r="H227" t="n">
         <v>6610</v>
@@ -7184,7 +7184,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G235" t="n">
-        <v>3.32428288459778</v>
+        <v>3.3242826461792</v>
       </c>
       <c r="H235" t="n">
         <v>800</v>
@@ -7213,7 +7213,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G236" t="n">
-        <v>3.32428288459778</v>
+        <v>3.3242826461792</v>
       </c>
       <c r="H236" t="n">
         <v>0</v>
@@ -7242,7 +7242,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G237" t="n">
-        <v>3.28956460952759</v>
+        <v>3.28956437110901</v>
       </c>
       <c r="H237" t="n">
         <v>451</v>
@@ -7271,7 +7271,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G238" t="n">
-        <v>3.23748707771301</v>
+        <v>3.23748683929443</v>
       </c>
       <c r="H238" t="n">
         <v>386</v>
@@ -7300,7 +7300,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G239" t="n">
-        <v>3.23748707771301</v>
+        <v>3.23748683929443</v>
       </c>
       <c r="H239" t="n">
         <v>0</v>
@@ -7329,7 +7329,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G240" t="n">
-        <v>3.2982439994812</v>
+        <v>3.29824423789978</v>
       </c>
       <c r="H240" t="n">
         <v>2500</v>
@@ -7387,7 +7387,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G242" t="n">
-        <v>3.28956460952759</v>
+        <v>3.28956437110901</v>
       </c>
       <c r="H242" t="n">
         <v>1</v>
@@ -7416,7 +7416,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G243" t="n">
-        <v>3.28956460952759</v>
+        <v>3.28956437110901</v>
       </c>
       <c r="H243" t="n">
         <v>0</v>
@@ -7503,7 +7503,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G246" t="n">
-        <v>3.2982439994812</v>
+        <v>3.29824423789978</v>
       </c>
       <c r="H246" t="n">
         <v>2471</v>
@@ -7648,7 +7648,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G251" t="n">
-        <v>3.18540954589844</v>
+        <v>3.18540978431702</v>
       </c>
       <c r="H251" t="n">
         <v>6820</v>
@@ -7677,7 +7677,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G252" t="n">
-        <v>3.21144843101501</v>
+        <v>3.21144819259644</v>
       </c>
       <c r="H252" t="n">
         <v>57</v>
@@ -7706,7 +7706,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G253" t="n">
-        <v>3.21144843101501</v>
+        <v>3.21144819259644</v>
       </c>
       <c r="H253" t="n">
         <v>0</v>
@@ -7735,7 +7735,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G254" t="n">
-        <v>3.28956460952759</v>
+        <v>3.28956437110901</v>
       </c>
       <c r="H254" t="n">
         <v>2105</v>
@@ -7764,7 +7764,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G255" t="n">
-        <v>3.18540954589844</v>
+        <v>3.18540978431702</v>
       </c>
       <c r="H255" t="n">
         <v>1005</v>
@@ -7822,7 +7822,7 @@
         <v>3.75</v>
       </c>
       <c r="G257" t="n">
-        <v>3.2548463344574</v>
+        <v>3.25484609603882</v>
       </c>
       <c r="H257" t="n">
         <v>3790</v>
@@ -7851,7 +7851,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G258" t="n">
-        <v>3.36768102645874</v>
+        <v>3.36768126487732</v>
       </c>
       <c r="H258" t="n">
         <v>1100</v>
@@ -8054,7 +8054,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G265" t="n">
-        <v>3.07257509231567</v>
+        <v>3.07257485389709</v>
       </c>
       <c r="H265" t="n">
         <v>1250</v>
@@ -8286,7 +8286,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G273" t="n">
-        <v>3.0204975605011</v>
+        <v>3.02049732208252</v>
       </c>
       <c r="H273" t="n">
         <v>5743</v>
@@ -8344,7 +8344,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G275" t="n">
-        <v>2.96842002868652</v>
+        <v>2.96841979026794</v>
       </c>
       <c r="H275" t="n">
         <v>11722</v>
@@ -8373,7 +8373,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G276" t="n">
-        <v>3.02917695045471</v>
+        <v>3.02917718887329</v>
       </c>
       <c r="H276" t="n">
         <v>4096</v>
@@ -8402,7 +8402,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G277" t="n">
-        <v>3.0204975605011</v>
+        <v>3.02049732208252</v>
       </c>
       <c r="H277" t="n">
         <v>10072</v>
@@ -8431,7 +8431,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G278" t="n">
-        <v>3.07257509231567</v>
+        <v>3.07257485389709</v>
       </c>
       <c r="H278" t="n">
         <v>4119</v>
@@ -8460,7 +8460,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G279" t="n">
-        <v>2.99445867538452</v>
+        <v>2.99445843696594</v>
       </c>
       <c r="H279" t="n">
         <v>4694</v>
@@ -8489,7 +8489,7 @@
         <v>3.5</v>
       </c>
       <c r="G280" t="n">
-        <v>3.03785634040833</v>
+        <v>3.0378565788269</v>
       </c>
       <c r="H280" t="n">
         <v>105</v>
@@ -8518,7 +8518,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G281" t="n">
-        <v>3.0638952255249</v>
+        <v>3.06389546394348</v>
       </c>
       <c r="H281" t="n">
         <v>1883</v>
@@ -8547,7 +8547,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G282" t="n">
-        <v>3.0638952255249</v>
+        <v>3.06389546394348</v>
       </c>
       <c r="H282" t="n">
         <v>0</v>
@@ -8576,7 +8576,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G283" t="n">
-        <v>3.0638952255249</v>
+        <v>3.06389546394348</v>
       </c>
       <c r="H283" t="n">
         <v>1100</v>
@@ -8663,7 +8663,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G286" t="n">
-        <v>2.98577904701233</v>
+        <v>2.98577928543091</v>
       </c>
       <c r="H286" t="n">
         <v>6281</v>
@@ -8692,7 +8692,7 @@
         <v>3.5</v>
       </c>
       <c r="G287" t="n">
-        <v>3.03785634040833</v>
+        <v>3.0378565788269</v>
       </c>
       <c r="H287" t="n">
         <v>3634</v>
@@ -8721,7 +8721,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G288" t="n">
-        <v>2.99445867538452</v>
+        <v>2.99445843696594</v>
       </c>
       <c r="H288" t="n">
         <v>1117</v>
@@ -8808,7 +8808,7 @@
         <v>3.5</v>
       </c>
       <c r="G291" t="n">
-        <v>3.03785634040833</v>
+        <v>3.0378565788269</v>
       </c>
       <c r="H291" t="n">
         <v>10</v>
@@ -8837,7 +8837,7 @@
         <v>3.5</v>
       </c>
       <c r="G292" t="n">
-        <v>3.03785634040833</v>
+        <v>3.0378565788269</v>
       </c>
       <c r="H292" t="n">
         <v>0</v>
@@ -8866,7 +8866,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G293" t="n">
-        <v>2.98577904701233</v>
+        <v>2.98577928543091</v>
       </c>
       <c r="H293" t="n">
         <v>2137</v>
@@ -8924,7 +8924,7 @@
         <v>3.5</v>
       </c>
       <c r="G295" t="n">
-        <v>3.03785634040833</v>
+        <v>3.0378565788269</v>
       </c>
       <c r="H295" t="n">
         <v>700</v>
@@ -9011,7 +9011,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G298" t="n">
-        <v>2.99445867538452</v>
+        <v>2.99445843696594</v>
       </c>
       <c r="H298" t="n">
         <v>6051</v>
@@ -9040,7 +9040,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G299" t="n">
-        <v>2.86426448822021</v>
+        <v>2.86426496505737</v>
       </c>
       <c r="H299" t="n">
         <v>18061</v>
@@ -9069,7 +9069,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G300" t="n">
-        <v>2.86426448822021</v>
+        <v>2.86426496505737</v>
       </c>
       <c r="H300" t="n">
         <v>0</v>
@@ -9098,7 +9098,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G301" t="n">
-        <v>2.86426448822021</v>
+        <v>2.86426496505737</v>
       </c>
       <c r="H301" t="n">
         <v>14192</v>
@@ -9156,7 +9156,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G303" t="n">
-        <v>2.88162398338318</v>
+        <v>2.8816237449646</v>
       </c>
       <c r="H303" t="n">
         <v>7318</v>
@@ -9214,7 +9214,7 @@
         <v>3.5</v>
       </c>
       <c r="G305" t="n">
-        <v>3.03785634040833</v>
+        <v>3.0378565788269</v>
       </c>
       <c r="H305" t="n">
         <v>28717</v>
@@ -9388,7 +9388,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G311" t="n">
-        <v>3.22012805938721</v>
+        <v>3.22012782096863</v>
       </c>
       <c r="H311" t="n">
         <v>688</v>
@@ -9417,7 +9417,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G312" t="n">
-        <v>3.22012805938721</v>
+        <v>3.22012782096863</v>
       </c>
       <c r="H312" t="n">
         <v>0</v>
@@ -9446,7 +9446,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G313" t="n">
-        <v>3.21144843101501</v>
+        <v>3.21144819259644</v>
       </c>
       <c r="H313" t="n">
         <v>2665</v>
@@ -9504,7 +9504,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G315" t="n">
-        <v>3.21144843101501</v>
+        <v>3.21144819259644</v>
       </c>
       <c r="H315" t="n">
         <v>456</v>
@@ -9533,7 +9533,7 @@
         <v>3.75</v>
       </c>
       <c r="G316" t="n">
-        <v>3.2548463344574</v>
+        <v>3.25484609603882</v>
       </c>
       <c r="H316" t="n">
         <v>2505</v>
@@ -9562,7 +9562,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G317" t="n">
-        <v>3.21144843101501</v>
+        <v>3.21144819259644</v>
       </c>
       <c r="H317" t="n">
         <v>1600</v>
@@ -9591,7 +9591,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G318" t="n">
-        <v>3.17673015594482</v>
+        <v>3.17672991752625</v>
       </c>
       <c r="H318" t="n">
         <v>6400</v>
@@ -9678,7 +9678,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G321" t="n">
-        <v>3.21144843101501</v>
+        <v>3.21144819259644</v>
       </c>
       <c r="H321" t="n">
         <v>2251</v>
@@ -9736,7 +9736,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G323" t="n">
-        <v>3.21144843101501</v>
+        <v>3.21144819259644</v>
       </c>
       <c r="H323" t="n">
         <v>220</v>
@@ -9765,7 +9765,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G324" t="n">
-        <v>3.21144843101501</v>
+        <v>3.21144819259644</v>
       </c>
       <c r="H324" t="n">
         <v>4700</v>
@@ -9794,7 +9794,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G325" t="n">
-        <v>3.21144843101501</v>
+        <v>3.21144819259644</v>
       </c>
       <c r="H325" t="n">
         <v>650</v>
@@ -9852,7 +9852,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G327" t="n">
-        <v>3.14201140403748</v>
+        <v>3.14201164245605</v>
       </c>
       <c r="H327" t="n">
         <v>1954</v>
@@ -9881,7 +9881,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G328" t="n">
-        <v>3.21144843101501</v>
+        <v>3.21144819259644</v>
       </c>
       <c r="H328" t="n">
         <v>2264</v>
@@ -9997,7 +9997,7 @@
         <v>3.5</v>
       </c>
       <c r="G332" t="n">
-        <v>3.03785634040833</v>
+        <v>3.0378565788269</v>
       </c>
       <c r="H332" t="n">
         <v>2958</v>
@@ -10026,7 +10026,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G333" t="n">
-        <v>3.02917695045471</v>
+        <v>3.02917718887329</v>
       </c>
       <c r="H333" t="n">
         <v>614</v>
@@ -10055,7 +10055,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G334" t="n">
-        <v>3.15069127082825</v>
+        <v>3.15069150924683</v>
       </c>
       <c r="H334" t="n">
         <v>1330</v>
@@ -10287,7 +10287,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G342" t="n">
-        <v>3.21144843101501</v>
+        <v>3.21144819259644</v>
       </c>
       <c r="H342" t="n">
         <v>3660</v>
@@ -10316,7 +10316,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G343" t="n">
-        <v>3.15069127082825</v>
+        <v>3.15069150924683</v>
       </c>
       <c r="H343" t="n">
         <v>3072</v>
@@ -10345,7 +10345,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G344" t="n">
-        <v>3.15069127082825</v>
+        <v>3.15069150924683</v>
       </c>
       <c r="H344" t="n">
         <v>8220</v>
@@ -10374,7 +10374,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G345" t="n">
-        <v>3.22012805938721</v>
+        <v>3.22012782096863</v>
       </c>
       <c r="H345" t="n">
         <v>3873</v>
@@ -10403,7 +10403,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G346" t="n">
-        <v>3.21144843101501</v>
+        <v>3.21144819259644</v>
       </c>
       <c r="H346" t="n">
         <v>5550</v>
@@ -10519,7 +10519,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G350" t="n">
-        <v>3.36768102645874</v>
+        <v>3.36768126487732</v>
       </c>
       <c r="H350" t="n">
         <v>10</v>
@@ -10606,7 +10606,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G353" t="n">
-        <v>3.28956460952759</v>
+        <v>3.28956437110901</v>
       </c>
       <c r="H353" t="n">
         <v>300</v>
@@ -10664,7 +10664,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G355" t="n">
-        <v>3.30692386627197</v>
+        <v>3.30692362785339</v>
       </c>
       <c r="H355" t="n">
         <v>20</v>
@@ -10867,7 +10867,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G362" t="n">
-        <v>3.52457284927368</v>
+        <v>3.52457308769226</v>
       </c>
       <c r="H362" t="n">
         <v>1633</v>
@@ -10896,7 +10896,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G363" t="n">
-        <v>3.53336215019226</v>
+        <v>3.53336191177368</v>
       </c>
       <c r="H363" t="n">
         <v>425644</v>
@@ -10925,7 +10925,7 @@
         <v>4</v>
       </c>
       <c r="G364" t="n">
-        <v>3.51578330993652</v>
+        <v>3.51578307151794</v>
       </c>
       <c r="H364" t="n">
         <v>16056</v>
@@ -10954,7 +10954,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G365" t="n">
-        <v>3.55973052978516</v>
+        <v>3.55973076820374</v>
       </c>
       <c r="H365" t="n">
         <v>10835</v>
@@ -11012,7 +11012,7 @@
         <v>4</v>
       </c>
       <c r="G367" t="n">
-        <v>3.51578330993652</v>
+        <v>3.51578307151794</v>
       </c>
       <c r="H367" t="n">
         <v>8651</v>
@@ -11041,7 +11041,7 @@
         <v>4</v>
       </c>
       <c r="G368" t="n">
-        <v>3.51578330993652</v>
+        <v>3.51578307151794</v>
       </c>
       <c r="H368" t="n">
         <v>6801</v>
@@ -11070,7 +11070,7 @@
         <v>4</v>
       </c>
       <c r="G369" t="n">
-        <v>3.51578330993652</v>
+        <v>3.51578307151794</v>
       </c>
       <c r="H369" t="n">
         <v>0</v>
@@ -11099,7 +11099,7 @@
         <v>4</v>
       </c>
       <c r="G370" t="n">
-        <v>3.51578330993652</v>
+        <v>3.51578307151794</v>
       </c>
       <c r="H370" t="n">
         <v>0</v>
@@ -11128,7 +11128,7 @@
         <v>4</v>
       </c>
       <c r="G371" t="n">
-        <v>3.51578330993652</v>
+        <v>3.51578307151794</v>
       </c>
       <c r="H371" t="n">
         <v>0</v>
@@ -11186,7 +11186,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G373" t="n">
-        <v>3.77946710586548</v>
+        <v>3.77946734428406</v>
       </c>
       <c r="H373" t="n">
         <v>36941</v>
@@ -11215,7 +11215,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G374" t="n">
-        <v>3.85857224464417</v>
+        <v>3.85857200622559</v>
       </c>
       <c r="H374" t="n">
         <v>3601</v>
@@ -11244,7 +11244,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G375" t="n">
-        <v>3.80583548545837</v>
+        <v>3.80583524703979</v>
       </c>
       <c r="H375" t="n">
         <v>1180</v>
@@ -11273,7 +11273,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G376" t="n">
-        <v>3.82341384887695</v>
+        <v>3.82341408729553</v>
       </c>
       <c r="H376" t="n">
         <v>4874</v>
@@ -11302,7 +11302,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G377" t="n">
-        <v>3.70915102958679</v>
+        <v>3.70915126800537</v>
       </c>
       <c r="H377" t="n">
         <v>1400</v>
@@ -11331,7 +11331,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G378" t="n">
-        <v>3.84978246688843</v>
+        <v>3.84978270530701</v>
       </c>
       <c r="H378" t="n">
         <v>9179</v>
@@ -11389,7 +11389,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G380" t="n">
-        <v>3.99041366577148</v>
+        <v>3.99041390419006</v>
       </c>
       <c r="H380" t="n">
         <v>6050</v>
@@ -11447,7 +11447,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G382" t="n">
-        <v>3.92888760566711</v>
+        <v>3.92888784408569</v>
       </c>
       <c r="H382" t="n">
         <v>12048</v>
@@ -11505,7 +11505,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G384" t="n">
-        <v>3.77946710586548</v>
+        <v>3.77946734428406</v>
       </c>
       <c r="H384" t="n">
         <v>4161</v>
@@ -11534,7 +11534,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G385" t="n">
-        <v>3.77946710586548</v>
+        <v>3.77946734428406</v>
       </c>
       <c r="H385" t="n">
         <v>2380</v>
@@ -11563,7 +11563,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G386" t="n">
-        <v>3.64762496948242</v>
+        <v>3.647625207901</v>
       </c>
       <c r="H386" t="n">
         <v>7282</v>
@@ -11592,7 +11592,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G387" t="n">
-        <v>3.42788863182068</v>
+        <v>3.42788910865784</v>
       </c>
       <c r="H387" t="n">
         <v>24073</v>
@@ -11650,7 +11650,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G389" t="n">
-        <v>3.58609867095947</v>
+        <v>3.58609890937805</v>
       </c>
       <c r="H389" t="n">
         <v>19347</v>
@@ -11679,7 +11679,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G390" t="n">
-        <v>3.69157195091248</v>
+        <v>3.69157218933105</v>
       </c>
       <c r="H390" t="n">
         <v>9963</v>
@@ -11708,7 +11708,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G391" t="n">
-        <v>3.52457284927368</v>
+        <v>3.52457308769226</v>
       </c>
       <c r="H391" t="n">
         <v>14867</v>
@@ -11737,7 +11737,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G392" t="n">
-        <v>3.62125682830811</v>
+        <v>3.62125658988953</v>
       </c>
       <c r="H392" t="n">
         <v>15062</v>
@@ -11824,7 +11824,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G395" t="n">
-        <v>3.74430918693542</v>
+        <v>3.74430966377258</v>
       </c>
       <c r="H395" t="n">
         <v>15241</v>
@@ -11853,7 +11853,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G396" t="n">
-        <v>3.77946710586548</v>
+        <v>3.77946734428406</v>
       </c>
       <c r="H396" t="n">
         <v>6483</v>
@@ -11882,7 +11882,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G397" t="n">
-        <v>3.82341384887695</v>
+        <v>3.82341408729553</v>
       </c>
       <c r="H397" t="n">
         <v>1515</v>
@@ -11911,7 +11911,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G398" t="n">
-        <v>3.77946710586548</v>
+        <v>3.77946734428406</v>
       </c>
       <c r="H398" t="n">
         <v>83</v>
@@ -11940,7 +11940,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G399" t="n">
-        <v>3.70915102958679</v>
+        <v>3.70915126800537</v>
       </c>
       <c r="H399" t="n">
         <v>1746</v>
@@ -11969,7 +11969,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G400" t="n">
-        <v>3.62125682830811</v>
+        <v>3.62125658988953</v>
       </c>
       <c r="H400" t="n">
         <v>1948</v>
@@ -11998,7 +11998,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G401" t="n">
-        <v>3.58609867095947</v>
+        <v>3.58609890937805</v>
       </c>
       <c r="H401" t="n">
         <v>2243</v>
@@ -12056,7 +12056,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G403" t="n">
-        <v>3.68278336524963</v>
+        <v>3.68278288841248</v>
       </c>
       <c r="H403" t="n">
         <v>5461</v>
@@ -12114,7 +12114,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G405" t="n">
-        <v>3.84978246688843</v>
+        <v>3.84978270530701</v>
       </c>
       <c r="H405" t="n">
         <v>10519</v>
@@ -12143,7 +12143,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G406" t="n">
-        <v>3.84099292755127</v>
+        <v>3.84099316596985</v>
       </c>
       <c r="H406" t="n">
         <v>7000</v>
@@ -12172,7 +12172,7 @@
         <v>4.25</v>
       </c>
       <c r="G407" t="n">
-        <v>3.73551964759827</v>
+        <v>3.73551940917969</v>
       </c>
       <c r="H407" t="n">
         <v>7140</v>
@@ -12230,7 +12230,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G409" t="n">
-        <v>4.04315042495728</v>
+        <v>4.04315090179443</v>
       </c>
       <c r="H409" t="n">
         <v>11444</v>
@@ -12259,7 +12259,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G410" t="n">
-        <v>3.99920392036438</v>
+        <v>3.99920415878296</v>
       </c>
       <c r="H410" t="n">
         <v>13066</v>
@@ -12288,7 +12288,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G411" t="n">
-        <v>3.99920392036438</v>
+        <v>3.99920415878296</v>
       </c>
       <c r="H411" t="n">
         <v>3045</v>
@@ -12317,7 +12317,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G412" t="n">
-        <v>3.97283530235291</v>
+        <v>3.97283506393433</v>
       </c>
       <c r="H412" t="n">
         <v>3835</v>
@@ -12346,7 +12346,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G413" t="n">
-        <v>4.06072998046875</v>
+        <v>4.06072950363159</v>
       </c>
       <c r="H413" t="n">
         <v>1119</v>
@@ -12375,7 +12375,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G414" t="n">
-        <v>4.04315042495728</v>
+        <v>4.04315090179443</v>
       </c>
       <c r="H414" t="n">
         <v>4777</v>
@@ -12404,7 +12404,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G415" t="n">
-        <v>4.04315042495728</v>
+        <v>4.04315090179443</v>
       </c>
       <c r="H415" t="n">
         <v>0</v>
@@ -12433,7 +12433,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G416" t="n">
-        <v>3.99920392036438</v>
+        <v>3.99920415878296</v>
       </c>
       <c r="H416" t="n">
         <v>20150</v>
@@ -12462,7 +12462,7 @@
         <v>4.59000015258789</v>
       </c>
       <c r="G417" t="n">
-        <v>4.03436183929443</v>
+        <v>4.03436136245728</v>
       </c>
       <c r="H417" t="n">
         <v>6334</v>
@@ -12491,7 +12491,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G418" t="n">
-        <v>4.08709859848022</v>
+        <v>4.08709812164307</v>
       </c>
       <c r="H418" t="n">
         <v>6771</v>
@@ -12549,7 +12549,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G420" t="n">
-        <v>4.30683469772339</v>
+        <v>4.30683422088623</v>
       </c>
       <c r="H420" t="n">
         <v>32975</v>
@@ -12578,7 +12578,7 @@
         <v>5</v>
       </c>
       <c r="G421" t="n">
-        <v>4.3947286605835</v>
+        <v>4.39472913742065</v>
       </c>
       <c r="H421" t="n">
         <v>12311</v>
@@ -12607,7 +12607,7 @@
         <v>5</v>
       </c>
       <c r="G422" t="n">
-        <v>4.3947286605835</v>
+        <v>4.39472913742065</v>
       </c>
       <c r="H422" t="n">
         <v>7994</v>
@@ -12665,7 +12665,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G424" t="n">
-        <v>4.30683469772339</v>
+        <v>4.30683422088623</v>
       </c>
       <c r="H424" t="n">
         <v>1866</v>
@@ -12723,7 +12723,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G426" t="n">
-        <v>4.25409746170044</v>
+        <v>4.2540979385376</v>
       </c>
       <c r="H426" t="n">
         <v>2079</v>
@@ -12752,7 +12752,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G427" t="n">
-        <v>4.34199237823486</v>
+        <v>4.34199190139771</v>
       </c>
       <c r="H427" t="n">
         <v>6045</v>
@@ -12810,7 +12810,7 @@
         <v>4.75</v>
       </c>
       <c r="G429" t="n">
-        <v>4.17499256134033</v>
+        <v>4.17499303817749</v>
       </c>
       <c r="H429" t="n">
         <v>10</v>
@@ -12839,7 +12839,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G430" t="n">
-        <v>4.28925561904907</v>
+        <v>4.28925609588623</v>
       </c>
       <c r="H430" t="n">
         <v>7986</v>
@@ -12868,7 +12868,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G431" t="n">
-        <v>4.28925561904907</v>
+        <v>4.28925609588623</v>
       </c>
       <c r="H431" t="n">
         <v>2210</v>
@@ -12926,7 +12926,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G433" t="n">
-        <v>4.32441329956055</v>
+        <v>4.32441377639771</v>
       </c>
       <c r="H433" t="n">
         <v>1529</v>
@@ -12955,7 +12955,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G434" t="n">
-        <v>4.22772932052612</v>
+        <v>4.22772884368896</v>
       </c>
       <c r="H434" t="n">
         <v>5368</v>
@@ -12984,7 +12984,7 @@
         <v>4.75</v>
       </c>
       <c r="G435" t="n">
-        <v>4.17499256134033</v>
+        <v>4.17499303817749</v>
       </c>
       <c r="H435" t="n">
         <v>1500</v>
@@ -13071,7 +13071,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G438" t="n">
-        <v>4.25409746170044</v>
+        <v>4.2540979385376</v>
       </c>
       <c r="H438" t="n">
         <v>3588</v>
@@ -13158,7 +13158,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G441" t="n">
-        <v>4.30683469772339</v>
+        <v>4.30683422088623</v>
       </c>
       <c r="H441" t="n">
         <v>14413</v>
@@ -13187,7 +13187,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G442" t="n">
-        <v>4.30683469772339</v>
+        <v>4.30683422088623</v>
       </c>
       <c r="H442" t="n">
         <v>5600</v>
@@ -13216,7 +13216,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G443" t="n">
-        <v>4.35078191757202</v>
+        <v>4.35078144073486</v>
       </c>
       <c r="H443" t="n">
         <v>180</v>
@@ -13245,7 +13245,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G444" t="n">
-        <v>4.34199237823486</v>
+        <v>4.34199190139771</v>
       </c>
       <c r="H444" t="n">
         <v>20</v>
@@ -13303,7 +13303,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G446" t="n">
-        <v>4.34199237823486</v>
+        <v>4.34199190139771</v>
       </c>
       <c r="H446" t="n">
         <v>1000</v>
@@ -13390,7 +13390,7 @@
         <v>5</v>
       </c>
       <c r="G449" t="n">
-        <v>4.3947286605835</v>
+        <v>4.39472913742065</v>
       </c>
       <c r="H449" t="n">
         <v>900</v>
@@ -13419,7 +13419,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G450" t="n">
-        <v>4.21893978118896</v>
+        <v>4.21894025802612</v>
       </c>
       <c r="H450" t="n">
         <v>4300</v>
@@ -13448,7 +13448,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G451" t="n">
-        <v>4.30683469772339</v>
+        <v>4.30683422088623</v>
       </c>
       <c r="H451" t="n">
         <v>600</v>
@@ -13477,7 +13477,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G452" t="n">
-        <v>4.21893978118896</v>
+        <v>4.21894025802612</v>
       </c>
       <c r="H452" t="n">
         <v>1223</v>
@@ -13535,7 +13535,7 @@
         <v>4.75</v>
       </c>
       <c r="G454" t="n">
-        <v>4.17499256134033</v>
+        <v>4.17499303817749</v>
       </c>
       <c r="H454" t="n">
         <v>220</v>
@@ -13593,7 +13593,7 @@
         <v>4.75</v>
       </c>
       <c r="G456" t="n">
-        <v>4.17499256134033</v>
+        <v>4.17499303817749</v>
       </c>
       <c r="H456" t="n">
         <v>7</v>
@@ -13622,7 +13622,7 @@
         <v>4.75</v>
       </c>
       <c r="G457" t="n">
-        <v>4.17499256134033</v>
+        <v>4.17499303817749</v>
       </c>
       <c r="H457" t="n">
         <v>0</v>
@@ -13651,7 +13651,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G458" t="n">
-        <v>4.05194044113159</v>
+        <v>4.05193996429443</v>
       </c>
       <c r="H458" t="n">
         <v>1015</v>
@@ -13680,7 +13680,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G459" t="n">
-        <v>4.02557229995728</v>
+        <v>4.02557182312012</v>
       </c>
       <c r="H459" t="n">
         <v>4000</v>
@@ -13709,7 +13709,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G460" t="n">
-        <v>4.02557229995728</v>
+        <v>4.02557182312012</v>
       </c>
       <c r="H460" t="n">
         <v>1607</v>
@@ -13738,7 +13738,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G461" t="n">
-        <v>4.02557229995728</v>
+        <v>4.02557182312012</v>
       </c>
       <c r="H461" t="n">
         <v>1400</v>
@@ -13767,7 +13767,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G462" t="n">
-        <v>4.08709859848022</v>
+        <v>4.08709812164307</v>
       </c>
       <c r="H462" t="n">
         <v>155</v>
@@ -13883,7 +13883,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G466" t="n">
-        <v>4.28925561904907</v>
+        <v>4.28925609588623</v>
       </c>
       <c r="H466" t="n">
         <v>1395</v>
@@ -13912,7 +13912,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G467" t="n">
-        <v>4.35078191757202</v>
+        <v>4.35078144073486</v>
       </c>
       <c r="H467" t="n">
         <v>12111</v>
@@ -13941,7 +13941,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G468" t="n">
-        <v>4.50020265579224</v>
+        <v>4.50020217895508</v>
       </c>
       <c r="H468" t="n">
         <v>25612</v>
@@ -14115,7 +14115,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G474" t="n">
-        <v>4.57807397842407</v>
+        <v>4.57807350158691</v>
       </c>
       <c r="H474" t="n">
         <v>5287</v>
@@ -14144,7 +14144,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G475" t="n">
-        <v>4.77250957489014</v>
+        <v>4.77250909805298</v>
       </c>
       <c r="H475" t="n">
         <v>3681</v>
@@ -14347,7 +14347,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G482" t="n">
-        <v>4.54272174835205</v>
+        <v>4.54272222518921</v>
       </c>
       <c r="H482" t="n">
         <v>600</v>
@@ -14463,7 +14463,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G486" t="n">
-        <v>4.37480020523071</v>
+        <v>4.37479972839355</v>
       </c>
       <c r="H486" t="n">
         <v>1753</v>
@@ -14666,7 +14666,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G493" t="n">
-        <v>4.26874446868896</v>
+        <v>4.26874494552612</v>
       </c>
       <c r="H493" t="n">
         <v>2410</v>
@@ -14695,7 +14695,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G494" t="n">
-        <v>4.22455453872681</v>
+        <v>4.22455501556396</v>
       </c>
       <c r="H494" t="n">
         <v>1787</v>
@@ -14898,7 +14898,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G501" t="n">
-        <v>4.02128124237061</v>
+        <v>4.02128171920776</v>
       </c>
       <c r="H501" t="n">
         <v>9940</v>
@@ -14927,7 +14927,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G502" t="n">
-        <v>4.0831470489502</v>
+        <v>4.08314657211304</v>
       </c>
       <c r="H502" t="n">
         <v>25</v>
@@ -15072,7 +15072,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G507" t="n">
-        <v>4.22455453872681</v>
+        <v>4.22455501556396</v>
       </c>
       <c r="H507" t="n">
         <v>450</v>
@@ -15478,7 +15478,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G521" t="n">
-        <v>4.52504587173462</v>
+        <v>4.52504539489746</v>
       </c>
       <c r="H521" t="n">
         <v>25920</v>
@@ -15623,7 +15623,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G526" t="n">
-        <v>4.57807397842407</v>
+        <v>4.57807350158691</v>
       </c>
       <c r="H526" t="n">
         <v>2094</v>
@@ -15652,7 +15652,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G527" t="n">
-        <v>4.57807397842407</v>
+        <v>4.57807350158691</v>
       </c>
       <c r="H527" t="n">
         <v>50</v>
@@ -15710,7 +15710,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G529" t="n">
-        <v>4.45434236526489</v>
+        <v>4.45434188842773</v>
       </c>
       <c r="H529" t="n">
         <v>1100</v>
@@ -15739,7 +15739,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G530" t="n">
-        <v>4.52504587173462</v>
+        <v>4.52504539489746</v>
       </c>
       <c r="H530" t="n">
         <v>700</v>
@@ -15768,7 +15768,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G531" t="n">
-        <v>4.52504587173462</v>
+        <v>4.52504539489746</v>
       </c>
       <c r="H531" t="n">
         <v>0</v>
@@ -15855,7 +15855,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G534" t="n">
-        <v>4.26874446868896</v>
+        <v>4.26874494552612</v>
       </c>
       <c r="H534" t="n">
         <v>1220</v>
@@ -15884,7 +15884,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G535" t="n">
-        <v>4.28641986846924</v>
+        <v>4.2864203453064</v>
       </c>
       <c r="H535" t="n">
         <v>1300</v>
@@ -15913,7 +15913,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G536" t="n">
-        <v>4.28641986846924</v>
+        <v>4.2864203453064</v>
       </c>
       <c r="H536" t="n">
         <v>20</v>
@@ -15942,7 +15942,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G537" t="n">
-        <v>4.28641986846924</v>
+        <v>4.2864203453064</v>
       </c>
       <c r="H537" t="n">
         <v>4125</v>
@@ -15971,7 +15971,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G538" t="n">
-        <v>4.28641986846924</v>
+        <v>4.2864203453064</v>
       </c>
       <c r="H538" t="n">
         <v>3365</v>
@@ -16000,7 +16000,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G539" t="n">
-        <v>4.41015195846558</v>
+        <v>4.41015148162842</v>
       </c>
       <c r="H539" t="n">
         <v>870</v>
@@ -16116,7 +16116,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G543" t="n">
-        <v>4.38363838195801</v>
+        <v>4.38363885879517</v>
       </c>
       <c r="H543" t="n">
         <v>902</v>
@@ -16145,7 +16145,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G544" t="n">
-        <v>4.36596250534058</v>
+        <v>4.36596202850342</v>
       </c>
       <c r="H544" t="n">
         <v>2872</v>
@@ -16174,7 +16174,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G545" t="n">
-        <v>4.36596250534058</v>
+        <v>4.36596202850342</v>
       </c>
       <c r="H545" t="n">
         <v>0</v>
@@ -16203,7 +16203,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G546" t="n">
-        <v>4.33944797515869</v>
+        <v>4.33944845199585</v>
       </c>
       <c r="H546" t="n">
         <v>1600</v>
@@ -16232,7 +16232,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G547" t="n">
-        <v>4.33944797515869</v>
+        <v>4.33944845199585</v>
       </c>
       <c r="H547" t="n">
         <v>0</v>
@@ -16261,7 +16261,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G548" t="n">
-        <v>4.33944797515869</v>
+        <v>4.33944845199585</v>
       </c>
       <c r="H548" t="n">
         <v>0</v>
@@ -16406,7 +16406,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G553" t="n">
-        <v>4.31293439865112</v>
+        <v>4.31293487548828</v>
       </c>
       <c r="H553" t="n">
         <v>11439</v>
@@ -16638,7 +16638,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G561" t="n">
-        <v>4.15385103225708</v>
+        <v>4.15385055541992</v>
       </c>
       <c r="H561" t="n">
         <v>11912</v>
@@ -16696,7 +16696,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G563" t="n">
-        <v>4.29525852203369</v>
+        <v>4.29525804519653</v>
       </c>
       <c r="H563" t="n">
         <v>16695</v>
@@ -16870,7 +16870,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G569" t="n">
-        <v>4.57807397842407</v>
+        <v>4.57807350158691</v>
       </c>
       <c r="H569" t="n">
         <v>10847</v>
@@ -16986,7 +16986,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G573" t="n">
-        <v>4.73715782165527</v>
+        <v>4.73715734481812</v>
       </c>
       <c r="H573" t="n">
         <v>798</v>
@@ -17102,7 +17102,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G577" t="n">
-        <v>4.91391658782959</v>
+        <v>4.91391706466675</v>
       </c>
       <c r="H577" t="n">
         <v>7024</v>
@@ -17160,7 +17160,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G579" t="n">
-        <v>4.89624118804932</v>
+        <v>4.89624071121216</v>
       </c>
       <c r="H579" t="n">
         <v>5879</v>
@@ -17189,7 +17189,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G580" t="n">
-        <v>4.94926881790161</v>
+        <v>4.94926929473877</v>
       </c>
       <c r="H580" t="n">
         <v>3440</v>
@@ -17218,7 +17218,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G581" t="n">
-        <v>5.10835266113281</v>
+        <v>5.10835313796997</v>
       </c>
       <c r="H581" t="n">
         <v>12053</v>
@@ -17247,7 +17247,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G582" t="n">
-        <v>5.26743602752686</v>
+        <v>5.26743650436401</v>
       </c>
       <c r="H582" t="n">
         <v>19700</v>
@@ -17305,7 +17305,7 @@
         <v>6.03999996185303</v>
       </c>
       <c r="G584" t="n">
-        <v>5.33814001083374</v>
+        <v>5.33813953399658</v>
       </c>
       <c r="H584" t="n">
         <v>12438</v>
@@ -17421,7 +17421,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G588" t="n">
-        <v>5.70933532714844</v>
+        <v>5.70933485031128</v>
       </c>
       <c r="H588" t="n">
         <v>1075</v>
@@ -17450,7 +17450,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G589" t="n">
-        <v>5.65630769729614</v>
+        <v>5.65630722045898</v>
       </c>
       <c r="H589" t="n">
         <v>6708</v>
@@ -17479,7 +17479,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G590" t="n">
-        <v>5.65630769729614</v>
+        <v>5.65630722045898</v>
       </c>
       <c r="H590" t="n">
         <v>1609</v>
@@ -17508,7 +17508,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G591" t="n">
-        <v>5.63863134384155</v>
+        <v>5.63863182067871</v>
       </c>
       <c r="H591" t="n">
         <v>4654</v>
@@ -17740,7 +17740,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G599" t="n">
-        <v>5.65630769729614</v>
+        <v>5.65630722045898</v>
       </c>
       <c r="H599" t="n">
         <v>6734</v>
@@ -17769,7 +17769,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G600" t="n">
-        <v>5.72701168060303</v>
+        <v>5.72701120376587</v>
       </c>
       <c r="H600" t="n">
         <v>9122</v>
@@ -17914,7 +17914,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G605" t="n">
-        <v>5.72701168060303</v>
+        <v>5.72701120376587</v>
       </c>
       <c r="H605" t="n">
         <v>1318</v>
@@ -17943,7 +17943,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G606" t="n">
-        <v>5.72701168060303</v>
+        <v>5.72701120376587</v>
       </c>
       <c r="H606" t="n">
         <v>11320</v>
@@ -18030,7 +18030,7 @@
         <v>6.42000007629395</v>
       </c>
       <c r="G609" t="n">
-        <v>5.67398357391357</v>
+        <v>5.67398405075073</v>
       </c>
       <c r="H609" t="n">
         <v>1520</v>
@@ -18059,7 +18059,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G610" t="n">
-        <v>5.70933532714844</v>
+        <v>5.70933485031128</v>
       </c>
       <c r="H610" t="n">
         <v>2183</v>
@@ -18088,7 +18088,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G611" t="n">
-        <v>5.72701168060303</v>
+        <v>5.72701120376587</v>
       </c>
       <c r="H611" t="n">
         <v>6700</v>
@@ -18117,7 +18117,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G612" t="n">
-        <v>5.72701168060303</v>
+        <v>5.72701120376587</v>
       </c>
       <c r="H612" t="n">
         <v>280</v>
@@ -18146,7 +18146,7 @@
         <v>6.53999996185303</v>
       </c>
       <c r="G613" t="n">
-        <v>5.78003931045532</v>
+        <v>5.78003883361816</v>
       </c>
       <c r="H613" t="n">
         <v>8888</v>
@@ -18175,7 +18175,7 @@
         <v>6.5</v>
       </c>
       <c r="G614" t="n">
-        <v>5.7446870803833</v>
+        <v>5.74468660354614</v>
       </c>
       <c r="H614" t="n">
         <v>2162</v>
@@ -18204,7 +18204,7 @@
         <v>6.5</v>
       </c>
       <c r="G615" t="n">
-        <v>5.7446870803833</v>
+        <v>5.74468660354614</v>
       </c>
       <c r="H615" t="n">
         <v>0</v>
@@ -18291,7 +18291,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G618" t="n">
-        <v>5.81539106369019</v>
+        <v>5.81539058685303</v>
       </c>
       <c r="H618" t="n">
         <v>2408</v>
@@ -18320,7 +18320,7 @@
         <v>6.5</v>
       </c>
       <c r="G619" t="n">
-        <v>5.7446870803833</v>
+        <v>5.74468660354614</v>
       </c>
       <c r="H619" t="n">
         <v>600</v>
@@ -18407,7 +18407,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G622" t="n">
-        <v>5.39116764068604</v>
+        <v>5.39116811752319</v>
       </c>
       <c r="H622" t="n">
         <v>10704</v>
@@ -18465,7 +18465,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G624" t="n">
-        <v>5.65630769729614</v>
+        <v>5.65630722045898</v>
       </c>
       <c r="H624" t="n">
         <v>4043</v>
@@ -18494,7 +18494,7 @@
         <v>6.5</v>
       </c>
       <c r="G625" t="n">
-        <v>5.7446870803833</v>
+        <v>5.74468660354614</v>
       </c>
       <c r="H625" t="n">
         <v>1890</v>
@@ -18523,7 +18523,7 @@
         <v>6.5</v>
       </c>
       <c r="G626" t="n">
-        <v>5.7446870803833</v>
+        <v>5.74468660354614</v>
       </c>
       <c r="H626" t="n">
         <v>4190</v>
@@ -18552,7 +18552,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G627" t="n">
-        <v>6.00982666015625</v>
+        <v>6.00982713699341</v>
       </c>
       <c r="H627" t="n">
         <v>6922</v>
@@ -18639,7 +18639,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G630" t="n">
-        <v>6.00982666015625</v>
+        <v>6.00982713699341</v>
       </c>
       <c r="H630" t="n">
         <v>16000</v>
@@ -18813,7 +18813,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G636" t="n">
-        <v>5.70933532714844</v>
+        <v>5.70933485031128</v>
       </c>
       <c r="H636" t="n">
         <v>250</v>
@@ -18842,7 +18842,7 @@
         <v>6.44000005722046</v>
       </c>
       <c r="G637" t="n">
-        <v>5.69165897369385</v>
+        <v>5.69165945053101</v>
       </c>
       <c r="H637" t="n">
         <v>405</v>
@@ -18871,7 +18871,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G638" t="n">
-        <v>5.63863134384155</v>
+        <v>5.63863182067871</v>
       </c>
       <c r="H638" t="n">
         <v>3872</v>
@@ -18929,7 +18929,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G640" t="n">
-        <v>5.70933532714844</v>
+        <v>5.70933485031128</v>
       </c>
       <c r="H640" t="n">
         <v>150</v>
@@ -18958,7 +18958,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G641" t="n">
-        <v>5.7977147102356</v>
+        <v>5.79771518707275</v>
       </c>
       <c r="H641" t="n">
         <v>258</v>
@@ -18987,7 +18987,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G642" t="n">
-        <v>5.7977147102356</v>
+        <v>5.79771518707275</v>
       </c>
       <c r="H642" t="n">
         <v>1057</v>
@@ -19016,7 +19016,7 @@
         <v>6.53999996185303</v>
       </c>
       <c r="G643" t="n">
-        <v>5.78003931045532</v>
+        <v>5.78003883361816</v>
       </c>
       <c r="H643" t="n">
         <v>282</v>
@@ -19161,7 +19161,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G648" t="n">
-        <v>5.26743602752686</v>
+        <v>5.26743650436401</v>
       </c>
       <c r="H648" t="n">
         <v>3000</v>
@@ -19190,7 +19190,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G649" t="n">
-        <v>5.39116764068604</v>
+        <v>5.39116811752319</v>
       </c>
       <c r="H649" t="n">
         <v>2460</v>
@@ -19219,7 +19219,7 @@
         <v>6</v>
       </c>
       <c r="G650" t="n">
-        <v>5.30278825759888</v>
+        <v>5.30278778076172</v>
       </c>
       <c r="H650" t="n">
         <v>2718</v>
@@ -19248,7 +19248,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G651" t="n">
-        <v>5.28511190414429</v>
+        <v>5.28511238098145</v>
       </c>
       <c r="H651" t="n">
         <v>1224</v>
@@ -19277,7 +19277,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G652" t="n">
-        <v>5.2144079208374</v>
+        <v>5.21440839767456</v>
       </c>
       <c r="H652" t="n">
         <v>7874</v>
@@ -19335,7 +19335,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G654" t="n">
-        <v>4.94926881790161</v>
+        <v>4.94926929473877</v>
       </c>
       <c r="H654" t="n">
         <v>3137</v>
@@ -19364,7 +19364,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G655" t="n">
-        <v>4.94926881790161</v>
+        <v>4.94926929473877</v>
       </c>
       <c r="H655" t="n">
         <v>14439</v>
@@ -19480,7 +19480,7 @@
         <v>6</v>
       </c>
       <c r="G659" t="n">
-        <v>5.30278825759888</v>
+        <v>5.30278778076172</v>
       </c>
       <c r="H659" t="n">
         <v>11330</v>
@@ -19625,7 +19625,7 @@
         <v>6</v>
       </c>
       <c r="G664" t="n">
-        <v>5.30278825759888</v>
+        <v>5.30278778076172</v>
       </c>
       <c r="H664" t="n">
         <v>7582</v>
@@ -19654,7 +19654,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G665" t="n">
-        <v>5.19673252105713</v>
+        <v>5.19673299789429</v>
       </c>
       <c r="H665" t="n">
         <v>500</v>
@@ -19683,7 +19683,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G666" t="n">
-        <v>4.71948146820068</v>
+        <v>4.71948194503784</v>
       </c>
       <c r="H666" t="n">
         <v>18954</v>
@@ -19712,7 +19712,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G667" t="n">
-        <v>4.77250957489014</v>
+        <v>4.77250909805298</v>
       </c>
       <c r="H667" t="n">
         <v>19980</v>
@@ -19799,7 +19799,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G670" t="n">
-        <v>4.71948146820068</v>
+        <v>4.71948194503784</v>
       </c>
       <c r="H670" t="n">
         <v>875</v>
@@ -19828,7 +19828,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G671" t="n">
-        <v>4.57807397842407</v>
+        <v>4.57807350158691</v>
       </c>
       <c r="H671" t="n">
         <v>623</v>
@@ -19886,7 +19886,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G673" t="n">
-        <v>4.28641986846924</v>
+        <v>4.2864203453064</v>
       </c>
       <c r="H673" t="n">
         <v>7472</v>
@@ -19915,7 +19915,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G674" t="n">
-        <v>4.28641986846924</v>
+        <v>4.2864203453064</v>
       </c>
       <c r="H674" t="n">
         <v>1700</v>
@@ -20147,7 +20147,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G682" t="n">
-        <v>4.71948146820068</v>
+        <v>4.71948194503784</v>
       </c>
       <c r="H682" t="n">
         <v>13546</v>
@@ -20176,7 +20176,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G683" t="n">
-        <v>4.77250957489014</v>
+        <v>4.77250909805298</v>
       </c>
       <c r="H683" t="n">
         <v>830</v>
@@ -20205,7 +20205,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G684" t="n">
-        <v>4.70180559158325</v>
+        <v>4.70180511474609</v>
       </c>
       <c r="H684" t="n">
         <v>8359</v>
@@ -20292,7 +20292,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G687" t="n">
-        <v>4.45434236526489</v>
+        <v>4.45434188842773</v>
       </c>
       <c r="H687" t="n">
         <v>1187</v>
@@ -20321,7 +20321,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G688" t="n">
-        <v>4.54272174835205</v>
+        <v>4.54272222518921</v>
       </c>
       <c r="H688" t="n">
         <v>650</v>
@@ -20379,7 +20379,7 @@
         <v>5.5</v>
       </c>
       <c r="G690" t="n">
-        <v>4.86088895797729</v>
+        <v>4.86088943481445</v>
       </c>
       <c r="H690" t="n">
         <v>2318</v>
@@ -20408,7 +20408,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G691" t="n">
-        <v>4.77250957489014</v>
+        <v>4.77250909805298</v>
       </c>
       <c r="H691" t="n">
         <v>4740</v>
@@ -20495,7 +20495,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G694" t="n">
-        <v>4.93159341812134</v>
+        <v>4.93159246444702</v>
       </c>
       <c r="H694" t="n">
         <v>1580</v>
@@ -20582,7 +20582,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G697" t="n">
-        <v>4.94926881790161</v>
+        <v>4.94926929473877</v>
       </c>
       <c r="H697" t="n">
         <v>6290</v>
@@ -20611,7 +20611,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G698" t="n">
-        <v>4.94926881790161</v>
+        <v>4.94926929473877</v>
       </c>
       <c r="H698" t="n">
         <v>190</v>
@@ -20640,7 +20640,7 @@
         <v>5.5</v>
       </c>
       <c r="G699" t="n">
-        <v>4.86088895797729</v>
+        <v>4.86088943481445</v>
       </c>
       <c r="H699" t="n">
         <v>1100</v>
@@ -20727,7 +20727,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G702" t="n">
-        <v>4.94926881790161</v>
+        <v>4.94926929473877</v>
       </c>
       <c r="H702" t="n">
         <v>4149</v>
@@ -20814,7 +20814,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G705" t="n">
-        <v>5.14370489120483</v>
+        <v>5.14370441436768</v>
       </c>
       <c r="H705" t="n">
         <v>60299</v>
@@ -20872,7 +20872,7 @@
         <v>5.8600001335144</v>
       </c>
       <c r="G707" t="n">
-        <v>5.1790566444397</v>
+        <v>5.17905616760254</v>
       </c>
       <c r="H707" t="n">
         <v>1856</v>
@@ -20988,7 +20988,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G711" t="n">
-        <v>5.14370489120483</v>
+        <v>5.14370441436768</v>
       </c>
       <c r="H711" t="n">
         <v>6657</v>
@@ -21017,7 +21017,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G712" t="n">
-        <v>5.14370489120483</v>
+        <v>5.14370441436768</v>
       </c>
       <c r="H712" t="n">
         <v>0</v>
@@ -21046,7 +21046,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G713" t="n">
-        <v>5.16138029098511</v>
+        <v>5.16138076782227</v>
       </c>
       <c r="H713" t="n">
         <v>3739</v>
@@ -21104,7 +21104,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G715" t="n">
-        <v>5.14370489120483</v>
+        <v>5.14370441436768</v>
       </c>
       <c r="H715" t="n">
         <v>3046</v>
@@ -21278,7 +21278,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G721" t="n">
-        <v>4.94926881790161</v>
+        <v>4.94926929473877</v>
       </c>
       <c r="H721" t="n">
         <v>277</v>
@@ -21307,7 +21307,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G722" t="n">
-        <v>5.16138029098511</v>
+        <v>5.16138076782227</v>
       </c>
       <c r="H722" t="n">
         <v>1500</v>
@@ -21336,7 +21336,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G723" t="n">
-        <v>5.16138029098511</v>
+        <v>5.16138076782227</v>
       </c>
       <c r="H723" t="n">
         <v>0</v>
@@ -21365,7 +21365,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G724" t="n">
-        <v>5.24976062774658</v>
+        <v>5.24976015090942</v>
       </c>
       <c r="H724" t="n">
         <v>4500</v>
@@ -21626,7 +21626,7 @@
         <v>5.8600001335144</v>
       </c>
       <c r="G733" t="n">
-        <v>5.24438142776489</v>
+        <v>5.24438095092773</v>
       </c>
       <c r="H733" t="n">
         <v>1735</v>
@@ -21655,7 +21655,7 @@
         <v>5.8600001335144</v>
       </c>
       <c r="G734" t="n">
-        <v>5.24438142776489</v>
+        <v>5.24438095092773</v>
       </c>
       <c r="H734" t="n">
         <v>0</v>
@@ -21771,7 +21771,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G738" t="n">
-        <v>5.26227998733521</v>
+        <v>5.26228046417236</v>
       </c>
       <c r="H738" t="n">
         <v>40</v>
@@ -22148,7 +22148,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G751" t="n">
-        <v>4.99379634857178</v>
+        <v>4.99379587173462</v>
       </c>
       <c r="H751" t="n">
         <v>470</v>
@@ -22351,7 +22351,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G758" t="n">
-        <v>5.31597709655762</v>
+        <v>5.31597661972046</v>
       </c>
       <c r="H758" t="n">
         <v>1333</v>
@@ -22380,7 +22380,7 @@
         <v>6</v>
       </c>
       <c r="G759" t="n">
-        <v>5.36967372894287</v>
+        <v>5.36967325210571</v>
       </c>
       <c r="H759" t="n">
         <v>304</v>
@@ -22409,7 +22409,7 @@
         <v>6</v>
       </c>
       <c r="G760" t="n">
-        <v>5.36967372894287</v>
+        <v>5.36967325210571</v>
       </c>
       <c r="H760" t="n">
         <v>829</v>
@@ -22438,7 +22438,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G761" t="n">
-        <v>5.47706699371338</v>
+        <v>5.47706651687622</v>
       </c>
       <c r="H761" t="n">
         <v>270</v>
@@ -22641,7 +22641,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G768" t="n">
-        <v>5.72765207290649</v>
+        <v>5.72765159606934</v>
       </c>
       <c r="H768" t="n">
         <v>2958</v>
@@ -22699,7 +22699,7 @@
         <v>6.51999998092651</v>
       </c>
       <c r="G770" t="n">
-        <v>5.83504486083984</v>
+        <v>5.835045337677</v>
       </c>
       <c r="H770" t="n">
         <v>667</v>
@@ -22728,7 +22728,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G771" t="n">
-        <v>5.72765207290649</v>
+        <v>5.72765159606934</v>
       </c>
       <c r="H771" t="n">
         <v>678</v>
@@ -22757,7 +22757,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G772" t="n">
-        <v>5.72765207290649</v>
+        <v>5.72765159606934</v>
       </c>
       <c r="H772" t="n">
         <v>1540</v>
@@ -22844,7 +22844,7 @@
         <v>6.5</v>
       </c>
       <c r="G775" t="n">
-        <v>5.81714630126953</v>
+        <v>5.81714582443237</v>
       </c>
       <c r="H775" t="n">
         <v>11</v>
@@ -22902,7 +22902,7 @@
         <v>6.5</v>
       </c>
       <c r="G777" t="n">
-        <v>5.81714630126953</v>
+        <v>5.81714582443237</v>
       </c>
       <c r="H777" t="n">
         <v>6650</v>
@@ -23018,7 +23018,7 @@
         <v>6.73999977111816</v>
       </c>
       <c r="G781" t="n">
-        <v>6.03193330764771</v>
+        <v>6.03193283081055</v>
       </c>
       <c r="H781" t="n">
         <v>1012</v>
@@ -23105,7 +23105,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G784" t="n">
-        <v>6.08562994003296</v>
+        <v>6.08563041687012</v>
       </c>
       <c r="H784" t="n">
         <v>2889</v>
@@ -23250,7 +23250,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G789" t="n">
-        <v>5.88874197006226</v>
+        <v>5.8887414932251</v>
       </c>
       <c r="H789" t="n">
         <v>3581</v>
@@ -23308,7 +23308,7 @@
         <v>6.53999996185303</v>
       </c>
       <c r="G791" t="n">
-        <v>5.85294437408447</v>
+        <v>5.85294389724731</v>
       </c>
       <c r="H791" t="n">
         <v>31</v>
@@ -23337,7 +23337,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G792" t="n">
-        <v>5.72765207290649</v>
+        <v>5.72765159606934</v>
       </c>
       <c r="H792" t="n">
         <v>40050</v>
@@ -23482,7 +23482,7 @@
         <v>6.5</v>
       </c>
       <c r="G797" t="n">
-        <v>5.81714630126953</v>
+        <v>5.81714582443237</v>
       </c>
       <c r="H797" t="n">
         <v>1055</v>
@@ -23511,7 +23511,7 @@
         <v>6.5</v>
       </c>
       <c r="G798" t="n">
-        <v>5.81714630126953</v>
+        <v>5.81714582443237</v>
       </c>
       <c r="H798" t="n">
         <v>30000</v>
@@ -23598,7 +23598,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G801" t="n">
-        <v>5.88874197006226</v>
+        <v>5.8887414932251</v>
       </c>
       <c r="H801" t="n">
         <v>550</v>
@@ -23772,7 +23772,7 @@
         <v>6.42000007629395</v>
       </c>
       <c r="G807" t="n">
-        <v>5.74555063247681</v>
+        <v>5.74555110931396</v>
       </c>
       <c r="H807" t="n">
         <v>50</v>
@@ -23888,7 +23888,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G811" t="n">
-        <v>5.5486626625061</v>
+        <v>5.54866218566895</v>
       </c>
       <c r="H811" t="n">
         <v>1520</v>
@@ -23946,7 +23946,7 @@
         <v>5.8600001335144</v>
       </c>
       <c r="G813" t="n">
-        <v>5.24438142776489</v>
+        <v>5.24438095092773</v>
       </c>
       <c r="H813" t="n">
         <v>595</v>
@@ -23975,7 +23975,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G814" t="n">
-        <v>5.13698768615723</v>
+        <v>5.13698720932007</v>
       </c>
       <c r="H814" t="n">
         <v>33740</v>
@@ -24004,7 +24004,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G815" t="n">
-        <v>5.13698768615723</v>
+        <v>5.13698720932007</v>
       </c>
       <c r="H815" t="n">
         <v>0</v>
@@ -24033,7 +24033,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G816" t="n">
-        <v>5.35177421569824</v>
+        <v>5.3517746925354</v>
       </c>
       <c r="H816" t="n">
         <v>30550</v>
@@ -24062,7 +24062,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G817" t="n">
-        <v>4.83270645141602</v>
+        <v>4.83270597457886</v>
       </c>
       <c r="H817" t="n">
         <v>29376</v>
@@ -24178,7 +24178,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G821" t="n">
-        <v>4.83270645141602</v>
+        <v>4.83270597457886</v>
       </c>
       <c r="H821" t="n">
         <v>677</v>
@@ -24236,7 +24236,7 @@
         <v>6</v>
       </c>
       <c r="G823" t="n">
-        <v>5.36967372894287</v>
+        <v>5.36967325210571</v>
       </c>
       <c r="H823" t="n">
         <v>1900</v>
@@ -24265,7 +24265,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G824" t="n">
-        <v>5.47706699371338</v>
+        <v>5.47706651687622</v>
       </c>
       <c r="H824" t="n">
         <v>100</v>
@@ -24323,7 +24323,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G826" t="n">
-        <v>5.5486626625061</v>
+        <v>5.54866218566895</v>
       </c>
       <c r="H826" t="n">
         <v>610</v>
@@ -24352,7 +24352,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G827" t="n">
-        <v>5.5486626625061</v>
+        <v>5.54866218566895</v>
       </c>
       <c r="H827" t="n">
         <v>0</v>
@@ -24381,7 +24381,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G828" t="n">
-        <v>5.5486626625061</v>
+        <v>5.54866218566895</v>
       </c>
       <c r="H828" t="n">
         <v>600</v>
@@ -24410,7 +24410,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G829" t="n">
-        <v>5.5486626625061</v>
+        <v>5.54866218566895</v>
       </c>
       <c r="H829" t="n">
         <v>0</v>
@@ -24439,7 +24439,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G830" t="n">
-        <v>5.72765207290649</v>
+        <v>5.72765159606934</v>
       </c>
       <c r="H830" t="n">
         <v>1323</v>
@@ -24497,7 +24497,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G832" t="n">
-        <v>5.72765207290649</v>
+        <v>5.72765159606934</v>
       </c>
       <c r="H832" t="n">
         <v>420</v>
@@ -24700,7 +24700,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G839" t="n">
-        <v>5.5486626625061</v>
+        <v>5.54866218566895</v>
       </c>
       <c r="H839" t="n">
         <v>400</v>
@@ -24729,7 +24729,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G840" t="n">
-        <v>5.53076314926147</v>
+        <v>5.53076362609863</v>
       </c>
       <c r="H840" t="n">
         <v>422</v>
@@ -24903,7 +24903,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G846" t="n">
-        <v>5.72765207290649</v>
+        <v>5.72765159606934</v>
       </c>
       <c r="H846" t="n">
         <v>100</v>
@@ -24961,7 +24961,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G848" t="n">
-        <v>5.72765207290649</v>
+        <v>5.72765159606934</v>
       </c>
       <c r="H848" t="n">
         <v>1038</v>
@@ -25048,7 +25048,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G851" t="n">
-        <v>5.70975255966187</v>
+        <v>5.70975303649902</v>
       </c>
       <c r="H851" t="n">
         <v>961</v>
@@ -25077,7 +25077,7 @@
         <v>6.5</v>
       </c>
       <c r="G852" t="n">
-        <v>5.81714630126953</v>
+        <v>5.81714582443237</v>
       </c>
       <c r="H852" t="n">
         <v>263</v>
@@ -25106,7 +25106,7 @@
         <v>6.5</v>
       </c>
       <c r="G853" t="n">
-        <v>5.81714630126953</v>
+        <v>5.81714582443237</v>
       </c>
       <c r="H853" t="n">
         <v>1153</v>
@@ -25193,7 +25193,7 @@
         <v>6.42000007629395</v>
       </c>
       <c r="G856" t="n">
-        <v>5.74555063247681</v>
+        <v>5.74555110931396</v>
       </c>
       <c r="H856" t="n">
         <v>396</v>
@@ -25222,7 +25222,7 @@
         <v>6.51999998092651</v>
       </c>
       <c r="G857" t="n">
-        <v>5.83504486083984</v>
+        <v>5.835045337677</v>
       </c>
       <c r="H857" t="n">
         <v>100</v>
@@ -25251,7 +25251,7 @@
         <v>6.51999998092651</v>
       </c>
       <c r="G858" t="n">
-        <v>5.83504486083984</v>
+        <v>5.835045337677</v>
       </c>
       <c r="H858" t="n">
         <v>0</v>
@@ -25280,7 +25280,7 @@
         <v>6.51999998092651</v>
       </c>
       <c r="G859" t="n">
-        <v>5.83504486083984</v>
+        <v>5.835045337677</v>
       </c>
       <c r="H859" t="n">
         <v>0</v>
@@ -25396,7 +25396,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G863" t="n">
-        <v>5.88874197006226</v>
+        <v>5.8887414932251</v>
       </c>
       <c r="H863" t="n">
         <v>1364</v>
@@ -25454,7 +25454,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G865" t="n">
-        <v>5.88874197006226</v>
+        <v>5.8887414932251</v>
       </c>
       <c r="H865" t="n">
         <v>1988</v>
@@ -25541,7 +25541,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G868" t="n">
-        <v>6.08562994003296</v>
+        <v>6.08563041687012</v>
       </c>
       <c r="H868" t="n">
         <v>500</v>
@@ -25570,7 +25570,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G869" t="n">
-        <v>6.08562994003296</v>
+        <v>6.08563041687012</v>
       </c>
       <c r="H869" t="n">
         <v>0</v>
@@ -25860,7 +25860,7 @@
         <v>6.5</v>
       </c>
       <c r="G879" t="n">
-        <v>5.81714630126953</v>
+        <v>5.81714582443237</v>
       </c>
       <c r="H879" t="n">
         <v>314</v>
@@ -25918,7 +25918,7 @@
         <v>6.73999977111816</v>
       </c>
       <c r="G881" t="n">
-        <v>6.03193330764771</v>
+        <v>6.03193283081055</v>
       </c>
       <c r="H881" t="n">
         <v>400</v>
@@ -25976,7 +25976,7 @@
         <v>6.71999979019165</v>
       </c>
       <c r="G883" t="n">
-        <v>6.01403379440308</v>
+        <v>6.01403427124023</v>
       </c>
       <c r="H883" t="n">
         <v>200</v>
@@ -26005,7 +26005,7 @@
         <v>6.71999979019165</v>
       </c>
       <c r="G884" t="n">
-        <v>6.01403379440308</v>
+        <v>6.01403427124023</v>
       </c>
       <c r="H884" t="n">
         <v>0</v>
@@ -26150,7 +26150,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G889" t="n">
-        <v>5.72765207290649</v>
+        <v>5.72765159606934</v>
       </c>
       <c r="H889" t="n">
         <v>1703</v>
@@ -26179,7 +26179,7 @@
         <v>6.5</v>
       </c>
       <c r="G890" t="n">
-        <v>5.81714630126953</v>
+        <v>5.81714582443237</v>
       </c>
       <c r="H890" t="n">
         <v>662</v>
@@ -26208,7 +26208,7 @@
         <v>6.71999979019165</v>
       </c>
       <c r="G891" t="n">
-        <v>6.01403379440308</v>
+        <v>6.01403427124023</v>
       </c>
       <c r="H891" t="n">
         <v>155</v>
@@ -26237,7 +26237,7 @@
         <v>6.71999979019165</v>
       </c>
       <c r="G892" t="n">
-        <v>6.01403379440308</v>
+        <v>6.01403427124023</v>
       </c>
       <c r="H892" t="n">
         <v>0</v>
@@ -26266,7 +26266,7 @@
         <v>6.71999979019165</v>
       </c>
       <c r="G893" t="n">
-        <v>6.01403379440308</v>
+        <v>6.01403427124023</v>
       </c>
       <c r="H893" t="n">
         <v>0</v>
@@ -26556,7 +26556,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G903" t="n">
-        <v>6.98057556152344</v>
+        <v>6.9805760383606</v>
       </c>
       <c r="H903" t="n">
         <v>2180</v>
@@ -26614,7 +26614,7 @@
         <v>7.57999992370605</v>
       </c>
       <c r="G905" t="n">
-        <v>6.78368759155273</v>
+        <v>6.78368711471558</v>
       </c>
       <c r="H905" t="n">
         <v>2196</v>
@@ -26701,7 +26701,7 @@
         <v>7.03999996185303</v>
       </c>
       <c r="G908" t="n">
-        <v>6.30041694641113</v>
+        <v>6.30041646957397</v>
       </c>
       <c r="H908" t="n">
         <v>5650</v>
@@ -26759,7 +26759,7 @@
         <v>7.1399998664856</v>
       </c>
       <c r="G910" t="n">
-        <v>6.38991117477417</v>
+        <v>6.38991165161133</v>
       </c>
       <c r="H910" t="n">
         <v>1158</v>
@@ -26962,7 +26962,7 @@
         <v>7.26000022888184</v>
       </c>
       <c r="G917" t="n">
-        <v>6.49730491638184</v>
+        <v>6.49730539321899</v>
       </c>
       <c r="H917" t="n">
         <v>3000</v>
@@ -26991,7 +26991,7 @@
         <v>7.42000007629395</v>
       </c>
       <c r="G918" t="n">
-        <v>6.64049673080444</v>
+        <v>6.64049625396729</v>
       </c>
       <c r="H918" t="n">
         <v>2331</v>
@@ -27078,7 +27078,7 @@
         <v>7.34000015258789</v>
       </c>
       <c r="G921" t="n">
-        <v>6.56890058517456</v>
+        <v>6.56890106201172</v>
       </c>
       <c r="H921" t="n">
         <v>250</v>
@@ -27136,7 +27136,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G923" t="n">
-        <v>6.80158615112305</v>
+        <v>6.80158662796021</v>
       </c>
       <c r="H923" t="n">
         <v>2203</v>
@@ -27397,7 +27397,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G932" t="n">
-        <v>6.80158615112305</v>
+        <v>6.80158662796021</v>
       </c>
       <c r="H932" t="n">
         <v>2264</v>
@@ -27455,7 +27455,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G934" t="n">
-        <v>6.80158615112305</v>
+        <v>6.80158662796021</v>
       </c>
       <c r="H934" t="n">
         <v>1250</v>
@@ -27513,7 +27513,7 @@
         <v>7.34000015258789</v>
       </c>
       <c r="G936" t="n">
-        <v>6.56890058517456</v>
+        <v>6.56890106201172</v>
       </c>
       <c r="H936" t="n">
         <v>75</v>
@@ -27687,7 +27687,7 @@
         <v>7.26000022888184</v>
       </c>
       <c r="G942" t="n">
-        <v>6.49730491638184</v>
+        <v>6.49730539321899</v>
       </c>
       <c r="H942" t="n">
         <v>4218</v>
@@ -27716,7 +27716,7 @@
         <v>7.26000022888184</v>
       </c>
       <c r="G943" t="n">
-        <v>6.49730491638184</v>
+        <v>6.49730539321899</v>
       </c>
       <c r="H943" t="n">
         <v>0</v>
@@ -27745,7 +27745,7 @@
         <v>7.26000022888184</v>
       </c>
       <c r="G944" t="n">
-        <v>6.49730491638184</v>
+        <v>6.49730539321899</v>
       </c>
       <c r="H944" t="n">
         <v>0</v>
@@ -27803,7 +27803,7 @@
         <v>7.21999979019165</v>
       </c>
       <c r="G946" t="n">
-        <v>6.46150732040405</v>
+        <v>6.46150684356689</v>
       </c>
       <c r="H946" t="n">
         <v>103974</v>
@@ -27832,7 +27832,7 @@
         <v>7.21999979019165</v>
       </c>
       <c r="G947" t="n">
-        <v>6.46150732040405</v>
+        <v>6.46150684356689</v>
       </c>
       <c r="H947" t="n">
         <v>574</v>
@@ -28238,7 +28238,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G961" t="n">
-        <v>6.08562994003296</v>
+        <v>6.08563041687012</v>
       </c>
       <c r="H961" t="n">
         <v>1113</v>
@@ -28557,7 +28557,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G972" t="n">
-        <v>6.08562994003296</v>
+        <v>6.08563041687012</v>
       </c>
       <c r="H972" t="n">
         <v>250</v>
@@ -30065,7 +30065,7 @@
         <v>7.25</v>
       </c>
       <c r="G1024" t="n">
-        <v>6.48835563659668</v>
+        <v>6.48835515975952</v>
       </c>
       <c r="H1024" t="n">
         <v>712</v>
@@ -30181,7 +30181,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G1028" t="n">
-        <v>6.84633350372314</v>
+        <v>6.8463339805603</v>
       </c>
       <c r="H1028" t="n">
         <v>12728</v>
@@ -30210,7 +30210,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G1029" t="n">
-        <v>6.98057556152344</v>
+        <v>6.9805760383606</v>
       </c>
       <c r="H1029" t="n">
         <v>238</v>
@@ -30239,7 +30239,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G1030" t="n">
-        <v>6.98057556152344</v>
+        <v>6.9805760383606</v>
       </c>
       <c r="H1030" t="n">
         <v>1</v>
@@ -30268,7 +30268,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G1031" t="n">
-        <v>6.98057556152344</v>
+        <v>6.9805760383606</v>
       </c>
       <c r="H1031" t="n">
         <v>100</v>
@@ -30326,7 +30326,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G1033" t="n">
-        <v>6.75683927536011</v>
+        <v>6.75683975219727</v>
       </c>
       <c r="H1033" t="n">
         <v>670</v>
@@ -30355,7 +30355,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G1034" t="n">
-        <v>6.75683927536011</v>
+        <v>6.75683975219727</v>
       </c>
       <c r="H1034" t="n">
         <v>0</v>
@@ -30384,7 +30384,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G1035" t="n">
-        <v>6.75683927536011</v>
+        <v>6.75683975219727</v>
       </c>
       <c r="H1035" t="n">
         <v>0</v>
@@ -30413,7 +30413,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G1036" t="n">
-        <v>6.75683927536011</v>
+        <v>6.75683975219727</v>
       </c>
       <c r="H1036" t="n">
         <v>0</v>
@@ -30442,7 +30442,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G1037" t="n">
-        <v>6.98057556152344</v>
+        <v>6.9805760383606</v>
       </c>
       <c r="H1037" t="n">
         <v>500</v>
@@ -30471,7 +30471,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G1038" t="n">
-        <v>6.80158615112305</v>
+        <v>6.80158662796021</v>
       </c>
       <c r="H1038" t="n">
         <v>730</v>
@@ -30500,7 +30500,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G1039" t="n">
-        <v>6.80158615112305</v>
+        <v>6.80158662796021</v>
       </c>
       <c r="H1039" t="n">
         <v>0</v>
@@ -30558,7 +30558,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G1041" t="n">
-        <v>6.80158615112305</v>
+        <v>6.80158662796021</v>
       </c>
       <c r="H1041" t="n">
         <v>13</v>
@@ -30587,7 +30587,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G1042" t="n">
-        <v>6.80158615112305</v>
+        <v>6.80158662796021</v>
       </c>
       <c r="H1042" t="n">
         <v>0</v>
@@ -30616,7 +30616,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G1043" t="n">
-        <v>6.80158615112305</v>
+        <v>6.80158662796021</v>
       </c>
       <c r="H1043" t="n">
         <v>0</v>
@@ -30645,7 +30645,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G1044" t="n">
-        <v>6.80158615112305</v>
+        <v>6.80158662796021</v>
       </c>
       <c r="H1044" t="n">
         <v>0</v>
@@ -30674,7 +30674,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G1045" t="n">
-        <v>6.80158615112305</v>
+        <v>6.80158662796021</v>
       </c>
       <c r="H1045" t="n">
         <v>0</v>
@@ -30703,7 +30703,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G1046" t="n">
-        <v>6.80158615112305</v>
+        <v>6.80158662796021</v>
       </c>
       <c r="H1046" t="n">
         <v>0</v>
@@ -30732,7 +30732,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G1047" t="n">
-        <v>6.80158615112305</v>
+        <v>6.80158662796021</v>
       </c>
       <c r="H1047" t="n">
         <v>0</v>
@@ -30761,7 +30761,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G1048" t="n">
-        <v>6.98057556152344</v>
+        <v>6.9805760383606</v>
       </c>
       <c r="H1048" t="n">
         <v>601</v>
@@ -30790,7 +30790,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G1049" t="n">
-        <v>6.84633350372314</v>
+        <v>6.8463339805603</v>
       </c>
       <c r="H1049" t="n">
         <v>100</v>
@@ -30819,7 +30819,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G1050" t="n">
-        <v>6.98057556152344</v>
+        <v>6.9805760383606</v>
       </c>
       <c r="H1050" t="n">
         <v>460</v>
@@ -30848,7 +30848,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G1051" t="n">
-        <v>6.98057556152344</v>
+        <v>6.9805760383606</v>
       </c>
       <c r="H1051" t="n">
         <v>125</v>
@@ -30877,7 +30877,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G1052" t="n">
-        <v>6.98057556152344</v>
+        <v>6.9805760383606</v>
       </c>
       <c r="H1052" t="n">
         <v>0</v>
@@ -30906,7 +30906,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G1053" t="n">
-        <v>6.80158615112305</v>
+        <v>6.80158662796021</v>
       </c>
       <c r="H1053" t="n">
         <v>1684</v>
@@ -31080,7 +31080,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G1059" t="n">
-        <v>6.75683927536011</v>
+        <v>6.75683975219727</v>
       </c>
       <c r="H1059" t="n">
         <v>400</v>
@@ -31109,7 +31109,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G1060" t="n">
-        <v>6.75683927536011</v>
+        <v>6.75683975219727</v>
       </c>
       <c r="H1060" t="n">
         <v>0</v>
@@ -31138,7 +31138,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G1061" t="n">
-        <v>6.75683927536011</v>
+        <v>6.75683975219727</v>
       </c>
       <c r="H1061" t="n">
         <v>0</v>
@@ -31602,7 +31602,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G1077" t="n">
-        <v>5.86189365386963</v>
+        <v>5.86189413070679</v>
       </c>
       <c r="H1077" t="n">
         <v>846</v>
@@ -31631,7 +31631,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G1078" t="n">
-        <v>5.72765207290649</v>
+        <v>5.72765159606934</v>
       </c>
       <c r="H1078" t="n">
         <v>2019</v>
@@ -31660,7 +31660,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G1079" t="n">
-        <v>5.86189365386963</v>
+        <v>5.86189413070679</v>
       </c>
       <c r="H1079" t="n">
         <v>100</v>
@@ -31747,7 +31747,7 @@
         <v>6</v>
       </c>
       <c r="G1082" t="n">
-        <v>5.36967372894287</v>
+        <v>5.36967325210571</v>
       </c>
       <c r="H1082" t="n">
         <v>11354</v>
@@ -31776,7 +31776,7 @@
         <v>6</v>
       </c>
       <c r="G1083" t="n">
-        <v>5.36967372894287</v>
+        <v>5.36967325210571</v>
       </c>
       <c r="H1083" t="n">
         <v>25500</v>
@@ -31805,7 +31805,7 @@
         <v>6</v>
       </c>
       <c r="G1084" t="n">
-        <v>5.36967372894287</v>
+        <v>5.36967325210571</v>
       </c>
       <c r="H1084" t="n">
         <v>0</v>
@@ -31863,7 +31863,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G1086" t="n">
-        <v>5.32492637634277</v>
+        <v>5.32492589950562</v>
       </c>
       <c r="H1086" t="n">
         <v>6465</v>
@@ -31892,7 +31892,7 @@
         <v>6</v>
       </c>
       <c r="G1087" t="n">
-        <v>5.36967372894287</v>
+        <v>5.36967325210571</v>
       </c>
       <c r="H1087" t="n">
         <v>6931</v>
@@ -31921,7 +31921,7 @@
         <v>6</v>
       </c>
       <c r="G1088" t="n">
-        <v>5.36967372894287</v>
+        <v>5.36967325210571</v>
       </c>
       <c r="H1088" t="n">
         <v>0</v>
@@ -31950,7 +31950,7 @@
         <v>6</v>
       </c>
       <c r="G1089" t="n">
-        <v>5.36967372894287</v>
+        <v>5.36967325210571</v>
       </c>
       <c r="H1089" t="n">
         <v>0</v>
@@ -31979,7 +31979,7 @@
         <v>6</v>
       </c>
       <c r="G1090" t="n">
-        <v>5.36967372894287</v>
+        <v>5.36967325210571</v>
       </c>
       <c r="H1090" t="n">
         <v>850</v>
@@ -32008,7 +32008,7 @@
         <v>6</v>
       </c>
       <c r="G1091" t="n">
-        <v>5.36967372894287</v>
+        <v>5.36967325210571</v>
       </c>
       <c r="H1091" t="n">
         <v>240</v>
@@ -32037,7 +32037,7 @@
         <v>6</v>
       </c>
       <c r="G1092" t="n">
-        <v>5.36967372894287</v>
+        <v>5.36967325210571</v>
       </c>
       <c r="H1092" t="n">
         <v>650</v>
@@ -32066,7 +32066,7 @@
         <v>6</v>
       </c>
       <c r="G1093" t="n">
-        <v>5.36967372894287</v>
+        <v>5.36967325210571</v>
       </c>
       <c r="H1093" t="n">
         <v>675</v>
@@ -32095,7 +32095,7 @@
         <v>6</v>
       </c>
       <c r="G1094" t="n">
-        <v>5.36967372894287</v>
+        <v>5.36967325210571</v>
       </c>
       <c r="H1094" t="n">
         <v>0</v>
@@ -32124,7 +32124,7 @@
         <v>6</v>
       </c>
       <c r="G1095" t="n">
-        <v>5.36967372894287</v>
+        <v>5.36967325210571</v>
       </c>
       <c r="H1095" t="n">
         <v>0</v>
@@ -32414,7 +32414,7 @@
         <v>6.25</v>
       </c>
       <c r="G1105" t="n">
-        <v>5.5934100151062</v>
+        <v>5.59340953826904</v>
       </c>
       <c r="H1105" t="n">
         <v>14260</v>
@@ -32443,7 +32443,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G1106" t="n">
-        <v>5.5486626625061</v>
+        <v>5.54866218566895</v>
       </c>
       <c r="H1106" t="n">
         <v>39658</v>
@@ -32559,7 +32559,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G1110" t="n">
-        <v>5.5486626625061</v>
+        <v>5.54866218566895</v>
       </c>
       <c r="H1110" t="n">
         <v>21380</v>
@@ -32617,7 +32617,7 @@
         <v>6.5</v>
       </c>
       <c r="G1112" t="n">
-        <v>5.81714630126953</v>
+        <v>5.81714582443237</v>
       </c>
       <c r="H1112" t="n">
         <v>29853</v>
@@ -32646,7 +32646,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G1113" t="n">
-        <v>5.72765207290649</v>
+        <v>5.72765159606934</v>
       </c>
       <c r="H1113" t="n">
         <v>31724</v>
@@ -32675,7 +32675,7 @@
         <v>6.5</v>
       </c>
       <c r="G1114" t="n">
-        <v>5.81714630126953</v>
+        <v>5.81714582443237</v>
       </c>
       <c r="H1114" t="n">
         <v>15604</v>
@@ -32791,7 +32791,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G1118" t="n">
-        <v>6.08562994003296</v>
+        <v>6.08563041687012</v>
       </c>
       <c r="H1118" t="n">
         <v>46505</v>
@@ -32965,7 +32965,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G1124" t="n">
-        <v>6.75683927536011</v>
+        <v>6.75683975219727</v>
       </c>
       <c r="H1124" t="n">
         <v>52998</v>
@@ -54112,6 +54112,35 @@
         <v>1000</v>
       </c>
       <c r="I1853" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1854">
+      <c r="A1854" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1854" s="1" t="n">
+        <v>46324.3333333333</v>
+      </c>
+      <c r="C1854" t="n">
+        <v>2.20000004768372</v>
+      </c>
+      <c r="D1854" t="n">
+        <v>2.20000004768372</v>
+      </c>
+      <c r="E1854" t="n">
+        <v>2.20000004768372</v>
+      </c>
+      <c r="F1854" t="n">
+        <v>2.20000004768372</v>
+      </c>
+      <c r="G1854" t="n">
+        <v>2.20000004768372</v>
+      </c>
+      <c r="H1854" t="n">
+        <v>350</v>
+      </c>
+      <c r="I1854" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/PTR.MI.xlsx
+++ b/data/PTR.MI.xlsx
@@ -427,7 +427,7 @@
         <v>3.75</v>
       </c>
       <c r="G2" t="n">
-        <v>3.25484609603882</v>
+        <v>3.2548463344574</v>
       </c>
       <c r="H2" t="n">
         <v>859316</v>
@@ -456,7 +456,7 @@
         <v>3.7409999370575</v>
       </c>
       <c r="G3" t="n">
-        <v>3.24703431129456</v>
+        <v>3.24703454971313</v>
       </c>
       <c r="H3" t="n">
         <v>329252</v>
@@ -485,7 +485,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G4" t="n">
-        <v>3.22012782096863</v>
+        <v>3.22012805938721</v>
       </c>
       <c r="H4" t="n">
         <v>98299</v>
@@ -514,7 +514,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G5" t="n">
-        <v>3.20276880264282</v>
+        <v>3.20276856422424</v>
       </c>
       <c r="H5" t="n">
         <v>56648</v>
@@ -572,7 +572,7 @@
         <v>3.56850004196167</v>
       </c>
       <c r="G7" t="n">
-        <v>3.09731149673462</v>
+        <v>3.0973117351532</v>
       </c>
       <c r="H7" t="n">
         <v>71079</v>
@@ -659,7 +659,7 @@
         <v>3.43199992179871</v>
       </c>
       <c r="G10" t="n">
-        <v>2.97883534431458</v>
+        <v>2.978835105896</v>
       </c>
       <c r="H10" t="n">
         <v>69299</v>
@@ -688,7 +688,7 @@
         <v>3.47849988937378</v>
       </c>
       <c r="G11" t="n">
-        <v>3.01919555664062</v>
+        <v>3.01919531822205</v>
       </c>
       <c r="H11" t="n">
         <v>324435</v>
@@ -920,7 +920,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G19" t="n">
-        <v>3.13333201408386</v>
+        <v>3.13333177566528</v>
       </c>
       <c r="H19" t="n">
         <v>26321</v>
@@ -1123,7 +1123,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G26" t="n">
-        <v>2.96841979026794</v>
+        <v>2.96842002868652</v>
       </c>
       <c r="H26" t="n">
         <v>3800</v>
@@ -1297,7 +1297,7 @@
         <v>3.48200011253357</v>
       </c>
       <c r="G32" t="n">
-        <v>3.02223348617554</v>
+        <v>3.02223324775696</v>
       </c>
       <c r="H32" t="n">
         <v>904</v>
@@ -1326,7 +1326,7 @@
         <v>3.48200011253357</v>
       </c>
       <c r="G33" t="n">
-        <v>3.02223348617554</v>
+        <v>3.02223324775696</v>
       </c>
       <c r="H33" t="n">
         <v>432</v>
@@ -1355,7 +1355,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G34" t="n">
-        <v>3.10729336738586</v>
+        <v>3.10729312896729</v>
       </c>
       <c r="H34" t="n">
         <v>3335</v>
@@ -1384,7 +1384,7 @@
         <v>3.5</v>
       </c>
       <c r="G35" t="n">
-        <v>3.0378565788269</v>
+        <v>3.03785634040833</v>
       </c>
       <c r="H35" t="n">
         <v>1400</v>
@@ -1529,7 +1529,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G40" t="n">
-        <v>3.20276880264282</v>
+        <v>3.20276856422424</v>
       </c>
       <c r="H40" t="n">
         <v>69445</v>
@@ -1587,7 +1587,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G42" t="n">
-        <v>3.29824423789978</v>
+        <v>3.2982439994812</v>
       </c>
       <c r="H42" t="n">
         <v>4451</v>
@@ -1616,7 +1616,7 @@
         <v>3.82500004768372</v>
       </c>
       <c r="G43" t="n">
-        <v>3.31994318962097</v>
+        <v>3.31994342803955</v>
       </c>
       <c r="H43" t="n">
         <v>5962</v>
@@ -1645,7 +1645,7 @@
         <v>3.67499995231628</v>
       </c>
       <c r="G44" t="n">
-        <v>3.18974947929382</v>
+        <v>3.18974924087524</v>
       </c>
       <c r="H44" t="n">
         <v>9040</v>
@@ -1703,7 +1703,7 @@
         <v>3.71499991416931</v>
       </c>
       <c r="G46" t="n">
-        <v>3.22446775436401</v>
+        <v>3.22446751594543</v>
       </c>
       <c r="H46" t="n">
         <v>3406</v>
@@ -1761,7 +1761,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G48" t="n">
-        <v>3.15069150924683</v>
+        <v>3.15069127082825</v>
       </c>
       <c r="H48" t="n">
         <v>190</v>
@@ -1819,7 +1819,7 @@
         <v>3.71499991416931</v>
       </c>
       <c r="G50" t="n">
-        <v>3.22446775436401</v>
+        <v>3.22446751594543</v>
       </c>
       <c r="H50" t="n">
         <v>7667</v>
@@ -1848,7 +1848,7 @@
         <v>3.75</v>
       </c>
       <c r="G51" t="n">
-        <v>3.25484609603882</v>
+        <v>3.2548463344574</v>
       </c>
       <c r="H51" t="n">
         <v>37160</v>
@@ -1993,7 +1993,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G56" t="n">
-        <v>3.15069150924683</v>
+        <v>3.15069127082825</v>
       </c>
       <c r="H56" t="n">
         <v>6760</v>
@@ -2022,7 +2022,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G57" t="n">
-        <v>3.15069150924683</v>
+        <v>3.15069127082825</v>
       </c>
       <c r="H57" t="n">
         <v>100</v>
@@ -2080,7 +2080,7 @@
         <v>3.66499996185303</v>
       </c>
       <c r="G59" t="n">
-        <v>3.18106985092163</v>
+        <v>3.18106961250305</v>
       </c>
       <c r="H59" t="n">
         <v>20</v>
@@ -2138,7 +2138,7 @@
         <v>3.66499996185303</v>
       </c>
       <c r="G61" t="n">
-        <v>3.18106985092163</v>
+        <v>3.18106961250305</v>
       </c>
       <c r="H61" t="n">
         <v>27542</v>
@@ -2312,7 +2312,7 @@
         <v>3.63499999046326</v>
       </c>
       <c r="G67" t="n">
-        <v>3.15503072738647</v>
+        <v>3.15503096580505</v>
       </c>
       <c r="H67" t="n">
         <v>1440</v>
@@ -2689,7 +2689,7 @@
         <v>3.67499995231628</v>
       </c>
       <c r="G80" t="n">
-        <v>3.18974947929382</v>
+        <v>3.18974924087524</v>
       </c>
       <c r="H80" t="n">
         <v>6929</v>
@@ -2776,7 +2776,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G83" t="n">
-        <v>3.29824423789978</v>
+        <v>3.2982439994812</v>
       </c>
       <c r="H83" t="n">
         <v>198082</v>
@@ -2805,7 +2805,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G84" t="n">
-        <v>3.29824423789978</v>
+        <v>3.2982439994812</v>
       </c>
       <c r="H84" t="n">
         <v>33903</v>
@@ -2834,7 +2834,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G85" t="n">
-        <v>3.29824423789978</v>
+        <v>3.2982439994812</v>
       </c>
       <c r="H85" t="n">
         <v>18308</v>
@@ -2863,7 +2863,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G86" t="n">
-        <v>3.29824423789978</v>
+        <v>3.2982439994812</v>
       </c>
       <c r="H86" t="n">
         <v>6890</v>
@@ -2892,7 +2892,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G87" t="n">
-        <v>3.37636065483093</v>
+        <v>3.37636089324951</v>
       </c>
       <c r="H87" t="n">
         <v>25644</v>
@@ -2979,7 +2979,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G90" t="n">
-        <v>3.41975855827332</v>
+        <v>3.41975879669189</v>
       </c>
       <c r="H90" t="n">
         <v>12161</v>
@@ -3008,7 +3008,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G91" t="n">
-        <v>3.51523399353027</v>
+        <v>3.51523423194885</v>
       </c>
       <c r="H91" t="n">
         <v>17593</v>
@@ -3037,7 +3037,7 @@
         <v>4</v>
       </c>
       <c r="G92" t="n">
-        <v>3.47183585166931</v>
+        <v>3.47183609008789</v>
       </c>
       <c r="H92" t="n">
         <v>9228</v>
@@ -3066,7 +3066,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G93" t="n">
-        <v>3.46315670013428</v>
+        <v>3.4631564617157</v>
       </c>
       <c r="H93" t="n">
         <v>250</v>
@@ -3095,7 +3095,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G94" t="n">
-        <v>3.41975855827332</v>
+        <v>3.41975879669189</v>
       </c>
       <c r="H94" t="n">
         <v>3029</v>
@@ -3124,7 +3124,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G95" t="n">
-        <v>3.51523399353027</v>
+        <v>3.51523423194885</v>
       </c>
       <c r="H95" t="n">
         <v>1936</v>
@@ -3240,7 +3240,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G99" t="n">
-        <v>3.59334993362427</v>
+        <v>3.59335017204285</v>
       </c>
       <c r="H99" t="n">
         <v>79600</v>
@@ -3269,7 +3269,7 @@
         <v>3.95499992370605</v>
       </c>
       <c r="G100" t="n">
-        <v>3.43277764320374</v>
+        <v>3.43277788162231</v>
       </c>
       <c r="H100" t="n">
         <v>9435</v>
@@ -3298,7 +3298,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G101" t="n">
-        <v>3.54127264022827</v>
+        <v>3.54127287864685</v>
       </c>
       <c r="H101" t="n">
         <v>4200</v>
@@ -3356,7 +3356,7 @@
         <v>4</v>
       </c>
       <c r="G103" t="n">
-        <v>3.47183585166931</v>
+        <v>3.47183609008789</v>
       </c>
       <c r="H103" t="n">
         <v>11798</v>
@@ -3414,7 +3414,7 @@
         <v>4</v>
       </c>
       <c r="G105" t="n">
-        <v>3.47183585166931</v>
+        <v>3.47183609008789</v>
       </c>
       <c r="H105" t="n">
         <v>5886</v>
@@ -3443,7 +3443,7 @@
         <v>4.03499984741211</v>
       </c>
       <c r="G106" t="n">
-        <v>3.50221467018127</v>
+        <v>3.5022144317627</v>
       </c>
       <c r="H106" t="n">
         <v>9593</v>
@@ -3472,7 +3472,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G107" t="n">
-        <v>3.51523399353027</v>
+        <v>3.51523423194885</v>
       </c>
       <c r="H107" t="n">
         <v>17133</v>
@@ -3559,7 +3559,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G110" t="n">
-        <v>3.64542746543884</v>
+        <v>3.64542770385742</v>
       </c>
       <c r="H110" t="n">
         <v>37685</v>
@@ -3588,7 +3588,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G111" t="n">
-        <v>3.64542746543884</v>
+        <v>3.64542770385742</v>
       </c>
       <c r="H111" t="n">
         <v>19204</v>
@@ -3617,7 +3617,7 @@
         <v>4.41499996185303</v>
       </c>
       <c r="G112" t="n">
-        <v>3.83203911781311</v>
+        <v>3.83203887939453</v>
       </c>
       <c r="H112" t="n">
         <v>30401</v>
@@ -3646,7 +3646,7 @@
         <v>4.5</v>
       </c>
       <c r="G113" t="n">
-        <v>3.9058153629303</v>
+        <v>3.90581512451172</v>
       </c>
       <c r="H113" t="n">
         <v>10114</v>
@@ -3675,7 +3675,7 @@
         <v>4.5</v>
       </c>
       <c r="G114" t="n">
-        <v>3.9058153629303</v>
+        <v>3.90581512451172</v>
       </c>
       <c r="H114" t="n">
         <v>36925</v>
@@ -3704,7 +3704,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G115" t="n">
-        <v>3.87109708786011</v>
+        <v>3.87109684944153</v>
       </c>
       <c r="H115" t="n">
         <v>4580</v>
@@ -3733,7 +3733,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G116" t="n">
-        <v>3.86241722106934</v>
+        <v>3.86241674423218</v>
       </c>
       <c r="H116" t="n">
         <v>17964</v>
@@ -3762,7 +3762,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G117" t="n">
-        <v>4.00997018814087</v>
+        <v>4.00997066497803</v>
       </c>
       <c r="H117" t="n">
         <v>10859</v>
@@ -3849,7 +3849,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G120" t="n">
-        <v>3.86241722106934</v>
+        <v>3.86241674423218</v>
       </c>
       <c r="H120" t="n">
         <v>34190</v>
@@ -3907,7 +3907,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G122" t="n">
-        <v>3.94053387641907</v>
+        <v>3.94053363800049</v>
       </c>
       <c r="H122" t="n">
         <v>5398</v>
@@ -3965,7 +3965,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G124" t="n">
-        <v>3.94921398162842</v>
+        <v>3.94921374320984</v>
       </c>
       <c r="H124" t="n">
         <v>5841</v>
@@ -3994,7 +3994,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G125" t="n">
-        <v>3.94921398162842</v>
+        <v>3.94921374320984</v>
       </c>
       <c r="H125" t="n">
         <v>21549</v>
@@ -4052,7 +4052,7 @@
         <v>4.88500022888184</v>
       </c>
       <c r="G127" t="n">
-        <v>4.23997926712036</v>
+        <v>4.23997974395752</v>
       </c>
       <c r="H127" t="n">
         <v>32038</v>
@@ -4081,7 +4081,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G128" t="n">
-        <v>4.37451314926147</v>
+        <v>4.37451267242432</v>
       </c>
       <c r="H128" t="n">
         <v>36739</v>
@@ -4255,7 +4255,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G134" t="n">
-        <v>4.24431896209717</v>
+        <v>4.24431943893433</v>
       </c>
       <c r="H134" t="n">
         <v>9475</v>
@@ -4284,7 +4284,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G135" t="n">
-        <v>4.24431896209717</v>
+        <v>4.24431943893433</v>
       </c>
       <c r="H135" t="n">
         <v>1852</v>
@@ -4342,7 +4342,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G137" t="n">
-        <v>4.14016437530518</v>
+        <v>4.14016485214233</v>
       </c>
       <c r="H137" t="n">
         <v>18698</v>
@@ -4371,7 +4371,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G138" t="n">
-        <v>4.16620397567749</v>
+        <v>4.16620349884033</v>
       </c>
       <c r="H138" t="n">
         <v>23142</v>
@@ -4429,7 +4429,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G140" t="n">
-        <v>4.51338624954224</v>
+        <v>4.51338672637939</v>
       </c>
       <c r="H140" t="n">
         <v>12739</v>
@@ -4487,7 +4487,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G142" t="n">
-        <v>4.35715436935425</v>
+        <v>4.35715389251709</v>
       </c>
       <c r="H142" t="n">
         <v>21331</v>
@@ -4574,7 +4574,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G145" t="n">
-        <v>4.51338624954224</v>
+        <v>4.51338672637939</v>
       </c>
       <c r="H145" t="n">
         <v>10888</v>
@@ -4603,7 +4603,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G146" t="n">
-        <v>4.54810523986816</v>
+        <v>4.54810476303101</v>
       </c>
       <c r="H146" t="n">
         <v>8672</v>
@@ -4690,7 +4690,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G149" t="n">
-        <v>4.54810523986816</v>
+        <v>4.54810476303101</v>
       </c>
       <c r="H149" t="n">
         <v>20634</v>
@@ -4748,7 +4748,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G151" t="n">
-        <v>4.54810523986816</v>
+        <v>4.54810476303101</v>
       </c>
       <c r="H151" t="n">
         <v>3706</v>
@@ -4777,7 +4777,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G152" t="n">
-        <v>4.51338624954224</v>
+        <v>4.51338672637939</v>
       </c>
       <c r="H152" t="n">
         <v>12525</v>
@@ -4980,7 +4980,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G159" t="n">
-        <v>4.09676599502563</v>
+        <v>4.09676647186279</v>
       </c>
       <c r="H159" t="n">
         <v>11440</v>
@@ -5009,7 +5009,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G160" t="n">
-        <v>4.06204795837402</v>
+        <v>4.06204843521118</v>
       </c>
       <c r="H160" t="n">
         <v>4897</v>
@@ -5038,7 +5038,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G161" t="n">
-        <v>4.04468822479248</v>
+        <v>4.04468870162964</v>
       </c>
       <c r="H161" t="n">
         <v>300</v>
@@ -5067,7 +5067,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G162" t="n">
-        <v>3.99261164665222</v>
+        <v>3.9926118850708</v>
       </c>
       <c r="H162" t="n">
         <v>1599</v>
@@ -5096,7 +5096,7 @@
         <v>4.24499988555908</v>
       </c>
       <c r="G163" t="n">
-        <v>3.684485912323</v>
+        <v>3.68448567390442</v>
       </c>
       <c r="H163" t="n">
         <v>8681</v>
@@ -5154,7 +5154,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G165" t="n">
-        <v>3.26352596282959</v>
+        <v>3.26352572441101</v>
       </c>
       <c r="H165" t="n">
         <v>12420</v>
@@ -5183,7 +5183,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G166" t="n">
-        <v>3.23748683929443</v>
+        <v>3.23748707771301</v>
       </c>
       <c r="H166" t="n">
         <v>4220</v>
@@ -5212,7 +5212,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G167" t="n">
-        <v>2.72539162635803</v>
+        <v>2.72539138793945</v>
       </c>
       <c r="H167" t="n">
         <v>16142</v>
@@ -5241,7 +5241,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G168" t="n">
-        <v>2.95974016189575</v>
+        <v>2.95974040031433</v>
       </c>
       <c r="H168" t="n">
         <v>11032</v>
@@ -5444,7 +5444,7 @@
         <v>3.72499990463257</v>
       </c>
       <c r="G175" t="n">
-        <v>3.23314714431763</v>
+        <v>3.23314690589905</v>
       </c>
       <c r="H175" t="n">
         <v>35922</v>
@@ -5531,7 +5531,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G178" t="n">
-        <v>3.28956437110901</v>
+        <v>3.28956460952759</v>
       </c>
       <c r="H178" t="n">
         <v>12475</v>
@@ -5589,7 +5589,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G180" t="n">
-        <v>3.31560325622559</v>
+        <v>3.31560349464417</v>
       </c>
       <c r="H180" t="n">
         <v>27302</v>
@@ -5618,7 +5618,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G181" t="n">
-        <v>3.30692362785339</v>
+        <v>3.30692386627197</v>
       </c>
       <c r="H181" t="n">
         <v>2000</v>
@@ -5647,7 +5647,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G182" t="n">
-        <v>3.28956437110901</v>
+        <v>3.28956460952759</v>
       </c>
       <c r="H182" t="n">
         <v>11896</v>
@@ -5763,7 +5763,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G186" t="n">
-        <v>3.22012782096863</v>
+        <v>3.22012805938721</v>
       </c>
       <c r="H186" t="n">
         <v>4810</v>
@@ -5821,7 +5821,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G188" t="n">
-        <v>3.29824423789978</v>
+        <v>3.2982439994812</v>
       </c>
       <c r="H188" t="n">
         <v>5632</v>
@@ -5879,7 +5879,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G190" t="n">
-        <v>3.18540978431702</v>
+        <v>3.18540954589844</v>
       </c>
       <c r="H190" t="n">
         <v>13689</v>
@@ -5966,7 +5966,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G193" t="n">
-        <v>3.29824423789978</v>
+        <v>3.2982439994812</v>
       </c>
       <c r="H193" t="n">
         <v>13631</v>
@@ -5995,7 +5995,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G194" t="n">
-        <v>3.29824423789978</v>
+        <v>3.2982439994812</v>
       </c>
       <c r="H194" t="n">
         <v>5341</v>
@@ -6111,7 +6111,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G198" t="n">
-        <v>3.59334993362427</v>
+        <v>3.59335017204285</v>
       </c>
       <c r="H198" t="n">
         <v>40730</v>
@@ -6169,7 +6169,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G200" t="n">
-        <v>3.48051595687866</v>
+        <v>3.48051571846008</v>
       </c>
       <c r="H200" t="n">
         <v>8475</v>
@@ -6227,7 +6227,7 @@
         <v>3.75</v>
       </c>
       <c r="G202" t="n">
-        <v>3.25484609603882</v>
+        <v>3.2548463344574</v>
       </c>
       <c r="H202" t="n">
         <v>25406</v>
@@ -6256,7 +6256,7 @@
         <v>3.75</v>
       </c>
       <c r="G203" t="n">
-        <v>3.25484609603882</v>
+        <v>3.2548463344574</v>
       </c>
       <c r="H203" t="n">
         <v>5500</v>
@@ -6314,7 +6314,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G205" t="n">
-        <v>3.29824423789978</v>
+        <v>3.2982439994812</v>
       </c>
       <c r="H205" t="n">
         <v>4357</v>
@@ -6343,7 +6343,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G206" t="n">
-        <v>3.31560325622559</v>
+        <v>3.31560349464417</v>
       </c>
       <c r="H206" t="n">
         <v>105630</v>
@@ -6372,7 +6372,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G207" t="n">
-        <v>3.37636065483093</v>
+        <v>3.37636089324951</v>
       </c>
       <c r="H207" t="n">
         <v>12630</v>
@@ -6401,7 +6401,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G208" t="n">
-        <v>3.30692362785339</v>
+        <v>3.30692386627197</v>
       </c>
       <c r="H208" t="n">
         <v>11449</v>
@@ -6430,7 +6430,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G209" t="n">
-        <v>3.24616670608521</v>
+        <v>3.24616646766663</v>
       </c>
       <c r="H209" t="n">
         <v>13675</v>
@@ -6488,7 +6488,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G211" t="n">
-        <v>3.29824423789978</v>
+        <v>3.2982439994812</v>
       </c>
       <c r="H211" t="n">
         <v>8606</v>
@@ -6604,7 +6604,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G215" t="n">
-        <v>3.26352596282959</v>
+        <v>3.26352572441101</v>
       </c>
       <c r="H215" t="n">
         <v>2689</v>
@@ -6662,7 +6662,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G217" t="n">
-        <v>3.29824423789978</v>
+        <v>3.2982439994812</v>
       </c>
       <c r="H217" t="n">
         <v>16383</v>
@@ -6720,7 +6720,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G219" t="n">
-        <v>3.29824423789978</v>
+        <v>3.2982439994812</v>
       </c>
       <c r="H219" t="n">
         <v>6884</v>
@@ -6749,7 +6749,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G220" t="n">
-        <v>3.26352596282959</v>
+        <v>3.26352572441101</v>
       </c>
       <c r="H220" t="n">
         <v>285</v>
@@ -6778,7 +6778,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G221" t="n">
-        <v>3.28956437110901</v>
+        <v>3.28956460952759</v>
       </c>
       <c r="H221" t="n">
         <v>8062</v>
@@ -6807,7 +6807,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G222" t="n">
-        <v>3.29824423789978</v>
+        <v>3.2982439994812</v>
       </c>
       <c r="H222" t="n">
         <v>4259</v>
@@ -6865,7 +6865,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G224" t="n">
-        <v>3.3850405216217</v>
+        <v>3.38504028320312</v>
       </c>
       <c r="H224" t="n">
         <v>2943</v>
@@ -6923,7 +6923,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G226" t="n">
-        <v>3.37636065483093</v>
+        <v>3.37636089324951</v>
       </c>
       <c r="H226" t="n">
         <v>19966</v>
@@ -6952,7 +6952,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G227" t="n">
-        <v>3.29824423789978</v>
+        <v>3.2982439994812</v>
       </c>
       <c r="H227" t="n">
         <v>6610</v>
@@ -7039,7 +7039,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G230" t="n">
-        <v>3.37636065483093</v>
+        <v>3.37636089324951</v>
       </c>
       <c r="H230" t="n">
         <v>4045</v>
@@ -7068,7 +7068,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G231" t="n">
-        <v>3.31560325622559</v>
+        <v>3.31560349464417</v>
       </c>
       <c r="H231" t="n">
         <v>5113</v>
@@ -7126,7 +7126,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G233" t="n">
-        <v>3.37636065483093</v>
+        <v>3.37636089324951</v>
       </c>
       <c r="H233" t="n">
         <v>111</v>
@@ -7155,7 +7155,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G234" t="n">
-        <v>3.37636065483093</v>
+        <v>3.37636089324951</v>
       </c>
       <c r="H234" t="n">
         <v>0</v>
@@ -7184,7 +7184,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G235" t="n">
-        <v>3.3242826461792</v>
+        <v>3.32428312301636</v>
       </c>
       <c r="H235" t="n">
         <v>800</v>
@@ -7213,7 +7213,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G236" t="n">
-        <v>3.3242826461792</v>
+        <v>3.32428312301636</v>
       </c>
       <c r="H236" t="n">
         <v>0</v>
@@ -7242,7 +7242,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G237" t="n">
-        <v>3.28956437110901</v>
+        <v>3.28956460952759</v>
       </c>
       <c r="H237" t="n">
         <v>451</v>
@@ -7271,7 +7271,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G238" t="n">
-        <v>3.23748683929443</v>
+        <v>3.23748707771301</v>
       </c>
       <c r="H238" t="n">
         <v>386</v>
@@ -7300,7 +7300,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G239" t="n">
-        <v>3.23748683929443</v>
+        <v>3.23748707771301</v>
       </c>
       <c r="H239" t="n">
         <v>0</v>
@@ -7329,7 +7329,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G240" t="n">
-        <v>3.29824423789978</v>
+        <v>3.2982439994812</v>
       </c>
       <c r="H240" t="n">
         <v>2500</v>
@@ -7387,7 +7387,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G242" t="n">
-        <v>3.28956437110901</v>
+        <v>3.28956460952759</v>
       </c>
       <c r="H242" t="n">
         <v>1</v>
@@ -7416,7 +7416,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G243" t="n">
-        <v>3.28956437110901</v>
+        <v>3.28956460952759</v>
       </c>
       <c r="H243" t="n">
         <v>0</v>
@@ -7503,7 +7503,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G246" t="n">
-        <v>3.29824423789978</v>
+        <v>3.2982439994812</v>
       </c>
       <c r="H246" t="n">
         <v>2471</v>
@@ -7532,7 +7532,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G247" t="n">
-        <v>3.24616670608521</v>
+        <v>3.24616646766663</v>
       </c>
       <c r="H247" t="n">
         <v>21876</v>
@@ -7561,7 +7561,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G248" t="n">
-        <v>3.24616670608521</v>
+        <v>3.24616646766663</v>
       </c>
       <c r="H248" t="n">
         <v>0</v>
@@ -7648,7 +7648,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G251" t="n">
-        <v>3.18540978431702</v>
+        <v>3.18540954589844</v>
       </c>
       <c r="H251" t="n">
         <v>6820</v>
@@ -7735,7 +7735,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G254" t="n">
-        <v>3.28956437110901</v>
+        <v>3.28956460952759</v>
       </c>
       <c r="H254" t="n">
         <v>2105</v>
@@ -7764,7 +7764,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G255" t="n">
-        <v>3.18540978431702</v>
+        <v>3.18540954589844</v>
       </c>
       <c r="H255" t="n">
         <v>1005</v>
@@ -7822,7 +7822,7 @@
         <v>3.75</v>
       </c>
       <c r="G257" t="n">
-        <v>3.25484609603882</v>
+        <v>3.2548463344574</v>
       </c>
       <c r="H257" t="n">
         <v>3790</v>
@@ -7851,7 +7851,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G258" t="n">
-        <v>3.36768126487732</v>
+        <v>3.36768102645874</v>
       </c>
       <c r="H258" t="n">
         <v>1100</v>
@@ -8025,7 +8025,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G264" t="n">
-        <v>3.13333201408386</v>
+        <v>3.13333177566528</v>
       </c>
       <c r="H264" t="n">
         <v>100</v>
@@ -8170,7 +8170,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G269" t="n">
-        <v>3.24616670608521</v>
+        <v>3.24616646766663</v>
       </c>
       <c r="H269" t="n">
         <v>750</v>
@@ -8228,7 +8228,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G271" t="n">
-        <v>3.13333201408386</v>
+        <v>3.13333177566528</v>
       </c>
       <c r="H271" t="n">
         <v>2533</v>
@@ -8286,7 +8286,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G273" t="n">
-        <v>3.02049732208252</v>
+        <v>3.0204975605011</v>
       </c>
       <c r="H273" t="n">
         <v>5743</v>
@@ -8344,7 +8344,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G275" t="n">
-        <v>2.96841979026794</v>
+        <v>2.96842002868652</v>
       </c>
       <c r="H275" t="n">
         <v>11722</v>
@@ -8402,7 +8402,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G277" t="n">
-        <v>3.02049732208252</v>
+        <v>3.0204975605011</v>
       </c>
       <c r="H277" t="n">
         <v>10072</v>
@@ -8460,7 +8460,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G279" t="n">
-        <v>2.99445843696594</v>
+        <v>2.99445867538452</v>
       </c>
       <c r="H279" t="n">
         <v>4694</v>
@@ -8489,7 +8489,7 @@
         <v>3.5</v>
       </c>
       <c r="G280" t="n">
-        <v>3.0378565788269</v>
+        <v>3.03785634040833</v>
       </c>
       <c r="H280" t="n">
         <v>105</v>
@@ -8518,7 +8518,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G281" t="n">
-        <v>3.06389546394348</v>
+        <v>3.0638952255249</v>
       </c>
       <c r="H281" t="n">
         <v>1883</v>
@@ -8547,7 +8547,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G282" t="n">
-        <v>3.06389546394348</v>
+        <v>3.0638952255249</v>
       </c>
       <c r="H282" t="n">
         <v>0</v>
@@ -8576,7 +8576,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G283" t="n">
-        <v>3.06389546394348</v>
+        <v>3.0638952255249</v>
       </c>
       <c r="H283" t="n">
         <v>1100</v>
@@ -8605,7 +8605,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G284" t="n">
-        <v>2.94238114356995</v>
+        <v>2.94238138198853</v>
       </c>
       <c r="H284" t="n">
         <v>2758</v>
@@ -8634,7 +8634,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G285" t="n">
-        <v>2.94238114356995</v>
+        <v>2.94238138198853</v>
       </c>
       <c r="H285" t="n">
         <v>20</v>
@@ -8692,7 +8692,7 @@
         <v>3.5</v>
       </c>
       <c r="G287" t="n">
-        <v>3.0378565788269</v>
+        <v>3.03785634040833</v>
       </c>
       <c r="H287" t="n">
         <v>3634</v>
@@ -8721,7 +8721,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G288" t="n">
-        <v>2.99445843696594</v>
+        <v>2.99445867538452</v>
       </c>
       <c r="H288" t="n">
         <v>1117</v>
@@ -8808,7 +8808,7 @@
         <v>3.5</v>
       </c>
       <c r="G291" t="n">
-        <v>3.0378565788269</v>
+        <v>3.03785634040833</v>
       </c>
       <c r="H291" t="n">
         <v>10</v>
@@ -8837,7 +8837,7 @@
         <v>3.5</v>
       </c>
       <c r="G292" t="n">
-        <v>3.0378565788269</v>
+        <v>3.03785634040833</v>
       </c>
       <c r="H292" t="n">
         <v>0</v>
@@ -8924,7 +8924,7 @@
         <v>3.5</v>
       </c>
       <c r="G295" t="n">
-        <v>3.0378565788269</v>
+        <v>3.03785634040833</v>
       </c>
       <c r="H295" t="n">
         <v>700</v>
@@ -9011,7 +9011,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G298" t="n">
-        <v>2.99445843696594</v>
+        <v>2.99445867538452</v>
       </c>
       <c r="H298" t="n">
         <v>6051</v>
@@ -9040,7 +9040,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G299" t="n">
-        <v>2.86426496505737</v>
+        <v>2.86426472663879</v>
       </c>
       <c r="H299" t="n">
         <v>18061</v>
@@ -9069,7 +9069,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G300" t="n">
-        <v>2.86426496505737</v>
+        <v>2.86426472663879</v>
       </c>
       <c r="H300" t="n">
         <v>0</v>
@@ -9098,7 +9098,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G301" t="n">
-        <v>2.86426496505737</v>
+        <v>2.86426472663879</v>
       </c>
       <c r="H301" t="n">
         <v>14192</v>
@@ -9127,7 +9127,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G302" t="n">
-        <v>2.95974016189575</v>
+        <v>2.95974040031433</v>
       </c>
       <c r="H302" t="n">
         <v>10987</v>
@@ -9156,7 +9156,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G303" t="n">
-        <v>2.8816237449646</v>
+        <v>2.88162398338318</v>
       </c>
       <c r="H303" t="n">
         <v>7318</v>
@@ -9185,7 +9185,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G304" t="n">
-        <v>2.87294411659241</v>
+        <v>2.87294459342957</v>
       </c>
       <c r="H304" t="n">
         <v>20000</v>
@@ -9214,7 +9214,7 @@
         <v>3.5</v>
       </c>
       <c r="G305" t="n">
-        <v>3.0378565788269</v>
+        <v>3.03785634040833</v>
       </c>
       <c r="H305" t="n">
         <v>28717</v>
@@ -9388,7 +9388,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G311" t="n">
-        <v>3.22012782096863</v>
+        <v>3.22012805938721</v>
       </c>
       <c r="H311" t="n">
         <v>688</v>
@@ -9417,7 +9417,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G312" t="n">
-        <v>3.22012782096863</v>
+        <v>3.22012805938721</v>
       </c>
       <c r="H312" t="n">
         <v>0</v>
@@ -9533,7 +9533,7 @@
         <v>3.75</v>
       </c>
       <c r="G316" t="n">
-        <v>3.25484609603882</v>
+        <v>3.2548463344574</v>
       </c>
       <c r="H316" t="n">
         <v>2505</v>
@@ -9649,7 +9649,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G320" t="n">
-        <v>3.20276880264282</v>
+        <v>3.20276856422424</v>
       </c>
       <c r="H320" t="n">
         <v>354</v>
@@ -9997,7 +9997,7 @@
         <v>3.5</v>
       </c>
       <c r="G332" t="n">
-        <v>3.0378565788269</v>
+        <v>3.03785634040833</v>
       </c>
       <c r="H332" t="n">
         <v>2958</v>
@@ -10055,7 +10055,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G334" t="n">
-        <v>3.15069150924683</v>
+        <v>3.15069127082825</v>
       </c>
       <c r="H334" t="n">
         <v>1330</v>
@@ -10084,7 +10084,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G335" t="n">
-        <v>3.20276880264282</v>
+        <v>3.20276856422424</v>
       </c>
       <c r="H335" t="n">
         <v>2012</v>
@@ -10113,7 +10113,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G336" t="n">
-        <v>3.20276880264282</v>
+        <v>3.20276856422424</v>
       </c>
       <c r="H336" t="n">
         <v>2020</v>
@@ -10142,7 +10142,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G337" t="n">
-        <v>3.20276880264282</v>
+        <v>3.20276856422424</v>
       </c>
       <c r="H337" t="n">
         <v>0</v>
@@ -10258,7 +10258,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G341" t="n">
-        <v>3.20276880264282</v>
+        <v>3.20276856422424</v>
       </c>
       <c r="H341" t="n">
         <v>2073</v>
@@ -10316,7 +10316,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G343" t="n">
-        <v>3.15069150924683</v>
+        <v>3.15069127082825</v>
       </c>
       <c r="H343" t="n">
         <v>3072</v>
@@ -10345,7 +10345,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G344" t="n">
-        <v>3.15069150924683</v>
+        <v>3.15069127082825</v>
       </c>
       <c r="H344" t="n">
         <v>8220</v>
@@ -10374,7 +10374,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G345" t="n">
-        <v>3.22012782096863</v>
+        <v>3.22012805938721</v>
       </c>
       <c r="H345" t="n">
         <v>3873</v>
@@ -10432,7 +10432,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G347" t="n">
-        <v>3.31560325622559</v>
+        <v>3.31560349464417</v>
       </c>
       <c r="H347" t="n">
         <v>11800</v>
@@ -10490,7 +10490,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G349" t="n">
-        <v>3.31560325622559</v>
+        <v>3.31560349464417</v>
       </c>
       <c r="H349" t="n">
         <v>1269</v>
@@ -10519,7 +10519,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G350" t="n">
-        <v>3.36768126487732</v>
+        <v>3.36768102645874</v>
       </c>
       <c r="H350" t="n">
         <v>10</v>
@@ -10548,7 +10548,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G351" t="n">
-        <v>3.31560325622559</v>
+        <v>3.31560349464417</v>
       </c>
       <c r="H351" t="n">
         <v>1729</v>
@@ -10606,7 +10606,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G353" t="n">
-        <v>3.28956437110901</v>
+        <v>3.28956460952759</v>
       </c>
       <c r="H353" t="n">
         <v>300</v>
@@ -10664,7 +10664,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G355" t="n">
-        <v>3.30692362785339</v>
+        <v>3.30692386627197</v>
       </c>
       <c r="H355" t="n">
         <v>20</v>
@@ -10751,7 +10751,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G358" t="n">
-        <v>3.37636065483093</v>
+        <v>3.37636089324951</v>
       </c>
       <c r="H358" t="n">
         <v>800</v>
@@ -10780,7 +10780,7 @@
         <v>4</v>
       </c>
       <c r="G359" t="n">
-        <v>3.47183585166931</v>
+        <v>3.47183609008789</v>
       </c>
       <c r="H359" t="n">
         <v>3169</v>
@@ -10809,7 +10809,7 @@
         <v>4</v>
       </c>
       <c r="G360" t="n">
-        <v>3.47183585166931</v>
+        <v>3.47183609008789</v>
       </c>
       <c r="H360" t="n">
         <v>12</v>
@@ -10838,7 +10838,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G361" t="n">
-        <v>3.46304655075073</v>
+        <v>3.46304678916931</v>
       </c>
       <c r="H361" t="n">
         <v>6479</v>
@@ -10867,7 +10867,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G362" t="n">
-        <v>3.52457308769226</v>
+        <v>3.52457284927368</v>
       </c>
       <c r="H362" t="n">
         <v>1633</v>
@@ -10925,7 +10925,7 @@
         <v>4</v>
       </c>
       <c r="G364" t="n">
-        <v>3.51578307151794</v>
+        <v>3.51578330993652</v>
       </c>
       <c r="H364" t="n">
         <v>16056</v>
@@ -11012,7 +11012,7 @@
         <v>4</v>
       </c>
       <c r="G367" t="n">
-        <v>3.51578307151794</v>
+        <v>3.51578330993652</v>
       </c>
       <c r="H367" t="n">
         <v>8651</v>
@@ -11041,7 +11041,7 @@
         <v>4</v>
       </c>
       <c r="G368" t="n">
-        <v>3.51578307151794</v>
+        <v>3.51578330993652</v>
       </c>
       <c r="H368" t="n">
         <v>6801</v>
@@ -11070,7 +11070,7 @@
         <v>4</v>
       </c>
       <c r="G369" t="n">
-        <v>3.51578307151794</v>
+        <v>3.51578330993652</v>
       </c>
       <c r="H369" t="n">
         <v>0</v>
@@ -11099,7 +11099,7 @@
         <v>4</v>
       </c>
       <c r="G370" t="n">
-        <v>3.51578307151794</v>
+        <v>3.51578330993652</v>
       </c>
       <c r="H370" t="n">
         <v>0</v>
@@ -11128,7 +11128,7 @@
         <v>4</v>
       </c>
       <c r="G371" t="n">
-        <v>3.51578307151794</v>
+        <v>3.51578330993652</v>
       </c>
       <c r="H371" t="n">
         <v>0</v>
@@ -11157,7 +11157,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G372" t="n">
-        <v>3.57730960845947</v>
+        <v>3.57730937004089</v>
       </c>
       <c r="H372" t="n">
         <v>5500</v>
@@ -11186,7 +11186,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G373" t="n">
-        <v>3.77946734428406</v>
+        <v>3.77946710586548</v>
       </c>
       <c r="H373" t="n">
         <v>36941</v>
@@ -11215,7 +11215,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G374" t="n">
-        <v>3.85857200622559</v>
+        <v>3.85857224464417</v>
       </c>
       <c r="H374" t="n">
         <v>3601</v>
@@ -11244,7 +11244,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G375" t="n">
-        <v>3.80583524703979</v>
+        <v>3.80583548545837</v>
       </c>
       <c r="H375" t="n">
         <v>1180</v>
@@ -11389,7 +11389,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G380" t="n">
-        <v>3.99041390419006</v>
+        <v>3.99041366577148</v>
       </c>
       <c r="H380" t="n">
         <v>6050</v>
@@ -11418,7 +11418,7 @@
         <v>4.5</v>
       </c>
       <c r="G381" t="n">
-        <v>3.95525622367859</v>
+        <v>3.95525598526001</v>
       </c>
       <c r="H381" t="n">
         <v>11250</v>
@@ -11447,7 +11447,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G382" t="n">
-        <v>3.92888784408569</v>
+        <v>3.92888736724854</v>
       </c>
       <c r="H382" t="n">
         <v>12048</v>
@@ -11476,7 +11476,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G383" t="n">
-        <v>3.92009830474854</v>
+        <v>3.92009806632996</v>
       </c>
       <c r="H383" t="n">
         <v>30</v>
@@ -11505,7 +11505,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G384" t="n">
-        <v>3.77946734428406</v>
+        <v>3.77946710586548</v>
       </c>
       <c r="H384" t="n">
         <v>4161</v>
@@ -11534,7 +11534,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G385" t="n">
-        <v>3.77946734428406</v>
+        <v>3.77946710586548</v>
       </c>
       <c r="H385" t="n">
         <v>2380</v>
@@ -11592,7 +11592,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G387" t="n">
-        <v>3.42788910865784</v>
+        <v>3.42788887023926</v>
       </c>
       <c r="H387" t="n">
         <v>24073</v>
@@ -11621,7 +11621,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G388" t="n">
-        <v>3.550940990448</v>
+        <v>3.55094122886658</v>
       </c>
       <c r="H388" t="n">
         <v>7442</v>
@@ -11679,7 +11679,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G390" t="n">
-        <v>3.69157218933105</v>
+        <v>3.69157195091248</v>
       </c>
       <c r="H390" t="n">
         <v>9963</v>
@@ -11708,7 +11708,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G391" t="n">
-        <v>3.52457308769226</v>
+        <v>3.52457284927368</v>
       </c>
       <c r="H391" t="n">
         <v>14867</v>
@@ -11737,7 +11737,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G392" t="n">
-        <v>3.62125658988953</v>
+        <v>3.62125682830811</v>
       </c>
       <c r="H392" t="n">
         <v>15062</v>
@@ -11824,7 +11824,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G395" t="n">
-        <v>3.74430966377258</v>
+        <v>3.74430918693542</v>
       </c>
       <c r="H395" t="n">
         <v>15241</v>
@@ -11853,7 +11853,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G396" t="n">
-        <v>3.77946734428406</v>
+        <v>3.77946710586548</v>
       </c>
       <c r="H396" t="n">
         <v>6483</v>
@@ -11911,7 +11911,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G398" t="n">
-        <v>3.77946734428406</v>
+        <v>3.77946710586548</v>
       </c>
       <c r="H398" t="n">
         <v>83</v>
@@ -11969,7 +11969,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G400" t="n">
-        <v>3.62125658988953</v>
+        <v>3.62125682830811</v>
       </c>
       <c r="H400" t="n">
         <v>1948</v>
@@ -12143,7 +12143,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G406" t="n">
-        <v>3.84099316596985</v>
+        <v>3.84099340438843</v>
       </c>
       <c r="H406" t="n">
         <v>7000</v>
@@ -12201,7 +12201,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G408" t="n">
-        <v>3.78825640678406</v>
+        <v>3.78825616836548</v>
       </c>
       <c r="H408" t="n">
         <v>9728</v>
@@ -12230,7 +12230,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G409" t="n">
-        <v>4.04315090179443</v>
+        <v>4.04315137863159</v>
       </c>
       <c r="H409" t="n">
         <v>11444</v>
@@ -12259,7 +12259,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G410" t="n">
-        <v>3.99920415878296</v>
+        <v>3.99920344352722</v>
       </c>
       <c r="H410" t="n">
         <v>13066</v>
@@ -12288,7 +12288,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G411" t="n">
-        <v>3.99920415878296</v>
+        <v>3.99920344352722</v>
       </c>
       <c r="H411" t="n">
         <v>3045</v>
@@ -12346,7 +12346,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G413" t="n">
-        <v>4.06072950363159</v>
+        <v>4.06072998046875</v>
       </c>
       <c r="H413" t="n">
         <v>1119</v>
@@ -12375,7 +12375,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G414" t="n">
-        <v>4.04315090179443</v>
+        <v>4.04315137863159</v>
       </c>
       <c r="H414" t="n">
         <v>4777</v>
@@ -12404,7 +12404,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G415" t="n">
-        <v>4.04315090179443</v>
+        <v>4.04315137863159</v>
       </c>
       <c r="H415" t="n">
         <v>0</v>
@@ -12433,7 +12433,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G416" t="n">
-        <v>3.99920415878296</v>
+        <v>3.99920344352722</v>
       </c>
       <c r="H416" t="n">
         <v>20150</v>
@@ -12462,7 +12462,7 @@
         <v>4.59000015258789</v>
       </c>
       <c r="G417" t="n">
-        <v>4.03436136245728</v>
+        <v>4.03436183929443</v>
       </c>
       <c r="H417" t="n">
         <v>6334</v>
@@ -12491,7 +12491,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G418" t="n">
-        <v>4.08709812164307</v>
+        <v>4.08709859848022</v>
       </c>
       <c r="H418" t="n">
         <v>6771</v>
@@ -12520,7 +12520,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G419" t="n">
-        <v>4.14862394332886</v>
+        <v>4.14862442016602</v>
       </c>
       <c r="H419" t="n">
         <v>3061</v>
@@ -12549,7 +12549,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G420" t="n">
-        <v>4.30683422088623</v>
+        <v>4.30683469772339</v>
       </c>
       <c r="H420" t="n">
         <v>32975</v>
@@ -12665,7 +12665,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G424" t="n">
-        <v>4.30683422088623</v>
+        <v>4.30683469772339</v>
       </c>
       <c r="H424" t="n">
         <v>1866</v>
@@ -12694,7 +12694,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G425" t="n">
-        <v>4.29804468154907</v>
+        <v>4.29804515838623</v>
       </c>
       <c r="H425" t="n">
         <v>2886</v>
@@ -12752,7 +12752,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G427" t="n">
-        <v>4.34199190139771</v>
+        <v>4.34199237823486</v>
       </c>
       <c r="H427" t="n">
         <v>6045</v>
@@ -12810,7 +12810,7 @@
         <v>4.75</v>
       </c>
       <c r="G429" t="n">
-        <v>4.17499303817749</v>
+        <v>4.17499256134033</v>
       </c>
       <c r="H429" t="n">
         <v>10</v>
@@ -12926,7 +12926,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G433" t="n">
-        <v>4.32441377639771</v>
+        <v>4.32441329956055</v>
       </c>
       <c r="H433" t="n">
         <v>1529</v>
@@ -12955,7 +12955,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G434" t="n">
-        <v>4.22772884368896</v>
+        <v>4.22772932052612</v>
       </c>
       <c r="H434" t="n">
         <v>5368</v>
@@ -12984,7 +12984,7 @@
         <v>4.75</v>
       </c>
       <c r="G435" t="n">
-        <v>4.17499303817749</v>
+        <v>4.17499256134033</v>
       </c>
       <c r="H435" t="n">
         <v>1500</v>
@@ -13100,7 +13100,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G439" t="n">
-        <v>4.38593912124634</v>
+        <v>4.3859395980835</v>
       </c>
       <c r="H439" t="n">
         <v>2700</v>
@@ -13129,7 +13129,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G440" t="n">
-        <v>4.38593912124634</v>
+        <v>4.3859395980835</v>
       </c>
       <c r="H440" t="n">
         <v>100</v>
@@ -13158,7 +13158,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G441" t="n">
-        <v>4.30683422088623</v>
+        <v>4.30683469772339</v>
       </c>
       <c r="H441" t="n">
         <v>14413</v>
@@ -13187,7 +13187,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G442" t="n">
-        <v>4.30683422088623</v>
+        <v>4.30683469772339</v>
       </c>
       <c r="H442" t="n">
         <v>5600</v>
@@ -13245,7 +13245,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G444" t="n">
-        <v>4.34199190139771</v>
+        <v>4.34199237823486</v>
       </c>
       <c r="H444" t="n">
         <v>20</v>
@@ -13303,7 +13303,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G446" t="n">
-        <v>4.34199190139771</v>
+        <v>4.34199237823486</v>
       </c>
       <c r="H446" t="n">
         <v>1000</v>
@@ -13332,7 +13332,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G447" t="n">
-        <v>4.38593912124634</v>
+        <v>4.3859395980835</v>
       </c>
       <c r="H447" t="n">
         <v>20</v>
@@ -13448,7 +13448,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G451" t="n">
-        <v>4.30683422088623</v>
+        <v>4.30683469772339</v>
       </c>
       <c r="H451" t="n">
         <v>600</v>
@@ -13535,7 +13535,7 @@
         <v>4.75</v>
       </c>
       <c r="G454" t="n">
-        <v>4.17499303817749</v>
+        <v>4.17499256134033</v>
       </c>
       <c r="H454" t="n">
         <v>220</v>
@@ -13564,7 +13564,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G455" t="n">
-        <v>4.11346626281738</v>
+        <v>4.11346673965454</v>
       </c>
       <c r="H455" t="n">
         <v>1631</v>
@@ -13593,7 +13593,7 @@
         <v>4.75</v>
       </c>
       <c r="G456" t="n">
-        <v>4.17499303817749</v>
+        <v>4.17499256134033</v>
       </c>
       <c r="H456" t="n">
         <v>7</v>
@@ -13622,7 +13622,7 @@
         <v>4.75</v>
       </c>
       <c r="G457" t="n">
-        <v>4.17499303817749</v>
+        <v>4.17499256134033</v>
       </c>
       <c r="H457" t="n">
         <v>0</v>
@@ -13651,7 +13651,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G458" t="n">
-        <v>4.05193996429443</v>
+        <v>4.05194044113159</v>
       </c>
       <c r="H458" t="n">
         <v>1015</v>
@@ -13767,7 +13767,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G462" t="n">
-        <v>4.08709812164307</v>
+        <v>4.08709859848022</v>
       </c>
       <c r="H462" t="n">
         <v>155</v>
@@ -13796,7 +13796,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G463" t="n">
-        <v>4.14862394332886</v>
+        <v>4.14862442016602</v>
       </c>
       <c r="H463" t="n">
         <v>13</v>
@@ -14202,7 +14202,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G477" t="n">
-        <v>4.75483369827271</v>
+        <v>4.75483322143555</v>
       </c>
       <c r="H477" t="n">
         <v>3810</v>
@@ -14347,7 +14347,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G482" t="n">
-        <v>4.54272222518921</v>
+        <v>4.54272174835205</v>
       </c>
       <c r="H482" t="n">
         <v>600</v>
@@ -14463,7 +14463,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G486" t="n">
-        <v>4.37479972839355</v>
+        <v>4.37480020523071</v>
       </c>
       <c r="H486" t="n">
         <v>1753</v>
@@ -14724,7 +14724,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G495" t="n">
-        <v>4.17152643203735</v>
+        <v>4.17152690887451</v>
       </c>
       <c r="H495" t="n">
         <v>3325</v>
@@ -14782,7 +14782,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G497" t="n">
-        <v>4.03011894226074</v>
+        <v>4.03011846542358</v>
       </c>
       <c r="H497" t="n">
         <v>4388</v>
@@ -14811,7 +14811,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G498" t="n">
-        <v>4.03011894226074</v>
+        <v>4.03011846542358</v>
       </c>
       <c r="H498" t="n">
         <v>18707</v>
@@ -14898,7 +14898,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G501" t="n">
-        <v>4.02128171920776</v>
+        <v>4.02128124237061</v>
       </c>
       <c r="H501" t="n">
         <v>9940</v>
@@ -14927,7 +14927,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G502" t="n">
-        <v>4.08314657211304</v>
+        <v>4.0831470489502</v>
       </c>
       <c r="H502" t="n">
         <v>25</v>
@@ -15449,7 +15449,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G520" t="n">
-        <v>4.4896936416626</v>
+        <v>4.48969411849976</v>
       </c>
       <c r="H520" t="n">
         <v>1048</v>
@@ -15478,7 +15478,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G521" t="n">
-        <v>4.52504539489746</v>
+        <v>4.52504587173462</v>
       </c>
       <c r="H521" t="n">
         <v>25920</v>
@@ -15739,7 +15739,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G530" t="n">
-        <v>4.52504539489746</v>
+        <v>4.52504587173462</v>
       </c>
       <c r="H530" t="n">
         <v>700</v>
@@ -15768,7 +15768,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G531" t="n">
-        <v>4.52504539489746</v>
+        <v>4.52504587173462</v>
       </c>
       <c r="H531" t="n">
         <v>0</v>
@@ -15826,7 +15826,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G533" t="n">
-        <v>4.33061027526855</v>
+        <v>4.33061075210571</v>
       </c>
       <c r="H533" t="n">
         <v>1000</v>
@@ -16000,7 +16000,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G539" t="n">
-        <v>4.41015148162842</v>
+        <v>4.41015195846558</v>
       </c>
       <c r="H539" t="n">
         <v>870</v>
@@ -16116,7 +16116,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G543" t="n">
-        <v>4.38363885879517</v>
+        <v>4.38363838195801</v>
       </c>
       <c r="H543" t="n">
         <v>902</v>
@@ -16319,7 +16319,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G550" t="n">
-        <v>4.21571636199951</v>
+        <v>4.21571683883667</v>
       </c>
       <c r="H550" t="n">
         <v>3340</v>
@@ -16493,7 +16493,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G556" t="n">
-        <v>4.1184983253479</v>
+        <v>4.11849880218506</v>
       </c>
       <c r="H556" t="n">
         <v>15801</v>
@@ -16522,7 +16522,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G557" t="n">
-        <v>4.0743088722229</v>
+        <v>4.07430934906006</v>
       </c>
       <c r="H557" t="n">
         <v>4755</v>
@@ -16638,7 +16638,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G561" t="n">
-        <v>4.15385055541992</v>
+        <v>4.15385103225708</v>
       </c>
       <c r="H561" t="n">
         <v>11912</v>
@@ -16696,7 +16696,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G563" t="n">
-        <v>4.29525804519653</v>
+        <v>4.29525852203369</v>
       </c>
       <c r="H563" t="n">
         <v>16695</v>
@@ -16725,7 +16725,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G564" t="n">
-        <v>4.33061027526855</v>
+        <v>4.33061075210571</v>
       </c>
       <c r="H564" t="n">
         <v>6148</v>
@@ -16754,7 +16754,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G565" t="n">
-        <v>4.33061027526855</v>
+        <v>4.33061075210571</v>
       </c>
       <c r="H565" t="n">
         <v>2408</v>
@@ -17102,7 +17102,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G577" t="n">
-        <v>4.91391706466675</v>
+        <v>4.91391658782959</v>
       </c>
       <c r="H577" t="n">
         <v>7024</v>
@@ -17131,7 +17131,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G578" t="n">
-        <v>4.96694469451904</v>
+        <v>4.9669451713562</v>
       </c>
       <c r="H578" t="n">
         <v>3512</v>
@@ -17305,7 +17305,7 @@
         <v>6.03999996185303</v>
       </c>
       <c r="G584" t="n">
-        <v>5.33813953399658</v>
+        <v>5.33814001083374</v>
       </c>
       <c r="H584" t="n">
         <v>12438</v>
@@ -17421,7 +17421,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G588" t="n">
-        <v>5.70933485031128</v>
+        <v>5.70933532714844</v>
       </c>
       <c r="H588" t="n">
         <v>1075</v>
@@ -17508,7 +17508,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G591" t="n">
-        <v>5.63863182067871</v>
+        <v>5.63863134384155</v>
       </c>
       <c r="H591" t="n">
         <v>4654</v>
@@ -17566,7 +17566,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G593" t="n">
-        <v>5.56792783737183</v>
+        <v>5.56792736053467</v>
       </c>
       <c r="H593" t="n">
         <v>3180</v>
@@ -17595,7 +17595,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G594" t="n">
-        <v>5.56792783737183</v>
+        <v>5.56792736053467</v>
       </c>
       <c r="H594" t="n">
         <v>3910</v>
@@ -17769,7 +17769,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G600" t="n">
-        <v>5.72701120376587</v>
+        <v>5.72701072692871</v>
       </c>
       <c r="H600" t="n">
         <v>9122</v>
@@ -17914,7 +17914,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G605" t="n">
-        <v>5.72701120376587</v>
+        <v>5.72701072692871</v>
       </c>
       <c r="H605" t="n">
         <v>1318</v>
@@ -17943,7 +17943,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G606" t="n">
-        <v>5.72701120376587</v>
+        <v>5.72701072692871</v>
       </c>
       <c r="H606" t="n">
         <v>11320</v>
@@ -18030,7 +18030,7 @@
         <v>6.42000007629395</v>
       </c>
       <c r="G609" t="n">
-        <v>5.67398405075073</v>
+        <v>5.67398357391357</v>
       </c>
       <c r="H609" t="n">
         <v>1520</v>
@@ -18059,7 +18059,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G610" t="n">
-        <v>5.70933485031128</v>
+        <v>5.70933532714844</v>
       </c>
       <c r="H610" t="n">
         <v>2183</v>
@@ -18088,7 +18088,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G611" t="n">
-        <v>5.72701120376587</v>
+        <v>5.72701072692871</v>
       </c>
       <c r="H611" t="n">
         <v>6700</v>
@@ -18117,7 +18117,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G612" t="n">
-        <v>5.72701120376587</v>
+        <v>5.72701072692871</v>
       </c>
       <c r="H612" t="n">
         <v>280</v>
@@ -18233,7 +18233,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G616" t="n">
-        <v>5.88609457015991</v>
+        <v>5.88609504699707</v>
       </c>
       <c r="H616" t="n">
         <v>1889</v>
@@ -18407,7 +18407,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G622" t="n">
-        <v>5.39116811752319</v>
+        <v>5.39116764068604</v>
       </c>
       <c r="H622" t="n">
         <v>10704</v>
@@ -18581,7 +18581,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G628" t="n">
-        <v>5.88609457015991</v>
+        <v>5.88609504699707</v>
       </c>
       <c r="H628" t="n">
         <v>1335</v>
@@ -18668,7 +18668,7 @@
         <v>6.78000020980835</v>
       </c>
       <c r="G631" t="n">
-        <v>5.99215078353882</v>
+        <v>5.99215126037598</v>
       </c>
       <c r="H631" t="n">
         <v>200</v>
@@ -18697,7 +18697,7 @@
         <v>6.78000020980835</v>
       </c>
       <c r="G632" t="n">
-        <v>5.99215078353882</v>
+        <v>5.99215126037598</v>
       </c>
       <c r="H632" t="n">
         <v>0</v>
@@ -18726,7 +18726,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G633" t="n">
-        <v>5.83306741714478</v>
+        <v>5.83306694030762</v>
       </c>
       <c r="H633" t="n">
         <v>2617</v>
@@ -18755,7 +18755,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G634" t="n">
-        <v>5.83306741714478</v>
+        <v>5.83306694030762</v>
       </c>
       <c r="H634" t="n">
         <v>0</v>
@@ -18784,7 +18784,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G635" t="n">
-        <v>5.83306741714478</v>
+        <v>5.83306694030762</v>
       </c>
       <c r="H635" t="n">
         <v>200</v>
@@ -18813,7 +18813,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G636" t="n">
-        <v>5.70933485031128</v>
+        <v>5.70933532714844</v>
       </c>
       <c r="H636" t="n">
         <v>250</v>
@@ -18871,7 +18871,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G638" t="n">
-        <v>5.63863182067871</v>
+        <v>5.63863134384155</v>
       </c>
       <c r="H638" t="n">
         <v>3872</v>
@@ -18929,7 +18929,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G640" t="n">
-        <v>5.70933485031128</v>
+        <v>5.70933532714844</v>
       </c>
       <c r="H640" t="n">
         <v>150</v>
@@ -18958,7 +18958,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G641" t="n">
-        <v>5.79771518707275</v>
+        <v>5.7977147102356</v>
       </c>
       <c r="H641" t="n">
         <v>258</v>
@@ -18987,7 +18987,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G642" t="n">
-        <v>5.79771518707275</v>
+        <v>5.7977147102356</v>
       </c>
       <c r="H642" t="n">
         <v>1057</v>
@@ -19132,7 +19132,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G647" t="n">
-        <v>5.3734917640686</v>
+        <v>5.37349224090576</v>
       </c>
       <c r="H647" t="n">
         <v>1250</v>
@@ -19190,7 +19190,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G649" t="n">
-        <v>5.39116811752319</v>
+        <v>5.39116764068604</v>
       </c>
       <c r="H649" t="n">
         <v>2460</v>
@@ -19219,7 +19219,7 @@
         <v>6</v>
       </c>
       <c r="G650" t="n">
-        <v>5.30278778076172</v>
+        <v>5.30278825759888</v>
       </c>
       <c r="H650" t="n">
         <v>2718</v>
@@ -19480,7 +19480,7 @@
         <v>6</v>
       </c>
       <c r="G659" t="n">
-        <v>5.30278778076172</v>
+        <v>5.30278825759888</v>
       </c>
       <c r="H659" t="n">
         <v>11330</v>
@@ -19509,7 +19509,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G660" t="n">
-        <v>5.23208475112915</v>
+        <v>5.23208427429199</v>
       </c>
       <c r="H660" t="n">
         <v>16216</v>
@@ -19625,7 +19625,7 @@
         <v>6</v>
       </c>
       <c r="G664" t="n">
-        <v>5.30278778076172</v>
+        <v>5.30278825759888</v>
       </c>
       <c r="H664" t="n">
         <v>7582</v>
@@ -19683,7 +19683,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G666" t="n">
-        <v>4.71948194503784</v>
+        <v>4.71948146820068</v>
       </c>
       <c r="H666" t="n">
         <v>18954</v>
@@ -19770,7 +19770,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G669" t="n">
-        <v>4.75483369827271</v>
+        <v>4.75483322143555</v>
       </c>
       <c r="H669" t="n">
         <v>1824</v>
@@ -19799,7 +19799,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G670" t="n">
-        <v>4.71948194503784</v>
+        <v>4.71948146820068</v>
       </c>
       <c r="H670" t="n">
         <v>875</v>
@@ -19944,7 +19944,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G675" t="n">
-        <v>4.33061027526855</v>
+        <v>4.33061075210571</v>
       </c>
       <c r="H675" t="n">
         <v>4500</v>
@@ -20031,7 +20031,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G678" t="n">
-        <v>4.33061027526855</v>
+        <v>4.33061075210571</v>
       </c>
       <c r="H678" t="n">
         <v>2456</v>
@@ -20147,7 +20147,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G682" t="n">
-        <v>4.71948194503784</v>
+        <v>4.71948146820068</v>
       </c>
       <c r="H682" t="n">
         <v>13546</v>
@@ -20321,7 +20321,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G688" t="n">
-        <v>4.54272222518921</v>
+        <v>4.54272174835205</v>
       </c>
       <c r="H688" t="n">
         <v>650</v>
@@ -20350,7 +20350,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G689" t="n">
-        <v>4.75483369827271</v>
+        <v>4.75483322143555</v>
       </c>
       <c r="H689" t="n">
         <v>2400</v>
@@ -20437,7 +20437,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G692" t="n">
-        <v>4.87856531143188</v>
+        <v>4.87856483459473</v>
       </c>
       <c r="H692" t="n">
         <v>314</v>
@@ -20466,7 +20466,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G693" t="n">
-        <v>4.87856531143188</v>
+        <v>4.87856483459473</v>
       </c>
       <c r="H693" t="n">
         <v>0</v>
@@ -20495,7 +20495,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G694" t="n">
-        <v>4.93159246444702</v>
+        <v>4.93159294128418</v>
       </c>
       <c r="H694" t="n">
         <v>1580</v>
@@ -20524,7 +20524,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G695" t="n">
-        <v>4.87856531143188</v>
+        <v>4.87856483459473</v>
       </c>
       <c r="H695" t="n">
         <v>4531</v>
@@ -20553,7 +20553,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G696" t="n">
-        <v>4.96694469451904</v>
+        <v>4.9669451713562</v>
       </c>
       <c r="H696" t="n">
         <v>1712</v>
@@ -20669,7 +20669,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G700" t="n">
-        <v>4.75483369827271</v>
+        <v>4.75483322143555</v>
       </c>
       <c r="H700" t="n">
         <v>1074</v>
@@ -20698,7 +20698,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G701" t="n">
-        <v>4.75483369827271</v>
+        <v>4.75483322143555</v>
       </c>
       <c r="H701" t="n">
         <v>1300</v>
@@ -20756,7 +20756,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G703" t="n">
-        <v>5.03764867782593</v>
+        <v>5.03764915466309</v>
       </c>
       <c r="H703" t="n">
         <v>303</v>
@@ -20785,7 +20785,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G704" t="n">
-        <v>5.03764867782593</v>
+        <v>5.03764915466309</v>
       </c>
       <c r="H704" t="n">
         <v>0</v>
@@ -20814,7 +20814,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G705" t="n">
-        <v>5.14370441436768</v>
+        <v>5.14370489120483</v>
       </c>
       <c r="H705" t="n">
         <v>60299</v>
@@ -20872,7 +20872,7 @@
         <v>5.8600001335144</v>
       </c>
       <c r="G707" t="n">
-        <v>5.17905616760254</v>
+        <v>5.1790566444397</v>
       </c>
       <c r="H707" t="n">
         <v>1856</v>
@@ -20901,7 +20901,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G708" t="n">
-        <v>4.98462057113647</v>
+        <v>4.98462104797363</v>
       </c>
       <c r="H708" t="n">
         <v>1299</v>
@@ -20988,7 +20988,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G711" t="n">
-        <v>5.14370441436768</v>
+        <v>5.14370489120483</v>
       </c>
       <c r="H711" t="n">
         <v>6657</v>
@@ -21017,7 +21017,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G712" t="n">
-        <v>5.14370441436768</v>
+        <v>5.14370489120483</v>
       </c>
       <c r="H712" t="n">
         <v>0</v>
@@ -21104,7 +21104,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G715" t="n">
-        <v>5.14370441436768</v>
+        <v>5.14370489120483</v>
       </c>
       <c r="H715" t="n">
         <v>3046</v>
@@ -21133,7 +21133,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G716" t="n">
-        <v>5.03764867782593</v>
+        <v>5.03764915466309</v>
       </c>
       <c r="H716" t="n">
         <v>2467</v>
@@ -21162,7 +21162,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G717" t="n">
-        <v>5.03764867782593</v>
+        <v>5.03764915466309</v>
       </c>
       <c r="H717" t="n">
         <v>0</v>
@@ -21191,7 +21191,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G718" t="n">
-        <v>5.03764867782593</v>
+        <v>5.03764915466309</v>
       </c>
       <c r="H718" t="n">
         <v>0</v>
@@ -21220,7 +21220,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G719" t="n">
-        <v>5.03764867782593</v>
+        <v>5.03764915466309</v>
       </c>
       <c r="H719" t="n">
         <v>0</v>
@@ -21249,7 +21249,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G720" t="n">
-        <v>5.03764867782593</v>
+        <v>5.03764915466309</v>
       </c>
       <c r="H720" t="n">
         <v>1250</v>
@@ -21394,7 +21394,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G725" t="n">
-        <v>5.03764867782593</v>
+        <v>5.03764915466309</v>
       </c>
       <c r="H725" t="n">
         <v>6899</v>
@@ -54141,6 +54141,35 @@
         <v>350</v>
       </c>
       <c r="I1854" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1855">
+      <c r="A1855" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1855" s="1" t="n">
+        <v>46325.3333333333</v>
+      </c>
+      <c r="C1855" t="n">
+        <v>2.16000008583069</v>
+      </c>
+      <c r="D1855" t="n">
+        <v>2.20000004768372</v>
+      </c>
+      <c r="E1855" t="n">
+        <v>2.16000008583069</v>
+      </c>
+      <c r="F1855" t="n">
+        <v>2.20000004768372</v>
+      </c>
+      <c r="G1855" t="n">
+        <v>2.20000004768372</v>
+      </c>
+      <c r="H1855" t="n">
+        <v>2200</v>
+      </c>
+      <c r="I1855" t="s">
         <v>9</v>
       </c>
     </row>
